--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -298,7 +298,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,6 +322,18 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -481,7 +493,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,6 +503,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.05"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -807,137 +825,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -967,6 +985,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1452,7 +1479,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="28.375" style="1" customWidth="1"/>
@@ -1806,6 +1833,62 @@
         <v>16</v>
       </c>
       <c r="G18" s="9"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:7">
+      <c r="A19" s="10">
+        <v>6001</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10">
+        <v>1</v>
+      </c>
+      <c r="D19" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:7">
+      <c r="A20" s="11">
+        <v>6011</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11">
+        <v>1</v>
+      </c>
+      <c r="D20" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:7">
+      <c r="A21" s="12">
+        <v>6090</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12">
+        <v>1</v>
+      </c>
+      <c r="D21" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:7">
+      <c r="A22" s="12">
+        <v>6091</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12">
+        <v>1</v>
+      </c>
+      <c r="D22" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -120,8 +120,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-0.强制引导
-1.非强制引导</t>
+0.非强制引导
+1.强制引导</t>
         </r>
       </text>
     </comment>
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="40">
   <si>
     <t>序号</t>
   </si>
@@ -226,6 +226,15 @@
   </si>
   <si>
     <t>guideTest.mp3</t>
+  </si>
+  <si>
+    <t>初入游戏</t>
+  </si>
+  <si>
+    <t>试玩[超级明星]</t>
+  </si>
+  <si>
+    <t>引导主线任务</t>
   </si>
   <si>
     <t>_</t>
@@ -298,7 +307,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,13 +336,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0070C0"/>
+      <color rgb="FF00B0F0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -825,137 +865,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -968,6 +1008,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -977,22 +1029,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1479,34 +1555,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="6" width="28.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.8166666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1416666666667" style="1" customWidth="1"/>
     <col min="13" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="H1"/>
@@ -1516,7 +1597,7 @@
       <c r="L1"/>
     </row>
     <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1528,13 +1609,13 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="4"/>
+      <c r="G2" s="8"/>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2"/>
@@ -1542,25 +1623,25 @@
       <c r="L2"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="8"/>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3"/>
@@ -1568,327 +1649,896 @@
       <c r="L3"/>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="6"/>
+      <c r="A4" s="10"/>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
     </row>
-    <row r="5" customHeight="1" spans="1:12">
-      <c r="A5" s="7">
+    <row r="5" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A5" s="11">
         <v>1001</v>
       </c>
-      <c r="B5" s="8">
-        <v>1</v>
-      </c>
-      <c r="C5" s="8">
-        <v>1</v>
-      </c>
-      <c r="D5" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8">
+      <c r="B5" s="12">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12">
+        <v>1</v>
+      </c>
+      <c r="D5" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="12">
         <v>4055101</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:12">
-      <c r="A6" s="7">
+      <c r="G5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+    </row>
+    <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A6" s="11">
         <v>1002</v>
       </c>
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="B6" s="12">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12">
+        <v>1</v>
+      </c>
+      <c r="D6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12">
         <v>4055102</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:12">
-      <c r="A7" s="7">
+      <c r="G6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+    </row>
+    <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A7" s="11">
         <v>1003</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:12">
-      <c r="A8" s="7">
+      <c r="B7" s="12"/>
+      <c r="C7" s="12">
+        <v>1</v>
+      </c>
+      <c r="D7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+    </row>
+    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A8" s="11">
         <v>1004</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:12">
-      <c r="A9" s="7">
+      <c r="B8" s="12"/>
+      <c r="C8" s="12">
+        <v>1</v>
+      </c>
+      <c r="D8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+    </row>
+    <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A9" s="11">
         <v>1005</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="9"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:12">
-      <c r="A10" s="7">
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+    </row>
+    <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A10" s="11">
         <v>1006</v>
       </c>
-      <c r="B10" s="8">
-        <v>1</v>
-      </c>
-      <c r="C10" s="8">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="B10" s="12">
+        <v>1</v>
+      </c>
+      <c r="C10" s="12">
+        <v>1</v>
+      </c>
+      <c r="D10" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="12">
         <v>4055103</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:12">
-      <c r="A11" s="7">
+      <c r="G10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+    </row>
+    <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A11" s="11">
         <v>1007</v>
       </c>
-      <c r="B11" s="8">
-        <v>1</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="B11" s="12">
+        <v>1</v>
+      </c>
+      <c r="C11" s="12">
+        <v>1</v>
+      </c>
+      <c r="D11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12">
         <v>4055104</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="9"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:12">
-      <c r="A12" s="7">
+      <c r="G11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+    </row>
+    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A12" s="11">
         <v>1008</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8">
-        <v>1</v>
-      </c>
-      <c r="D12" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:12">
-      <c r="A13" s="7">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+    </row>
+    <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A13" s="11">
         <v>1009</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:12">
-      <c r="A14" s="7">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+    </row>
+    <row r="14" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A14" s="11">
         <v>1010</v>
       </c>
-      <c r="B14" s="8">
-        <v>1</v>
-      </c>
-      <c r="C14" s="8">
-        <v>1</v>
-      </c>
-      <c r="D14" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="B14" s="12">
+        <v>1</v>
+      </c>
+      <c r="C14" s="12">
+        <v>1</v>
+      </c>
+      <c r="D14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="12">
+        <v>4055105</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+    </row>
+    <row r="15" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A15" s="11">
+        <v>1011</v>
+      </c>
+      <c r="B15" s="12">
+        <v>1</v>
+      </c>
+      <c r="C15" s="12">
+        <v>1</v>
+      </c>
+      <c r="D15" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="12">
         <v>4055106</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F15" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="9"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:12">
-      <c r="A15" s="7">
-        <v>1011</v>
-      </c>
-      <c r="B15" s="8">
-        <v>1</v>
-      </c>
-      <c r="C15" s="8">
-        <v>1</v>
-      </c>
-      <c r="D15" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="8">
+      <c r="G15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+    </row>
+    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A16" s="11">
+        <v>1012</v>
+      </c>
+      <c r="B16" s="12">
+        <v>1</v>
+      </c>
+      <c r="C16" s="12">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="12">
         <v>4055107</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F16" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="9"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:12">
-      <c r="A16" s="7">
-        <v>1012</v>
-      </c>
-      <c r="B16" s="8">
-        <v>1</v>
-      </c>
-      <c r="C16" s="8">
-        <v>1</v>
-      </c>
-      <c r="D16" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="8">
+      <c r="G16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+    </row>
+    <row r="17" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A17" s="11">
+        <v>1013</v>
+      </c>
+      <c r="B17" s="12">
+        <v>1</v>
+      </c>
+      <c r="C17" s="12">
+        <v>1</v>
+      </c>
+      <c r="D17" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="12">
         <v>4055108</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F17" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:7">
-      <c r="A17" s="7">
-        <v>1013</v>
-      </c>
-      <c r="B17" s="8">
-        <v>1</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1</v>
-      </c>
-      <c r="D17" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8">
+      <c r="G17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+    </row>
+    <row r="18" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A18" s="11">
+        <v>1014</v>
+      </c>
+      <c r="B18" s="12">
+        <v>1</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1</v>
+      </c>
+      <c r="D18" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="12">
         <v>4055109</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F18" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="9"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:7">
-      <c r="A18" s="7">
-        <v>1014</v>
-      </c>
-      <c r="B18" s="8">
-        <v>1</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="8">
-        <v>4055110</v>
-      </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+    </row>
+    <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A19" s="14">
+        <v>1101</v>
+      </c>
+      <c r="B19" s="15">
+        <v>1</v>
+      </c>
+      <c r="C19" s="15">
+        <v>1</v>
+      </c>
+      <c r="D19" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15">
+        <v>4055121</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="9"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:7">
-      <c r="A19" s="10">
+      <c r="G19" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+    </row>
+    <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A20" s="14">
+        <v>1102</v>
+      </c>
+      <c r="B20" s="15">
+        <v>1</v>
+      </c>
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>4055122</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+    </row>
+    <row r="21" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A21" s="14">
+        <v>1103</v>
+      </c>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15">
+        <v>2</v>
+      </c>
+      <c r="D21" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+    </row>
+    <row r="22" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A22" s="14">
+        <v>1104</v>
+      </c>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+    </row>
+    <row r="23" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A23" s="14">
+        <v>1105</v>
+      </c>
+      <c r="B23" s="15">
+        <v>2</v>
+      </c>
+      <c r="C23" s="15">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>4055123</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+    </row>
+    <row r="24" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A24" s="14">
+        <v>1106</v>
+      </c>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15">
+        <v>1</v>
+      </c>
+      <c r="D24" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+    </row>
+    <row r="25" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="14">
+        <v>1107</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15">
+        <v>1</v>
+      </c>
+      <c r="D25" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+    </row>
+    <row r="26" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A26" s="14">
+        <v>1108</v>
+      </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+    </row>
+    <row r="27" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A27" s="14">
+        <v>1109</v>
+      </c>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+    </row>
+    <row r="28" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A28" s="14">
+        <v>1110</v>
+      </c>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+    </row>
+    <row r="29" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A29" s="14">
+        <v>1111</v>
+      </c>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15">
+        <v>1</v>
+      </c>
+      <c r="D29" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+    </row>
+    <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A30" s="18">
+        <v>1121</v>
+      </c>
+      <c r="B30" s="19">
+        <v>1</v>
+      </c>
+      <c r="C30" s="19">
+        <v>1</v>
+      </c>
+      <c r="D30" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="19">
+        <v>4055131</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+    </row>
+    <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A31" s="18">
+        <v>1122</v>
+      </c>
+      <c r="B31" s="19">
+        <v>1</v>
+      </c>
+      <c r="C31" s="19">
+        <v>1</v>
+      </c>
+      <c r="D31" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="19">
+        <v>4055132</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+    </row>
+    <row r="32" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A32" s="18">
+        <v>1123</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19">
+        <v>1</v>
+      </c>
+      <c r="D32" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+    </row>
+    <row r="33" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A33" s="18">
+        <v>1124</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19">
+        <v>1</v>
+      </c>
+      <c r="D33" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+    </row>
+    <row r="34" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A34" s="18">
+        <v>1125</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19">
+        <v>1</v>
+      </c>
+      <c r="D34" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+    </row>
+    <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A35" s="18">
+        <v>1126</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19">
+        <v>1</v>
+      </c>
+      <c r="D35" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+    </row>
+    <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A36" s="18">
+        <v>1127</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19">
+        <v>1</v>
+      </c>
+      <c r="D36" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+    </row>
+    <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A37" s="18">
+        <v>1128</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19">
+        <v>1</v>
+      </c>
+      <c r="D37" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+    </row>
+    <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A38" s="18">
+        <v>1129</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19">
+        <v>1</v>
+      </c>
+      <c r="D38" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:12">
+      <c r="A39" s="22">
         <v>6001</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10">
-        <v>1</v>
-      </c>
-      <c r="D19" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:7">
-      <c r="A20" s="11">
+      <c r="B39" s="22"/>
+      <c r="C39" s="22">
+        <v>1</v>
+      </c>
+      <c r="D39" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:12">
+      <c r="A40" s="23">
         <v>6011</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11">
-        <v>1</v>
-      </c>
-      <c r="D20" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:7">
-      <c r="A21" s="12">
+      <c r="B40" s="23"/>
+      <c r="C40" s="23">
+        <v>1</v>
+      </c>
+      <c r="D40" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:12">
+      <c r="A41" s="24">
         <v>6090</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12">
-        <v>1</v>
-      </c>
-      <c r="D21" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:7">
-      <c r="A22" s="12">
+      <c r="B41" s="24"/>
+      <c r="C41" s="24">
+        <v>1</v>
+      </c>
+      <c r="D41" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:12">
+      <c r="A42" s="24">
         <v>6091</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12">
-        <v>1</v>
-      </c>
-      <c r="D22" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24">
+        <v>1</v>
+      </c>
+      <c r="D42" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1948,14 +2598,14 @@
         <v>1001</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>1001_</v>
       </c>
       <c r="M5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -1964,7 +2614,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1974,14 +2624,14 @@
         <v>1002</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K18" si="0">I6&amp;J6</f>
         <v>1002_</v>
       </c>
       <c r="M6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1989,14 +2639,14 @@
         <v>1003</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>1003_</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2004,14 +2654,14 @@
         <v>1004</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>1004_</v>
       </c>
       <c r="M8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2019,14 +2669,14 @@
         <v>1005</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="0"/>
         <v>1005_</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2034,14 +2684,14 @@
         <v>1006</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="0"/>
         <v>1006_</v>
       </c>
       <c r="M10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2049,14 +2699,14 @@
         <v>1007</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="0"/>
         <v>1007_</v>
       </c>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2064,14 +2714,14 @@
         <v>1008</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="0"/>
         <v>1008_</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2079,32 +2729,32 @@
         <v>1009</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="0"/>
         <v>1009_</v>
       </c>
       <c r="M13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I14">
         <v>1010</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="0"/>
         <v>1010_</v>
       </c>
       <c r="M14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -2112,14 +2762,14 @@
         <v>1011</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="0"/>
         <v>1011_</v>
       </c>
       <c r="M15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2127,14 +2777,14 @@
         <v>1012</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="0"/>
         <v>1012_</v>
       </c>
       <c r="M16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -2142,14 +2792,14 @@
         <v>1013</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="0"/>
         <v>1013_</v>
       </c>
       <c r="M17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -2157,29 +2807,29 @@
         <v>1014</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="0"/>
         <v>1014_</v>
       </c>
       <c r="M18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="41">
   <si>
     <t>序号</t>
   </si>
@@ -234,7 +234,10 @@
     <t>试玩[超级明星]</t>
   </si>
   <si>
-    <t>引导主线任务</t>
+    <t>主线任务</t>
+  </si>
+  <si>
+    <t>SLOT升级词条</t>
   </si>
   <si>
     <t>_</t>
@@ -307,7 +310,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,12 +350,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -360,13 +357,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -865,137 +855,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1017,7 +1007,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1035,7 +1025,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1047,25 +1037,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1555,7 +1536,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -2275,270 +2256,746 @@
       <c r="L29" s="17"/>
     </row>
     <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="18">
+      <c r="A30" s="11">
         <v>1121</v>
       </c>
-      <c r="B30" s="19">
-        <v>1</v>
-      </c>
-      <c r="C30" s="19">
-        <v>1</v>
-      </c>
-      <c r="D30" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="19">
+      <c r="B30" s="12">
+        <v>1</v>
+      </c>
+      <c r="C30" s="12">
+        <v>1</v>
+      </c>
+      <c r="D30" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="12">
         <v>4055131</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="F30" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="G30" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
     </row>
     <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="18">
+      <c r="A31" s="11">
         <v>1122</v>
       </c>
-      <c r="B31" s="19">
-        <v>1</v>
-      </c>
-      <c r="C31" s="19">
-        <v>1</v>
-      </c>
-      <c r="D31" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="19">
+      <c r="B31" s="12">
+        <v>1</v>
+      </c>
+      <c r="C31" s="12">
+        <v>1</v>
+      </c>
+      <c r="D31" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="12">
         <v>4055132</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="20" t="s">
+      <c r="G31" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
     </row>
     <row r="32" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="18">
+      <c r="A32" s="11">
         <v>1123</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19">
-        <v>1</v>
-      </c>
-      <c r="D32" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="20" t="s">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12">
+        <v>1</v>
+      </c>
+      <c r="D32" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
     </row>
     <row r="33" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="18">
+      <c r="A33" s="11">
         <v>1124</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19">
-        <v>1</v>
-      </c>
-      <c r="D33" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="20" t="s">
+      <c r="B33" s="12"/>
+      <c r="C33" s="12">
+        <v>1</v>
+      </c>
+      <c r="D33" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
     </row>
     <row r="34" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="18">
+      <c r="A34" s="11">
         <v>1125</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19">
-        <v>1</v>
-      </c>
-      <c r="D34" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="20" t="s">
+      <c r="B34" s="12"/>
+      <c r="C34" s="12">
+        <v>1</v>
+      </c>
+      <c r="D34" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
     </row>
     <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="18">
+      <c r="A35" s="11">
         <v>1126</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19">
-        <v>1</v>
-      </c>
-      <c r="D35" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="20" t="s">
+      <c r="B35" s="12"/>
+      <c r="C35" s="12">
+        <v>1</v>
+      </c>
+      <c r="D35" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
     </row>
     <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="18">
+      <c r="A36" s="11">
         <v>1127</v>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19">
-        <v>1</v>
-      </c>
-      <c r="D36" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="20" t="s">
+      <c r="B36" s="12"/>
+      <c r="C36" s="12">
+        <v>1</v>
+      </c>
+      <c r="D36" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
     </row>
     <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="18">
+      <c r="A37" s="11">
         <v>1128</v>
       </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19">
-        <v>1</v>
-      </c>
-      <c r="D37" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="20" t="s">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12">
+        <v>1</v>
+      </c>
+      <c r="D37" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
     </row>
     <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="18">
+      <c r="A38" s="11">
         <v>1129</v>
       </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19">
-        <v>1</v>
-      </c>
-      <c r="D38" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="20" t="s">
+      <c r="B38" s="12"/>
+      <c r="C38" s="12">
+        <v>1</v>
+      </c>
+      <c r="D38" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:12">
-      <c r="A39" s="22">
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A39" s="14">
+        <v>1141</v>
+      </c>
+      <c r="B39" s="15">
+        <v>1</v>
+      </c>
+      <c r="C39" s="15">
+        <v>1</v>
+      </c>
+      <c r="D39" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="15">
+        <v>4055141</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+    </row>
+    <row r="40" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A40" s="14">
+        <v>1142</v>
+      </c>
+      <c r="B40" s="15">
+        <v>1</v>
+      </c>
+      <c r="C40" s="15">
+        <v>1</v>
+      </c>
+      <c r="D40" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="15">
+        <v>4055142</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+    </row>
+    <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A41" s="14">
+        <v>1143</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15">
+        <v>1</v>
+      </c>
+      <c r="D41" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+    </row>
+    <row r="42" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A42" s="14">
+        <v>1144</v>
+      </c>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15">
+        <v>1</v>
+      </c>
+      <c r="D42" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+    </row>
+    <row r="43" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A43" s="14">
+        <v>1145</v>
+      </c>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15">
+        <v>1</v>
+      </c>
+      <c r="D43" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+    </row>
+    <row r="44" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A44" s="14">
+        <v>1146</v>
+      </c>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15">
+        <v>1</v>
+      </c>
+      <c r="D44" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+    </row>
+    <row r="45" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A45" s="14">
+        <v>1147</v>
+      </c>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15">
+        <v>1</v>
+      </c>
+      <c r="D45" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+    </row>
+    <row r="46" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A46" s="14">
+        <v>1148</v>
+      </c>
+      <c r="B46" s="15">
+        <v>1</v>
+      </c>
+      <c r="C46" s="15">
+        <v>1</v>
+      </c>
+      <c r="D46" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="15">
+        <v>4055143</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+    </row>
+    <row r="47" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A47" s="14">
+        <v>1149</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15">
+        <v>1</v>
+      </c>
+      <c r="D47" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+    </row>
+    <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="14">
+        <v>1150</v>
+      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15">
+        <v>1</v>
+      </c>
+      <c r="D48" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+    </row>
+    <row r="49" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A49" s="14">
+        <v>1151</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15">
+        <v>1</v>
+      </c>
+      <c r="D49" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+    </row>
+    <row r="50" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A50" s="14">
+        <v>1152</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15">
+        <v>1</v>
+      </c>
+      <c r="D50" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+    </row>
+    <row r="51" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A51" s="14">
+        <v>1153</v>
+      </c>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15">
+        <v>1</v>
+      </c>
+      <c r="D51" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+    </row>
+    <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A52" s="14">
+        <v>1154</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15">
+        <v>1</v>
+      </c>
+      <c r="D52" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+    </row>
+    <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A53" s="14">
+        <v>1155</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15">
+        <v>1</v>
+      </c>
+      <c r="D53" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+    </row>
+    <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A54" s="14">
+        <v>1156</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15">
+        <v>1</v>
+      </c>
+      <c r="D54" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+    </row>
+    <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A55" s="14">
+        <v>1157</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15">
+        <v>1</v>
+      </c>
+      <c r="D55" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+    </row>
+    <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A56" s="14">
+        <v>1158</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15">
+        <v>1</v>
+      </c>
+      <c r="D56" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+    </row>
+    <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A57" s="14">
+        <v>1159</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15">
+        <v>1</v>
+      </c>
+      <c r="D57" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
+    </row>
+    <row r="58" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A58" s="14">
+        <v>1160</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15">
+        <v>1</v>
+      </c>
+      <c r="D58" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+    </row>
+    <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A59" s="14">
+        <v>1161</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:12">
+      <c r="A60" s="19">
         <v>6001</v>
       </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22">
-        <v>1</v>
-      </c>
-      <c r="D39" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:12">
-      <c r="A40" s="23">
+      <c r="B60" s="19"/>
+      <c r="C60" s="19">
+        <v>1</v>
+      </c>
+      <c r="D60" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:12">
+      <c r="A61" s="20">
         <v>6011</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23">
-        <v>1</v>
-      </c>
-      <c r="D40" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:12">
-      <c r="A41" s="24">
+      <c r="B61" s="20"/>
+      <c r="C61" s="20">
+        <v>1</v>
+      </c>
+      <c r="D61" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+    </row>
+    <row r="62" customHeight="1" spans="1:12">
+      <c r="A62" s="21">
         <v>6090</v>
       </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24">
-        <v>1</v>
-      </c>
-      <c r="D41" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:12">
-      <c r="A42" s="24">
+      <c r="B62" s="21"/>
+      <c r="C62" s="21">
+        <v>1</v>
+      </c>
+      <c r="D62" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:12">
+      <c r="A63" s="21">
         <v>6091</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24">
-        <v>1</v>
-      </c>
-      <c r="D42" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="21">
+        <v>1</v>
+      </c>
+      <c r="D63" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2598,14 +3055,14 @@
         <v>1001</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>1001_</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -2614,7 +3071,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -2624,14 +3081,14 @@
         <v>1002</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K18" si="0">I6&amp;J6</f>
         <v>1002_</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2639,14 +3096,14 @@
         <v>1003</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>1003_</v>
       </c>
       <c r="M7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2654,14 +3111,14 @@
         <v>1004</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>1004_</v>
       </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2669,14 +3126,14 @@
         <v>1005</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="0"/>
         <v>1005_</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2684,14 +3141,14 @@
         <v>1006</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="0"/>
         <v>1006_</v>
       </c>
       <c r="M10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2699,14 +3156,14 @@
         <v>1007</v>
       </c>
       <c r="J11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="0"/>
         <v>1007_</v>
       </c>
       <c r="M11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2714,14 +3171,14 @@
         <v>1008</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="0"/>
         <v>1008_</v>
       </c>
       <c r="M12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2729,32 +3186,32 @@
         <v>1009</v>
       </c>
       <c r="J13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="0"/>
         <v>1009_</v>
       </c>
       <c r="M13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14">
         <v>1010</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="0"/>
         <v>1010_</v>
       </c>
       <c r="M14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -2762,14 +3219,14 @@
         <v>1011</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="0"/>
         <v>1011_</v>
       </c>
       <c r="M15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2777,14 +3234,14 @@
         <v>1012</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="0"/>
         <v>1012_</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -2792,14 +3249,14 @@
         <v>1013</v>
       </c>
       <c r="J17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="0"/>
         <v>1013_</v>
       </c>
       <c r="M17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -2807,29 +3264,29 @@
         <v>1014</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="0"/>
         <v>1014_</v>
       </c>
       <c r="M18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="44">
   <si>
     <t>序号</t>
   </si>
@@ -228,16 +228,25 @@
     <t>guideTest.mp3</t>
   </si>
   <si>
-    <t>初入游戏</t>
-  </si>
-  <si>
-    <t>试玩[超级明星]</t>
-  </si>
-  <si>
-    <t>主线任务</t>
-  </si>
-  <si>
-    <t>SLOT升级词条</t>
+    <t>初入游戏-创建新号到经营大厅</t>
+  </si>
+  <si>
+    <t>试玩[超级明星]-默认解锁</t>
+  </si>
+  <si>
+    <t>主线任务第1次引导</t>
+  </si>
+  <si>
+    <t>研究院-SLOT升级词条-超级明星-解锁投注底数</t>
+  </si>
+  <si>
+    <t>主线任务第2次引导</t>
+  </si>
+  <si>
+    <t>研究院升级-解锁第2个游戏【麻将胡了】</t>
+  </si>
+  <si>
+    <t>解锁捕鱼机台建筑-1110</t>
   </si>
   <si>
     <t>_</t>
@@ -1536,7 +1545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -1545,7 +1554,7 @@
     <col min="4" max="4" width="15.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1416666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="56.9083333333333" style="1" customWidth="1"/>
     <col min="13" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
@@ -1997,7 +2006,7 @@
     </row>
     <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A19" s="14">
-        <v>1101</v>
+        <v>1201</v>
       </c>
       <c r="B19" s="15">
         <v>1</v>
@@ -2025,7 +2034,7 @@
     </row>
     <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A20" s="14">
-        <v>1102</v>
+        <v>1202</v>
       </c>
       <c r="B20" s="15">
         <v>1</v>
@@ -2053,7 +2062,7 @@
     </row>
     <row r="21" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A21" s="14">
-        <v>1103</v>
+        <v>1203</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15">
@@ -2075,7 +2084,7 @@
     </row>
     <row r="22" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A22" s="14">
-        <v>1104</v>
+        <v>1204</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15">
@@ -2097,7 +2106,7 @@
     </row>
     <row r="23" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A23" s="14">
-        <v>1105</v>
+        <v>1205</v>
       </c>
       <c r="B23" s="15">
         <v>2</v>
@@ -2125,7 +2134,7 @@
     </row>
     <row r="24" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A24" s="14">
-        <v>1106</v>
+        <v>1206</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15">
@@ -2147,7 +2156,7 @@
     </row>
     <row r="25" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A25" s="14">
-        <v>1107</v>
+        <v>1207</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15">
@@ -2169,7 +2178,7 @@
     </row>
     <row r="26" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A26" s="14">
-        <v>1108</v>
+        <v>1208</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15">
@@ -2191,7 +2200,7 @@
     </row>
     <row r="27" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A27" s="14">
-        <v>1109</v>
+        <v>1209</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15">
@@ -2213,7 +2222,7 @@
     </row>
     <row r="28" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A28" s="14">
-        <v>1110</v>
+        <v>1210</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15">
@@ -2235,7 +2244,7 @@
     </row>
     <row r="29" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A29" s="14">
-        <v>1111</v>
+        <v>1211</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15">
@@ -2257,7 +2266,7 @@
     </row>
     <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A30" s="11">
-        <v>1121</v>
+        <v>1301</v>
       </c>
       <c r="B30" s="12">
         <v>1</v>
@@ -2285,7 +2294,7 @@
     </row>
     <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A31" s="11">
-        <v>1122</v>
+        <v>1302</v>
       </c>
       <c r="B31" s="12">
         <v>1</v>
@@ -2313,7 +2322,7 @@
     </row>
     <row r="32" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A32" s="11">
-        <v>1123</v>
+        <v>1303</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12">
@@ -2335,7 +2344,7 @@
     </row>
     <row r="33" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A33" s="11">
-        <v>1124</v>
+        <v>1304</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12">
@@ -2357,7 +2366,7 @@
     </row>
     <row r="34" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A34" s="11">
-        <v>1125</v>
+        <v>1305</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12">
@@ -2379,7 +2388,7 @@
     </row>
     <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A35" s="11">
-        <v>1126</v>
+        <v>1306</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12">
@@ -2401,7 +2410,7 @@
     </row>
     <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A36" s="11">
-        <v>1127</v>
+        <v>1307</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12">
@@ -2423,7 +2432,7 @@
     </row>
     <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A37" s="11">
-        <v>1128</v>
+        <v>1308</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="12">
@@ -2445,7 +2454,7 @@
     </row>
     <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A38" s="11">
-        <v>1129</v>
+        <v>1309</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12">
@@ -2467,7 +2476,7 @@
     </row>
     <row r="39" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A39" s="14">
-        <v>1141</v>
+        <v>1401</v>
       </c>
       <c r="B39" s="15">
         <v>1</v>
@@ -2495,7 +2504,7 @@
     </row>
     <row r="40" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A40" s="14">
-        <v>1142</v>
+        <v>1402</v>
       </c>
       <c r="B40" s="15">
         <v>1</v>
@@ -2523,7 +2532,7 @@
     </row>
     <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A41" s="14">
-        <v>1143</v>
+        <v>1403</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15">
@@ -2545,7 +2554,7 @@
     </row>
     <row r="42" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A42" s="14">
-        <v>1144</v>
+        <v>1404</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15">
@@ -2567,7 +2576,7 @@
     </row>
     <row r="43" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A43" s="14">
-        <v>1145</v>
+        <v>1405</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15">
@@ -2589,7 +2598,7 @@
     </row>
     <row r="44" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A44" s="14">
-        <v>1146</v>
+        <v>1406</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15">
@@ -2611,7 +2620,7 @@
     </row>
     <row r="45" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A45" s="14">
-        <v>1147</v>
+        <v>1407</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15">
@@ -2633,7 +2642,7 @@
     </row>
     <row r="46" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A46" s="14">
-        <v>1148</v>
+        <v>1408</v>
       </c>
       <c r="B46" s="15">
         <v>1</v>
@@ -2661,7 +2670,7 @@
     </row>
     <row r="47" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A47" s="14">
-        <v>1149</v>
+        <v>1409</v>
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="15">
@@ -2683,7 +2692,7 @@
     </row>
     <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A48" s="14">
-        <v>1150</v>
+        <v>1410</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15">
@@ -2705,7 +2714,7 @@
     </row>
     <row r="49" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A49" s="14">
-        <v>1151</v>
+        <v>1411</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15">
@@ -2727,7 +2736,7 @@
     </row>
     <row r="50" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A50" s="14">
-        <v>1152</v>
+        <v>1412</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15">
@@ -2749,7 +2758,7 @@
     </row>
     <row r="51" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A51" s="14">
-        <v>1153</v>
+        <v>1413</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="15">
@@ -2771,7 +2780,7 @@
     </row>
     <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A52" s="14">
-        <v>1154</v>
+        <v>1414</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15">
@@ -2793,7 +2802,7 @@
     </row>
     <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A53" s="14">
-        <v>1155</v>
+        <v>1415</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="15">
@@ -2815,7 +2824,7 @@
     </row>
     <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A54" s="14">
-        <v>1156</v>
+        <v>1416</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15">
@@ -2837,7 +2846,7 @@
     </row>
     <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A55" s="14">
-        <v>1157</v>
+        <v>1417</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15">
@@ -2859,7 +2868,7 @@
     </row>
     <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A56" s="14">
-        <v>1158</v>
+        <v>1418</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15">
@@ -2881,7 +2890,7 @@
     </row>
     <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A57" s="14">
-        <v>1159</v>
+        <v>1419</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15">
@@ -2903,7 +2912,7 @@
     </row>
     <row r="58" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A58" s="14">
-        <v>1160</v>
+        <v>1420</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15">
@@ -2925,7 +2934,7 @@
     </row>
     <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A59" s="14">
-        <v>1161</v>
+        <v>1421</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -2941,61 +2950,773 @@
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
     </row>
-    <row r="60" customHeight="1" spans="1:12">
-      <c r="A60" s="19">
+    <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A60" s="11">
+        <v>1501</v>
+      </c>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12">
+        <v>1</v>
+      </c>
+      <c r="D60" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+    </row>
+    <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A61" s="11">
+        <v>1502</v>
+      </c>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12">
+        <v>1</v>
+      </c>
+      <c r="D61" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+    </row>
+    <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A62" s="11">
+        <v>1503</v>
+      </c>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12">
+        <v>1</v>
+      </c>
+      <c r="D62" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+    </row>
+    <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A63" s="11">
+        <v>1504</v>
+      </c>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12">
+        <v>1</v>
+      </c>
+      <c r="D63" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="13"/>
+    </row>
+    <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A64" s="11">
+        <v>1505</v>
+      </c>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12">
+        <v>1</v>
+      </c>
+      <c r="D64" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="13"/>
+      <c r="L64" s="13"/>
+    </row>
+    <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A65" s="11">
+        <v>1506</v>
+      </c>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12">
+        <v>1</v>
+      </c>
+      <c r="D65" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
+      <c r="L65" s="13"/>
+    </row>
+    <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A66" s="11">
+        <v>1507</v>
+      </c>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12">
+        <v>1</v>
+      </c>
+      <c r="D66" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+    </row>
+    <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A67" s="14">
+        <v>1601</v>
+      </c>
+      <c r="B67" s="15">
+        <v>1</v>
+      </c>
+      <c r="C67" s="15">
+        <v>1</v>
+      </c>
+      <c r="D67" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="15">
+        <v>4055151</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+    </row>
+    <row r="68" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A68" s="14">
+        <v>1602</v>
+      </c>
+      <c r="B68" s="15">
+        <v>1</v>
+      </c>
+      <c r="C68" s="15">
+        <v>1</v>
+      </c>
+      <c r="D68" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" s="15">
+        <v>4055152</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
+      <c r="L68" s="17"/>
+    </row>
+    <row r="69" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A69" s="14">
+        <v>1603</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="15">
+        <v>1</v>
+      </c>
+      <c r="D69" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="15"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="17"/>
+      <c r="K69" s="17"/>
+      <c r="L69" s="17"/>
+    </row>
+    <row r="70" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A70" s="14">
+        <v>1604</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15">
+        <v>1</v>
+      </c>
+      <c r="D70" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="17"/>
+      <c r="K70" s="17"/>
+      <c r="L70" s="17"/>
+    </row>
+    <row r="71" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A71" s="14">
+        <v>1605</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15">
+        <v>1</v>
+      </c>
+      <c r="D71" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="15"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+      <c r="L71" s="17"/>
+    </row>
+    <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A72" s="14">
+        <v>1606</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="15">
+        <v>1</v>
+      </c>
+      <c r="D72" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="15"/>
+      <c r="F72" s="15"/>
+      <c r="G72" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="17"/>
+      <c r="K72" s="17"/>
+      <c r="L72" s="17"/>
+    </row>
+    <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A73" s="14">
+        <v>1607</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="15">
+        <v>1</v>
+      </c>
+      <c r="D73" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="15"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="17"/>
+      <c r="I73" s="17"/>
+      <c r="J73" s="17"/>
+      <c r="K73" s="17"/>
+      <c r="L73" s="17"/>
+    </row>
+    <row r="74" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A74" s="14">
+        <v>1608</v>
+      </c>
+      <c r="B74" s="15">
+        <v>1</v>
+      </c>
+      <c r="C74" s="15">
+        <v>1</v>
+      </c>
+      <c r="D74" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="15">
+        <v>4055153</v>
+      </c>
+      <c r="F74" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" s="17"/>
+      <c r="I74" s="17"/>
+      <c r="J74" s="17"/>
+      <c r="K74" s="17"/>
+      <c r="L74" s="17"/>
+    </row>
+    <row r="75" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A75" s="14">
+        <v>1609</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="15">
+        <v>1</v>
+      </c>
+      <c r="D75" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75" s="17"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
+      <c r="L75" s="17"/>
+    </row>
+    <row r="76" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A76" s="14">
+        <v>1610</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="15">
+        <v>1</v>
+      </c>
+      <c r="D76" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" s="15"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H76" s="17"/>
+      <c r="I76" s="17"/>
+      <c r="J76" s="17"/>
+      <c r="K76" s="17"/>
+      <c r="L76" s="17"/>
+    </row>
+    <row r="77" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A77" s="14">
+        <v>1611</v>
+      </c>
+      <c r="B77" s="15"/>
+      <c r="C77" s="15">
+        <v>1</v>
+      </c>
+      <c r="D77" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
+      <c r="K77" s="17"/>
+      <c r="L77" s="17"/>
+    </row>
+    <row r="78" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A78" s="14">
+        <v>1612</v>
+      </c>
+      <c r="B78" s="15"/>
+      <c r="C78" s="15">
+        <v>1</v>
+      </c>
+      <c r="D78" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" s="17"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="17"/>
+      <c r="K78" s="17"/>
+      <c r="L78" s="17"/>
+    </row>
+    <row r="79" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A79" s="14">
+        <v>1613</v>
+      </c>
+      <c r="B79" s="15"/>
+      <c r="C79" s="15">
+        <v>1</v>
+      </c>
+      <c r="D79" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="17"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="17"/>
+      <c r="K79" s="17"/>
+      <c r="L79" s="17"/>
+    </row>
+    <row r="80" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="14">
+        <v>1614</v>
+      </c>
+      <c r="B80" s="15"/>
+      <c r="C80" s="15">
+        <v>1</v>
+      </c>
+      <c r="D80" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="17"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="17"/>
+      <c r="K80" s="17"/>
+      <c r="L80" s="17"/>
+    </row>
+    <row r="81" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A81" s="14">
+        <v>1615</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="15">
+        <v>1</v>
+      </c>
+      <c r="D81" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" s="15"/>
+      <c r="F81" s="15"/>
+      <c r="G81" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="17"/>
+      <c r="K81" s="17"/>
+      <c r="L81" s="17"/>
+    </row>
+    <row r="82" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A82" s="11">
+        <v>1701</v>
+      </c>
+      <c r="B82" s="12">
+        <v>1</v>
+      </c>
+      <c r="C82" s="12">
+        <v>1</v>
+      </c>
+      <c r="D82" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="12">
+        <v>4055171</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G82" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="13"/>
+      <c r="K82" s="13"/>
+      <c r="L82" s="13"/>
+    </row>
+    <row r="83" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A83" s="11">
+        <v>1702</v>
+      </c>
+      <c r="B83" s="12">
+        <v>1</v>
+      </c>
+      <c r="C83" s="12">
+        <v>1</v>
+      </c>
+      <c r="D83" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="12">
+        <v>4055172</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" s="13"/>
+      <c r="I83" s="13"/>
+      <c r="J83" s="13"/>
+      <c r="K83" s="13"/>
+      <c r="L83" s="13"/>
+    </row>
+    <row r="84" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A84" s="11">
+        <v>1703</v>
+      </c>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12">
+        <v>1</v>
+      </c>
+      <c r="D84" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="13"/>
+      <c r="K84" s="13"/>
+      <c r="L84" s="13"/>
+    </row>
+    <row r="85" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A85" s="11">
+        <v>1704</v>
+      </c>
+      <c r="B85" s="12"/>
+      <c r="C85" s="12">
+        <v>1</v>
+      </c>
+      <c r="D85" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" s="13"/>
+      <c r="I85" s="13"/>
+      <c r="J85" s="13"/>
+      <c r="K85" s="13"/>
+      <c r="L85" s="13"/>
+    </row>
+    <row r="86" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A86" s="11">
+        <v>1705</v>
+      </c>
+      <c r="B86" s="12"/>
+      <c r="C86" s="12">
+        <v>1</v>
+      </c>
+      <c r="D86" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
+      <c r="J86" s="13"/>
+      <c r="K86" s="13"/>
+      <c r="L86" s="13"/>
+    </row>
+    <row r="87" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A87" s="11">
+        <v>1706</v>
+      </c>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12">
+        <v>1</v>
+      </c>
+      <c r="D87" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" s="13"/>
+      <c r="I87" s="13"/>
+      <c r="J87" s="13"/>
+      <c r="K87" s="13"/>
+      <c r="L87" s="13"/>
+    </row>
+    <row r="88" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A88" s="11">
+        <v>1707</v>
+      </c>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12">
+        <v>1</v>
+      </c>
+      <c r="D88" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" s="13"/>
+      <c r="I88" s="13"/>
+      <c r="J88" s="13"/>
+      <c r="K88" s="13"/>
+      <c r="L88" s="13"/>
+    </row>
+    <row r="89" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A89" s="11">
+        <v>1708</v>
+      </c>
+      <c r="B89" s="12"/>
+      <c r="C89" s="12">
+        <v>1</v>
+      </c>
+      <c r="D89" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="12"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
+      <c r="J89" s="13"/>
+      <c r="K89" s="13"/>
+      <c r="L89" s="13"/>
+    </row>
+    <row r="90" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A90" s="11">
+        <v>1709</v>
+      </c>
+      <c r="B90" s="12"/>
+      <c r="C90" s="12">
+        <v>1</v>
+      </c>
+      <c r="D90" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="13"/>
+      <c r="K90" s="13"/>
+      <c r="L90" s="13"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:12">
+      <c r="A91" s="19">
         <v>6001</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19">
-        <v>1</v>
-      </c>
-      <c r="D60" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-    </row>
-    <row r="61" customHeight="1" spans="1:12">
-      <c r="A61" s="20">
+      <c r="B91" s="19"/>
+      <c r="C91" s="19">
+        <v>1</v>
+      </c>
+      <c r="D91" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="19"/>
+      <c r="F91" s="19"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:12">
+      <c r="A92" s="20">
         <v>6011</v>
       </c>
-      <c r="B61" s="20"/>
-      <c r="C61" s="20">
-        <v>1</v>
-      </c>
-      <c r="D61" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-    </row>
-    <row r="62" customHeight="1" spans="1:12">
-      <c r="A62" s="21">
+      <c r="B92" s="20"/>
+      <c r="C92" s="20">
+        <v>1</v>
+      </c>
+      <c r="D92" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
+    </row>
+    <row r="93" customHeight="1" spans="1:12">
+      <c r="A93" s="21">
         <v>6090</v>
       </c>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21">
-        <v>1</v>
-      </c>
-      <c r="D62" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-    </row>
-    <row r="63" customHeight="1" spans="1:12">
-      <c r="A63" s="21">
+      <c r="B93" s="21"/>
+      <c r="C93" s="21">
+        <v>1</v>
+      </c>
+      <c r="D93" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="21"/>
+      <c r="F93" s="21"/>
+    </row>
+    <row r="94" customHeight="1" spans="1:12">
+      <c r="A94" s="21">
         <v>6091</v>
       </c>
-      <c r="B63" s="21"/>
-      <c r="C63" s="21">
-        <v>1</v>
-      </c>
-      <c r="D63" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
+      <c r="B94" s="21"/>
+      <c r="C94" s="21">
+        <v>1</v>
+      </c>
+      <c r="D94" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="21"/>
+      <c r="F94" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3055,14 +3776,14 @@
         <v>1001</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>1001_</v>
       </c>
       <c r="M5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -3071,7 +3792,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3081,14 +3802,14 @@
         <v>1002</v>
       </c>
       <c r="J6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K18" si="0">I6&amp;J6</f>
         <v>1002_</v>
       </c>
       <c r="M6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3096,14 +3817,14 @@
         <v>1003</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>1003_</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3111,14 +3832,14 @@
         <v>1004</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>1004_</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -3126,14 +3847,14 @@
         <v>1005</v>
       </c>
       <c r="J9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="0"/>
         <v>1005_</v>
       </c>
       <c r="M9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -3141,14 +3862,14 @@
         <v>1006</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="0"/>
         <v>1006_</v>
       </c>
       <c r="M10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -3156,14 +3877,14 @@
         <v>1007</v>
       </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="0"/>
         <v>1007_</v>
       </c>
       <c r="M11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3171,14 +3892,14 @@
         <v>1008</v>
       </c>
       <c r="J12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="0"/>
         <v>1008_</v>
       </c>
       <c r="M12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -3186,32 +3907,32 @@
         <v>1009</v>
       </c>
       <c r="J13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="0"/>
         <v>1009_</v>
       </c>
       <c r="M13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I14">
         <v>1010</v>
       </c>
       <c r="J14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="0"/>
         <v>1010_</v>
       </c>
       <c r="M14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -3219,14 +3940,14 @@
         <v>1011</v>
       </c>
       <c r="J15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="0"/>
         <v>1011_</v>
       </c>
       <c r="M15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -3234,14 +3955,14 @@
         <v>1012</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="0"/>
         <v>1012_</v>
       </c>
       <c r="M16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3249,14 +3970,14 @@
         <v>1013</v>
       </c>
       <c r="J17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="0"/>
         <v>1013_</v>
       </c>
       <c r="M17" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -3264,29 +3985,29 @@
         <v>1014</v>
       </c>
       <c r="J18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="0"/>
         <v>1014_</v>
       </c>
       <c r="M18" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="51">
   <si>
     <t>序号</t>
   </si>
@@ -247,6 +247,27 @@
   </si>
   <si>
     <t>解锁捕鱼机台建筑-1110</t>
+  </si>
+  <si>
+    <t>解锁游客&amp;游客升星</t>
+  </si>
+  <si>
+    <t>主线任务第3次引导</t>
+  </si>
+  <si>
+    <t>解锁雇员&amp;雇员升级</t>
+  </si>
+  <si>
+    <t>FASLE</t>
+  </si>
+  <si>
+    <t>解锁联盟&amp;加入联盟</t>
+  </si>
+  <si>
+    <t>获得道具-主线任务界面</t>
+  </si>
+  <si>
+    <t>获得道具-联盟任务界面</t>
   </si>
   <si>
     <t>_</t>
@@ -994,7 +1015,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1019,6 +1040,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1051,6 +1075,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1545,7 +1581,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -1559,25 +1595,25 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
       <c r="H1"/>
@@ -1587,7 +1623,7 @@
       <c r="L1"/>
     </row>
     <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1599,13 +1635,13 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="8"/>
+      <c r="G2" s="9"/>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2"/>
@@ -1613,25 +1649,25 @@
       <c r="L2"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="8"/>
+      <c r="G3" s="9"/>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3"/>
@@ -1639,7 +1675,7 @@
       <c r="L3"/>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="10"/>
+      <c r="A4" s="11"/>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4"/>
@@ -1647,2076 +1683,2880 @@
       <c r="L4"/>
     </row>
     <row r="5" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="11">
+      <c r="A5" s="12">
         <v>1001</v>
       </c>
-      <c r="B5" s="12">
-        <v>1</v>
-      </c>
-      <c r="C5" s="12">
-        <v>1</v>
-      </c>
-      <c r="D5" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12">
+      <c r="B5" s="13">
+        <v>1</v>
+      </c>
+      <c r="C5" s="13">
+        <v>1</v>
+      </c>
+      <c r="D5" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="13">
         <v>4055101</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="11">
+      <c r="A6" s="12">
         <v>1002</v>
       </c>
-      <c r="B6" s="12">
-        <v>1</v>
-      </c>
-      <c r="C6" s="12">
-        <v>1</v>
-      </c>
-      <c r="D6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12">
+      <c r="B6" s="13">
+        <v>1</v>
+      </c>
+      <c r="C6" s="13">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="13">
         <v>4055102</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="11">
+      <c r="A7" s="12">
         <v>1003</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12">
-        <v>1</v>
-      </c>
-      <c r="D7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13">
+        <v>1</v>
+      </c>
+      <c r="D7" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
       <c r="G7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="11">
+      <c r="A8" s="12">
         <v>1004</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12">
-        <v>1</v>
-      </c>
-      <c r="D8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
       <c r="G8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="11">
+      <c r="A9" s="12">
         <v>1005</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
       <c r="G9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="11">
+      <c r="A10" s="12">
         <v>1006</v>
       </c>
-      <c r="B10" s="12">
-        <v>1</v>
-      </c>
-      <c r="C10" s="12">
-        <v>1</v>
-      </c>
-      <c r="D10" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="12">
+      <c r="B10" s="13">
+        <v>1</v>
+      </c>
+      <c r="C10" s="13">
+        <v>1</v>
+      </c>
+      <c r="D10" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13">
         <v>4055103</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="11">
+      <c r="A11" s="12">
         <v>1007</v>
       </c>
-      <c r="B11" s="12">
-        <v>1</v>
-      </c>
-      <c r="C11" s="12">
-        <v>1</v>
-      </c>
-      <c r="D11" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="12">
+      <c r="B11" s="13">
+        <v>1</v>
+      </c>
+      <c r="C11" s="13">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="13">
         <v>4055104</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="11">
+      <c r="A12" s="12">
         <v>1008</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12">
-        <v>1</v>
-      </c>
-      <c r="D12" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
       <c r="G12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="11">
+      <c r="A13" s="12">
         <v>1009</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
       <c r="G13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
     </row>
     <row r="14" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="11">
+      <c r="A14" s="12">
         <v>1010</v>
       </c>
-      <c r="B14" s="12">
-        <v>1</v>
-      </c>
-      <c r="C14" s="12">
-        <v>1</v>
-      </c>
-      <c r="D14" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="12">
+      <c r="B14" s="13">
+        <v>1</v>
+      </c>
+      <c r="C14" s="13">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="13">
         <v>4055105</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
     </row>
     <row r="15" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="11">
+      <c r="A15" s="12">
         <v>1011</v>
       </c>
-      <c r="B15" s="12">
-        <v>1</v>
-      </c>
-      <c r="C15" s="12">
-        <v>1</v>
-      </c>
-      <c r="D15" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="12">
+      <c r="B15" s="13">
+        <v>1</v>
+      </c>
+      <c r="C15" s="13">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13">
         <v>4055106</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
     </row>
     <row r="16" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="11">
+      <c r="A16" s="12">
         <v>1012</v>
       </c>
-      <c r="B16" s="12">
-        <v>1</v>
-      </c>
-      <c r="C16" s="12">
-        <v>1</v>
-      </c>
-      <c r="D16" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="12">
+      <c r="B16" s="13">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13">
         <v>4055107</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
     </row>
     <row r="17" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="11">
+      <c r="A17" s="12">
         <v>1013</v>
       </c>
-      <c r="B17" s="12">
-        <v>1</v>
-      </c>
-      <c r="C17" s="12">
-        <v>1</v>
-      </c>
-      <c r="D17" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="12">
+      <c r="B17" s="13">
+        <v>1</v>
+      </c>
+      <c r="C17" s="13">
+        <v>1</v>
+      </c>
+      <c r="D17" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="13">
         <v>4055108</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
     </row>
     <row r="18" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="11">
+      <c r="A18" s="12">
         <v>1014</v>
       </c>
-      <c r="B18" s="12">
-        <v>1</v>
-      </c>
-      <c r="C18" s="12">
-        <v>1</v>
-      </c>
-      <c r="D18" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="12">
+      <c r="B18" s="13">
+        <v>1</v>
+      </c>
+      <c r="C18" s="13">
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="13">
         <v>4055109</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
     </row>
     <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="14">
+      <c r="A19" s="15">
         <v>1201</v>
       </c>
-      <c r="B19" s="15">
-        <v>1</v>
-      </c>
-      <c r="C19" s="15">
-        <v>1</v>
-      </c>
-      <c r="D19" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="15">
+      <c r="B19" s="16">
+        <v>1</v>
+      </c>
+      <c r="C19" s="16">
+        <v>1</v>
+      </c>
+      <c r="D19" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="16">
         <v>4055121</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
     </row>
     <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="14">
+      <c r="A20" s="15">
         <v>1202</v>
       </c>
-      <c r="B20" s="15">
-        <v>1</v>
-      </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="B20" s="16">
+        <v>1</v>
+      </c>
+      <c r="C20" s="16">
+        <v>1</v>
+      </c>
+      <c r="D20" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="16">
         <v>4055122</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
     </row>
     <row r="21" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="14">
+      <c r="A21" s="15">
         <v>1203</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16">
         <v>2</v>
       </c>
-      <c r="D21" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16" t="s">
+      <c r="D21" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
     </row>
     <row r="22" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="14">
+      <c r="A22" s="15">
         <v>1204</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16" t="s">
+      <c r="B22" s="16"/>
+      <c r="C22" s="16">
+        <v>1</v>
+      </c>
+      <c r="D22" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
     </row>
     <row r="23" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A23" s="14">
+      <c r="A23" s="15">
         <v>1205</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="16">
         <v>2</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
+      <c r="C23" s="16">
+        <v>1</v>
+      </c>
+      <c r="D23" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="16">
         <v>4055123</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
     </row>
     <row r="24" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A24" s="14">
+      <c r="A24" s="15">
         <v>1206</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15">
-        <v>1</v>
-      </c>
-      <c r="D24" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="16" t="s">
+      <c r="B24" s="16"/>
+      <c r="C24" s="16">
+        <v>1</v>
+      </c>
+      <c r="D24" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
     </row>
     <row r="25" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="14">
+      <c r="A25" s="15">
         <v>1207</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15">
-        <v>1</v>
-      </c>
-      <c r="D25" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="16" t="s">
+      <c r="B25" s="16"/>
+      <c r="C25" s="16">
+        <v>1</v>
+      </c>
+      <c r="D25" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
     </row>
     <row r="26" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="14">
+      <c r="A26" s="15">
         <v>1208</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15">
-        <v>1</v>
-      </c>
-      <c r="D26" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="16" t="s">
+      <c r="B26" s="16"/>
+      <c r="C26" s="16">
+        <v>1</v>
+      </c>
+      <c r="D26" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="14">
+      <c r="A27" s="15">
         <v>1209</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16" t="s">
+      <c r="B27" s="16"/>
+      <c r="C27" s="16">
+        <v>1</v>
+      </c>
+      <c r="D27" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
     </row>
     <row r="28" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="14">
+      <c r="A28" s="15">
         <v>1210</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16" t="s">
+      <c r="B28" s="16"/>
+      <c r="C28" s="16">
+        <v>1</v>
+      </c>
+      <c r="D28" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
     </row>
     <row r="29" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="14">
+      <c r="A29" s="15">
         <v>1211</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15">
-        <v>1</v>
-      </c>
-      <c r="D29" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="16" t="s">
+      <c r="B29" s="16"/>
+      <c r="C29" s="16">
+        <v>1</v>
+      </c>
+      <c r="D29" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="11">
+      <c r="A30" s="12">
         <v>1301</v>
       </c>
-      <c r="B30" s="12">
-        <v>1</v>
-      </c>
-      <c r="C30" s="12">
-        <v>1</v>
-      </c>
-      <c r="D30" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="12">
+      <c r="B30" s="13">
+        <v>1</v>
+      </c>
+      <c r="C30" s="13">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="13">
         <v>4055131</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
     </row>
     <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="11">
+      <c r="A31" s="12">
         <v>1302</v>
       </c>
-      <c r="B31" s="12">
-        <v>1</v>
-      </c>
-      <c r="C31" s="12">
-        <v>1</v>
-      </c>
-      <c r="D31" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="12">
+      <c r="B31" s="13">
+        <v>1</v>
+      </c>
+      <c r="C31" s="13">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="13">
         <v>4055132</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F31" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="18" t="s">
+      <c r="G31" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
     </row>
     <row r="32" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="11">
+      <c r="A32" s="12">
         <v>1303</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12">
-        <v>1</v>
-      </c>
-      <c r="D32" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="18" t="s">
+      <c r="B32" s="13"/>
+      <c r="C32" s="13">
+        <v>1</v>
+      </c>
+      <c r="D32" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
     </row>
     <row r="33" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="11">
+      <c r="A33" s="12">
         <v>1304</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12">
-        <v>1</v>
-      </c>
-      <c r="D33" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="18" t="s">
+      <c r="B33" s="13"/>
+      <c r="C33" s="13">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
     </row>
     <row r="34" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="11">
+      <c r="A34" s="12">
         <v>1305</v>
       </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12">
-        <v>1</v>
-      </c>
-      <c r="D34" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="18" t="s">
+      <c r="B34" s="13"/>
+      <c r="C34" s="13">
+        <v>1</v>
+      </c>
+      <c r="D34" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
     </row>
     <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="11">
+      <c r="A35" s="12">
         <v>1306</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12">
-        <v>1</v>
-      </c>
-      <c r="D35" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="18" t="s">
+      <c r="B35" s="13"/>
+      <c r="C35" s="13">
+        <v>1</v>
+      </c>
+      <c r="D35" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
     </row>
     <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="11">
+      <c r="A36" s="12">
         <v>1307</v>
       </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12">
-        <v>1</v>
-      </c>
-      <c r="D36" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="18" t="s">
+      <c r="B36" s="13"/>
+      <c r="C36" s="13">
+        <v>1</v>
+      </c>
+      <c r="D36" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-    </row>
-    <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="11">
-        <v>1308</v>
-      </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12">
-        <v>1</v>
-      </c>
-      <c r="D37" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-    </row>
-    <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="11">
-        <v>1309</v>
-      </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12">
-        <v>1</v>
-      </c>
-      <c r="D38" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+    </row>
+    <row r="37" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A37" s="15">
+        <v>1401</v>
+      </c>
+      <c r="B37" s="16">
+        <v>1</v>
+      </c>
+      <c r="C37" s="16">
+        <v>1</v>
+      </c>
+      <c r="D37" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="16">
+        <v>4055141</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+    </row>
+    <row r="38" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A38" s="15">
+        <v>1402</v>
+      </c>
+      <c r="B38" s="16">
+        <v>1</v>
+      </c>
+      <c r="C38" s="16">
+        <v>1</v>
+      </c>
+      <c r="D38" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="16">
+        <v>4055142</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
     </row>
     <row r="39" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A39" s="14">
-        <v>1401</v>
-      </c>
-      <c r="B39" s="15">
-        <v>1</v>
-      </c>
-      <c r="C39" s="15">
-        <v>1</v>
-      </c>
-      <c r="D39" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="15">
-        <v>4055141</v>
-      </c>
-      <c r="F39" s="15" t="s">
+      <c r="A39" s="15">
+        <v>1403</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16">
+        <v>1</v>
+      </c>
+      <c r="D39" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A40" s="15">
+        <v>1404</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16">
+        <v>1</v>
+      </c>
+      <c r="D40" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A41" s="15">
+        <v>1405</v>
+      </c>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16">
+        <v>1</v>
+      </c>
+      <c r="D41" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A42" s="15">
+        <v>1406</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16">
+        <v>1</v>
+      </c>
+      <c r="D42" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+    <row r="43" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A43" s="15">
+        <v>1407</v>
+      </c>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16">
+        <v>1</v>
+      </c>
+      <c r="D43" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+    </row>
+    <row r="44" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A44" s="15">
+        <v>1408</v>
+      </c>
+      <c r="B44" s="16">
+        <v>1</v>
+      </c>
+      <c r="C44" s="16">
+        <v>1</v>
+      </c>
+      <c r="D44" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="16">
+        <v>4055143</v>
+      </c>
+      <c r="F44" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="16" t="s">
+      <c r="G44" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-    </row>
-    <row r="40" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="14">
-        <v>1402</v>
-      </c>
-      <c r="B40" s="15">
-        <v>1</v>
-      </c>
-      <c r="C40" s="15">
-        <v>1</v>
-      </c>
-      <c r="D40" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="15">
-        <v>4055142</v>
-      </c>
-      <c r="F40" s="15" t="s">
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+    </row>
+    <row r="45" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A45" s="15">
+        <v>1409</v>
+      </c>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16">
+        <v>1</v>
+      </c>
+      <c r="D45" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+    </row>
+    <row r="46" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A46" s="15">
+        <v>1410</v>
+      </c>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16">
+        <v>1</v>
+      </c>
+      <c r="D46" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+    </row>
+    <row r="47" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A47" s="15">
+        <v>1411</v>
+      </c>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16">
+        <v>1</v>
+      </c>
+      <c r="D47" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+    </row>
+    <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="15">
+        <v>1412</v>
+      </c>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16">
+        <v>1</v>
+      </c>
+      <c r="D48" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+    </row>
+    <row r="49" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A49" s="15">
+        <v>1413</v>
+      </c>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16">
+        <v>1</v>
+      </c>
+      <c r="D49" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+    </row>
+    <row r="50" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A50" s="15">
+        <v>1414</v>
+      </c>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16">
+        <v>1</v>
+      </c>
+      <c r="D50" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+    </row>
+    <row r="51" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A51" s="15">
+        <v>1415</v>
+      </c>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16">
+        <v>1</v>
+      </c>
+      <c r="D51" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="18"/>
+    </row>
+    <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A52" s="15">
+        <v>1416</v>
+      </c>
+      <c r="B52" s="16"/>
+      <c r="C52" s="16">
+        <v>1</v>
+      </c>
+      <c r="D52" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+    </row>
+    <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A53" s="15">
+        <v>1417</v>
+      </c>
+      <c r="B53" s="16"/>
+      <c r="C53" s="16">
+        <v>1</v>
+      </c>
+      <c r="D53" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+    </row>
+    <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A54" s="15">
+        <v>1418</v>
+      </c>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16">
+        <v>1</v>
+      </c>
+      <c r="D54" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+    </row>
+    <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A55" s="15">
+        <v>1419</v>
+      </c>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16">
+        <v>1</v>
+      </c>
+      <c r="D55" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+    </row>
+    <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A56" s="15">
+        <v>1420</v>
+      </c>
+      <c r="B56" s="16"/>
+      <c r="C56" s="16">
+        <v>1</v>
+      </c>
+      <c r="D56" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+    </row>
+    <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A57" s="15">
+        <v>1421</v>
+      </c>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
+    </row>
+    <row r="58" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A58" s="12">
+        <v>1501</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13">
+        <v>1</v>
+      </c>
+      <c r="D58" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+    </row>
+    <row r="59" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A59" s="12">
+        <v>1502</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13">
+        <v>1</v>
+      </c>
+      <c r="D59" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+    </row>
+    <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A60" s="12">
+        <v>1503</v>
+      </c>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13">
+        <v>1</v>
+      </c>
+      <c r="D60" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+    </row>
+    <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A61" s="12">
+        <v>1504</v>
+      </c>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13">
+        <v>1</v>
+      </c>
+      <c r="D61" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14"/>
+    </row>
+    <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A62" s="12">
+        <v>1505</v>
+      </c>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13">
+        <v>1</v>
+      </c>
+      <c r="D62" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
+      <c r="L62" s="14"/>
+    </row>
+    <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A63" s="12">
+        <v>1506</v>
+      </c>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13">
+        <v>1</v>
+      </c>
+      <c r="D63" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="14"/>
+    </row>
+    <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A64" s="12">
+        <v>1507</v>
+      </c>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13">
+        <v>1</v>
+      </c>
+      <c r="D64" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="14"/>
+      <c r="L64" s="14"/>
+    </row>
+    <row r="65" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A65" s="15">
+        <v>1601</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1</v>
+      </c>
+      <c r="C65" s="16">
+        <v>1</v>
+      </c>
+      <c r="D65" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="16">
+        <v>4055151</v>
+      </c>
+      <c r="F65" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G40" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-    </row>
-    <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="14">
-        <v>1403</v>
-      </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15">
-        <v>1</v>
-      </c>
-      <c r="D41" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-    </row>
-    <row r="42" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="14">
-        <v>1404</v>
-      </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15">
-        <v>1</v>
-      </c>
-      <c r="D42" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-    </row>
-    <row r="43" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="14">
-        <v>1405</v>
-      </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15">
-        <v>1</v>
-      </c>
-      <c r="D43" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-    </row>
-    <row r="44" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="14">
-        <v>1406</v>
-      </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15">
-        <v>1</v>
-      </c>
-      <c r="D44" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-    </row>
-    <row r="45" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="14">
-        <v>1407</v>
-      </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15">
-        <v>1</v>
-      </c>
-      <c r="D45" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-    </row>
-    <row r="46" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="14">
-        <v>1408</v>
-      </c>
-      <c r="B46" s="15">
-        <v>1</v>
-      </c>
-      <c r="C46" s="15">
-        <v>1</v>
-      </c>
-      <c r="D46" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="15">
-        <v>4055143</v>
-      </c>
-      <c r="F46" s="15" t="s">
+      <c r="G65" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="18"/>
+      <c r="L65" s="18"/>
+    </row>
+    <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A66" s="15">
+        <v>1602</v>
+      </c>
+      <c r="B66" s="16">
+        <v>1</v>
+      </c>
+      <c r="C66" s="16">
+        <v>1</v>
+      </c>
+      <c r="D66" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="16">
+        <v>4055152</v>
+      </c>
+      <c r="F66" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G46" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-    </row>
-    <row r="47" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="14">
-        <v>1409</v>
-      </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15">
-        <v>1</v>
-      </c>
-      <c r="D47" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-    </row>
-    <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="14">
-        <v>1410</v>
-      </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15">
-        <v>1</v>
-      </c>
-      <c r="D48" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-    </row>
-    <row r="49" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="14">
-        <v>1411</v>
-      </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15">
-        <v>1</v>
-      </c>
-      <c r="D49" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-    </row>
-    <row r="50" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A50" s="14">
-        <v>1412</v>
-      </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15">
-        <v>1</v>
-      </c>
-      <c r="D50" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-    </row>
-    <row r="51" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A51" s="14">
-        <v>1413</v>
-      </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15">
-        <v>1</v>
-      </c>
-      <c r="D51" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-    </row>
-    <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A52" s="14">
-        <v>1414</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15">
-        <v>1</v>
-      </c>
-      <c r="D52" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-    </row>
-    <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A53" s="14">
-        <v>1415</v>
-      </c>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15">
-        <v>1</v>
-      </c>
-      <c r="D53" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-    </row>
-    <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A54" s="14">
-        <v>1416</v>
-      </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15">
-        <v>1</v>
-      </c>
-      <c r="D54" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-    </row>
-    <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A55" s="14">
-        <v>1417</v>
-      </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15">
-        <v>1</v>
-      </c>
-      <c r="D55" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-    </row>
-    <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A56" s="14">
-        <v>1418</v>
-      </c>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15">
-        <v>1</v>
-      </c>
-      <c r="D56" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-    </row>
-    <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A57" s="14">
-        <v>1419</v>
-      </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15">
-        <v>1</v>
-      </c>
-      <c r="D57" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H57" s="17"/>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-    </row>
-    <row r="58" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A58" s="14">
-        <v>1420</v>
-      </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15">
-        <v>1</v>
-      </c>
-      <c r="D58" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-    </row>
-    <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="14">
-        <v>1421</v>
-      </c>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H59" s="17"/>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-    </row>
-    <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="11">
-        <v>1501</v>
-      </c>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12">
-        <v>1</v>
-      </c>
-      <c r="D60" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
-    </row>
-    <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="11">
-        <v>1502</v>
-      </c>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12">
-        <v>1</v>
-      </c>
-      <c r="D61" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
-      <c r="K61" s="13"/>
-      <c r="L61" s="13"/>
-    </row>
-    <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A62" s="11">
-        <v>1503</v>
-      </c>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12">
-        <v>1</v>
-      </c>
-      <c r="D62" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
-      <c r="K62" s="13"/>
-      <c r="L62" s="13"/>
-    </row>
-    <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A63" s="11">
-        <v>1504</v>
-      </c>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12">
-        <v>1</v>
-      </c>
-      <c r="D63" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
-      <c r="K63" s="13"/>
-      <c r="L63" s="13"/>
-    </row>
-    <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A64" s="11">
-        <v>1505</v>
-      </c>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12">
-        <v>1</v>
-      </c>
-      <c r="D64" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
-      <c r="K64" s="13"/>
-      <c r="L64" s="13"/>
-    </row>
-    <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A65" s="11">
-        <v>1506</v>
-      </c>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12">
-        <v>1</v>
-      </c>
-      <c r="D65" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H65" s="13"/>
-      <c r="I65" s="13"/>
-      <c r="J65" s="13"/>
-      <c r="K65" s="13"/>
-      <c r="L65" s="13"/>
-    </row>
-    <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="11">
-        <v>1507</v>
-      </c>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12">
-        <v>1</v>
-      </c>
-      <c r="D66" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="13"/>
-      <c r="L66" s="13"/>
+      <c r="G66" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H66" s="18"/>
+      <c r="I66" s="18"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="18"/>
+      <c r="L66" s="18"/>
     </row>
     <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="14">
-        <v>1601</v>
-      </c>
-      <c r="B67" s="15">
-        <v>1</v>
-      </c>
-      <c r="C67" s="15">
-        <v>1</v>
-      </c>
-      <c r="D67" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="15">
-        <v>4055151</v>
-      </c>
-      <c r="F67" s="15" t="s">
+      <c r="A67" s="15">
+        <v>1603</v>
+      </c>
+      <c r="B67" s="16"/>
+      <c r="C67" s="16">
+        <v>1</v>
+      </c>
+      <c r="D67" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="18"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="18"/>
+      <c r="L67" s="18"/>
+    </row>
+    <row r="68" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A68" s="15">
+        <v>1604</v>
+      </c>
+      <c r="B68" s="16"/>
+      <c r="C68" s="16">
+        <v>1</v>
+      </c>
+      <c r="D68" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H68" s="18"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="18"/>
+      <c r="L68" s="18"/>
+    </row>
+    <row r="69" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A69" s="15">
+        <v>1605</v>
+      </c>
+      <c r="B69" s="16"/>
+      <c r="C69" s="16">
+        <v>1</v>
+      </c>
+      <c r="D69" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" s="18"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
+      <c r="L69" s="18"/>
+    </row>
+    <row r="70" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A70" s="15">
+        <v>1606</v>
+      </c>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16">
+        <v>1</v>
+      </c>
+      <c r="D70" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
+    </row>
+    <row r="71" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A71" s="15">
+        <v>1607</v>
+      </c>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16">
+        <v>1</v>
+      </c>
+      <c r="D71" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H71" s="18"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
+      <c r="L71" s="18"/>
+    </row>
+    <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A72" s="15">
+        <v>1608</v>
+      </c>
+      <c r="B72" s="16">
+        <v>1</v>
+      </c>
+      <c r="C72" s="16">
+        <v>1</v>
+      </c>
+      <c r="D72" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="16">
+        <v>4055153</v>
+      </c>
+      <c r="F72" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G67" s="16" t="s">
+      <c r="G72" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="17"/>
-      <c r="L67" s="17"/>
-    </row>
-    <row r="68" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="14">
-        <v>1602</v>
-      </c>
-      <c r="B68" s="15">
-        <v>1</v>
-      </c>
-      <c r="C68" s="15">
-        <v>1</v>
-      </c>
-      <c r="D68" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E68" s="15">
-        <v>4055152</v>
-      </c>
-      <c r="F68" s="15" t="s">
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="18"/>
+      <c r="L72" s="18"/>
+    </row>
+    <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A73" s="15">
+        <v>1609</v>
+      </c>
+      <c r="B73" s="16"/>
+      <c r="C73" s="16">
+        <v>1</v>
+      </c>
+      <c r="D73" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
+      <c r="L73" s="18"/>
+    </row>
+    <row r="74" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A74" s="15">
+        <v>1610</v>
+      </c>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16">
+        <v>1</v>
+      </c>
+      <c r="D74" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" s="18"/>
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="18"/>
+      <c r="L74" s="18"/>
+    </row>
+    <row r="75" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A75" s="15">
+        <v>1611</v>
+      </c>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16">
+        <v>1</v>
+      </c>
+      <c r="D75" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75" s="18"/>
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="18"/>
+      <c r="L75" s="18"/>
+    </row>
+    <row r="76" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A76" s="15">
+        <v>1612</v>
+      </c>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16">
+        <v>1</v>
+      </c>
+      <c r="D76" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H76" s="18"/>
+      <c r="I76" s="18"/>
+      <c r="J76" s="18"/>
+      <c r="K76" s="18"/>
+      <c r="L76" s="18"/>
+    </row>
+    <row r="77" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A77" s="15">
+        <v>1613</v>
+      </c>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16">
+        <v>1</v>
+      </c>
+      <c r="D77" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H77" s="18"/>
+      <c r="I77" s="18"/>
+      <c r="J77" s="18"/>
+      <c r="K77" s="18"/>
+      <c r="L77" s="18"/>
+    </row>
+    <row r="78" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A78" s="15">
+        <v>1614</v>
+      </c>
+      <c r="B78" s="16"/>
+      <c r="C78" s="16">
+        <v>1</v>
+      </c>
+      <c r="D78" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" s="18"/>
+      <c r="I78" s="18"/>
+      <c r="J78" s="18"/>
+      <c r="K78" s="18"/>
+      <c r="L78" s="18"/>
+    </row>
+    <row r="79" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A79" s="15">
+        <v>1615</v>
+      </c>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16">
+        <v>1</v>
+      </c>
+      <c r="D79" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="18"/>
+      <c r="I79" s="18"/>
+      <c r="J79" s="18"/>
+      <c r="K79" s="18"/>
+      <c r="L79" s="18"/>
+    </row>
+    <row r="80" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="12">
+        <v>1701</v>
+      </c>
+      <c r="B80" s="13">
+        <v>1</v>
+      </c>
+      <c r="C80" s="13">
+        <v>1</v>
+      </c>
+      <c r="D80" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" s="13">
+        <v>4055171</v>
+      </c>
+      <c r="F80" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G68" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="17"/>
-      <c r="L68" s="17"/>
-    </row>
-    <row r="69" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A69" s="14">
-        <v>1603</v>
-      </c>
-      <c r="B69" s="15"/>
-      <c r="C69" s="15">
-        <v>1</v>
-      </c>
-      <c r="D69" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H69" s="17"/>
-      <c r="I69" s="17"/>
-      <c r="J69" s="17"/>
-      <c r="K69" s="17"/>
-      <c r="L69" s="17"/>
-    </row>
-    <row r="70" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="14">
-        <v>1604</v>
-      </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15">
-        <v>1</v>
-      </c>
-      <c r="D70" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H70" s="17"/>
-      <c r="I70" s="17"/>
-      <c r="J70" s="17"/>
-      <c r="K70" s="17"/>
-      <c r="L70" s="17"/>
-    </row>
-    <row r="71" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="14">
-        <v>1605</v>
-      </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15">
-        <v>1</v>
-      </c>
-      <c r="D71" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="17"/>
-    </row>
-    <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="14">
-        <v>1606</v>
-      </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="15">
-        <v>1</v>
-      </c>
-      <c r="D72" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-      <c r="J72" s="17"/>
-      <c r="K72" s="17"/>
-      <c r="L72" s="17"/>
-    </row>
-    <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A73" s="14">
-        <v>1607</v>
-      </c>
-      <c r="B73" s="15"/>
-      <c r="C73" s="15">
-        <v>1</v>
-      </c>
-      <c r="D73" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H73" s="17"/>
-      <c r="I73" s="17"/>
-      <c r="J73" s="17"/>
-      <c r="K73" s="17"/>
-      <c r="L73" s="17"/>
-    </row>
-    <row r="74" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="14">
-        <v>1608</v>
-      </c>
-      <c r="B74" s="15">
-        <v>1</v>
-      </c>
-      <c r="C74" s="15">
-        <v>1</v>
-      </c>
-      <c r="D74" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" s="15">
-        <v>4055153</v>
-      </c>
-      <c r="F74" s="15" t="s">
+      <c r="G80" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+      <c r="K80" s="14"/>
+      <c r="L80" s="14"/>
+    </row>
+    <row r="81" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A81" s="12">
+        <v>1702</v>
+      </c>
+      <c r="B81" s="13">
+        <v>1</v>
+      </c>
+      <c r="C81" s="13">
+        <v>1</v>
+      </c>
+      <c r="D81" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" s="13">
+        <v>4055172</v>
+      </c>
+      <c r="F81" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G74" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H74" s="17"/>
-      <c r="I74" s="17"/>
-      <c r="J74" s="17"/>
-      <c r="K74" s="17"/>
-      <c r="L74" s="17"/>
-    </row>
-    <row r="75" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="14">
-        <v>1609</v>
-      </c>
-      <c r="B75" s="15"/>
-      <c r="C75" s="15">
-        <v>1</v>
-      </c>
-      <c r="D75" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H75" s="17"/>
-      <c r="I75" s="17"/>
-      <c r="J75" s="17"/>
-      <c r="K75" s="17"/>
-      <c r="L75" s="17"/>
-    </row>
-    <row r="76" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A76" s="14">
-        <v>1610</v>
-      </c>
-      <c r="B76" s="15"/>
-      <c r="C76" s="15">
-        <v>1</v>
-      </c>
-      <c r="D76" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H76" s="17"/>
-      <c r="I76" s="17"/>
-      <c r="J76" s="17"/>
-      <c r="K76" s="17"/>
-      <c r="L76" s="17"/>
-    </row>
-    <row r="77" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A77" s="14">
-        <v>1611</v>
-      </c>
-      <c r="B77" s="15"/>
-      <c r="C77" s="15">
-        <v>1</v>
-      </c>
-      <c r="D77" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
-      <c r="K77" s="17"/>
-      <c r="L77" s="17"/>
-    </row>
-    <row r="78" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A78" s="14">
-        <v>1612</v>
-      </c>
-      <c r="B78" s="15"/>
-      <c r="C78" s="15">
-        <v>1</v>
-      </c>
-      <c r="D78" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H78" s="17"/>
-      <c r="I78" s="17"/>
-      <c r="J78" s="17"/>
-      <c r="K78" s="17"/>
-      <c r="L78" s="17"/>
-    </row>
-    <row r="79" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="14">
-        <v>1613</v>
-      </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15">
-        <v>1</v>
-      </c>
-      <c r="D79" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79" s="17"/>
-      <c r="I79" s="17"/>
-      <c r="J79" s="17"/>
-      <c r="K79" s="17"/>
-      <c r="L79" s="17"/>
-    </row>
-    <row r="80" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="14">
-        <v>1614</v>
-      </c>
-      <c r="B80" s="15"/>
-      <c r="C80" s="15">
-        <v>1</v>
-      </c>
-      <c r="D80" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="17"/>
-      <c r="L80" s="17"/>
-    </row>
-    <row r="81" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="14">
-        <v>1615</v>
-      </c>
-      <c r="B81" s="15"/>
-      <c r="C81" s="15">
-        <v>1</v>
-      </c>
-      <c r="D81" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" s="15"/>
-      <c r="F81" s="15"/>
-      <c r="G81" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
-      <c r="K81" s="17"/>
-      <c r="L81" s="17"/>
+      <c r="G81" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="14"/>
+      <c r="L81" s="14"/>
     </row>
     <row r="82" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="11">
-        <v>1701</v>
-      </c>
-      <c r="B82" s="12">
-        <v>1</v>
-      </c>
-      <c r="C82" s="12">
-        <v>1</v>
-      </c>
-      <c r="D82" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" s="12">
-        <v>4055171</v>
-      </c>
-      <c r="F82" s="12" t="s">
+      <c r="A82" s="12">
+        <v>1703</v>
+      </c>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13">
+        <v>1</v>
+      </c>
+      <c r="D82" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="14"/>
+      <c r="L82" s="14"/>
+    </row>
+    <row r="83" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A83" s="12">
+        <v>1704</v>
+      </c>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13">
+        <v>1</v>
+      </c>
+      <c r="D83" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+      <c r="K83" s="14"/>
+      <c r="L83" s="14"/>
+    </row>
+    <row r="84" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A84" s="12">
+        <v>1705</v>
+      </c>
+      <c r="B84" s="13"/>
+      <c r="C84" s="13">
+        <v>1</v>
+      </c>
+      <c r="D84" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="14"/>
+      <c r="L84" s="14"/>
+    </row>
+    <row r="85" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A85" s="12">
+        <v>1706</v>
+      </c>
+      <c r="B85" s="13"/>
+      <c r="C85" s="13">
+        <v>1</v>
+      </c>
+      <c r="D85" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="14"/>
+      <c r="L85" s="14"/>
+    </row>
+    <row r="86" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A86" s="12">
+        <v>1707</v>
+      </c>
+      <c r="B86" s="13"/>
+      <c r="C86" s="13">
+        <v>1</v>
+      </c>
+      <c r="D86" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+      <c r="K86" s="14"/>
+      <c r="L86" s="14"/>
+    </row>
+    <row r="87" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A87" s="12">
+        <v>1708</v>
+      </c>
+      <c r="B87" s="13"/>
+      <c r="C87" s="13">
+        <v>1</v>
+      </c>
+      <c r="D87" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+      <c r="K87" s="14"/>
+      <c r="L87" s="14"/>
+    </row>
+    <row r="88" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A88" s="12">
+        <v>1709</v>
+      </c>
+      <c r="B88" s="13"/>
+      <c r="C88" s="13">
+        <v>1</v>
+      </c>
+      <c r="D88" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="13"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+      <c r="K88" s="14"/>
+      <c r="L88" s="14"/>
+    </row>
+    <row r="89" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A89" s="15">
+        <v>1801</v>
+      </c>
+      <c r="B89" s="16">
+        <v>1</v>
+      </c>
+      <c r="C89" s="16">
+        <v>1</v>
+      </c>
+      <c r="D89" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="16">
+        <v>4055191</v>
+      </c>
+      <c r="F89" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G82" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H82" s="13"/>
-      <c r="I82" s="13"/>
-      <c r="J82" s="13"/>
-      <c r="K82" s="13"/>
-      <c r="L82" s="13"/>
-    </row>
-    <row r="83" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A83" s="11">
-        <v>1702</v>
-      </c>
-      <c r="B83" s="12">
-        <v>1</v>
-      </c>
-      <c r="C83" s="12">
-        <v>1</v>
-      </c>
-      <c r="D83" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="12">
-        <v>4055172</v>
-      </c>
-      <c r="F83" s="12" t="s">
+      <c r="G89" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H89" s="18"/>
+      <c r="I89" s="18"/>
+      <c r="J89" s="18"/>
+      <c r="K89" s="18"/>
+      <c r="L89" s="18"/>
+    </row>
+    <row r="90" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A90" s="15">
+        <v>1802</v>
+      </c>
+      <c r="B90" s="16">
+        <v>1</v>
+      </c>
+      <c r="C90" s="16">
+        <v>1</v>
+      </c>
+      <c r="D90" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="16">
+        <v>4055192</v>
+      </c>
+      <c r="F90" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G83" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13"/>
-      <c r="K83" s="13"/>
-      <c r="L83" s="13"/>
-    </row>
-    <row r="84" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A84" s="11">
-        <v>1703</v>
-      </c>
-      <c r="B84" s="12"/>
-      <c r="C84" s="12">
-        <v>1</v>
-      </c>
-      <c r="D84" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13"/>
-      <c r="K84" s="13"/>
-      <c r="L84" s="13"/>
-    </row>
-    <row r="85" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A85" s="11">
-        <v>1704</v>
-      </c>
-      <c r="B85" s="12"/>
-      <c r="C85" s="12">
-        <v>1</v>
-      </c>
-      <c r="D85" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" s="12"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
-      <c r="J85" s="13"/>
-      <c r="K85" s="13"/>
-      <c r="L85" s="13"/>
-    </row>
-    <row r="86" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A86" s="11">
-        <v>1705</v>
-      </c>
-      <c r="B86" s="12"/>
-      <c r="C86" s="12">
-        <v>1</v>
-      </c>
-      <c r="D86" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H86" s="13"/>
-      <c r="I86" s="13"/>
-      <c r="J86" s="13"/>
-      <c r="K86" s="13"/>
-      <c r="L86" s="13"/>
-    </row>
-    <row r="87" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A87" s="11">
-        <v>1706</v>
-      </c>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12">
-        <v>1</v>
-      </c>
-      <c r="D87" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H87" s="13"/>
-      <c r="I87" s="13"/>
-      <c r="J87" s="13"/>
-      <c r="K87" s="13"/>
-      <c r="L87" s="13"/>
-    </row>
-    <row r="88" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A88" s="11">
-        <v>1707</v>
-      </c>
-      <c r="B88" s="12"/>
-      <c r="C88" s="12">
-        <v>1</v>
-      </c>
-      <c r="D88" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" s="12"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H88" s="13"/>
-      <c r="I88" s="13"/>
-      <c r="J88" s="13"/>
-      <c r="K88" s="13"/>
-      <c r="L88" s="13"/>
-    </row>
-    <row r="89" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A89" s="11">
-        <v>1708</v>
-      </c>
-      <c r="B89" s="12"/>
-      <c r="C89" s="12">
-        <v>1</v>
-      </c>
-      <c r="D89" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" s="12"/>
-      <c r="F89" s="12"/>
-      <c r="G89" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
-      <c r="J89" s="13"/>
-      <c r="K89" s="13"/>
-      <c r="L89" s="13"/>
-    </row>
-    <row r="90" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A90" s="11">
-        <v>1709</v>
-      </c>
-      <c r="B90" s="12"/>
-      <c r="C90" s="12">
-        <v>1</v>
-      </c>
-      <c r="D90" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E90" s="12"/>
-      <c r="F90" s="12"/>
-      <c r="G90" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
-      <c r="J90" s="13"/>
-      <c r="K90" s="13"/>
-      <c r="L90" s="13"/>
-    </row>
-    <row r="91" customHeight="1" spans="1:12">
-      <c r="A91" s="19">
+      <c r="G90" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H90" s="18"/>
+      <c r="I90" s="18"/>
+      <c r="J90" s="18"/>
+      <c r="K90" s="18"/>
+      <c r="L90" s="18"/>
+    </row>
+    <row r="91" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A91" s="15">
+        <v>1803</v>
+      </c>
+      <c r="B91" s="16"/>
+      <c r="C91" s="16">
+        <v>1</v>
+      </c>
+      <c r="D91" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="16"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H91" s="18"/>
+      <c r="I91" s="18"/>
+      <c r="J91" s="18"/>
+      <c r="K91" s="18"/>
+      <c r="L91" s="18"/>
+    </row>
+    <row r="92" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A92" s="15">
+        <v>1804</v>
+      </c>
+      <c r="B92" s="16"/>
+      <c r="C92" s="16">
+        <v>1</v>
+      </c>
+      <c r="D92" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="16"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H92" s="18"/>
+      <c r="I92" s="18"/>
+      <c r="J92" s="18"/>
+      <c r="K92" s="18"/>
+      <c r="L92" s="18"/>
+    </row>
+    <row r="93" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A93" s="15">
+        <v>1805</v>
+      </c>
+      <c r="B93" s="16"/>
+      <c r="C93" s="16">
+        <v>1</v>
+      </c>
+      <c r="D93" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="16"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H93" s="18"/>
+      <c r="I93" s="18"/>
+      <c r="J93" s="18"/>
+      <c r="K93" s="18"/>
+      <c r="L93" s="18"/>
+    </row>
+    <row r="94" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A94" s="15">
+        <v>1806</v>
+      </c>
+      <c r="B94" s="16"/>
+      <c r="C94" s="16">
+        <v>1</v>
+      </c>
+      <c r="D94" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="16"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H94" s="18"/>
+      <c r="I94" s="18"/>
+      <c r="J94" s="18"/>
+      <c r="K94" s="18"/>
+      <c r="L94" s="18"/>
+    </row>
+    <row r="95" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A95" s="15">
+        <v>1807</v>
+      </c>
+      <c r="B95" s="16"/>
+      <c r="C95" s="16">
+        <v>1</v>
+      </c>
+      <c r="D95" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="16"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H95" s="18"/>
+      <c r="I95" s="18"/>
+      <c r="J95" s="18"/>
+      <c r="K95" s="18"/>
+      <c r="L95" s="18"/>
+    </row>
+    <row r="96" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A96" s="15">
+        <v>1808</v>
+      </c>
+      <c r="B96" s="16"/>
+      <c r="C96" s="16">
+        <v>1</v>
+      </c>
+      <c r="D96" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" s="16"/>
+      <c r="F96" s="16"/>
+      <c r="G96" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="18"/>
+      <c r="I96" s="18"/>
+      <c r="J96" s="18"/>
+      <c r="K96" s="18"/>
+      <c r="L96" s="18"/>
+    </row>
+    <row r="97" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A97" s="15">
+        <v>1809</v>
+      </c>
+      <c r="B97" s="16"/>
+      <c r="C97" s="16">
+        <v>1</v>
+      </c>
+      <c r="D97" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" s="16"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H97" s="18"/>
+      <c r="I97" s="18"/>
+      <c r="J97" s="18"/>
+      <c r="K97" s="18"/>
+      <c r="L97" s="18"/>
+    </row>
+    <row r="98" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A98" s="15">
+        <v>1810</v>
+      </c>
+      <c r="B98" s="16"/>
+      <c r="C98" s="16">
+        <v>1</v>
+      </c>
+      <c r="D98" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" s="16"/>
+      <c r="F98" s="16"/>
+      <c r="G98" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H98" s="18"/>
+      <c r="I98" s="18"/>
+      <c r="J98" s="18"/>
+      <c r="K98" s="18"/>
+      <c r="L98" s="18"/>
+    </row>
+    <row r="99" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A99" s="12">
+        <v>1821</v>
+      </c>
+      <c r="B99" s="13">
+        <v>1</v>
+      </c>
+      <c r="C99" s="13">
+        <v>1</v>
+      </c>
+      <c r="D99" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" s="13">
+        <v>4055211</v>
+      </c>
+      <c r="F99" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G99" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H99" s="14"/>
+      <c r="I99" s="14"/>
+      <c r="J99" s="14"/>
+      <c r="K99" s="14"/>
+      <c r="L99" s="14"/>
+    </row>
+    <row r="100" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A100" s="12">
+        <v>1822</v>
+      </c>
+      <c r="B100" s="13">
+        <v>1</v>
+      </c>
+      <c r="C100" s="13">
+        <v>1</v>
+      </c>
+      <c r="D100" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" s="13">
+        <v>4055212</v>
+      </c>
+      <c r="F100" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H100" s="14"/>
+      <c r="I100" s="14"/>
+      <c r="J100" s="14"/>
+      <c r="K100" s="14"/>
+      <c r="L100" s="14"/>
+    </row>
+    <row r="101" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A101" s="12">
+        <v>1823</v>
+      </c>
+      <c r="B101" s="13"/>
+      <c r="C101" s="13">
+        <v>1</v>
+      </c>
+      <c r="D101" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E101" s="13"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H101" s="14"/>
+      <c r="I101" s="14"/>
+      <c r="J101" s="14"/>
+      <c r="K101" s="14"/>
+      <c r="L101" s="14"/>
+    </row>
+    <row r="102" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A102" s="12">
+        <v>1824</v>
+      </c>
+      <c r="B102" s="13"/>
+      <c r="C102" s="13">
+        <v>1</v>
+      </c>
+      <c r="D102" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E102" s="13"/>
+      <c r="F102" s="13"/>
+      <c r="G102" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H102" s="14"/>
+      <c r="I102" s="14"/>
+      <c r="J102" s="14"/>
+      <c r="K102" s="14"/>
+      <c r="L102" s="14"/>
+    </row>
+    <row r="103" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A103" s="12">
+        <v>1825</v>
+      </c>
+      <c r="B103" s="13"/>
+      <c r="C103" s="13">
+        <v>1</v>
+      </c>
+      <c r="D103" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103" s="13"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H103" s="14"/>
+      <c r="I103" s="14"/>
+      <c r="J103" s="14"/>
+      <c r="K103" s="14"/>
+      <c r="L103" s="14"/>
+    </row>
+    <row r="104" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A104" s="12">
+        <v>1826</v>
+      </c>
+      <c r="B104" s="13"/>
+      <c r="C104" s="13">
+        <v>1</v>
+      </c>
+      <c r="D104" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E104" s="13"/>
+      <c r="F104" s="13"/>
+      <c r="G104" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H104" s="14"/>
+      <c r="I104" s="14"/>
+      <c r="J104" s="14"/>
+      <c r="K104" s="14"/>
+      <c r="L104" s="14"/>
+    </row>
+    <row r="105" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A105" s="12">
+        <v>1827</v>
+      </c>
+      <c r="B105" s="13"/>
+      <c r="C105" s="13">
+        <v>1</v>
+      </c>
+      <c r="D105" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" s="13"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H105" s="14"/>
+      <c r="I105" s="14"/>
+      <c r="J105" s="14"/>
+      <c r="K105" s="14"/>
+      <c r="L105" s="14"/>
+    </row>
+    <row r="106" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A106" s="20">
+        <v>1841</v>
+      </c>
+      <c r="B106" s="21">
+        <v>1</v>
+      </c>
+      <c r="C106" s="21">
+        <v>1</v>
+      </c>
+      <c r="D106" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E106" s="21">
+        <v>4055231</v>
+      </c>
+      <c r="F106" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G106" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H106" s="23"/>
+      <c r="I106" s="23"/>
+      <c r="J106" s="23"/>
+      <c r="K106" s="23"/>
+      <c r="L106" s="23"/>
+    </row>
+    <row r="107" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A107" s="20">
+        <v>1842</v>
+      </c>
+      <c r="B107" s="21">
+        <v>1</v>
+      </c>
+      <c r="C107" s="21">
+        <v>1</v>
+      </c>
+      <c r="D107" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E107" s="21">
+        <v>4055232</v>
+      </c>
+      <c r="F107" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G107" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H107" s="23"/>
+      <c r="I107" s="23"/>
+      <c r="J107" s="23"/>
+      <c r="K107" s="23"/>
+      <c r="L107" s="23"/>
+    </row>
+    <row r="108" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A108" s="20">
+        <v>1843</v>
+      </c>
+      <c r="B108" s="21"/>
+      <c r="C108" s="21">
+        <v>1</v>
+      </c>
+      <c r="D108" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E108" s="21"/>
+      <c r="F108" s="21"/>
+      <c r="G108" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H108" s="23"/>
+      <c r="I108" s="23"/>
+      <c r="J108" s="23"/>
+      <c r="K108" s="23"/>
+      <c r="L108" s="23"/>
+    </row>
+    <row r="109" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A109" s="20">
+        <v>1844</v>
+      </c>
+      <c r="B109" s="21"/>
+      <c r="C109" s="21">
+        <v>1</v>
+      </c>
+      <c r="D109" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E109" s="21"/>
+      <c r="F109" s="21"/>
+      <c r="G109" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H109" s="23"/>
+      <c r="I109" s="23"/>
+      <c r="J109" s="23"/>
+      <c r="K109" s="23"/>
+      <c r="L109" s="23"/>
+    </row>
+    <row r="110" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A110" s="20">
+        <v>1845</v>
+      </c>
+      <c r="B110" s="21"/>
+      <c r="C110" s="21">
+        <v>1</v>
+      </c>
+      <c r="D110" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E110" s="21"/>
+      <c r="F110" s="21"/>
+      <c r="G110" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H110" s="23"/>
+      <c r="I110" s="23"/>
+      <c r="J110" s="23"/>
+      <c r="K110" s="23"/>
+      <c r="L110" s="23"/>
+    </row>
+    <row r="111" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A111" s="20">
+        <v>1846</v>
+      </c>
+      <c r="B111" s="21"/>
+      <c r="C111" s="21">
+        <v>1</v>
+      </c>
+      <c r="D111" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E111" s="21"/>
+      <c r="F111" s="21"/>
+      <c r="G111" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H111" s="23"/>
+      <c r="I111" s="23"/>
+      <c r="J111" s="23"/>
+      <c r="K111" s="23"/>
+      <c r="L111" s="23"/>
+    </row>
+    <row r="112" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A112" s="20">
+        <v>1847</v>
+      </c>
+      <c r="B112" s="21"/>
+      <c r="C112" s="21">
+        <v>1</v>
+      </c>
+      <c r="D112" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E112" s="21"/>
+      <c r="F112" s="21"/>
+      <c r="G112" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H112" s="23"/>
+      <c r="I112" s="23"/>
+      <c r="J112" s="23"/>
+      <c r="K112" s="23"/>
+      <c r="L112" s="23"/>
+    </row>
+    <row r="113" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A113" s="20">
+        <v>1848</v>
+      </c>
+      <c r="B113" s="21">
+        <v>1</v>
+      </c>
+      <c r="C113" s="21">
+        <v>1</v>
+      </c>
+      <c r="D113" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E113" s="21">
+        <v>4055233</v>
+      </c>
+      <c r="F113" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H113" s="23"/>
+      <c r="I113" s="23"/>
+      <c r="J113" s="23"/>
+      <c r="K113" s="23"/>
+      <c r="L113" s="23"/>
+    </row>
+    <row r="114" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A114" s="20">
+        <v>1849</v>
+      </c>
+      <c r="B114" s="21"/>
+      <c r="C114" s="21">
+        <v>1</v>
+      </c>
+      <c r="D114" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E114" s="21"/>
+      <c r="F114" s="21"/>
+      <c r="G114" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H114" s="23"/>
+      <c r="I114" s="23"/>
+      <c r="J114" s="23"/>
+      <c r="K114" s="23"/>
+      <c r="L114" s="23"/>
+    </row>
+    <row r="115" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A115" s="20">
+        <v>1850</v>
+      </c>
+      <c r="B115" s="21"/>
+      <c r="C115" s="21">
+        <v>1</v>
+      </c>
+      <c r="D115" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E115" s="21"/>
+      <c r="F115" s="21"/>
+      <c r="G115" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H115" s="23"/>
+      <c r="I115" s="23"/>
+      <c r="J115" s="23"/>
+      <c r="K115" s="23"/>
+      <c r="L115" s="23"/>
+    </row>
+    <row r="116" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A116" s="20">
+        <v>1851</v>
+      </c>
+      <c r="B116" s="21"/>
+      <c r="C116" s="21">
+        <v>1</v>
+      </c>
+      <c r="D116" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E116" s="21"/>
+      <c r="F116" s="21"/>
+      <c r="G116" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H116" s="23"/>
+      <c r="I116" s="23"/>
+      <c r="J116" s="23"/>
+      <c r="K116" s="23"/>
+      <c r="L116" s="23"/>
+    </row>
+    <row r="117" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A117" s="20">
+        <v>1852</v>
+      </c>
+      <c r="B117" s="21"/>
+      <c r="C117" s="21">
+        <v>1</v>
+      </c>
+      <c r="D117" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E117" s="21"/>
+      <c r="F117" s="21"/>
+      <c r="G117" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H117" s="23"/>
+      <c r="I117" s="23"/>
+      <c r="J117" s="23"/>
+      <c r="K117" s="23"/>
+      <c r="L117" s="23"/>
+    </row>
+    <row r="118" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A118" s="12">
+        <v>1861</v>
+      </c>
+      <c r="B118" s="13">
+        <v>1</v>
+      </c>
+      <c r="C118" s="13">
+        <v>1</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E118" s="13">
+        <v>4055251</v>
+      </c>
+      <c r="F118" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G118" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H118" s="14"/>
+      <c r="I118" s="14"/>
+      <c r="J118" s="14"/>
+      <c r="K118" s="14"/>
+      <c r="L118" s="14"/>
+    </row>
+    <row r="119" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A119" s="12">
+        <v>1862</v>
+      </c>
+      <c r="B119" s="13">
+        <v>1</v>
+      </c>
+      <c r="C119" s="13">
+        <v>1</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E119" s="13">
+        <v>4055252</v>
+      </c>
+      <c r="F119" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G119" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H119" s="14"/>
+      <c r="I119" s="14"/>
+      <c r="J119" s="14"/>
+      <c r="K119" s="14"/>
+      <c r="L119" s="14"/>
+    </row>
+    <row r="120" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A120" s="12">
+        <v>1863</v>
+      </c>
+      <c r="B120" s="13"/>
+      <c r="C120" s="13"/>
+      <c r="D120" s="13"/>
+      <c r="E120" s="13"/>
+      <c r="F120" s="13"/>
+      <c r="G120" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H120" s="14"/>
+      <c r="I120" s="14"/>
+      <c r="J120" s="14"/>
+      <c r="K120" s="14"/>
+      <c r="L120" s="14"/>
+    </row>
+    <row r="121" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A121" s="12">
+        <v>1864</v>
+      </c>
+      <c r="B121" s="13">
+        <v>1</v>
+      </c>
+      <c r="C121" s="13">
+        <v>1</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E121" s="13">
+        <v>4055253</v>
+      </c>
+      <c r="F121" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H121" s="14"/>
+      <c r="I121" s="14"/>
+      <c r="J121" s="14"/>
+      <c r="K121" s="14"/>
+      <c r="L121" s="14"/>
+    </row>
+    <row r="122" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A122" s="12">
+        <v>1865</v>
+      </c>
+      <c r="B122" s="13"/>
+      <c r="C122" s="13"/>
+      <c r="D122" s="13"/>
+      <c r="E122" s="13"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H122" s="14"/>
+      <c r="I122" s="14"/>
+      <c r="J122" s="14"/>
+      <c r="K122" s="14"/>
+      <c r="L122" s="14"/>
+    </row>
+    <row r="123" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A123" s="12">
+        <v>1866</v>
+      </c>
+      <c r="B123" s="13"/>
+      <c r="C123" s="13"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="13"/>
+      <c r="F123" s="13"/>
+      <c r="G123" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H123" s="14"/>
+      <c r="I123" s="14"/>
+      <c r="J123" s="14"/>
+      <c r="K123" s="14"/>
+      <c r="L123" s="14"/>
+    </row>
+    <row r="124" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A124" s="12">
+        <v>1867</v>
+      </c>
+      <c r="B124" s="13"/>
+      <c r="C124" s="13"/>
+      <c r="D124" s="13"/>
+      <c r="E124" s="13"/>
+      <c r="F124" s="13"/>
+      <c r="G124" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H124" s="14"/>
+      <c r="I124" s="14"/>
+      <c r="J124" s="14"/>
+      <c r="K124" s="14"/>
+      <c r="L124" s="14"/>
+    </row>
+    <row r="125" customHeight="1" spans="1:12">
+      <c r="A125" s="24">
         <v>6001</v>
       </c>
-      <c r="B91" s="19"/>
-      <c r="C91" s="19">
-        <v>1</v>
-      </c>
-      <c r="D91" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" s="19"/>
-      <c r="F91" s="19"/>
-    </row>
-    <row r="92" customHeight="1" spans="1:12">
-      <c r="A92" s="20">
+      <c r="B125" s="24"/>
+      <c r="C125" s="24">
+        <v>1</v>
+      </c>
+      <c r="D125" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" s="24"/>
+      <c r="F125" s="24"/>
+      <c r="G125" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="1:12">
+      <c r="A126" s="25">
         <v>6011</v>
       </c>
-      <c r="B92" s="20"/>
-      <c r="C92" s="20">
-        <v>1</v>
-      </c>
-      <c r="D92" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" s="20"/>
-      <c r="F92" s="20"/>
-    </row>
-    <row r="93" customHeight="1" spans="1:12">
-      <c r="A93" s="21">
+      <c r="B126" s="25"/>
+      <c r="C126" s="25">
+        <v>1</v>
+      </c>
+      <c r="D126" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E126" s="25"/>
+      <c r="F126" s="25"/>
+      <c r="G126" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="1:12">
+      <c r="A127" s="26">
         <v>6090</v>
       </c>
-      <c r="B93" s="21"/>
-      <c r="C93" s="21">
-        <v>1</v>
-      </c>
-      <c r="D93" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="21"/>
-      <c r="F93" s="21"/>
-    </row>
-    <row r="94" customHeight="1" spans="1:12">
-      <c r="A94" s="21">
+      <c r="B127" s="26"/>
+      <c r="C127" s="26">
+        <v>1</v>
+      </c>
+      <c r="D127" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E127" s="26"/>
+      <c r="F127" s="26"/>
+      <c r="G127" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="1:12">
+      <c r="A128" s="26">
         <v>6091</v>
       </c>
-      <c r="B94" s="21"/>
-      <c r="C94" s="21">
-        <v>1</v>
-      </c>
-      <c r="D94" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E94" s="21"/>
-      <c r="F94" s="21"/>
+      <c r="B128" s="26"/>
+      <c r="C128" s="26">
+        <v>1</v>
+      </c>
+      <c r="D128" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E128" s="26"/>
+      <c r="F128" s="26"/>
+      <c r="G128" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3776,14 +4616,14 @@
         <v>1001</v>
       </c>
       <c r="J5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>1001_</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -3792,7 +4632,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3802,14 +4642,14 @@
         <v>1002</v>
       </c>
       <c r="J6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K18" si="0">I6&amp;J6</f>
         <v>1002_</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3817,14 +4657,14 @@
         <v>1003</v>
       </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>1003_</v>
       </c>
       <c r="M7" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3832,14 +4672,14 @@
         <v>1004</v>
       </c>
       <c r="J8" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>1004_</v>
       </c>
       <c r="M8" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -3847,14 +4687,14 @@
         <v>1005</v>
       </c>
       <c r="J9" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="0"/>
         <v>1005_</v>
       </c>
       <c r="M9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -3862,14 +4702,14 @@
         <v>1006</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="0"/>
         <v>1006_</v>
       </c>
       <c r="M10" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -3877,14 +4717,14 @@
         <v>1007</v>
       </c>
       <c r="J11" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="0"/>
         <v>1007_</v>
       </c>
       <c r="M11" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3892,14 +4732,14 @@
         <v>1008</v>
       </c>
       <c r="J12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="0"/>
         <v>1008_</v>
       </c>
       <c r="M12" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -3907,32 +4747,32 @@
         <v>1009</v>
       </c>
       <c r="J13" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="0"/>
         <v>1009_</v>
       </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I14">
         <v>1010</v>
       </c>
       <c r="J14" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="0"/>
         <v>1010_</v>
       </c>
       <c r="M14" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -3940,14 +4780,14 @@
         <v>1011</v>
       </c>
       <c r="J15" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="0"/>
         <v>1011_</v>
       </c>
       <c r="M15" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -3955,14 +4795,14 @@
         <v>1012</v>
       </c>
       <c r="J16" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="0"/>
         <v>1012_</v>
       </c>
       <c r="M16" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3970,14 +4810,14 @@
         <v>1013</v>
       </c>
       <c r="J17" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="0"/>
         <v>1013_</v>
       </c>
       <c r="M17" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -3985,29 +4825,29 @@
         <v>1014</v>
       </c>
       <c r="J18" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="0"/>
         <v>1014_</v>
       </c>
       <c r="M18" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="50">
   <si>
     <t>序号</t>
   </si>
@@ -256,9 +256,6 @@
   </si>
   <si>
     <t>解锁雇员&amp;雇员升级</t>
-  </si>
-  <si>
-    <t>FASLE</t>
   </si>
   <si>
     <t>解锁联盟&amp;加入联盟</t>
@@ -1581,7 +1578,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L127"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -4222,21 +4219,15 @@
       <c r="A113" s="20">
         <v>1848</v>
       </c>
-      <c r="B113" s="21">
-        <v>1</v>
-      </c>
+      <c r="B113" s="21"/>
       <c r="C113" s="21">
         <v>1</v>
       </c>
       <c r="D113" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="E113" s="21">
-        <v>4055233</v>
-      </c>
-      <c r="F113" s="21" t="s">
-        <v>16</v>
-      </c>
+      <c r="E113" s="21"/>
+      <c r="F113" s="21"/>
       <c r="G113" s="22" t="s">
         <v>26</v>
       </c>
@@ -4272,15 +4263,21 @@
       <c r="A115" s="20">
         <v>1850</v>
       </c>
-      <c r="B115" s="21"/>
+      <c r="B115" s="21">
+        <v>1</v>
+      </c>
       <c r="C115" s="21">
         <v>1</v>
       </c>
       <c r="D115" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="E115" s="21"/>
-      <c r="F115" s="21"/>
+      <c r="E115" s="21">
+        <v>4055233</v>
+      </c>
+      <c r="F115" s="21" t="s">
+        <v>16</v>
+      </c>
       <c r="G115" s="22" t="s">
         <v>26</v>
       </c>
@@ -4334,37 +4331,31 @@
       <c r="K117" s="23"/>
       <c r="L117" s="23"/>
     </row>
-    <row r="118" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A118" s="12">
-        <v>1861</v>
-      </c>
-      <c r="B118" s="13">
-        <v>1</v>
-      </c>
-      <c r="C118" s="13">
-        <v>1</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E118" s="13">
-        <v>4055251</v>
-      </c>
-      <c r="F118" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G118" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="H118" s="14"/>
-      <c r="I118" s="14"/>
-      <c r="J118" s="14"/>
-      <c r="K118" s="14"/>
-      <c r="L118" s="14"/>
+    <row r="118" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A118" s="20">
+        <v>1853</v>
+      </c>
+      <c r="B118" s="21"/>
+      <c r="C118" s="21">
+        <v>1</v>
+      </c>
+      <c r="D118" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E118" s="21"/>
+      <c r="F118" s="21"/>
+      <c r="G118" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H118" s="23"/>
+      <c r="I118" s="23"/>
+      <c r="J118" s="23"/>
+      <c r="K118" s="23"/>
+      <c r="L118" s="23"/>
     </row>
     <row r="119" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A119" s="12">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="B119" s="13">
         <v>1</v>
@@ -4372,17 +4363,17 @@
       <c r="C119" s="13">
         <v>1</v>
       </c>
-      <c r="D119" s="13" t="s">
-        <v>27</v>
+      <c r="D119" s="13" t="b">
+        <v>0</v>
       </c>
       <c r="E119" s="13">
-        <v>4055252</v>
+        <v>4055251</v>
       </c>
       <c r="F119" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H119" s="14"/>
       <c r="I119" s="14"/>
@@ -4392,15 +4383,25 @@
     </row>
     <row r="120" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A120" s="12">
-        <v>1863</v>
-      </c>
-      <c r="B120" s="13"/>
-      <c r="C120" s="13"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
+        <v>1862</v>
+      </c>
+      <c r="B120" s="13">
+        <v>1</v>
+      </c>
+      <c r="C120" s="13">
+        <v>1</v>
+      </c>
+      <c r="D120" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E120" s="13">
+        <v>4055252</v>
+      </c>
+      <c r="F120" s="13" t="s">
+        <v>16</v>
+      </c>
       <c r="G120" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H120" s="14"/>
       <c r="I120" s="14"/>
@@ -4410,25 +4411,15 @@
     </row>
     <row r="121" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A121" s="12">
-        <v>1864</v>
-      </c>
-      <c r="B121" s="13">
-        <v>1</v>
-      </c>
-      <c r="C121" s="13">
-        <v>1</v>
-      </c>
-      <c r="D121" s="13" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B121" s="13"/>
+      <c r="C121" s="13"/>
+      <c r="D121" s="13"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="19" t="s">
         <v>27</v>
-      </c>
-      <c r="E121" s="13">
-        <v>4055253</v>
-      </c>
-      <c r="F121" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G121" s="19" t="s">
-        <v>28</v>
       </c>
       <c r="H121" s="14"/>
       <c r="I121" s="14"/>
@@ -4438,15 +4429,25 @@
     </row>
     <row r="122" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A122" s="12">
-        <v>1865</v>
-      </c>
-      <c r="B122" s="13"/>
-      <c r="C122" s="13"/>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
-      <c r="F122" s="13"/>
+        <v>1864</v>
+      </c>
+      <c r="B122" s="13">
+        <v>1</v>
+      </c>
+      <c r="C122" s="13">
+        <v>1</v>
+      </c>
+      <c r="D122" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E122" s="13">
+        <v>4055253</v>
+      </c>
+      <c r="F122" s="13" t="s">
+        <v>16</v>
+      </c>
       <c r="G122" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H122" s="14"/>
       <c r="I122" s="14"/>
@@ -4456,7 +4457,7 @@
     </row>
     <row r="123" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A123" s="12">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="B123" s="13"/>
       <c r="C123" s="13"/>
@@ -4464,7 +4465,7 @@
       <c r="E123" s="13"/>
       <c r="F123" s="13"/>
       <c r="G123" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H123" s="14"/>
       <c r="I123" s="14"/>
@@ -4472,61 +4473,60 @@
       <c r="K123" s="14"/>
       <c r="L123" s="14"/>
     </row>
-    <row r="124" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A124" s="12">
-        <v>1867</v>
-      </c>
-      <c r="B124" s="13"/>
-      <c r="C124" s="13"/>
-      <c r="D124" s="13"/>
-      <c r="E124" s="13"/>
-      <c r="F124" s="13"/>
-      <c r="G124" s="19" t="s">
+    <row r="124" customHeight="1" spans="1:12">
+      <c r="A124" s="24">
+        <v>6001</v>
+      </c>
+      <c r="B124" s="24"/>
+      <c r="C124" s="24">
+        <v>1</v>
+      </c>
+      <c r="D124" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E124" s="24"/>
+      <c r="F124" s="24"/>
+      <c r="G124" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H124" s="14"/>
-      <c r="I124" s="14"/>
-      <c r="J124" s="14"/>
-      <c r="K124" s="14"/>
-      <c r="L124" s="14"/>
     </row>
     <row r="125" customHeight="1" spans="1:12">
-      <c r="A125" s="24">
-        <v>6001</v>
-      </c>
-      <c r="B125" s="24"/>
-      <c r="C125" s="24">
-        <v>1</v>
-      </c>
-      <c r="D125" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E125" s="24"/>
-      <c r="F125" s="24"/>
+      <c r="A125" s="25">
+        <v>6011</v>
+      </c>
+      <c r="B125" s="25"/>
+      <c r="C125" s="25">
+        <v>1</v>
+      </c>
+      <c r="D125" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" s="25"/>
+      <c r="F125" s="25"/>
       <c r="G125" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:12">
-      <c r="A126" s="25">
-        <v>6011</v>
-      </c>
-      <c r="B126" s="25"/>
-      <c r="C126" s="25">
-        <v>1</v>
-      </c>
-      <c r="D126" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E126" s="25"/>
-      <c r="F126" s="25"/>
+      <c r="A126" s="26">
+        <v>6090</v>
+      </c>
+      <c r="B126" s="26"/>
+      <c r="C126" s="26">
+        <v>1</v>
+      </c>
+      <c r="D126" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E126" s="26"/>
+      <c r="F126" s="26"/>
       <c r="G126" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:12">
       <c r="A127" s="26">
-        <v>6090</v>
+        <v>6091</v>
       </c>
       <c r="B127" s="26"/>
       <c r="C127" s="26">
@@ -4538,24 +4538,7 @@
       <c r="E127" s="26"/>
       <c r="F127" s="26"/>
       <c r="G127" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="128" customHeight="1" spans="1:12">
-      <c r="A128" s="26">
-        <v>6091</v>
-      </c>
-      <c r="B128" s="26"/>
-      <c r="C128" s="26">
-        <v>1</v>
-      </c>
-      <c r="D128" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E128" s="26"/>
-      <c r="F128" s="26"/>
-      <c r="G128" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -4616,14 +4599,14 @@
         <v>1001</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>1001_</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -4632,7 +4615,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4642,14 +4625,14 @@
         <v>1002</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K18" si="0">I6&amp;J6</f>
         <v>1002_</v>
       </c>
       <c r="M6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4657,14 +4640,14 @@
         <v>1003</v>
       </c>
       <c r="J7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>1003_</v>
       </c>
       <c r="M7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4672,14 +4655,14 @@
         <v>1004</v>
       </c>
       <c r="J8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>1004_</v>
       </c>
       <c r="M8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4687,14 +4670,14 @@
         <v>1005</v>
       </c>
       <c r="J9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="0"/>
         <v>1005_</v>
       </c>
       <c r="M9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4702,14 +4685,14 @@
         <v>1006</v>
       </c>
       <c r="J10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="0"/>
         <v>1006_</v>
       </c>
       <c r="M10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4717,14 +4700,14 @@
         <v>1007</v>
       </c>
       <c r="J11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="0"/>
         <v>1007_</v>
       </c>
       <c r="M11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4732,14 +4715,14 @@
         <v>1008</v>
       </c>
       <c r="J12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="0"/>
         <v>1008_</v>
       </c>
       <c r="M12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4747,32 +4730,32 @@
         <v>1009</v>
       </c>
       <c r="J13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="0"/>
         <v>1009_</v>
       </c>
       <c r="M13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I14">
         <v>1010</v>
       </c>
       <c r="J14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="0"/>
         <v>1010_</v>
       </c>
       <c r="M14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4780,14 +4763,14 @@
         <v>1011</v>
       </c>
       <c r="J15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="0"/>
         <v>1011_</v>
       </c>
       <c r="M15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4795,14 +4778,14 @@
         <v>1012</v>
       </c>
       <c r="J16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="0"/>
         <v>1012_</v>
       </c>
       <c r="M16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4810,14 +4793,14 @@
         <v>1013</v>
       </c>
       <c r="J17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="0"/>
         <v>1013_</v>
       </c>
       <c r="M17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4825,29 +4808,29 @@
         <v>1014</v>
       </c>
       <c r="J18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="0"/>
         <v>1014_</v>
       </c>
       <c r="M18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="39">
   <si>
     <t>序号</t>
   </si>
@@ -505,12 +505,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1538,7 +1538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -1547,7 +1547,7 @@
     <col min="4" max="4" width="15.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="56.9083333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28.375" style="1" customWidth="1"/>
     <col min="13" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="13" t="b">
         <v>1</v>
@@ -1725,7 +1725,9 @@
       <c r="C8" s="13">
         <v>1</v>
       </c>
-      <c r="D8" s="13"/>
+      <c r="D8" s="13" t="b">
+        <v>1</v>
+      </c>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
       <c r="G8" s="4" t="s">
@@ -1744,7 +1746,9 @@
       <c r="B9" s="13">
         <v>1</v>
       </c>
-      <c r="C9" s="13"/>
+      <c r="C9" s="13">
+        <v>1</v>
+      </c>
       <c r="D9" s="13" t="b">
         <v>1</v>
       </c>
@@ -1840,7 +1844,9 @@
         <v>1009</v>
       </c>
       <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
+      <c r="C13" s="13">
+        <v>1</v>
+      </c>
       <c r="D13" s="13" t="b">
         <v>1</v>
       </c>
@@ -1952,7 +1958,9 @@
       <c r="D17" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="16"/>
+      <c r="E17" s="16">
+        <v>4055121</v>
+      </c>
       <c r="F17" s="16"/>
       <c r="G17" s="17" t="s">
         <v>18</v>
@@ -1976,7 +1984,9 @@
       <c r="D18" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E18" s="16"/>
+      <c r="E18" s="16">
+        <v>4055122</v>
+      </c>
       <c r="F18" s="16"/>
       <c r="G18" s="17" t="s">
         <v>18</v>
@@ -2000,7 +2010,9 @@
       <c r="D19" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="16"/>
+      <c r="E19" s="16">
+        <v>4055123</v>
+      </c>
       <c r="F19" s="16"/>
       <c r="G19" s="17" t="s">
         <v>18</v>
@@ -2025,11 +2037,9 @@
         <v>1</v>
       </c>
       <c r="E20" s="13">
-        <v>4055131</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>16</v>
-      </c>
+        <v>4055141</v>
+      </c>
+      <c r="F20" s="13"/>
       <c r="G20" s="19" t="s">
         <v>19</v>
       </c>
@@ -2052,7 +2062,9 @@
       <c r="D21" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="13"/>
+      <c r="E21" s="13">
+        <v>4055142</v>
+      </c>
       <c r="F21" s="13"/>
       <c r="G21" s="19" t="s">
         <v>19</v>
@@ -2076,7 +2088,9 @@
       <c r="D22" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E22" s="13"/>
+      <c r="E22" s="13">
+        <v>4055143</v>
+      </c>
       <c r="F22" s="13"/>
       <c r="G22" s="19" t="s">
         <v>19</v>
@@ -2091,9 +2105,7 @@
       <c r="A23" s="12">
         <v>1304</v>
       </c>
-      <c r="B23" s="13">
-        <v>2</v>
-      </c>
+      <c r="B23" s="13"/>
       <c r="C23" s="13">
         <v>1</v>
       </c>
@@ -2133,31 +2145,35 @@
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="12">
-        <v>1306</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13">
-        <v>1</v>
-      </c>
-      <c r="D25" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
+    <row r="25" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="15">
+        <v>1401</v>
+      </c>
+      <c r="B25" s="16">
+        <v>2</v>
+      </c>
+      <c r="C25" s="16">
+        <v>1</v>
+      </c>
+      <c r="D25" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="16">
+        <v>4055161</v>
+      </c>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
     </row>
     <row r="26" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A26" s="15">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B26" s="16">
         <v>2</v>
@@ -2169,11 +2185,9 @@
         <v>1</v>
       </c>
       <c r="E26" s="16">
-        <v>4055141</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>16</v>
-      </c>
+        <v>4055162</v>
+      </c>
+      <c r="F26" s="16"/>
       <c r="G26" s="17" t="s">
         <v>20</v>
       </c>
@@ -2185,7 +2199,7 @@
     </row>
     <row r="27" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A27" s="15">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B27" s="16">
         <v>2</v>
@@ -2197,11 +2211,9 @@
         <v>1</v>
       </c>
       <c r="E27" s="16">
-        <v>4055142</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>16</v>
-      </c>
+        <v>4055163</v>
+      </c>
+      <c r="F27" s="16"/>
       <c r="G27" s="17" t="s">
         <v>20</v>
       </c>
@@ -2213,7 +2225,7 @@
     </row>
     <row r="28" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A28" s="15">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B28" s="16">
         <v>2</v>
@@ -2224,7 +2236,9 @@
       <c r="D28" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E28" s="16"/>
+      <c r="E28" s="16">
+        <v>4055164</v>
+      </c>
       <c r="F28" s="16"/>
       <c r="G28" s="17" t="s">
         <v>20</v>
@@ -2237,11 +2251,9 @@
     </row>
     <row r="29" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A29" s="15">
-        <v>1404</v>
-      </c>
-      <c r="B29" s="16">
-        <v>2</v>
-      </c>
+        <v>1405</v>
+      </c>
+      <c r="B29" s="16"/>
       <c r="C29" s="16">
         <v>1</v>
       </c>
@@ -2261,16 +2273,20 @@
     </row>
     <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A30" s="15">
-        <v>1405</v>
-      </c>
-      <c r="B30" s="16"/>
+        <v>1406</v>
+      </c>
+      <c r="B30" s="16">
+        <v>2</v>
+      </c>
       <c r="C30" s="16">
         <v>1</v>
       </c>
       <c r="D30" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E30" s="16"/>
+      <c r="E30" s="16">
+        <v>4055165</v>
+      </c>
       <c r="F30" s="16"/>
       <c r="G30" s="17" t="s">
         <v>20</v>
@@ -2281,33 +2297,35 @@
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
     </row>
-    <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="15">
-        <v>1406</v>
-      </c>
-      <c r="B31" s="16">
-        <v>2</v>
-      </c>
-      <c r="C31" s="16">
-        <v>1</v>
-      </c>
-      <c r="D31" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
+    <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A31" s="12">
+        <v>1501</v>
+      </c>
+      <c r="B31" s="13">
+        <v>2</v>
+      </c>
+      <c r="C31" s="13">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="13">
+        <v>4055181</v>
+      </c>
+      <c r="F31" s="13"/>
+      <c r="G31" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
     </row>
     <row r="32" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A32" s="12">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B32" s="13">
         <v>2</v>
@@ -2318,7 +2336,9 @@
       <c r="D32" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E32" s="13"/>
+      <c r="E32" s="13">
+        <v>4055182</v>
+      </c>
       <c r="F32" s="13"/>
       <c r="G32" s="19" t="s">
         <v>21</v>
@@ -2331,11 +2351,9 @@
     </row>
     <row r="33" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A33" s="12">
-        <v>1502</v>
-      </c>
-      <c r="B33" s="13">
-        <v>2</v>
-      </c>
+        <v>1503</v>
+      </c>
+      <c r="B33" s="13"/>
       <c r="C33" s="13">
         <v>1</v>
       </c>
@@ -2355,10 +2373,12 @@
     </row>
     <row r="34" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A34" s="12">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
+      <c r="C34" s="13">
+        <v>1</v>
+      </c>
       <c r="D34" s="13" t="b">
         <v>1</v>
       </c>
@@ -2373,47 +2393,41 @@
       <c r="K34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="12">
-        <v>1504</v>
-      </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13">
-        <v>1</v>
-      </c>
-      <c r="D35" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
+    <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A35" s="15">
+        <v>1601</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16">
+        <v>1</v>
+      </c>
+      <c r="D35" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
     </row>
     <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A36" s="15">
-        <v>1601</v>
-      </c>
-      <c r="B36" s="16">
-        <v>1</v>
-      </c>
+        <v>1602</v>
+      </c>
+      <c r="B36" s="16"/>
       <c r="C36" s="16">
         <v>1</v>
       </c>
       <c r="D36" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E36" s="16">
-        <v>4055151</v>
-      </c>
-      <c r="F36" s="16" t="s">
-        <v>16</v>
-      </c>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
       <c r="G36" s="17" t="s">
         <v>22</v>
       </c>
@@ -2425,7 +2439,7 @@
     </row>
     <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A37" s="15">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B37" s="16">
         <v>1</v>
@@ -2437,7 +2451,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="16">
-        <v>4055152</v>
+        <v>4055201</v>
       </c>
       <c r="F37" s="16" t="s">
         <v>16</v>
@@ -2453,10 +2467,10 @@
     </row>
     <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A38" s="15">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B38" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" s="16">
         <v>1</v>
@@ -2464,8 +2478,12 @@
       <c r="D38" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
+      <c r="E38" s="16">
+        <v>4055202</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>16</v>
+      </c>
       <c r="G38" s="17" t="s">
         <v>22</v>
       </c>
@@ -2477,7 +2495,7 @@
     </row>
     <row r="39" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A39" s="15">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B39" s="16">
         <v>2</v>
@@ -2488,7 +2506,9 @@
       <c r="D39" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E39" s="16"/>
+      <c r="E39" s="16">
+        <v>4055203</v>
+      </c>
       <c r="F39" s="16"/>
       <c r="G39" s="17" t="s">
         <v>22</v>
@@ -2501,11 +2521,9 @@
     </row>
     <row r="40" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A40" s="15">
-        <v>1605</v>
-      </c>
-      <c r="B40" s="16">
-        <v>2</v>
-      </c>
+        <v>1606</v>
+      </c>
+      <c r="B40" s="16"/>
       <c r="C40" s="16">
         <v>1</v>
       </c>
@@ -2525,7 +2543,7 @@
     </row>
     <row r="41" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A41" s="15">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B41" s="16">
         <v>2</v>
@@ -2536,7 +2554,9 @@
       <c r="D41" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E41" s="16"/>
+      <c r="E41" s="16">
+        <v>4055204</v>
+      </c>
       <c r="F41" s="16"/>
       <c r="G41" s="17" t="s">
         <v>22</v>
@@ -2549,11 +2569,9 @@
     </row>
     <row r="42" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A42" s="15">
-        <v>1607</v>
-      </c>
-      <c r="B42" s="16">
-        <v>2</v>
-      </c>
+        <v>1608</v>
+      </c>
+      <c r="B42" s="16"/>
       <c r="C42" s="16">
         <v>1</v>
       </c>
@@ -2573,11 +2591,9 @@
     </row>
     <row r="43" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A43" s="15">
-        <v>1608</v>
-      </c>
-      <c r="B43" s="16">
-        <v>2</v>
-      </c>
+        <v>1609</v>
+      </c>
+      <c r="B43" s="16"/>
       <c r="C43" s="16">
         <v>1</v>
       </c>
@@ -2597,7 +2613,7 @@
     </row>
     <row r="44" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A44" s="15">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B44" s="16">
         <v>2</v>
@@ -2608,7 +2624,9 @@
       <c r="D44" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E44" s="16"/>
+      <c r="E44" s="16">
+        <v>4055205</v>
+      </c>
       <c r="F44" s="16"/>
       <c r="G44" s="17" t="s">
         <v>22</v>
@@ -2621,7 +2639,7 @@
     </row>
     <row r="45" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A45" s="15">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B45" s="16">
         <v>2</v>
@@ -2632,7 +2650,9 @@
       <c r="D45" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E45" s="16"/>
+      <c r="E45" s="16">
+        <v>4055206</v>
+      </c>
       <c r="F45" s="16"/>
       <c r="G45" s="17" t="s">
         <v>22</v>
@@ -2645,7 +2665,7 @@
     </row>
     <row r="46" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A46" s="15">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B46" s="16">
         <v>2</v>
@@ -2656,7 +2676,9 @@
       <c r="D46" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E46" s="16"/>
+      <c r="E46" s="16">
+        <v>4055207</v>
+      </c>
       <c r="F46" s="16"/>
       <c r="G46" s="17" t="s">
         <v>22</v>
@@ -2669,7 +2691,7 @@
     </row>
     <row r="47" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A47" s="15">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B47" s="16">
         <v>2</v>
@@ -2680,7 +2702,9 @@
       <c r="D47" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E47" s="16"/>
+      <c r="E47" s="16">
+        <v>4055208</v>
+      </c>
       <c r="F47" s="16"/>
       <c r="G47" s="17" t="s">
         <v>22</v>
@@ -2691,41 +2715,37 @@
       <c r="K47" s="18"/>
       <c r="L47" s="18"/>
     </row>
-    <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="12">
-        <v>1701</v>
-      </c>
-      <c r="B48" s="13">
-        <v>1</v>
-      </c>
-      <c r="C48" s="13">
-        <v>1</v>
-      </c>
-      <c r="D48" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="13">
-        <v>4055171</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
+    <row r="48" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="15">
+        <v>1614</v>
+      </c>
+      <c r="B48" s="16">
+        <v>2</v>
+      </c>
+      <c r="C48" s="16">
+        <v>1</v>
+      </c>
+      <c r="D48" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="16">
+        <v>4055209</v>
+      </c>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
     </row>
     <row r="49" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A49" s="12">
-        <v>1702</v>
-      </c>
-      <c r="B49" s="13">
-        <v>2</v>
-      </c>
+        <v>1701</v>
+      </c>
+      <c r="B49" s="13"/>
       <c r="C49" s="13">
         <v>1</v>
       </c>
@@ -2745,10 +2765,10 @@
     </row>
     <row r="50" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A50" s="12">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="B50" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="13">
         <v>1</v>
@@ -2756,8 +2776,12 @@
       <c r="D50" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
+      <c r="E50" s="13">
+        <v>4055221</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>16</v>
+      </c>
       <c r="G50" s="19" t="s">
         <v>23</v>
       </c>
@@ -2769,7 +2793,7 @@
     </row>
     <row r="51" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A51" s="12">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="B51" s="13">
         <v>2</v>
@@ -2780,7 +2804,9 @@
       <c r="D51" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E51" s="13"/>
+      <c r="E51" s="13">
+        <v>4055222</v>
+      </c>
       <c r="F51" s="13"/>
       <c r="G51" s="19" t="s">
         <v>23</v>
@@ -2793,7 +2819,7 @@
     </row>
     <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A52" s="12">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="B52" s="13">
         <v>2</v>
@@ -2804,7 +2830,9 @@
       <c r="D52" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E52" s="13"/>
+      <c r="E52" s="13">
+        <v>4055223</v>
+      </c>
       <c r="F52" s="13"/>
       <c r="G52" s="19" t="s">
         <v>23</v>
@@ -2817,7 +2845,7 @@
     </row>
     <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A53" s="12">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="B53" s="13">
         <v>2</v>
@@ -2828,7 +2856,9 @@
       <c r="D53" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E53" s="13"/>
+      <c r="E53" s="13">
+        <v>4055224</v>
+      </c>
       <c r="F53" s="13"/>
       <c r="G53" s="19" t="s">
         <v>23</v>
@@ -2841,11 +2871,9 @@
     </row>
     <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A54" s="12">
-        <v>1707</v>
-      </c>
-      <c r="B54" s="13">
-        <v>2</v>
-      </c>
+        <v>1706</v>
+      </c>
+      <c r="B54" s="13"/>
       <c r="C54" s="13">
         <v>1</v>
       </c>
@@ -2865,7 +2893,7 @@
     </row>
     <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A55" s="12">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="B55" s="13">
         <v>2</v>
@@ -2876,7 +2904,9 @@
       <c r="D55" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E55" s="13"/>
+      <c r="E55" s="13">
+        <v>4055225</v>
+      </c>
       <c r="F55" s="13"/>
       <c r="G55" s="19" t="s">
         <v>23</v>
@@ -2889,7 +2919,7 @@
     </row>
     <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A56" s="12">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="B56" s="13">
         <v>2</v>
@@ -2900,7 +2930,9 @@
       <c r="D56" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E56" s="13"/>
+      <c r="E56" s="13">
+        <v>4055226</v>
+      </c>
       <c r="F56" s="13"/>
       <c r="G56" s="19" t="s">
         <v>23</v>
@@ -2913,15 +2945,15 @@
     </row>
     <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A57" s="12">
-        <v>1710</v>
-      </c>
-      <c r="B57" s="13">
-        <v>2</v>
-      </c>
+        <v>1709</v>
+      </c>
+      <c r="B57" s="13"/>
       <c r="C57" s="13">
         <v>1</v>
       </c>
-      <c r="D57" s="13"/>
+      <c r="D57" s="13" t="b">
+        <v>1</v>
+      </c>
       <c r="E57" s="13"/>
       <c r="F57" s="13"/>
       <c r="G57" s="19" t="s">
@@ -2935,15 +2967,15 @@
     </row>
     <row r="58" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A58" s="12">
-        <v>1711</v>
-      </c>
-      <c r="B58" s="13">
-        <v>2</v>
-      </c>
+        <v>1710</v>
+      </c>
+      <c r="B58" s="13"/>
       <c r="C58" s="13">
         <v>1</v>
       </c>
-      <c r="D58" s="13"/>
+      <c r="D58" s="13" t="b">
+        <v>1</v>
+      </c>
       <c r="E58" s="13"/>
       <c r="F58" s="13"/>
       <c r="G58" s="19" t="s">
@@ -2957,14 +2989,20 @@
     </row>
     <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A59" s="12">
-        <v>1712</v>
-      </c>
-      <c r="B59" s="13"/>
+        <v>1711</v>
+      </c>
+      <c r="B59" s="13">
+        <v>2</v>
+      </c>
       <c r="C59" s="13">
         <v>1</v>
       </c>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
+      <c r="D59" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="13">
+        <v>4055227</v>
+      </c>
       <c r="F59" s="13"/>
       <c r="G59" s="19" t="s">
         <v>23</v>
@@ -2975,53 +3013,45 @@
       <c r="K59" s="14"/>
       <c r="L59" s="14"/>
     </row>
-    <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="15">
-        <v>1801</v>
-      </c>
-      <c r="B60" s="16">
-        <v>1</v>
-      </c>
-      <c r="C60" s="16">
-        <v>1</v>
-      </c>
-      <c r="D60" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="16">
-        <v>4055191</v>
-      </c>
-      <c r="F60" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G60" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H60" s="18"/>
-      <c r="I60" s="18"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
-      <c r="L60" s="18"/>
+    <row r="60" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A60" s="12">
+        <v>1712</v>
+      </c>
+      <c r="B60" s="13">
+        <v>2</v>
+      </c>
+      <c r="C60" s="13">
+        <v>1</v>
+      </c>
+      <c r="D60" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="13">
+        <v>4055228</v>
+      </c>
+      <c r="F60" s="13"/>
+      <c r="G60" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
     </row>
     <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A61" s="15">
-        <v>1802</v>
-      </c>
-      <c r="B61" s="16">
-        <v>1</v>
-      </c>
+        <v>1801</v>
+      </c>
+      <c r="B61" s="16"/>
       <c r="C61" s="16">
         <v>1</v>
       </c>
       <c r="D61" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E61" s="16">
-        <v>4055192</v>
-      </c>
-      <c r="F61" s="16" t="s">
-        <v>16</v>
-      </c>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
       <c r="G61" s="17" t="s">
         <v>24</v>
       </c>
@@ -3033,11 +3063,9 @@
     </row>
     <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A62" s="15">
-        <v>1803</v>
-      </c>
-      <c r="B62" s="16">
-        <v>2</v>
-      </c>
+        <v>1802</v>
+      </c>
+      <c r="B62" s="16"/>
       <c r="C62" s="16">
         <v>1</v>
       </c>
@@ -3057,10 +3085,10 @@
     </row>
     <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A63" s="15">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="B63" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" s="16">
         <v>1</v>
@@ -3068,8 +3096,12 @@
       <c r="D63" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
+      <c r="E63" s="16">
+        <v>4055241</v>
+      </c>
+      <c r="F63" s="16" t="s">
+        <v>16</v>
+      </c>
       <c r="G63" s="17" t="s">
         <v>24</v>
       </c>
@@ -3081,10 +3113,10 @@
     </row>
     <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A64" s="15">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="B64" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" s="16">
         <v>1</v>
@@ -3092,8 +3124,12 @@
       <c r="D64" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
+      <c r="E64" s="16">
+        <v>4055242</v>
+      </c>
+      <c r="F64" s="16" t="s">
+        <v>16</v>
+      </c>
       <c r="G64" s="17" t="s">
         <v>24</v>
       </c>
@@ -3105,7 +3141,7 @@
     </row>
     <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A65" s="15">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B65" s="16">
         <v>2</v>
@@ -3116,7 +3152,9 @@
       <c r="D65" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="16">
+        <v>4055243</v>
+      </c>
       <c r="F65" s="16"/>
       <c r="G65" s="17" t="s">
         <v>24</v>
@@ -3129,7 +3167,7 @@
     </row>
     <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A66" s="15">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B66" s="16">
         <v>2</v>
@@ -3140,7 +3178,9 @@
       <c r="D66" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E66" s="16"/>
+      <c r="E66" s="16">
+        <v>4055244</v>
+      </c>
       <c r="F66" s="16"/>
       <c r="G66" s="17" t="s">
         <v>24</v>
@@ -3151,93 +3191,89 @@
       <c r="K66" s="18"/>
       <c r="L66" s="18"/>
     </row>
-    <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="12">
-        <v>1901</v>
-      </c>
-      <c r="B67" s="13">
-        <v>1</v>
-      </c>
-      <c r="C67" s="13">
-        <v>1</v>
-      </c>
-      <c r="D67" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="13">
-        <v>4055211</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H67" s="14"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="14"/>
-      <c r="L67" s="14"/>
-    </row>
-    <row r="68" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="12">
-        <v>1902</v>
-      </c>
-      <c r="B68" s="13">
-        <v>1</v>
-      </c>
-      <c r="C68" s="13">
-        <v>1</v>
-      </c>
-      <c r="D68" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E68" s="13">
-        <v>4055212</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G68" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="14"/>
-      <c r="L68" s="14"/>
-    </row>
-    <row r="69" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A69" s="12">
-        <v>1903</v>
-      </c>
-      <c r="B69" s="13">
-        <v>2</v>
-      </c>
-      <c r="C69" s="13">
-        <v>1</v>
-      </c>
-      <c r="D69" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
+    <row r="67" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A67" s="15">
+        <v>1807</v>
+      </c>
+      <c r="B67" s="16">
+        <v>2</v>
+      </c>
+      <c r="C67" s="16">
+        <v>1</v>
+      </c>
+      <c r="D67" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="16">
+        <v>4055245</v>
+      </c>
+      <c r="F67" s="16"/>
+      <c r="G67" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H67" s="18"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="18"/>
+      <c r="L67" s="18"/>
+    </row>
+    <row r="68" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A68" s="15">
+        <v>1808</v>
+      </c>
+      <c r="B68" s="16">
+        <v>2</v>
+      </c>
+      <c r="C68" s="16">
+        <v>1</v>
+      </c>
+      <c r="D68" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" s="16">
+        <v>4055246</v>
+      </c>
+      <c r="F68" s="16"/>
+      <c r="G68" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H68" s="18"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="18"/>
+      <c r="L68" s="18"/>
+    </row>
+    <row r="69" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A69" s="15">
+        <v>1809</v>
+      </c>
+      <c r="B69" s="16">
+        <v>2</v>
+      </c>
+      <c r="C69" s="16">
+        <v>1</v>
+      </c>
+      <c r="D69" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="16">
+        <v>4055247</v>
+      </c>
+      <c r="F69" s="16"/>
+      <c r="G69" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H69" s="18"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
+      <c r="L69" s="18"/>
     </row>
     <row r="70" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A70" s="12">
-        <v>1904</v>
-      </c>
-      <c r="B70" s="13">
-        <v>2</v>
-      </c>
+        <v>1901</v>
+      </c>
+      <c r="B70" s="13"/>
       <c r="C70" s="13">
         <v>1</v>
       </c>
@@ -3255,115 +3291,119 @@
       <c r="K70" s="14"/>
       <c r="L70" s="14"/>
     </row>
-    <row r="71" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="20">
-        <v>2001</v>
-      </c>
-      <c r="B71" s="21">
-        <v>2</v>
-      </c>
-      <c r="C71" s="21">
-        <v>1</v>
-      </c>
-      <c r="D71" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E71" s="21">
-        <v>4055231</v>
-      </c>
-      <c r="F71" s="21" t="s">
+    <row r="71" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A71" s="12">
+        <v>1902</v>
+      </c>
+      <c r="B71" s="13">
+        <v>1</v>
+      </c>
+      <c r="C71" s="13">
+        <v>1</v>
+      </c>
+      <c r="D71" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="13">
+        <v>4055261</v>
+      </c>
+      <c r="F71" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H71" s="23"/>
-      <c r="I71" s="23"/>
-      <c r="J71" s="23"/>
-      <c r="K71" s="23"/>
-      <c r="L71" s="23"/>
-    </row>
-    <row r="72" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="20">
-        <v>2002</v>
-      </c>
-      <c r="B72" s="21"/>
-      <c r="C72" s="21">
-        <v>1</v>
-      </c>
-      <c r="D72" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E72" s="21">
-        <v>4055232</v>
-      </c>
-      <c r="F72" s="21" t="s">
+      <c r="G71" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="14"/>
+    </row>
+    <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A72" s="12">
+        <v>1903</v>
+      </c>
+      <c r="B72" s="13">
+        <v>1</v>
+      </c>
+      <c r="C72" s="13">
+        <v>1</v>
+      </c>
+      <c r="D72" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="13">
+        <v>4055262</v>
+      </c>
+      <c r="F72" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G72" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H72" s="23"/>
-      <c r="I72" s="23"/>
-      <c r="J72" s="23"/>
-      <c r="K72" s="23"/>
-      <c r="L72" s="23"/>
-    </row>
-    <row r="73" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A73" s="20">
-        <v>2003</v>
-      </c>
-      <c r="B73" s="21">
-        <v>2</v>
-      </c>
-      <c r="C73" s="21">
-        <v>1</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H73" s="23"/>
-      <c r="I73" s="23"/>
-      <c r="J73" s="23"/>
-      <c r="K73" s="23"/>
-      <c r="L73" s="23"/>
-    </row>
-    <row r="74" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="20">
-        <v>2004</v>
-      </c>
-      <c r="B74" s="21">
-        <v>2</v>
-      </c>
-      <c r="C74" s="21">
-        <v>1</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H74" s="23"/>
-      <c r="I74" s="23"/>
-      <c r="J74" s="23"/>
-      <c r="K74" s="23"/>
-      <c r="L74" s="23"/>
+      <c r="G72" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="14"/>
+    </row>
+    <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A73" s="12">
+        <v>1904</v>
+      </c>
+      <c r="B73" s="13">
+        <v>2</v>
+      </c>
+      <c r="C73" s="13">
+        <v>1</v>
+      </c>
+      <c r="D73" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="13">
+        <v>4055263</v>
+      </c>
+      <c r="F73" s="13"/>
+      <c r="G73" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="14"/>
+    </row>
+    <row r="74" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A74" s="12">
+        <v>1905</v>
+      </c>
+      <c r="B74" s="13">
+        <v>2</v>
+      </c>
+      <c r="C74" s="13">
+        <v>1</v>
+      </c>
+      <c r="D74" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="13">
+        <v>4055264</v>
+      </c>
+      <c r="F74" s="13"/>
+      <c r="G74" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="14"/>
     </row>
     <row r="75" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A75" s="20">
-        <v>2005</v>
-      </c>
-      <c r="B75" s="21">
-        <v>2</v>
-      </c>
+        <v>2001</v>
+      </c>
+      <c r="B75" s="21"/>
       <c r="C75" s="21">
         <v>1</v>
       </c>
@@ -3383,7 +3423,7 @@
     </row>
     <row r="76" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A76" s="20">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="B76" s="21">
         <v>2</v>
@@ -3394,7 +3434,9 @@
       <c r="D76" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E76" s="21"/>
+      <c r="E76" s="21">
+        <v>4055281</v>
+      </c>
       <c r="F76" s="21"/>
       <c r="G76" s="22" t="s">
         <v>27</v>
@@ -3407,7 +3449,7 @@
     </row>
     <row r="77" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A77" s="20">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="B77" s="21">
         <v>2</v>
@@ -3418,7 +3460,9 @@
       <c r="D77" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E77" s="21"/>
+      <c r="E77" s="21">
+        <v>4055282</v>
+      </c>
       <c r="F77" s="21"/>
       <c r="G77" s="22" t="s">
         <v>27</v>
@@ -3431,7 +3475,7 @@
     </row>
     <row r="78" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A78" s="20">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="B78" s="21">
         <v>2</v>
@@ -3442,7 +3486,9 @@
       <c r="D78" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E78" s="21"/>
+      <c r="E78" s="21">
+        <v>4055283</v>
+      </c>
       <c r="F78" s="21"/>
       <c r="G78" s="22" t="s">
         <v>27</v>
@@ -3453,77 +3499,161 @@
       <c r="K78" s="23"/>
       <c r="L78" s="23"/>
     </row>
-    <row r="79" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="24">
+    <row r="79" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A79" s="20">
+        <v>2005</v>
+      </c>
+      <c r="B79" s="21">
+        <v>2</v>
+      </c>
+      <c r="C79" s="21">
+        <v>1</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" s="21">
+        <v>4055284</v>
+      </c>
+      <c r="F79" s="21"/>
+      <c r="G79" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H79" s="23"/>
+      <c r="I79" s="23"/>
+      <c r="J79" s="23"/>
+      <c r="K79" s="23"/>
+      <c r="L79" s="23"/>
+    </row>
+    <row r="80" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="20">
+        <v>2006</v>
+      </c>
+      <c r="B80" s="21">
+        <v>2</v>
+      </c>
+      <c r="C80" s="21">
+        <v>1</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E80" s="21">
+        <v>4055285</v>
+      </c>
+      <c r="F80" s="21"/>
+      <c r="G80" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H80" s="23"/>
+      <c r="I80" s="23"/>
+      <c r="J80" s="23"/>
+      <c r="K80" s="23"/>
+      <c r="L80" s="23"/>
+    </row>
+    <row r="81" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A81" s="20">
+        <v>2007</v>
+      </c>
+      <c r="B81" s="21">
+        <v>2</v>
+      </c>
+      <c r="C81" s="21">
+        <v>1</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" s="21">
+        <v>4055286</v>
+      </c>
+      <c r="F81" s="21"/>
+      <c r="G81" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" s="23"/>
+      <c r="I81" s="23"/>
+      <c r="J81" s="23"/>
+      <c r="K81" s="23"/>
+      <c r="L81" s="23"/>
+    </row>
+    <row r="82" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A82" s="24">
         <v>2101</v>
       </c>
-      <c r="B79" s="24">
-        <v>1</v>
-      </c>
-      <c r="C79" s="24">
-        <v>1</v>
-      </c>
-      <c r="D79" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="24"/>
-      <c r="F79" s="24"/>
-      <c r="G79" s="5" t="s">
+      <c r="B82" s="24">
+        <v>1</v>
+      </c>
+      <c r="C82" s="24">
+        <v>1</v>
+      </c>
+      <c r="D82" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="24">
+        <v>4055301</v>
+      </c>
+      <c r="F82" s="24"/>
+      <c r="G82" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H79" s="18"/>
-      <c r="I79" s="18"/>
-      <c r="J79" s="18"/>
-      <c r="K79" s="18"/>
-      <c r="L79" s="18"/>
-    </row>
-    <row r="80" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="24">
+      <c r="H82" s="18"/>
+      <c r="I82" s="18"/>
+      <c r="J82" s="18"/>
+      <c r="K82" s="18"/>
+      <c r="L82" s="18"/>
+    </row>
+    <row r="83" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A83" s="24">
         <v>2102</v>
       </c>
-      <c r="B80" s="24">
-        <v>2</v>
-      </c>
-      <c r="C80" s="24">
-        <v>1</v>
-      </c>
-      <c r="D80" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="5" t="s">
+      <c r="B83" s="24">
+        <v>2</v>
+      </c>
+      <c r="C83" s="24">
+        <v>1</v>
+      </c>
+      <c r="D83" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="24">
+        <v>4055302</v>
+      </c>
+      <c r="F83" s="24"/>
+      <c r="G83" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H80" s="18"/>
-      <c r="I80" s="18"/>
-      <c r="J80" s="18"/>
-      <c r="K80" s="18"/>
-      <c r="L80" s="18"/>
-    </row>
-    <row r="81" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="24">
+      <c r="H83" s="18"/>
+      <c r="I83" s="18"/>
+      <c r="J83" s="18"/>
+      <c r="K83" s="18"/>
+      <c r="L83" s="18"/>
+    </row>
+    <row r="84" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A84" s="24">
         <v>2103</v>
       </c>
-      <c r="B81" s="24">
-        <v>1</v>
-      </c>
-      <c r="C81" s="24">
-        <v>1</v>
-      </c>
-      <c r="D81" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" s="24"/>
-      <c r="F81" s="24"/>
-      <c r="G81" s="5" t="s">
+      <c r="B84" s="24">
+        <v>1</v>
+      </c>
+      <c r="C84" s="24">
+        <v>1</v>
+      </c>
+      <c r="D84" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="24">
+        <v>4055303</v>
+      </c>
+      <c r="F84" s="24"/>
+      <c r="G84" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H81" s="18"/>
-      <c r="I81" s="18"/>
-      <c r="J81" s="18"/>
-      <c r="K81" s="18"/>
-      <c r="L81" s="18"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="18"/>
+      <c r="J84" s="18"/>
+      <c r="K84" s="18"/>
+      <c r="L84" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="40">
   <si>
     <t>序号</t>
   </si>
@@ -257,10 +257,13 @@
     <t>建筑-象财神-升级</t>
   </si>
   <si>
-    <t>赛季-界面</t>
+    <t>赛季-界面-SLOT</t>
   </si>
   <si>
     <t>FASLE</t>
+  </si>
+  <si>
+    <t>赛季-斗仙牌-前置</t>
   </si>
   <si>
     <t>赛季-斗仙牌</t>
@@ -505,12 +508,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -978,7 +981,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1003,9 +1006,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1038,18 +1038,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1538,7 +1526,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -1552,25 +1540,25 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="H1"/>
@@ -1580,7 +1568,7 @@
       <c r="L1"/>
     </row>
     <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1592,13 +1580,13 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="9"/>
+      <c r="G2" s="8"/>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2"/>
@@ -1606,25 +1594,25 @@
       <c r="L2"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="9"/>
+      <c r="G3" s="8"/>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3"/>
@@ -1632,7 +1620,7 @@
       <c r="L3"/>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="11"/>
+      <c r="A4" s="10"/>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4"/>
@@ -1640,2020 +1628,2090 @@
       <c r="L4"/>
     </row>
     <row r="5" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>1001</v>
       </c>
-      <c r="B5" s="13">
-        <v>1</v>
-      </c>
-      <c r="C5" s="13">
-        <v>1</v>
-      </c>
-      <c r="D5" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="13">
+      <c r="B5" s="12">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12">
+        <v>1</v>
+      </c>
+      <c r="D5" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="12">
         <v>4055101</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>1002</v>
       </c>
-      <c r="B6" s="13">
-        <v>1</v>
-      </c>
-      <c r="C6" s="13">
-        <v>1</v>
-      </c>
-      <c r="D6" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="13">
+      <c r="B6" s="12">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12">
+        <v>1</v>
+      </c>
+      <c r="D6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12">
         <v>4055102</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="12">
+      <c r="A7" s="11">
         <v>1003</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13">
-        <v>2</v>
-      </c>
-      <c r="D7" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12">
+        <v>2</v>
+      </c>
+      <c r="D7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
       <c r="G7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>1004</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13">
-        <v>1</v>
-      </c>
-      <c r="D8" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12">
+        <v>1</v>
+      </c>
+      <c r="D8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
       <c r="G8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>1005</v>
       </c>
-      <c r="B9" s="13">
-        <v>1</v>
-      </c>
-      <c r="C9" s="13">
-        <v>1</v>
-      </c>
-      <c r="D9" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="13">
+      <c r="B9" s="12">
+        <v>1</v>
+      </c>
+      <c r="C9" s="12">
+        <v>1</v>
+      </c>
+      <c r="D9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="12">
         <v>4055103</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>1006</v>
       </c>
-      <c r="B10" s="13">
-        <v>1</v>
-      </c>
-      <c r="C10" s="13">
-        <v>1</v>
-      </c>
-      <c r="D10" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="13">
+      <c r="B10" s="12">
+        <v>1</v>
+      </c>
+      <c r="C10" s="12">
+        <v>1</v>
+      </c>
+      <c r="D10" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="12">
         <v>4055104</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="12">
+      <c r="A11" s="11">
         <v>1007</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13">
-        <v>1</v>
-      </c>
-      <c r="D11" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12">
+        <v>1</v>
+      </c>
+      <c r="D11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
       <c r="G11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="12">
+      <c r="A12" s="11">
         <v>1008</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13">
-        <v>1</v>
-      </c>
-      <c r="D12" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
       <c r="G12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="12">
+      <c r="A13" s="11">
         <v>1009</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13">
-        <v>1</v>
-      </c>
-      <c r="D13" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12">
+        <v>1</v>
+      </c>
+      <c r="D13" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
       <c r="G13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
     </row>
     <row r="14" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="12">
+      <c r="A14" s="11">
         <v>1010</v>
       </c>
-      <c r="B14" s="13">
-        <v>1</v>
-      </c>
-      <c r="C14" s="13">
-        <v>1</v>
-      </c>
-      <c r="D14" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="13">
+      <c r="B14" s="12">
+        <v>1</v>
+      </c>
+      <c r="C14" s="12">
+        <v>1</v>
+      </c>
+      <c r="D14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="12">
         <v>4055105</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
     </row>
     <row r="15" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="12">
+      <c r="A15" s="11">
         <v>1011</v>
       </c>
-      <c r="B15" s="13">
-        <v>1</v>
-      </c>
-      <c r="C15" s="13">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="13">
+      <c r="B15" s="12">
+        <v>1</v>
+      </c>
+      <c r="C15" s="12">
+        <v>1</v>
+      </c>
+      <c r="D15" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="12">
         <v>4055106</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
     </row>
     <row r="16" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="12">
+      <c r="A16" s="11">
         <v>1012</v>
       </c>
-      <c r="B16" s="13">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="13">
+      <c r="B16" s="12">
+        <v>1</v>
+      </c>
+      <c r="C16" s="12">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="12">
         <v>4055107</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
     </row>
     <row r="17" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>1201</v>
       </c>
-      <c r="B17" s="16">
-        <v>2</v>
-      </c>
-      <c r="C17" s="16">
-        <v>2</v>
-      </c>
-      <c r="D17" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="16">
+      <c r="B17" s="15">
+        <v>2</v>
+      </c>
+      <c r="C17" s="15">
+        <v>2</v>
+      </c>
+      <c r="D17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
         <v>4055121</v>
       </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17" t="s">
+      <c r="F17" s="15"/>
+      <c r="G17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
     </row>
     <row r="18" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>1202</v>
       </c>
-      <c r="B18" s="16">
-        <v>2</v>
-      </c>
-      <c r="C18" s="16">
-        <v>1</v>
-      </c>
-      <c r="D18" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="16">
+      <c r="B18" s="15">
+        <v>2</v>
+      </c>
+      <c r="C18" s="15">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
         <v>4055122</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17" t="s">
+      <c r="F18" s="15"/>
+      <c r="G18" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
     </row>
     <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>1203</v>
       </c>
-      <c r="B19" s="16">
-        <v>2</v>
-      </c>
-      <c r="C19" s="16">
-        <v>1</v>
-      </c>
-      <c r="D19" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="16">
+      <c r="B19" s="15">
+        <v>2</v>
+      </c>
+      <c r="C19" s="15">
+        <v>1</v>
+      </c>
+      <c r="D19" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15">
         <v>4055123</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="17" t="s">
+      <c r="F19" s="15"/>
+      <c r="G19" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
     </row>
     <row r="20" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="12">
+      <c r="A20" s="11">
         <v>1301</v>
       </c>
-      <c r="B20" s="13">
-        <v>2</v>
-      </c>
-      <c r="C20" s="13">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="13">
+      <c r="B20" s="12">
+        <v>2</v>
+      </c>
+      <c r="C20" s="12">
+        <v>1</v>
+      </c>
+      <c r="D20" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="12">
         <v>4055141</v>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="19" t="s">
+      <c r="F20" s="12"/>
+      <c r="G20" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
     </row>
     <row r="21" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="12">
+      <c r="A21" s="11">
         <v>1302</v>
       </c>
-      <c r="B21" s="13">
-        <v>2</v>
-      </c>
-      <c r="C21" s="13">
-        <v>1</v>
-      </c>
-      <c r="D21" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="13">
+      <c r="B21" s="12">
+        <v>2</v>
+      </c>
+      <c r="C21" s="12">
+        <v>1</v>
+      </c>
+      <c r="D21" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="12">
         <v>4055142</v>
       </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="19" t="s">
+      <c r="F21" s="12"/>
+      <c r="G21" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="12">
+      <c r="A22" s="11">
         <v>1303</v>
       </c>
-      <c r="B22" s="13">
-        <v>2</v>
-      </c>
-      <c r="C22" s="13">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="13">
+      <c r="B22" s="12">
+        <v>2</v>
+      </c>
+      <c r="C22" s="12">
+        <v>1</v>
+      </c>
+      <c r="D22" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="12">
         <v>4055143</v>
       </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="19" t="s">
+      <c r="F22" s="12"/>
+      <c r="G22" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
     </row>
     <row r="23" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A23" s="12">
+      <c r="A23" s="11">
         <v>1304</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="19" t="s">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12">
+        <v>1</v>
+      </c>
+      <c r="D23" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
     </row>
     <row r="24" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A24" s="12">
+      <c r="A24" s="11">
         <v>1305</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13">
-        <v>1</v>
-      </c>
-      <c r="D24" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="19" t="s">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12">
+        <v>1</v>
+      </c>
+      <c r="D24" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
     </row>
     <row r="25" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>1401</v>
       </c>
-      <c r="B25" s="16">
-        <v>2</v>
-      </c>
-      <c r="C25" s="16">
-        <v>1</v>
-      </c>
-      <c r="D25" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="16">
+      <c r="B25" s="15">
+        <v>2</v>
+      </c>
+      <c r="C25" s="15">
+        <v>1</v>
+      </c>
+      <c r="D25" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15">
         <v>4055161</v>
       </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17" t="s">
+      <c r="F25" s="15"/>
+      <c r="G25" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
     </row>
     <row r="26" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="15">
+      <c r="A26" s="14">
         <v>1402</v>
       </c>
-      <c r="B26" s="16">
-        <v>2</v>
-      </c>
-      <c r="C26" s="16">
-        <v>1</v>
-      </c>
-      <c r="D26" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="16">
+      <c r="B26" s="15">
+        <v>2</v>
+      </c>
+      <c r="C26" s="15">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15">
         <v>4055162</v>
       </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17" t="s">
+      <c r="F26" s="15"/>
+      <c r="G26" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
     </row>
     <row r="27" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="15">
+      <c r="A27" s="14">
         <v>1403</v>
       </c>
-      <c r="B27" s="16">
-        <v>2</v>
-      </c>
-      <c r="C27" s="16">
-        <v>1</v>
-      </c>
-      <c r="D27" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="16">
+      <c r="B27" s="15">
+        <v>2</v>
+      </c>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
         <v>4055163</v>
       </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="17" t="s">
+      <c r="F27" s="15"/>
+      <c r="G27" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
     </row>
     <row r="28" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>1404</v>
       </c>
-      <c r="B28" s="16">
-        <v>2</v>
-      </c>
-      <c r="C28" s="16">
-        <v>1</v>
-      </c>
-      <c r="D28" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="16">
+      <c r="B28" s="15">
+        <v>2</v>
+      </c>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
         <v>4055164</v>
       </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="17" t="s">
+      <c r="F28" s="15"/>
+      <c r="G28" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
     </row>
     <row r="29" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="15">
+      <c r="A29" s="14">
         <v>1405</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16">
-        <v>1</v>
-      </c>
-      <c r="D29" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="17" t="s">
+      <c r="B29" s="15"/>
+      <c r="C29" s="15">
+        <v>1</v>
+      </c>
+      <c r="D29" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
     </row>
     <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="15">
+      <c r="A30" s="14">
         <v>1406</v>
       </c>
-      <c r="B30" s="16">
-        <v>2</v>
-      </c>
-      <c r="C30" s="16">
-        <v>1</v>
-      </c>
-      <c r="D30" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="16">
+      <c r="B30" s="15">
+        <v>2</v>
+      </c>
+      <c r="C30" s="15">
+        <v>1</v>
+      </c>
+      <c r="D30" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
         <v>4055165</v>
       </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="17" t="s">
+      <c r="F30" s="15"/>
+      <c r="G30" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
     </row>
     <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="12">
+      <c r="A31" s="11">
         <v>1501</v>
       </c>
-      <c r="B31" s="13">
-        <v>2</v>
-      </c>
-      <c r="C31" s="13">
-        <v>1</v>
-      </c>
-      <c r="D31" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="13">
+      <c r="B31" s="12">
+        <v>2</v>
+      </c>
+      <c r="C31" s="12">
+        <v>1</v>
+      </c>
+      <c r="D31" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="12">
         <v>4055181</v>
       </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="19" t="s">
+      <c r="F31" s="12"/>
+      <c r="G31" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
     </row>
     <row r="32" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="12">
+      <c r="A32" s="11">
         <v>1502</v>
       </c>
-      <c r="B32" s="13">
-        <v>2</v>
-      </c>
-      <c r="C32" s="13">
-        <v>1</v>
-      </c>
-      <c r="D32" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="13">
+      <c r="B32" s="12">
+        <v>2</v>
+      </c>
+      <c r="C32" s="12">
+        <v>1</v>
+      </c>
+      <c r="D32" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="12">
         <v>4055182</v>
       </c>
-      <c r="F32" s="13"/>
-      <c r="G32" s="19" t="s">
+      <c r="F32" s="12"/>
+      <c r="G32" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
     </row>
     <row r="33" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="12">
+      <c r="A33" s="11">
         <v>1503</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13">
-        <v>1</v>
-      </c>
-      <c r="D33" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="19" t="s">
+      <c r="B33" s="12"/>
+      <c r="C33" s="12">
+        <v>1</v>
+      </c>
+      <c r="D33" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
     </row>
     <row r="34" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="12">
+      <c r="A34" s="11">
         <v>1504</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13">
-        <v>1</v>
-      </c>
-      <c r="D34" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="19" t="s">
+      <c r="B34" s="12"/>
+      <c r="C34" s="12">
+        <v>1</v>
+      </c>
+      <c r="D34" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
     </row>
     <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="15">
+      <c r="A35" s="14">
         <v>1601</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16">
-        <v>1</v>
-      </c>
-      <c r="D35" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="17" t="s">
+      <c r="B35" s="15"/>
+      <c r="C35" s="15">
+        <v>1</v>
+      </c>
+      <c r="D35" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
     </row>
     <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="15">
+      <c r="A36" s="14">
         <v>1602</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16">
-        <v>1</v>
-      </c>
-      <c r="D36" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="17" t="s">
+      <c r="B36" s="15"/>
+      <c r="C36" s="15">
+        <v>1</v>
+      </c>
+      <c r="D36" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
     </row>
     <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="15">
+      <c r="A37" s="14">
         <v>1603</v>
       </c>
-      <c r="B37" s="16">
-        <v>1</v>
-      </c>
-      <c r="C37" s="16">
-        <v>1</v>
-      </c>
-      <c r="D37" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="16">
+      <c r="B37" s="15">
+        <v>1</v>
+      </c>
+      <c r="C37" s="15">
+        <v>1</v>
+      </c>
+      <c r="D37" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="15">
         <v>4055201</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="F37" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="17" t="s">
+      <c r="G37" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
     </row>
     <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="15">
+      <c r="A38" s="14">
         <v>1604</v>
       </c>
-      <c r="B38" s="16">
-        <v>1</v>
-      </c>
-      <c r="C38" s="16">
-        <v>1</v>
-      </c>
-      <c r="D38" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="16">
+      <c r="B38" s="15">
+        <v>1</v>
+      </c>
+      <c r="C38" s="15">
+        <v>1</v>
+      </c>
+      <c r="D38" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="15">
         <v>4055202</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="F38" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="17" t="s">
+      <c r="G38" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
     </row>
     <row r="39" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A39" s="15">
+      <c r="A39" s="14">
         <v>1605</v>
       </c>
-      <c r="B39" s="16">
-        <v>2</v>
-      </c>
-      <c r="C39" s="16">
-        <v>1</v>
-      </c>
-      <c r="D39" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="16">
+      <c r="B39" s="15">
+        <v>2</v>
+      </c>
+      <c r="C39" s="15">
+        <v>1</v>
+      </c>
+      <c r="D39" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="15">
         <v>4055203</v>
       </c>
-      <c r="F39" s="16"/>
-      <c r="G39" s="17" t="s">
+      <c r="F39" s="15"/>
+      <c r="G39" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
     </row>
     <row r="40" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="15">
+      <c r="A40" s="14">
         <v>1606</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16">
-        <v>1</v>
-      </c>
-      <c r="D40" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="17" t="s">
+      <c r="B40" s="15"/>
+      <c r="C40" s="15">
+        <v>1</v>
+      </c>
+      <c r="D40" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
     </row>
     <row r="41" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="15">
+      <c r="A41" s="14">
         <v>1607</v>
       </c>
-      <c r="B41" s="16">
-        <v>2</v>
-      </c>
-      <c r="C41" s="16">
-        <v>1</v>
-      </c>
-      <c r="D41" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="16">
+      <c r="B41" s="15">
+        <v>2</v>
+      </c>
+      <c r="C41" s="15">
+        <v>1</v>
+      </c>
+      <c r="D41" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="15">
         <v>4055204</v>
       </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="17" t="s">
+      <c r="F41" s="15"/>
+      <c r="G41" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
     </row>
     <row r="42" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="15">
+      <c r="A42" s="14">
         <v>1608</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16">
-        <v>1</v>
-      </c>
-      <c r="D42" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="17" t="s">
+      <c r="B42" s="15"/>
+      <c r="C42" s="15">
+        <v>1</v>
+      </c>
+      <c r="D42" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
     </row>
     <row r="43" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="15">
+      <c r="A43" s="14">
         <v>1609</v>
       </c>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16">
-        <v>1</v>
-      </c>
-      <c r="D43" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="17" t="s">
+      <c r="B43" s="15"/>
+      <c r="C43" s="15">
+        <v>1</v>
+      </c>
+      <c r="D43" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="18"/>
-      <c r="L43" s="18"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
     </row>
     <row r="44" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="15">
+      <c r="A44" s="14">
         <v>1610</v>
       </c>
-      <c r="B44" s="16">
-        <v>2</v>
-      </c>
-      <c r="C44" s="16">
-        <v>1</v>
-      </c>
-      <c r="D44" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="16">
+      <c r="B44" s="15">
+        <v>2</v>
+      </c>
+      <c r="C44" s="15">
+        <v>1</v>
+      </c>
+      <c r="D44" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="15">
         <v>4055205</v>
       </c>
-      <c r="F44" s="16"/>
-      <c r="G44" s="17" t="s">
+      <c r="F44" s="15"/>
+      <c r="G44" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
     </row>
     <row r="45" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="15">
+      <c r="A45" s="14">
         <v>1611</v>
       </c>
-      <c r="B45" s="16">
-        <v>2</v>
-      </c>
-      <c r="C45" s="16">
-        <v>1</v>
-      </c>
-      <c r="D45" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="16">
+      <c r="B45" s="15">
+        <v>2</v>
+      </c>
+      <c r="C45" s="15">
+        <v>1</v>
+      </c>
+      <c r="D45" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="15">
         <v>4055206</v>
       </c>
-      <c r="F45" s="16"/>
-      <c r="G45" s="17" t="s">
+      <c r="F45" s="15"/>
+      <c r="G45" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
     </row>
     <row r="46" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="15">
+      <c r="A46" s="14">
         <v>1612</v>
       </c>
-      <c r="B46" s="16">
-        <v>2</v>
-      </c>
-      <c r="C46" s="16">
-        <v>1</v>
-      </c>
-      <c r="D46" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="16">
+      <c r="B46" s="15">
+        <v>2</v>
+      </c>
+      <c r="C46" s="15">
+        <v>1</v>
+      </c>
+      <c r="D46" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="15">
         <v>4055207</v>
       </c>
-      <c r="F46" s="16"/>
-      <c r="G46" s="17" t="s">
+      <c r="F46" s="15"/>
+      <c r="G46" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="18"/>
-      <c r="K46" s="18"/>
-      <c r="L46" s="18"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
     </row>
     <row r="47" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="15">
+      <c r="A47" s="14">
         <v>1613</v>
       </c>
-      <c r="B47" s="16">
-        <v>2</v>
-      </c>
-      <c r="C47" s="16">
-        <v>1</v>
-      </c>
-      <c r="D47" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="16">
+      <c r="B47" s="15">
+        <v>2</v>
+      </c>
+      <c r="C47" s="15">
+        <v>1</v>
+      </c>
+      <c r="D47" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="15">
         <v>4055208</v>
       </c>
-      <c r="F47" s="16"/>
-      <c r="G47" s="17" t="s">
+      <c r="F47" s="15"/>
+      <c r="G47" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="18"/>
-      <c r="K47" s="18"/>
-      <c r="L47" s="18"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
     </row>
     <row r="48" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="15">
+      <c r="A48" s="14">
         <v>1614</v>
       </c>
-      <c r="B48" s="16">
-        <v>2</v>
-      </c>
-      <c r="C48" s="16">
-        <v>1</v>
-      </c>
-      <c r="D48" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="16">
+      <c r="B48" s="15">
+        <v>2</v>
+      </c>
+      <c r="C48" s="15">
+        <v>1</v>
+      </c>
+      <c r="D48" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="15">
         <v>4055209</v>
       </c>
-      <c r="F48" s="16"/>
-      <c r="G48" s="17" t="s">
+      <c r="F48" s="15"/>
+      <c r="G48" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="18"/>
-      <c r="K48" s="18"/>
-      <c r="L48" s="18"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
     </row>
     <row r="49" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="12">
+      <c r="A49" s="11">
         <v>1701</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13">
-        <v>1</v>
-      </c>
-      <c r="D49" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="19" t="s">
+      <c r="B49" s="12"/>
+      <c r="C49" s="12">
+        <v>1</v>
+      </c>
+      <c r="D49" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="13"/>
     </row>
     <row r="50" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A50" s="12">
+      <c r="A50" s="11">
         <v>1702</v>
       </c>
-      <c r="B50" s="13">
-        <v>1</v>
-      </c>
-      <c r="C50" s="13">
-        <v>1</v>
-      </c>
-      <c r="D50" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" s="13">
+      <c r="B50" s="12">
+        <v>1</v>
+      </c>
+      <c r="C50" s="12">
+        <v>1</v>
+      </c>
+      <c r="D50" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" s="12">
         <v>4055221</v>
       </c>
-      <c r="F50" s="13" t="s">
+      <c r="F50" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G50" s="19" t="s">
+      <c r="G50" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
     </row>
     <row r="51" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A51" s="12">
+      <c r="A51" s="11">
         <v>1703</v>
       </c>
-      <c r="B51" s="13">
-        <v>2</v>
-      </c>
-      <c r="C51" s="13">
-        <v>1</v>
-      </c>
-      <c r="D51" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="13">
+      <c r="B51" s="12">
+        <v>2</v>
+      </c>
+      <c r="C51" s="12">
+        <v>1</v>
+      </c>
+      <c r="D51" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="12">
         <v>4055222</v>
       </c>
-      <c r="F51" s="13"/>
-      <c r="G51" s="19" t="s">
+      <c r="F51" s="12"/>
+      <c r="G51" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
     </row>
     <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A52" s="12">
+      <c r="A52" s="11">
         <v>1704</v>
       </c>
-      <c r="B52" s="13">
-        <v>2</v>
-      </c>
-      <c r="C52" s="13">
-        <v>1</v>
-      </c>
-      <c r="D52" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="13">
+      <c r="B52" s="12">
+        <v>2</v>
+      </c>
+      <c r="C52" s="12">
+        <v>1</v>
+      </c>
+      <c r="D52" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="12">
         <v>4055223</v>
       </c>
-      <c r="F52" s="13"/>
-      <c r="G52" s="19" t="s">
+      <c r="F52" s="12"/>
+      <c r="G52" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
     </row>
     <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A53" s="12">
+      <c r="A53" s="11">
         <v>1705</v>
       </c>
-      <c r="B53" s="13">
-        <v>2</v>
-      </c>
-      <c r="C53" s="13">
-        <v>1</v>
-      </c>
-      <c r="D53" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="13">
+      <c r="B53" s="12">
+        <v>2</v>
+      </c>
+      <c r="C53" s="12">
+        <v>1</v>
+      </c>
+      <c r="D53" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="12">
         <v>4055224</v>
       </c>
-      <c r="F53" s="13"/>
-      <c r="G53" s="19" t="s">
+      <c r="F53" s="12"/>
+      <c r="G53" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
     </row>
     <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A54" s="12">
+      <c r="A54" s="11">
         <v>1706</v>
       </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13">
-        <v>1</v>
-      </c>
-      <c r="D54" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="19" t="s">
+      <c r="B54" s="12"/>
+      <c r="C54" s="12">
+        <v>1</v>
+      </c>
+      <c r="D54" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
     </row>
     <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A55" s="12">
+      <c r="A55" s="11">
         <v>1707</v>
       </c>
-      <c r="B55" s="13">
-        <v>2</v>
-      </c>
-      <c r="C55" s="13">
-        <v>1</v>
-      </c>
-      <c r="D55" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="13">
+      <c r="B55" s="12">
+        <v>2</v>
+      </c>
+      <c r="C55" s="12">
+        <v>1</v>
+      </c>
+      <c r="D55" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="12">
         <v>4055225</v>
       </c>
-      <c r="F55" s="13"/>
-      <c r="G55" s="19" t="s">
+      <c r="F55" s="12"/>
+      <c r="G55" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
     </row>
     <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A56" s="12">
+      <c r="A56" s="11">
         <v>1708</v>
       </c>
-      <c r="B56" s="13">
-        <v>2</v>
-      </c>
-      <c r="C56" s="13">
-        <v>1</v>
-      </c>
-      <c r="D56" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="13">
+      <c r="B56" s="12">
+        <v>2</v>
+      </c>
+      <c r="C56" s="12">
+        <v>1</v>
+      </c>
+      <c r="D56" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="12">
         <v>4055226</v>
       </c>
-      <c r="F56" s="13"/>
-      <c r="G56" s="19" t="s">
+      <c r="F56" s="12"/>
+      <c r="G56" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13"/>
     </row>
     <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A57" s="12">
+      <c r="A57" s="11">
         <v>1709</v>
       </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13">
-        <v>1</v>
-      </c>
-      <c r="D57" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="19" t="s">
+      <c r="B57" s="12"/>
+      <c r="C57" s="12">
+        <v>1</v>
+      </c>
+      <c r="D57" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
     </row>
     <row r="58" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A58" s="12">
+      <c r="A58" s="11">
         <v>1710</v>
       </c>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13">
-        <v>1</v>
-      </c>
-      <c r="D58" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="19" t="s">
+      <c r="B58" s="12"/>
+      <c r="C58" s="12">
+        <v>1</v>
+      </c>
+      <c r="D58" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="13"/>
     </row>
     <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="12">
+      <c r="A59" s="11">
         <v>1711</v>
       </c>
-      <c r="B59" s="13">
-        <v>2</v>
-      </c>
-      <c r="C59" s="13">
-        <v>1</v>
-      </c>
-      <c r="D59" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="13">
+      <c r="B59" s="12">
+        <v>2</v>
+      </c>
+      <c r="C59" s="12">
+        <v>1</v>
+      </c>
+      <c r="D59" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="12">
         <v>4055227</v>
       </c>
-      <c r="F59" s="13"/>
-      <c r="G59" s="19" t="s">
+      <c r="F59" s="12"/>
+      <c r="G59" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H59" s="14"/>
-      <c r="I59" s="14"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="14"/>
-      <c r="L59" s="14"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
     </row>
     <row r="60" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="12">
+      <c r="A60" s="11">
         <v>1712</v>
       </c>
-      <c r="B60" s="13">
-        <v>2</v>
-      </c>
-      <c r="C60" s="13">
-        <v>1</v>
-      </c>
-      <c r="D60" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="13">
+      <c r="B60" s="12">
+        <v>2</v>
+      </c>
+      <c r="C60" s="12">
+        <v>1</v>
+      </c>
+      <c r="D60" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="12">
         <v>4055228</v>
       </c>
-      <c r="F60" s="13"/>
-      <c r="G60" s="19" t="s">
+      <c r="F60" s="12"/>
+      <c r="G60" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
     </row>
     <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="15">
+      <c r="A61" s="14">
         <v>1801</v>
       </c>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16">
-        <v>1</v>
-      </c>
-      <c r="D61" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="17" t="s">
+      <c r="B61" s="15"/>
+      <c r="C61" s="15">
+        <v>1</v>
+      </c>
+      <c r="D61" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H61" s="18"/>
-      <c r="I61" s="18"/>
-      <c r="J61" s="18"/>
-      <c r="K61" s="18"/>
-      <c r="L61" s="18"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="17"/>
     </row>
     <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A62" s="15">
+      <c r="A62" s="14">
         <v>1802</v>
       </c>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16">
-        <v>1</v>
-      </c>
-      <c r="D62" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="17" t="s">
+      <c r="B62" s="15"/>
+      <c r="C62" s="15">
+        <v>1</v>
+      </c>
+      <c r="D62" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="15"/>
+      <c r="F62" s="15"/>
+      <c r="G62" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H62" s="18"/>
-      <c r="I62" s="18"/>
-      <c r="J62" s="18"/>
-      <c r="K62" s="18"/>
-      <c r="L62" s="18"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="17"/>
     </row>
     <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A63" s="15">
+      <c r="A63" s="14">
         <v>1803</v>
       </c>
-      <c r="B63" s="16">
-        <v>1</v>
-      </c>
-      <c r="C63" s="16">
-        <v>1</v>
-      </c>
-      <c r="D63" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="16">
+      <c r="B63" s="15">
+        <v>1</v>
+      </c>
+      <c r="C63" s="15">
+        <v>1</v>
+      </c>
+      <c r="D63" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="15">
         <v>4055241</v>
       </c>
-      <c r="F63" s="16" t="s">
+      <c r="F63" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G63" s="17" t="s">
+      <c r="G63" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H63" s="18"/>
-      <c r="I63" s="18"/>
-      <c r="J63" s="18"/>
-      <c r="K63" s="18"/>
-      <c r="L63" s="18"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="17"/>
+      <c r="K63" s="17"/>
+      <c r="L63" s="17"/>
     </row>
     <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A64" s="15">
+      <c r="A64" s="14">
         <v>1804</v>
       </c>
-      <c r="B64" s="16">
-        <v>1</v>
-      </c>
-      <c r="C64" s="16">
-        <v>1</v>
-      </c>
-      <c r="D64" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="16">
+      <c r="B64" s="15">
+        <v>1</v>
+      </c>
+      <c r="C64" s="15">
+        <v>1</v>
+      </c>
+      <c r="D64" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="15">
         <v>4055242</v>
       </c>
-      <c r="F64" s="16" t="s">
+      <c r="F64" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="17" t="s">
+      <c r="G64" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H64" s="18"/>
-      <c r="I64" s="18"/>
-      <c r="J64" s="18"/>
-      <c r="K64" s="18"/>
-      <c r="L64" s="18"/>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="17"/>
+      <c r="K64" s="17"/>
+      <c r="L64" s="17"/>
     </row>
     <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A65" s="15">
+      <c r="A65" s="14">
         <v>1805</v>
       </c>
-      <c r="B65" s="16">
-        <v>2</v>
-      </c>
-      <c r="C65" s="16">
-        <v>1</v>
-      </c>
-      <c r="D65" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="16">
+      <c r="B65" s="15">
+        <v>2</v>
+      </c>
+      <c r="C65" s="15">
+        <v>1</v>
+      </c>
+      <c r="D65" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="15">
         <v>4055243</v>
       </c>
-      <c r="F65" s="16"/>
-      <c r="G65" s="17" t="s">
+      <c r="F65" s="15"/>
+      <c r="G65" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H65" s="18"/>
-      <c r="I65" s="18"/>
-      <c r="J65" s="18"/>
-      <c r="K65" s="18"/>
-      <c r="L65" s="18"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="17"/>
+      <c r="K65" s="17"/>
+      <c r="L65" s="17"/>
     </row>
     <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="15">
+      <c r="A66" s="14">
         <v>1806</v>
       </c>
-      <c r="B66" s="16">
-        <v>2</v>
-      </c>
-      <c r="C66" s="16">
-        <v>1</v>
-      </c>
-      <c r="D66" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="16">
+      <c r="B66" s="15">
+        <v>2</v>
+      </c>
+      <c r="C66" s="15">
+        <v>1</v>
+      </c>
+      <c r="D66" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="15">
         <v>4055244</v>
       </c>
-      <c r="F66" s="16"/>
-      <c r="G66" s="17" t="s">
+      <c r="F66" s="15"/>
+      <c r="G66" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H66" s="18"/>
-      <c r="I66" s="18"/>
-      <c r="J66" s="18"/>
-      <c r="K66" s="18"/>
-      <c r="L66" s="18"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
+      <c r="L66" s="17"/>
     </row>
     <row r="67" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="15">
+      <c r="A67" s="14">
         <v>1807</v>
       </c>
-      <c r="B67" s="16">
-        <v>2</v>
-      </c>
-      <c r="C67" s="16">
-        <v>1</v>
-      </c>
-      <c r="D67" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="16">
+      <c r="B67" s="15">
+        <v>2</v>
+      </c>
+      <c r="C67" s="15">
+        <v>1</v>
+      </c>
+      <c r="D67" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="15">
         <v>4055245</v>
       </c>
-      <c r="F67" s="16"/>
-      <c r="G67" s="17" t="s">
+      <c r="F67" s="15"/>
+      <c r="G67" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H67" s="18"/>
-      <c r="I67" s="18"/>
-      <c r="J67" s="18"/>
-      <c r="K67" s="18"/>
-      <c r="L67" s="18"/>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
     </row>
     <row r="68" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="15">
+      <c r="A68" s="14">
         <v>1808</v>
       </c>
-      <c r="B68" s="16">
-        <v>2</v>
-      </c>
-      <c r="C68" s="16">
-        <v>1</v>
-      </c>
-      <c r="D68" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E68" s="16">
+      <c r="B68" s="15">
+        <v>2</v>
+      </c>
+      <c r="C68" s="15">
+        <v>1</v>
+      </c>
+      <c r="D68" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" s="15">
         <v>4055246</v>
       </c>
-      <c r="F68" s="16"/>
-      <c r="G68" s="17" t="s">
+      <c r="F68" s="15"/>
+      <c r="G68" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H68" s="18"/>
-      <c r="I68" s="18"/>
-      <c r="J68" s="18"/>
-      <c r="K68" s="18"/>
-      <c r="L68" s="18"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
+      <c r="L68" s="17"/>
     </row>
     <row r="69" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A69" s="15">
+      <c r="A69" s="14">
         <v>1809</v>
       </c>
-      <c r="B69" s="16">
-        <v>2</v>
-      </c>
-      <c r="C69" s="16">
-        <v>1</v>
-      </c>
-      <c r="D69" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" s="16">
+      <c r="B69" s="15">
+        <v>2</v>
+      </c>
+      <c r="C69" s="15">
+        <v>1</v>
+      </c>
+      <c r="D69" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="15">
         <v>4055247</v>
       </c>
-      <c r="F69" s="16"/>
-      <c r="G69" s="17" t="s">
+      <c r="F69" s="15"/>
+      <c r="G69" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H69" s="18"/>
-      <c r="I69" s="18"/>
-      <c r="J69" s="18"/>
-      <c r="K69" s="18"/>
-      <c r="L69" s="18"/>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="17"/>
+      <c r="K69" s="17"/>
+      <c r="L69" s="17"/>
     </row>
     <row r="70" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="12">
+      <c r="A70" s="11">
         <v>1901</v>
       </c>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13">
-        <v>1</v>
-      </c>
-      <c r="D70" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="19" t="s">
+      <c r="B70" s="12"/>
+      <c r="C70" s="12">
+        <v>1</v>
+      </c>
+      <c r="D70" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="13"/>
+      <c r="L70" s="13"/>
     </row>
     <row r="71" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="12">
+      <c r="A71" s="11">
         <v>1902</v>
       </c>
-      <c r="B71" s="13">
-        <v>1</v>
-      </c>
-      <c r="C71" s="13">
-        <v>1</v>
-      </c>
-      <c r="D71" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" s="13">
+      <c r="B71" s="12">
+        <v>1</v>
+      </c>
+      <c r="C71" s="12">
+        <v>1</v>
+      </c>
+      <c r="D71" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="12">
         <v>4055261</v>
       </c>
-      <c r="F71" s="13" t="s">
+      <c r="F71" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="19" t="s">
+      <c r="G71" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H71" s="14"/>
-      <c r="I71" s="14"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="14"/>
-      <c r="L71" s="14"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="13"/>
+      <c r="L71" s="13"/>
     </row>
     <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="12">
+      <c r="A72" s="11">
         <v>1903</v>
       </c>
-      <c r="B72" s="13">
-        <v>1</v>
-      </c>
-      <c r="C72" s="13">
-        <v>1</v>
-      </c>
-      <c r="D72" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" s="13">
+      <c r="B72" s="12">
+        <v>1</v>
+      </c>
+      <c r="C72" s="12">
+        <v>1</v>
+      </c>
+      <c r="D72" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="12">
         <v>4055262</v>
       </c>
-      <c r="F72" s="13" t="s">
+      <c r="F72" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G72" s="19" t="s">
+      <c r="G72" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14"/>
-      <c r="L72" s="14"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
+      <c r="K72" s="13"/>
+      <c r="L72" s="13"/>
     </row>
     <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A73" s="12">
+      <c r="A73" s="11">
         <v>1904</v>
       </c>
-      <c r="B73" s="13">
-        <v>2</v>
-      </c>
-      <c r="C73" s="13">
-        <v>1</v>
-      </c>
-      <c r="D73" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" s="13">
+      <c r="B73" s="12">
+        <v>2</v>
+      </c>
+      <c r="C73" s="12">
+        <v>1</v>
+      </c>
+      <c r="D73" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="12">
         <v>4055263</v>
       </c>
-      <c r="F73" s="13"/>
-      <c r="G73" s="19" t="s">
+      <c r="F73" s="12"/>
+      <c r="G73" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
-      <c r="J73" s="14"/>
-      <c r="K73" s="14"/>
-      <c r="L73" s="14"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+      <c r="K73" s="13"/>
+      <c r="L73" s="13"/>
     </row>
     <row r="74" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="12">
+      <c r="A74" s="11">
         <v>1905</v>
       </c>
-      <c r="B74" s="13">
-        <v>2</v>
-      </c>
-      <c r="C74" s="13">
-        <v>1</v>
-      </c>
-      <c r="D74" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" s="13">
+      <c r="B74" s="12">
+        <v>2</v>
+      </c>
+      <c r="C74" s="12">
+        <v>1</v>
+      </c>
+      <c r="D74" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="12">
         <v>4055264</v>
       </c>
-      <c r="F74" s="13"/>
-      <c r="G74" s="19" t="s">
+      <c r="F74" s="12"/>
+      <c r="G74" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14"/>
-      <c r="K74" s="14"/>
-      <c r="L74" s="14"/>
-    </row>
-    <row r="75" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="20">
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+      <c r="K74" s="13"/>
+      <c r="L74" s="13"/>
+    </row>
+    <row r="75" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A75" s="14">
+        <v>1981</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="15">
+        <v>1</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" s="17"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
+      <c r="L75" s="17"/>
+    </row>
+    <row r="76" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A76" s="14">
+        <v>1982</v>
+      </c>
+      <c r="B76" s="15"/>
+      <c r="C76" s="15">
+        <v>1</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" s="15"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H76" s="17"/>
+      <c r="I76" s="17"/>
+      <c r="J76" s="17"/>
+      <c r="K76" s="17"/>
+      <c r="L76" s="17"/>
+    </row>
+    <row r="77" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A77" s="14">
+        <v>1983</v>
+      </c>
+      <c r="B77" s="15">
+        <v>2</v>
+      </c>
+      <c r="C77" s="15">
+        <v>1</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" s="15">
+        <v>4055321</v>
+      </c>
+      <c r="F77" s="15"/>
+      <c r="G77" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
+      <c r="K77" s="17"/>
+      <c r="L77" s="17"/>
+    </row>
+    <row r="78" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A78" s="11">
         <v>2001</v>
       </c>
-      <c r="B75" s="21"/>
-      <c r="C75" s="21">
-        <v>1</v>
-      </c>
-      <c r="D75" s="21" t="s">
+      <c r="B78" s="12"/>
+      <c r="C78" s="12">
+        <v>1</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23"/>
-      <c r="J75" s="23"/>
-      <c r="K75" s="23"/>
-      <c r="L75" s="23"/>
-    </row>
-    <row r="76" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A76" s="20">
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13"/>
+      <c r="K78" s="13"/>
+      <c r="L78" s="13"/>
+    </row>
+    <row r="79" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A79" s="11">
         <v>2002</v>
       </c>
-      <c r="B76" s="21">
-        <v>2</v>
-      </c>
-      <c r="C76" s="21">
-        <v>1</v>
-      </c>
-      <c r="D76" s="21" t="s">
+      <c r="B79" s="12">
+        <v>2</v>
+      </c>
+      <c r="C79" s="12">
+        <v>1</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E76" s="21">
+      <c r="E79" s="12">
         <v>4055281</v>
       </c>
-      <c r="F76" s="21"/>
-      <c r="G76" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H76" s="23"/>
-      <c r="I76" s="23"/>
-      <c r="J76" s="23"/>
-      <c r="K76" s="23"/>
-      <c r="L76" s="23"/>
-    </row>
-    <row r="77" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A77" s="20">
+      <c r="F79" s="12"/>
+      <c r="G79" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13"/>
+      <c r="K79" s="13"/>
+      <c r="L79" s="13"/>
+    </row>
+    <row r="80" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="11">
         <v>2003</v>
       </c>
-      <c r="B77" s="21">
-        <v>2</v>
-      </c>
-      <c r="C77" s="21">
-        <v>1</v>
-      </c>
-      <c r="D77" s="21" t="s">
+      <c r="B80" s="12">
+        <v>2</v>
+      </c>
+      <c r="C80" s="12">
+        <v>1</v>
+      </c>
+      <c r="D80" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E77" s="21">
+      <c r="E80" s="12">
         <v>4055282</v>
       </c>
-      <c r="F77" s="21"/>
-      <c r="G77" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H77" s="23"/>
-      <c r="I77" s="23"/>
-      <c r="J77" s="23"/>
-      <c r="K77" s="23"/>
-      <c r="L77" s="23"/>
-    </row>
-    <row r="78" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A78" s="20">
+      <c r="F80" s="12"/>
+      <c r="G80" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="13"/>
+      <c r="K80" s="13"/>
+      <c r="L80" s="13"/>
+    </row>
+    <row r="81" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A81" s="11">
         <v>2004</v>
       </c>
-      <c r="B78" s="21">
-        <v>2</v>
-      </c>
-      <c r="C78" s="21">
-        <v>1</v>
-      </c>
-      <c r="D78" s="21" t="s">
+      <c r="B81" s="12">
+        <v>2</v>
+      </c>
+      <c r="C81" s="12">
+        <v>1</v>
+      </c>
+      <c r="D81" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E78" s="21">
+      <c r="E81" s="12">
         <v>4055283</v>
       </c>
-      <c r="F78" s="21"/>
-      <c r="G78" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H78" s="23"/>
-      <c r="I78" s="23"/>
-      <c r="J78" s="23"/>
-      <c r="K78" s="23"/>
-      <c r="L78" s="23"/>
-    </row>
-    <row r="79" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="20">
+      <c r="F81" s="12"/>
+      <c r="G81" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="13"/>
+      <c r="K81" s="13"/>
+      <c r="L81" s="13"/>
+    </row>
+    <row r="82" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A82" s="11">
         <v>2005</v>
       </c>
-      <c r="B79" s="21">
-        <v>2</v>
-      </c>
-      <c r="C79" s="21">
-        <v>1</v>
-      </c>
-      <c r="D79" s="21" t="s">
+      <c r="B82" s="12">
+        <v>2</v>
+      </c>
+      <c r="C82" s="12">
+        <v>1</v>
+      </c>
+      <c r="D82" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E79" s="21">
+      <c r="E82" s="12">
         <v>4055284</v>
       </c>
-      <c r="F79" s="21"/>
-      <c r="G79" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="23"/>
-      <c r="K79" s="23"/>
-      <c r="L79" s="23"/>
-    </row>
-    <row r="80" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="20">
+      <c r="F82" s="12"/>
+      <c r="G82" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="13"/>
+      <c r="K82" s="13"/>
+      <c r="L82" s="13"/>
+    </row>
+    <row r="83" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A83" s="11">
         <v>2006</v>
       </c>
-      <c r="B80" s="21">
-        <v>2</v>
-      </c>
-      <c r="C80" s="21">
-        <v>1</v>
-      </c>
-      <c r="D80" s="21" t="s">
+      <c r="B83" s="12">
+        <v>2</v>
+      </c>
+      <c r="C83" s="12">
+        <v>1</v>
+      </c>
+      <c r="D83" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E80" s="21">
+      <c r="E83" s="12">
         <v>4055285</v>
       </c>
-      <c r="F80" s="21"/>
-      <c r="G80" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
-      <c r="J80" s="23"/>
-      <c r="K80" s="23"/>
-      <c r="L80" s="23"/>
-    </row>
-    <row r="81" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="20">
+      <c r="F83" s="12"/>
+      <c r="G83" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H83" s="13"/>
+      <c r="I83" s="13"/>
+      <c r="J83" s="13"/>
+      <c r="K83" s="13"/>
+      <c r="L83" s="13"/>
+    </row>
+    <row r="84" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A84" s="11">
         <v>2007</v>
       </c>
-      <c r="B81" s="21">
-        <v>2</v>
-      </c>
-      <c r="C81" s="21">
-        <v>1</v>
-      </c>
-      <c r="D81" s="21" t="s">
+      <c r="B84" s="12">
+        <v>2</v>
+      </c>
+      <c r="C84" s="12">
+        <v>1</v>
+      </c>
+      <c r="D84" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E81" s="21">
+      <c r="E84" s="12">
         <v>4055286</v>
       </c>
-      <c r="F81" s="21"/>
-      <c r="G81" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H81" s="23"/>
-      <c r="I81" s="23"/>
-      <c r="J81" s="23"/>
-      <c r="K81" s="23"/>
-      <c r="L81" s="23"/>
-    </row>
-    <row r="82" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="24">
+      <c r="F84" s="12"/>
+      <c r="G84" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="13"/>
+      <c r="K84" s="13"/>
+      <c r="L84" s="13"/>
+    </row>
+    <row r="85" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A85" s="19">
         <v>2101</v>
       </c>
-      <c r="B82" s="24">
-        <v>1</v>
-      </c>
-      <c r="C82" s="24">
-        <v>1</v>
-      </c>
-      <c r="D82" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" s="24">
+      <c r="B85" s="19">
+        <v>1</v>
+      </c>
+      <c r="C85" s="19">
+        <v>1</v>
+      </c>
+      <c r="D85" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="19">
         <v>4055301</v>
       </c>
-      <c r="F82" s="24"/>
-      <c r="G82" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H82" s="18"/>
-      <c r="I82" s="18"/>
-      <c r="J82" s="18"/>
-      <c r="K82" s="18"/>
-      <c r="L82" s="18"/>
-    </row>
-    <row r="83" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A83" s="24">
+      <c r="F85" s="19"/>
+      <c r="G85" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H85" s="17"/>
+      <c r="I85" s="17"/>
+      <c r="J85" s="17"/>
+      <c r="K85" s="17"/>
+      <c r="L85" s="17"/>
+    </row>
+    <row r="86" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A86" s="19">
         <v>2102</v>
       </c>
-      <c r="B83" s="24">
-        <v>2</v>
-      </c>
-      <c r="C83" s="24">
-        <v>1</v>
-      </c>
-      <c r="D83" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="24">
+      <c r="B86" s="19">
+        <v>2</v>
+      </c>
+      <c r="C86" s="19">
+        <v>1</v>
+      </c>
+      <c r="D86" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="19">
         <v>4055302</v>
       </c>
-      <c r="F83" s="24"/>
-      <c r="G83" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H83" s="18"/>
-      <c r="I83" s="18"/>
-      <c r="J83" s="18"/>
-      <c r="K83" s="18"/>
-      <c r="L83" s="18"/>
-    </row>
-    <row r="84" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A84" s="24">
+      <c r="F86" s="19"/>
+      <c r="G86" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H86" s="17"/>
+      <c r="I86" s="17"/>
+      <c r="J86" s="17"/>
+      <c r="K86" s="17"/>
+      <c r="L86" s="17"/>
+    </row>
+    <row r="87" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A87" s="19">
         <v>2103</v>
       </c>
-      <c r="B84" s="24">
-        <v>1</v>
-      </c>
-      <c r="C84" s="24">
-        <v>1</v>
-      </c>
-      <c r="D84" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" s="24">
+      <c r="B87" s="19">
+        <v>1</v>
+      </c>
+      <c r="C87" s="19">
+        <v>1</v>
+      </c>
+      <c r="D87" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="19">
         <v>4055303</v>
       </c>
-      <c r="F84" s="24"/>
-      <c r="G84" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H84" s="18"/>
-      <c r="I84" s="18"/>
-      <c r="J84" s="18"/>
-      <c r="K84" s="18"/>
-      <c r="L84" s="18"/>
+      <c r="F87" s="19"/>
+      <c r="G87" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H87" s="17"/>
+      <c r="I87" s="17"/>
+      <c r="J87" s="17"/>
+      <c r="K87" s="17"/>
+      <c r="L87" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3713,14 +3771,14 @@
         <v>2101</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2101_</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -3729,7 +3787,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3739,14 +3797,14 @@
         <v>2102</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2102_</v>
       </c>
       <c r="M6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3754,14 +3812,14 @@
         <v>2103</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2103_</v>
       </c>
       <c r="M7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3769,34 +3827,34 @@
         <v>2104</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2104_</v>
       </c>
       <c r="M8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="40">
   <si>
     <t>序号</t>
   </si>
@@ -508,12 +508,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1526,7 +1526,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -1631,12 +1631,8 @@
       <c r="A5" s="11">
         <v>1001</v>
       </c>
-      <c r="B5" s="12">
-        <v>1</v>
-      </c>
-      <c r="C5" s="12">
-        <v>1</v>
-      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
       <c r="D5" s="12" t="b">
         <v>1</v>
       </c>
@@ -1659,12 +1655,8 @@
       <c r="A6" s="11">
         <v>1002</v>
       </c>
-      <c r="B6" s="12">
-        <v>1</v>
-      </c>
-      <c r="C6" s="12">
-        <v>1</v>
-      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
       <c r="D6" s="12" t="b">
         <v>1</v>
       </c>
@@ -1688,14 +1680,16 @@
         <v>1003</v>
       </c>
       <c r="B7" s="12"/>
-      <c r="C7" s="12">
-        <v>2</v>
-      </c>
+      <c r="C7" s="12"/>
       <c r="D7" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+      <c r="E7" s="12">
+        <v>4055103</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="G7" s="4" t="s">
         <v>17</v>
       </c>
@@ -1710,9 +1704,7 @@
         <v>1004</v>
       </c>
       <c r="B8" s="12"/>
-      <c r="C8" s="12">
-        <v>1</v>
-      </c>
+      <c r="C8" s="12"/>
       <c r="D8" s="12" t="b">
         <v>1</v>
       </c>
@@ -1731,21 +1723,13 @@
       <c r="A9" s="11">
         <v>1005</v>
       </c>
-      <c r="B9" s="12">
-        <v>1</v>
-      </c>
-      <c r="C9" s="12">
-        <v>1</v>
-      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
       <c r="D9" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="12">
-        <v>4055103</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
       <c r="G9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1759,12 +1743,8 @@
       <c r="A10" s="11">
         <v>1006</v>
       </c>
-      <c r="B10" s="12">
-        <v>1</v>
-      </c>
-      <c r="C10" s="12">
-        <v>1</v>
-      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
       <c r="D10" s="12" t="b">
         <v>1</v>
       </c>
@@ -1788,14 +1768,16 @@
         <v>1007</v>
       </c>
       <c r="B11" s="12"/>
-      <c r="C11" s="12">
-        <v>1</v>
-      </c>
+      <c r="C11" s="12"/>
       <c r="D11" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="E11" s="12">
+        <v>4055105</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="G11" s="4" t="s">
         <v>17</v>
       </c>
@@ -1810,9 +1792,7 @@
         <v>1008</v>
       </c>
       <c r="B12" s="12"/>
-      <c r="C12" s="12">
-        <v>1</v>
-      </c>
+      <c r="C12" s="12"/>
       <c r="D12" s="12" t="b">
         <v>1</v>
       </c>
@@ -1832,9 +1812,7 @@
         <v>1009</v>
       </c>
       <c r="B13" s="12"/>
-      <c r="C13" s="12">
-        <v>1</v>
-      </c>
+      <c r="C13" s="12"/>
       <c r="D13" s="12" t="b">
         <v>1</v>
       </c>
@@ -1853,21 +1831,13 @@
       <c r="A14" s="11">
         <v>1010</v>
       </c>
-      <c r="B14" s="12">
-        <v>1</v>
-      </c>
-      <c r="C14" s="12">
-        <v>1</v>
-      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
       <c r="D14" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="12">
-        <v>4055105</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
       <c r="G14" s="4" t="s">
         <v>17</v>
       </c>
@@ -1881,12 +1851,8 @@
       <c r="A15" s="11">
         <v>1011</v>
       </c>
-      <c r="B15" s="12">
-        <v>1</v>
-      </c>
-      <c r="C15" s="12">
-        <v>1</v>
-      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
       <c r="D15" s="12" t="b">
         <v>1</v>
       </c>
@@ -1909,12 +1875,8 @@
       <c r="A16" s="11">
         <v>1012</v>
       </c>
-      <c r="B16" s="12">
-        <v>1</v>
-      </c>
-      <c r="C16" s="12">
-        <v>1</v>
-      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
       <c r="D16" s="12" t="b">
         <v>1</v>
       </c>
@@ -1933,49 +1895,49 @@
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
     </row>
-    <row r="17" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="14">
-        <v>1201</v>
-      </c>
-      <c r="B17" s="15">
-        <v>2</v>
-      </c>
-      <c r="C17" s="15">
-        <v>2</v>
-      </c>
-      <c r="D17" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="15">
-        <v>4055121</v>
-      </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
+    <row r="17" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A17" s="11">
+        <v>1013</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="12">
+        <v>4055108</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
     </row>
     <row r="18" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A18" s="14">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B18" s="15">
         <v>2</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15" t="b">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>4055122</v>
-      </c>
-      <c r="F18" s="15"/>
+        <v>4055121</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>16</v>
+      </c>
       <c r="G18" s="16" t="s">
         <v>18</v>
       </c>
@@ -1987,7 +1949,7 @@
     </row>
     <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A19" s="14">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B19" s="15">
         <v>2</v>
@@ -1999,9 +1961,11 @@
         <v>1</v>
       </c>
       <c r="E19" s="15">
-        <v>4055123</v>
-      </c>
-      <c r="F19" s="15"/>
+        <v>4055122</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>16</v>
+      </c>
       <c r="G19" s="16" t="s">
         <v>18</v>
       </c>
@@ -2011,35 +1975,37 @@
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
     </row>
-    <row r="20" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="11">
-        <v>1301</v>
-      </c>
-      <c r="B20" s="12">
-        <v>2</v>
-      </c>
-      <c r="C20" s="12">
-        <v>1</v>
-      </c>
-      <c r="D20" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="12">
-        <v>4055141</v>
-      </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
+    <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A20" s="14">
+        <v>1203</v>
+      </c>
+      <c r="B20" s="15">
+        <v>2</v>
+      </c>
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>4055123</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
     </row>
     <row r="21" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A21" s="11">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B21" s="12">
         <v>2</v>
@@ -2051,9 +2017,11 @@
         <v>1</v>
       </c>
       <c r="E21" s="12">
-        <v>4055142</v>
-      </c>
-      <c r="F21" s="12"/>
+        <v>4055141</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="G21" s="18" t="s">
         <v>19</v>
       </c>
@@ -2065,7 +2033,7 @@
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A22" s="11">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B22" s="12">
         <v>2</v>
@@ -2077,9 +2045,11 @@
         <v>1</v>
       </c>
       <c r="E22" s="12">
-        <v>4055143</v>
-      </c>
-      <c r="F22" s="12"/>
+        <v>4055142</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="G22" s="18" t="s">
         <v>19</v>
       </c>
@@ -2091,17 +2061,23 @@
     </row>
     <row r="23" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A23" s="11">
-        <v>1304</v>
-      </c>
-      <c r="B23" s="12"/>
+        <v>1303</v>
+      </c>
+      <c r="B23" s="12">
+        <v>2</v>
+      </c>
       <c r="C23" s="12">
         <v>1</v>
       </c>
       <c r="D23" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="E23" s="12">
+        <v>4055143</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="G23" s="18" t="s">
         <v>19</v>
       </c>
@@ -2113,7 +2089,7 @@
     </row>
     <row r="24" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A24" s="11">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12">
@@ -2133,35 +2109,31 @@
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
     </row>
-    <row r="25" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="14">
-        <v>1401</v>
-      </c>
-      <c r="B25" s="15">
-        <v>2</v>
-      </c>
-      <c r="C25" s="15">
-        <v>1</v>
-      </c>
-      <c r="D25" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="15">
-        <v>4055161</v>
-      </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
+    <row r="25" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="11">
+        <v>1305</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12">
+        <v>1</v>
+      </c>
+      <c r="D25" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
     </row>
     <row r="26" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A26" s="14">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B26" s="15">
         <v>2</v>
@@ -2173,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="15">
-        <v>4055162</v>
+        <v>4055161</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="16" t="s">
@@ -2187,7 +2159,7 @@
     </row>
     <row r="27" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A27" s="14">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B27" s="15">
         <v>2</v>
@@ -2199,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>4055163</v>
+        <v>4055162</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="16" t="s">
@@ -2213,7 +2185,7 @@
     </row>
     <row r="28" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A28" s="14">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B28" s="15">
         <v>2</v>
@@ -2225,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>4055164</v>
+        <v>4055163</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="16" t="s">
@@ -2239,16 +2211,20 @@
     </row>
     <row r="29" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A29" s="14">
-        <v>1405</v>
-      </c>
-      <c r="B29" s="15"/>
+        <v>1404</v>
+      </c>
+      <c r="B29" s="15">
+        <v>2</v>
+      </c>
       <c r="C29" s="15">
         <v>1</v>
       </c>
       <c r="D29" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E29" s="15"/>
+      <c r="E29" s="15">
+        <v>4055164</v>
+      </c>
       <c r="F29" s="15"/>
       <c r="G29" s="16" t="s">
         <v>20</v>
@@ -2261,20 +2237,16 @@
     </row>
     <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A30" s="14">
-        <v>1406</v>
-      </c>
-      <c r="B30" s="15">
-        <v>2</v>
-      </c>
+        <v>1405</v>
+      </c>
+      <c r="B30" s="15"/>
       <c r="C30" s="15">
         <v>1</v>
       </c>
       <c r="D30" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E30" s="15">
-        <v>4055165</v>
-      </c>
+      <c r="E30" s="15"/>
       <c r="F30" s="15"/>
       <c r="G30" s="16" t="s">
         <v>20</v>
@@ -2285,35 +2257,35 @@
       <c r="K30" s="17"/>
       <c r="L30" s="17"/>
     </row>
-    <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="11">
-        <v>1501</v>
-      </c>
-      <c r="B31" s="12">
-        <v>2</v>
-      </c>
-      <c r="C31" s="12">
-        <v>1</v>
-      </c>
-      <c r="D31" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="12">
-        <v>4055181</v>
-      </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
+    <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A31" s="14">
+        <v>1406</v>
+      </c>
+      <c r="B31" s="15">
+        <v>2</v>
+      </c>
+      <c r="C31" s="15">
+        <v>1</v>
+      </c>
+      <c r="D31" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>4055165</v>
+      </c>
+      <c r="F31" s="15"/>
+      <c r="G31" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
     </row>
     <row r="32" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A32" s="11">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B32" s="12">
         <v>2</v>
@@ -2325,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="12">
-        <v>4055182</v>
+        <v>4055181</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="18" t="s">
@@ -2339,16 +2311,20 @@
     </row>
     <row r="33" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A33" s="11">
-        <v>1503</v>
-      </c>
-      <c r="B33" s="12"/>
+        <v>1502</v>
+      </c>
+      <c r="B33" s="12">
+        <v>2</v>
+      </c>
       <c r="C33" s="12">
         <v>1</v>
       </c>
       <c r="D33" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E33" s="12"/>
+      <c r="E33" s="12">
+        <v>4055182</v>
+      </c>
       <c r="F33" s="12"/>
       <c r="G33" s="18" t="s">
         <v>21</v>
@@ -2361,7 +2337,7 @@
     </row>
     <row r="34" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A34" s="11">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12">
@@ -2381,31 +2357,31 @@
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
     </row>
-    <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="14">
-        <v>1601</v>
-      </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15">
-        <v>1</v>
-      </c>
-      <c r="D35" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
+    <row r="35" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A35" s="11">
+        <v>1504</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12">
+        <v>1</v>
+      </c>
+      <c r="D35" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
     </row>
     <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A36" s="14">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15">
@@ -2427,23 +2403,17 @@
     </row>
     <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A37" s="14">
-        <v>1603</v>
-      </c>
-      <c r="B37" s="15">
-        <v>1</v>
-      </c>
+        <v>1602</v>
+      </c>
+      <c r="B37" s="15"/>
       <c r="C37" s="15">
         <v>1</v>
       </c>
       <c r="D37" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E37" s="15">
-        <v>4055201</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>16</v>
-      </c>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
       <c r="G37" s="16" t="s">
         <v>22</v>
       </c>
@@ -2455,11 +2425,9 @@
     </row>
     <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A38" s="14">
-        <v>1604</v>
-      </c>
-      <c r="B38" s="15">
-        <v>1</v>
-      </c>
+        <v>1603</v>
+      </c>
+      <c r="B38" s="15"/>
       <c r="C38" s="15">
         <v>1</v>
       </c>
@@ -2467,9 +2435,9 @@
         <v>1</v>
       </c>
       <c r="E38" s="15">
-        <v>4055202</v>
-      </c>
-      <c r="F38" s="15" t="s">
+        <v>4055203</v>
+      </c>
+      <c r="F38" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G38" s="16" t="s">
@@ -2483,20 +2451,16 @@
     </row>
     <row r="39" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A39" s="14">
-        <v>1605</v>
-      </c>
-      <c r="B39" s="15">
-        <v>2</v>
-      </c>
+        <v>1604</v>
+      </c>
+      <c r="B39" s="15"/>
       <c r="C39" s="15">
         <v>1</v>
       </c>
       <c r="D39" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E39" s="15">
-        <v>4055203</v>
-      </c>
+      <c r="E39" s="15"/>
       <c r="F39" s="15"/>
       <c r="G39" s="16" t="s">
         <v>22</v>
@@ -2509,17 +2473,23 @@
     </row>
     <row r="40" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A40" s="14">
-        <v>1606</v>
-      </c>
-      <c r="B40" s="15"/>
+        <v>1605</v>
+      </c>
+      <c r="B40" s="15">
+        <v>2</v>
+      </c>
       <c r="C40" s="15">
         <v>1</v>
       </c>
       <c r="D40" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
+      <c r="E40" s="15">
+        <v>4055204</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="G40" s="16" t="s">
         <v>22</v>
       </c>
@@ -2531,20 +2501,16 @@
     </row>
     <row r="41" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A41" s="14">
-        <v>1607</v>
-      </c>
-      <c r="B41" s="15">
-        <v>2</v>
-      </c>
+        <v>1606</v>
+      </c>
+      <c r="B41" s="15"/>
       <c r="C41" s="15">
         <v>1</v>
       </c>
       <c r="D41" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E41" s="15">
-        <v>4055204</v>
-      </c>
+      <c r="E41" s="15"/>
       <c r="F41" s="15"/>
       <c r="G41" s="16" t="s">
         <v>22</v>
@@ -2557,9 +2523,11 @@
     </row>
     <row r="42" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A42" s="14">
-        <v>1608</v>
-      </c>
-      <c r="B42" s="15"/>
+        <v>1607</v>
+      </c>
+      <c r="B42" s="15">
+        <v>2</v>
+      </c>
       <c r="C42" s="15">
         <v>1</v>
       </c>
@@ -2579,7 +2547,7 @@
     </row>
     <row r="43" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A43" s="14">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15">
@@ -2588,8 +2556,12 @@
       <c r="D43" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
+      <c r="E43" s="15">
+        <v>4055205</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="G43" s="16" t="s">
         <v>22</v>
       </c>
@@ -2601,11 +2573,9 @@
     </row>
     <row r="44" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A44" s="14">
-        <v>1610</v>
-      </c>
-      <c r="B44" s="15">
-        <v>2</v>
-      </c>
+        <v>1609</v>
+      </c>
+      <c r="B44" s="15"/>
       <c r="C44" s="15">
         <v>1</v>
       </c>
@@ -2613,9 +2583,11 @@
         <v>1</v>
       </c>
       <c r="E44" s="15">
-        <v>4055205</v>
-      </c>
-      <c r="F44" s="15"/>
+        <v>4055206</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="G44" s="16" t="s">
         <v>22</v>
       </c>
@@ -2627,7 +2599,7 @@
     </row>
     <row r="45" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A45" s="14">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B45" s="15">
         <v>2</v>
@@ -2639,9 +2611,11 @@
         <v>1</v>
       </c>
       <c r="E45" s="15">
-        <v>4055206</v>
-      </c>
-      <c r="F45" s="15"/>
+        <v>4055207</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="G45" s="16" t="s">
         <v>22</v>
       </c>
@@ -2653,7 +2627,7 @@
     </row>
     <row r="46" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A46" s="14">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="B46" s="15">
         <v>2</v>
@@ -2665,9 +2639,11 @@
         <v>1</v>
       </c>
       <c r="E46" s="15">
-        <v>4055207</v>
-      </c>
-      <c r="F46" s="15"/>
+        <v>4055208</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="G46" s="16" t="s">
         <v>22</v>
       </c>
@@ -2679,7 +2655,7 @@
     </row>
     <row r="47" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A47" s="14">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B47" s="15">
         <v>2</v>
@@ -2691,9 +2667,11 @@
         <v>1</v>
       </c>
       <c r="E47" s="15">
-        <v>4055208</v>
-      </c>
-      <c r="F47" s="15"/>
+        <v>4055209</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="G47" s="16" t="s">
         <v>22</v>
       </c>
@@ -2703,44 +2681,44 @@
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
     </row>
-    <row r="48" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="14">
-        <v>1614</v>
-      </c>
-      <c r="B48" s="15">
-        <v>2</v>
-      </c>
-      <c r="C48" s="15">
-        <v>1</v>
-      </c>
-      <c r="D48" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="15">
-        <v>4055209</v>
-      </c>
-      <c r="F48" s="15"/>
-      <c r="G48" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
+    <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="11">
+        <v>1701</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12">
+        <v>1</v>
+      </c>
+      <c r="D48" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
     </row>
     <row r="49" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A49" s="11">
-        <v>1701</v>
-      </c>
-      <c r="B49" s="12"/>
+        <v>1702</v>
+      </c>
+      <c r="B49" s="12">
+        <v>2</v>
+      </c>
       <c r="C49" s="12">
         <v>1</v>
       </c>
       <c r="D49" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E49" s="12"/>
+      <c r="E49" s="12">
+        <v>4055222</v>
+      </c>
       <c r="F49" s="12"/>
       <c r="G49" s="18" t="s">
         <v>23</v>
@@ -2753,10 +2731,10 @@
     </row>
     <row r="50" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A50" s="11">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B50" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" s="12">
         <v>1</v>
@@ -2765,11 +2743,9 @@
         <v>1</v>
       </c>
       <c r="E50" s="12">
-        <v>4055221</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>16</v>
-      </c>
+        <v>4055223</v>
+      </c>
+      <c r="F50" s="12"/>
       <c r="G50" s="18" t="s">
         <v>23</v>
       </c>
@@ -2781,7 +2757,7 @@
     </row>
     <row r="51" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A51" s="11">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B51" s="12">
         <v>2</v>
@@ -2793,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="12">
-        <v>4055222</v>
+        <v>4055224</v>
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="18" t="s">
@@ -2807,20 +2783,16 @@
     </row>
     <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A52" s="11">
-        <v>1704</v>
-      </c>
-      <c r="B52" s="12">
-        <v>2</v>
-      </c>
+        <v>1705</v>
+      </c>
+      <c r="B52" s="12"/>
       <c r="C52" s="12">
         <v>1</v>
       </c>
       <c r="D52" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E52" s="12">
-        <v>4055223</v>
-      </c>
+      <c r="E52" s="12"/>
       <c r="F52" s="12"/>
       <c r="G52" s="18" t="s">
         <v>23</v>
@@ -2833,7 +2805,7 @@
     </row>
     <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A53" s="11">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B53" s="12">
         <v>2</v>
@@ -2845,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="12">
-        <v>4055224</v>
+        <v>4055225</v>
       </c>
       <c r="F53" s="12"/>
       <c r="G53" s="18" t="s">
@@ -2859,16 +2831,20 @@
     </row>
     <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A54" s="11">
-        <v>1706</v>
-      </c>
-      <c r="B54" s="12"/>
+        <v>1707</v>
+      </c>
+      <c r="B54" s="12">
+        <v>2</v>
+      </c>
       <c r="C54" s="12">
         <v>1</v>
       </c>
       <c r="D54" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E54" s="12"/>
+      <c r="E54" s="12">
+        <v>4055226</v>
+      </c>
       <c r="F54" s="12"/>
       <c r="G54" s="18" t="s">
         <v>23</v>
@@ -2881,20 +2857,16 @@
     </row>
     <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A55" s="11">
-        <v>1707</v>
-      </c>
-      <c r="B55" s="12">
-        <v>2</v>
-      </c>
+        <v>1708</v>
+      </c>
+      <c r="B55" s="12"/>
       <c r="C55" s="12">
         <v>1</v>
       </c>
       <c r="D55" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E55" s="12">
-        <v>4055225</v>
-      </c>
+      <c r="E55" s="12"/>
       <c r="F55" s="12"/>
       <c r="G55" s="18" t="s">
         <v>23</v>
@@ -2907,20 +2879,16 @@
     </row>
     <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A56" s="11">
-        <v>1708</v>
-      </c>
-      <c r="B56" s="12">
-        <v>2</v>
-      </c>
+        <v>1709</v>
+      </c>
+      <c r="B56" s="12"/>
       <c r="C56" s="12">
         <v>1</v>
       </c>
       <c r="D56" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E56" s="12">
-        <v>4055226</v>
-      </c>
+      <c r="E56" s="12"/>
       <c r="F56" s="12"/>
       <c r="G56" s="18" t="s">
         <v>23</v>
@@ -2933,16 +2901,20 @@
     </row>
     <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A57" s="11">
-        <v>1709</v>
-      </c>
-      <c r="B57" s="12"/>
+        <v>1710</v>
+      </c>
+      <c r="B57" s="12">
+        <v>2</v>
+      </c>
       <c r="C57" s="12">
         <v>1</v>
       </c>
       <c r="D57" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E57" s="12"/>
+      <c r="E57" s="12">
+        <v>4055227</v>
+      </c>
       <c r="F57" s="12"/>
       <c r="G57" s="18" t="s">
         <v>23</v>
@@ -2955,16 +2927,20 @@
     </row>
     <row r="58" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A58" s="11">
-        <v>1710</v>
-      </c>
-      <c r="B58" s="12"/>
+        <v>1711</v>
+      </c>
+      <c r="B58" s="12">
+        <v>2</v>
+      </c>
       <c r="C58" s="12">
         <v>1</v>
       </c>
       <c r="D58" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E58" s="12"/>
+      <c r="E58" s="12">
+        <v>4055228</v>
+      </c>
       <c r="F58" s="12"/>
       <c r="G58" s="18" t="s">
         <v>23</v>
@@ -2975,71 +2951,69 @@
       <c r="K58" s="13"/>
       <c r="L58" s="13"/>
     </row>
-    <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="11">
-        <v>1711</v>
-      </c>
-      <c r="B59" s="12">
-        <v>2</v>
-      </c>
-      <c r="C59" s="12">
-        <v>1</v>
-      </c>
-      <c r="D59" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="12">
-        <v>4055227</v>
-      </c>
-      <c r="F59" s="12"/>
-      <c r="G59" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
-    </row>
-    <row r="60" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="11">
-        <v>1712</v>
-      </c>
-      <c r="B60" s="12">
-        <v>2</v>
-      </c>
-      <c r="C60" s="12">
-        <v>1</v>
-      </c>
-      <c r="D60" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="12">
-        <v>4055228</v>
-      </c>
-      <c r="F60" s="12"/>
-      <c r="G60" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
+    <row r="59" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A59" s="14">
+        <v>1801</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15">
+        <v>1</v>
+      </c>
+      <c r="D59" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+    </row>
+    <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A60" s="14">
+        <v>1802</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15">
+        <v>1</v>
+      </c>
+      <c r="D60" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
     </row>
     <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A61" s="14">
-        <v>1801</v>
-      </c>
-      <c r="B61" s="15"/>
+        <v>1803</v>
+      </c>
+      <c r="B61" s="15">
+        <v>2</v>
+      </c>
       <c r="C61" s="15">
         <v>1</v>
       </c>
       <c r="D61" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
+      <c r="E61" s="15">
+        <v>4055243</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>16</v>
+      </c>
       <c r="G61" s="16" t="s">
         <v>24</v>
       </c>
@@ -3051,17 +3025,23 @@
     </row>
     <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A62" s="14">
-        <v>1802</v>
-      </c>
-      <c r="B62" s="15"/>
+        <v>1804</v>
+      </c>
+      <c r="B62" s="15">
+        <v>2</v>
+      </c>
       <c r="C62" s="15">
         <v>1</v>
       </c>
       <c r="D62" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
+      <c r="E62" s="15">
+        <v>4055244</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>16</v>
+      </c>
       <c r="G62" s="16" t="s">
         <v>24</v>
       </c>
@@ -3073,10 +3053,10 @@
     </row>
     <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A63" s="14">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="B63" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63" s="15">
         <v>1</v>
@@ -3085,11 +3065,9 @@
         <v>1</v>
       </c>
       <c r="E63" s="15">
-        <v>4055241</v>
-      </c>
-      <c r="F63" s="15" t="s">
-        <v>16</v>
-      </c>
+        <v>4055245</v>
+      </c>
+      <c r="F63" s="15"/>
       <c r="G63" s="16" t="s">
         <v>24</v>
       </c>
@@ -3101,10 +3079,10 @@
     </row>
     <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A64" s="14">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="B64" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" s="15">
         <v>1</v>
@@ -3113,11 +3091,9 @@
         <v>1</v>
       </c>
       <c r="E64" s="15">
-        <v>4055242</v>
-      </c>
-      <c r="F64" s="15" t="s">
-        <v>16</v>
-      </c>
+        <v>4055246</v>
+      </c>
+      <c r="F64" s="15"/>
       <c r="G64" s="16" t="s">
         <v>24</v>
       </c>
@@ -3129,7 +3105,7 @@
     </row>
     <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A65" s="14">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="B65" s="15">
         <v>2</v>
@@ -3141,7 +3117,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="15">
-        <v>4055243</v>
+        <v>4055247</v>
       </c>
       <c r="F65" s="15"/>
       <c r="G65" s="16" t="s">
@@ -3153,103 +3129,95 @@
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
     </row>
-    <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="14">
-        <v>1806</v>
-      </c>
-      <c r="B66" s="15">
-        <v>2</v>
-      </c>
-      <c r="C66" s="15">
-        <v>1</v>
-      </c>
-      <c r="D66" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="15">
-        <v>4055244</v>
-      </c>
-      <c r="F66" s="15"/>
-      <c r="G66" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="17"/>
-    </row>
-    <row r="67" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="14">
-        <v>1807</v>
-      </c>
-      <c r="B67" s="15">
-        <v>2</v>
-      </c>
-      <c r="C67" s="15">
-        <v>1</v>
-      </c>
-      <c r="D67" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="15">
-        <v>4055245</v>
-      </c>
-      <c r="F67" s="15"/>
-      <c r="G67" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="17"/>
-      <c r="L67" s="17"/>
-    </row>
-    <row r="68" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="14">
-        <v>1808</v>
-      </c>
-      <c r="B68" s="15">
-        <v>2</v>
-      </c>
-      <c r="C68" s="15">
-        <v>1</v>
-      </c>
-      <c r="D68" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E68" s="15">
-        <v>4055246</v>
-      </c>
-      <c r="F68" s="15"/>
-      <c r="G68" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="17"/>
-      <c r="L68" s="17"/>
+    <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A66" s="11">
+        <v>1901</v>
+      </c>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12">
+        <v>1</v>
+      </c>
+      <c r="D66" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+    </row>
+    <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A67" s="11">
+        <v>1902</v>
+      </c>
+      <c r="B67" s="12">
+        <v>2</v>
+      </c>
+      <c r="C67" s="12">
+        <v>1</v>
+      </c>
+      <c r="D67" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="12">
+        <v>4055263</v>
+      </c>
+      <c r="F67" s="12"/>
+      <c r="G67" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13"/>
+      <c r="L67" s="13"/>
+    </row>
+    <row r="68" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A68" s="11">
+        <v>1903</v>
+      </c>
+      <c r="B68" s="12">
+        <v>2</v>
+      </c>
+      <c r="C68" s="12">
+        <v>1</v>
+      </c>
+      <c r="D68" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" s="12">
+        <v>4055264</v>
+      </c>
+      <c r="F68" s="12"/>
+      <c r="G68" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
     </row>
     <row r="69" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A69" s="14">
-        <v>1809</v>
-      </c>
-      <c r="B69" s="15">
-        <v>2</v>
-      </c>
+        <v>1981</v>
+      </c>
+      <c r="B69" s="15"/>
       <c r="C69" s="15">
         <v>1</v>
       </c>
-      <c r="D69" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" s="15">
-        <v>4055247</v>
-      </c>
+      <c r="D69" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" s="15"/>
       <c r="F69" s="15"/>
       <c r="G69" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H69" s="17"/>
       <c r="I69" s="17"/>
@@ -3257,77 +3225,69 @@
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
     </row>
-    <row r="70" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="11">
-        <v>1901</v>
-      </c>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12">
-        <v>1</v>
-      </c>
-      <c r="D70" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="13"/>
-      <c r="K70" s="13"/>
-      <c r="L70" s="13"/>
-    </row>
-    <row r="71" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="11">
-        <v>1902</v>
-      </c>
-      <c r="B71" s="12">
-        <v>1</v>
-      </c>
-      <c r="C71" s="12">
-        <v>1</v>
-      </c>
-      <c r="D71" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" s="12">
-        <v>4055261</v>
-      </c>
-      <c r="F71" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G71" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="13"/>
-      <c r="L71" s="13"/>
+    <row r="70" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A70" s="14">
+        <v>1982</v>
+      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15">
+        <v>1</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="17"/>
+      <c r="K70" s="17"/>
+      <c r="L70" s="17"/>
+    </row>
+    <row r="71" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A71" s="14">
+        <v>1983</v>
+      </c>
+      <c r="B71" s="15">
+        <v>2</v>
+      </c>
+      <c r="C71" s="15">
+        <v>1</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E71" s="15">
+        <v>4055321</v>
+      </c>
+      <c r="F71" s="15"/>
+      <c r="G71" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+      <c r="L71" s="17"/>
     </row>
     <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A72" s="11">
-        <v>1903</v>
-      </c>
-      <c r="B72" s="12">
-        <v>1</v>
-      </c>
+        <v>2001</v>
+      </c>
+      <c r="B72" s="12"/>
       <c r="C72" s="12">
         <v>1</v>
       </c>
-      <c r="D72" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" s="12">
-        <v>4055262</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="D72" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
       <c r="G72" s="18" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
@@ -3337,7 +3297,7 @@
     </row>
     <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A73" s="11">
-        <v>1904</v>
+        <v>2002</v>
       </c>
       <c r="B73" s="12">
         <v>2</v>
@@ -3345,15 +3305,15 @@
       <c r="C73" s="12">
         <v>1</v>
       </c>
-      <c r="D73" s="12" t="b">
-        <v>1</v>
+      <c r="D73" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="E73" s="12">
-        <v>4055263</v>
+        <v>4055281</v>
       </c>
       <c r="F73" s="12"/>
       <c r="G73" s="18" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H73" s="13"/>
       <c r="I73" s="13"/>
@@ -3363,7 +3323,7 @@
     </row>
     <row r="74" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A74" s="11">
-        <v>1905</v>
+        <v>2003</v>
       </c>
       <c r="B74" s="12">
         <v>2</v>
@@ -3371,15 +3331,15 @@
       <c r="C74" s="12">
         <v>1</v>
       </c>
-      <c r="D74" s="12" t="b">
-        <v>1</v>
+      <c r="D74" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="E74" s="12">
-        <v>4055264</v>
+        <v>4055282</v>
       </c>
       <c r="F74" s="12"/>
       <c r="G74" s="18" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H74" s="13"/>
       <c r="I74" s="13"/>
@@ -3387,88 +3347,100 @@
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
     </row>
-    <row r="75" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="14">
-        <v>1981</v>
-      </c>
-      <c r="B75" s="15"/>
-      <c r="C75" s="15">
-        <v>1</v>
-      </c>
-      <c r="D75" s="15" t="s">
+    <row r="75" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A75" s="11">
+        <v>2004</v>
+      </c>
+      <c r="B75" s="12">
+        <v>2</v>
+      </c>
+      <c r="C75" s="12">
+        <v>1</v>
+      </c>
+      <c r="D75" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H75" s="17"/>
-      <c r="I75" s="17"/>
-      <c r="J75" s="17"/>
-      <c r="K75" s="17"/>
-      <c r="L75" s="17"/>
-    </row>
-    <row r="76" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A76" s="14">
-        <v>1982</v>
-      </c>
-      <c r="B76" s="15"/>
-      <c r="C76" s="15">
-        <v>1</v>
-      </c>
-      <c r="D76" s="15" t="s">
+      <c r="E75" s="12">
+        <v>4055283</v>
+      </c>
+      <c r="F75" s="12"/>
+      <c r="G75" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+      <c r="K75" s="13"/>
+      <c r="L75" s="13"/>
+    </row>
+    <row r="76" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A76" s="11">
+        <v>2005</v>
+      </c>
+      <c r="B76" s="12">
+        <v>2</v>
+      </c>
+      <c r="C76" s="12">
+        <v>1</v>
+      </c>
+      <c r="D76" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H76" s="17"/>
-      <c r="I76" s="17"/>
-      <c r="J76" s="17"/>
-      <c r="K76" s="17"/>
-      <c r="L76" s="17"/>
-    </row>
-    <row r="77" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A77" s="14">
-        <v>1983</v>
-      </c>
-      <c r="B77" s="15">
-        <v>2</v>
-      </c>
-      <c r="C77" s="15">
-        <v>1</v>
-      </c>
-      <c r="D77" s="15" t="s">
+      <c r="E76" s="12">
+        <v>4055284</v>
+      </c>
+      <c r="F76" s="12"/>
+      <c r="G76" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="13"/>
+      <c r="K76" s="13"/>
+      <c r="L76" s="13"/>
+    </row>
+    <row r="77" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A77" s="11">
+        <v>2006</v>
+      </c>
+      <c r="B77" s="12">
+        <v>2</v>
+      </c>
+      <c r="C77" s="12">
+        <v>1</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E77" s="15">
-        <v>4055321</v>
-      </c>
-      <c r="F77" s="15"/>
-      <c r="G77" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
-      <c r="K77" s="17"/>
-      <c r="L77" s="17"/>
+      <c r="E77" s="12">
+        <v>4055285</v>
+      </c>
+      <c r="F77" s="12"/>
+      <c r="G77" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+      <c r="K77" s="13"/>
+      <c r="L77" s="13"/>
     </row>
     <row r="78" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A78" s="11">
-        <v>2001</v>
-      </c>
-      <c r="B78" s="12"/>
+        <v>2007</v>
+      </c>
+      <c r="B78" s="12">
+        <v>2</v>
+      </c>
       <c r="C78" s="12">
         <v>1</v>
       </c>
       <c r="D78" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E78" s="12"/>
+      <c r="E78" s="12">
+        <v>4055286</v>
+      </c>
       <c r="F78" s="12"/>
       <c r="G78" s="18" t="s">
         <v>28</v>
@@ -3479,239 +3451,59 @@
       <c r="K78" s="13"/>
       <c r="L78" s="13"/>
     </row>
-    <row r="79" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="11">
-        <v>2002</v>
-      </c>
-      <c r="B79" s="12">
-        <v>2</v>
-      </c>
-      <c r="C79" s="12">
-        <v>1</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E79" s="12">
-        <v>4055281</v>
-      </c>
-      <c r="F79" s="12"/>
-      <c r="G79" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-      <c r="J79" s="13"/>
-      <c r="K79" s="13"/>
-      <c r="L79" s="13"/>
-    </row>
-    <row r="80" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="11">
-        <v>2003</v>
-      </c>
-      <c r="B80" s="12">
-        <v>2</v>
-      </c>
-      <c r="C80" s="12">
-        <v>1</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E80" s="12">
-        <v>4055282</v>
-      </c>
-      <c r="F80" s="12"/>
-      <c r="G80" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
-      <c r="J80" s="13"/>
-      <c r="K80" s="13"/>
-      <c r="L80" s="13"/>
-    </row>
-    <row r="81" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="11">
-        <v>2004</v>
-      </c>
-      <c r="B81" s="12">
-        <v>2</v>
-      </c>
-      <c r="C81" s="12">
-        <v>1</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E81" s="12">
-        <v>4055283</v>
-      </c>
-      <c r="F81" s="12"/>
-      <c r="G81" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H81" s="13"/>
-      <c r="I81" s="13"/>
-      <c r="J81" s="13"/>
-      <c r="K81" s="13"/>
-      <c r="L81" s="13"/>
-    </row>
-    <row r="82" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="11">
-        <v>2005</v>
-      </c>
-      <c r="B82" s="12">
-        <v>2</v>
-      </c>
-      <c r="C82" s="12">
-        <v>1</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E82" s="12">
-        <v>4055284</v>
-      </c>
-      <c r="F82" s="12"/>
-      <c r="G82" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H82" s="13"/>
-      <c r="I82" s="13"/>
-      <c r="J82" s="13"/>
-      <c r="K82" s="13"/>
-      <c r="L82" s="13"/>
-    </row>
-    <row r="83" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A83" s="11">
-        <v>2006</v>
-      </c>
-      <c r="B83" s="12">
-        <v>2</v>
-      </c>
-      <c r="C83" s="12">
-        <v>1</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E83" s="12">
-        <v>4055285</v>
-      </c>
-      <c r="F83" s="12"/>
-      <c r="G83" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13"/>
-      <c r="K83" s="13"/>
-      <c r="L83" s="13"/>
-    </row>
-    <row r="84" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A84" s="11">
-        <v>2007</v>
-      </c>
-      <c r="B84" s="12">
-        <v>2</v>
-      </c>
-      <c r="C84" s="12">
-        <v>1</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E84" s="12">
-        <v>4055286</v>
-      </c>
-      <c r="F84" s="12"/>
-      <c r="G84" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13"/>
-      <c r="K84" s="13"/>
-      <c r="L84" s="13"/>
-    </row>
-    <row r="85" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A85" s="19">
+    <row r="79" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A79" s="19">
         <v>2101</v>
       </c>
-      <c r="B85" s="19">
-        <v>1</v>
-      </c>
-      <c r="C85" s="19">
-        <v>1</v>
-      </c>
-      <c r="D85" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" s="19">
+      <c r="B79" s="19">
+        <v>2</v>
+      </c>
+      <c r="C79" s="19">
+        <v>1</v>
+      </c>
+      <c r="D79" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="19">
         <v>4055301</v>
       </c>
-      <c r="F85" s="19"/>
-      <c r="G85" s="5" t="s">
+      <c r="F79" s="19"/>
+      <c r="G79" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H85" s="17"/>
-      <c r="I85" s="17"/>
-      <c r="J85" s="17"/>
-      <c r="K85" s="17"/>
-      <c r="L85" s="17"/>
-    </row>
-    <row r="86" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A86" s="19">
+      <c r="H79" s="17"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="17"/>
+      <c r="K79" s="17"/>
+      <c r="L79" s="17"/>
+    </row>
+    <row r="80" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="19">
         <v>2102</v>
       </c>
-      <c r="B86" s="19">
-        <v>2</v>
-      </c>
-      <c r="C86" s="19">
-        <v>1</v>
-      </c>
-      <c r="D86" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" s="19">
-        <v>4055302</v>
-      </c>
-      <c r="F86" s="19"/>
-      <c r="G86" s="5" t="s">
+      <c r="B80" s="19">
+        <v>1</v>
+      </c>
+      <c r="C80" s="19">
+        <v>1</v>
+      </c>
+      <c r="D80" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" s="19">
+        <v>4055303</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G80" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H86" s="17"/>
-      <c r="I86" s="17"/>
-      <c r="J86" s="17"/>
-      <c r="K86" s="17"/>
-      <c r="L86" s="17"/>
-    </row>
-    <row r="87" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A87" s="19">
-        <v>2103</v>
-      </c>
-      <c r="B87" s="19">
-        <v>1</v>
-      </c>
-      <c r="C87" s="19">
-        <v>1</v>
-      </c>
-      <c r="D87" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="19">
-        <v>4055303</v>
-      </c>
-      <c r="F87" s="19"/>
-      <c r="G87" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H87" s="17"/>
-      <c r="I87" s="17"/>
-      <c r="J87" s="17"/>
-      <c r="K87" s="17"/>
-      <c r="L87" s="17"/>
+      <c r="H80" s="17"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="17"/>
+      <c r="K80" s="17"/>
+      <c r="L80" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="40">
   <si>
     <t>序号</t>
   </si>
@@ -1526,7 +1526,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -2707,17 +2707,11 @@
       <c r="A49" s="11">
         <v>1702</v>
       </c>
-      <c r="B49" s="12">
-        <v>2</v>
-      </c>
       <c r="C49" s="12">
         <v>1</v>
       </c>
       <c r="D49" s="12" t="b">
         <v>1</v>
-      </c>
-      <c r="E49" s="12">
-        <v>4055222</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="18" t="s">
@@ -2743,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="E50" s="12">
-        <v>4055223</v>
+        <v>4055222</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="18" t="s">
@@ -2769,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="12">
-        <v>4055224</v>
+        <v>4055223</v>
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="18" t="s">
@@ -2785,14 +2779,18 @@
       <c r="A52" s="11">
         <v>1705</v>
       </c>
-      <c r="B52" s="12"/>
+      <c r="B52" s="12">
+        <v>2</v>
+      </c>
       <c r="C52" s="12">
         <v>1</v>
       </c>
       <c r="D52" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E52" s="12"/>
+      <c r="E52" s="12">
+        <v>4055224</v>
+      </c>
       <c r="F52" s="12"/>
       <c r="G52" s="18" t="s">
         <v>23</v>
@@ -2807,18 +2805,14 @@
       <c r="A53" s="11">
         <v>1706</v>
       </c>
-      <c r="B53" s="12">
-        <v>2</v>
-      </c>
+      <c r="B53" s="12"/>
       <c r="C53" s="12">
         <v>1</v>
       </c>
       <c r="D53" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E53" s="12">
-        <v>4055225</v>
-      </c>
+      <c r="E53" s="12"/>
       <c r="F53" s="12"/>
       <c r="G53" s="18" t="s">
         <v>23</v>
@@ -2843,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="12">
-        <v>4055226</v>
+        <v>4055225</v>
       </c>
       <c r="F54" s="12"/>
       <c r="G54" s="18" t="s">
@@ -2859,14 +2853,18 @@
       <c r="A55" s="11">
         <v>1708</v>
       </c>
-      <c r="B55" s="12"/>
+      <c r="B55" s="12">
+        <v>2</v>
+      </c>
       <c r="C55" s="12">
         <v>1</v>
       </c>
       <c r="D55" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E55" s="12"/>
+      <c r="E55" s="12">
+        <v>4055226</v>
+      </c>
       <c r="F55" s="12"/>
       <c r="G55" s="18" t="s">
         <v>23</v>
@@ -2903,18 +2901,14 @@
       <c r="A57" s="11">
         <v>1710</v>
       </c>
-      <c r="B57" s="12">
-        <v>2</v>
-      </c>
+      <c r="B57" s="12"/>
       <c r="C57" s="12">
         <v>1</v>
       </c>
       <c r="D57" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E57" s="12">
-        <v>4055227</v>
-      </c>
+      <c r="E57" s="12"/>
       <c r="F57" s="12"/>
       <c r="G57" s="18" t="s">
         <v>23</v>
@@ -2939,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="E58" s="12">
-        <v>4055228</v>
+        <v>4055227</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="18" t="s">
@@ -2951,31 +2945,35 @@
       <c r="K58" s="13"/>
       <c r="L58" s="13"/>
     </row>
-    <row r="59" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="14">
-        <v>1801</v>
-      </c>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15">
-        <v>1</v>
-      </c>
-      <c r="D59" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H59" s="17"/>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
+    <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A59" s="11">
+        <v>1712</v>
+      </c>
+      <c r="B59" s="12">
+        <v>2</v>
+      </c>
+      <c r="C59" s="12">
+        <v>1</v>
+      </c>
+      <c r="D59" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="12">
+        <v>4055228</v>
+      </c>
+      <c r="F59" s="12"/>
+      <c r="G59" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
     </row>
     <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A60" s="14">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15">
@@ -2997,23 +2995,17 @@
     </row>
     <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A61" s="14">
-        <v>1803</v>
-      </c>
-      <c r="B61" s="15">
-        <v>2</v>
-      </c>
+        <v>1802</v>
+      </c>
+      <c r="B61" s="15"/>
       <c r="C61" s="15">
         <v>1</v>
       </c>
       <c r="D61" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="E61" s="15">
-        <v>4055243</v>
-      </c>
-      <c r="F61" s="15" t="s">
-        <v>16</v>
-      </c>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
       <c r="G61" s="16" t="s">
         <v>24</v>
       </c>
@@ -3025,7 +3017,7 @@
     </row>
     <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A62" s="14">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="B62" s="15">
         <v>2</v>
@@ -3037,7 +3029,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="15">
-        <v>4055244</v>
+        <v>4055243</v>
       </c>
       <c r="F62" s="15" t="s">
         <v>16</v>
@@ -3053,7 +3045,7 @@
     </row>
     <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A63" s="14">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="B63" s="15">
         <v>2</v>
@@ -3065,9 +3057,11 @@
         <v>1</v>
       </c>
       <c r="E63" s="15">
-        <v>4055245</v>
-      </c>
-      <c r="F63" s="15"/>
+        <v>4055244</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>16</v>
+      </c>
       <c r="G63" s="16" t="s">
         <v>24</v>
       </c>
@@ -3079,7 +3073,7 @@
     </row>
     <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A64" s="14">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B64" s="15">
         <v>2</v>
@@ -3091,7 +3085,7 @@
         <v>1</v>
       </c>
       <c r="E64" s="15">
-        <v>4055246</v>
+        <v>4055245</v>
       </c>
       <c r="F64" s="15"/>
       <c r="G64" s="16" t="s">
@@ -3105,7 +3099,7 @@
     </row>
     <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A65" s="14">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B65" s="15">
         <v>2</v>
@@ -3117,7 +3111,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="15">
-        <v>4055247</v>
+        <v>4055246</v>
       </c>
       <c r="F65" s="15"/>
       <c r="G65" s="16" t="s">
@@ -3129,44 +3123,44 @@
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
     </row>
-    <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="11">
-        <v>1901</v>
-      </c>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12">
-        <v>1</v>
-      </c>
-      <c r="D66" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="13"/>
-      <c r="L66" s="13"/>
+    <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A66" s="14">
+        <v>1807</v>
+      </c>
+      <c r="B66" s="15">
+        <v>2</v>
+      </c>
+      <c r="C66" s="15">
+        <v>1</v>
+      </c>
+      <c r="D66" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="15">
+        <v>4055247</v>
+      </c>
+      <c r="F66" s="15"/>
+      <c r="G66" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
+      <c r="L66" s="17"/>
     </row>
     <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A67" s="11">
-        <v>1902</v>
-      </c>
-      <c r="B67" s="12">
-        <v>2</v>
-      </c>
+        <v>1901</v>
+      </c>
+      <c r="B67" s="12"/>
       <c r="C67" s="12">
         <v>1</v>
       </c>
       <c r="D67" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E67" s="12">
-        <v>4055263</v>
-      </c>
+      <c r="E67" s="12"/>
       <c r="F67" s="12"/>
       <c r="G67" s="18" t="s">
         <v>25</v>
@@ -3179,7 +3173,7 @@
     </row>
     <row r="68" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A68" s="11">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B68" s="12">
         <v>2</v>
@@ -3191,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="12">
-        <v>4055264</v>
+        <v>4055263</v>
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="18" t="s">
@@ -3203,31 +3197,35 @@
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
     </row>
-    <row r="69" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A69" s="14">
-        <v>1981</v>
-      </c>
-      <c r="B69" s="15"/>
-      <c r="C69" s="15">
-        <v>1</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H69" s="17"/>
-      <c r="I69" s="17"/>
-      <c r="J69" s="17"/>
-      <c r="K69" s="17"/>
-      <c r="L69" s="17"/>
+    <row r="69" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A69" s="11">
+        <v>1903</v>
+      </c>
+      <c r="B69" s="12">
+        <v>2</v>
+      </c>
+      <c r="C69" s="12">
+        <v>1</v>
+      </c>
+      <c r="D69" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="12">
+        <v>4055264</v>
+      </c>
+      <c r="F69" s="12"/>
+      <c r="G69" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
+      <c r="L69" s="13"/>
     </row>
     <row r="70" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A70" s="14">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="15">
@@ -3249,20 +3247,16 @@
     </row>
     <row r="71" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A71" s="14">
-        <v>1983</v>
-      </c>
-      <c r="B71" s="15">
-        <v>2</v>
-      </c>
+        <v>1982</v>
+      </c>
+      <c r="B71" s="15"/>
       <c r="C71" s="15">
         <v>1</v>
       </c>
       <c r="D71" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E71" s="15">
-        <v>4055321</v>
-      </c>
+      <c r="E71" s="15"/>
       <c r="F71" s="15"/>
       <c r="G71" s="16" t="s">
         <v>27</v>
@@ -3273,44 +3267,44 @@
       <c r="K71" s="17"/>
       <c r="L71" s="17"/>
     </row>
-    <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="11">
-        <v>2001</v>
-      </c>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12">
-        <v>1</v>
-      </c>
-      <c r="D72" s="12" t="s">
+    <row r="72" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A72" s="14">
+        <v>1983</v>
+      </c>
+      <c r="B72" s="15">
+        <v>2</v>
+      </c>
+      <c r="C72" s="15">
+        <v>1</v>
+      </c>
+      <c r="D72" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E72" s="12"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="13"/>
+      <c r="E72" s="15">
+        <v>4055321</v>
+      </c>
+      <c r="F72" s="15"/>
+      <c r="G72" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="17"/>
+      <c r="K72" s="17"/>
+      <c r="L72" s="17"/>
     </row>
     <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A73" s="11">
-        <v>2002</v>
-      </c>
-      <c r="B73" s="12">
-        <v>2</v>
-      </c>
+        <v>2001</v>
+      </c>
+      <c r="B73" s="12"/>
       <c r="C73" s="12">
         <v>1</v>
       </c>
       <c r="D73" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E73" s="12">
-        <v>4055281</v>
-      </c>
+      <c r="E73" s="12"/>
       <c r="F73" s="12"/>
       <c r="G73" s="18" t="s">
         <v>28</v>
@@ -3323,7 +3317,7 @@
     </row>
     <row r="74" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A74" s="11">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B74" s="12">
         <v>2</v>
@@ -3335,7 +3329,7 @@
         <v>26</v>
       </c>
       <c r="E74" s="12">
-        <v>4055282</v>
+        <v>4055281</v>
       </c>
       <c r="F74" s="12"/>
       <c r="G74" s="18" t="s">
@@ -3349,7 +3343,7 @@
     </row>
     <row r="75" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A75" s="11">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B75" s="12">
         <v>2</v>
@@ -3361,7 +3355,7 @@
         <v>26</v>
       </c>
       <c r="E75" s="12">
-        <v>4055283</v>
+        <v>4055282</v>
       </c>
       <c r="F75" s="12"/>
       <c r="G75" s="18" t="s">
@@ -3375,7 +3369,7 @@
     </row>
     <row r="76" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A76" s="11">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B76" s="12">
         <v>2</v>
@@ -3387,7 +3381,7 @@
         <v>26</v>
       </c>
       <c r="E76" s="12">
-        <v>4055284</v>
+        <v>4055283</v>
       </c>
       <c r="F76" s="12"/>
       <c r="G76" s="18" t="s">
@@ -3401,7 +3395,7 @@
     </row>
     <row r="77" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A77" s="11">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B77" s="12">
         <v>2</v>
@@ -3413,7 +3407,7 @@
         <v>26</v>
       </c>
       <c r="E77" s="12">
-        <v>4055285</v>
+        <v>4055284</v>
       </c>
       <c r="F77" s="12"/>
       <c r="G77" s="18" t="s">
@@ -3427,7 +3421,7 @@
     </row>
     <row r="78" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A78" s="11">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B78" s="12">
         <v>2</v>
@@ -3439,7 +3433,7 @@
         <v>26</v>
       </c>
       <c r="E78" s="12">
-        <v>4055286</v>
+        <v>4055285</v>
       </c>
       <c r="F78" s="12"/>
       <c r="G78" s="18" t="s">
@@ -3451,38 +3445,38 @@
       <c r="K78" s="13"/>
       <c r="L78" s="13"/>
     </row>
-    <row r="79" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="19">
-        <v>2101</v>
-      </c>
-      <c r="B79" s="19">
-        <v>2</v>
-      </c>
-      <c r="C79" s="19">
-        <v>1</v>
-      </c>
-      <c r="D79" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="19">
-        <v>4055301</v>
-      </c>
-      <c r="F79" s="19"/>
-      <c r="G79" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H79" s="17"/>
-      <c r="I79" s="17"/>
-      <c r="J79" s="17"/>
-      <c r="K79" s="17"/>
-      <c r="L79" s="17"/>
+    <row r="79" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A79" s="11">
+        <v>2007</v>
+      </c>
+      <c r="B79" s="12">
+        <v>2</v>
+      </c>
+      <c r="C79" s="12">
+        <v>1</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" s="12">
+        <v>4055286</v>
+      </c>
+      <c r="F79" s="12"/>
+      <c r="G79" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13"/>
+      <c r="K79" s="13"/>
+      <c r="L79" s="13"/>
     </row>
     <row r="80" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A80" s="19">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B80" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" s="19">
         <v>1</v>
@@ -3491,11 +3485,9 @@
         <v>1</v>
       </c>
       <c r="E80" s="19">
-        <v>4055303</v>
-      </c>
-      <c r="F80" s="19" t="s">
-        <v>16</v>
-      </c>
+        <v>4055301</v>
+      </c>
+      <c r="F80" s="19"/>
       <c r="G80" s="5" t="s">
         <v>29</v>
       </c>
@@ -3504,6 +3496,34 @@
       <c r="J80" s="17"/>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
+    </row>
+    <row r="81" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A81" s="19">
+        <v>2102</v>
+      </c>
+      <c r="B81" s="19">
+        <v>1</v>
+      </c>
+      <c r="C81" s="19">
+        <v>1</v>
+      </c>
+      <c r="D81" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" s="19">
+        <v>4055303</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="17"/>
+      <c r="K81" s="17"/>
+      <c r="L81" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="39">
   <si>
     <t>序号</t>
   </si>
@@ -258,9 +258,6 @@
   </si>
   <si>
     <t>赛季-界面-SLOT</t>
-  </si>
-  <si>
-    <t>FASLE</t>
   </si>
   <si>
     <t>赛季-斗仙牌-前置</t>
@@ -1634,7 +1631,7 @@
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="12">
         <v>4055101</v>
@@ -1658,7 +1655,7 @@
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="12">
         <v>4055102</v>
@@ -1682,7 +1679,7 @@
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
       <c r="D7" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="12">
         <v>4055103</v>
@@ -1706,7 +1703,7 @@
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -1726,7 +1723,7 @@
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1746,7 +1743,7 @@
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="12">
         <v>4055104</v>
@@ -1770,7 +1767,7 @@
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="12">
         <v>4055105</v>
@@ -1794,7 +1791,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -1814,7 +1811,7 @@
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1834,7 +1831,7 @@
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
@@ -1854,7 +1851,7 @@
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="12">
         <v>4055106</v>
@@ -1878,7 +1875,7 @@
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="12">
         <v>4055107</v>
@@ -1902,7 +1899,7 @@
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="12">
         <v>4055108</v>
@@ -1929,8 +1926,8 @@
       <c r="C18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="15" t="b">
-        <v>1</v>
+      <c r="D18" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E18" s="15">
         <v>4055121</v>
@@ -1957,8 +1954,8 @@
       <c r="C19" s="15">
         <v>1</v>
       </c>
-      <c r="D19" s="15" t="b">
-        <v>1</v>
+      <c r="D19" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E19" s="15">
         <v>4055122</v>
@@ -1985,8 +1982,8 @@
       <c r="C20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="15" t="b">
-        <v>1</v>
+      <c r="D20" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E20" s="15">
         <v>4055123</v>
@@ -2014,7 +2011,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="12">
         <v>4055141</v>
@@ -2042,7 +2039,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="12">
         <v>4055142</v>
@@ -2070,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="12">
         <v>4055143</v>
@@ -2096,7 +2093,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -2118,7 +2115,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -2141,8 +2138,8 @@
       <c r="C26" s="15">
         <v>1</v>
       </c>
-      <c r="D26" s="15" t="b">
-        <v>1</v>
+      <c r="D26" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E26" s="15">
         <v>4055161</v>
@@ -2167,8 +2164,8 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="15" t="b">
-        <v>1</v>
+      <c r="D27" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E27" s="15">
         <v>4055162</v>
@@ -2193,8 +2190,8 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15" t="b">
-        <v>1</v>
+      <c r="D28" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E28" s="15">
         <v>4055163</v>
@@ -2219,8 +2216,8 @@
       <c r="C29" s="15">
         <v>1</v>
       </c>
-      <c r="D29" s="15" t="b">
-        <v>1</v>
+      <c r="D29" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E29" s="15">
         <v>4055164</v>
@@ -2243,8 +2240,8 @@
       <c r="C30" s="15">
         <v>1</v>
       </c>
-      <c r="D30" s="15" t="b">
-        <v>1</v>
+      <c r="D30" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="15"/>
@@ -2267,8 +2264,8 @@
       <c r="C31" s="15">
         <v>1</v>
       </c>
-      <c r="D31" s="15" t="b">
-        <v>1</v>
+      <c r="D31" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E31" s="15">
         <v>4055165</v>
@@ -2294,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="12">
         <v>4055181</v>
@@ -2320,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="12">
         <v>4055182</v>
@@ -2344,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
@@ -2366,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
@@ -2387,8 +2384,8 @@
       <c r="C36" s="15">
         <v>1</v>
       </c>
-      <c r="D36" s="15" t="b">
-        <v>1</v>
+      <c r="D36" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
@@ -2409,8 +2406,8 @@
       <c r="C37" s="15">
         <v>1</v>
       </c>
-      <c r="D37" s="15" t="b">
-        <v>1</v>
+      <c r="D37" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="15"/>
@@ -2431,8 +2428,8 @@
       <c r="C38" s="15">
         <v>1</v>
       </c>
-      <c r="D38" s="15" t="b">
-        <v>1</v>
+      <c r="D38" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E38" s="15">
         <v>4055203</v>
@@ -2457,8 +2454,8 @@
       <c r="C39" s="15">
         <v>1</v>
       </c>
-      <c r="D39" s="15" t="b">
-        <v>1</v>
+      <c r="D39" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="15"/>
@@ -2481,8 +2478,8 @@
       <c r="C40" s="15">
         <v>1</v>
       </c>
-      <c r="D40" s="15" t="b">
-        <v>1</v>
+      <c r="D40" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E40" s="15">
         <v>4055204</v>
@@ -2507,8 +2504,8 @@
       <c r="C41" s="15">
         <v>1</v>
       </c>
-      <c r="D41" s="15" t="b">
-        <v>1</v>
+      <c r="D41" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="15"/>
@@ -2531,8 +2528,8 @@
       <c r="C42" s="15">
         <v>1</v>
       </c>
-      <c r="D42" s="15" t="b">
-        <v>1</v>
+      <c r="D42" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="15"/>
@@ -2553,8 +2550,8 @@
       <c r="C43" s="15">
         <v>1</v>
       </c>
-      <c r="D43" s="15" t="b">
-        <v>1</v>
+      <c r="D43" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E43" s="15">
         <v>4055205</v>
@@ -2579,8 +2576,8 @@
       <c r="C44" s="15">
         <v>1</v>
       </c>
-      <c r="D44" s="15" t="b">
-        <v>1</v>
+      <c r="D44" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E44" s="15">
         <v>4055206</v>
@@ -2607,8 +2604,8 @@
       <c r="C45" s="15">
         <v>1</v>
       </c>
-      <c r="D45" s="15" t="b">
-        <v>1</v>
+      <c r="D45" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E45" s="15">
         <v>4055207</v>
@@ -2635,8 +2632,8 @@
       <c r="C46" s="15">
         <v>1</v>
       </c>
-      <c r="D46" s="15" t="b">
-        <v>1</v>
+      <c r="D46" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E46" s="15">
         <v>4055208</v>
@@ -2663,8 +2660,8 @@
       <c r="C47" s="15">
         <v>1</v>
       </c>
-      <c r="D47" s="15" t="b">
-        <v>1</v>
+      <c r="D47" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E47" s="15">
         <v>4055209</v>
@@ -2690,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
@@ -2711,7 +2708,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="18" t="s">
@@ -2734,7 +2731,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="12">
         <v>4055222</v>
@@ -2760,7 +2757,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="12">
         <v>4055223</v>
@@ -2786,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="12">
         <v>4055224</v>
@@ -2810,7 +2807,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
@@ -2834,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="12">
         <v>4055225</v>
@@ -2860,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="12">
         <v>4055226</v>
@@ -2884,7 +2881,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12"/>
@@ -2906,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12"/>
@@ -2930,7 +2927,7 @@
         <v>1</v>
       </c>
       <c r="D58" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="12">
         <v>4055227</v>
@@ -2956,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="12">
         <v>4055228</v>
@@ -2979,8 +2976,8 @@
       <c r="C60" s="15">
         <v>1</v>
       </c>
-      <c r="D60" s="15" t="b">
-        <v>1</v>
+      <c r="D60" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="15"/>
@@ -3001,8 +2998,8 @@
       <c r="C61" s="15">
         <v>1</v>
       </c>
-      <c r="D61" s="15" t="b">
-        <v>1</v>
+      <c r="D61" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E61" s="15"/>
       <c r="F61" s="15"/>
@@ -3025,8 +3022,8 @@
       <c r="C62" s="15">
         <v>1</v>
       </c>
-      <c r="D62" s="15" t="b">
-        <v>1</v>
+      <c r="D62" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E62" s="15">
         <v>4055243</v>
@@ -3053,8 +3050,8 @@
       <c r="C63" s="15">
         <v>1</v>
       </c>
-      <c r="D63" s="15" t="b">
-        <v>1</v>
+      <c r="D63" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E63" s="15">
         <v>4055244</v>
@@ -3081,8 +3078,8 @@
       <c r="C64" s="15">
         <v>1</v>
       </c>
-      <c r="D64" s="15" t="b">
-        <v>1</v>
+      <c r="D64" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E64" s="15">
         <v>4055245</v>
@@ -3107,8 +3104,8 @@
       <c r="C65" s="15">
         <v>1</v>
       </c>
-      <c r="D65" s="15" t="b">
-        <v>1</v>
+      <c r="D65" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E65" s="15">
         <v>4055246</v>
@@ -3133,8 +3130,8 @@
       <c r="C66" s="15">
         <v>1</v>
       </c>
-      <c r="D66" s="15" t="b">
-        <v>1</v>
+      <c r="D66" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E66" s="15">
         <v>4055247</v>
@@ -3158,7 +3155,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
@@ -3182,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="D68" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" s="12">
         <v>4055263</v>
@@ -3208,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="12">
         <v>4055264</v>
@@ -3231,13 +3228,13 @@
       <c r="C70" s="15">
         <v>1</v>
       </c>
-      <c r="D70" s="15" t="s">
-        <v>26</v>
+      <c r="D70" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E70" s="15"/>
       <c r="F70" s="15"/>
       <c r="G70" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H70" s="17"/>
       <c r="I70" s="17"/>
@@ -3253,13 +3250,13 @@
       <c r="C71" s="15">
         <v>1</v>
       </c>
-      <c r="D71" s="15" t="s">
-        <v>26</v>
+      <c r="D71" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="15"/>
       <c r="G71" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H71" s="17"/>
       <c r="I71" s="17"/>
@@ -3277,15 +3274,15 @@
       <c r="C72" s="15">
         <v>1</v>
       </c>
-      <c r="D72" s="15" t="s">
-        <v>26</v>
+      <c r="D72" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E72" s="15">
         <v>4055321</v>
       </c>
       <c r="F72" s="15"/>
       <c r="G72" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H72" s="17"/>
       <c r="I72" s="17"/>
@@ -3301,13 +3298,13 @@
       <c r="C73" s="12">
         <v>1</v>
       </c>
-      <c r="D73" s="12" t="s">
-        <v>26</v>
+      <c r="D73" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12"/>
       <c r="G73" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H73" s="13"/>
       <c r="I73" s="13"/>
@@ -3325,15 +3322,15 @@
       <c r="C74" s="12">
         <v>1</v>
       </c>
-      <c r="D74" s="12" t="s">
-        <v>26</v>
+      <c r="D74" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E74" s="12">
         <v>4055281</v>
       </c>
       <c r="F74" s="12"/>
       <c r="G74" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H74" s="13"/>
       <c r="I74" s="13"/>
@@ -3351,15 +3348,15 @@
       <c r="C75" s="12">
         <v>1</v>
       </c>
-      <c r="D75" s="12" t="s">
-        <v>26</v>
+      <c r="D75" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E75" s="12">
         <v>4055282</v>
       </c>
       <c r="F75" s="12"/>
       <c r="G75" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H75" s="13"/>
       <c r="I75" s="13"/>
@@ -3377,15 +3374,15 @@
       <c r="C76" s="12">
         <v>1</v>
       </c>
-      <c r="D76" s="12" t="s">
-        <v>26</v>
+      <c r="D76" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E76" s="12">
         <v>4055283</v>
       </c>
       <c r="F76" s="12"/>
       <c r="G76" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H76" s="13"/>
       <c r="I76" s="13"/>
@@ -3403,15 +3400,15 @@
       <c r="C77" s="12">
         <v>1</v>
       </c>
-      <c r="D77" s="12" t="s">
-        <v>26</v>
+      <c r="D77" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E77" s="12">
         <v>4055284</v>
       </c>
       <c r="F77" s="12"/>
       <c r="G77" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H77" s="13"/>
       <c r="I77" s="13"/>
@@ -3429,15 +3426,15 @@
       <c r="C78" s="12">
         <v>1</v>
       </c>
-      <c r="D78" s="12" t="s">
-        <v>26</v>
+      <c r="D78" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E78" s="12">
         <v>4055285</v>
       </c>
       <c r="F78" s="12"/>
       <c r="G78" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H78" s="13"/>
       <c r="I78" s="13"/>
@@ -3455,15 +3452,15 @@
       <c r="C79" s="12">
         <v>1</v>
       </c>
-      <c r="D79" s="12" t="s">
-        <v>26</v>
+      <c r="D79" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E79" s="12">
         <v>4055286</v>
       </c>
       <c r="F79" s="12"/>
       <c r="G79" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H79" s="13"/>
       <c r="I79" s="13"/>
@@ -3481,15 +3478,15 @@
       <c r="C80" s="19">
         <v>1</v>
       </c>
-      <c r="D80" s="19" t="b">
-        <v>1</v>
+      <c r="D80" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E80" s="19">
         <v>4055301</v>
       </c>
       <c r="F80" s="19"/>
       <c r="G80" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H80" s="17"/>
       <c r="I80" s="17"/>
@@ -3507,8 +3504,8 @@
       <c r="C81" s="19">
         <v>1</v>
       </c>
-      <c r="D81" s="19" t="b">
-        <v>1</v>
+      <c r="D81" s="12" t="b">
+        <v>0</v>
       </c>
       <c r="E81" s="19">
         <v>4055303</v>
@@ -3517,7 +3514,7 @@
         <v>16</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H81" s="17"/>
       <c r="I81" s="17"/>
@@ -3583,14 +3580,14 @@
         <v>2101</v>
       </c>
       <c r="J5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2101_</v>
       </c>
       <c r="M5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -3599,7 +3596,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3609,14 +3606,14 @@
         <v>2102</v>
       </c>
       <c r="J6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2102_</v>
       </c>
       <c r="M6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3624,14 +3621,14 @@
         <v>2103</v>
       </c>
       <c r="J7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2103_</v>
       </c>
       <c r="M7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3639,34 +3636,34 @@
         <v>2104</v>
       </c>
       <c r="J8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2104_</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="39">
   <si>
     <t>序号</t>
   </si>
@@ -1705,7 +1705,9 @@
       <c r="D8" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="12"/>
+      <c r="E8" s="12">
+        <v>4055104</v>
+      </c>
       <c r="F8" s="12"/>
       <c r="G8" s="4" t="s">
         <v>17</v>
@@ -1746,11 +1748,9 @@
         <v>0</v>
       </c>
       <c r="E10" s="12">
-        <v>4055104</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>16</v>
-      </c>
+        <v>4055105</v>
+      </c>
+      <c r="F10" s="12"/>
       <c r="G10" s="4" t="s">
         <v>17</v>
       </c>
@@ -1770,11 +1770,9 @@
         <v>0</v>
       </c>
       <c r="E11" s="12">
-        <v>4055105</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>16</v>
-      </c>
+        <v>4055106</v>
+      </c>
+      <c r="F11" s="12"/>
       <c r="G11" s="4" t="s">
         <v>17</v>
       </c>
@@ -1854,11 +1852,9 @@
         <v>0</v>
       </c>
       <c r="E15" s="12">
-        <v>4055106</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>16</v>
-      </c>
+        <v>4055107</v>
+      </c>
+      <c r="F15" s="12"/>
       <c r="G15" s="4" t="s">
         <v>17</v>
       </c>
@@ -1878,11 +1874,9 @@
         <v>0</v>
       </c>
       <c r="E16" s="12">
-        <v>4055107</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>16</v>
-      </c>
+        <v>4055108</v>
+      </c>
+      <c r="F16" s="12"/>
       <c r="G16" s="4" t="s">
         <v>17</v>
       </c>
@@ -1902,11 +1896,9 @@
         <v>0</v>
       </c>
       <c r="E17" s="12">
-        <v>4055108</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>16</v>
-      </c>
+        <v>4055109</v>
+      </c>
+      <c r="F17" s="12"/>
       <c r="G17" s="4" t="s">
         <v>17</v>
       </c>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="38">
   <si>
     <t>序号</t>
   </si>
@@ -228,9 +228,6 @@
   </si>
   <si>
     <t>SoundFile</t>
-  </si>
-  <si>
-    <t>guideTest.mp3</t>
   </si>
   <si>
     <t>初入游戏-创建新号到经营大厅</t>
@@ -309,7 +306,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,6 +356,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.5"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -848,137 +851,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1018,15 +1021,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1035,6 +1038,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1630,23 +1636,21 @@
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
-      <c r="D5" s="12" t="b">
-        <v>0</v>
+      <c r="D5" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E5" s="12">
         <v>4055101</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="12"/>
+      <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A6" s="11">
@@ -1654,23 +1658,21 @@
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
-      <c r="D6" s="12" t="b">
-        <v>0</v>
+      <c r="D6" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E6" s="12">
         <v>4055102</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="12"/>
+      <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A7" s="11">
@@ -1678,23 +1680,21 @@
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
-      <c r="D7" s="12" t="b">
-        <v>0</v>
+      <c r="D7" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E7" s="12">
         <v>4055103</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A8" s="11">
@@ -1702,21 +1702,21 @@
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
-      <c r="D8" s="12" t="b">
-        <v>0</v>
+      <c r="D8" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E8" s="12">
         <v>4055104</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A9" s="11">
@@ -1724,19 +1724,19 @@
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
-      <c r="D9" s="12" t="b">
-        <v>0</v>
+      <c r="D9" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A10" s="11">
@@ -1744,21 +1744,21 @@
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
-      <c r="D10" s="12" t="b">
-        <v>0</v>
+      <c r="D10" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E10" s="12">
         <v>4055105</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A11" s="11">
@@ -1766,21 +1766,21 @@
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
-      <c r="D11" s="12" t="b">
-        <v>0</v>
+      <c r="D11" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E11" s="12">
         <v>4055106</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A12" s="11">
@@ -1788,19 +1788,19 @@
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
-      <c r="D12" s="12" t="b">
-        <v>0</v>
+      <c r="D12" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A13" s="11">
@@ -1808,19 +1808,19 @@
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
-      <c r="D13" s="12" t="b">
-        <v>0</v>
+      <c r="D13" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
     </row>
     <row r="14" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A14" s="11">
@@ -1828,19 +1828,19 @@
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
-      <c r="D14" s="12" t="b">
-        <v>0</v>
+      <c r="D14" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
       <c r="G14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
     </row>
     <row r="15" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A15" s="11">
@@ -1848,21 +1848,21 @@
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
-      <c r="D15" s="12" t="b">
-        <v>0</v>
+      <c r="D15" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E15" s="12">
         <v>4055107</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
     </row>
     <row r="16" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A16" s="11">
@@ -1870,21 +1870,21 @@
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
-      <c r="D16" s="12" t="b">
-        <v>0</v>
+      <c r="D16" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E16" s="12">
         <v>4055108</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
     </row>
     <row r="17" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A17" s="11">
@@ -1892,43 +1892,41 @@
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="12" t="b">
-        <v>0</v>
+      <c r="D17" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E17" s="12">
         <v>4055109</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+    </row>
+    <row r="18" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A18" s="15">
+        <v>1201</v>
+      </c>
+      <c r="B18" s="13">
+        <v>2</v>
+      </c>
+      <c r="C18" s="13">
+        <v>2</v>
+      </c>
+      <c r="D18" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="13">
+        <v>4055121</v>
+      </c>
+      <c r="F18" s="13"/>
+      <c r="G18" s="16" t="s">
         <v>17</v>
-      </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-    </row>
-    <row r="18" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="14">
-        <v>1201</v>
-      </c>
-      <c r="B18" s="15">
-        <v>2</v>
-      </c>
-      <c r="C18" s="15">
-        <v>2</v>
-      </c>
-      <c r="D18" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="15">
-        <v>4055121</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>18</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -1937,26 +1935,24 @@
       <c r="L18" s="17"/>
     </row>
     <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="14">
+      <c r="A19" s="15">
         <v>1202</v>
       </c>
-      <c r="B19" s="15">
-        <v>2</v>
-      </c>
-      <c r="C19" s="15">
-        <v>1</v>
-      </c>
-      <c r="D19" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="15">
+      <c r="B19" s="13">
+        <v>2</v>
+      </c>
+      <c r="C19" s="13">
+        <v>1</v>
+      </c>
+      <c r="D19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="13">
         <v>4055122</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>16</v>
-      </c>
+      <c r="F19" s="13"/>
       <c r="G19" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -1965,26 +1961,24 @@
       <c r="L19" s="17"/>
     </row>
     <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="14">
+      <c r="A20" s="15">
         <v>1203</v>
       </c>
-      <c r="B20" s="15">
-        <v>2</v>
-      </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="B20" s="13">
+        <v>2</v>
+      </c>
+      <c r="C20" s="13">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="13">
         <v>4055123</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>16</v>
-      </c>
+      <c r="F20" s="13"/>
       <c r="G20" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -2002,23 +1996,21 @@
       <c r="C21" s="12">
         <v>1</v>
       </c>
-      <c r="D21" s="12" t="b">
-        <v>0</v>
+      <c r="D21" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E21" s="12">
         <v>4055141</v>
       </c>
-      <c r="F21" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="F21" s="12"/>
       <c r="G21" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A22" s="11">
@@ -2030,23 +2022,21 @@
       <c r="C22" s="12">
         <v>1</v>
       </c>
-      <c r="D22" s="12" t="b">
-        <v>0</v>
+      <c r="D22" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E22" s="12">
         <v>4055142</v>
       </c>
-      <c r="F22" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="F22" s="12"/>
       <c r="G22" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
     </row>
     <row r="23" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A23" s="11">
@@ -2058,23 +2048,21 @@
       <c r="C23" s="12">
         <v>1</v>
       </c>
-      <c r="D23" s="12" t="b">
-        <v>0</v>
+      <c r="D23" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E23" s="12">
         <v>4055143</v>
       </c>
-      <c r="F23" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="F23" s="12"/>
       <c r="G23" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
     </row>
     <row r="24" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A24" s="11">
@@ -2084,19 +2072,19 @@
       <c r="C24" s="12">
         <v>1</v>
       </c>
-      <c r="D24" s="12" t="b">
-        <v>0</v>
+      <c r="D24" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
       <c r="G24" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
     </row>
     <row r="25" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A25" s="11">
@@ -2106,39 +2094,39 @@
       <c r="C25" s="12">
         <v>1</v>
       </c>
-      <c r="D25" s="12" t="b">
-        <v>0</v>
+      <c r="D25" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
       <c r="G25" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+    </row>
+    <row r="26" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A26" s="15">
+        <v>1401</v>
+      </c>
+      <c r="B26" s="13">
+        <v>2</v>
+      </c>
+      <c r="C26" s="13">
+        <v>1</v>
+      </c>
+      <c r="D26" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="13">
+        <v>4055161</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="G26" s="16" t="s">
         <v>19</v>
-      </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-    </row>
-    <row r="26" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="14">
-        <v>1401</v>
-      </c>
-      <c r="B26" s="15">
-        <v>2</v>
-      </c>
-      <c r="C26" s="15">
-        <v>1</v>
-      </c>
-      <c r="D26" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="15">
-        <v>4055161</v>
-      </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="16" t="s">
-        <v>20</v>
       </c>
       <c r="H26" s="17"/>
       <c r="I26" s="17"/>
@@ -2147,24 +2135,24 @@
       <c r="L26" s="17"/>
     </row>
     <row r="27" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="14">
+      <c r="A27" s="15">
         <v>1402</v>
       </c>
-      <c r="B27" s="15">
-        <v>2</v>
-      </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="15">
+      <c r="B27" s="13">
+        <v>2</v>
+      </c>
+      <c r="C27" s="13">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="13">
         <v>4055162</v>
       </c>
-      <c r="F27" s="15"/>
+      <c r="F27" s="13"/>
       <c r="G27" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -2173,24 +2161,24 @@
       <c r="L27" s="17"/>
     </row>
     <row r="28" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="14">
+      <c r="A28" s="15">
         <v>1403</v>
       </c>
-      <c r="B28" s="15">
-        <v>2</v>
-      </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="15">
+      <c r="B28" s="13">
+        <v>2</v>
+      </c>
+      <c r="C28" s="13">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="13">
         <v>4055163</v>
       </c>
-      <c r="F28" s="15"/>
+      <c r="F28" s="13"/>
       <c r="G28" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
@@ -2199,24 +2187,24 @@
       <c r="L28" s="17"/>
     </row>
     <row r="29" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="14">
+      <c r="A29" s="15">
         <v>1404</v>
       </c>
-      <c r="B29" s="15">
-        <v>2</v>
-      </c>
-      <c r="C29" s="15">
-        <v>1</v>
-      </c>
-      <c r="D29" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="15">
+      <c r="B29" s="13">
+        <v>2</v>
+      </c>
+      <c r="C29" s="13">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="13">
         <v>4055164</v>
       </c>
-      <c r="F29" s="15"/>
+      <c r="F29" s="13"/>
       <c r="G29" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
@@ -2225,20 +2213,20 @@
       <c r="L29" s="17"/>
     </row>
     <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="14">
+      <c r="A30" s="15">
         <v>1405</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15">
-        <v>1</v>
-      </c>
-      <c r="D30" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
       <c r="G30" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H30" s="17"/>
       <c r="I30" s="17"/>
@@ -2247,24 +2235,24 @@
       <c r="L30" s="17"/>
     </row>
     <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="14">
+      <c r="A31" s="15">
         <v>1406</v>
       </c>
-      <c r="B31" s="15">
-        <v>2</v>
-      </c>
-      <c r="C31" s="15">
-        <v>1</v>
-      </c>
-      <c r="D31" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" s="15">
+      <c r="B31" s="13">
+        <v>2</v>
+      </c>
+      <c r="C31" s="13">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="13">
         <v>4055165</v>
       </c>
-      <c r="F31" s="15"/>
+      <c r="F31" s="13"/>
       <c r="G31" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H31" s="17"/>
       <c r="I31" s="17"/>
@@ -2282,21 +2270,21 @@
       <c r="C32" s="12">
         <v>1</v>
       </c>
-      <c r="D32" s="12" t="b">
-        <v>0</v>
+      <c r="D32" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E32" s="12">
         <v>4055181</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
     </row>
     <row r="33" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A33" s="11">
@@ -2308,21 +2296,21 @@
       <c r="C33" s="12">
         <v>1</v>
       </c>
-      <c r="D33" s="12" t="b">
-        <v>0</v>
+      <c r="D33" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E33" s="12">
         <v>4055182</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
     </row>
     <row r="34" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A34" s="11">
@@ -2332,19 +2320,19 @@
       <c r="C34" s="12">
         <v>1</v>
       </c>
-      <c r="D34" s="12" t="b">
-        <v>0</v>
+      <c r="D34" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
       <c r="G34" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
     </row>
     <row r="35" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A35" s="11">
@@ -2354,35 +2342,35 @@
       <c r="C35" s="12">
         <v>1</v>
       </c>
-      <c r="D35" s="12" t="b">
-        <v>0</v>
+      <c r="D35" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
       <c r="G35" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+    </row>
+    <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A36" s="15">
+        <v>1601</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13">
+        <v>1</v>
+      </c>
+      <c r="D36" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="16" t="s">
         <v>21</v>
-      </c>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-    </row>
-    <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="14">
-        <v>1601</v>
-      </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15">
-        <v>1</v>
-      </c>
-      <c r="D36" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="16" t="s">
-        <v>22</v>
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="17"/>
@@ -2391,20 +2379,20 @@
       <c r="L36" s="17"/>
     </row>
     <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="14">
+      <c r="A37" s="15">
         <v>1602</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15">
-        <v>1</v>
-      </c>
-      <c r="D37" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13">
+        <v>1</v>
+      </c>
+      <c r="D37" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
       <c r="G37" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
@@ -2413,24 +2401,22 @@
       <c r="L37" s="17"/>
     </row>
     <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="14">
+      <c r="A38" s="15">
         <v>1603</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15">
-        <v>1</v>
-      </c>
-      <c r="D38" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" s="15">
+      <c r="B38" s="13"/>
+      <c r="C38" s="13">
+        <v>1</v>
+      </c>
+      <c r="D38" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="13">
         <v>4055203</v>
       </c>
-      <c r="F38" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="F38" s="12"/>
       <c r="G38" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H38" s="17"/>
       <c r="I38" s="17"/>
@@ -2439,20 +2425,20 @@
       <c r="L38" s="17"/>
     </row>
     <row r="39" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A39" s="14">
+      <c r="A39" s="15">
         <v>1604</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15">
-        <v>1</v>
-      </c>
-      <c r="D39" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13">
+        <v>1</v>
+      </c>
+      <c r="D39" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
       <c r="G39" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H39" s="17"/>
       <c r="I39" s="17"/>
@@ -2461,26 +2447,24 @@
       <c r="L39" s="17"/>
     </row>
     <row r="40" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="14">
+      <c r="A40" s="15">
         <v>1605</v>
       </c>
-      <c r="B40" s="15">
-        <v>2</v>
-      </c>
-      <c r="C40" s="15">
-        <v>1</v>
-      </c>
-      <c r="D40" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" s="15">
+      <c r="B40" s="13">
+        <v>2</v>
+      </c>
+      <c r="C40" s="13">
+        <v>1</v>
+      </c>
+      <c r="D40" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="13">
         <v>4055204</v>
       </c>
-      <c r="F40" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="F40" s="12"/>
       <c r="G40" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H40" s="17"/>
       <c r="I40" s="17"/>
@@ -2489,20 +2473,20 @@
       <c r="L40" s="17"/>
     </row>
     <row r="41" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="14">
+      <c r="A41" s="15">
         <v>1606</v>
       </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15">
-        <v>1</v>
-      </c>
-      <c r="D41" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13">
+        <v>1</v>
+      </c>
+      <c r="D41" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
       <c r="G41" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H41" s="17"/>
       <c r="I41" s="17"/>
@@ -2511,22 +2495,22 @@
       <c r="L41" s="17"/>
     </row>
     <row r="42" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="14">
+      <c r="A42" s="15">
         <v>1607</v>
       </c>
-      <c r="B42" s="15">
-        <v>2</v>
-      </c>
-      <c r="C42" s="15">
-        <v>1</v>
-      </c>
-      <c r="D42" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
+      <c r="B42" s="13">
+        <v>2</v>
+      </c>
+      <c r="C42" s="13">
+        <v>1</v>
+      </c>
+      <c r="D42" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
       <c r="G42" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H42" s="17"/>
       <c r="I42" s="17"/>
@@ -2535,24 +2519,22 @@
       <c r="L42" s="17"/>
     </row>
     <row r="43" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="14">
+      <c r="A43" s="15">
         <v>1608</v>
       </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15">
-        <v>1</v>
-      </c>
-      <c r="D43" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" s="15">
+      <c r="B43" s="13"/>
+      <c r="C43" s="13">
+        <v>1</v>
+      </c>
+      <c r="D43" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="13">
         <v>4055205</v>
       </c>
-      <c r="F43" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="F43" s="12"/>
       <c r="G43" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H43" s="17"/>
       <c r="I43" s="17"/>
@@ -2561,24 +2543,22 @@
       <c r="L43" s="17"/>
     </row>
     <row r="44" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="14">
+      <c r="A44" s="15">
         <v>1609</v>
       </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15">
-        <v>1</v>
-      </c>
-      <c r="D44" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E44" s="15">
+      <c r="B44" s="13"/>
+      <c r="C44" s="13">
+        <v>1</v>
+      </c>
+      <c r="D44" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="13">
         <v>4055206</v>
       </c>
-      <c r="F44" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="F44" s="12"/>
       <c r="G44" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="17"/>
@@ -2587,26 +2567,24 @@
       <c r="L44" s="17"/>
     </row>
     <row r="45" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="14">
+      <c r="A45" s="15">
         <v>1610</v>
       </c>
-      <c r="B45" s="15">
-        <v>2</v>
-      </c>
-      <c r="C45" s="15">
-        <v>1</v>
-      </c>
-      <c r="D45" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" s="15">
+      <c r="B45" s="13">
+        <v>2</v>
+      </c>
+      <c r="C45" s="13">
+        <v>1</v>
+      </c>
+      <c r="D45" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="13">
         <v>4055207</v>
       </c>
-      <c r="F45" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="F45" s="12"/>
       <c r="G45" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H45" s="17"/>
       <c r="I45" s="17"/>
@@ -2615,26 +2593,24 @@
       <c r="L45" s="17"/>
     </row>
     <row r="46" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="14">
+      <c r="A46" s="15">
         <v>1611</v>
       </c>
-      <c r="B46" s="15">
-        <v>2</v>
-      </c>
-      <c r="C46" s="15">
-        <v>1</v>
-      </c>
-      <c r="D46" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" s="15">
+      <c r="B46" s="13">
+        <v>2</v>
+      </c>
+      <c r="C46" s="13">
+        <v>1</v>
+      </c>
+      <c r="D46" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="13">
         <v>4055208</v>
       </c>
-      <c r="F46" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="F46" s="12"/>
       <c r="G46" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H46" s="17"/>
       <c r="I46" s="17"/>
@@ -2643,26 +2619,24 @@
       <c r="L46" s="17"/>
     </row>
     <row r="47" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="14">
+      <c r="A47" s="15">
         <v>1612</v>
       </c>
-      <c r="B47" s="15">
-        <v>2</v>
-      </c>
-      <c r="C47" s="15">
-        <v>1</v>
-      </c>
-      <c r="D47" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" s="15">
+      <c r="B47" s="13">
+        <v>2</v>
+      </c>
+      <c r="C47" s="13">
+        <v>1</v>
+      </c>
+      <c r="D47" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="13">
         <v>4055209</v>
       </c>
-      <c r="F47" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="F47" s="12"/>
       <c r="G47" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H47" s="17"/>
       <c r="I47" s="17"/>
@@ -2678,19 +2652,19 @@
       <c r="C48" s="12">
         <v>1</v>
       </c>
-      <c r="D48" s="12" t="b">
-        <v>0</v>
+      <c r="D48" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
       <c r="G48" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
-      <c r="L48" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
     </row>
     <row r="49" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A49" s="11">
@@ -2699,18 +2673,18 @@
       <c r="C49" s="12">
         <v>1</v>
       </c>
-      <c r="D49" s="12" t="b">
-        <v>0</v>
+      <c r="D49" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
-      <c r="L49" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
     </row>
     <row r="50" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A50" s="11">
@@ -2722,21 +2696,21 @@
       <c r="C50" s="12">
         <v>1</v>
       </c>
-      <c r="D50" s="12" t="b">
-        <v>0</v>
+      <c r="D50" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E50" s="12">
         <v>4055222</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="14"/>
     </row>
     <row r="51" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A51" s="11">
@@ -2748,21 +2722,21 @@
       <c r="C51" s="12">
         <v>1</v>
       </c>
-      <c r="D51" s="12" t="b">
-        <v>0</v>
+      <c r="D51" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E51" s="12">
         <v>4055223</v>
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
-      <c r="L51" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="14"/>
     </row>
     <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A52" s="11">
@@ -2774,21 +2748,21 @@
       <c r="C52" s="12">
         <v>1</v>
       </c>
-      <c r="D52" s="12" t="b">
-        <v>0</v>
+      <c r="D52" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E52" s="12">
         <v>4055224</v>
       </c>
       <c r="F52" s="12"/>
       <c r="G52" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
-      <c r="L52" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
     </row>
     <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A53" s="11">
@@ -2798,19 +2772,19 @@
       <c r="C53" s="12">
         <v>1</v>
       </c>
-      <c r="D53" s="12" t="b">
-        <v>0</v>
+      <c r="D53" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
       <c r="G53" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
-      <c r="K53" s="13"/>
-      <c r="L53" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="14"/>
     </row>
     <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A54" s="11">
@@ -2822,21 +2796,21 @@
       <c r="C54" s="12">
         <v>1</v>
       </c>
-      <c r="D54" s="12" t="b">
-        <v>0</v>
+      <c r="D54" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E54" s="12">
         <v>4055225</v>
       </c>
       <c r="F54" s="12"/>
       <c r="G54" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
-      <c r="L54" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+      <c r="L54" s="14"/>
     </row>
     <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A55" s="11">
@@ -2848,21 +2822,21 @@
       <c r="C55" s="12">
         <v>1</v>
       </c>
-      <c r="D55" s="12" t="b">
-        <v>0</v>
+      <c r="D55" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E55" s="12">
         <v>4055226</v>
       </c>
       <c r="F55" s="12"/>
       <c r="G55" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
-      <c r="L55" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
     </row>
     <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A56" s="11">
@@ -2872,19 +2846,19 @@
       <c r="C56" s="12">
         <v>1</v>
       </c>
-      <c r="D56" s="12" t="b">
-        <v>0</v>
+      <c r="D56" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12"/>
       <c r="G56" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
-      <c r="L56" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
     </row>
     <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A57" s="11">
@@ -2894,19 +2868,19 @@
       <c r="C57" s="12">
         <v>1</v>
       </c>
-      <c r="D57" s="12" t="b">
-        <v>0</v>
+      <c r="D57" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12"/>
       <c r="G57" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="K57" s="13"/>
-      <c r="L57" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="14"/>
     </row>
     <row r="58" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A58" s="11">
@@ -2918,21 +2892,21 @@
       <c r="C58" s="12">
         <v>1</v>
       </c>
-      <c r="D58" s="12" t="b">
-        <v>0</v>
+      <c r="D58" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E58" s="12">
         <v>4055227</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
-      <c r="L58" s="13"/>
+        <v>22</v>
+      </c>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
     </row>
     <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A59" s="11">
@@ -2944,37 +2918,37 @@
       <c r="C59" s="12">
         <v>1</v>
       </c>
-      <c r="D59" s="12" t="b">
-        <v>0</v>
+      <c r="D59" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="E59" s="12">
         <v>4055228</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+    </row>
+    <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A60" s="15">
+        <v>1801</v>
+      </c>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13">
+        <v>1</v>
+      </c>
+      <c r="D60" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="16" t="s">
         <v>23</v>
-      </c>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
-    </row>
-    <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="14">
-        <v>1801</v>
-      </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15">
-        <v>1</v>
-      </c>
-      <c r="D60" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="16" t="s">
-        <v>24</v>
       </c>
       <c r="H60" s="17"/>
       <c r="I60" s="17"/>
@@ -2983,20 +2957,20 @@
       <c r="L60" s="17"/>
     </row>
     <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="14">
+      <c r="A61" s="15">
         <v>1802</v>
       </c>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15">
-        <v>1</v>
-      </c>
-      <c r="D61" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13">
+        <v>1</v>
+      </c>
+      <c r="D61" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
       <c r="G61" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H61" s="17"/>
       <c r="I61" s="17"/>
@@ -3005,26 +2979,24 @@
       <c r="L61" s="17"/>
     </row>
     <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A62" s="14">
+      <c r="A62" s="15">
         <v>1803</v>
       </c>
-      <c r="B62" s="15">
-        <v>2</v>
-      </c>
-      <c r="C62" s="15">
-        <v>1</v>
-      </c>
-      <c r="D62" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E62" s="15">
+      <c r="B62" s="13">
+        <v>2</v>
+      </c>
+      <c r="C62" s="13">
+        <v>1</v>
+      </c>
+      <c r="D62" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="13">
         <v>4055243</v>
       </c>
-      <c r="F62" s="15" t="s">
-        <v>16</v>
-      </c>
+      <c r="F62" s="13"/>
       <c r="G62" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H62" s="17"/>
       <c r="I62" s="17"/>
@@ -3033,26 +3005,24 @@
       <c r="L62" s="17"/>
     </row>
     <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A63" s="14">
+      <c r="A63" s="15">
         <v>1804</v>
       </c>
-      <c r="B63" s="15">
-        <v>2</v>
-      </c>
-      <c r="C63" s="15">
-        <v>1</v>
-      </c>
-      <c r="D63" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E63" s="15">
+      <c r="B63" s="13">
+        <v>2</v>
+      </c>
+      <c r="C63" s="13">
+        <v>1</v>
+      </c>
+      <c r="D63" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="13">
         <v>4055244</v>
       </c>
-      <c r="F63" s="15" t="s">
-        <v>16</v>
-      </c>
+      <c r="F63" s="13"/>
       <c r="G63" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H63" s="17"/>
       <c r="I63" s="17"/>
@@ -3061,24 +3031,24 @@
       <c r="L63" s="17"/>
     </row>
     <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A64" s="14">
+      <c r="A64" s="15">
         <v>1805</v>
       </c>
-      <c r="B64" s="15">
-        <v>2</v>
-      </c>
-      <c r="C64" s="15">
-        <v>1</v>
-      </c>
-      <c r="D64" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E64" s="15">
+      <c r="B64" s="13">
+        <v>2</v>
+      </c>
+      <c r="C64" s="13">
+        <v>1</v>
+      </c>
+      <c r="D64" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="13">
         <v>4055245</v>
       </c>
-      <c r="F64" s="15"/>
+      <c r="F64" s="13"/>
       <c r="G64" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H64" s="17"/>
       <c r="I64" s="17"/>
@@ -3087,24 +3057,24 @@
       <c r="L64" s="17"/>
     </row>
     <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A65" s="14">
+      <c r="A65" s="15">
         <v>1806</v>
       </c>
-      <c r="B65" s="15">
-        <v>2</v>
-      </c>
-      <c r="C65" s="15">
-        <v>1</v>
-      </c>
-      <c r="D65" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E65" s="15">
+      <c r="B65" s="13">
+        <v>2</v>
+      </c>
+      <c r="C65" s="13">
+        <v>1</v>
+      </c>
+      <c r="D65" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="13">
         <v>4055246</v>
       </c>
-      <c r="F65" s="15"/>
+      <c r="F65" s="13"/>
       <c r="G65" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H65" s="17"/>
       <c r="I65" s="17"/>
@@ -3113,24 +3083,24 @@
       <c r="L65" s="17"/>
     </row>
     <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="14">
+      <c r="A66" s="15">
         <v>1807</v>
       </c>
-      <c r="B66" s="15">
-        <v>2</v>
-      </c>
-      <c r="C66" s="15">
-        <v>1</v>
-      </c>
-      <c r="D66" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E66" s="15">
+      <c r="B66" s="13">
+        <v>2</v>
+      </c>
+      <c r="C66" s="13">
+        <v>1</v>
+      </c>
+      <c r="D66" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="13">
         <v>4055247</v>
       </c>
-      <c r="F66" s="15"/>
+      <c r="F66" s="13"/>
       <c r="G66" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H66" s="17"/>
       <c r="I66" s="17"/>
@@ -3146,19 +3116,19 @@
       <c r="C67" s="12">
         <v>1</v>
       </c>
-      <c r="D67" s="12" t="b">
+      <c r="D67" s="19" t="b">
         <v>0</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
       <c r="G67" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="13"/>
-      <c r="K67" s="13"/>
-      <c r="L67" s="13"/>
+        <v>24</v>
+      </c>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="14"/>
+      <c r="L67" s="14"/>
     </row>
     <row r="68" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A68" s="11">
@@ -3170,7 +3140,7 @@
       <c r="C68" s="12">
         <v>1</v>
       </c>
-      <c r="D68" s="12" t="b">
+      <c r="D68" s="19" t="b">
         <v>0</v>
       </c>
       <c r="E68" s="12">
@@ -3178,13 +3148,13 @@
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
-      <c r="L68" s="13"/>
+        <v>24</v>
+      </c>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="14"/>
     </row>
     <row r="69" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A69" s="11">
@@ -3196,7 +3166,7 @@
       <c r="C69" s="12">
         <v>1</v>
       </c>
-      <c r="D69" s="12" t="b">
+      <c r="D69" s="19" t="b">
         <v>0</v>
       </c>
       <c r="E69" s="12">
@@ -3204,29 +3174,29 @@
       </c>
       <c r="F69" s="12"/>
       <c r="G69" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="14"/>
+      <c r="L69" s="14"/>
+    </row>
+    <row r="70" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A70" s="15">
+        <v>1981</v>
+      </c>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13">
+        <v>1</v>
+      </c>
+      <c r="D70" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="16" t="s">
         <v>25</v>
-      </c>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
-      <c r="L69" s="13"/>
-    </row>
-    <row r="70" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="14">
-        <v>1981</v>
-      </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15">
-        <v>1</v>
-      </c>
-      <c r="D70" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="16" t="s">
-        <v>26</v>
       </c>
       <c r="H70" s="17"/>
       <c r="I70" s="17"/>
@@ -3235,20 +3205,20 @@
       <c r="L70" s="17"/>
     </row>
     <row r="71" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="14">
+      <c r="A71" s="15">
         <v>1982</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15">
-        <v>1</v>
-      </c>
-      <c r="D71" s="12" t="b">
+      <c r="B71" s="13"/>
+      <c r="C71" s="13">
+        <v>1</v>
+      </c>
+      <c r="D71" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
       <c r="G71" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H71" s="17"/>
       <c r="I71" s="17"/>
@@ -3257,24 +3227,24 @@
       <c r="L71" s="17"/>
     </row>
     <row r="72" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="14">
+      <c r="A72" s="15">
         <v>1983</v>
       </c>
-      <c r="B72" s="15">
-        <v>2</v>
-      </c>
-      <c r="C72" s="15">
-        <v>1</v>
-      </c>
-      <c r="D72" s="12" t="b">
+      <c r="B72" s="13">
+        <v>2</v>
+      </c>
+      <c r="C72" s="13">
+        <v>1</v>
+      </c>
+      <c r="D72" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="15">
+      <c r="E72" s="13">
         <v>4055321</v>
       </c>
-      <c r="F72" s="15"/>
+      <c r="F72" s="13"/>
       <c r="G72" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H72" s="17"/>
       <c r="I72" s="17"/>
@@ -3290,19 +3260,19 @@
       <c r="C73" s="12">
         <v>1</v>
       </c>
-      <c r="D73" s="12" t="b">
+      <c r="D73" s="19" t="b">
         <v>0</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12"/>
       <c r="G73" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="14"/>
     </row>
     <row r="74" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A74" s="11">
@@ -3314,7 +3284,7 @@
       <c r="C74" s="12">
         <v>1</v>
       </c>
-      <c r="D74" s="12" t="b">
+      <c r="D74" s="19" t="b">
         <v>0</v>
       </c>
       <c r="E74" s="12">
@@ -3322,13 +3292,13 @@
       </c>
       <c r="F74" s="12"/>
       <c r="G74" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="14"/>
     </row>
     <row r="75" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A75" s="11">
@@ -3340,7 +3310,7 @@
       <c r="C75" s="12">
         <v>1</v>
       </c>
-      <c r="D75" s="12" t="b">
+      <c r="D75" s="19" t="b">
         <v>0</v>
       </c>
       <c r="E75" s="12">
@@ -3348,13 +3318,13 @@
       </c>
       <c r="F75" s="12"/>
       <c r="G75" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
-      <c r="J75" s="13"/>
-      <c r="K75" s="13"/>
-      <c r="L75" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="14"/>
+      <c r="L75" s="14"/>
     </row>
     <row r="76" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A76" s="11">
@@ -3366,7 +3336,7 @@
       <c r="C76" s="12">
         <v>1</v>
       </c>
-      <c r="D76" s="12" t="b">
+      <c r="D76" s="19" t="b">
         <v>0</v>
       </c>
       <c r="E76" s="12">
@@ -3374,13 +3344,13 @@
       </c>
       <c r="F76" s="12"/>
       <c r="G76" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
-      <c r="J76" s="13"/>
-      <c r="K76" s="13"/>
-      <c r="L76" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+      <c r="K76" s="14"/>
+      <c r="L76" s="14"/>
     </row>
     <row r="77" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A77" s="11">
@@ -3392,7 +3362,7 @@
       <c r="C77" s="12">
         <v>1</v>
       </c>
-      <c r="D77" s="12" t="b">
+      <c r="D77" s="19" t="b">
         <v>0</v>
       </c>
       <c r="E77" s="12">
@@ -3400,13 +3370,13 @@
       </c>
       <c r="F77" s="12"/>
       <c r="G77" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
-      <c r="J77" s="13"/>
-      <c r="K77" s="13"/>
-      <c r="L77" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+      <c r="K77" s="14"/>
+      <c r="L77" s="14"/>
     </row>
     <row r="78" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A78" s="11">
@@ -3418,7 +3388,7 @@
       <c r="C78" s="12">
         <v>1</v>
       </c>
-      <c r="D78" s="12" t="b">
+      <c r="D78" s="19" t="b">
         <v>0</v>
       </c>
       <c r="E78" s="12">
@@ -3426,13 +3396,13 @@
       </c>
       <c r="F78" s="12"/>
       <c r="G78" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13"/>
-      <c r="K78" s="13"/>
-      <c r="L78" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+      <c r="K78" s="14"/>
+      <c r="L78" s="14"/>
     </row>
     <row r="79" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A79" s="11">
@@ -3444,7 +3414,7 @@
       <c r="C79" s="12">
         <v>1</v>
       </c>
-      <c r="D79" s="12" t="b">
+      <c r="D79" s="19" t="b">
         <v>0</v>
       </c>
       <c r="E79" s="12">
@@ -3452,33 +3422,33 @@
       </c>
       <c r="F79" s="12"/>
       <c r="G79" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="14"/>
+      <c r="L79" s="14"/>
+    </row>
+    <row r="80" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="20">
+        <v>2101</v>
+      </c>
+      <c r="B80" s="20">
+        <v>2</v>
+      </c>
+      <c r="C80" s="20">
+        <v>1</v>
+      </c>
+      <c r="D80" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" s="20">
+        <v>4055301</v>
+      </c>
+      <c r="F80" s="20"/>
+      <c r="G80" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-      <c r="J79" s="13"/>
-      <c r="K79" s="13"/>
-      <c r="L79" s="13"/>
-    </row>
-    <row r="80" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="19">
-        <v>2101</v>
-      </c>
-      <c r="B80" s="19">
-        <v>2</v>
-      </c>
-      <c r="C80" s="19">
-        <v>1</v>
-      </c>
-      <c r="D80" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E80" s="19">
-        <v>4055301</v>
-      </c>
-      <c r="F80" s="19"/>
-      <c r="G80" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="H80" s="17"/>
       <c r="I80" s="17"/>
@@ -3487,26 +3457,24 @@
       <c r="L80" s="17"/>
     </row>
     <row r="81" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="19">
+      <c r="A81" s="20">
         <v>2102</v>
       </c>
-      <c r="B81" s="19">
-        <v>1</v>
-      </c>
-      <c r="C81" s="19">
-        <v>1</v>
-      </c>
-      <c r="D81" s="12" t="b">
+      <c r="B81" s="20">
+        <v>1</v>
+      </c>
+      <c r="C81" s="20">
+        <v>1</v>
+      </c>
+      <c r="D81" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="E81" s="19">
+      <c r="E81" s="20">
         <v>4055303</v>
       </c>
-      <c r="F81" s="19" t="s">
-        <v>16</v>
-      </c>
+      <c r="F81" s="20"/>
       <c r="G81" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H81" s="17"/>
       <c r="I81" s="17"/>
@@ -3572,14 +3540,14 @@
         <v>2101</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2101_</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -3588,7 +3556,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3598,14 +3566,14 @@
         <v>2102</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2102_</v>
       </c>
       <c r="M6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3613,14 +3581,14 @@
         <v>2103</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2103_</v>
       </c>
       <c r="M7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3628,34 +3596,34 @@
         <v>2104</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2104_</v>
       </c>
       <c r="M8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="38">
   <si>
     <t>序号</t>
   </si>
@@ -1000,10 +1000,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1529,7 +1529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -1942,7 +1942,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="13" t="b">
         <v>1</v>
@@ -1987,46 +1987,46 @@
       <c r="L20" s="17"/>
     </row>
     <row r="21" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="11">
+      <c r="A21" s="15">
+        <v>1204</v>
+      </c>
+      <c r="B21" s="13">
+        <v>2</v>
+      </c>
+      <c r="C21" s="13">
+        <v>1</v>
+      </c>
+      <c r="D21" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="13">
+        <v>4055124</v>
+      </c>
+      <c r="F21" s="13"/>
+      <c r="G21" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+    </row>
+    <row r="22" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A22" s="11">
         <v>1301</v>
       </c>
-      <c r="B21" s="12">
-        <v>2</v>
-      </c>
-      <c r="C21" s="12">
-        <v>1</v>
-      </c>
-      <c r="D21" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12">
+      <c r="B22" s="12">
+        <v>2</v>
+      </c>
+      <c r="C22" s="12">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="12">
         <v>4055141</v>
-      </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-    </row>
-    <row r="22" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="11">
-        <v>1302</v>
-      </c>
-      <c r="B22" s="12">
-        <v>2</v>
-      </c>
-      <c r="C22" s="12">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="12">
-        <v>4055142</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="18" t="s">
@@ -2038,9 +2038,9 @@
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="23" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A23" s="11">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B23" s="12">
         <v>2</v>
@@ -2052,7 +2052,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="12">
-        <v>4055143</v>
+        <v>4055142</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="18" t="s">
@@ -2064,18 +2064,22 @@
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="24" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A24" s="11">
-        <v>1304</v>
-      </c>
-      <c r="B24" s="12"/>
+        <v>1303</v>
+      </c>
+      <c r="B24" s="12">
+        <v>2</v>
+      </c>
       <c r="C24" s="12">
         <v>1</v>
       </c>
       <c r="D24" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E24" s="12"/>
+      <c r="E24" s="12">
+        <v>4055143</v>
+      </c>
       <c r="F24" s="12"/>
       <c r="G24" s="18" t="s">
         <v>18</v>
@@ -2086,9 +2090,9 @@
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="25" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A25" s="11">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12">
@@ -2109,46 +2113,42 @@
       <c r="L25" s="14"/>
     </row>
     <row r="26" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="15">
+      <c r="A26" s="11">
+        <v>1305</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12">
+        <v>1</v>
+      </c>
+      <c r="D26" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+    </row>
+    <row r="27" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A27" s="15">
         <v>1401</v>
       </c>
-      <c r="B26" s="13">
-        <v>2</v>
-      </c>
-      <c r="C26" s="13">
-        <v>1</v>
-      </c>
-      <c r="D26" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="13">
+      <c r="B27" s="13">
+        <v>2</v>
+      </c>
+      <c r="C27" s="13">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="13">
         <v>4055161</v>
-      </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-    </row>
-    <row r="27" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="15">
-        <v>1402</v>
-      </c>
-      <c r="B27" s="13">
-        <v>2</v>
-      </c>
-      <c r="C27" s="13">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="13">
-        <v>4055162</v>
       </c>
       <c r="F27" s="13"/>
       <c r="G27" s="16" t="s">
@@ -2160,9 +2160,9 @@
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
     </row>
-    <row r="28" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="28" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A28" s="15">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B28" s="13">
         <v>2</v>
@@ -2174,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="13">
-        <v>4055163</v>
+        <v>4055162</v>
       </c>
       <c r="F28" s="13"/>
       <c r="G28" s="16" t="s">
@@ -2186,9 +2186,9 @@
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
     </row>
-    <row r="29" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="29" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A29" s="15">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B29" s="13">
         <v>2</v>
@@ -2200,7 +2200,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="13">
-        <v>4055164</v>
+        <v>4055163</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="16" t="s">
@@ -2212,18 +2212,22 @@
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
     </row>
-    <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="30" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A30" s="15">
-        <v>1405</v>
-      </c>
-      <c r="B30" s="13"/>
+        <v>1404</v>
+      </c>
+      <c r="B30" s="13">
+        <v>2</v>
+      </c>
       <c r="C30" s="13">
         <v>1</v>
       </c>
       <c r="D30" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E30" s="13"/>
+      <c r="E30" s="13">
+        <v>4055164</v>
+      </c>
       <c r="F30" s="13"/>
       <c r="G30" s="16" t="s">
         <v>19</v>
@@ -2234,22 +2238,18 @@
       <c r="K30" s="17"/>
       <c r="L30" s="17"/>
     </row>
-    <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A31" s="15">
-        <v>1406</v>
-      </c>
-      <c r="B31" s="13">
-        <v>2</v>
-      </c>
+        <v>1405</v>
+      </c>
+      <c r="B31" s="13"/>
       <c r="C31" s="13">
         <v>1</v>
       </c>
       <c r="D31" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E31" s="13">
-        <v>4055165</v>
-      </c>
+      <c r="E31" s="13"/>
       <c r="F31" s="13"/>
       <c r="G31" s="16" t="s">
         <v>19</v>
@@ -2261,46 +2261,46 @@
       <c r="L31" s="17"/>
     </row>
     <row r="32" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="11">
+      <c r="A32" s="15">
+        <v>1406</v>
+      </c>
+      <c r="B32" s="13">
+        <v>2</v>
+      </c>
+      <c r="C32" s="13">
+        <v>1</v>
+      </c>
+      <c r="D32" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="13">
+        <v>4055165</v>
+      </c>
+      <c r="F32" s="13"/>
+      <c r="G32" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+    </row>
+    <row r="33" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A33" s="11">
         <v>1501</v>
       </c>
-      <c r="B32" s="12">
-        <v>2</v>
-      </c>
-      <c r="C32" s="12">
-        <v>1</v>
-      </c>
-      <c r="D32" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="12">
+      <c r="B33" s="12">
+        <v>2</v>
+      </c>
+      <c r="C33" s="12">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="12">
         <v>4055181</v>
-      </c>
-      <c r="F32" s="12"/>
-      <c r="G32" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-    </row>
-    <row r="33" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="11">
-        <v>1502</v>
-      </c>
-      <c r="B33" s="12">
-        <v>2</v>
-      </c>
-      <c r="C33" s="12">
-        <v>1</v>
-      </c>
-      <c r="D33" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="12">
-        <v>4055182</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="18" t="s">
@@ -2312,18 +2312,22 @@
       <c r="K33" s="14"/>
       <c r="L33" s="14"/>
     </row>
-    <row r="34" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="34" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A34" s="11">
-        <v>1503</v>
-      </c>
-      <c r="B34" s="12"/>
+        <v>1502</v>
+      </c>
+      <c r="B34" s="12">
+        <v>2</v>
+      </c>
       <c r="C34" s="12">
         <v>1</v>
       </c>
       <c r="D34" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E34" s="12"/>
+      <c r="E34" s="12">
+        <v>4055182</v>
+      </c>
       <c r="F34" s="12"/>
       <c r="G34" s="18" t="s">
         <v>20</v>
@@ -2334,9 +2338,9 @@
       <c r="K34" s="14"/>
       <c r="L34" s="14"/>
     </row>
-    <row r="35" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A35" s="11">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12">
@@ -2357,30 +2361,30 @@
       <c r="L35" s="14"/>
     </row>
     <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="15">
+      <c r="A36" s="11">
+        <v>1504</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12">
+        <v>1</v>
+      </c>
+      <c r="D36" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+    </row>
+    <row r="37" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A37" s="15">
         <v>1601</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13">
-        <v>1</v>
-      </c>
-      <c r="D36" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-    </row>
-    <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="15">
-        <v>1602</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="13">
@@ -2400,9 +2404,9 @@
       <c r="K37" s="17"/>
       <c r="L37" s="17"/>
     </row>
-    <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="38" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A38" s="15">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13">
@@ -2411,10 +2415,8 @@
       <c r="D38" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E38" s="13">
-        <v>4055203</v>
-      </c>
-      <c r="F38" s="12"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
       <c r="G38" s="16" t="s">
         <v>21</v>
       </c>
@@ -2424,9 +2426,9 @@
       <c r="K38" s="17"/>
       <c r="L38" s="17"/>
     </row>
-    <row r="39" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="39" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A39" s="15">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="13">
@@ -2435,8 +2437,10 @@
       <c r="D39" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
+      <c r="E39" s="13">
+        <v>4055203</v>
+      </c>
+      <c r="F39" s="12"/>
       <c r="G39" s="16" t="s">
         <v>21</v>
       </c>
@@ -2446,23 +2450,19 @@
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
     </row>
-    <row r="40" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="40" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A40" s="15">
-        <v>1605</v>
-      </c>
-      <c r="B40" s="13">
-        <v>2</v>
-      </c>
+        <v>1604</v>
+      </c>
+      <c r="B40" s="13"/>
       <c r="C40" s="13">
         <v>1</v>
       </c>
       <c r="D40" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E40" s="13">
-        <v>4055204</v>
-      </c>
-      <c r="F40" s="12"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
       <c r="G40" s="16" t="s">
         <v>21</v>
       </c>
@@ -2472,19 +2472,23 @@
       <c r="K40" s="17"/>
       <c r="L40" s="17"/>
     </row>
-    <row r="41" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A41" s="15">
-        <v>1606</v>
-      </c>
-      <c r="B41" s="13"/>
+        <v>1605</v>
+      </c>
+      <c r="B41" s="13">
+        <v>2</v>
+      </c>
       <c r="C41" s="13">
         <v>1</v>
       </c>
       <c r="D41" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
+      <c r="E41" s="13">
+        <v>4055204</v>
+      </c>
+      <c r="F41" s="12"/>
       <c r="G41" s="16" t="s">
         <v>21</v>
       </c>
@@ -2494,13 +2498,11 @@
       <c r="K41" s="17"/>
       <c r="L41" s="17"/>
     </row>
-    <row r="42" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="42" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A42" s="15">
-        <v>1607</v>
-      </c>
-      <c r="B42" s="13">
-        <v>2</v>
-      </c>
+        <v>1606</v>
+      </c>
+      <c r="B42" s="13"/>
       <c r="C42" s="13">
         <v>1</v>
       </c>
@@ -2518,21 +2520,21 @@
       <c r="K42" s="17"/>
       <c r="L42" s="17"/>
     </row>
-    <row r="43" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="43" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A43" s="15">
-        <v>1608</v>
-      </c>
-      <c r="B43" s="13"/>
+        <v>1607</v>
+      </c>
+      <c r="B43" s="13">
+        <v>2</v>
+      </c>
       <c r="C43" s="13">
         <v>1</v>
       </c>
       <c r="D43" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E43" s="13">
-        <v>4055205</v>
-      </c>
-      <c r="F43" s="12"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
       <c r="G43" s="16" t="s">
         <v>21</v>
       </c>
@@ -2542,9 +2544,9 @@
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
     </row>
-    <row r="44" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="44" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A44" s="15">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="13">
@@ -2554,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="13">
-        <v>4055206</v>
+        <v>4055205</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="16" t="s">
@@ -2566,13 +2568,11 @@
       <c r="K44" s="17"/>
       <c r="L44" s="17"/>
     </row>
-    <row r="45" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="45" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A45" s="15">
-        <v>1610</v>
-      </c>
-      <c r="B45" s="13">
-        <v>2</v>
-      </c>
+        <v>1609</v>
+      </c>
+      <c r="B45" s="13"/>
       <c r="C45" s="13">
         <v>1</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="13">
-        <v>4055207</v>
+        <v>4055206</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="16" t="s">
@@ -2592,9 +2592,9 @@
       <c r="K45" s="17"/>
       <c r="L45" s="17"/>
     </row>
-    <row r="46" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="46" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A46" s="15">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B46" s="13">
         <v>2</v>
@@ -2606,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="13">
-        <v>4055208</v>
+        <v>4055207</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="16" t="s">
@@ -2618,9 +2618,9 @@
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
     </row>
-    <row r="47" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="47" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A47" s="15">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="B47" s="13">
         <v>2</v>
@@ -2632,7 +2632,7 @@
         <v>1</v>
       </c>
       <c r="E47" s="13">
-        <v>4055209</v>
+        <v>4055208</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="16" t="s">
@@ -2645,37 +2645,43 @@
       <c r="L47" s="17"/>
     </row>
     <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="11">
+      <c r="A48" s="15">
+        <v>1612</v>
+      </c>
+      <c r="B48" s="13">
+        <v>2</v>
+      </c>
+      <c r="C48" s="13">
+        <v>1</v>
+      </c>
+      <c r="D48" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="13">
+        <v>4055209</v>
+      </c>
+      <c r="F48" s="12"/>
+      <c r="G48" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+    </row>
+    <row r="49" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A49" s="11">
         <v>1701</v>
       </c>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12">
-        <v>1</v>
-      </c>
-      <c r="D48" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-    </row>
-    <row r="49" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="11">
-        <v>1702</v>
-      </c>
+      <c r="B49" s="12"/>
       <c r="C49" s="12">
         <v>1</v>
       </c>
       <c r="D49" s="13" t="b">
         <v>1</v>
       </c>
+      <c r="E49" s="12"/>
       <c r="F49" s="12"/>
       <c r="G49" s="18" t="s">
         <v>22</v>
@@ -2686,21 +2692,15 @@
       <c r="K49" s="14"/>
       <c r="L49" s="14"/>
     </row>
-    <row r="50" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="50" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A50" s="11">
-        <v>1703</v>
-      </c>
-      <c r="B50" s="12">
-        <v>2</v>
+        <v>1702</v>
       </c>
       <c r="C50" s="12">
         <v>1</v>
       </c>
       <c r="D50" s="13" t="b">
         <v>1</v>
-      </c>
-      <c r="E50" s="12">
-        <v>4055222</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="18" t="s">
@@ -2712,9 +2712,9 @@
       <c r="K50" s="14"/>
       <c r="L50" s="14"/>
     </row>
-    <row r="51" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="51" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A51" s="11">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="B51" s="12">
         <v>2</v>
@@ -2726,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="12">
-        <v>4055223</v>
+        <v>4055222</v>
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="18" t="s">
@@ -2738,9 +2738,9 @@
       <c r="K51" s="14"/>
       <c r="L51" s="14"/>
     </row>
-    <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="52" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A52" s="11">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="B52" s="12">
         <v>2</v>
@@ -2752,7 +2752,7 @@
         <v>1</v>
       </c>
       <c r="E52" s="12">
-        <v>4055224</v>
+        <v>4055223</v>
       </c>
       <c r="F52" s="12"/>
       <c r="G52" s="18" t="s">
@@ -2764,18 +2764,22 @@
       <c r="K52" s="14"/>
       <c r="L52" s="14"/>
     </row>
-    <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="53" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A53" s="11">
-        <v>1706</v>
-      </c>
-      <c r="B53" s="12"/>
+        <v>1705</v>
+      </c>
+      <c r="B53" s="12">
+        <v>2</v>
+      </c>
       <c r="C53" s="12">
         <v>1</v>
       </c>
       <c r="D53" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E53" s="12"/>
+      <c r="E53" s="12">
+        <v>4055224</v>
+      </c>
       <c r="F53" s="12"/>
       <c r="G53" s="18" t="s">
         <v>22</v>
@@ -2786,22 +2790,18 @@
       <c r="K53" s="14"/>
       <c r="L53" s="14"/>
     </row>
-    <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="54" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A54" s="11">
-        <v>1707</v>
-      </c>
-      <c r="B54" s="12">
-        <v>2</v>
-      </c>
+        <v>1706</v>
+      </c>
+      <c r="B54" s="12"/>
       <c r="C54" s="12">
         <v>1</v>
       </c>
       <c r="D54" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E54" s="12">
-        <v>4055225</v>
-      </c>
+      <c r="E54" s="12"/>
       <c r="F54" s="12"/>
       <c r="G54" s="18" t="s">
         <v>22</v>
@@ -2812,9 +2812,9 @@
       <c r="K54" s="14"/>
       <c r="L54" s="14"/>
     </row>
-    <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="55" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A55" s="11">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="B55" s="12">
         <v>2</v>
@@ -2826,7 +2826,7 @@
         <v>1</v>
       </c>
       <c r="E55" s="12">
-        <v>4055226</v>
+        <v>4055225</v>
       </c>
       <c r="F55" s="12"/>
       <c r="G55" s="18" t="s">
@@ -2838,18 +2838,22 @@
       <c r="K55" s="14"/>
       <c r="L55" s="14"/>
     </row>
-    <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="56" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A56" s="11">
-        <v>1709</v>
-      </c>
-      <c r="B56" s="12"/>
+        <v>1708</v>
+      </c>
+      <c r="B56" s="12">
+        <v>2</v>
+      </c>
       <c r="C56" s="12">
         <v>1</v>
       </c>
       <c r="D56" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E56" s="12"/>
+      <c r="E56" s="12">
+        <v>4055226</v>
+      </c>
       <c r="F56" s="12"/>
       <c r="G56" s="18" t="s">
         <v>22</v>
@@ -2860,9 +2864,9 @@
       <c r="K56" s="14"/>
       <c r="L56" s="14"/>
     </row>
-    <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="57" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A57" s="11">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="12">
@@ -2882,22 +2886,18 @@
       <c r="K57" s="14"/>
       <c r="L57" s="14"/>
     </row>
-    <row r="58" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="58" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A58" s="11">
-        <v>1711</v>
-      </c>
-      <c r="B58" s="12">
-        <v>2</v>
-      </c>
+        <v>1710</v>
+      </c>
+      <c r="B58" s="12"/>
       <c r="C58" s="12">
         <v>1</v>
       </c>
       <c r="D58" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E58" s="12">
-        <v>4055227</v>
-      </c>
+      <c r="E58" s="12"/>
       <c r="F58" s="12"/>
       <c r="G58" s="18" t="s">
         <v>22</v>
@@ -2908,9 +2908,9 @@
       <c r="K58" s="14"/>
       <c r="L58" s="14"/>
     </row>
-    <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="59" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A59" s="11">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="B59" s="12">
         <v>2</v>
@@ -2922,7 +2922,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="12">
-        <v>4055228</v>
+        <v>4055227</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="18" t="s">
@@ -2935,30 +2935,34 @@
       <c r="L59" s="14"/>
     </row>
     <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="15">
+      <c r="A60" s="11">
+        <v>1712</v>
+      </c>
+      <c r="B60" s="12">
+        <v>2</v>
+      </c>
+      <c r="C60" s="12">
+        <v>1</v>
+      </c>
+      <c r="D60" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="12">
+        <v>4055228</v>
+      </c>
+      <c r="F60" s="12"/>
+      <c r="G60" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+    </row>
+    <row r="61" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A61" s="15">
         <v>1801</v>
-      </c>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13">
-        <v>1</v>
-      </c>
-      <c r="D60" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
-    </row>
-    <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="15">
-        <v>1802</v>
       </c>
       <c r="B61" s="13"/>
       <c r="C61" s="13">
@@ -2978,22 +2982,18 @@
       <c r="K61" s="17"/>
       <c r="L61" s="17"/>
     </row>
-    <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="62" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A62" s="15">
-        <v>1803</v>
-      </c>
-      <c r="B62" s="13">
-        <v>2</v>
-      </c>
+        <v>1802</v>
+      </c>
+      <c r="B62" s="13"/>
       <c r="C62" s="13">
         <v>1</v>
       </c>
       <c r="D62" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E62" s="13">
-        <v>4055243</v>
-      </c>
+      <c r="E62" s="13"/>
       <c r="F62" s="13"/>
       <c r="G62" s="16" t="s">
         <v>23</v>
@@ -3004,9 +3004,9 @@
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
     </row>
-    <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="63" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A63" s="15">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="B63" s="13">
         <v>2</v>
@@ -3018,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="E63" s="13">
-        <v>4055244</v>
+        <v>4055243</v>
       </c>
       <c r="F63" s="13"/>
       <c r="G63" s="16" t="s">
@@ -3030,9 +3030,9 @@
       <c r="K63" s="17"/>
       <c r="L63" s="17"/>
     </row>
-    <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="64" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A64" s="15">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="B64" s="13">
         <v>2</v>
@@ -3044,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="E64" s="13">
-        <v>4055245</v>
+        <v>4055244</v>
       </c>
       <c r="F64" s="13"/>
       <c r="G64" s="16" t="s">
@@ -3056,9 +3056,9 @@
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
     </row>
-    <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="65" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A65" s="15">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B65" s="13">
         <v>2</v>
@@ -3070,7 +3070,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="13">
-        <v>4055246</v>
+        <v>4055245</v>
       </c>
       <c r="F65" s="13"/>
       <c r="G65" s="16" t="s">
@@ -3082,9 +3082,9 @@
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
     </row>
-    <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A66" s="15">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B66" s="13">
         <v>2</v>
@@ -3096,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="13">
-        <v>4055247</v>
+        <v>4055246</v>
       </c>
       <c r="F66" s="13"/>
       <c r="G66" s="16" t="s">
@@ -3109,43 +3109,43 @@
       <c r="L66" s="17"/>
     </row>
     <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="11">
+      <c r="A67" s="15">
+        <v>1807</v>
+      </c>
+      <c r="B67" s="13">
+        <v>2</v>
+      </c>
+      <c r="C67" s="13">
+        <v>1</v>
+      </c>
+      <c r="D67" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="13">
+        <v>4055247</v>
+      </c>
+      <c r="F67" s="13"/>
+      <c r="G67" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+    </row>
+    <row r="68" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A68" s="11">
         <v>1901</v>
       </c>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12">
-        <v>1</v>
-      </c>
-      <c r="D67" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H67" s="14"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="14"/>
-      <c r="L67" s="14"/>
-    </row>
-    <row r="68" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="11">
-        <v>1902</v>
-      </c>
-      <c r="B68" s="12">
-        <v>2</v>
-      </c>
+      <c r="B68" s="12"/>
       <c r="C68" s="12">
         <v>1</v>
       </c>
       <c r="D68" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="E68" s="12">
-        <v>4055263</v>
-      </c>
+      <c r="E68" s="12"/>
       <c r="F68" s="12"/>
       <c r="G68" s="18" t="s">
         <v>24</v>
@@ -3156,9 +3156,9 @@
       <c r="K68" s="14"/>
       <c r="L68" s="14"/>
     </row>
-    <row r="69" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="69" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A69" s="11">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B69" s="12">
         <v>2</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="12">
-        <v>4055264</v>
+        <v>4055263</v>
       </c>
       <c r="F69" s="12"/>
       <c r="G69" s="18" t="s">
@@ -3183,30 +3183,34 @@
       <c r="L69" s="14"/>
     </row>
     <row r="70" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="15">
-        <v>1981</v>
-      </c>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13">
+      <c r="A70" s="11">
+        <v>1903</v>
+      </c>
+      <c r="B70" s="12">
+        <v>2</v>
+      </c>
+      <c r="C70" s="12">
         <v>1</v>
       </c>
       <c r="D70" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H70" s="17"/>
-      <c r="I70" s="17"/>
-      <c r="J70" s="17"/>
-      <c r="K70" s="17"/>
-      <c r="L70" s="17"/>
-    </row>
-    <row r="71" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="E70" s="12">
+        <v>4055264</v>
+      </c>
+      <c r="F70" s="12"/>
+      <c r="G70" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="14"/>
+      <c r="L70" s="14"/>
+    </row>
+    <row r="71" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A71" s="15">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B71" s="13"/>
       <c r="C71" s="13">
@@ -3226,22 +3230,18 @@
       <c r="K71" s="17"/>
       <c r="L71" s="17"/>
     </row>
-    <row r="72" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A72" s="15">
-        <v>1983</v>
-      </c>
-      <c r="B72" s="13">
-        <v>2</v>
-      </c>
+        <v>1982</v>
+      </c>
+      <c r="B72" s="13"/>
       <c r="C72" s="13">
         <v>1</v>
       </c>
       <c r="D72" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="13">
-        <v>4055321</v>
-      </c>
+      <c r="E72" s="13"/>
       <c r="F72" s="13"/>
       <c r="G72" s="16" t="s">
         <v>25</v>
@@ -3253,43 +3253,43 @@
       <c r="L72" s="17"/>
     </row>
     <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A73" s="11">
-        <v>2001</v>
-      </c>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12">
+      <c r="A73" s="15">
+        <v>1983</v>
+      </c>
+      <c r="B73" s="13">
+        <v>2</v>
+      </c>
+      <c r="C73" s="13">
         <v>1</v>
       </c>
       <c r="D73" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="E73" s="12"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
-      <c r="J73" s="14"/>
-      <c r="K73" s="14"/>
-      <c r="L73" s="14"/>
-    </row>
-    <row r="74" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="E73" s="13">
+        <v>4055321</v>
+      </c>
+      <c r="F73" s="13"/>
+      <c r="G73" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H73" s="17"/>
+      <c r="I73" s="17"/>
+      <c r="J73" s="17"/>
+      <c r="K73" s="17"/>
+      <c r="L73" s="17"/>
+    </row>
+    <row r="74" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A74" s="11">
-        <v>2002</v>
-      </c>
-      <c r="B74" s="12">
-        <v>2</v>
-      </c>
+        <v>2001</v>
+      </c>
+      <c r="B74" s="12"/>
       <c r="C74" s="12">
         <v>1</v>
       </c>
       <c r="D74" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="E74" s="12">
-        <v>4055281</v>
-      </c>
+      <c r="E74" s="12"/>
       <c r="F74" s="12"/>
       <c r="G74" s="18" t="s">
         <v>26</v>
@@ -3300,9 +3300,9 @@
       <c r="K74" s="14"/>
       <c r="L74" s="14"/>
     </row>
-    <row r="75" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="75" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A75" s="11">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B75" s="12">
         <v>2</v>
@@ -3314,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="12">
-        <v>4055282</v>
+        <v>4055281</v>
       </c>
       <c r="F75" s="12"/>
       <c r="G75" s="18" t="s">
@@ -3326,9 +3326,9 @@
       <c r="K75" s="14"/>
       <c r="L75" s="14"/>
     </row>
-    <row r="76" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="76" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A76" s="11">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B76" s="12">
         <v>2</v>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="12">
-        <v>4055283</v>
+        <v>4055282</v>
       </c>
       <c r="F76" s="12"/>
       <c r="G76" s="18" t="s">
@@ -3352,9 +3352,9 @@
       <c r="K76" s="14"/>
       <c r="L76" s="14"/>
     </row>
-    <row r="77" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="77" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A77" s="11">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B77" s="12">
         <v>2</v>
@@ -3366,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="12">
-        <v>4055284</v>
+        <v>4055283</v>
       </c>
       <c r="F77" s="12"/>
       <c r="G77" s="18" t="s">
@@ -3378,9 +3378,9 @@
       <c r="K77" s="14"/>
       <c r="L77" s="14"/>
     </row>
-    <row r="78" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="78" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A78" s="11">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B78" s="12">
         <v>2</v>
@@ -3392,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="12">
-        <v>4055285</v>
+        <v>4055284</v>
       </c>
       <c r="F78" s="12"/>
       <c r="G78" s="18" t="s">
@@ -3404,9 +3404,9 @@
       <c r="K78" s="14"/>
       <c r="L78" s="14"/>
     </row>
-    <row r="79" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="79" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A79" s="11">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B79" s="12">
         <v>2</v>
@@ -3418,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="12">
-        <v>4055286</v>
+        <v>4055285</v>
       </c>
       <c r="F79" s="12"/>
       <c r="G79" s="18" t="s">
@@ -3430,38 +3430,38 @@
       <c r="K79" s="14"/>
       <c r="L79" s="14"/>
     </row>
-    <row r="80" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="20">
-        <v>2101</v>
-      </c>
-      <c r="B80" s="20">
-        <v>2</v>
-      </c>
-      <c r="C80" s="20">
+    <row r="80" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="11">
+        <v>2007</v>
+      </c>
+      <c r="B80" s="12">
+        <v>2</v>
+      </c>
+      <c r="C80" s="12">
         <v>1</v>
       </c>
       <c r="D80" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="E80" s="20">
-        <v>4055301</v>
-      </c>
-      <c r="F80" s="20"/>
-      <c r="G80" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="17"/>
-      <c r="L80" s="17"/>
+      <c r="E80" s="12">
+        <v>4055286</v>
+      </c>
+      <c r="F80" s="12"/>
+      <c r="G80" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+      <c r="K80" s="14"/>
+      <c r="L80" s="14"/>
     </row>
     <row r="81" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A81" s="20">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B81" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" s="20">
         <v>1</v>
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="20">
-        <v>4055303</v>
+        <v>4055301</v>
       </c>
       <c r="F81" s="20"/>
       <c r="G81" s="5" t="s">
@@ -3481,6 +3481,32 @@
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
       <c r="L81" s="17"/>
+    </row>
+    <row r="82" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A82" s="20">
+        <v>2102</v>
+      </c>
+      <c r="B82" s="20">
+        <v>1</v>
+      </c>
+      <c r="C82" s="20">
+        <v>1</v>
+      </c>
+      <c r="D82" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" s="20">
+        <v>4055303</v>
+      </c>
+      <c r="F82" s="20"/>
+      <c r="G82" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H82" s="17"/>
+      <c r="I82" s="17"/>
+      <c r="J82" s="17"/>
+      <c r="K82" s="17"/>
+      <c r="L82" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="90">
   <si>
     <t>序号</t>
   </si>
@@ -233,37 +233,194 @@
     <t>初入游戏-创建新号到经营大厅</t>
   </si>
   <si>
+    <t>欢迎来到GECA黄金星娱乐城，梦想由此启航！</t>
+  </si>
+  <si>
+    <t>娱乐城处处是机遇！</t>
+  </si>
+  <si>
+    <t>先前往SLOT区试试手气！</t>
+  </si>
+  <si>
+    <t>点击&lt;color=#00bfff&gt;旋转&lt;/color&gt;按钮，赢取大奖！</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>恭喜获得大奖！</t>
+  </si>
+  <si>
+    <t>聘请您成为GECA黄金星娱乐城经理人！</t>
+  </si>
+  <si>
+    <t>很高兴加入集团，将娱乐城打造为世界第一！</t>
+  </si>
+  <si>
+    <t>持续研发游戏、扩建新区，提升收益发展娱乐城！</t>
+  </si>
+  <si>
+    <t>开始经营娱乐城！</t>
+  </si>
+  <si>
     <t>建筑-愤怒的小鸟-升级1次</t>
   </si>
   <si>
+    <t>点击[+]图标解锁SLOT游戏&lt;color=#00bfff&gt;萌宠小队&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>点击&lt;color=#00bfff&gt;游戏建筑&lt;/color&gt;进行升级提升收益。</t>
+  </si>
+  <si>
+    <t>点击&lt;color=#00bfff&gt;升级&lt;/color&gt;按钮，对建筑进行升级。</t>
+  </si>
+  <si>
+    <t>点击&lt;color=#00bfff&gt;开始游戏&lt;/color&gt;进入SLOT游戏，探索新玩法。</t>
+  </si>
+  <si>
     <t>建筑-愤怒的小鸟-SLOT</t>
   </si>
   <si>
+    <t>消耗&lt;sprite name="tiliIcon"&gt;赢奖有机会获得研究值
+[&lt;sprite name="yjdIcon"&gt;研究点：用于升级提升爆奖属性和经营收益</t>
+  </si>
+  <si>
+    <t>点击&lt;color=#00bfff&gt;旋转&lt;/color&gt;按钮，开启SLOT游戏旅程！</t>
+  </si>
+  <si>
+    <t>请&lt;color=#00bfff&gt;再次旋转&lt;/color&gt;游戏</t>
+  </si>
+  <si>
     <t>建筑-愤怒的小鸟-升到2级</t>
   </si>
   <si>
+    <t>请再次&lt;color=#00bfff&gt;连续点击&lt;/color&gt;升级按钮</t>
+  </si>
+  <si>
+    <t>建筑升级需要时间，使用&lt;color=#00bfff&gt;加速卡、钻石或观看广告&lt;/color&gt;可以加速完成</t>
+  </si>
+  <si>
+    <t>提高爆率赢取大奖需要提升科研等级！点击&lt;color=#00bfff&gt;科研&lt;/color&gt;进行升级</t>
+  </si>
+  <si>
+    <t>每个游戏可以进行多项科研，科研等级越高，中奖概率越大！</t>
+  </si>
+  <si>
+    <t>科研升级成功！进入游戏体验爆奖效果。</t>
+  </si>
+  <si>
     <t>建筑-愤怒的小鸟-SLOT2</t>
   </si>
   <si>
+    <t>请点击&lt;color=#00bfff&gt;旋转按钮&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>请&lt;color=#00bfff&gt;再次旋转游戏&lt;/color&gt;</t>
+  </si>
+  <si>
     <t>雇员-抽卡-升级-升星</t>
   </si>
   <si>
+    <t>前往招募管理人才！</t>
+  </si>
+  <si>
+    <t>点击&lt;color=#00bfff&gt;按钮&lt;/color&gt;开始招募！</t>
+  </si>
+  <si>
+    <t>选择雇员类型&lt;color=#00bfff&gt;游戏经理&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>游戏经理可为建筑增加收益加成。每类建筑可任命一名雇员作为主管。</t>
+  </si>
+  <si>
+    <t>将雇员任命为主管，雇员特殊属性才会生效。</t>
+  </si>
+  <si>
+    <t>雇员等级越高，固定加成越多。培训可提升等级！</t>
+  </si>
+  <si>
+    <t>任命主管人员星级越高，建筑加成比例越高，需重点培养！</t>
+  </si>
+  <si>
     <t>游客-抽卡-升星</t>
   </si>
   <si>
+    <t>点击这里进入&lt;color=#00bfff&gt;邀请特殊游客&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>点击这里查看并使用已获得的&lt;color=#00bfff&gt;游客特邀卡&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>特邀卡支持一键邀请或单个邀请，邀请后游客会带来丰厚的收益。</t>
+  </si>
+  <si>
+    <t>成功邀请特殊游客！继续解锁新游客！</t>
+  </si>
+  <si>
+    <t>请点击&lt;color=#00bfff&gt;游客&lt;/color&gt;按钮</t>
+  </si>
+  <si>
+    <t>获得特殊游客！&lt;color=#00bfff&gt;升星&lt;/color&gt;可提升游客价值。</t>
+  </si>
+  <si>
+    <t>游客升星提升游客价值增加运营收益，有&lt;color=#00bfff&gt;概率掉落稀有道具&lt;/color&gt;</t>
+  </si>
+  <si>
     <t>建筑-象财神-升级</t>
   </si>
   <si>
+    <t>新建筑需解锁后才能激活新游戏！</t>
+  </si>
+  <si>
+    <t>请及时对建筑进行升级，提高运营收益。</t>
+  </si>
+  <si>
+    <t>&lt;color=#00bfff&gt;连续点击&lt;/color&gt;对当前建筑进行升级</t>
+  </si>
+  <si>
+    <t>建筑升级需要等待，使用&lt;color=#00bfff&gt;加速卡、钻石或观看广告&lt;/color&gt;可加速完成</t>
+  </si>
+  <si>
+    <t>游戏&lt;color=#00bfff&gt;象财神&lt;/color&gt;已解锁，前往体验！</t>
+  </si>
+  <si>
     <t>赛季-界面-SLOT</t>
   </si>
   <si>
+    <t>点击这里进入&lt;color=#00bfff&gt;赛季&lt;/color&gt;界面</t>
+  </si>
+  <si>
+    <t>体验经典游戏！游戏需消耗&lt;color=#00bfff&gt;赛季币&lt;/color&gt;，赚取赛季币也是重要目标。</t>
+  </si>
+  <si>
     <t>赛季-斗仙牌-前置</t>
   </si>
   <si>
+    <t>【Aether Trial】是赛季核心&lt;color=#00bfff&gt;多人竞技玩法&lt;/color&gt;，使用赛季币参与。</t>
+  </si>
+  <si>
     <t>赛季-斗仙牌</t>
   </si>
   <si>
+    <t>准备好了吗？开始游戏！</t>
+  </si>
+  <si>
+    <t>点击区域可以快速提起该区域最大牌型</t>
+  </si>
+  <si>
+    <t>点击&lt;color=#00bfff&gt;放入&lt;/color&gt;牌型到指定区域内</t>
+  </si>
+  <si>
+    <t>在未提牌时，点击区域内的牌可将牌&lt;color=#00bfff&gt;取回&lt;/color&gt;</t>
+  </si>
+  <si>
     <t>联盟</t>
+  </si>
+  <si>
+    <t>和好友完成联盟任务与每日捐献，可获得稀有联盟道具！</t>
+  </si>
+  <si>
+    <t>加入联盟有两种方式：加入他人联盟或自己创建，和好友共同赚取收益！</t>
   </si>
   <si>
     <t>_</t>
@@ -346,13 +503,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B0F0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -981,7 +1138,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1006,6 +1163,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1027,14 +1187,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1539,39 +1699,40 @@
     <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="85.2916666666667" style="8" customWidth="1"/>
     <col min="13" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1"/>
+      <c r="H1" s="8"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
       <c r="L1"/>
     </row>
     <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1583,1930 +1744,2086 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="8"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="8"/>
       <c r="I3"/>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="10"/>
-      <c r="H4"/>
+      <c r="A4" s="11"/>
+      <c r="H4" s="8"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
     </row>
     <row r="5" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="11">
+      <c r="A5" s="12">
         <v>1001</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="13">
         <v>4055101</v>
       </c>
-      <c r="F5" s="12"/>
+      <c r="F5" s="13"/>
       <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
+      <c r="H5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="11">
+      <c r="A6" s="12">
         <v>1002</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="13">
         <v>4055102</v>
       </c>
-      <c r="F6" s="12"/>
+      <c r="F6" s="13"/>
       <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
+      <c r="H6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="11">
+      <c r="A7" s="12">
         <v>1003</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="12">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="13">
         <v>4055103</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="13"/>
       <c r="G7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
+      <c r="H7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="11">
+      <c r="A8" s="12">
         <v>1004</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="12">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13">
         <v>4055104</v>
       </c>
-      <c r="F8" s="12"/>
+      <c r="F8" s="13"/>
       <c r="G8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
+      <c r="H8" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="11">
+      <c r="A9" s="12">
         <v>1005</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
       <c r="G9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="H9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="11">
+      <c r="A10" s="12">
         <v>1006</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="12">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13">
         <v>4055105</v>
       </c>
-      <c r="F10" s="12"/>
+      <c r="F10" s="13"/>
       <c r="G10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
+      <c r="H10" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="11">
+      <c r="A11" s="12">
         <v>1007</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="12">
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="13">
         <v>4055106</v>
       </c>
-      <c r="F11" s="12"/>
+      <c r="F11" s="13"/>
       <c r="G11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
+      <c r="H11" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="11">
+      <c r="A12" s="12">
         <v>1008</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
       <c r="G12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
+      <c r="H12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="11">
+      <c r="A13" s="12">
         <v>1009</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
       <c r="G13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
+      <c r="H13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
     </row>
     <row r="14" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="11">
+      <c r="A14" s="12">
         <v>1010</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
       <c r="G14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
+      <c r="H14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
     </row>
     <row r="15" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="11">
+      <c r="A15" s="12">
         <v>1011</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="12">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13">
         <v>4055107</v>
       </c>
-      <c r="F15" s="12"/>
+      <c r="F15" s="13"/>
       <c r="G15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
+      <c r="H15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
     </row>
     <row r="16" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="11">
+      <c r="A16" s="12">
         <v>1012</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="12">
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13">
         <v>4055108</v>
       </c>
-      <c r="F16" s="12"/>
+      <c r="F16" s="13"/>
       <c r="G16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
+      <c r="H16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
     </row>
     <row r="17" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="11">
+      <c r="A17" s="12">
         <v>1013</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="12">
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="13">
         <v>4055109</v>
       </c>
-      <c r="F17" s="12"/>
+      <c r="F17" s="13"/>
       <c r="G17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
+      <c r="H17" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
     </row>
     <row r="18" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="15">
+      <c r="A18" s="17">
         <v>1201</v>
       </c>
-      <c r="B18" s="13">
-        <v>2</v>
-      </c>
-      <c r="C18" s="13">
-        <v>2</v>
-      </c>
-      <c r="D18" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="13">
+      <c r="B18" s="14">
+        <v>2</v>
+      </c>
+      <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
         <v>4055121</v>
       </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
     </row>
     <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="15">
+      <c r="A19" s="17">
         <v>1202</v>
       </c>
-      <c r="B19" s="13">
-        <v>2</v>
-      </c>
-      <c r="C19" s="13">
-        <v>2</v>
-      </c>
-      <c r="D19" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="13">
+      <c r="B19" s="14">
+        <v>2</v>
+      </c>
+      <c r="C19" s="14">
+        <v>2</v>
+      </c>
+      <c r="D19" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14">
         <v>4055122</v>
       </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
     </row>
     <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="15">
+      <c r="A20" s="17">
         <v>1203</v>
       </c>
-      <c r="B20" s="13">
-        <v>2</v>
-      </c>
-      <c r="C20" s="13">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="13">
+      <c r="B20" s="14">
+        <v>2</v>
+      </c>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
         <v>4055123</v>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
     </row>
     <row r="21" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="15">
+      <c r="A21" s="17">
         <v>1204</v>
       </c>
-      <c r="B21" s="13">
-        <v>2</v>
-      </c>
-      <c r="C21" s="13">
-        <v>1</v>
-      </c>
-      <c r="D21" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="13">
+      <c r="B21" s="14">
+        <v>2</v>
+      </c>
+      <c r="C21" s="14">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="14">
         <v>4055124</v>
       </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="11">
+      <c r="A22" s="12">
         <v>1301</v>
       </c>
-      <c r="B22" s="12">
-        <v>2</v>
-      </c>
-      <c r="C22" s="12">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="12">
+      <c r="B22" s="13">
+        <v>2</v>
+      </c>
+      <c r="C22" s="13">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="13">
         <v>4055141</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
     </row>
     <row r="23" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A23" s="11">
+      <c r="A23" s="12">
         <v>1302</v>
       </c>
-      <c r="B23" s="12">
-        <v>2</v>
-      </c>
-      <c r="C23" s="12">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="12">
+      <c r="B23" s="13">
+        <v>2</v>
+      </c>
+      <c r="C23" s="13">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="13">
         <v>4055142</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
     </row>
     <row r="24" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A24" s="11">
+      <c r="A24" s="12">
         <v>1303</v>
       </c>
-      <c r="B24" s="12">
-        <v>2</v>
-      </c>
-      <c r="C24" s="12">
-        <v>1</v>
-      </c>
-      <c r="D24" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="12">
+      <c r="B24" s="13">
+        <v>2</v>
+      </c>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="13">
         <v>4055143</v>
       </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
     </row>
     <row r="25" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="11">
+      <c r="A25" s="12">
         <v>1304</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12">
-        <v>1</v>
-      </c>
-      <c r="D25" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
     </row>
     <row r="26" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="11">
+      <c r="A26" s="12">
         <v>1305</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12">
-        <v>1</v>
-      </c>
-      <c r="D26" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13">
+        <v>1</v>
+      </c>
+      <c r="D26" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
     </row>
     <row r="27" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="15">
+      <c r="A27" s="17">
         <v>1401</v>
       </c>
-      <c r="B27" s="13">
-        <v>2</v>
-      </c>
-      <c r="C27" s="13">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="13">
+      <c r="B27" s="14">
+        <v>2</v>
+      </c>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
         <v>4055161</v>
       </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
     </row>
     <row r="28" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="15">
+      <c r="A28" s="17">
         <v>1402</v>
       </c>
-      <c r="B28" s="13">
-        <v>2</v>
-      </c>
-      <c r="C28" s="13">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="13">
+      <c r="B28" s="14">
+        <v>2</v>
+      </c>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
         <v>4055162</v>
       </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
     </row>
     <row r="29" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="15">
+      <c r="A29" s="17">
         <v>1403</v>
       </c>
-      <c r="B29" s="13">
-        <v>2</v>
-      </c>
-      <c r="C29" s="13">
-        <v>1</v>
-      </c>
-      <c r="D29" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="13">
+      <c r="B29" s="14">
+        <v>2</v>
+      </c>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14">
         <v>4055163</v>
       </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
     </row>
     <row r="30" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="15">
+      <c r="A30" s="17">
         <v>1404</v>
       </c>
-      <c r="B30" s="13">
-        <v>2</v>
-      </c>
-      <c r="C30" s="13">
-        <v>1</v>
-      </c>
-      <c r="D30" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="13">
+      <c r="B30" s="14">
+        <v>2</v>
+      </c>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14">
         <v>4055164</v>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
     </row>
     <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="15">
+      <c r="A31" s="17">
         <v>1405</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13">
-        <v>1</v>
-      </c>
-      <c r="D31" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
     </row>
     <row r="32" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="15">
+      <c r="A32" s="17">
         <v>1406</v>
       </c>
-      <c r="B32" s="13">
-        <v>2</v>
-      </c>
-      <c r="C32" s="13">
-        <v>1</v>
-      </c>
-      <c r="D32" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="13">
+      <c r="B32" s="14">
+        <v>2</v>
+      </c>
+      <c r="C32" s="14">
+        <v>1</v>
+      </c>
+      <c r="D32" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="14">
         <v>4055165</v>
       </c>
-      <c r="F32" s="13"/>
-      <c r="G32" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
     </row>
     <row r="33" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="11">
+      <c r="A33" s="12">
         <v>1501</v>
       </c>
-      <c r="B33" s="12">
-        <v>2</v>
-      </c>
-      <c r="C33" s="12">
-        <v>1</v>
-      </c>
-      <c r="D33" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="12">
+      <c r="B33" s="13">
+        <v>2</v>
+      </c>
+      <c r="C33" s="13">
+        <v>1</v>
+      </c>
+      <c r="D33" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13">
         <v>4055181</v>
       </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
     </row>
     <row r="34" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="11">
+      <c r="A34" s="12">
         <v>1502</v>
       </c>
-      <c r="B34" s="12">
-        <v>2</v>
-      </c>
-      <c r="C34" s="12">
-        <v>1</v>
-      </c>
-      <c r="D34" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="12">
+      <c r="B34" s="13">
+        <v>2</v>
+      </c>
+      <c r="C34" s="13">
+        <v>1</v>
+      </c>
+      <c r="D34" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="13">
         <v>4055182</v>
       </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
     </row>
     <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="11">
+      <c r="A35" s="12">
         <v>1503</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12">
-        <v>1</v>
-      </c>
-      <c r="D35" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13">
+        <v>1</v>
+      </c>
+      <c r="D35" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
     </row>
     <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="11">
+      <c r="A36" s="12">
         <v>1504</v>
       </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12">
-        <v>1</v>
-      </c>
-      <c r="D36" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13">
+        <v>1</v>
+      </c>
+      <c r="D36" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
     </row>
     <row r="37" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="15">
+      <c r="A37" s="17">
         <v>1601</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13">
-        <v>1</v>
-      </c>
-      <c r="D37" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="16" t="s">
+      <c r="B37" s="14"/>
+      <c r="C37" s="14">
+        <v>1</v>
+      </c>
+      <c r="D37" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H37" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
     </row>
     <row r="38" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="15">
+      <c r="A38" s="17">
         <v>1602</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13">
-        <v>1</v>
-      </c>
-      <c r="D38" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="16" t="s">
+      <c r="B38" s="14"/>
+      <c r="C38" s="14">
+        <v>1</v>
+      </c>
+      <c r="D38" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H38" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
     </row>
     <row r="39" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A39" s="15">
+      <c r="A39" s="17">
         <v>1603</v>
       </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13">
-        <v>1</v>
-      </c>
-      <c r="D39" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="13">
+      <c r="B39" s="14"/>
+      <c r="C39" s="14">
+        <v>1</v>
+      </c>
+      <c r="D39" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="14">
         <v>4055203</v>
       </c>
-      <c r="F39" s="12"/>
-      <c r="G39" s="16" t="s">
+      <c r="F39" s="13"/>
+      <c r="G39" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+    </row>
+    <row r="40" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A40" s="17">
+        <v>1604</v>
+      </c>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14">
+        <v>1</v>
+      </c>
+      <c r="D40" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H40" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-    </row>
-    <row r="40" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="15">
-        <v>1604</v>
-      </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13">
-        <v>1</v>
-      </c>
-      <c r="D40" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="16" t="s">
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+    </row>
+    <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A41" s="17">
+        <v>1605</v>
+      </c>
+      <c r="B41" s="14">
+        <v>2</v>
+      </c>
+      <c r="C41" s="14">
+        <v>1</v>
+      </c>
+      <c r="D41" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="14">
+        <v>4055204</v>
+      </c>
+      <c r="F41" s="13"/>
+      <c r="G41" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+    </row>
+    <row r="42" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A42" s="17">
+        <v>1606</v>
+      </c>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14">
+        <v>1</v>
+      </c>
+      <c r="D42" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H42" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-    </row>
-    <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="15">
-        <v>1605</v>
-      </c>
-      <c r="B41" s="13">
-        <v>2</v>
-      </c>
-      <c r="C41" s="13">
-        <v>1</v>
-      </c>
-      <c r="D41" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="13">
-        <v>4055204</v>
-      </c>
-      <c r="F41" s="12"/>
-      <c r="G41" s="16" t="s">
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+    </row>
+    <row r="43" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A43" s="17">
+        <v>1607</v>
+      </c>
+      <c r="B43" s="14">
+        <v>2</v>
+      </c>
+      <c r="C43" s="14">
+        <v>1</v>
+      </c>
+      <c r="D43" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H43" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-    </row>
-    <row r="42" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="15">
-        <v>1606</v>
-      </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13">
-        <v>1</v>
-      </c>
-      <c r="D42" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="16" t="s">
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="15"/>
+    </row>
+    <row r="44" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A44" s="17">
+        <v>1608</v>
+      </c>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14">
+        <v>1</v>
+      </c>
+      <c r="D44" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="14">
+        <v>4055205</v>
+      </c>
+      <c r="F44" s="13"/>
+      <c r="G44" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+    </row>
+    <row r="45" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A45" s="17">
+        <v>1609</v>
+      </c>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14">
+        <v>1</v>
+      </c>
+      <c r="D45" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="14">
+        <v>4055206</v>
+      </c>
+      <c r="F45" s="13"/>
+      <c r="G45" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+    </row>
+    <row r="46" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A46" s="17">
+        <v>1610</v>
+      </c>
+      <c r="B46" s="14">
+        <v>2</v>
+      </c>
+      <c r="C46" s="14">
+        <v>1</v>
+      </c>
+      <c r="D46" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="14">
+        <v>4055207</v>
+      </c>
+      <c r="F46" s="13"/>
+      <c r="G46" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H46" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+    </row>
+    <row r="47" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A47" s="17">
+        <v>1611</v>
+      </c>
+      <c r="B47" s="14">
+        <v>2</v>
+      </c>
+      <c r="C47" s="14">
+        <v>1</v>
+      </c>
+      <c r="D47" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="14">
+        <v>4055208</v>
+      </c>
+      <c r="F47" s="13"/>
+      <c r="G47" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+    </row>
+    <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="17">
+        <v>1612</v>
+      </c>
+      <c r="B48" s="14">
+        <v>2</v>
+      </c>
+      <c r="C48" s="14">
+        <v>1</v>
+      </c>
+      <c r="D48" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="14">
+        <v>4055209</v>
+      </c>
+      <c r="F48" s="13"/>
+      <c r="G48" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H48" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+    </row>
+    <row r="49" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A49" s="12">
+        <v>1701</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13">
+        <v>1</v>
+      </c>
+      <c r="D49" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H49" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-    </row>
-    <row r="43" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="15">
-        <v>1607</v>
-      </c>
-      <c r="B43" s="13">
-        <v>2</v>
-      </c>
-      <c r="C43" s="13">
-        <v>1</v>
-      </c>
-      <c r="D43" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="16" t="s">
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+    </row>
+    <row r="50" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A50" s="12">
+        <v>1702</v>
+      </c>
+      <c r="C50" s="13">
+        <v>1</v>
+      </c>
+      <c r="D50" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="13"/>
+      <c r="G50" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H50" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-    </row>
-    <row r="44" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="15">
-        <v>1608</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13">
-        <v>1</v>
-      </c>
-      <c r="D44" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="13">
-        <v>4055205</v>
-      </c>
-      <c r="F44" s="12"/>
-      <c r="G44" s="16" t="s">
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+    </row>
+    <row r="51" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A51" s="12">
+        <v>1703</v>
+      </c>
+      <c r="B51" s="13">
+        <v>2</v>
+      </c>
+      <c r="C51" s="13">
+        <v>1</v>
+      </c>
+      <c r="D51" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="13">
+        <v>4055222</v>
+      </c>
+      <c r="F51" s="13"/>
+      <c r="G51" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H51" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+    </row>
+    <row r="52" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A52" s="12">
+        <v>1704</v>
+      </c>
+      <c r="B52" s="13">
+        <v>2</v>
+      </c>
+      <c r="C52" s="13">
+        <v>1</v>
+      </c>
+      <c r="D52" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="13">
+        <v>4055223</v>
+      </c>
+      <c r="F52" s="13"/>
+      <c r="G52" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H52" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+    </row>
+    <row r="53" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A53" s="12">
+        <v>1705</v>
+      </c>
+      <c r="B53" s="13">
+        <v>2</v>
+      </c>
+      <c r="C53" s="13">
+        <v>1</v>
+      </c>
+      <c r="D53" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="13">
+        <v>4055224</v>
+      </c>
+      <c r="F53" s="13"/>
+      <c r="G53" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H53" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+    </row>
+    <row r="54" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A54" s="12">
+        <v>1706</v>
+      </c>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13">
+        <v>1</v>
+      </c>
+      <c r="D54" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H54" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-    </row>
-    <row r="45" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="15">
-        <v>1609</v>
-      </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13">
-        <v>1</v>
-      </c>
-      <c r="D45" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="13">
-        <v>4055206</v>
-      </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="16" t="s">
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+    </row>
+    <row r="55" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A55" s="12">
+        <v>1707</v>
+      </c>
+      <c r="B55" s="13">
+        <v>2</v>
+      </c>
+      <c r="C55" s="13">
+        <v>1</v>
+      </c>
+      <c r="D55" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="13">
+        <v>4055225</v>
+      </c>
+      <c r="F55" s="13"/>
+      <c r="G55" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H55" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+    </row>
+    <row r="56" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A56" s="12">
+        <v>1708</v>
+      </c>
+      <c r="B56" s="13">
+        <v>2</v>
+      </c>
+      <c r="C56" s="13">
+        <v>1</v>
+      </c>
+      <c r="D56" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="13">
+        <v>4055226</v>
+      </c>
+      <c r="F56" s="13"/>
+      <c r="G56" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H56" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I56" s="16"/>
+      <c r="J56" s="16"/>
+      <c r="K56" s="16"/>
+      <c r="L56" s="16"/>
+    </row>
+    <row r="57" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A57" s="12">
+        <v>1709</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13">
+        <v>1</v>
+      </c>
+      <c r="D57" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H57" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-    </row>
-    <row r="46" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="15">
-        <v>1610</v>
-      </c>
-      <c r="B46" s="13">
-        <v>2</v>
-      </c>
-      <c r="C46" s="13">
-        <v>1</v>
-      </c>
-      <c r="D46" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="13">
-        <v>4055207</v>
-      </c>
-      <c r="F46" s="12"/>
-      <c r="G46" s="16" t="s">
+      <c r="I57" s="16"/>
+      <c r="J57" s="16"/>
+      <c r="K57" s="16"/>
+      <c r="L57" s="16"/>
+    </row>
+    <row r="58" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A58" s="12">
+        <v>1710</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13">
+        <v>1</v>
+      </c>
+      <c r="D58" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H58" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-    </row>
-    <row r="47" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="15">
-        <v>1611</v>
-      </c>
-      <c r="B47" s="13">
-        <v>2</v>
-      </c>
-      <c r="C47" s="13">
-        <v>1</v>
-      </c>
-      <c r="D47" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="13">
-        <v>4055208</v>
-      </c>
-      <c r="F47" s="12"/>
-      <c r="G47" s="16" t="s">
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+    </row>
+    <row r="59" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A59" s="12">
+        <v>1711</v>
+      </c>
+      <c r="B59" s="13">
+        <v>2</v>
+      </c>
+      <c r="C59" s="13">
+        <v>1</v>
+      </c>
+      <c r="D59" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="13">
+        <v>4055227</v>
+      </c>
+      <c r="F59" s="13"/>
+      <c r="G59" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H59" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="I59" s="16"/>
+      <c r="J59" s="16"/>
+      <c r="K59" s="16"/>
+      <c r="L59" s="16"/>
+    </row>
+    <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A60" s="12">
+        <v>1712</v>
+      </c>
+      <c r="B60" s="13">
+        <v>2</v>
+      </c>
+      <c r="C60" s="13">
+        <v>1</v>
+      </c>
+      <c r="D60" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="13">
+        <v>4055228</v>
+      </c>
+      <c r="F60" s="13"/>
+      <c r="G60" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H60" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="16"/>
+      <c r="L60" s="16"/>
+    </row>
+    <row r="61" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A61" s="17">
+        <v>1801</v>
+      </c>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14">
+        <v>1</v>
+      </c>
+      <c r="D61" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H61" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-    </row>
-    <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="15">
-        <v>1612</v>
-      </c>
-      <c r="B48" s="13">
-        <v>2</v>
-      </c>
-      <c r="C48" s="13">
-        <v>1</v>
-      </c>
-      <c r="D48" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="13">
-        <v>4055209</v>
-      </c>
-      <c r="F48" s="12"/>
-      <c r="G48" s="16" t="s">
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15"/>
+    </row>
+    <row r="62" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A62" s="17">
+        <v>1802</v>
+      </c>
+      <c r="B62" s="14"/>
+      <c r="C62" s="14">
+        <v>1</v>
+      </c>
+      <c r="D62" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H62" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-    </row>
-    <row r="49" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="11">
-        <v>1701</v>
-      </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12">
-        <v>1</v>
-      </c>
-      <c r="D49" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-    </row>
-    <row r="50" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A50" s="11">
-        <v>1702</v>
-      </c>
-      <c r="C50" s="12">
-        <v>1</v>
-      </c>
-      <c r="D50" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="12"/>
-      <c r="G50" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-    </row>
-    <row r="51" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A51" s="11">
-        <v>1703</v>
-      </c>
-      <c r="B51" s="12">
-        <v>2</v>
-      </c>
-      <c r="C51" s="12">
-        <v>1</v>
-      </c>
-      <c r="D51" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="12">
-        <v>4055222</v>
-      </c>
-      <c r="F51" s="12"/>
-      <c r="G51" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-    </row>
-    <row r="52" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A52" s="11">
-        <v>1704</v>
-      </c>
-      <c r="B52" s="12">
-        <v>2</v>
-      </c>
-      <c r="C52" s="12">
-        <v>1</v>
-      </c>
-      <c r="D52" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="12">
-        <v>4055223</v>
-      </c>
-      <c r="F52" s="12"/>
-      <c r="G52" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-    </row>
-    <row r="53" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A53" s="11">
-        <v>1705</v>
-      </c>
-      <c r="B53" s="12">
-        <v>2</v>
-      </c>
-      <c r="C53" s="12">
-        <v>1</v>
-      </c>
-      <c r="D53" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="12">
-        <v>4055224</v>
-      </c>
-      <c r="F53" s="12"/>
-      <c r="G53" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-    </row>
-    <row r="54" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A54" s="11">
-        <v>1706</v>
-      </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12">
-        <v>1</v>
-      </c>
-      <c r="D54" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-    </row>
-    <row r="55" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A55" s="11">
-        <v>1707</v>
-      </c>
-      <c r="B55" s="12">
-        <v>2</v>
-      </c>
-      <c r="C55" s="12">
-        <v>1</v>
-      </c>
-      <c r="D55" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="12">
-        <v>4055225</v>
-      </c>
-      <c r="F55" s="12"/>
-      <c r="G55" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-    </row>
-    <row r="56" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A56" s="11">
-        <v>1708</v>
-      </c>
-      <c r="B56" s="12">
-        <v>2</v>
-      </c>
-      <c r="C56" s="12">
-        <v>1</v>
-      </c>
-      <c r="D56" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="12">
-        <v>4055226</v>
-      </c>
-      <c r="F56" s="12"/>
-      <c r="G56" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-    </row>
-    <row r="57" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A57" s="11">
-        <v>1709</v>
-      </c>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12">
-        <v>1</v>
-      </c>
-      <c r="D57" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-    </row>
-    <row r="58" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A58" s="11">
-        <v>1710</v>
-      </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12">
-        <v>1</v>
-      </c>
-      <c r="D58" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-    </row>
-    <row r="59" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="11">
-        <v>1711</v>
-      </c>
-      <c r="B59" s="12">
-        <v>2</v>
-      </c>
-      <c r="C59" s="12">
-        <v>1</v>
-      </c>
-      <c r="D59" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="12">
-        <v>4055227</v>
-      </c>
-      <c r="F59" s="12"/>
-      <c r="G59" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H59" s="14"/>
-      <c r="I59" s="14"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="14"/>
-      <c r="L59" s="14"/>
-    </row>
-    <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="11">
-        <v>1712</v>
-      </c>
-      <c r="B60" s="12">
-        <v>2</v>
-      </c>
-      <c r="C60" s="12">
-        <v>1</v>
-      </c>
-      <c r="D60" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="12">
-        <v>4055228</v>
-      </c>
-      <c r="F60" s="12"/>
-      <c r="G60" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-    </row>
-    <row r="61" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="15">
-        <v>1801</v>
-      </c>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13">
-        <v>1</v>
-      </c>
-      <c r="D61" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="17"/>
-    </row>
-    <row r="62" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A62" s="15">
-        <v>1802</v>
-      </c>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13">
-        <v>1</v>
-      </c>
-      <c r="D62" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="15"/>
     </row>
     <row r="63" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A63" s="15">
+      <c r="A63" s="17">
         <v>1803</v>
       </c>
-      <c r="B63" s="13">
-        <v>2</v>
-      </c>
-      <c r="C63" s="13">
-        <v>1</v>
-      </c>
-      <c r="D63" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="13">
+      <c r="B63" s="14">
+        <v>2</v>
+      </c>
+      <c r="C63" s="14">
+        <v>1</v>
+      </c>
+      <c r="D63" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="14">
         <v>4055243</v>
       </c>
-      <c r="F63" s="13"/>
-      <c r="G63" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="15"/>
     </row>
     <row r="64" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A64" s="15">
+      <c r="A64" s="17">
         <v>1804</v>
       </c>
-      <c r="B64" s="13">
-        <v>2</v>
-      </c>
-      <c r="C64" s="13">
-        <v>1</v>
-      </c>
-      <c r="D64" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="13">
+      <c r="B64" s="14">
+        <v>2</v>
+      </c>
+      <c r="C64" s="14">
+        <v>1</v>
+      </c>
+      <c r="D64" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="14">
         <v>4055244</v>
       </c>
-      <c r="F64" s="13"/>
-      <c r="G64" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
-      <c r="J64" s="17"/>
-      <c r="K64" s="17"/>
-      <c r="L64" s="17"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H64" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+      <c r="L64" s="15"/>
     </row>
     <row r="65" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A65" s="15">
+      <c r="A65" s="17">
         <v>1805</v>
       </c>
-      <c r="B65" s="13">
-        <v>2</v>
-      </c>
-      <c r="C65" s="13">
-        <v>1</v>
-      </c>
-      <c r="D65" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="13">
+      <c r="B65" s="14">
+        <v>2</v>
+      </c>
+      <c r="C65" s="14">
+        <v>1</v>
+      </c>
+      <c r="D65" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="14">
         <v>4055245</v>
       </c>
-      <c r="F65" s="13"/>
-      <c r="G65" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="17"/>
-      <c r="K65" s="17"/>
-      <c r="L65" s="17"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H65" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+      <c r="L65" s="15"/>
     </row>
     <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="15">
+      <c r="A66" s="17">
         <v>1806</v>
       </c>
-      <c r="B66" s="13">
-        <v>2</v>
-      </c>
-      <c r="C66" s="13">
-        <v>1</v>
-      </c>
-      <c r="D66" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="13">
+      <c r="B66" s="14">
+        <v>2</v>
+      </c>
+      <c r="C66" s="14">
+        <v>1</v>
+      </c>
+      <c r="D66" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="14">
         <v>4055246</v>
       </c>
-      <c r="F66" s="13"/>
-      <c r="G66" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="17"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H66" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15"/>
     </row>
     <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="15">
+      <c r="A67" s="17">
         <v>1807</v>
       </c>
-      <c r="B67" s="13">
-        <v>2</v>
-      </c>
-      <c r="C67" s="13">
-        <v>1</v>
-      </c>
-      <c r="D67" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="13">
+      <c r="B67" s="14">
+        <v>2</v>
+      </c>
+      <c r="C67" s="14">
+        <v>1</v>
+      </c>
+      <c r="D67" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="14">
         <v>4055247</v>
       </c>
-      <c r="F67" s="13"/>
-      <c r="G67" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="17"/>
-      <c r="L67" s="17"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H67" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="15"/>
     </row>
     <row r="68" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="11">
+      <c r="A68" s="12">
         <v>1901</v>
       </c>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12">
-        <v>1</v>
-      </c>
-      <c r="D68" s="19" t="b">
+      <c r="B68" s="13"/>
+      <c r="C68" s="13">
+        <v>1</v>
+      </c>
+      <c r="D68" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="14"/>
-      <c r="L68" s="14"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" s="16"/>
+      <c r="J68" s="16"/>
+      <c r="K68" s="16"/>
+      <c r="L68" s="16"/>
     </row>
     <row r="69" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A69" s="11">
+      <c r="A69" s="12">
         <v>1902</v>
       </c>
-      <c r="B69" s="12">
-        <v>2</v>
-      </c>
-      <c r="C69" s="12">
-        <v>1</v>
-      </c>
-      <c r="D69" s="19" t="b">
+      <c r="B69" s="13">
+        <v>2</v>
+      </c>
+      <c r="C69" s="13">
+        <v>1</v>
+      </c>
+      <c r="D69" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E69" s="13">
         <v>4055263</v>
       </c>
-      <c r="F69" s="12"/>
-      <c r="G69" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="H69" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
     </row>
     <row r="70" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="11">
+      <c r="A70" s="12">
         <v>1903</v>
       </c>
-      <c r="B70" s="12">
-        <v>2</v>
-      </c>
-      <c r="C70" s="12">
-        <v>1</v>
-      </c>
-      <c r="D70" s="19" t="b">
+      <c r="B70" s="13">
+        <v>2</v>
+      </c>
+      <c r="C70" s="13">
+        <v>1</v>
+      </c>
+      <c r="D70" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E70" s="12">
+      <c r="E70" s="13">
         <v>4055264</v>
       </c>
-      <c r="F70" s="12"/>
-      <c r="G70" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="H70" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="I70" s="16"/>
+      <c r="J70" s="16"/>
+      <c r="K70" s="16"/>
+      <c r="L70" s="16"/>
     </row>
     <row r="71" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="15">
+      <c r="A71" s="17">
         <v>1981</v>
       </c>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13">
-        <v>1</v>
-      </c>
-      <c r="D71" s="19" t="b">
+      <c r="B71" s="14"/>
+      <c r="C71" s="14">
+        <v>1</v>
+      </c>
+      <c r="D71" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="17"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H71" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="15"/>
     </row>
     <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="15">
+      <c r="A72" s="17">
         <v>1982</v>
       </c>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13">
-        <v>1</v>
-      </c>
-      <c r="D72" s="19" t="b">
+      <c r="B72" s="14"/>
+      <c r="C72" s="14">
+        <v>1</v>
+      </c>
+      <c r="D72" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-      <c r="J72" s="17"/>
-      <c r="K72" s="17"/>
-      <c r="L72" s="17"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
+      <c r="L72" s="15"/>
     </row>
     <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A73" s="15">
+      <c r="A73" s="17">
         <v>1983</v>
       </c>
-      <c r="B73" s="13">
-        <v>2</v>
-      </c>
-      <c r="C73" s="13">
-        <v>1</v>
-      </c>
-      <c r="D73" s="19" t="b">
+      <c r="B73" s="14">
+        <v>2</v>
+      </c>
+      <c r="C73" s="14">
+        <v>1</v>
+      </c>
+      <c r="D73" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E73" s="13">
+      <c r="E73" s="14">
         <v>4055321</v>
       </c>
-      <c r="F73" s="13"/>
-      <c r="G73" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H73" s="17"/>
-      <c r="I73" s="17"/>
-      <c r="J73" s="17"/>
-      <c r="K73" s="17"/>
-      <c r="L73" s="17"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+      <c r="L73" s="15"/>
     </row>
     <row r="74" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="11">
+      <c r="A74" s="12">
         <v>2001</v>
       </c>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12">
-        <v>1</v>
-      </c>
-      <c r="D74" s="19" t="b">
+      <c r="B74" s="13"/>
+      <c r="C74" s="13">
+        <v>1</v>
+      </c>
+      <c r="D74" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E74" s="12"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14"/>
-      <c r="K74" s="14"/>
-      <c r="L74" s="14"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H74" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="16"/>
+      <c r="L74" s="16"/>
     </row>
     <row r="75" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="11">
+      <c r="A75" s="12">
         <v>2002</v>
       </c>
-      <c r="B75" s="12">
-        <v>2</v>
-      </c>
-      <c r="C75" s="12">
-        <v>1</v>
-      </c>
-      <c r="D75" s="19" t="b">
+      <c r="B75" s="13">
+        <v>2</v>
+      </c>
+      <c r="C75" s="13">
+        <v>1</v>
+      </c>
+      <c r="D75" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E75" s="12">
+      <c r="E75" s="13">
         <v>4055281</v>
       </c>
-      <c r="F75" s="12"/>
-      <c r="G75" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="14"/>
-      <c r="I75" s="14"/>
-      <c r="J75" s="14"/>
-      <c r="K75" s="14"/>
-      <c r="L75" s="14"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H75" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I75" s="16"/>
+      <c r="J75" s="16"/>
+      <c r="K75" s="16"/>
+      <c r="L75" s="16"/>
     </row>
     <row r="76" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A76" s="11">
+      <c r="A76" s="12">
         <v>2003</v>
       </c>
-      <c r="B76" s="12">
-        <v>2</v>
-      </c>
-      <c r="C76" s="12">
-        <v>1</v>
-      </c>
-      <c r="D76" s="19" t="b">
+      <c r="B76" s="13">
+        <v>2</v>
+      </c>
+      <c r="C76" s="13">
+        <v>1</v>
+      </c>
+      <c r="D76" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E76" s="12">
+      <c r="E76" s="13">
         <v>4055282</v>
       </c>
-      <c r="F76" s="12"/>
-      <c r="G76" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="14"/>
-      <c r="I76" s="14"/>
-      <c r="J76" s="14"/>
-      <c r="K76" s="14"/>
-      <c r="L76" s="14"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H76" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I76" s="16"/>
+      <c r="J76" s="16"/>
+      <c r="K76" s="16"/>
+      <c r="L76" s="16"/>
     </row>
     <row r="77" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A77" s="11">
+      <c r="A77" s="12">
         <v>2004</v>
       </c>
-      <c r="B77" s="12">
-        <v>2</v>
-      </c>
-      <c r="C77" s="12">
-        <v>1</v>
-      </c>
-      <c r="D77" s="19" t="b">
+      <c r="B77" s="13">
+        <v>2</v>
+      </c>
+      <c r="C77" s="13">
+        <v>1</v>
+      </c>
+      <c r="D77" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E77" s="12">
+      <c r="E77" s="13">
         <v>4055283</v>
       </c>
-      <c r="F77" s="12"/>
-      <c r="G77" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="14"/>
-      <c r="I77" s="14"/>
-      <c r="J77" s="14"/>
-      <c r="K77" s="14"/>
-      <c r="L77" s="14"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H77" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16"/>
+      <c r="K77" s="16"/>
+      <c r="L77" s="16"/>
     </row>
     <row r="78" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A78" s="11">
+      <c r="A78" s="12">
         <v>2005</v>
       </c>
-      <c r="B78" s="12">
-        <v>2</v>
-      </c>
-      <c r="C78" s="12">
-        <v>1</v>
-      </c>
-      <c r="D78" s="19" t="b">
+      <c r="B78" s="13">
+        <v>2</v>
+      </c>
+      <c r="C78" s="13">
+        <v>1</v>
+      </c>
+      <c r="D78" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E78" s="12">
+      <c r="E78" s="13">
         <v>4055284</v>
       </c>
-      <c r="F78" s="12"/>
-      <c r="G78" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="14"/>
-      <c r="I78" s="14"/>
-      <c r="J78" s="14"/>
-      <c r="K78" s="14"/>
-      <c r="L78" s="14"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H78" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I78" s="16"/>
+      <c r="J78" s="16"/>
+      <c r="K78" s="16"/>
+      <c r="L78" s="16"/>
     </row>
     <row r="79" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="11">
+      <c r="A79" s="12">
         <v>2006</v>
       </c>
-      <c r="B79" s="12">
-        <v>2</v>
-      </c>
-      <c r="C79" s="12">
-        <v>1</v>
-      </c>
-      <c r="D79" s="19" t="b">
+      <c r="B79" s="13">
+        <v>2</v>
+      </c>
+      <c r="C79" s="13">
+        <v>1</v>
+      </c>
+      <c r="D79" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E79" s="12">
+      <c r="E79" s="13">
         <v>4055285</v>
       </c>
-      <c r="F79" s="12"/>
-      <c r="G79" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="14"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H79" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I79" s="16"/>
+      <c r="J79" s="16"/>
+      <c r="K79" s="16"/>
+      <c r="L79" s="16"/>
     </row>
     <row r="80" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="11">
+      <c r="A80" s="12">
         <v>2007</v>
       </c>
-      <c r="B80" s="12">
-        <v>2</v>
-      </c>
-      <c r="C80" s="12">
-        <v>1</v>
-      </c>
-      <c r="D80" s="19" t="b">
+      <c r="B80" s="13">
+        <v>2</v>
+      </c>
+      <c r="C80" s="13">
+        <v>1</v>
+      </c>
+      <c r="D80" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E80" s="12">
+      <c r="E80" s="13">
         <v>4055286</v>
       </c>
-      <c r="F80" s="12"/>
-      <c r="G80" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14"/>
-      <c r="K80" s="14"/>
-      <c r="L80" s="14"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H80" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I80" s="16"/>
+      <c r="J80" s="16"/>
+      <c r="K80" s="16"/>
+      <c r="L80" s="16"/>
     </row>
     <row r="81" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="20">
+      <c r="A81" s="21">
         <v>2101</v>
       </c>
-      <c r="B81" s="20">
-        <v>2</v>
-      </c>
-      <c r="C81" s="20">
-        <v>1</v>
-      </c>
-      <c r="D81" s="19" t="b">
+      <c r="B81" s="21">
+        <v>2</v>
+      </c>
+      <c r="C81" s="21">
+        <v>1</v>
+      </c>
+      <c r="D81" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E81" s="20">
+      <c r="E81" s="21">
         <v>4055301</v>
       </c>
-      <c r="F81" s="20"/>
+      <c r="F81" s="21"/>
       <c r="G81" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
-      <c r="K81" s="17"/>
-      <c r="L81" s="17"/>
+        <v>77</v>
+      </c>
+      <c r="H81" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I81" s="15"/>
+      <c r="J81" s="15"/>
+      <c r="K81" s="15"/>
+      <c r="L81" s="15"/>
     </row>
     <row r="82" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="20">
+      <c r="A82" s="21">
         <v>2102</v>
       </c>
-      <c r="B82" s="20">
-        <v>1</v>
-      </c>
-      <c r="C82" s="20">
-        <v>1</v>
-      </c>
-      <c r="D82" s="19" t="b">
+      <c r="B82" s="21">
+        <v>1</v>
+      </c>
+      <c r="C82" s="21">
+        <v>1</v>
+      </c>
+      <c r="D82" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E82" s="20">
+      <c r="E82" s="21">
         <v>4055303</v>
       </c>
-      <c r="F82" s="20"/>
+      <c r="F82" s="21"/>
       <c r="G82" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H82" s="17"/>
-      <c r="I82" s="17"/>
-      <c r="J82" s="17"/>
-      <c r="K82" s="17"/>
-      <c r="L82" s="17"/>
+        <v>77</v>
+      </c>
+      <c r="H82" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="I82" s="15"/>
+      <c r="J82" s="15"/>
+      <c r="K82" s="15"/>
+      <c r="L82" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3566,14 +3883,14 @@
         <v>2101</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2101_</v>
       </c>
       <c r="M5" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -3582,7 +3899,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3592,14 +3909,14 @@
         <v>2102</v>
       </c>
       <c r="J6" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2102_</v>
       </c>
       <c r="M6" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3607,14 +3924,14 @@
         <v>2103</v>
       </c>
       <c r="J7" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2103_</v>
       </c>
       <c r="M7" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3622,34 +3939,34 @@
         <v>2104</v>
       </c>
       <c r="J8" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2104_</v>
       </c>
       <c r="M8" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="101">
   <si>
     <t>序号</t>
   </si>
@@ -423,25 +423,58 @@
     <t>加入联盟有两种方式：加入他人联盟或自己创建，和好友共同赚取收益！</t>
   </si>
   <si>
+    <t>小鸟建筑升级</t>
+  </si>
+  <si>
     <t>_</t>
   </si>
   <si>
-    <t>2101_</t>
+    <t>2201_</t>
   </si>
   <si>
     <t>1. 小助手</t>
   </si>
   <si>
-    <t>2102_</t>
-  </si>
-  <si>
-    <t>2103_</t>
-  </si>
-  <si>
-    <t>2104_</t>
+    <t>2202_</t>
+  </si>
+  <si>
+    <t>2203_</t>
+  </si>
+  <si>
+    <t>2204_</t>
+  </si>
+  <si>
+    <t>2205_</t>
+  </si>
+  <si>
+    <t>2206_</t>
+  </si>
+  <si>
+    <t>2207_</t>
+  </si>
+  <si>
+    <t>2208_</t>
+  </si>
+  <si>
+    <t>2209_</t>
   </si>
   <si>
     <t>2. 气泡</t>
+  </si>
+  <si>
+    <t>2210_</t>
+  </si>
+  <si>
+    <t>2211_</t>
+  </si>
+  <si>
+    <t>2212_</t>
+  </si>
+  <si>
+    <t>2213_</t>
+  </si>
+  <si>
+    <t>2214_</t>
   </si>
   <si>
     <t>指引显示类型</t>
@@ -1138,7 +1171,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1163,6 +1196,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1184,9 +1220,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1204,6 +1237,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1689,7 +1731,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -1699,40 +1741,40 @@
     <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="85.2916666666667" style="8" customWidth="1"/>
+    <col min="8" max="8" width="85.2916666666667" style="9" customWidth="1"/>
     <col min="13" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8"/>
+      <c r="H1" s="9"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
       <c r="L1"/>
     </row>
     <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1744,70 +1786,70 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="8"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="9"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="8"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="9"/>
       <c r="I3"/>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="11"/>
-      <c r="H4" s="8"/>
+      <c r="A4" s="12"/>
+      <c r="H4" s="9"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
     </row>
     <row r="5" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="12">
+      <c r="A5" s="13">
         <v>1001</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="13">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="14">
         <v>4055101</v>
       </c>
-      <c r="F5" s="13"/>
+      <c r="F5" s="14"/>
       <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="16"/>
@@ -1816,22 +1858,22 @@
       <c r="L5" s="16"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="12">
+      <c r="A6" s="13">
         <v>1002</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="13">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14">
         <v>4055102</v>
       </c>
-      <c r="F6" s="13"/>
+      <c r="F6" s="14"/>
       <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I6" s="16"/>
@@ -1840,22 +1882,22 @@
       <c r="L6" s="16"/>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="12">
+      <c r="A7" s="13">
         <v>1003</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="13">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="14">
         <v>4055103</v>
       </c>
-      <c r="F7" s="13"/>
+      <c r="F7" s="14"/>
       <c r="G7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I7" s="16"/>
@@ -1864,22 +1906,22 @@
       <c r="L7" s="16"/>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="12">
+      <c r="A8" s="13">
         <v>1004</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="13">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
         <v>4055104</v>
       </c>
-      <c r="F8" s="13"/>
+      <c r="F8" s="14"/>
       <c r="G8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I8" s="16"/>
@@ -1888,20 +1930,20 @@
       <c r="L8" s="16"/>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="12">
+      <c r="A9" s="13">
         <v>1005</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
       <c r="G9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="16"/>
@@ -1910,22 +1952,22 @@
       <c r="L9" s="16"/>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>1006</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="13">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14">
         <v>4055105</v>
       </c>
-      <c r="F10" s="13"/>
+      <c r="F10" s="14"/>
       <c r="G10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="9" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="16"/>
@@ -1934,22 +1976,22 @@
       <c r="L10" s="16"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="12">
+      <c r="A11" s="13">
         <v>1007</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="13">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="14">
         <v>4055106</v>
       </c>
-      <c r="F11" s="13"/>
+      <c r="F11" s="14"/>
       <c r="G11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="9" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="16"/>
@@ -1958,20 +2000,20 @@
       <c r="L11" s="16"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="12">
+      <c r="A12" s="13">
         <v>1008</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
       <c r="G12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I12" s="16"/>
@@ -1980,20 +2022,20 @@
       <c r="L12" s="16"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="12">
+      <c r="A13" s="13">
         <v>1009</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
       <c r="G13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I13" s="16"/>
@@ -2002,20 +2044,20 @@
       <c r="L13" s="16"/>
     </row>
     <row r="14" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="12">
+      <c r="A14" s="13">
         <v>1010</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
       <c r="G14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I14" s="16"/>
@@ -2024,22 +2066,22 @@
       <c r="L14" s="16"/>
     </row>
     <row r="15" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="12">
+      <c r="A15" s="13">
         <v>1011</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="13">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
         <v>4055107</v>
       </c>
-      <c r="F15" s="13"/>
+      <c r="F15" s="14"/>
       <c r="G15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="9" t="s">
         <v>24</v>
       </c>
       <c r="I15" s="16"/>
@@ -2048,22 +2090,22 @@
       <c r="L15" s="16"/>
     </row>
     <row r="16" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="12">
+      <c r="A16" s="13">
         <v>1012</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="13">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
         <v>4055108</v>
       </c>
-      <c r="F16" s="13"/>
+      <c r="F16" s="14"/>
       <c r="G16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="9" t="s">
         <v>25</v>
       </c>
       <c r="I16" s="16"/>
@@ -2072,22 +2114,22 @@
       <c r="L16" s="16"/>
     </row>
     <row r="17" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="12">
+      <c r="A17" s="13">
         <v>1013</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="13">
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="14">
         <v>4055109</v>
       </c>
-      <c r="F17" s="13"/>
+      <c r="F17" s="14"/>
       <c r="G17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="I17" s="16"/>
@@ -2099,135 +2141,135 @@
       <c r="A18" s="17">
         <v>1201</v>
       </c>
-      <c r="B18" s="14">
-        <v>2</v>
-      </c>
-      <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
+      <c r="B18" s="15">
+        <v>2</v>
+      </c>
+      <c r="C18" s="15">
+        <v>2</v>
+      </c>
+      <c r="D18" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
         <v>4055121</v>
       </c>
-      <c r="F18" s="14"/>
+      <c r="F18" s="15"/>
       <c r="G18" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
     </row>
     <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A19" s="17">
         <v>1202</v>
       </c>
-      <c r="B19" s="14">
-        <v>2</v>
-      </c>
-      <c r="C19" s="14">
-        <v>2</v>
-      </c>
-      <c r="D19" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="14">
+      <c r="B19" s="15">
+        <v>2</v>
+      </c>
+      <c r="C19" s="15">
+        <v>2</v>
+      </c>
+      <c r="D19" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15">
         <v>4055122</v>
       </c>
-      <c r="F19" s="14"/>
+      <c r="F19" s="15"/>
       <c r="G19" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
     </row>
     <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A20" s="17">
         <v>1203</v>
       </c>
-      <c r="B20" s="14">
-        <v>2</v>
-      </c>
-      <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
+      <c r="B20" s="15">
+        <v>2</v>
+      </c>
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
         <v>4055123</v>
       </c>
-      <c r="F20" s="14"/>
+      <c r="F20" s="15"/>
       <c r="G20" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="H20" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
     </row>
     <row r="21" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A21" s="17">
         <v>1204</v>
       </c>
-      <c r="B21" s="14">
-        <v>2</v>
-      </c>
-      <c r="C21" s="14">
-        <v>1</v>
-      </c>
-      <c r="D21" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="14">
+      <c r="B21" s="15">
+        <v>2</v>
+      </c>
+      <c r="C21" s="15">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="15">
         <v>4055124</v>
       </c>
-      <c r="F21" s="14"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
     </row>
     <row r="22" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="12">
+      <c r="A22" s="13">
         <v>1301</v>
       </c>
-      <c r="B22" s="13">
-        <v>2</v>
-      </c>
-      <c r="C22" s="13">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="13">
+      <c r="B22" s="14">
+        <v>2</v>
+      </c>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
         <v>4055141</v>
       </c>
-      <c r="F22" s="13"/>
+      <c r="F22" s="14"/>
       <c r="G22" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="15" t="s">
+      <c r="H22" s="9" t="s">
         <v>33</v>
       </c>
       <c r="I22" s="16"/>
@@ -2236,26 +2278,26 @@
       <c r="L22" s="16"/>
     </row>
     <row r="23" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A23" s="12">
+      <c r="A23" s="13">
         <v>1302</v>
       </c>
-      <c r="B23" s="13">
-        <v>2</v>
-      </c>
-      <c r="C23" s="13">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="13">
+      <c r="B23" s="14">
+        <v>2</v>
+      </c>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
         <v>4055142</v>
       </c>
-      <c r="F23" s="13"/>
+      <c r="F23" s="14"/>
       <c r="G23" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="15" t="s">
+      <c r="H23" s="9" t="s">
         <v>34</v>
       </c>
       <c r="I23" s="16"/>
@@ -2264,26 +2306,26 @@
       <c r="L23" s="16"/>
     </row>
     <row r="24" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A24" s="12">
+      <c r="A24" s="13">
         <v>1303</v>
       </c>
-      <c r="B24" s="13">
-        <v>2</v>
-      </c>
-      <c r="C24" s="13">
-        <v>1</v>
-      </c>
-      <c r="D24" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="13">
+      <c r="B24" s="14">
+        <v>2</v>
+      </c>
+      <c r="C24" s="14">
+        <v>1</v>
+      </c>
+      <c r="D24" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="14">
         <v>4055143</v>
       </c>
-      <c r="F24" s="13"/>
+      <c r="F24" s="14"/>
       <c r="G24" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="15" t="s">
+      <c r="H24" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I24" s="16"/>
@@ -2292,22 +2334,22 @@
       <c r="L24" s="16"/>
     </row>
     <row r="25" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="12">
+      <c r="A25" s="13">
         <v>1304</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13">
-        <v>1</v>
-      </c>
-      <c r="D25" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14">
+        <v>1</v>
+      </c>
+      <c r="D25" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
       <c r="G25" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="15" t="s">
+      <c r="H25" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I25" s="16"/>
@@ -2316,22 +2358,22 @@
       <c r="L25" s="16"/>
     </row>
     <row r="26" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="12">
+      <c r="A26" s="13">
         <v>1305</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13">
-        <v>1</v>
-      </c>
-      <c r="D26" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
       <c r="G26" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="H26" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I26" s="16"/>
@@ -2343,187 +2385,187 @@
       <c r="A27" s="17">
         <v>1401</v>
       </c>
-      <c r="B27" s="14">
-        <v>2</v>
-      </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
+      <c r="B27" s="15">
+        <v>2</v>
+      </c>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
         <v>4055161</v>
       </c>
-      <c r="F27" s="14"/>
+      <c r="F27" s="15"/>
       <c r="G27" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H27" s="15" t="s">
+      <c r="H27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
     </row>
     <row r="28" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A28" s="17">
         <v>1402</v>
       </c>
-      <c r="B28" s="14">
-        <v>2</v>
-      </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
+      <c r="B28" s="15">
+        <v>2</v>
+      </c>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
         <v>4055162</v>
       </c>
-      <c r="F28" s="14"/>
+      <c r="F28" s="15"/>
       <c r="G28" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="H28" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
     </row>
     <row r="29" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A29" s="17">
         <v>1403</v>
       </c>
-      <c r="B29" s="14">
-        <v>2</v>
-      </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14">
+      <c r="B29" s="15">
+        <v>2</v>
+      </c>
+      <c r="C29" s="15">
+        <v>1</v>
+      </c>
+      <c r="D29" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
         <v>4055163</v>
       </c>
-      <c r="F29" s="14"/>
+      <c r="F29" s="15"/>
       <c r="G29" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="15" t="s">
+      <c r="H29" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
     </row>
     <row r="30" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A30" s="17">
         <v>1404</v>
       </c>
-      <c r="B30" s="14">
-        <v>2</v>
-      </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="14">
+      <c r="B30" s="15">
+        <v>2</v>
+      </c>
+      <c r="C30" s="15">
+        <v>1</v>
+      </c>
+      <c r="D30" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
         <v>4055164</v>
       </c>
-      <c r="F30" s="14"/>
+      <c r="F30" s="15"/>
       <c r="G30" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="15" t="s">
+      <c r="H30" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
     </row>
     <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A31" s="17">
         <v>1405</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14">
-        <v>1</v>
-      </c>
-      <c r="D31" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15">
+        <v>1</v>
+      </c>
+      <c r="D31" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
       <c r="G31" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H31" s="15" t="s">
+      <c r="H31" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
     </row>
     <row r="32" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A32" s="17">
         <v>1406</v>
       </c>
-      <c r="B32" s="14">
-        <v>2</v>
-      </c>
-      <c r="C32" s="14">
-        <v>1</v>
-      </c>
-      <c r="D32" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="14">
+      <c r="B32" s="15">
+        <v>2</v>
+      </c>
+      <c r="C32" s="15">
+        <v>1</v>
+      </c>
+      <c r="D32" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="15">
         <v>4055165</v>
       </c>
-      <c r="F32" s="14"/>
+      <c r="F32" s="15"/>
       <c r="G32" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H32" s="15" t="s">
+      <c r="H32" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
     </row>
     <row r="33" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="12">
+      <c r="A33" s="13">
         <v>1501</v>
       </c>
-      <c r="B33" s="13">
-        <v>2</v>
-      </c>
-      <c r="C33" s="13">
-        <v>1</v>
-      </c>
-      <c r="D33" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="13">
+      <c r="B33" s="14">
+        <v>2</v>
+      </c>
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14">
         <v>4055181</v>
       </c>
-      <c r="F33" s="13"/>
+      <c r="F33" s="14"/>
       <c r="G33" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="H33" s="15" t="s">
+      <c r="H33" s="9" t="s">
         <v>43</v>
       </c>
       <c r="I33" s="16"/>
@@ -2532,26 +2574,26 @@
       <c r="L33" s="16"/>
     </row>
     <row r="34" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="12">
+      <c r="A34" s="13">
         <v>1502</v>
       </c>
-      <c r="B34" s="13">
-        <v>2</v>
-      </c>
-      <c r="C34" s="13">
-        <v>1</v>
-      </c>
-      <c r="D34" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="13">
+      <c r="B34" s="14">
+        <v>2</v>
+      </c>
+      <c r="C34" s="14">
+        <v>1</v>
+      </c>
+      <c r="D34" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="14">
         <v>4055182</v>
       </c>
-      <c r="F34" s="13"/>
+      <c r="F34" s="14"/>
       <c r="G34" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="H34" s="15" t="s">
+      <c r="H34" s="9" t="s">
         <v>44</v>
       </c>
       <c r="I34" s="16"/>
@@ -2560,22 +2602,22 @@
       <c r="L34" s="16"/>
     </row>
     <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="12">
+      <c r="A35" s="13">
         <v>1503</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13">
-        <v>1</v>
-      </c>
-      <c r="D35" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14">
+        <v>1</v>
+      </c>
+      <c r="D35" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
       <c r="G35" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="15" t="s">
+      <c r="H35" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I35" s="16"/>
@@ -2584,22 +2626,22 @@
       <c r="L35" s="16"/>
     </row>
     <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="12">
+      <c r="A36" s="13">
         <v>1504</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13">
-        <v>1</v>
-      </c>
-      <c r="D36" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14">
+        <v>1</v>
+      </c>
+      <c r="D36" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
       <c r="G36" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="H36" s="15" t="s">
+      <c r="H36" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I36" s="16"/>
@@ -2611,331 +2653,331 @@
       <c r="A37" s="17">
         <v>1601</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14">
-        <v>1</v>
-      </c>
-      <c r="D37" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15">
+        <v>1</v>
+      </c>
+      <c r="D37" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
       <c r="G37" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H37" s="15" t="s">
+      <c r="H37" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
     </row>
     <row r="38" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A38" s="17">
         <v>1602</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14">
-        <v>1</v>
-      </c>
-      <c r="D38" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15">
+        <v>1</v>
+      </c>
+      <c r="D38" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
       <c r="G38" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H38" s="15" t="s">
+      <c r="H38" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
     </row>
     <row r="39" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A39" s="17">
         <v>1603</v>
       </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14">
-        <v>1</v>
-      </c>
-      <c r="D39" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="14">
+      <c r="B39" s="15"/>
+      <c r="C39" s="15">
+        <v>1</v>
+      </c>
+      <c r="D39" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="15">
         <v>4055203</v>
       </c>
-      <c r="F39" s="13"/>
+      <c r="F39" s="14"/>
       <c r="G39" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H39" s="15" t="s">
+      <c r="H39" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
     </row>
     <row r="40" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A40" s="17">
         <v>1604</v>
       </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14">
-        <v>1</v>
-      </c>
-      <c r="D40" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15">
+        <v>1</v>
+      </c>
+      <c r="D40" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
       <c r="G40" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H40" s="15" t="s">
+      <c r="H40" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
     </row>
     <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A41" s="17">
         <v>1605</v>
       </c>
-      <c r="B41" s="14">
-        <v>2</v>
-      </c>
-      <c r="C41" s="14">
-        <v>1</v>
-      </c>
-      <c r="D41" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="14">
+      <c r="B41" s="15">
+        <v>2</v>
+      </c>
+      <c r="C41" s="15">
+        <v>1</v>
+      </c>
+      <c r="D41" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="15">
         <v>4055204</v>
       </c>
-      <c r="F41" s="13"/>
+      <c r="F41" s="14"/>
       <c r="G41" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H41" s="15" t="s">
+      <c r="H41" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
     </row>
     <row r="42" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A42" s="17">
         <v>1606</v>
       </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14">
-        <v>1</v>
-      </c>
-      <c r="D42" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15">
+        <v>1</v>
+      </c>
+      <c r="D42" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
       <c r="G42" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="15" t="s">
+      <c r="H42" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
     </row>
     <row r="43" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A43" s="17">
         <v>1607</v>
       </c>
-      <c r="B43" s="14">
-        <v>2</v>
-      </c>
-      <c r="C43" s="14">
-        <v>1</v>
-      </c>
-      <c r="D43" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
+      <c r="B43" s="15">
+        <v>2</v>
+      </c>
+      <c r="C43" s="15">
+        <v>1</v>
+      </c>
+      <c r="D43" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
       <c r="G43" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H43" s="15" t="s">
+      <c r="H43" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
     </row>
     <row r="44" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A44" s="17">
         <v>1608</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14">
-        <v>1</v>
-      </c>
-      <c r="D44" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="14">
+      <c r="B44" s="15"/>
+      <c r="C44" s="15">
+        <v>1</v>
+      </c>
+      <c r="D44" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="15">
         <v>4055205</v>
       </c>
-      <c r="F44" s="13"/>
+      <c r="F44" s="14"/>
       <c r="G44" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H44" s="15" t="s">
+      <c r="H44" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
     </row>
     <row r="45" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A45" s="17">
         <v>1609</v>
       </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14">
-        <v>1</v>
-      </c>
-      <c r="D45" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="14">
+      <c r="B45" s="15"/>
+      <c r="C45" s="15">
+        <v>1</v>
+      </c>
+      <c r="D45" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="15">
         <v>4055206</v>
       </c>
-      <c r="F45" s="13"/>
+      <c r="F45" s="14"/>
       <c r="G45" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H45" s="15" t="s">
+      <c r="H45" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
     </row>
     <row r="46" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A46" s="17">
         <v>1610</v>
       </c>
-      <c r="B46" s="14">
-        <v>2</v>
-      </c>
-      <c r="C46" s="14">
-        <v>1</v>
-      </c>
-      <c r="D46" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="14">
+      <c r="B46" s="15">
+        <v>2</v>
+      </c>
+      <c r="C46" s="15">
+        <v>1</v>
+      </c>
+      <c r="D46" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="15">
         <v>4055207</v>
       </c>
-      <c r="F46" s="13"/>
+      <c r="F46" s="14"/>
       <c r="G46" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H46" s="15" t="s">
+      <c r="H46" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
     </row>
     <row r="47" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A47" s="17">
         <v>1611</v>
       </c>
-      <c r="B47" s="14">
-        <v>2</v>
-      </c>
-      <c r="C47" s="14">
-        <v>1</v>
-      </c>
-      <c r="D47" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="14">
+      <c r="B47" s="15">
+        <v>2</v>
+      </c>
+      <c r="C47" s="15">
+        <v>1</v>
+      </c>
+      <c r="D47" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="15">
         <v>4055208</v>
       </c>
-      <c r="F47" s="13"/>
+      <c r="F47" s="14"/>
       <c r="G47" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H47" s="15" t="s">
+      <c r="H47" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
     </row>
     <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A48" s="17">
         <v>1612</v>
       </c>
-      <c r="B48" s="14">
-        <v>2</v>
-      </c>
-      <c r="C48" s="14">
-        <v>1</v>
-      </c>
-      <c r="D48" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="14">
+      <c r="B48" s="15">
+        <v>2</v>
+      </c>
+      <c r="C48" s="15">
+        <v>1</v>
+      </c>
+      <c r="D48" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="15">
         <v>4055209</v>
       </c>
-      <c r="F48" s="13"/>
+      <c r="F48" s="14"/>
       <c r="G48" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="15" t="s">
+      <c r="H48" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
     </row>
     <row r="49" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="12">
+      <c r="A49" s="13">
         <v>1701</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13">
-        <v>1</v>
-      </c>
-      <c r="D49" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14">
+        <v>1</v>
+      </c>
+      <c r="D49" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
       <c r="G49" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H49" s="15" t="s">
+      <c r="H49" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I49" s="16"/>
@@ -2944,20 +2986,20 @@
       <c r="L49" s="16"/>
     </row>
     <row r="50" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A50" s="12">
+      <c r="A50" s="13">
         <v>1702</v>
       </c>
-      <c r="C50" s="13">
-        <v>1</v>
-      </c>
-      <c r="D50" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="13"/>
+      <c r="C50" s="14">
+        <v>1</v>
+      </c>
+      <c r="D50" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="14"/>
       <c r="G50" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H50" s="15" t="s">
+      <c r="H50" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I50" s="16"/>
@@ -2966,26 +3008,26 @@
       <c r="L50" s="16"/>
     </row>
     <row r="51" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A51" s="12">
+      <c r="A51" s="13">
         <v>1703</v>
       </c>
-      <c r="B51" s="13">
-        <v>2</v>
-      </c>
-      <c r="C51" s="13">
-        <v>1</v>
-      </c>
-      <c r="D51" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="13">
+      <c r="B51" s="14">
+        <v>2</v>
+      </c>
+      <c r="C51" s="14">
+        <v>1</v>
+      </c>
+      <c r="D51" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="14">
         <v>4055222</v>
       </c>
-      <c r="F51" s="13"/>
+      <c r="F51" s="14"/>
       <c r="G51" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H51" s="15" t="s">
+      <c r="H51" s="9" t="s">
         <v>54</v>
       </c>
       <c r="I51" s="16"/>
@@ -2994,26 +3036,26 @@
       <c r="L51" s="16"/>
     </row>
     <row r="52" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A52" s="12">
+      <c r="A52" s="13">
         <v>1704</v>
       </c>
-      <c r="B52" s="13">
-        <v>2</v>
-      </c>
-      <c r="C52" s="13">
-        <v>1</v>
-      </c>
-      <c r="D52" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="13">
+      <c r="B52" s="14">
+        <v>2</v>
+      </c>
+      <c r="C52" s="14">
+        <v>1</v>
+      </c>
+      <c r="D52" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="14">
         <v>4055223</v>
       </c>
-      <c r="F52" s="13"/>
+      <c r="F52" s="14"/>
       <c r="G52" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H52" s="15" t="s">
+      <c r="H52" s="9" t="s">
         <v>55</v>
       </c>
       <c r="I52" s="16"/>
@@ -3022,26 +3064,26 @@
       <c r="L52" s="16"/>
     </row>
     <row r="53" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A53" s="12">
+      <c r="A53" s="13">
         <v>1705</v>
       </c>
-      <c r="B53" s="13">
-        <v>2</v>
-      </c>
-      <c r="C53" s="13">
-        <v>1</v>
-      </c>
-      <c r="D53" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="13">
+      <c r="B53" s="14">
+        <v>2</v>
+      </c>
+      <c r="C53" s="14">
+        <v>1</v>
+      </c>
+      <c r="D53" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="14">
         <v>4055224</v>
       </c>
-      <c r="F53" s="13"/>
+      <c r="F53" s="14"/>
       <c r="G53" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H53" s="15" t="s">
+      <c r="H53" s="9" t="s">
         <v>56</v>
       </c>
       <c r="I53" s="16"/>
@@ -3050,22 +3092,22 @@
       <c r="L53" s="16"/>
     </row>
     <row r="54" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A54" s="12">
+      <c r="A54" s="13">
         <v>1706</v>
       </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13">
-        <v>1</v>
-      </c>
-      <c r="D54" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14">
+        <v>1</v>
+      </c>
+      <c r="D54" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
       <c r="G54" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H54" s="15" t="s">
+      <c r="H54" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I54" s="16"/>
@@ -3074,26 +3116,26 @@
       <c r="L54" s="16"/>
     </row>
     <row r="55" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A55" s="12">
+      <c r="A55" s="13">
         <v>1707</v>
       </c>
-      <c r="B55" s="13">
-        <v>2</v>
-      </c>
-      <c r="C55" s="13">
-        <v>1</v>
-      </c>
-      <c r="D55" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="13">
+      <c r="B55" s="14">
+        <v>2</v>
+      </c>
+      <c r="C55" s="14">
+        <v>1</v>
+      </c>
+      <c r="D55" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="14">
         <v>4055225</v>
       </c>
-      <c r="F55" s="13"/>
+      <c r="F55" s="14"/>
       <c r="G55" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H55" s="15" t="s">
+      <c r="H55" s="9" t="s">
         <v>57</v>
       </c>
       <c r="I55" s="16"/>
@@ -3102,26 +3144,26 @@
       <c r="L55" s="16"/>
     </row>
     <row r="56" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A56" s="12">
+      <c r="A56" s="13">
         <v>1708</v>
       </c>
-      <c r="B56" s="13">
-        <v>2</v>
-      </c>
-      <c r="C56" s="13">
-        <v>1</v>
-      </c>
-      <c r="D56" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="13">
+      <c r="B56" s="14">
+        <v>2</v>
+      </c>
+      <c r="C56" s="14">
+        <v>1</v>
+      </c>
+      <c r="D56" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="14">
         <v>4055226</v>
       </c>
-      <c r="F56" s="13"/>
+      <c r="F56" s="14"/>
       <c r="G56" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H56" s="15" t="s">
+      <c r="H56" s="9" t="s">
         <v>58</v>
       </c>
       <c r="I56" s="16"/>
@@ -3130,22 +3172,22 @@
       <c r="L56" s="16"/>
     </row>
     <row r="57" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A57" s="12">
+      <c r="A57" s="13">
         <v>1709</v>
       </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13">
-        <v>1</v>
-      </c>
-      <c r="D57" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14">
+        <v>1</v>
+      </c>
+      <c r="D57" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
       <c r="G57" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H57" s="15" t="s">
+      <c r="H57" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I57" s="16"/>
@@ -3154,22 +3196,22 @@
       <c r="L57" s="16"/>
     </row>
     <row r="58" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A58" s="12">
+      <c r="A58" s="13">
         <v>1710</v>
       </c>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13">
-        <v>1</v>
-      </c>
-      <c r="D58" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14">
+        <v>1</v>
+      </c>
+      <c r="D58" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
       <c r="G58" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H58" s="15" t="s">
+      <c r="H58" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I58" s="16"/>
@@ -3178,26 +3220,26 @@
       <c r="L58" s="16"/>
     </row>
     <row r="59" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="12">
+      <c r="A59" s="13">
         <v>1711</v>
       </c>
-      <c r="B59" s="13">
-        <v>2</v>
-      </c>
-      <c r="C59" s="13">
-        <v>1</v>
-      </c>
-      <c r="D59" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="13">
+      <c r="B59" s="14">
+        <v>2</v>
+      </c>
+      <c r="C59" s="14">
+        <v>1</v>
+      </c>
+      <c r="D59" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="14">
         <v>4055227</v>
       </c>
-      <c r="F59" s="13"/>
+      <c r="F59" s="14"/>
       <c r="G59" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H59" s="15" t="s">
+      <c r="H59" s="9" t="s">
         <v>59</v>
       </c>
       <c r="I59" s="16"/>
@@ -3206,26 +3248,26 @@
       <c r="L59" s="16"/>
     </row>
     <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="12">
+      <c r="A60" s="13">
         <v>1712</v>
       </c>
-      <c r="B60" s="13">
-        <v>2</v>
-      </c>
-      <c r="C60" s="13">
-        <v>1</v>
-      </c>
-      <c r="D60" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="13">
+      <c r="B60" s="14">
+        <v>2</v>
+      </c>
+      <c r="C60" s="14">
+        <v>1</v>
+      </c>
+      <c r="D60" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="14">
         <v>4055228</v>
       </c>
-      <c r="F60" s="13"/>
+      <c r="F60" s="14"/>
       <c r="G60" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H60" s="15" t="s">
+      <c r="H60" s="9" t="s">
         <v>60</v>
       </c>
       <c r="I60" s="16"/>
@@ -3237,207 +3279,207 @@
       <c r="A61" s="17">
         <v>1801</v>
       </c>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14">
-        <v>1</v>
-      </c>
-      <c r="D61" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15">
+        <v>1</v>
+      </c>
+      <c r="D61" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
       <c r="G61" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H61" s="15" t="s">
+      <c r="H61" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
-      <c r="L61" s="15"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
     </row>
     <row r="62" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A62" s="17">
         <v>1802</v>
       </c>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14">
-        <v>1</v>
-      </c>
-      <c r="D62" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15">
+        <v>1</v>
+      </c>
+      <c r="D62" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="15"/>
+      <c r="F62" s="15"/>
       <c r="G62" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H62" s="15" t="s">
+      <c r="H62" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="15"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
     </row>
     <row r="63" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A63" s="17">
         <v>1803</v>
       </c>
-      <c r="B63" s="14">
-        <v>2</v>
-      </c>
-      <c r="C63" s="14">
-        <v>1</v>
-      </c>
-      <c r="D63" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="14">
+      <c r="B63" s="15">
+        <v>2</v>
+      </c>
+      <c r="C63" s="15">
+        <v>1</v>
+      </c>
+      <c r="D63" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="15">
         <v>4055243</v>
       </c>
-      <c r="F63" s="14"/>
+      <c r="F63" s="15"/>
       <c r="G63" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H63" s="15" t="s">
+      <c r="H63" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
-      <c r="K63" s="15"/>
-      <c r="L63" s="15"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="9"/>
     </row>
     <row r="64" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A64" s="17">
         <v>1804</v>
       </c>
-      <c r="B64" s="14">
-        <v>2</v>
-      </c>
-      <c r="C64" s="14">
-        <v>1</v>
-      </c>
-      <c r="D64" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="14">
+      <c r="B64" s="15">
+        <v>2</v>
+      </c>
+      <c r="C64" s="15">
+        <v>1</v>
+      </c>
+      <c r="D64" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="15">
         <v>4055244</v>
       </c>
-      <c r="F64" s="14"/>
+      <c r="F64" s="15"/>
       <c r="G64" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H64" s="15" t="s">
+      <c r="H64" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I64" s="15"/>
-      <c r="J64" s="15"/>
-      <c r="K64" s="15"/>
-      <c r="L64" s="15"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
     </row>
     <row r="65" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A65" s="17">
         <v>1805</v>
       </c>
-      <c r="B65" s="14">
-        <v>2</v>
-      </c>
-      <c r="C65" s="14">
-        <v>1</v>
-      </c>
-      <c r="D65" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="14">
+      <c r="B65" s="15">
+        <v>2</v>
+      </c>
+      <c r="C65" s="15">
+        <v>1</v>
+      </c>
+      <c r="D65" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="15">
         <v>4055245</v>
       </c>
-      <c r="F65" s="14"/>
+      <c r="F65" s="15"/>
       <c r="G65" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H65" s="15" t="s">
+      <c r="H65" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15"/>
-      <c r="K65" s="15"/>
-      <c r="L65" s="15"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="9"/>
     </row>
     <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A66" s="17">
         <v>1806</v>
       </c>
-      <c r="B66" s="14">
-        <v>2</v>
-      </c>
-      <c r="C66" s="14">
-        <v>1</v>
-      </c>
-      <c r="D66" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="14">
+      <c r="B66" s="15">
+        <v>2</v>
+      </c>
+      <c r="C66" s="15">
+        <v>1</v>
+      </c>
+      <c r="D66" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="15">
         <v>4055246</v>
       </c>
-      <c r="F66" s="14"/>
+      <c r="F66" s="15"/>
       <c r="G66" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H66" s="15" t="s">
+      <c r="H66" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="I66" s="15"/>
-      <c r="J66" s="15"/>
-      <c r="K66" s="15"/>
-      <c r="L66" s="15"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="9"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
     </row>
     <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A67" s="17">
         <v>1807</v>
       </c>
-      <c r="B67" s="14">
-        <v>2</v>
-      </c>
-      <c r="C67" s="14">
-        <v>1</v>
-      </c>
-      <c r="D67" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="14">
+      <c r="B67" s="15">
+        <v>2</v>
+      </c>
+      <c r="C67" s="15">
+        <v>1</v>
+      </c>
+      <c r="D67" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="15">
         <v>4055247</v>
       </c>
-      <c r="F67" s="14"/>
+      <c r="F67" s="15"/>
       <c r="G67" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H67" s="15" t="s">
+      <c r="H67" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-      <c r="L67" s="15"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="9"/>
+      <c r="K67" s="9"/>
+      <c r="L67" s="9"/>
     </row>
     <row r="68" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="12">
+      <c r="A68" s="13">
         <v>1901</v>
       </c>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13">
+      <c r="B68" s="14"/>
+      <c r="C68" s="14">
         <v>1</v>
       </c>
       <c r="D68" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
       <c r="G68" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H68" s="15" t="s">
+      <c r="H68" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I68" s="16"/>
@@ -3446,26 +3488,26 @@
       <c r="L68" s="16"/>
     </row>
     <row r="69" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A69" s="12">
+      <c r="A69" s="13">
         <v>1902</v>
       </c>
-      <c r="B69" s="13">
-        <v>2</v>
-      </c>
-      <c r="C69" s="13">
+      <c r="B69" s="14">
+        <v>2</v>
+      </c>
+      <c r="C69" s="14">
         <v>1</v>
       </c>
       <c r="D69" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E69" s="13">
+      <c r="E69" s="14">
         <v>4055263</v>
       </c>
-      <c r="F69" s="13"/>
+      <c r="F69" s="14"/>
       <c r="G69" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H69" s="15" t="s">
+      <c r="H69" s="9" t="s">
         <v>68</v>
       </c>
       <c r="I69" s="16"/>
@@ -3474,26 +3516,26 @@
       <c r="L69" s="16"/>
     </row>
     <row r="70" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="12">
+      <c r="A70" s="13">
         <v>1903</v>
       </c>
-      <c r="B70" s="13">
-        <v>2</v>
-      </c>
-      <c r="C70" s="13">
+      <c r="B70" s="14">
+        <v>2</v>
+      </c>
+      <c r="C70" s="14">
         <v>1</v>
       </c>
       <c r="D70" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="14">
         <v>4055264</v>
       </c>
-      <c r="F70" s="13"/>
+      <c r="F70" s="14"/>
       <c r="G70" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H70" s="15" t="s">
+      <c r="H70" s="9" t="s">
         <v>69</v>
       </c>
       <c r="I70" s="16"/>
@@ -3505,95 +3547,95 @@
       <c r="A71" s="17">
         <v>1981</v>
       </c>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14">
+      <c r="B71" s="15"/>
+      <c r="C71" s="15">
         <v>1</v>
       </c>
       <c r="D71" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="15"/>
       <c r="G71" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="H71" s="15" t="s">
+      <c r="H71" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="9"/>
+      <c r="K71" s="9"/>
+      <c r="L71" s="9"/>
     </row>
     <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A72" s="17">
         <v>1982</v>
       </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14">
+      <c r="B72" s="15"/>
+      <c r="C72" s="15">
         <v>1</v>
       </c>
       <c r="D72" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="15"/>
       <c r="G72" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="H72" s="15" t="s">
+      <c r="H72" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I72" s="15"/>
-      <c r="J72" s="15"/>
-      <c r="K72" s="15"/>
-      <c r="L72" s="15"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="9"/>
+      <c r="K72" s="9"/>
+      <c r="L72" s="9"/>
     </row>
     <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A73" s="17">
         <v>1983</v>
       </c>
-      <c r="B73" s="14">
-        <v>2</v>
-      </c>
-      <c r="C73" s="14">
+      <c r="B73" s="15">
+        <v>2</v>
+      </c>
+      <c r="C73" s="15">
         <v>1</v>
       </c>
       <c r="D73" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E73" s="14">
+      <c r="E73" s="15">
         <v>4055321</v>
       </c>
-      <c r="F73" s="14"/>
+      <c r="F73" s="15"/>
       <c r="G73" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="H73" s="15" t="s">
+      <c r="H73" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I73" s="15"/>
-      <c r="J73" s="15"/>
-      <c r="K73" s="15"/>
-      <c r="L73" s="15"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9"/>
+      <c r="K73" s="9"/>
+      <c r="L73" s="9"/>
     </row>
     <row r="74" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="12">
+      <c r="A74" s="13">
         <v>2001</v>
       </c>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13">
+      <c r="B74" s="14"/>
+      <c r="C74" s="14">
         <v>1</v>
       </c>
       <c r="D74" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
       <c r="G74" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H74" s="15" t="s">
+      <c r="H74" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I74" s="16"/>
@@ -3602,26 +3644,26 @@
       <c r="L74" s="16"/>
     </row>
     <row r="75" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="12">
+      <c r="A75" s="13">
         <v>2002</v>
       </c>
-      <c r="B75" s="13">
-        <v>2</v>
-      </c>
-      <c r="C75" s="13">
+      <c r="B75" s="14">
+        <v>2</v>
+      </c>
+      <c r="C75" s="14">
         <v>1</v>
       </c>
       <c r="D75" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E75" s="13">
+      <c r="E75" s="14">
         <v>4055281</v>
       </c>
-      <c r="F75" s="13"/>
+      <c r="F75" s="14"/>
       <c r="G75" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H75" s="15" t="s">
+      <c r="H75" s="9" t="s">
         <v>73</v>
       </c>
       <c r="I75" s="16"/>
@@ -3630,26 +3672,26 @@
       <c r="L75" s="16"/>
     </row>
     <row r="76" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A76" s="12">
+      <c r="A76" s="13">
         <v>2003</v>
       </c>
-      <c r="B76" s="13">
-        <v>2</v>
-      </c>
-      <c r="C76" s="13">
+      <c r="B76" s="14">
+        <v>2</v>
+      </c>
+      <c r="C76" s="14">
         <v>1</v>
       </c>
       <c r="D76" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E76" s="13">
+      <c r="E76" s="14">
         <v>4055282</v>
       </c>
-      <c r="F76" s="13"/>
+      <c r="F76" s="14"/>
       <c r="G76" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H76" s="15" t="s">
+      <c r="H76" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I76" s="16"/>
@@ -3658,26 +3700,26 @@
       <c r="L76" s="16"/>
     </row>
     <row r="77" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A77" s="12">
+      <c r="A77" s="13">
         <v>2004</v>
       </c>
-      <c r="B77" s="13">
-        <v>2</v>
-      </c>
-      <c r="C77" s="13">
+      <c r="B77" s="14">
+        <v>2</v>
+      </c>
+      <c r="C77" s="14">
         <v>1</v>
       </c>
       <c r="D77" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E77" s="13">
+      <c r="E77" s="14">
         <v>4055283</v>
       </c>
-      <c r="F77" s="13"/>
+      <c r="F77" s="14"/>
       <c r="G77" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H77" s="15" t="s">
+      <c r="H77" s="9" t="s">
         <v>75</v>
       </c>
       <c r="I77" s="16"/>
@@ -3686,26 +3728,26 @@
       <c r="L77" s="16"/>
     </row>
     <row r="78" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A78" s="12">
+      <c r="A78" s="13">
         <v>2005</v>
       </c>
-      <c r="B78" s="13">
-        <v>2</v>
-      </c>
-      <c r="C78" s="13">
+      <c r="B78" s="14">
+        <v>2</v>
+      </c>
+      <c r="C78" s="14">
         <v>1</v>
       </c>
       <c r="D78" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E78" s="13">
+      <c r="E78" s="14">
         <v>4055284</v>
       </c>
-      <c r="F78" s="13"/>
+      <c r="F78" s="14"/>
       <c r="G78" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H78" s="15" t="s">
+      <c r="H78" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I78" s="16"/>
@@ -3714,26 +3756,26 @@
       <c r="L78" s="16"/>
     </row>
     <row r="79" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="12">
+      <c r="A79" s="13">
         <v>2006</v>
       </c>
-      <c r="B79" s="13">
-        <v>2</v>
-      </c>
-      <c r="C79" s="13">
+      <c r="B79" s="14">
+        <v>2</v>
+      </c>
+      <c r="C79" s="14">
         <v>1</v>
       </c>
       <c r="D79" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E79" s="13">
+      <c r="E79" s="14">
         <v>4055285</v>
       </c>
-      <c r="F79" s="13"/>
+      <c r="F79" s="14"/>
       <c r="G79" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H79" s="15" t="s">
+      <c r="H79" s="9" t="s">
         <v>75</v>
       </c>
       <c r="I79" s="16"/>
@@ -3742,26 +3784,26 @@
       <c r="L79" s="16"/>
     </row>
     <row r="80" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="12">
+      <c r="A80" s="13">
         <v>2007</v>
       </c>
-      <c r="B80" s="13">
-        <v>2</v>
-      </c>
-      <c r="C80" s="13">
+      <c r="B80" s="14">
+        <v>2</v>
+      </c>
+      <c r="C80" s="14">
         <v>1</v>
       </c>
       <c r="D80" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E80" s="13">
+      <c r="E80" s="14">
         <v>4055286</v>
       </c>
-      <c r="F80" s="13"/>
+      <c r="F80" s="14"/>
       <c r="G80" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H80" s="15" t="s">
+      <c r="H80" s="9" t="s">
         <v>76</v>
       </c>
       <c r="I80" s="16"/>
@@ -3789,13 +3831,13 @@
       <c r="G81" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H81" s="15" t="s">
+      <c r="H81" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="I81" s="15"/>
-      <c r="J81" s="15"/>
-      <c r="K81" s="15"/>
-      <c r="L81" s="15"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="9"/>
+      <c r="K81" s="9"/>
+      <c r="L81" s="9"/>
     </row>
     <row r="82" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A82" s="21">
@@ -3817,13 +3859,299 @@
       <c r="G82" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H82" s="15" t="s">
+      <c r="H82" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="I82" s="15"/>
-      <c r="J82" s="15"/>
-      <c r="K82" s="15"/>
-      <c r="L82" s="15"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="9"/>
+      <c r="K82" s="9"/>
+      <c r="L82" s="9"/>
+    </row>
+    <row r="83" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A83" s="8">
+        <v>2201</v>
+      </c>
+      <c r="B83" s="8">
+        <v>1</v>
+      </c>
+      <c r="C83" s="8">
+        <v>2</v>
+      </c>
+      <c r="D83" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="8">
+        <v>4055341</v>
+      </c>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H83" s="23"/>
+      <c r="I83" s="24"/>
+      <c r="J83" s="24"/>
+      <c r="K83" s="24"/>
+      <c r="L83" s="24"/>
+    </row>
+    <row r="84" customHeight="1" spans="1:12">
+      <c r="A84" s="8">
+        <v>2202</v>
+      </c>
+      <c r="B84" s="1">
+        <v>2</v>
+      </c>
+      <c r="C84" s="1">
+        <v>1</v>
+      </c>
+      <c r="D84" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="1">
+        <v>4055342</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="1:12">
+      <c r="A85" s="8">
+        <v>2203</v>
+      </c>
+      <c r="B85" s="1">
+        <v>3</v>
+      </c>
+      <c r="C85" s="1">
+        <v>1</v>
+      </c>
+      <c r="D85" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="1">
+        <v>4055343</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="1:12">
+      <c r="A86" s="8">
+        <v>2204</v>
+      </c>
+      <c r="B86" s="1">
+        <v>4</v>
+      </c>
+      <c r="C86" s="1">
+        <v>1</v>
+      </c>
+      <c r="D86" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="1">
+        <v>4055344</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:12">
+      <c r="A87" s="8">
+        <v>2205</v>
+      </c>
+      <c r="B87" s="1">
+        <v>5</v>
+      </c>
+      <c r="C87" s="1">
+        <v>1</v>
+      </c>
+      <c r="D87" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="1">
+        <v>4055345</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="1:12">
+      <c r="A88" s="8">
+        <v>2206</v>
+      </c>
+      <c r="B88" s="1">
+        <v>6</v>
+      </c>
+      <c r="C88" s="1">
+        <v>1</v>
+      </c>
+      <c r="D88" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="1">
+        <v>4055346</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:12">
+      <c r="A89" s="8">
+        <v>2207</v>
+      </c>
+      <c r="B89" s="1">
+        <v>7</v>
+      </c>
+      <c r="C89" s="1">
+        <v>1</v>
+      </c>
+      <c r="D89" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="1">
+        <v>4055347</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:12">
+      <c r="A90" s="8">
+        <v>2208</v>
+      </c>
+      <c r="B90" s="1">
+        <v>8</v>
+      </c>
+      <c r="C90" s="1">
+        <v>1</v>
+      </c>
+      <c r="D90" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="1">
+        <v>4055348</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:12">
+      <c r="A91" s="8">
+        <v>2209</v>
+      </c>
+      <c r="B91" s="1">
+        <v>9</v>
+      </c>
+      <c r="C91" s="1">
+        <v>1</v>
+      </c>
+      <c r="D91" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="1">
+        <v>4055349</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="1:12">
+      <c r="A92" s="8">
+        <v>2210</v>
+      </c>
+      <c r="B92" s="1">
+        <v>10</v>
+      </c>
+      <c r="C92" s="1">
+        <v>1</v>
+      </c>
+      <c r="D92" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="1">
+        <v>4055350</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:12">
+      <c r="A93" s="8">
+        <v>2211</v>
+      </c>
+      <c r="B93" s="1">
+        <v>11</v>
+      </c>
+      <c r="C93" s="1">
+        <v>1</v>
+      </c>
+      <c r="D93" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="1">
+        <v>4055351</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="1:12">
+      <c r="A94" s="8">
+        <v>2212</v>
+      </c>
+      <c r="B94" s="1">
+        <v>12</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1</v>
+      </c>
+      <c r="D94" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="1">
+        <v>4055352</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="1:12">
+      <c r="A95" s="8">
+        <v>2213</v>
+      </c>
+      <c r="B95" s="1">
+        <v>13</v>
+      </c>
+      <c r="C95" s="1">
+        <v>1</v>
+      </c>
+      <c r="D95" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="1">
+        <v>4055353</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="1:12">
+      <c r="A96" s="8">
+        <v>2214</v>
+      </c>
+      <c r="B96" s="1">
+        <v>14</v>
+      </c>
+      <c r="C96" s="1">
+        <v>1</v>
+      </c>
+      <c r="D96" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" s="1">
+        <v>4055354</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>80</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3880,93 +4208,241 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="I5">
-        <v>2101</v>
+        <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
-        <v>2101_</v>
+        <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
-        <v>2101_2102_2103_2104_</v>
+        <v>2201_2202_2203_2204_2205_2206_2207_2208_2209_2210_2211_2212_2213_2214_</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="I6">
-        <v>2102</v>
+        <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
-        <v>2102_</v>
+        <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="I7">
-        <v>2103</v>
+        <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
-        <v>2103_</v>
+        <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="I8">
-        <v>2104</v>
+        <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
-        <v>2104_</v>
+        <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="I9">
+        <v>2205</v>
+      </c>
+      <c r="J9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
+        <v>2205_</v>
+      </c>
+      <c r="M9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="I10">
+        <v>2206</v>
+      </c>
+      <c r="J10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="1"/>
+        <v>2206_</v>
+      </c>
+      <c r="M10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="I11">
+        <v>2207</v>
+      </c>
+      <c r="J11" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" t="str">
+        <f t="shared" si="1"/>
+        <v>2207_</v>
+      </c>
+      <c r="M11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="I12">
+        <v>2208</v>
+      </c>
+      <c r="J12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="1"/>
+        <v>2208_</v>
+      </c>
+      <c r="M12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="I13">
+        <v>2209</v>
+      </c>
+      <c r="J13" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" t="str">
+        <f t="shared" si="1"/>
+        <v>2209_</v>
+      </c>
+      <c r="M13" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
+        <v>92</v>
+      </c>
+      <c r="I14">
+        <v>2210</v>
+      </c>
+      <c r="J14" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="1"/>
+        <v>2210_</v>
+      </c>
+      <c r="M14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="I15">
+        <v>2211</v>
+      </c>
+      <c r="J15" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" si="1"/>
+        <v>2211_</v>
+      </c>
+      <c r="M15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="I16">
+        <v>2212</v>
+      </c>
+      <c r="J16" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="1"/>
+        <v>2212_</v>
+      </c>
+      <c r="M16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="I17">
+        <v>2213</v>
+      </c>
+      <c r="J17" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="1"/>
+        <v>2213_</v>
+      </c>
+      <c r="M17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="I18">
+        <v>2214</v>
+      </c>
+      <c r="J18" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="1"/>
+        <v>2214_</v>
+      </c>
+      <c r="M18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="101">
   <si>
     <t>序号</t>
   </si>
@@ -233,34 +233,31 @@
     <t>初入游戏-创建新号到经营大厅</t>
   </si>
   <si>
-    <t>欢迎来到GECA黄金星娱乐城，梦想由此启航！</t>
-  </si>
-  <si>
-    <t>娱乐城处处是机遇！</t>
-  </si>
-  <si>
-    <t>先前往SLOT区试试手气！</t>
-  </si>
-  <si>
-    <t>点击&lt;color=#00bfff&gt;旋转&lt;/color&gt;按钮，赢取大奖！</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>恭喜获得大奖！</t>
-  </si>
-  <si>
-    <t>聘请您成为GECA黄金星娱乐城经理人！</t>
-  </si>
-  <si>
-    <t>很高兴加入集团，将娱乐城打造为世界第一！</t>
-  </si>
-  <si>
-    <t>持续研发游戏、扩建新区，提升收益发展娱乐城！</t>
-  </si>
-  <si>
-    <t>开始经营娱乐城！</t>
+    <t>欢迎来到GECA黄金星娱乐城，梦想由此启航</t>
+  </si>
+  <si>
+    <t>娱乐城处处是机遇</t>
+  </si>
+  <si>
+    <t>先前往SLOT区试试手气</t>
+  </si>
+  <si>
+    <t>点击旋转按钮，赢取大奖</t>
+  </si>
+  <si>
+    <t>真的爆大奖了</t>
+  </si>
+  <si>
+    <t>恭喜您，我们将聘请您成为GECA黄金星娱乐城经理人</t>
+  </si>
+  <si>
+    <t>很高兴加入集团，将娱乐城打造为世界第一城</t>
+  </si>
+  <si>
+    <t>持续研发游戏、扩建新区，提升收益发展娱乐城</t>
+  </si>
+  <si>
+    <t>开始经营娱乐城</t>
   </si>
   <si>
     <t>建筑-愤怒的小鸟-升级1次</t>
@@ -289,6 +286,9 @@
   </si>
   <si>
     <t>请&lt;color=#00bfff&gt;再次旋转&lt;/color&gt;游戏</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>建筑-愤怒的小鸟-升到2级</t>
@@ -496,7 +496,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,6 +536,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0" tint="-0.15"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -552,6 +558,13 @@
       <color theme="0" tint="-0.5"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.15"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1041,137 +1054,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1199,7 +1212,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1220,7 +1236,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1232,7 +1248,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1241,10 +1257,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1741,40 +1763,40 @@
     <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="85.2916666666667" style="9" customWidth="1"/>
+    <col min="8" max="8" width="85.2916666666667" style="10" customWidth="1"/>
     <col min="13" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="11" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9"/>
+      <c r="H1" s="10"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
       <c r="L1"/>
     </row>
     <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1786,2086 +1808,2078 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="9"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="10"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="9"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10"/>
       <c r="I3"/>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="12"/>
-      <c r="H4" s="9"/>
+      <c r="A4" s="13"/>
+      <c r="H4" s="10"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
     </row>
     <row r="5" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>1001</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="14">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15">
         <v>4055101</v>
       </c>
-      <c r="F5" s="14"/>
+      <c r="F5" s="15"/>
       <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>1002</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="14">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="15">
         <v>4055102</v>
       </c>
-      <c r="F6" s="14"/>
+      <c r="F6" s="15"/>
       <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="13">
+      <c r="A7" s="14">
         <v>1003</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="14">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="15">
         <v>4055103</v>
       </c>
-      <c r="F7" s="14"/>
+      <c r="F7" s="15"/>
       <c r="G7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>1004</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="14">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15">
         <v>4055104</v>
       </c>
-      <c r="F8" s="14"/>
+      <c r="F8" s="15"/>
       <c r="G8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>1005</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
       <c r="G9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>1006</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="14">
-        <v>4055105</v>
-      </c>
-      <c r="F10" s="14"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15">
+        <v>4055106</v>
+      </c>
+      <c r="F10" s="15"/>
       <c r="G10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
+      <c r="H10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>1007</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="14">
-        <v>4055106</v>
-      </c>
-      <c r="F11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="15">
+        <v>4055107</v>
+      </c>
+      <c r="F11" s="15"/>
       <c r="G11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
+      <c r="H11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>1008</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
       <c r="G12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>1009</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
       <c r="G13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
     </row>
     <row r="14" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>1010</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
       <c r="G14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
     </row>
     <row r="15" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>1011</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>4055107</v>
-      </c>
-      <c r="F15" s="14"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>4055111</v>
+      </c>
+      <c r="F15" s="15"/>
       <c r="G15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
+      <c r="H15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
     </row>
     <row r="16" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>1012</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>4055108</v>
-      </c>
-      <c r="F16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>4055112</v>
+      </c>
+      <c r="F16" s="15"/>
       <c r="G16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
+      <c r="H16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
     </row>
     <row r="17" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="13">
+      <c r="A17" s="14">
         <v>1013</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14">
-        <v>4055109</v>
-      </c>
-      <c r="F17" s="14"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
+        <v>4055113</v>
+      </c>
+      <c r="F17" s="15"/>
       <c r="G17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+    </row>
+    <row r="18" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A18" s="18">
+        <v>1201</v>
+      </c>
+      <c r="B18" s="16">
+        <v>2</v>
+      </c>
+      <c r="C18" s="16">
+        <v>2</v>
+      </c>
+      <c r="D18" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="16">
+        <v>4055121</v>
+      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-    </row>
-    <row r="18" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="17">
-        <v>1201</v>
-      </c>
-      <c r="B18" s="15">
-        <v>2</v>
-      </c>
-      <c r="C18" s="15">
-        <v>2</v>
-      </c>
-      <c r="D18" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>4055121</v>
-      </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="18" t="s">
+      <c r="H18" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+    </row>
+    <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A19" s="18">
+        <v>1202</v>
+      </c>
+      <c r="B19" s="16">
+        <v>2</v>
+      </c>
+      <c r="C19" s="16">
+        <v>2</v>
+      </c>
+      <c r="D19" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="16">
+        <v>4055122</v>
+      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-    </row>
-    <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="17">
-        <v>1202</v>
-      </c>
-      <c r="B19" s="15">
-        <v>2</v>
-      </c>
-      <c r="C19" s="15">
-        <v>2</v>
-      </c>
-      <c r="D19" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="15">
-        <v>4055122</v>
-      </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="9" t="s">
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+    </row>
+    <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A20" s="18">
+        <v>1203</v>
+      </c>
+      <c r="B20" s="16">
+        <v>2</v>
+      </c>
+      <c r="C20" s="16">
+        <v>1</v>
+      </c>
+      <c r="D20" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="16">
+        <v>4055123</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-    </row>
-    <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="17">
-        <v>1203</v>
-      </c>
-      <c r="B20" s="15">
-        <v>2</v>
-      </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>4055123</v>
-      </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="9" t="s">
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+    </row>
+    <row r="21" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A21" s="18">
+        <v>1204</v>
+      </c>
+      <c r="B21" s="16">
+        <v>2</v>
+      </c>
+      <c r="C21" s="16">
+        <v>1</v>
+      </c>
+      <c r="D21" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="16">
+        <v>4055124</v>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-    </row>
-    <row r="21" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="17">
-        <v>1204</v>
-      </c>
-      <c r="B21" s="15">
-        <v>2</v>
-      </c>
-      <c r="C21" s="15">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="15">
-        <v>4055124</v>
-      </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" s="9" t="s">
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+    </row>
+    <row r="22" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A22" s="14">
+        <v>1301</v>
+      </c>
+      <c r="B22" s="15">
+        <v>2</v>
+      </c>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>4055141</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-    </row>
-    <row r="22" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="13">
-        <v>1301</v>
-      </c>
-      <c r="B22" s="14">
-        <v>2</v>
-      </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>4055141</v>
-      </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="19" t="s">
+      <c r="H22" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+    </row>
+    <row r="23" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A23" s="14">
+        <v>1302</v>
+      </c>
+      <c r="B23" s="15">
+        <v>2</v>
+      </c>
+      <c r="C23" s="15">
+        <v>1</v>
+      </c>
+      <c r="D23" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>4055142</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-    </row>
-    <row r="23" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A23" s="13">
-        <v>1302</v>
-      </c>
-      <c r="B23" s="14">
-        <v>2</v>
-      </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>4055142</v>
-      </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="9" t="s">
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+    </row>
+    <row r="24" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A24" s="14">
+        <v>1303</v>
+      </c>
+      <c r="B24" s="15">
+        <v>2</v>
+      </c>
+      <c r="C24" s="15">
+        <v>1</v>
+      </c>
+      <c r="D24" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15">
+        <v>4055143</v>
+      </c>
+      <c r="F24" s="15"/>
+      <c r="G24" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-    </row>
-    <row r="24" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A24" s="13">
-        <v>1303</v>
-      </c>
-      <c r="B24" s="14">
-        <v>2</v>
-      </c>
-      <c r="C24" s="14">
-        <v>1</v>
-      </c>
-      <c r="D24" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="14">
-        <v>4055143</v>
-      </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="9" t="s">
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+    </row>
+    <row r="25" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="14">
+        <v>1304</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15">
+        <v>1</v>
+      </c>
+      <c r="D25" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-    </row>
-    <row r="25" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="13">
-        <v>1304</v>
-      </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14">
-        <v>1</v>
-      </c>
-      <c r="D25" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
     </row>
     <row r="26" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="13">
+      <c r="A26" s="14">
         <v>1305</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14">
-        <v>1</v>
-      </c>
-      <c r="D26" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15">
+        <v>1</v>
+      </c>
+      <c r="D26" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
     </row>
     <row r="27" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="17">
+      <c r="A27" s="18">
         <v>1401</v>
       </c>
-      <c r="B27" s="15">
-        <v>2</v>
-      </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
+      <c r="B27" s="16">
+        <v>2</v>
+      </c>
+      <c r="C27" s="16">
+        <v>1</v>
+      </c>
+      <c r="D27" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="16">
         <v>4055161</v>
       </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="18" t="s">
+      <c r="F27" s="16"/>
+      <c r="G27" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
     </row>
     <row r="28" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="17">
+      <c r="A28" s="18">
         <v>1402</v>
       </c>
-      <c r="B28" s="15">
-        <v>2</v>
-      </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
+      <c r="B28" s="16">
+        <v>2</v>
+      </c>
+      <c r="C28" s="16">
+        <v>1</v>
+      </c>
+      <c r="D28" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="16">
         <v>4055162</v>
       </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="18" t="s">
+      <c r="F28" s="16"/>
+      <c r="G28" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
     </row>
     <row r="29" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="17">
+      <c r="A29" s="18">
         <v>1403</v>
       </c>
-      <c r="B29" s="15">
-        <v>2</v>
-      </c>
-      <c r="C29" s="15">
-        <v>1</v>
-      </c>
-      <c r="D29" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
+      <c r="B29" s="16">
+        <v>2</v>
+      </c>
+      <c r="C29" s="16">
+        <v>1</v>
+      </c>
+      <c r="D29" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="16">
         <v>4055163</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="18" t="s">
+      <c r="F29" s="16"/>
+      <c r="G29" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
     </row>
     <row r="30" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="17">
+      <c r="A30" s="18">
         <v>1404</v>
       </c>
-      <c r="B30" s="15">
-        <v>2</v>
-      </c>
-      <c r="C30" s="15">
-        <v>1</v>
-      </c>
-      <c r="D30" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
+      <c r="B30" s="16">
+        <v>2</v>
+      </c>
+      <c r="C30" s="16">
+        <v>1</v>
+      </c>
+      <c r="D30" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="16">
         <v>4055164</v>
       </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="18" t="s">
+      <c r="F30" s="16"/>
+      <c r="G30" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
     </row>
     <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="17">
+      <c r="A31" s="18">
         <v>1405</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15">
-        <v>1</v>
-      </c>
-      <c r="D31" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="18" t="s">
+      <c r="B31" s="16"/>
+      <c r="C31" s="16">
+        <v>1</v>
+      </c>
+      <c r="D31" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H31" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
+      <c r="H31" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
     </row>
     <row r="32" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="17">
+      <c r="A32" s="18">
         <v>1406</v>
       </c>
-      <c r="B32" s="15">
-        <v>2</v>
-      </c>
-      <c r="C32" s="15">
-        <v>1</v>
-      </c>
-      <c r="D32" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="15">
+      <c r="B32" s="16">
+        <v>2</v>
+      </c>
+      <c r="C32" s="16">
+        <v>1</v>
+      </c>
+      <c r="D32" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="16">
         <v>4055165</v>
       </c>
-      <c r="F32" s="15"/>
-      <c r="G32" s="18" t="s">
+      <c r="F32" s="16"/>
+      <c r="G32" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
     </row>
     <row r="33" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="13">
+      <c r="A33" s="14">
         <v>1501</v>
       </c>
-      <c r="B33" s="14">
-        <v>2</v>
-      </c>
-      <c r="C33" s="14">
-        <v>1</v>
-      </c>
-      <c r="D33" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="14">
+      <c r="B33" s="15">
+        <v>2</v>
+      </c>
+      <c r="C33" s="15">
+        <v>1</v>
+      </c>
+      <c r="D33" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
         <v>4055181</v>
       </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="19" t="s">
+      <c r="F33" s="15"/>
+      <c r="G33" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
     </row>
     <row r="34" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="13">
+      <c r="A34" s="14">
         <v>1502</v>
       </c>
-      <c r="B34" s="14">
-        <v>2</v>
-      </c>
-      <c r="C34" s="14">
-        <v>1</v>
-      </c>
-      <c r="D34" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="14">
+      <c r="B34" s="15">
+        <v>2</v>
+      </c>
+      <c r="C34" s="15">
+        <v>1</v>
+      </c>
+      <c r="D34" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="15">
         <v>4055182</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="19" t="s">
+      <c r="F34" s="15"/>
+      <c r="G34" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
     </row>
     <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="13">
+      <c r="A35" s="14">
         <v>1503</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14">
-        <v>1</v>
-      </c>
-      <c r="D35" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="19" t="s">
+      <c r="B35" s="15"/>
+      <c r="C35" s="15">
+        <v>1</v>
+      </c>
+      <c r="D35" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
+      <c r="H35" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
     </row>
     <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="13">
+      <c r="A36" s="14">
         <v>1504</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14">
-        <v>1</v>
-      </c>
-      <c r="D36" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="19" t="s">
+      <c r="B36" s="15"/>
+      <c r="C36" s="15">
+        <v>1</v>
+      </c>
+      <c r="D36" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="H36" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+      <c r="H36" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
     </row>
     <row r="37" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="17">
+      <c r="A37" s="18">
         <v>1601</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15">
-        <v>1</v>
-      </c>
-      <c r="D37" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="18" t="s">
+      <c r="B37" s="16"/>
+      <c r="C37" s="16">
+        <v>1</v>
+      </c>
+      <c r="D37" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H37" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
+      <c r="H37" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
     </row>
     <row r="38" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="17">
+      <c r="A38" s="18">
         <v>1602</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15">
-        <v>1</v>
-      </c>
-      <c r="D38" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="18" t="s">
+      <c r="B38" s="16"/>
+      <c r="C38" s="16">
+        <v>1</v>
+      </c>
+      <c r="D38" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H38" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
+      <c r="H38" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
     </row>
     <row r="39" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A39" s="17">
+      <c r="A39" s="18">
         <v>1603</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15">
-        <v>1</v>
-      </c>
-      <c r="D39" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="15">
+      <c r="B39" s="16"/>
+      <c r="C39" s="16">
+        <v>1</v>
+      </c>
+      <c r="D39" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="16">
         <v>4055203</v>
       </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="18" t="s">
+      <c r="F39" s="15"/>
+      <c r="G39" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
     </row>
     <row r="40" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="17">
+      <c r="A40" s="18">
         <v>1604</v>
       </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15">
-        <v>1</v>
-      </c>
-      <c r="D40" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="18" t="s">
+      <c r="B40" s="16"/>
+      <c r="C40" s="16">
+        <v>1</v>
+      </c>
+      <c r="D40" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H40" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
+      <c r="H40" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
     </row>
     <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="17">
+      <c r="A41" s="18">
         <v>1605</v>
       </c>
-      <c r="B41" s="15">
-        <v>2</v>
-      </c>
-      <c r="C41" s="15">
-        <v>1</v>
-      </c>
-      <c r="D41" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="15">
+      <c r="B41" s="16">
+        <v>2</v>
+      </c>
+      <c r="C41" s="16">
+        <v>1</v>
+      </c>
+      <c r="D41" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="16">
         <v>4055204</v>
       </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="18" t="s">
+      <c r="F41" s="15"/>
+      <c r="G41" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
     </row>
     <row r="42" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="17">
+      <c r="A42" s="18">
         <v>1606</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15">
-        <v>1</v>
-      </c>
-      <c r="D42" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="18" t="s">
+      <c r="B42" s="16"/>
+      <c r="C42" s="16">
+        <v>1</v>
+      </c>
+      <c r="D42" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
+      <c r="H42" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
     </row>
     <row r="43" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="17">
+      <c r="A43" s="18">
         <v>1607</v>
       </c>
-      <c r="B43" s="15">
-        <v>2</v>
-      </c>
-      <c r="C43" s="15">
-        <v>1</v>
-      </c>
-      <c r="D43" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="18" t="s">
+      <c r="B43" s="16">
+        <v>2</v>
+      </c>
+      <c r="C43" s="16">
+        <v>1</v>
+      </c>
+      <c r="D43" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H43" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
+      <c r="H43" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
     </row>
     <row r="44" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="17">
+      <c r="A44" s="18">
         <v>1608</v>
       </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15">
-        <v>1</v>
-      </c>
-      <c r="D44" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="15">
+      <c r="B44" s="16"/>
+      <c r="C44" s="16">
+        <v>1</v>
+      </c>
+      <c r="D44" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="16">
         <v>4055205</v>
       </c>
-      <c r="F44" s="14"/>
-      <c r="G44" s="18" t="s">
+      <c r="F44" s="15"/>
+      <c r="G44" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H44" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
     </row>
     <row r="45" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="17">
+      <c r="A45" s="18">
         <v>1609</v>
       </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15">
-        <v>1</v>
-      </c>
-      <c r="D45" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="15">
+      <c r="B45" s="16"/>
+      <c r="C45" s="16">
+        <v>1</v>
+      </c>
+      <c r="D45" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="16">
         <v>4055206</v>
       </c>
-      <c r="F45" s="14"/>
-      <c r="G45" s="18" t="s">
+      <c r="F45" s="15"/>
+      <c r="G45" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
     </row>
     <row r="46" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="17">
+      <c r="A46" s="18">
         <v>1610</v>
       </c>
-      <c r="B46" s="15">
-        <v>2</v>
-      </c>
-      <c r="C46" s="15">
-        <v>1</v>
-      </c>
-      <c r="D46" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="15">
+      <c r="B46" s="16">
+        <v>2</v>
+      </c>
+      <c r="C46" s="16">
+        <v>1</v>
+      </c>
+      <c r="D46" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="16">
         <v>4055207</v>
       </c>
-      <c r="F46" s="14"/>
-      <c r="G46" s="18" t="s">
+      <c r="F46" s="15"/>
+      <c r="G46" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H46" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
     </row>
     <row r="47" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="17">
+      <c r="A47" s="18">
         <v>1611</v>
       </c>
-      <c r="B47" s="15">
-        <v>2</v>
-      </c>
-      <c r="C47" s="15">
-        <v>1</v>
-      </c>
-      <c r="D47" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="15">
+      <c r="B47" s="16">
+        <v>2</v>
+      </c>
+      <c r="C47" s="16">
+        <v>1</v>
+      </c>
+      <c r="D47" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="16">
         <v>4055208</v>
       </c>
-      <c r="F47" s="14"/>
-      <c r="G47" s="18" t="s">
+      <c r="F47" s="15"/>
+      <c r="G47" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H47" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
     </row>
     <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="17">
+      <c r="A48" s="18">
         <v>1612</v>
       </c>
-      <c r="B48" s="15">
-        <v>2</v>
-      </c>
-      <c r="C48" s="15">
-        <v>1</v>
-      </c>
-      <c r="D48" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="15">
+      <c r="B48" s="16">
+        <v>2</v>
+      </c>
+      <c r="C48" s="16">
+        <v>1</v>
+      </c>
+      <c r="D48" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="16">
         <v>4055209</v>
       </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="18" t="s">
+      <c r="F48" s="15"/>
+      <c r="G48" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="9" t="s">
+      <c r="H48" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I48" s="9"/>
-      <c r="J48" s="9"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
     </row>
     <row r="49" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="13">
+      <c r="A49" s="14">
         <v>1701</v>
       </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14">
-        <v>1</v>
-      </c>
-      <c r="D49" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="19" t="s">
+      <c r="B49" s="15"/>
+      <c r="C49" s="15">
+        <v>1</v>
+      </c>
+      <c r="D49" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H49" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
+      <c r="H49" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
     </row>
     <row r="50" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A50" s="13">
+      <c r="A50" s="14">
         <v>1702</v>
       </c>
-      <c r="C50" s="14">
-        <v>1</v>
-      </c>
-      <c r="D50" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="14"/>
-      <c r="G50" s="19" t="s">
+      <c r="C50" s="15">
+        <v>1</v>
+      </c>
+      <c r="D50" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="15"/>
+      <c r="G50" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H50" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I50" s="16"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
+      <c r="H50" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
     </row>
     <row r="51" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A51" s="13">
+      <c r="A51" s="14">
         <v>1703</v>
       </c>
-      <c r="B51" s="14">
-        <v>2</v>
-      </c>
-      <c r="C51" s="14">
-        <v>1</v>
-      </c>
-      <c r="D51" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="14">
+      <c r="B51" s="15">
+        <v>2</v>
+      </c>
+      <c r="C51" s="15">
+        <v>1</v>
+      </c>
+      <c r="D51" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="15">
         <v>4055222</v>
       </c>
-      <c r="F51" s="14"/>
-      <c r="G51" s="19" t="s">
+      <c r="F51" s="15"/>
+      <c r="G51" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H51" s="9" t="s">
+      <c r="H51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I51" s="16"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
     </row>
     <row r="52" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A52" s="13">
+      <c r="A52" s="14">
         <v>1704</v>
       </c>
-      <c r="B52" s="14">
-        <v>2</v>
-      </c>
-      <c r="C52" s="14">
-        <v>1</v>
-      </c>
-      <c r="D52" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="14">
+      <c r="B52" s="15">
+        <v>2</v>
+      </c>
+      <c r="C52" s="15">
+        <v>1</v>
+      </c>
+      <c r="D52" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="15">
         <v>4055223</v>
       </c>
-      <c r="F52" s="14"/>
-      <c r="G52" s="19" t="s">
+      <c r="F52" s="15"/>
+      <c r="G52" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H52" s="9" t="s">
+      <c r="H52" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
     </row>
     <row r="53" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A53" s="13">
+      <c r="A53" s="14">
         <v>1705</v>
       </c>
-      <c r="B53" s="14">
-        <v>2</v>
-      </c>
-      <c r="C53" s="14">
-        <v>1</v>
-      </c>
-      <c r="D53" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="14">
+      <c r="B53" s="15">
+        <v>2</v>
+      </c>
+      <c r="C53" s="15">
+        <v>1</v>
+      </c>
+      <c r="D53" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="15">
         <v>4055224</v>
       </c>
-      <c r="F53" s="14"/>
-      <c r="G53" s="19" t="s">
+      <c r="F53" s="15"/>
+      <c r="G53" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H53" s="9" t="s">
+      <c r="H53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="I53" s="16"/>
-      <c r="J53" s="16"/>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
     </row>
     <row r="54" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A54" s="13">
+      <c r="A54" s="14">
         <v>1706</v>
       </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14">
-        <v>1</v>
-      </c>
-      <c r="D54" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="19" t="s">
+      <c r="B54" s="15"/>
+      <c r="C54" s="15">
+        <v>1</v>
+      </c>
+      <c r="D54" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H54" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I54" s="16"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
+      <c r="H54" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
     </row>
     <row r="55" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A55" s="13">
+      <c r="A55" s="14">
         <v>1707</v>
       </c>
-      <c r="B55" s="14">
-        <v>2</v>
-      </c>
-      <c r="C55" s="14">
-        <v>1</v>
-      </c>
-      <c r="D55" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="14">
+      <c r="B55" s="15">
+        <v>2</v>
+      </c>
+      <c r="C55" s="15">
+        <v>1</v>
+      </c>
+      <c r="D55" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="15">
         <v>4055225</v>
       </c>
-      <c r="F55" s="14"/>
-      <c r="G55" s="19" t="s">
+      <c r="F55" s="15"/>
+      <c r="G55" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H55" s="9" t="s">
+      <c r="H55" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="I55" s="16"/>
-      <c r="J55" s="16"/>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
     </row>
     <row r="56" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A56" s="13">
+      <c r="A56" s="14">
         <v>1708</v>
       </c>
-      <c r="B56" s="14">
-        <v>2</v>
-      </c>
-      <c r="C56" s="14">
-        <v>1</v>
-      </c>
-      <c r="D56" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="14">
+      <c r="B56" s="15">
+        <v>2</v>
+      </c>
+      <c r="C56" s="15">
+        <v>1</v>
+      </c>
+      <c r="D56" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="15">
         <v>4055226</v>
       </c>
-      <c r="F56" s="14"/>
-      <c r="G56" s="19" t="s">
+      <c r="F56" s="15"/>
+      <c r="G56" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H56" s="9" t="s">
+      <c r="H56" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="I56" s="16"/>
-      <c r="J56" s="16"/>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
     </row>
     <row r="57" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A57" s="13">
+      <c r="A57" s="14">
         <v>1709</v>
       </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14">
-        <v>1</v>
-      </c>
-      <c r="D57" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="19" t="s">
+      <c r="B57" s="15"/>
+      <c r="C57" s="15">
+        <v>1</v>
+      </c>
+      <c r="D57" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H57" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I57" s="16"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
+      <c r="H57" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
     </row>
     <row r="58" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A58" s="13">
+      <c r="A58" s="14">
         <v>1710</v>
       </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14">
-        <v>1</v>
-      </c>
-      <c r="D58" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="19" t="s">
+      <c r="B58" s="15"/>
+      <c r="C58" s="15">
+        <v>1</v>
+      </c>
+      <c r="D58" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H58" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I58" s="16"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
+      <c r="H58" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
     </row>
     <row r="59" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="13">
+      <c r="A59" s="14">
         <v>1711</v>
       </c>
-      <c r="B59" s="14">
-        <v>2</v>
-      </c>
-      <c r="C59" s="14">
-        <v>1</v>
-      </c>
-      <c r="D59" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="14">
+      <c r="B59" s="15">
+        <v>2</v>
+      </c>
+      <c r="C59" s="15">
+        <v>1</v>
+      </c>
+      <c r="D59" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="15">
         <v>4055227</v>
       </c>
-      <c r="F59" s="14"/>
-      <c r="G59" s="19" t="s">
+      <c r="F59" s="15"/>
+      <c r="G59" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H59" s="9" t="s">
+      <c r="H59" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I59" s="16"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
     </row>
     <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="13">
+      <c r="A60" s="14">
         <v>1712</v>
       </c>
-      <c r="B60" s="14">
-        <v>2</v>
-      </c>
-      <c r="C60" s="14">
-        <v>1</v>
-      </c>
-      <c r="D60" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="14">
+      <c r="B60" s="15">
+        <v>2</v>
+      </c>
+      <c r="C60" s="15">
+        <v>1</v>
+      </c>
+      <c r="D60" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="15">
         <v>4055228</v>
       </c>
-      <c r="F60" s="14"/>
-      <c r="G60" s="19" t="s">
+      <c r="F60" s="15"/>
+      <c r="G60" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H60" s="9" t="s">
+      <c r="H60" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="I60" s="16"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
     </row>
     <row r="61" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="17">
+      <c r="A61" s="18">
         <v>1801</v>
       </c>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15">
-        <v>1</v>
-      </c>
-      <c r="D61" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="18" t="s">
+      <c r="B61" s="16"/>
+      <c r="C61" s="16">
+        <v>1</v>
+      </c>
+      <c r="D61" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H61" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61" s="9"/>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="9"/>
+      <c r="H61" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
     </row>
     <row r="62" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A62" s="17">
+      <c r="A62" s="18">
         <v>1802</v>
       </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15">
-        <v>1</v>
-      </c>
-      <c r="D62" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="18" t="s">
+      <c r="B62" s="16"/>
+      <c r="C62" s="16">
+        <v>1</v>
+      </c>
+      <c r="D62" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H62" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I62" s="9"/>
-      <c r="J62" s="9"/>
-      <c r="K62" s="9"/>
-      <c r="L62" s="9"/>
+      <c r="H62" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
     </row>
     <row r="63" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A63" s="17">
+      <c r="A63" s="18">
         <v>1803</v>
       </c>
-      <c r="B63" s="15">
-        <v>2</v>
-      </c>
-      <c r="C63" s="15">
-        <v>1</v>
-      </c>
-      <c r="D63" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="15">
+      <c r="B63" s="16">
+        <v>2</v>
+      </c>
+      <c r="C63" s="16">
+        <v>1</v>
+      </c>
+      <c r="D63" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="16">
         <v>4055243</v>
       </c>
-      <c r="F63" s="15"/>
-      <c r="G63" s="18" t="s">
+      <c r="F63" s="16"/>
+      <c r="G63" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H63" s="9" t="s">
+      <c r="H63" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="I63" s="9"/>
-      <c r="J63" s="9"/>
-      <c r="K63" s="9"/>
-      <c r="L63" s="9"/>
+      <c r="I63" s="10"/>
+      <c r="J63" s="10"/>
+      <c r="K63" s="10"/>
+      <c r="L63" s="10"/>
     </row>
     <row r="64" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A64" s="17">
+      <c r="A64" s="18">
         <v>1804</v>
       </c>
-      <c r="B64" s="15">
-        <v>2</v>
-      </c>
-      <c r="C64" s="15">
-        <v>1</v>
-      </c>
-      <c r="D64" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="15">
+      <c r="B64" s="16">
+        <v>2</v>
+      </c>
+      <c r="C64" s="16">
+        <v>1</v>
+      </c>
+      <c r="D64" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="16">
         <v>4055244</v>
       </c>
-      <c r="F64" s="15"/>
-      <c r="G64" s="18" t="s">
+      <c r="F64" s="16"/>
+      <c r="G64" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H64" s="9" t="s">
+      <c r="H64" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I64" s="9"/>
-      <c r="J64" s="9"/>
-      <c r="K64" s="9"/>
-      <c r="L64" s="9"/>
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+      <c r="L64" s="10"/>
     </row>
     <row r="65" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A65" s="17">
+      <c r="A65" s="18">
         <v>1805</v>
       </c>
-      <c r="B65" s="15">
-        <v>2</v>
-      </c>
-      <c r="C65" s="15">
-        <v>1</v>
-      </c>
-      <c r="D65" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="15">
+      <c r="B65" s="16">
+        <v>2</v>
+      </c>
+      <c r="C65" s="16">
+        <v>1</v>
+      </c>
+      <c r="D65" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="16">
         <v>4055245</v>
       </c>
-      <c r="F65" s="15"/>
-      <c r="G65" s="18" t="s">
+      <c r="F65" s="16"/>
+      <c r="G65" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H65" s="9" t="s">
+      <c r="H65" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I65" s="9"/>
-      <c r="J65" s="9"/>
-      <c r="K65" s="9"/>
-      <c r="L65" s="9"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10"/>
+      <c r="L65" s="10"/>
     </row>
     <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="17">
+      <c r="A66" s="18">
         <v>1806</v>
       </c>
-      <c r="B66" s="15">
-        <v>2</v>
-      </c>
-      <c r="C66" s="15">
-        <v>1</v>
-      </c>
-      <c r="D66" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="15">
+      <c r="B66" s="16">
+        <v>2</v>
+      </c>
+      <c r="C66" s="16">
+        <v>1</v>
+      </c>
+      <c r="D66" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="16">
         <v>4055246</v>
       </c>
-      <c r="F66" s="15"/>
-      <c r="G66" s="18" t="s">
+      <c r="F66" s="16"/>
+      <c r="G66" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H66" s="9" t="s">
+      <c r="H66" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="I66" s="9"/>
-      <c r="J66" s="9"/>
-      <c r="K66" s="9"/>
-      <c r="L66" s="9"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="10"/>
     </row>
     <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="17">
+      <c r="A67" s="18">
         <v>1807</v>
       </c>
-      <c r="B67" s="15">
-        <v>2</v>
-      </c>
-      <c r="C67" s="15">
-        <v>1</v>
-      </c>
-      <c r="D67" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="15">
+      <c r="B67" s="16">
+        <v>2</v>
+      </c>
+      <c r="C67" s="16">
+        <v>1</v>
+      </c>
+      <c r="D67" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="16">
         <v>4055247</v>
       </c>
-      <c r="F67" s="15"/>
-      <c r="G67" s="18" t="s">
+      <c r="F67" s="16"/>
+      <c r="G67" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="H67" s="9" t="s">
+      <c r="H67" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I67" s="9"/>
-      <c r="J67" s="9"/>
-      <c r="K67" s="9"/>
-      <c r="L67" s="9"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10"/>
+      <c r="L67" s="10"/>
     </row>
     <row r="68" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="13">
+      <c r="A68" s="14">
         <v>1901</v>
       </c>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14">
-        <v>1</v>
-      </c>
-      <c r="D68" s="20" t="b">
+      <c r="B68" s="15"/>
+      <c r="C68" s="15">
+        <v>1</v>
+      </c>
+      <c r="D68" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="19" t="s">
+      <c r="E68" s="15"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="H68" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I68" s="16"/>
-      <c r="J68" s="16"/>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
+      <c r="H68" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
+      <c r="L68" s="17"/>
     </row>
     <row r="69" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A69" s="13">
+      <c r="A69" s="14">
         <v>1902</v>
       </c>
-      <c r="B69" s="14">
-        <v>2</v>
-      </c>
-      <c r="C69" s="14">
-        <v>1</v>
-      </c>
-      <c r="D69" s="20" t="b">
+      <c r="B69" s="15">
+        <v>2</v>
+      </c>
+      <c r="C69" s="15">
+        <v>1</v>
+      </c>
+      <c r="D69" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E69" s="14">
+      <c r="E69" s="15">
         <v>4055263</v>
       </c>
-      <c r="F69" s="14"/>
-      <c r="G69" s="19" t="s">
+      <c r="F69" s="15"/>
+      <c r="G69" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="H69" s="9" t="s">
+      <c r="H69" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="I69" s="16"/>
-      <c r="J69" s="16"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="17"/>
+      <c r="K69" s="17"/>
+      <c r="L69" s="17"/>
     </row>
     <row r="70" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="13">
+      <c r="A70" s="14">
         <v>1903</v>
       </c>
-      <c r="B70" s="14">
-        <v>2</v>
-      </c>
-      <c r="C70" s="14">
-        <v>1</v>
-      </c>
-      <c r="D70" s="20" t="b">
+      <c r="B70" s="15">
+        <v>2</v>
+      </c>
+      <c r="C70" s="15">
+        <v>1</v>
+      </c>
+      <c r="D70" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E70" s="14">
+      <c r="E70" s="15">
         <v>4055264</v>
       </c>
-      <c r="F70" s="14"/>
-      <c r="G70" s="19" t="s">
+      <c r="F70" s="15"/>
+      <c r="G70" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="H70" s="9" t="s">
+      <c r="H70" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="I70" s="16"/>
-      <c r="J70" s="16"/>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="17"/>
+      <c r="K70" s="17"/>
+      <c r="L70" s="17"/>
     </row>
     <row r="71" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="17">
+      <c r="A71" s="18">
         <v>1981</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15">
-        <v>1</v>
-      </c>
-      <c r="D71" s="20" t="b">
+      <c r="B71" s="16"/>
+      <c r="C71" s="16">
+        <v>1</v>
+      </c>
+      <c r="D71" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="18" t="s">
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="H71" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I71" s="9"/>
-      <c r="J71" s="9"/>
-      <c r="K71" s="9"/>
-      <c r="L71" s="9"/>
+      <c r="H71" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="10"/>
     </row>
     <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="17">
+      <c r="A72" s="18">
         <v>1982</v>
       </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="15">
-        <v>1</v>
-      </c>
-      <c r="D72" s="20" t="b">
+      <c r="B72" s="16"/>
+      <c r="C72" s="16">
+        <v>1</v>
+      </c>
+      <c r="D72" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="18" t="s">
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="H72" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I72" s="9"/>
-      <c r="J72" s="9"/>
-      <c r="K72" s="9"/>
-      <c r="L72" s="9"/>
+      <c r="H72" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72" s="10"/>
+      <c r="J72" s="10"/>
+      <c r="K72" s="10"/>
+      <c r="L72" s="10"/>
     </row>
     <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A73" s="17">
+      <c r="A73" s="18">
         <v>1983</v>
       </c>
-      <c r="B73" s="15">
-        <v>2</v>
-      </c>
-      <c r="C73" s="15">
-        <v>1</v>
-      </c>
-      <c r="D73" s="20" t="b">
+      <c r="B73" s="16">
+        <v>2</v>
+      </c>
+      <c r="C73" s="16">
+        <v>1</v>
+      </c>
+      <c r="D73" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E73" s="15">
+      <c r="E73" s="16">
         <v>4055321</v>
       </c>
-      <c r="F73" s="15"/>
-      <c r="G73" s="18" t="s">
+      <c r="F73" s="16"/>
+      <c r="G73" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="H73" s="9" t="s">
+      <c r="H73" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9"/>
-      <c r="K73" s="9"/>
-      <c r="L73" s="9"/>
+      <c r="I73" s="10"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="10"/>
+      <c r="L73" s="10"/>
     </row>
     <row r="74" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="13">
+      <c r="A74" s="14">
         <v>2001</v>
       </c>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14">
-        <v>1</v>
-      </c>
-      <c r="D74" s="20" t="b">
+      <c r="B74" s="15"/>
+      <c r="C74" s="15">
+        <v>1</v>
+      </c>
+      <c r="D74" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="19" t="s">
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H74" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I74" s="16"/>
-      <c r="J74" s="16"/>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
+      <c r="H74" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74" s="17"/>
+      <c r="J74" s="17"/>
+      <c r="K74" s="17"/>
+      <c r="L74" s="17"/>
     </row>
     <row r="75" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="13">
+      <c r="A75" s="14">
         <v>2002</v>
       </c>
-      <c r="B75" s="14">
-        <v>2</v>
-      </c>
-      <c r="C75" s="14">
-        <v>1</v>
-      </c>
-      <c r="D75" s="20" t="b">
+      <c r="B75" s="15">
+        <v>2</v>
+      </c>
+      <c r="C75" s="15">
+        <v>1</v>
+      </c>
+      <c r="D75" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E75" s="14">
+      <c r="E75" s="15">
         <v>4055281</v>
       </c>
-      <c r="F75" s="14"/>
-      <c r="G75" s="19" t="s">
+      <c r="F75" s="15"/>
+      <c r="G75" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H75" s="9" t="s">
+      <c r="H75" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="16"/>
-      <c r="J75" s="16"/>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
+      <c r="L75" s="17"/>
     </row>
     <row r="76" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A76" s="13">
+      <c r="A76" s="14">
         <v>2003</v>
       </c>
-      <c r="B76" s="14">
-        <v>2</v>
-      </c>
-      <c r="C76" s="14">
-        <v>1</v>
-      </c>
-      <c r="D76" s="20" t="b">
+      <c r="B76" s="15">
+        <v>2</v>
+      </c>
+      <c r="C76" s="15">
+        <v>1</v>
+      </c>
+      <c r="D76" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E76" s="14">
+      <c r="E76" s="15">
         <v>4055282</v>
       </c>
-      <c r="F76" s="14"/>
-      <c r="G76" s="19" t="s">
+      <c r="F76" s="15"/>
+      <c r="G76" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H76" s="9" t="s">
+      <c r="H76" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I76" s="16"/>
-      <c r="J76" s="16"/>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
+      <c r="I76" s="17"/>
+      <c r="J76" s="17"/>
+      <c r="K76" s="17"/>
+      <c r="L76" s="17"/>
     </row>
     <row r="77" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A77" s="13">
+      <c r="A77" s="14">
         <v>2004</v>
       </c>
-      <c r="B77" s="14">
-        <v>2</v>
-      </c>
-      <c r="C77" s="14">
-        <v>1</v>
-      </c>
-      <c r="D77" s="20" t="b">
+      <c r="B77" s="15">
+        <v>2</v>
+      </c>
+      <c r="C77" s="15">
+        <v>1</v>
+      </c>
+      <c r="D77" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E77" s="14">
+      <c r="E77" s="15">
         <v>4055283</v>
       </c>
-      <c r="F77" s="14"/>
-      <c r="G77" s="19" t="s">
+      <c r="F77" s="15"/>
+      <c r="G77" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H77" s="9" t="s">
+      <c r="H77" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I77" s="16"/>
-      <c r="J77" s="16"/>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
+      <c r="K77" s="17"/>
+      <c r="L77" s="17"/>
     </row>
     <row r="78" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A78" s="13">
+      <c r="A78" s="14">
         <v>2005</v>
       </c>
-      <c r="B78" s="14">
-        <v>2</v>
-      </c>
-      <c r="C78" s="14">
-        <v>1</v>
-      </c>
-      <c r="D78" s="20" t="b">
+      <c r="B78" s="15">
+        <v>2</v>
+      </c>
+      <c r="C78" s="15">
+        <v>1</v>
+      </c>
+      <c r="D78" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E78" s="14">
+      <c r="E78" s="15">
         <v>4055284</v>
       </c>
-      <c r="F78" s="14"/>
-      <c r="G78" s="19" t="s">
+      <c r="F78" s="15"/>
+      <c r="G78" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H78" s="9" t="s">
+      <c r="H78" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I78" s="16"/>
-      <c r="J78" s="16"/>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="17"/>
+      <c r="K78" s="17"/>
+      <c r="L78" s="17"/>
     </row>
     <row r="79" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="13">
+      <c r="A79" s="14">
         <v>2006</v>
       </c>
-      <c r="B79" s="14">
-        <v>2</v>
-      </c>
-      <c r="C79" s="14">
-        <v>1</v>
-      </c>
-      <c r="D79" s="20" t="b">
+      <c r="B79" s="15">
+        <v>2</v>
+      </c>
+      <c r="C79" s="15">
+        <v>1</v>
+      </c>
+      <c r="D79" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E79" s="14">
+      <c r="E79" s="15">
         <v>4055285</v>
       </c>
-      <c r="F79" s="14"/>
-      <c r="G79" s="19" t="s">
+      <c r="F79" s="15"/>
+      <c r="G79" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H79" s="9" t="s">
+      <c r="H79" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I79" s="16"/>
-      <c r="J79" s="16"/>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="17"/>
+      <c r="K79" s="17"/>
+      <c r="L79" s="17"/>
     </row>
     <row r="80" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="13">
+      <c r="A80" s="14">
         <v>2007</v>
       </c>
-      <c r="B80" s="14">
-        <v>2</v>
-      </c>
-      <c r="C80" s="14">
-        <v>1</v>
-      </c>
-      <c r="D80" s="20" t="b">
+      <c r="B80" s="15">
+        <v>2</v>
+      </c>
+      <c r="C80" s="15">
+        <v>1</v>
+      </c>
+      <c r="D80" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E80" s="14">
+      <c r="E80" s="15">
         <v>4055286</v>
       </c>
-      <c r="F80" s="14"/>
-      <c r="G80" s="19" t="s">
+      <c r="F80" s="15"/>
+      <c r="G80" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H80" s="9" t="s">
+      <c r="H80" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I80" s="16"/>
-      <c r="J80" s="16"/>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="17"/>
+      <c r="K80" s="17"/>
+      <c r="L80" s="17"/>
     </row>
     <row r="81" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="21">
+      <c r="A81" s="22">
         <v>2101</v>
       </c>
-      <c r="B81" s="21">
-        <v>2</v>
-      </c>
-      <c r="C81" s="21">
-        <v>1</v>
-      </c>
-      <c r="D81" s="20" t="b">
+      <c r="B81" s="22">
+        <v>2</v>
+      </c>
+      <c r="C81" s="22">
+        <v>1</v>
+      </c>
+      <c r="D81" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E81" s="21">
+      <c r="E81" s="22">
         <v>4055301</v>
       </c>
-      <c r="F81" s="21"/>
+      <c r="F81" s="22"/>
       <c r="G81" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H81" s="9" t="s">
+      <c r="H81" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9"/>
-      <c r="K81" s="9"/>
-      <c r="L81" s="9"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="10"/>
+      <c r="L81" s="10"/>
     </row>
     <row r="82" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="21">
+      <c r="A82" s="22">
         <v>2102</v>
       </c>
-      <c r="B82" s="21">
-        <v>1</v>
-      </c>
-      <c r="C82" s="21">
-        <v>1</v>
-      </c>
-      <c r="D82" s="20" t="b">
+      <c r="B82" s="22">
+        <v>1</v>
+      </c>
+      <c r="C82" s="22">
+        <v>1</v>
+      </c>
+      <c r="D82" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="E82" s="21">
+      <c r="E82" s="22">
         <v>4055303</v>
       </c>
-      <c r="F82" s="21"/>
+      <c r="F82" s="22"/>
       <c r="G82" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H82" s="9" t="s">
+      <c r="H82" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I82" s="9"/>
-      <c r="J82" s="9"/>
-      <c r="K82" s="9"/>
-      <c r="L82" s="9"/>
+      <c r="I82" s="10"/>
+      <c r="J82" s="10"/>
+      <c r="K82" s="10"/>
+      <c r="L82" s="10"/>
     </row>
     <row r="83" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A83" s="8">
@@ -3877,7 +3891,7 @@
       <c r="C83" s="8">
         <v>2</v>
       </c>
-      <c r="D83" s="22" t="b">
+      <c r="D83" s="23" t="b">
         <v>1</v>
       </c>
       <c r="E83" s="8">
@@ -3887,11 +3901,11 @@
       <c r="G83" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H83" s="23"/>
-      <c r="I83" s="24"/>
-      <c r="J83" s="24"/>
-      <c r="K83" s="24"/>
-      <c r="L83" s="24"/>
+      <c r="H83" s="24"/>
+      <c r="I83" s="25"/>
+      <c r="J83" s="25"/>
+      <c r="K83" s="25"/>
+      <c r="L83" s="25"/>
     </row>
     <row r="84" customHeight="1" spans="1:12">
       <c r="A84" s="8">
@@ -3903,7 +3917,7 @@
       <c r="C84" s="1">
         <v>1</v>
       </c>
-      <c r="D84" s="22" t="b">
+      <c r="D84" s="23" t="b">
         <v>1</v>
       </c>
       <c r="E84" s="1">
@@ -3923,7 +3937,7 @@
       <c r="C85" s="1">
         <v>1</v>
       </c>
-      <c r="D85" s="22" t="b">
+      <c r="D85" s="23" t="b">
         <v>1</v>
       </c>
       <c r="E85" s="1">
@@ -3943,7 +3957,7 @@
       <c r="C86" s="1">
         <v>1</v>
       </c>
-      <c r="D86" s="22" t="b">
+      <c r="D86" s="23" t="b">
         <v>1</v>
       </c>
       <c r="E86" s="1">
@@ -3963,7 +3977,7 @@
       <c r="C87" s="1">
         <v>1</v>
       </c>
-      <c r="D87" s="22" t="b">
+      <c r="D87" s="23" t="b">
         <v>1</v>
       </c>
       <c r="E87" s="1">
@@ -3983,7 +3997,7 @@
       <c r="C88" s="1">
         <v>1</v>
       </c>
-      <c r="D88" s="22" t="b">
+      <c r="D88" s="23" t="b">
         <v>1</v>
       </c>
       <c r="E88" s="1">
@@ -4003,7 +4017,7 @@
       <c r="C89" s="1">
         <v>1</v>
       </c>
-      <c r="D89" s="22" t="b">
+      <c r="D89" s="23" t="b">
         <v>1</v>
       </c>
       <c r="E89" s="1">
@@ -4023,11 +4037,8 @@
       <c r="C90" s="1">
         <v>1</v>
       </c>
-      <c r="D90" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E90" s="1">
-        <v>4055348</v>
+      <c r="D90" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="G90" s="8" t="s">
         <v>80</v>
@@ -4043,7 +4054,7 @@
       <c r="C91" s="1">
         <v>1</v>
       </c>
-      <c r="D91" s="22" t="b">
+      <c r="D91" s="23" t="b">
         <v>1</v>
       </c>
       <c r="E91" s="1">
@@ -4053,25 +4064,31 @@
         <v>80</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="1:12">
-      <c r="A92" s="8">
+    <row r="92" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A92" s="26">
         <v>2210</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92" s="9">
         <v>10</v>
       </c>
-      <c r="C92" s="1">
-        <v>1</v>
-      </c>
-      <c r="D92" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" s="1">
+      <c r="C92" s="9">
+        <v>1</v>
+      </c>
+      <c r="D92" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="9">
         <v>4055350</v>
       </c>
-      <c r="G92" s="8" t="s">
+      <c r="F92" s="9"/>
+      <c r="G92" s="26" t="s">
         <v>80</v>
       </c>
+      <c r="H92" s="27"/>
+      <c r="I92" s="27"/>
+      <c r="J92" s="27"/>
+      <c r="K92" s="27"/>
+      <c r="L92" s="27"/>
     </row>
     <row r="93" customHeight="1" spans="1:12">
       <c r="A93" s="8">
@@ -4083,7 +4100,7 @@
       <c r="C93" s="1">
         <v>1</v>
       </c>
-      <c r="D93" s="22" t="b">
+      <c r="D93" s="23" t="b">
         <v>1</v>
       </c>
       <c r="E93" s="1">
@@ -4103,11 +4120,8 @@
       <c r="C94" s="1">
         <v>1</v>
       </c>
-      <c r="D94" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E94" s="1">
-        <v>4055352</v>
+      <c r="D94" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="G94" s="8" t="s">
         <v>80</v>
@@ -4123,11 +4137,8 @@
       <c r="C95" s="1">
         <v>1</v>
       </c>
-      <c r="D95" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E95" s="1">
-        <v>4055353</v>
+      <c r="D95" s="23" t="b">
+        <v>1</v>
       </c>
       <c r="G95" s="8" t="s">
         <v>80</v>
@@ -4143,7 +4154,7 @@
       <c r="C96" s="1">
         <v>1</v>
       </c>
-      <c r="D96" s="22" t="b">
+      <c r="D96" s="23" t="b">
         <v>1</v>
       </c>
       <c r="E96" s="1">

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -242,16 +242,16 @@
     <t>先前往SLOT区试试手气</t>
   </si>
   <si>
-    <t>点击旋转按钮，赢取大奖</t>
-  </si>
-  <si>
-    <t>真的爆大奖了</t>
-  </si>
-  <si>
-    <t>恭喜您，我们将聘请您成为GECA黄金星娱乐城经理人</t>
-  </si>
-  <si>
-    <t>很高兴加入集团，将娱乐城打造为世界第一城</t>
+    <t>点击&lt;color=#00bfff&gt;旋转&lt;/color&gt;按钮，赢得大奖</t>
+  </si>
+  <si>
+    <t>哇，真的爆大奖了</t>
+  </si>
+  <si>
+    <t>恭喜！将聘请您成为GECA黄金星娱乐城经理人</t>
+  </si>
+  <si>
+    <t>很高兴加入，我会把娱乐城发展为全球第一城</t>
   </si>
   <si>
     <t>持续研发游戏、扩建新区，提升收益发展娱乐城</t>
@@ -496,7 +496,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,6 +531,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0" tint="-0.25"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -549,6 +555,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.25"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1054,137 +1067,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1203,7 +1216,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1212,10 +1228,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1233,40 +1249,49 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1763,40 +1788,40 @@
     <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="85.2916666666667" style="10" customWidth="1"/>
+    <col min="8" max="8" width="85.2916666666667" style="11" customWidth="1"/>
     <col min="13" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10"/>
+      <c r="H1" s="11"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
       <c r="L1"/>
     </row>
     <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1808,2107 +1833,2107 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="10"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="11"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="10"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="11"/>
       <c r="I3"/>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="13"/>
-      <c r="H4" s="10"/>
+      <c r="A4" s="14"/>
+      <c r="H4" s="11"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
     </row>
     <row r="5" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="14">
+      <c r="A5" s="15">
         <v>1001</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="15">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="16">
         <v>4055101</v>
       </c>
-      <c r="F5" s="15"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <v>1002</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="15">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="16">
         <v>4055102</v>
       </c>
-      <c r="F6" s="15"/>
+      <c r="F6" s="16"/>
       <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <v>1003</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="15">
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="16">
         <v>4055103</v>
       </c>
-      <c r="F7" s="15"/>
+      <c r="F7" s="16"/>
       <c r="G7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="14">
+      <c r="A8" s="15">
         <v>1004</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="15">
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="16">
         <v>4055104</v>
       </c>
-      <c r="F8" s="15"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <v>1005</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="16">
+        <v>4055109</v>
+      </c>
+      <c r="F9" s="16"/>
       <c r="G9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
+      <c r="H9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <v>1006</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="15">
-        <v>4055106</v>
-      </c>
-      <c r="F10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="16">
+        <v>4055105</v>
+      </c>
+      <c r="F10" s="16"/>
       <c r="G10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
+      <c r="H10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <v>1007</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="15">
-        <v>4055107</v>
-      </c>
-      <c r="F11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="16">
+        <v>4055106</v>
+      </c>
+      <c r="F11" s="16"/>
       <c r="G11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
+      <c r="H11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="14">
+      <c r="A12" s="15">
         <v>1008</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="16">
+        <v>4055107</v>
+      </c>
+      <c r="F12" s="16"/>
       <c r="G12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
+      <c r="H12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="14">
+      <c r="A13" s="15">
         <v>1009</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="16">
+        <v>4055108</v>
+      </c>
+      <c r="F13" s="16"/>
       <c r="G13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-    </row>
-    <row r="14" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="14">
+      <c r="H13" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+    </row>
+    <row r="14" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A14" s="19">
         <v>1010</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="4" t="s">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="10"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-    </row>
-    <row r="15" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="14">
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+    </row>
+    <row r="15" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A15" s="19">
         <v>1011</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>4055111</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="4" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-    </row>
-    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="14">
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+    </row>
+    <row r="16" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A16" s="19">
         <v>1012</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>4055112</v>
-      </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="4" t="s">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-    </row>
-    <row r="17" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="14">
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+    </row>
+    <row r="17" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A17" s="19">
         <v>1013</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="15">
-        <v>4055113</v>
-      </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="4" t="s">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-    </row>
-    <row r="18" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="18">
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+    </row>
+    <row r="18" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A18" s="22">
         <v>1201</v>
       </c>
-      <c r="B18" s="16">
-        <v>2</v>
-      </c>
-      <c r="C18" s="16">
-        <v>2</v>
-      </c>
-      <c r="D18" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="16">
+      <c r="B18" s="17">
+        <v>2</v>
+      </c>
+      <c r="C18" s="17">
+        <v>2</v>
+      </c>
+      <c r="D18" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="17">
         <v>4055121</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="19" t="s">
+      <c r="F18" s="17"/>
+      <c r="G18" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="18">
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+    </row>
+    <row r="19" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A19" s="22">
         <v>1202</v>
       </c>
-      <c r="B19" s="16">
-        <v>2</v>
-      </c>
-      <c r="C19" s="16">
-        <v>2</v>
-      </c>
-      <c r="D19" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="16">
+      <c r="B19" s="17">
+        <v>2</v>
+      </c>
+      <c r="C19" s="17">
+        <v>2</v>
+      </c>
+      <c r="D19" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="17">
         <v>4055122</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="19" t="s">
+      <c r="F19" s="17"/>
+      <c r="G19" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-    </row>
-    <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="18">
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+    </row>
+    <row r="20" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A20" s="22">
         <v>1203</v>
       </c>
-      <c r="B20" s="16">
-        <v>2</v>
-      </c>
-      <c r="C20" s="16">
-        <v>1</v>
-      </c>
-      <c r="D20" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="16">
+      <c r="B20" s="17">
+        <v>2</v>
+      </c>
+      <c r="C20" s="17">
+        <v>1</v>
+      </c>
+      <c r="D20" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="17">
         <v>4055123</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="19" t="s">
+      <c r="F20" s="17"/>
+      <c r="G20" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-    </row>
-    <row r="21" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="18">
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+    </row>
+    <row r="21" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A21" s="22">
         <v>1204</v>
       </c>
-      <c r="B21" s="16">
-        <v>2</v>
-      </c>
-      <c r="C21" s="16">
-        <v>1</v>
-      </c>
-      <c r="D21" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="16">
+      <c r="B21" s="17">
+        <v>2</v>
+      </c>
+      <c r="C21" s="17">
+        <v>1</v>
+      </c>
+      <c r="D21" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="17">
         <v>4055124</v>
       </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="19" t="s">
+      <c r="F21" s="17"/>
+      <c r="G21" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-    </row>
-    <row r="22" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="14">
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+    </row>
+    <row r="22" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A22" s="15">
         <v>1301</v>
       </c>
-      <c r="B22" s="15">
-        <v>2</v>
-      </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
+      <c r="B22" s="16">
+        <v>2</v>
+      </c>
+      <c r="C22" s="16">
+        <v>1</v>
+      </c>
+      <c r="D22" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="16">
         <v>4055141</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="20" t="s">
+      <c r="F22" s="16"/>
+      <c r="G22" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-    </row>
-    <row r="23" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A23" s="14">
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+    </row>
+    <row r="23" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A23" s="15">
         <v>1302</v>
       </c>
-      <c r="B23" s="15">
-        <v>2</v>
-      </c>
-      <c r="C23" s="15">
-        <v>1</v>
-      </c>
-      <c r="D23" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
+      <c r="B23" s="16">
+        <v>2</v>
+      </c>
+      <c r="C23" s="16">
+        <v>1</v>
+      </c>
+      <c r="D23" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="16">
         <v>4055142</v>
       </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="20" t="s">
+      <c r="F23" s="16"/>
+      <c r="G23" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-    </row>
-    <row r="24" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A24" s="14">
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+    </row>
+    <row r="24" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A24" s="15">
         <v>1303</v>
       </c>
-      <c r="B24" s="15">
-        <v>2</v>
-      </c>
-      <c r="C24" s="15">
-        <v>1</v>
-      </c>
-      <c r="D24" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="15">
+      <c r="B24" s="16">
+        <v>2</v>
+      </c>
+      <c r="C24" s="16">
+        <v>1</v>
+      </c>
+      <c r="D24" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="16">
         <v>4055143</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="20" t="s">
+      <c r="F24" s="16"/>
+      <c r="G24" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-    </row>
-    <row r="25" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="14">
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+    </row>
+    <row r="25" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="15">
         <v>1304</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15">
-        <v>1</v>
-      </c>
-      <c r="D25" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="20" t="s">
+      <c r="B25" s="16"/>
+      <c r="C25" s="16">
+        <v>1</v>
+      </c>
+      <c r="D25" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-    </row>
-    <row r="26" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="14">
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+    </row>
+    <row r="26" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A26" s="15">
         <v>1305</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15">
-        <v>1</v>
-      </c>
-      <c r="D26" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="20" t="s">
+      <c r="B26" s="16"/>
+      <c r="C26" s="16">
+        <v>1</v>
+      </c>
+      <c r="D26" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-    </row>
-    <row r="27" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="18">
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+    </row>
+    <row r="27" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A27" s="22">
         <v>1401</v>
       </c>
-      <c r="B27" s="16">
-        <v>2</v>
-      </c>
-      <c r="C27" s="16">
-        <v>1</v>
-      </c>
-      <c r="D27" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="16">
+      <c r="B27" s="17">
+        <v>2</v>
+      </c>
+      <c r="C27" s="17">
+        <v>1</v>
+      </c>
+      <c r="D27" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="17">
         <v>4055161</v>
       </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="19" t="s">
+      <c r="F27" s="17"/>
+      <c r="G27" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-    </row>
-    <row r="28" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="18">
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+    </row>
+    <row r="28" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A28" s="22">
         <v>1402</v>
       </c>
-      <c r="B28" s="16">
-        <v>2</v>
-      </c>
-      <c r="C28" s="16">
-        <v>1</v>
-      </c>
-      <c r="D28" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="16">
+      <c r="B28" s="17">
+        <v>2</v>
+      </c>
+      <c r="C28" s="17">
+        <v>1</v>
+      </c>
+      <c r="D28" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="17">
         <v>4055162</v>
       </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="19" t="s">
+      <c r="F28" s="17"/>
+      <c r="G28" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-    </row>
-    <row r="29" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="18">
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+    </row>
+    <row r="29" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A29" s="22">
         <v>1403</v>
       </c>
-      <c r="B29" s="16">
-        <v>2</v>
-      </c>
-      <c r="C29" s="16">
-        <v>1</v>
-      </c>
-      <c r="D29" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="16">
+      <c r="B29" s="17">
+        <v>2</v>
+      </c>
+      <c r="C29" s="17">
+        <v>1</v>
+      </c>
+      <c r="D29" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="17">
         <v>4055163</v>
       </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="19" t="s">
+      <c r="F29" s="17"/>
+      <c r="G29" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-    </row>
-    <row r="30" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="18">
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+    </row>
+    <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A30" s="22">
         <v>1404</v>
       </c>
-      <c r="B30" s="16">
-        <v>2</v>
-      </c>
-      <c r="C30" s="16">
-        <v>1</v>
-      </c>
-      <c r="D30" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="16">
+      <c r="B30" s="17">
+        <v>2</v>
+      </c>
+      <c r="C30" s="17">
+        <v>1</v>
+      </c>
+      <c r="D30" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="17">
         <v>4055164</v>
       </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="19" t="s">
+      <c r="F30" s="17"/>
+      <c r="G30" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-    </row>
-    <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="18">
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+    </row>
+    <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A31" s="22">
         <v>1405</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16">
-        <v>1</v>
-      </c>
-      <c r="D31" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="19" t="s">
+      <c r="B31" s="17"/>
+      <c r="C31" s="17">
+        <v>1</v>
+      </c>
+      <c r="D31" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-    </row>
-    <row r="32" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="18">
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+    </row>
+    <row r="32" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A32" s="22">
         <v>1406</v>
       </c>
-      <c r="B32" s="16">
-        <v>2</v>
-      </c>
-      <c r="C32" s="16">
-        <v>1</v>
-      </c>
-      <c r="D32" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="16">
+      <c r="B32" s="17">
+        <v>2</v>
+      </c>
+      <c r="C32" s="17">
+        <v>1</v>
+      </c>
+      <c r="D32" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="17">
         <v>4055165</v>
       </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="19" t="s">
+      <c r="F32" s="17"/>
+      <c r="G32" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-    </row>
-    <row r="33" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="14">
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+    </row>
+    <row r="33" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A33" s="15">
         <v>1501</v>
       </c>
-      <c r="B33" s="15">
-        <v>2</v>
-      </c>
-      <c r="C33" s="15">
-        <v>1</v>
-      </c>
-      <c r="D33" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
+      <c r="B33" s="16">
+        <v>2</v>
+      </c>
+      <c r="C33" s="16">
+        <v>1</v>
+      </c>
+      <c r="D33" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="16">
         <v>4055181</v>
       </c>
-      <c r="F33" s="15"/>
-      <c r="G33" s="20" t="s">
+      <c r="F33" s="16"/>
+      <c r="G33" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-    </row>
-    <row r="34" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="14">
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+    </row>
+    <row r="34" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A34" s="15">
         <v>1502</v>
       </c>
-      <c r="B34" s="15">
-        <v>2</v>
-      </c>
-      <c r="C34" s="15">
-        <v>1</v>
-      </c>
-      <c r="D34" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="15">
+      <c r="B34" s="16">
+        <v>2</v>
+      </c>
+      <c r="C34" s="16">
+        <v>1</v>
+      </c>
+      <c r="D34" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="16">
         <v>4055182</v>
       </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="20" t="s">
+      <c r="F34" s="16"/>
+      <c r="G34" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-    </row>
-    <row r="35" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="14">
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+    </row>
+    <row r="35" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A35" s="15">
         <v>1503</v>
       </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15">
-        <v>1</v>
-      </c>
-      <c r="D35" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="20" t="s">
+      <c r="B35" s="16"/>
+      <c r="C35" s="16">
+        <v>1</v>
+      </c>
+      <c r="D35" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-    </row>
-    <row r="36" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="14">
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+    </row>
+    <row r="36" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A36" s="15">
         <v>1504</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15">
-        <v>1</v>
-      </c>
-      <c r="D36" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="20" t="s">
+      <c r="B36" s="16"/>
+      <c r="C36" s="16">
+        <v>1</v>
+      </c>
+      <c r="D36" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-    </row>
-    <row r="37" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="18">
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+    </row>
+    <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A37" s="22">
         <v>1601</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16">
-        <v>1</v>
-      </c>
-      <c r="D37" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="19" t="s">
+      <c r="B37" s="17"/>
+      <c r="C37" s="17">
+        <v>1</v>
+      </c>
+      <c r="D37" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-    </row>
-    <row r="38" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="18">
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+    </row>
+    <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A38" s="22">
         <v>1602</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16">
-        <v>1</v>
-      </c>
-      <c r="D38" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="19" t="s">
+      <c r="B38" s="17"/>
+      <c r="C38" s="17">
+        <v>1</v>
+      </c>
+      <c r="D38" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-    </row>
-    <row r="39" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A39" s="18">
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+    </row>
+    <row r="39" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A39" s="22">
         <v>1603</v>
       </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16">
-        <v>1</v>
-      </c>
-      <c r="D39" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="16">
+      <c r="B39" s="17"/>
+      <c r="C39" s="17">
+        <v>1</v>
+      </c>
+      <c r="D39" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="17">
         <v>4055203</v>
       </c>
-      <c r="F39" s="15"/>
-      <c r="G39" s="19" t="s">
+      <c r="F39" s="16"/>
+      <c r="G39" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-    </row>
-    <row r="40" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="18">
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+    </row>
+    <row r="40" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A40" s="22">
         <v>1604</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16">
-        <v>1</v>
-      </c>
-      <c r="D40" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="19" t="s">
+      <c r="B40" s="17"/>
+      <c r="C40" s="17">
+        <v>1</v>
+      </c>
+      <c r="D40" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-    </row>
-    <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="18">
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+    </row>
+    <row r="41" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A41" s="22">
         <v>1605</v>
       </c>
-      <c r="B41" s="16">
-        <v>2</v>
-      </c>
-      <c r="C41" s="16">
-        <v>1</v>
-      </c>
-      <c r="D41" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="16">
+      <c r="B41" s="17">
+        <v>2</v>
+      </c>
+      <c r="C41" s="17">
+        <v>1</v>
+      </c>
+      <c r="D41" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="17">
         <v>4055204</v>
       </c>
-      <c r="F41" s="15"/>
-      <c r="G41" s="19" t="s">
+      <c r="F41" s="16"/>
+      <c r="G41" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-    </row>
-    <row r="42" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="18">
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+    </row>
+    <row r="42" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A42" s="22">
         <v>1606</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16">
-        <v>1</v>
-      </c>
-      <c r="D42" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="19" t="s">
+      <c r="B42" s="17"/>
+      <c r="C42" s="17">
+        <v>1</v>
+      </c>
+      <c r="D42" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-    </row>
-    <row r="43" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="18">
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+    </row>
+    <row r="43" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A43" s="22">
         <v>1607</v>
       </c>
-      <c r="B43" s="16">
-        <v>2</v>
-      </c>
-      <c r="C43" s="16">
-        <v>1</v>
-      </c>
-      <c r="D43" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="19" t="s">
+      <c r="B43" s="17">
+        <v>2</v>
+      </c>
+      <c r="C43" s="17">
+        <v>1</v>
+      </c>
+      <c r="D43" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-    </row>
-    <row r="44" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="18">
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+    </row>
+    <row r="44" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A44" s="22">
         <v>1608</v>
       </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16">
-        <v>1</v>
-      </c>
-      <c r="D44" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="16">
+      <c r="B44" s="17"/>
+      <c r="C44" s="17">
+        <v>1</v>
+      </c>
+      <c r="D44" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="17">
         <v>4055205</v>
       </c>
-      <c r="F44" s="15"/>
-      <c r="G44" s="19" t="s">
+      <c r="F44" s="16"/>
+      <c r="G44" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-    </row>
-    <row r="45" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="18">
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+    </row>
+    <row r="45" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A45" s="22">
         <v>1609</v>
       </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16">
-        <v>1</v>
-      </c>
-      <c r="D45" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="16">
+      <c r="B45" s="17"/>
+      <c r="C45" s="17">
+        <v>1</v>
+      </c>
+      <c r="D45" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="17">
         <v>4055206</v>
       </c>
-      <c r="F45" s="15"/>
-      <c r="G45" s="19" t="s">
+      <c r="F45" s="16"/>
+      <c r="G45" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-    </row>
-    <row r="46" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="18">
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+    </row>
+    <row r="46" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A46" s="22">
         <v>1610</v>
       </c>
-      <c r="B46" s="16">
-        <v>2</v>
-      </c>
-      <c r="C46" s="16">
-        <v>1</v>
-      </c>
-      <c r="D46" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="16">
+      <c r="B46" s="17">
+        <v>2</v>
+      </c>
+      <c r="C46" s="17">
+        <v>1</v>
+      </c>
+      <c r="D46" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="17">
         <v>4055207</v>
       </c>
-      <c r="F46" s="15"/>
-      <c r="G46" s="19" t="s">
+      <c r="F46" s="16"/>
+      <c r="G46" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H46" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-    </row>
-    <row r="47" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="18">
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+    </row>
+    <row r="47" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A47" s="22">
         <v>1611</v>
       </c>
-      <c r="B47" s="16">
-        <v>2</v>
-      </c>
-      <c r="C47" s="16">
-        <v>1</v>
-      </c>
-      <c r="D47" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="16">
+      <c r="B47" s="17">
+        <v>2</v>
+      </c>
+      <c r="C47" s="17">
+        <v>1</v>
+      </c>
+      <c r="D47" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="17">
         <v>4055208</v>
       </c>
-      <c r="F47" s="15"/>
-      <c r="G47" s="19" t="s">
+      <c r="F47" s="16"/>
+      <c r="G47" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-    </row>
-    <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="18">
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+    </row>
+    <row r="48" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="22">
         <v>1612</v>
       </c>
-      <c r="B48" s="16">
-        <v>2</v>
-      </c>
-      <c r="C48" s="16">
-        <v>1</v>
-      </c>
-      <c r="D48" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="16">
+      <c r="B48" s="17">
+        <v>2</v>
+      </c>
+      <c r="C48" s="17">
+        <v>1</v>
+      </c>
+      <c r="D48" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="17">
         <v>4055209</v>
       </c>
-      <c r="F48" s="15"/>
-      <c r="G48" s="19" t="s">
+      <c r="F48" s="16"/>
+      <c r="G48" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H48" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-    </row>
-    <row r="49" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="14">
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+    </row>
+    <row r="49" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A49" s="15">
         <v>1701</v>
       </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15">
-        <v>1</v>
-      </c>
-      <c r="D49" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="20" t="s">
+      <c r="B49" s="16"/>
+      <c r="C49" s="16">
+        <v>1</v>
+      </c>
+      <c r="D49" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-    </row>
-    <row r="50" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A50" s="14">
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+    </row>
+    <row r="50" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A50" s="15">
         <v>1702</v>
       </c>
-      <c r="C50" s="15">
-        <v>1</v>
-      </c>
-      <c r="D50" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="15"/>
-      <c r="G50" s="20" t="s">
+      <c r="C50" s="16">
+        <v>1</v>
+      </c>
+      <c r="D50" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="16"/>
+      <c r="G50" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="H50" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-    </row>
-    <row r="51" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A51" s="14">
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+    </row>
+    <row r="51" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A51" s="15">
         <v>1703</v>
       </c>
-      <c r="B51" s="15">
-        <v>2</v>
-      </c>
-      <c r="C51" s="15">
-        <v>1</v>
-      </c>
-      <c r="D51" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="15">
+      <c r="B51" s="16">
+        <v>2</v>
+      </c>
+      <c r="C51" s="16">
+        <v>1</v>
+      </c>
+      <c r="D51" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="16">
         <v>4055222</v>
       </c>
-      <c r="F51" s="15"/>
-      <c r="G51" s="20" t="s">
+      <c r="F51" s="16"/>
+      <c r="G51" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-    </row>
-    <row r="52" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A52" s="14">
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="18"/>
+    </row>
+    <row r="52" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A52" s="15">
         <v>1704</v>
       </c>
-      <c r="B52" s="15">
-        <v>2</v>
-      </c>
-      <c r="C52" s="15">
-        <v>1</v>
-      </c>
-      <c r="D52" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="15">
+      <c r="B52" s="16">
+        <v>2</v>
+      </c>
+      <c r="C52" s="16">
+        <v>1</v>
+      </c>
+      <c r="D52" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="16">
         <v>4055223</v>
       </c>
-      <c r="F52" s="15"/>
-      <c r="G52" s="20" t="s">
+      <c r="F52" s="16"/>
+      <c r="G52" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H52" s="10" t="s">
+      <c r="H52" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-    </row>
-    <row r="53" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A53" s="14">
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+    </row>
+    <row r="53" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A53" s="15">
         <v>1705</v>
       </c>
-      <c r="B53" s="15">
-        <v>2</v>
-      </c>
-      <c r="C53" s="15">
-        <v>1</v>
-      </c>
-      <c r="D53" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="15">
+      <c r="B53" s="16">
+        <v>2</v>
+      </c>
+      <c r="C53" s="16">
+        <v>1</v>
+      </c>
+      <c r="D53" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="16">
         <v>4055224</v>
       </c>
-      <c r="F53" s="15"/>
-      <c r="G53" s="20" t="s">
+      <c r="F53" s="16"/>
+      <c r="G53" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="H53" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-    </row>
-    <row r="54" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A54" s="14">
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+    </row>
+    <row r="54" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A54" s="15">
         <v>1706</v>
       </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15">
-        <v>1</v>
-      </c>
-      <c r="D54" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="20" t="s">
+      <c r="B54" s="16"/>
+      <c r="C54" s="16">
+        <v>1</v>
+      </c>
+      <c r="D54" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H54" s="10" t="s">
+      <c r="H54" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-    </row>
-    <row r="55" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A55" s="14">
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+    </row>
+    <row r="55" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A55" s="15">
         <v>1707</v>
       </c>
-      <c r="B55" s="15">
-        <v>2</v>
-      </c>
-      <c r="C55" s="15">
-        <v>1</v>
-      </c>
-      <c r="D55" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="15">
+      <c r="B55" s="16">
+        <v>2</v>
+      </c>
+      <c r="C55" s="16">
+        <v>1</v>
+      </c>
+      <c r="D55" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="16">
         <v>4055225</v>
       </c>
-      <c r="F55" s="15"/>
-      <c r="G55" s="20" t="s">
+      <c r="F55" s="16"/>
+      <c r="G55" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-    </row>
-    <row r="56" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A56" s="14">
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+    </row>
+    <row r="56" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A56" s="15">
         <v>1708</v>
       </c>
-      <c r="B56" s="15">
-        <v>2</v>
-      </c>
-      <c r="C56" s="15">
-        <v>1</v>
-      </c>
-      <c r="D56" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="15">
+      <c r="B56" s="16">
+        <v>2</v>
+      </c>
+      <c r="C56" s="16">
+        <v>1</v>
+      </c>
+      <c r="D56" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="16">
         <v>4055226</v>
       </c>
-      <c r="F56" s="15"/>
-      <c r="G56" s="20" t="s">
+      <c r="F56" s="16"/>
+      <c r="G56" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H56" s="10" t="s">
+      <c r="H56" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-    </row>
-    <row r="57" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A57" s="14">
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+    </row>
+    <row r="57" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A57" s="15">
         <v>1709</v>
       </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15">
-        <v>1</v>
-      </c>
-      <c r="D57" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="20" t="s">
+      <c r="B57" s="16"/>
+      <c r="C57" s="16">
+        <v>1</v>
+      </c>
+      <c r="D57" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="H57" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-    </row>
-    <row r="58" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A58" s="14">
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
+    </row>
+    <row r="58" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A58" s="15">
         <v>1710</v>
       </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15">
-        <v>1</v>
-      </c>
-      <c r="D58" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="20" t="s">
+      <c r="B58" s="16"/>
+      <c r="C58" s="16">
+        <v>1</v>
+      </c>
+      <c r="D58" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H58" s="10" t="s">
+      <c r="H58" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-    </row>
-    <row r="59" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="14">
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="18"/>
+    </row>
+    <row r="59" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A59" s="15">
         <v>1711</v>
       </c>
-      <c r="B59" s="15">
-        <v>2</v>
-      </c>
-      <c r="C59" s="15">
-        <v>1</v>
-      </c>
-      <c r="D59" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="15">
+      <c r="B59" s="16">
+        <v>2</v>
+      </c>
+      <c r="C59" s="16">
+        <v>1</v>
+      </c>
+      <c r="D59" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="16">
         <v>4055227</v>
       </c>
-      <c r="F59" s="15"/>
-      <c r="G59" s="20" t="s">
+      <c r="F59" s="16"/>
+      <c r="G59" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H59" s="10" t="s">
+      <c r="H59" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-    </row>
-    <row r="60" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="14">
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
+      <c r="L59" s="18"/>
+    </row>
+    <row r="60" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A60" s="15">
         <v>1712</v>
       </c>
-      <c r="B60" s="15">
-        <v>2</v>
-      </c>
-      <c r="C60" s="15">
-        <v>1</v>
-      </c>
-      <c r="D60" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="15">
+      <c r="B60" s="16">
+        <v>2</v>
+      </c>
+      <c r="C60" s="16">
+        <v>1</v>
+      </c>
+      <c r="D60" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="16">
         <v>4055228</v>
       </c>
-      <c r="F60" s="15"/>
-      <c r="G60" s="20" t="s">
+      <c r="F60" s="16"/>
+      <c r="G60" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H60" s="10" t="s">
+      <c r="H60" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
-    </row>
-    <row r="61" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="18">
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+    </row>
+    <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A61" s="22">
         <v>1801</v>
       </c>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16">
-        <v>1</v>
-      </c>
-      <c r="D61" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="19" t="s">
+      <c r="B61" s="17"/>
+      <c r="C61" s="17">
+        <v>1</v>
+      </c>
+      <c r="D61" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="H61" s="10" t="s">
+      <c r="H61" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-    </row>
-    <row r="62" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A62" s="18">
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+    </row>
+    <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A62" s="22">
         <v>1802</v>
       </c>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16">
-        <v>1</v>
-      </c>
-      <c r="D62" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="19" t="s">
+      <c r="B62" s="17"/>
+      <c r="C62" s="17">
+        <v>1</v>
+      </c>
+      <c r="D62" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="H62" s="10" t="s">
+      <c r="H62" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
-    </row>
-    <row r="63" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A63" s="18">
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+    </row>
+    <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A63" s="22">
         <v>1803</v>
       </c>
-      <c r="B63" s="16">
-        <v>2</v>
-      </c>
-      <c r="C63" s="16">
-        <v>1</v>
-      </c>
-      <c r="D63" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="16">
+      <c r="B63" s="17">
+        <v>2</v>
+      </c>
+      <c r="C63" s="17">
+        <v>1</v>
+      </c>
+      <c r="D63" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="17">
         <v>4055243</v>
       </c>
-      <c r="F63" s="16"/>
-      <c r="G63" s="19" t="s">
+      <c r="F63" s="17"/>
+      <c r="G63" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="H63" s="10" t="s">
+      <c r="H63" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="10"/>
-    </row>
-    <row r="64" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A64" s="18">
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="11"/>
+    </row>
+    <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A64" s="22">
         <v>1804</v>
       </c>
-      <c r="B64" s="16">
-        <v>2</v>
-      </c>
-      <c r="C64" s="16">
-        <v>1</v>
-      </c>
-      <c r="D64" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="16">
+      <c r="B64" s="17">
+        <v>2</v>
+      </c>
+      <c r="C64" s="17">
+        <v>1</v>
+      </c>
+      <c r="D64" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="17">
         <v>4055244</v>
       </c>
-      <c r="F64" s="16"/>
-      <c r="G64" s="19" t="s">
+      <c r="F64" s="17"/>
+      <c r="G64" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="H64" s="10" t="s">
+      <c r="H64" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="10"/>
-    </row>
-    <row r="65" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A65" s="18">
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="11"/>
+    </row>
+    <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A65" s="22">
         <v>1805</v>
       </c>
-      <c r="B65" s="16">
-        <v>2</v>
-      </c>
-      <c r="C65" s="16">
-        <v>1</v>
-      </c>
-      <c r="D65" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="16">
+      <c r="B65" s="17">
+        <v>2</v>
+      </c>
+      <c r="C65" s="17">
+        <v>1</v>
+      </c>
+      <c r="D65" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="17">
         <v>4055245</v>
       </c>
-      <c r="F65" s="16"/>
-      <c r="G65" s="19" t="s">
+      <c r="F65" s="17"/>
+      <c r="G65" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="H65" s="10" t="s">
+      <c r="H65" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
-    </row>
-    <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="18">
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+    </row>
+    <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A66" s="22">
         <v>1806</v>
       </c>
-      <c r="B66" s="16">
-        <v>2</v>
-      </c>
-      <c r="C66" s="16">
-        <v>1</v>
-      </c>
-      <c r="D66" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="16">
+      <c r="B66" s="17">
+        <v>2</v>
+      </c>
+      <c r="C66" s="17">
+        <v>1</v>
+      </c>
+      <c r="D66" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="17">
         <v>4055246</v>
       </c>
-      <c r="F66" s="16"/>
-      <c r="G66" s="19" t="s">
+      <c r="F66" s="17"/>
+      <c r="G66" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="H66" s="10" t="s">
+      <c r="H66" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="10"/>
-    </row>
-    <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="18">
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+    </row>
+    <row r="67" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A67" s="22">
         <v>1807</v>
       </c>
-      <c r="B67" s="16">
-        <v>2</v>
-      </c>
-      <c r="C67" s="16">
-        <v>1</v>
-      </c>
-      <c r="D67" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="16">
+      <c r="B67" s="17">
+        <v>2</v>
+      </c>
+      <c r="C67" s="17">
+        <v>1</v>
+      </c>
+      <c r="D67" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="17">
         <v>4055247</v>
       </c>
-      <c r="F67" s="16"/>
-      <c r="G67" s="19" t="s">
+      <c r="F67" s="17"/>
+      <c r="G67" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="H67" s="10" t="s">
+      <c r="H67" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="10"/>
-    </row>
-    <row r="68" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="14">
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+    </row>
+    <row r="68" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A68" s="15">
         <v>1901</v>
       </c>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15">
-        <v>1</v>
-      </c>
-      <c r="D68" s="21" t="b">
+      <c r="B68" s="16"/>
+      <c r="C68" s="16">
+        <v>1</v>
+      </c>
+      <c r="D68" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="20" t="s">
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="H68" s="10" t="s">
+      <c r="H68" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I68" s="17"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="17"/>
-      <c r="L68" s="17"/>
-    </row>
-    <row r="69" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A69" s="14">
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="18"/>
+      <c r="L68" s="18"/>
+    </row>
+    <row r="69" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A69" s="15">
         <v>1902</v>
       </c>
-      <c r="B69" s="15">
-        <v>2</v>
-      </c>
-      <c r="C69" s="15">
-        <v>1</v>
-      </c>
-      <c r="D69" s="21" t="b">
+      <c r="B69" s="16">
+        <v>2</v>
+      </c>
+      <c r="C69" s="16">
+        <v>1</v>
+      </c>
+      <c r="D69" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E69" s="15">
+      <c r="E69" s="16">
         <v>4055263</v>
       </c>
-      <c r="F69" s="15"/>
-      <c r="G69" s="20" t="s">
+      <c r="F69" s="16"/>
+      <c r="G69" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="H69" s="10" t="s">
+      <c r="H69" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="I69" s="17"/>
-      <c r="J69" s="17"/>
-      <c r="K69" s="17"/>
-      <c r="L69" s="17"/>
-    </row>
-    <row r="70" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="14">
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
+      <c r="L69" s="18"/>
+    </row>
+    <row r="70" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A70" s="15">
         <v>1903</v>
       </c>
-      <c r="B70" s="15">
-        <v>2</v>
-      </c>
-      <c r="C70" s="15">
-        <v>1</v>
-      </c>
-      <c r="D70" s="21" t="b">
+      <c r="B70" s="16">
+        <v>2</v>
+      </c>
+      <c r="C70" s="16">
+        <v>1</v>
+      </c>
+      <c r="D70" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E70" s="15">
+      <c r="E70" s="16">
         <v>4055264</v>
       </c>
-      <c r="F70" s="15"/>
-      <c r="G70" s="20" t="s">
+      <c r="F70" s="16"/>
+      <c r="G70" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="H70" s="10" t="s">
+      <c r="H70" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="I70" s="17"/>
-      <c r="J70" s="17"/>
-      <c r="K70" s="17"/>
-      <c r="L70" s="17"/>
-    </row>
-    <row r="71" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="18">
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
+    </row>
+    <row r="71" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A71" s="22">
         <v>1981</v>
       </c>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16">
-        <v>1</v>
-      </c>
-      <c r="D71" s="21" t="b">
+      <c r="B71" s="17"/>
+      <c r="C71" s="17">
+        <v>1</v>
+      </c>
+      <c r="D71" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="19" t="s">
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="H71" s="10" t="s">
+      <c r="H71" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="10"/>
-    </row>
-    <row r="72" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="18">
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+    </row>
+    <row r="72" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A72" s="22">
         <v>1982</v>
       </c>
-      <c r="B72" s="16"/>
-      <c r="C72" s="16">
-        <v>1</v>
-      </c>
-      <c r="D72" s="21" t="b">
+      <c r="B72" s="17"/>
+      <c r="C72" s="17">
+        <v>1</v>
+      </c>
+      <c r="D72" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="19" t="s">
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="H72" s="10" t="s">
+      <c r="H72" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I72" s="10"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="10"/>
-      <c r="L72" s="10"/>
-    </row>
-    <row r="73" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A73" s="18">
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+    </row>
+    <row r="73" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A73" s="22">
         <v>1983</v>
       </c>
-      <c r="B73" s="16">
-        <v>2</v>
-      </c>
-      <c r="C73" s="16">
-        <v>1</v>
-      </c>
-      <c r="D73" s="21" t="b">
+      <c r="B73" s="17">
+        <v>2</v>
+      </c>
+      <c r="C73" s="17">
+        <v>1</v>
+      </c>
+      <c r="D73" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E73" s="16">
+      <c r="E73" s="17">
         <v>4055321</v>
       </c>
-      <c r="F73" s="16"/>
-      <c r="G73" s="19" t="s">
+      <c r="F73" s="17"/>
+      <c r="G73" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="H73" s="10" t="s">
+      <c r="H73" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10"/>
-      <c r="K73" s="10"/>
-      <c r="L73" s="10"/>
-    </row>
-    <row r="74" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="14">
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+    </row>
+    <row r="74" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A74" s="15">
         <v>2001</v>
       </c>
-      <c r="B74" s="15"/>
-      <c r="C74" s="15">
-        <v>1</v>
-      </c>
-      <c r="D74" s="21" t="b">
+      <c r="B74" s="16"/>
+      <c r="C74" s="16">
+        <v>1</v>
+      </c>
+      <c r="D74" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="20" t="s">
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H74" s="10" t="s">
+      <c r="H74" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I74" s="17"/>
-      <c r="J74" s="17"/>
-      <c r="K74" s="17"/>
-      <c r="L74" s="17"/>
-    </row>
-    <row r="75" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="14">
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="18"/>
+      <c r="L74" s="18"/>
+    </row>
+    <row r="75" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A75" s="15">
         <v>2002</v>
       </c>
-      <c r="B75" s="15">
-        <v>2</v>
-      </c>
-      <c r="C75" s="15">
-        <v>1</v>
-      </c>
-      <c r="D75" s="21" t="b">
+      <c r="B75" s="16">
+        <v>2</v>
+      </c>
+      <c r="C75" s="16">
+        <v>1</v>
+      </c>
+      <c r="D75" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E75" s="15">
+      <c r="E75" s="16">
         <v>4055281</v>
       </c>
-      <c r="F75" s="15"/>
-      <c r="G75" s="20" t="s">
+      <c r="F75" s="16"/>
+      <c r="G75" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H75" s="10" t="s">
+      <c r="H75" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="17"/>
-      <c r="J75" s="17"/>
-      <c r="K75" s="17"/>
-      <c r="L75" s="17"/>
-    </row>
-    <row r="76" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A76" s="14">
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="18"/>
+      <c r="L75" s="18"/>
+    </row>
+    <row r="76" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A76" s="15">
         <v>2003</v>
       </c>
-      <c r="B76" s="15">
-        <v>2</v>
-      </c>
-      <c r="C76" s="15">
-        <v>1</v>
-      </c>
-      <c r="D76" s="21" t="b">
+      <c r="B76" s="16">
+        <v>2</v>
+      </c>
+      <c r="C76" s="16">
+        <v>1</v>
+      </c>
+      <c r="D76" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E76" s="15">
+      <c r="E76" s="16">
         <v>4055282</v>
       </c>
-      <c r="F76" s="15"/>
-      <c r="G76" s="20" t="s">
+      <c r="F76" s="16"/>
+      <c r="G76" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H76" s="10" t="s">
+      <c r="H76" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="I76" s="17"/>
-      <c r="J76" s="17"/>
-      <c r="K76" s="17"/>
-      <c r="L76" s="17"/>
-    </row>
-    <row r="77" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A77" s="14">
+      <c r="I76" s="18"/>
+      <c r="J76" s="18"/>
+      <c r="K76" s="18"/>
+      <c r="L76" s="18"/>
+    </row>
+    <row r="77" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A77" s="15">
         <v>2004</v>
       </c>
-      <c r="B77" s="15">
-        <v>2</v>
-      </c>
-      <c r="C77" s="15">
-        <v>1</v>
-      </c>
-      <c r="D77" s="21" t="b">
+      <c r="B77" s="16">
+        <v>2</v>
+      </c>
+      <c r="C77" s="16">
+        <v>1</v>
+      </c>
+      <c r="D77" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E77" s="15">
+      <c r="E77" s="16">
         <v>4055283</v>
       </c>
-      <c r="F77" s="15"/>
-      <c r="G77" s="20" t="s">
+      <c r="F77" s="16"/>
+      <c r="G77" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H77" s="10" t="s">
+      <c r="H77" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
-      <c r="K77" s="17"/>
-      <c r="L77" s="17"/>
-    </row>
-    <row r="78" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A78" s="14">
+      <c r="I77" s="18"/>
+      <c r="J77" s="18"/>
+      <c r="K77" s="18"/>
+      <c r="L77" s="18"/>
+    </row>
+    <row r="78" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A78" s="15">
         <v>2005</v>
       </c>
-      <c r="B78" s="15">
-        <v>2</v>
-      </c>
-      <c r="C78" s="15">
-        <v>1</v>
-      </c>
-      <c r="D78" s="21" t="b">
+      <c r="B78" s="16">
+        <v>2</v>
+      </c>
+      <c r="C78" s="16">
+        <v>1</v>
+      </c>
+      <c r="D78" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E78" s="15">
+      <c r="E78" s="16">
         <v>4055284</v>
       </c>
-      <c r="F78" s="15"/>
-      <c r="G78" s="20" t="s">
+      <c r="F78" s="16"/>
+      <c r="G78" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H78" s="10" t="s">
+      <c r="H78" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="I78" s="17"/>
-      <c r="J78" s="17"/>
-      <c r="K78" s="17"/>
-      <c r="L78" s="17"/>
-    </row>
-    <row r="79" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="14">
+      <c r="I78" s="18"/>
+      <c r="J78" s="18"/>
+      <c r="K78" s="18"/>
+      <c r="L78" s="18"/>
+    </row>
+    <row r="79" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A79" s="15">
         <v>2006</v>
       </c>
-      <c r="B79" s="15">
-        <v>2</v>
-      </c>
-      <c r="C79" s="15">
-        <v>1</v>
-      </c>
-      <c r="D79" s="21" t="b">
+      <c r="B79" s="16">
+        <v>2</v>
+      </c>
+      <c r="C79" s="16">
+        <v>1</v>
+      </c>
+      <c r="D79" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E79" s="15">
+      <c r="E79" s="16">
         <v>4055285</v>
       </c>
-      <c r="F79" s="15"/>
-      <c r="G79" s="20" t="s">
+      <c r="F79" s="16"/>
+      <c r="G79" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H79" s="10" t="s">
+      <c r="H79" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="I79" s="17"/>
-      <c r="J79" s="17"/>
-      <c r="K79" s="17"/>
-      <c r="L79" s="17"/>
-    </row>
-    <row r="80" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="14">
+      <c r="I79" s="18"/>
+      <c r="J79" s="18"/>
+      <c r="K79" s="18"/>
+      <c r="L79" s="18"/>
+    </row>
+    <row r="80" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="15">
         <v>2007</v>
       </c>
-      <c r="B80" s="15">
-        <v>2</v>
-      </c>
-      <c r="C80" s="15">
-        <v>1</v>
-      </c>
-      <c r="D80" s="21" t="b">
+      <c r="B80" s="16">
+        <v>2</v>
+      </c>
+      <c r="C80" s="16">
+        <v>1</v>
+      </c>
+      <c r="D80" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E80" s="15">
+      <c r="E80" s="16">
         <v>4055286</v>
       </c>
-      <c r="F80" s="15"/>
-      <c r="G80" s="20" t="s">
+      <c r="F80" s="16"/>
+      <c r="G80" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H80" s="10" t="s">
+      <c r="H80" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="I80" s="17"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="17"/>
-      <c r="L80" s="17"/>
-    </row>
-    <row r="81" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="22">
+      <c r="I80" s="18"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="18"/>
+      <c r="L80" s="18"/>
+    </row>
+    <row r="81" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A81" s="26">
         <v>2101</v>
       </c>
-      <c r="B81" s="22">
-        <v>2</v>
-      </c>
-      <c r="C81" s="22">
-        <v>1</v>
-      </c>
-      <c r="D81" s="21" t="b">
+      <c r="B81" s="26">
+        <v>2</v>
+      </c>
+      <c r="C81" s="26">
+        <v>1</v>
+      </c>
+      <c r="D81" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E81" s="22">
+      <c r="E81" s="26">
         <v>4055301</v>
       </c>
-      <c r="F81" s="22"/>
-      <c r="G81" s="5" t="s">
+      <c r="F81" s="26"/>
+      <c r="G81" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H81" s="10" t="s">
+      <c r="H81" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="10"/>
-      <c r="L81" s="10"/>
-    </row>
-    <row r="82" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="22">
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11"/>
+    </row>
+    <row r="82" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A82" s="26">
         <v>2102</v>
       </c>
-      <c r="B82" s="22">
-        <v>1</v>
-      </c>
-      <c r="C82" s="22">
-        <v>1</v>
-      </c>
-      <c r="D82" s="21" t="b">
+      <c r="B82" s="26">
+        <v>1</v>
+      </c>
+      <c r="C82" s="26">
+        <v>1</v>
+      </c>
+      <c r="D82" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="E82" s="22">
+      <c r="E82" s="26">
         <v>4055303</v>
       </c>
-      <c r="F82" s="22"/>
-      <c r="G82" s="5" t="s">
+      <c r="F82" s="26"/>
+      <c r="G82" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H82" s="10" t="s">
+      <c r="H82" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="I82" s="10"/>
-      <c r="J82" s="10"/>
-      <c r="K82" s="10"/>
-      <c r="L82" s="10"/>
-    </row>
-    <row r="83" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A83" s="8">
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="11"/>
+      <c r="L82" s="11"/>
+    </row>
+    <row r="83" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A83" s="9">
         <v>2201</v>
       </c>
-      <c r="B83" s="8">
-        <v>1</v>
-      </c>
-      <c r="C83" s="8">
-        <v>2</v>
-      </c>
-      <c r="D83" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="8">
+      <c r="B83" s="9">
+        <v>1</v>
+      </c>
+      <c r="C83" s="9">
+        <v>2</v>
+      </c>
+      <c r="D83" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="9">
         <v>4055341</v>
       </c>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8" t="s">
+      <c r="F83" s="9"/>
+      <c r="G83" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="H83" s="24"/>
-      <c r="I83" s="25"/>
-      <c r="J83" s="25"/>
-      <c r="K83" s="25"/>
-      <c r="L83" s="25"/>
+      <c r="H83" s="28"/>
+      <c r="I83" s="29"/>
+      <c r="J83" s="29"/>
+      <c r="K83" s="29"/>
+      <c r="L83" s="29"/>
     </row>
     <row r="84" customHeight="1" spans="1:12">
-      <c r="A84" s="8">
+      <c r="A84" s="9">
         <v>2202</v>
       </c>
       <c r="B84" s="1">
@@ -3917,18 +3942,18 @@
       <c r="C84" s="1">
         <v>1</v>
       </c>
-      <c r="D84" s="23" t="b">
+      <c r="D84" s="27" t="b">
         <v>1</v>
       </c>
       <c r="E84" s="1">
         <v>4055342</v>
       </c>
-      <c r="G84" s="8" t="s">
+      <c r="G84" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:12">
-      <c r="A85" s="8">
+      <c r="A85" s="9">
         <v>2203</v>
       </c>
       <c r="B85" s="1">
@@ -3937,18 +3962,18 @@
       <c r="C85" s="1">
         <v>1</v>
       </c>
-      <c r="D85" s="23" t="b">
+      <c r="D85" s="27" t="b">
         <v>1</v>
       </c>
       <c r="E85" s="1">
         <v>4055343</v>
       </c>
-      <c r="G85" s="8" t="s">
+      <c r="G85" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:12">
-      <c r="A86" s="8">
+      <c r="A86" s="9">
         <v>2204</v>
       </c>
       <c r="B86" s="1">
@@ -3957,18 +3982,18 @@
       <c r="C86" s="1">
         <v>1</v>
       </c>
-      <c r="D86" s="23" t="b">
+      <c r="D86" s="27" t="b">
         <v>1</v>
       </c>
       <c r="E86" s="1">
         <v>4055344</v>
       </c>
-      <c r="G86" s="8" t="s">
+      <c r="G86" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:12">
-      <c r="A87" s="8">
+      <c r="A87" s="9">
         <v>2205</v>
       </c>
       <c r="B87" s="1">
@@ -3977,18 +4002,18 @@
       <c r="C87" s="1">
         <v>1</v>
       </c>
-      <c r="D87" s="23" t="b">
+      <c r="D87" s="27" t="b">
         <v>1</v>
       </c>
       <c r="E87" s="1">
         <v>4055345</v>
       </c>
-      <c r="G87" s="8" t="s">
+      <c r="G87" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:12">
-      <c r="A88" s="8">
+      <c r="A88" s="9">
         <v>2206</v>
       </c>
       <c r="B88" s="1">
@@ -3997,18 +4022,18 @@
       <c r="C88" s="1">
         <v>1</v>
       </c>
-      <c r="D88" s="23" t="b">
+      <c r="D88" s="27" t="b">
         <v>1</v>
       </c>
       <c r="E88" s="1">
         <v>4055346</v>
       </c>
-      <c r="G88" s="8" t="s">
+      <c r="G88" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:12">
-      <c r="A89" s="8">
+      <c r="A89" s="9">
         <v>2207</v>
       </c>
       <c r="B89" s="1">
@@ -4017,18 +4042,18 @@
       <c r="C89" s="1">
         <v>1</v>
       </c>
-      <c r="D89" s="23" t="b">
+      <c r="D89" s="27" t="b">
         <v>1</v>
       </c>
       <c r="E89" s="1">
         <v>4055347</v>
       </c>
-      <c r="G89" s="8" t="s">
+      <c r="G89" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:12">
-      <c r="A90" s="8">
+      <c r="A90" s="9">
         <v>2208</v>
       </c>
       <c r="B90" s="1">
@@ -4037,15 +4062,15 @@
       <c r="C90" s="1">
         <v>1</v>
       </c>
-      <c r="D90" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G90" s="8" t="s">
+      <c r="D90" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G90" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:12">
-      <c r="A91" s="8">
+      <c r="A91" s="9">
         <v>2209</v>
       </c>
       <c r="B91" s="1">
@@ -4054,44 +4079,44 @@
       <c r="C91" s="1">
         <v>1</v>
       </c>
-      <c r="D91" s="23" t="b">
+      <c r="D91" s="27" t="b">
         <v>1</v>
       </c>
       <c r="E91" s="1">
         <v>4055349</v>
       </c>
-      <c r="G91" s="8" t="s">
+      <c r="G91" s="9" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="92" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A92" s="26">
+    <row r="92" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A92" s="30">
         <v>2210</v>
       </c>
-      <c r="B92" s="9">
+      <c r="B92" s="10">
         <v>10</v>
       </c>
-      <c r="C92" s="9">
-        <v>1</v>
-      </c>
-      <c r="D92" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" s="9">
+      <c r="C92" s="10">
+        <v>1</v>
+      </c>
+      <c r="D92" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="10">
         <v>4055350</v>
       </c>
-      <c r="F92" s="9"/>
-      <c r="G92" s="26" t="s">
+      <c r="F92" s="10"/>
+      <c r="G92" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="H92" s="27"/>
-      <c r="I92" s="27"/>
-      <c r="J92" s="27"/>
-      <c r="K92" s="27"/>
-      <c r="L92" s="27"/>
+      <c r="H92" s="31"/>
+      <c r="I92" s="31"/>
+      <c r="J92" s="31"/>
+      <c r="K92" s="31"/>
+      <c r="L92" s="31"/>
     </row>
     <row r="93" customHeight="1" spans="1:12">
-      <c r="A93" s="8">
+      <c r="A93" s="9">
         <v>2211</v>
       </c>
       <c r="B93" s="1">
@@ -4100,18 +4125,18 @@
       <c r="C93" s="1">
         <v>1</v>
       </c>
-      <c r="D93" s="23" t="b">
+      <c r="D93" s="27" t="b">
         <v>1</v>
       </c>
       <c r="E93" s="1">
         <v>4055351</v>
       </c>
-      <c r="G93" s="8" t="s">
+      <c r="G93" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="1:12">
-      <c r="A94" s="8">
+      <c r="A94" s="9">
         <v>2212</v>
       </c>
       <c r="B94" s="1">
@@ -4120,15 +4145,15 @@
       <c r="C94" s="1">
         <v>1</v>
       </c>
-      <c r="D94" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G94" s="8" t="s">
+      <c r="D94" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G94" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="1:12">
-      <c r="A95" s="8">
+      <c r="A95" s="9">
         <v>2213</v>
       </c>
       <c r="B95" s="1">
@@ -4137,15 +4162,15 @@
       <c r="C95" s="1">
         <v>1</v>
       </c>
-      <c r="D95" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G95" s="8" t="s">
+      <c r="D95" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G95" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="1:12">
-      <c r="A96" s="8">
+      <c r="A96" s="9">
         <v>2214</v>
       </c>
       <c r="B96" s="1">
@@ -4154,13 +4179,13 @@
       <c r="C96" s="1">
         <v>1</v>
       </c>
-      <c r="D96" s="23" t="b">
+      <c r="D96" s="27" t="b">
         <v>1</v>
       </c>
       <c r="E96" s="1">
         <v>4055354</v>
       </c>
-      <c r="G96" s="8" t="s">
+      <c r="G96" s="9" t="s">
         <v>80</v>
       </c>
     </row>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="109">
   <si>
     <t>序号</t>
   </si>
@@ -424,6 +424,30 @@
   </si>
   <si>
     <t>小鸟建筑升级</t>
+  </si>
+  <si>
+    <t>点击[+]图标解锁&lt;color=#00bfff&gt;萌宠小队&lt;/color&gt;游戏</t>
+  </si>
+  <si>
+    <t>点击去完成&lt;color=#00bfff&gt;主线任务&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>点击按钮&lt;color=#00bfff&gt;进行升级&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#00bfff&gt;连续点击或长按&lt;/color&gt;升级至进度条完成</t>
+  </si>
+  <si>
+    <t>建筑升级期间会有一定的等待时间，&lt;color=#00bfff&gt;使用加速卡、钻石或观看广告&lt;/color&gt;可以快速清除等待时间</t>
+  </si>
+  <si>
+    <t>娱乐城已&lt;color=#00bfff&gt;提升到2级&lt;/color&gt;，解锁了一些&lt;color=#00bfff&gt;新功能&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>解锁 &lt;color=#00bfff&gt;SWEET WIN 大奖&lt;/color&gt;技能</t>
+  </si>
+  <si>
+    <t>在&lt;color=#00bfff&gt;萌宠小队&lt;/color&gt;游戏中概率&lt;color=#00bfff&gt;中奖SWEET WIN 大奖&lt;/color&gt;</t>
   </si>
   <si>
     <t>_</t>
@@ -496,7 +520,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,12 +566,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.15"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -571,13 +589,6 @@
       <color theme="0" tint="-0.5"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.15"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1067,137 +1078,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1228,10 +1239,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1252,7 +1260,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1261,7 +1269,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1273,7 +1281,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1282,16 +1290,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1778,7 +1780,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -1788,40 +1790,40 @@
     <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="85.2916666666667" style="11" customWidth="1"/>
+    <col min="8" max="8" width="85.2916666666667" style="10" customWidth="1"/>
     <col min="13" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="13" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11"/>
+      <c r="H1" s="10"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
       <c r="L1"/>
     </row>
     <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1833,2078 +1835,2078 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="10"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10"/>
       <c r="I3"/>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="14"/>
-      <c r="H4" s="11"/>
+      <c r="A4" s="13"/>
+      <c r="H4" s="10"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
     </row>
     <row r="5" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>1001</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="16">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15">
         <v>4055101</v>
       </c>
-      <c r="F5" s="16"/>
+      <c r="F5" s="15"/>
       <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>1002</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="16">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="15">
         <v>4055102</v>
       </c>
-      <c r="F6" s="16"/>
+      <c r="F6" s="15"/>
       <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>1003</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="16">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="15">
         <v>4055103</v>
       </c>
-      <c r="F7" s="16"/>
+      <c r="F7" s="15"/>
       <c r="G7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>1004</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="16">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15">
         <v>4055104</v>
       </c>
-      <c r="F8" s="16"/>
+      <c r="F8" s="15"/>
       <c r="G8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>1005</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="16">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15">
         <v>4055109</v>
       </c>
-      <c r="F9" s="16"/>
+      <c r="F9" s="15"/>
       <c r="G9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>1006</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15">
         <v>4055105</v>
       </c>
-      <c r="F10" s="16"/>
+      <c r="F10" s="15"/>
       <c r="G10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>1007</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="16">
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="15">
         <v>4055106</v>
       </c>
-      <c r="F11" s="16"/>
+      <c r="F11" s="15"/>
       <c r="G11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>1008</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="16">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15">
         <v>4055107</v>
       </c>
-      <c r="F12" s="16"/>
+      <c r="F12" s="15"/>
       <c r="G12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="15">
+      <c r="A13" s="14">
         <v>1009</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="16">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="15">
         <v>4055108</v>
       </c>
-      <c r="F13" s="16"/>
+      <c r="F13" s="15"/>
       <c r="G13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
     </row>
     <row r="14" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="19">
+      <c r="A14" s="18">
         <v>1010</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
     </row>
     <row r="15" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="19">
+      <c r="A15" s="18">
         <v>1011</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="16" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="19">
+      <c r="A16" s="18">
         <v>1012</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
     </row>
     <row r="17" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="19">
+      <c r="A17" s="18">
         <v>1013</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
     </row>
     <row r="18" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="22">
+      <c r="A18" s="21">
         <v>1201</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="16">
         <v>2</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="16">
         <v>2</v>
       </c>
-      <c r="D18" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="17">
+      <c r="D18" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="16">
         <v>4055121</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="23" t="s">
+      <c r="F18" s="16"/>
+      <c r="G18" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
     </row>
     <row r="19" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="22">
+      <c r="A19" s="21">
         <v>1202</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="16">
         <v>2</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="16">
         <v>2</v>
       </c>
-      <c r="D19" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="17">
+      <c r="D19" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="16">
         <v>4055122</v>
       </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="23" t="s">
+      <c r="F19" s="16"/>
+      <c r="G19" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
     </row>
     <row r="20" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="22">
+      <c r="A20" s="21">
         <v>1203</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="16">
         <v>2</v>
       </c>
-      <c r="C20" s="17">
-        <v>1</v>
-      </c>
-      <c r="D20" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="17">
+      <c r="C20" s="16">
+        <v>1</v>
+      </c>
+      <c r="D20" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="16">
         <v>4055123</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="23" t="s">
+      <c r="F20" s="16"/>
+      <c r="G20" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
     </row>
     <row r="21" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="22">
+      <c r="A21" s="21">
         <v>1204</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="16">
         <v>2</v>
       </c>
-      <c r="C21" s="17">
-        <v>1</v>
-      </c>
-      <c r="D21" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="17">
+      <c r="C21" s="16">
+        <v>1</v>
+      </c>
+      <c r="D21" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="16">
         <v>4055124</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="23" t="s">
+      <c r="F21" s="16"/>
+      <c r="G21" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
     </row>
     <row r="22" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>1301</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="15">
         <v>2</v>
       </c>
-      <c r="C22" s="16">
-        <v>1</v>
-      </c>
-      <c r="D22" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="16">
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
         <v>4055141</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="24" t="s">
+      <c r="F22" s="15"/>
+      <c r="G22" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
     </row>
     <row r="23" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>1302</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="15">
         <v>2</v>
       </c>
-      <c r="C23" s="16">
-        <v>1</v>
-      </c>
-      <c r="D23" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="16">
+      <c r="C23" s="15">
+        <v>1</v>
+      </c>
+      <c r="D23" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
         <v>4055142</v>
       </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="24" t="s">
+      <c r="F23" s="15"/>
+      <c r="G23" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
     </row>
     <row r="24" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>1303</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="15">
         <v>2</v>
       </c>
-      <c r="C24" s="16">
-        <v>1</v>
-      </c>
-      <c r="D24" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="16">
+      <c r="C24" s="15">
+        <v>1</v>
+      </c>
+      <c r="D24" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15">
         <v>4055143</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="24" t="s">
+      <c r="F24" s="15"/>
+      <c r="G24" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
     </row>
     <row r="25" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>1304</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16">
-        <v>1</v>
-      </c>
-      <c r="D25" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="24" t="s">
+      <c r="B25" s="15"/>
+      <c r="C25" s="15">
+        <v>1</v>
+      </c>
+      <c r="D25" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
     </row>
     <row r="26" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="15">
+      <c r="A26" s="14">
         <v>1305</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16">
-        <v>1</v>
-      </c>
-      <c r="D26" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="24" t="s">
+      <c r="B26" s="15"/>
+      <c r="C26" s="15">
+        <v>1</v>
+      </c>
+      <c r="D26" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
     </row>
     <row r="27" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="22">
+      <c r="A27" s="21">
         <v>1401</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="16">
         <v>2</v>
       </c>
-      <c r="C27" s="17">
-        <v>1</v>
-      </c>
-      <c r="D27" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="17">
+      <c r="C27" s="16">
+        <v>1</v>
+      </c>
+      <c r="D27" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="16">
         <v>4055161</v>
       </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="23" t="s">
+      <c r="F27" s="16"/>
+      <c r="G27" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
     </row>
     <row r="28" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="22">
+      <c r="A28" s="21">
         <v>1402</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="16">
         <v>2</v>
       </c>
-      <c r="C28" s="17">
-        <v>1</v>
-      </c>
-      <c r="D28" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="17">
+      <c r="C28" s="16">
+        <v>1</v>
+      </c>
+      <c r="D28" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="16">
         <v>4055162</v>
       </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="23" t="s">
+      <c r="F28" s="16"/>
+      <c r="G28" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
     </row>
     <row r="29" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="22">
+      <c r="A29" s="21">
         <v>1403</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="16">
         <v>2</v>
       </c>
-      <c r="C29" s="17">
-        <v>1</v>
-      </c>
-      <c r="D29" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="17">
+      <c r="C29" s="16">
+        <v>1</v>
+      </c>
+      <c r="D29" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="16">
         <v>4055163</v>
       </c>
-      <c r="F29" s="17"/>
-      <c r="G29" s="23" t="s">
+      <c r="F29" s="16"/>
+      <c r="G29" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
     </row>
     <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="22">
+      <c r="A30" s="21">
         <v>1404</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="16">
         <v>2</v>
       </c>
-      <c r="C30" s="17">
-        <v>1</v>
-      </c>
-      <c r="D30" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="17">
+      <c r="C30" s="16">
+        <v>1</v>
+      </c>
+      <c r="D30" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="16">
         <v>4055164</v>
       </c>
-      <c r="F30" s="17"/>
-      <c r="G30" s="23" t="s">
+      <c r="F30" s="16"/>
+      <c r="G30" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
     </row>
     <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="22">
+      <c r="A31" s="21">
         <v>1405</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17">
-        <v>1</v>
-      </c>
-      <c r="D31" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="23" t="s">
+      <c r="B31" s="16"/>
+      <c r="C31" s="16">
+        <v>1</v>
+      </c>
+      <c r="D31" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
     </row>
     <row r="32" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="22">
+      <c r="A32" s="21">
         <v>1406</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="16">
         <v>2</v>
       </c>
-      <c r="C32" s="17">
-        <v>1</v>
-      </c>
-      <c r="D32" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="17">
+      <c r="C32" s="16">
+        <v>1</v>
+      </c>
+      <c r="D32" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="16">
         <v>4055165</v>
       </c>
-      <c r="F32" s="17"/>
-      <c r="G32" s="23" t="s">
+      <c r="F32" s="16"/>
+      <c r="G32" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
     </row>
     <row r="33" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="15">
+      <c r="A33" s="14">
         <v>1501</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="15">
         <v>2</v>
       </c>
-      <c r="C33" s="16">
-        <v>1</v>
-      </c>
-      <c r="D33" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="16">
+      <c r="C33" s="15">
+        <v>1</v>
+      </c>
+      <c r="D33" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
         <v>4055181</v>
       </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="24" t="s">
+      <c r="F33" s="15"/>
+      <c r="G33" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
     </row>
     <row r="34" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="15">
+      <c r="A34" s="14">
         <v>1502</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="15">
         <v>2</v>
       </c>
-      <c r="C34" s="16">
-        <v>1</v>
-      </c>
-      <c r="D34" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="16">
+      <c r="C34" s="15">
+        <v>1</v>
+      </c>
+      <c r="D34" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="15">
         <v>4055182</v>
       </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="24" t="s">
+      <c r="F34" s="15"/>
+      <c r="G34" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
     </row>
     <row r="35" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="15">
+      <c r="A35" s="14">
         <v>1503</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16">
-        <v>1</v>
-      </c>
-      <c r="D35" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="24" t="s">
+      <c r="B35" s="15"/>
+      <c r="C35" s="15">
+        <v>1</v>
+      </c>
+      <c r="D35" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
     </row>
     <row r="36" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="15">
+      <c r="A36" s="14">
         <v>1504</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16">
-        <v>1</v>
-      </c>
-      <c r="D36" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="24" t="s">
+      <c r="B36" s="15"/>
+      <c r="C36" s="15">
+        <v>1</v>
+      </c>
+      <c r="D36" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
     </row>
     <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="22">
+      <c r="A37" s="21">
         <v>1601</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17">
-        <v>1</v>
-      </c>
-      <c r="D37" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="23" t="s">
+      <c r="B37" s="16"/>
+      <c r="C37" s="16">
+        <v>1</v>
+      </c>
+      <c r="D37" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
     </row>
     <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="22">
+      <c r="A38" s="21">
         <v>1602</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17">
-        <v>1</v>
-      </c>
-      <c r="D38" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="23" t="s">
+      <c r="B38" s="16"/>
+      <c r="C38" s="16">
+        <v>1</v>
+      </c>
+      <c r="D38" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
     </row>
     <row r="39" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A39" s="22">
+      <c r="A39" s="21">
         <v>1603</v>
       </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17">
-        <v>1</v>
-      </c>
-      <c r="D39" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="17">
+      <c r="B39" s="16"/>
+      <c r="C39" s="16">
+        <v>1</v>
+      </c>
+      <c r="D39" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="16">
         <v>4055203</v>
       </c>
-      <c r="F39" s="16"/>
-      <c r="G39" s="23" t="s">
+      <c r="F39" s="15"/>
+      <c r="G39" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H39" s="11" t="s">
+      <c r="H39" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
     </row>
     <row r="40" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="22">
+      <c r="A40" s="21">
         <v>1604</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17">
-        <v>1</v>
-      </c>
-      <c r="D40" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="23" t="s">
+      <c r="B40" s="16"/>
+      <c r="C40" s="16">
+        <v>1</v>
+      </c>
+      <c r="D40" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
     </row>
     <row r="41" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="22">
+      <c r="A41" s="21">
         <v>1605</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="16">
         <v>2</v>
       </c>
-      <c r="C41" s="17">
-        <v>1</v>
-      </c>
-      <c r="D41" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="17">
+      <c r="C41" s="16">
+        <v>1</v>
+      </c>
+      <c r="D41" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="16">
         <v>4055204</v>
       </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="23" t="s">
+      <c r="F41" s="15"/>
+      <c r="G41" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H41" s="11" t="s">
+      <c r="H41" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
     </row>
     <row r="42" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="22">
+      <c r="A42" s="21">
         <v>1606</v>
       </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17">
-        <v>1</v>
-      </c>
-      <c r="D42" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="23" t="s">
+      <c r="B42" s="16"/>
+      <c r="C42" s="16">
+        <v>1</v>
+      </c>
+      <c r="D42" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
     </row>
     <row r="43" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="22">
+      <c r="A43" s="21">
         <v>1607</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="16">
         <v>2</v>
       </c>
-      <c r="C43" s="17">
-        <v>1</v>
-      </c>
-      <c r="D43" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="23" t="s">
+      <c r="C43" s="16">
+        <v>1</v>
+      </c>
+      <c r="D43" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="H43" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
     </row>
     <row r="44" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="22">
+      <c r="A44" s="21">
         <v>1608</v>
       </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17">
-        <v>1</v>
-      </c>
-      <c r="D44" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="17">
+      <c r="B44" s="16"/>
+      <c r="C44" s="16">
+        <v>1</v>
+      </c>
+      <c r="D44" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="16">
         <v>4055205</v>
       </c>
-      <c r="F44" s="16"/>
-      <c r="G44" s="23" t="s">
+      <c r="F44" s="15"/>
+      <c r="G44" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
     </row>
     <row r="45" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="22">
+      <c r="A45" s="21">
         <v>1609</v>
       </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17">
-        <v>1</v>
-      </c>
-      <c r="D45" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="17">
+      <c r="B45" s="16"/>
+      <c r="C45" s="16">
+        <v>1</v>
+      </c>
+      <c r="D45" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="16">
         <v>4055206</v>
       </c>
-      <c r="F45" s="16"/>
-      <c r="G45" s="23" t="s">
+      <c r="F45" s="15"/>
+      <c r="G45" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
     </row>
     <row r="46" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="22">
+      <c r="A46" s="21">
         <v>1610</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="16">
         <v>2</v>
       </c>
-      <c r="C46" s="17">
-        <v>1</v>
-      </c>
-      <c r="D46" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="17">
+      <c r="C46" s="16">
+        <v>1</v>
+      </c>
+      <c r="D46" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="16">
         <v>4055207</v>
       </c>
-      <c r="F46" s="16"/>
-      <c r="G46" s="23" t="s">
+      <c r="F46" s="15"/>
+      <c r="G46" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
     </row>
     <row r="47" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="22">
+      <c r="A47" s="21">
         <v>1611</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="16">
         <v>2</v>
       </c>
-      <c r="C47" s="17">
-        <v>1</v>
-      </c>
-      <c r="D47" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="17">
+      <c r="C47" s="16">
+        <v>1</v>
+      </c>
+      <c r="D47" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="16">
         <v>4055208</v>
       </c>
-      <c r="F47" s="16"/>
-      <c r="G47" s="23" t="s">
+      <c r="F47" s="15"/>
+      <c r="G47" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
     </row>
     <row r="48" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="22">
+      <c r="A48" s="21">
         <v>1612</v>
       </c>
-      <c r="B48" s="17">
+      <c r="B48" s="16">
         <v>2</v>
       </c>
-      <c r="C48" s="17">
-        <v>1</v>
-      </c>
-      <c r="D48" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="17">
+      <c r="C48" s="16">
+        <v>1</v>
+      </c>
+      <c r="D48" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="16">
         <v>4055209</v>
       </c>
-      <c r="F48" s="16"/>
-      <c r="G48" s="23" t="s">
+      <c r="F48" s="15"/>
+      <c r="G48" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
     </row>
     <row r="49" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="15">
+      <c r="A49" s="14">
         <v>1701</v>
       </c>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16">
-        <v>1</v>
-      </c>
-      <c r="D49" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="24" t="s">
+      <c r="B49" s="15"/>
+      <c r="C49" s="15">
+        <v>1</v>
+      </c>
+      <c r="D49" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="H49" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I49" s="18"/>
-      <c r="J49" s="18"/>
-      <c r="K49" s="18"/>
-      <c r="L49" s="18"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
     </row>
     <row r="50" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A50" s="15">
+      <c r="A50" s="14">
         <v>1702</v>
       </c>
-      <c r="C50" s="16">
-        <v>1</v>
-      </c>
-      <c r="D50" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="24" t="s">
+      <c r="C50" s="15">
+        <v>1</v>
+      </c>
+      <c r="D50" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" s="15"/>
+      <c r="G50" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I50" s="18"/>
-      <c r="J50" s="18"/>
-      <c r="K50" s="18"/>
-      <c r="L50" s="18"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
     </row>
     <row r="51" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A51" s="15">
+      <c r="A51" s="14">
         <v>1703</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="15">
         <v>2</v>
       </c>
-      <c r="C51" s="16">
-        <v>1</v>
-      </c>
-      <c r="D51" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="16">
+      <c r="C51" s="15">
+        <v>1</v>
+      </c>
+      <c r="D51" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="15">
         <v>4055222</v>
       </c>
-      <c r="F51" s="16"/>
-      <c r="G51" s="24" t="s">
+      <c r="F51" s="15"/>
+      <c r="G51" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I51" s="18"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="18"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
     </row>
     <row r="52" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A52" s="15">
+      <c r="A52" s="14">
         <v>1704</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="15">
         <v>2</v>
       </c>
-      <c r="C52" s="16">
-        <v>1</v>
-      </c>
-      <c r="D52" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="16">
+      <c r="C52" s="15">
+        <v>1</v>
+      </c>
+      <c r="D52" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="15">
         <v>4055223</v>
       </c>
-      <c r="F52" s="16"/>
-      <c r="G52" s="24" t="s">
+      <c r="F52" s="15"/>
+      <c r="G52" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I52" s="18"/>
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="18"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
     </row>
     <row r="53" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A53" s="15">
+      <c r="A53" s="14">
         <v>1705</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="15">
         <v>2</v>
       </c>
-      <c r="C53" s="16">
-        <v>1</v>
-      </c>
-      <c r="D53" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="16">
+      <c r="C53" s="15">
+        <v>1</v>
+      </c>
+      <c r="D53" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="15">
         <v>4055224</v>
       </c>
-      <c r="F53" s="16"/>
-      <c r="G53" s="24" t="s">
+      <c r="F53" s="15"/>
+      <c r="G53" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
     </row>
     <row r="54" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A54" s="15">
+      <c r="A54" s="14">
         <v>1706</v>
       </c>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16">
-        <v>1</v>
-      </c>
-      <c r="D54" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="24" t="s">
+      <c r="B54" s="15"/>
+      <c r="C54" s="15">
+        <v>1</v>
+      </c>
+      <c r="D54" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I54" s="18"/>
-      <c r="J54" s="18"/>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
     </row>
     <row r="55" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A55" s="15">
+      <c r="A55" s="14">
         <v>1707</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="15">
         <v>2</v>
       </c>
-      <c r="C55" s="16">
-        <v>1</v>
-      </c>
-      <c r="D55" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="16">
+      <c r="C55" s="15">
+        <v>1</v>
+      </c>
+      <c r="D55" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="15">
         <v>4055225</v>
       </c>
-      <c r="F55" s="16"/>
-      <c r="G55" s="24" t="s">
+      <c r="F55" s="15"/>
+      <c r="G55" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="I55" s="18"/>
-      <c r="J55" s="18"/>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
     </row>
     <row r="56" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A56" s="15">
+      <c r="A56" s="14">
         <v>1708</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="15">
         <v>2</v>
       </c>
-      <c r="C56" s="16">
-        <v>1</v>
-      </c>
-      <c r="D56" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="16">
+      <c r="C56" s="15">
+        <v>1</v>
+      </c>
+      <c r="D56" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="15">
         <v>4055226</v>
       </c>
-      <c r="F56" s="16"/>
-      <c r="G56" s="24" t="s">
+      <c r="F56" s="15"/>
+      <c r="G56" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H56" s="11" t="s">
+      <c r="H56" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
-      <c r="L56" s="18"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
     </row>
     <row r="57" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A57" s="15">
+      <c r="A57" s="14">
         <v>1709</v>
       </c>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16">
-        <v>1</v>
-      </c>
-      <c r="D57" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="24" t="s">
+      <c r="B57" s="15"/>
+      <c r="C57" s="15">
+        <v>1</v>
+      </c>
+      <c r="D57" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="H57" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="18"/>
-      <c r="L57" s="18"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
     </row>
     <row r="58" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A58" s="15">
+      <c r="A58" s="14">
         <v>1710</v>
       </c>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16">
-        <v>1</v>
-      </c>
-      <c r="D58" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="24" t="s">
+      <c r="B58" s="15"/>
+      <c r="C58" s="15">
+        <v>1</v>
+      </c>
+      <c r="D58" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I58" s="18"/>
-      <c r="J58" s="18"/>
-      <c r="K58" s="18"/>
-      <c r="L58" s="18"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
     </row>
     <row r="59" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="15">
+      <c r="A59" s="14">
         <v>1711</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="15">
         <v>2</v>
       </c>
-      <c r="C59" s="16">
-        <v>1</v>
-      </c>
-      <c r="D59" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="16">
+      <c r="C59" s="15">
+        <v>1</v>
+      </c>
+      <c r="D59" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="15">
         <v>4055227</v>
       </c>
-      <c r="F59" s="16"/>
-      <c r="G59" s="24" t="s">
+      <c r="F59" s="15"/>
+      <c r="G59" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="H59" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
     </row>
     <row r="60" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="15">
+      <c r="A60" s="14">
         <v>1712</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="15">
         <v>2</v>
       </c>
-      <c r="C60" s="16">
-        <v>1</v>
-      </c>
-      <c r="D60" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="16">
+      <c r="C60" s="15">
+        <v>1</v>
+      </c>
+      <c r="D60" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="15">
         <v>4055228</v>
       </c>
-      <c r="F60" s="16"/>
-      <c r="G60" s="24" t="s">
+      <c r="F60" s="15"/>
+      <c r="G60" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="H60" s="11" t="s">
+      <c r="H60" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="I60" s="18"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
-      <c r="L60" s="18"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
     </row>
     <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="22">
+      <c r="A61" s="21">
         <v>1801</v>
       </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17">
-        <v>1</v>
-      </c>
-      <c r="D61" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="17"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="23" t="s">
+      <c r="B61" s="16"/>
+      <c r="C61" s="16">
+        <v>1</v>
+      </c>
+      <c r="D61" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="H61" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
     </row>
     <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A62" s="22">
+      <c r="A62" s="21">
         <v>1802</v>
       </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17">
-        <v>1</v>
-      </c>
-      <c r="D62" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="23" t="s">
+      <c r="B62" s="16"/>
+      <c r="C62" s="16">
+        <v>1</v>
+      </c>
+      <c r="D62" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
     </row>
     <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A63" s="22">
+      <c r="A63" s="21">
         <v>1803</v>
       </c>
-      <c r="B63" s="17">
+      <c r="B63" s="16">
         <v>2</v>
       </c>
-      <c r="C63" s="17">
-        <v>1</v>
-      </c>
-      <c r="D63" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="17">
+      <c r="C63" s="16">
+        <v>1</v>
+      </c>
+      <c r="D63" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="16">
         <v>4055243</v>
       </c>
-      <c r="F63" s="17"/>
-      <c r="G63" s="23" t="s">
+      <c r="F63" s="16"/>
+      <c r="G63" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="H63" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="I63" s="11"/>
-      <c r="J63" s="11"/>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
+      <c r="I63" s="10"/>
+      <c r="J63" s="10"/>
+      <c r="K63" s="10"/>
+      <c r="L63" s="10"/>
     </row>
     <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A64" s="22">
+      <c r="A64" s="21">
         <v>1804</v>
       </c>
-      <c r="B64" s="17">
+      <c r="B64" s="16">
         <v>2</v>
       </c>
-      <c r="C64" s="17">
-        <v>1</v>
-      </c>
-      <c r="D64" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="17">
+      <c r="C64" s="16">
+        <v>1</v>
+      </c>
+      <c r="D64" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="16">
         <v>4055244</v>
       </c>
-      <c r="F64" s="17"/>
-      <c r="G64" s="23" t="s">
+      <c r="F64" s="16"/>
+      <c r="G64" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="H64" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I64" s="11"/>
-      <c r="J64" s="11"/>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+      <c r="L64" s="10"/>
     </row>
     <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A65" s="22">
+      <c r="A65" s="21">
         <v>1805</v>
       </c>
-      <c r="B65" s="17">
+      <c r="B65" s="16">
         <v>2</v>
       </c>
-      <c r="C65" s="17">
-        <v>1</v>
-      </c>
-      <c r="D65" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="17">
+      <c r="C65" s="16">
+        <v>1</v>
+      </c>
+      <c r="D65" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="16">
         <v>4055245</v>
       </c>
-      <c r="F65" s="17"/>
-      <c r="G65" s="23" t="s">
+      <c r="F65" s="16"/>
+      <c r="G65" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10"/>
+      <c r="L65" s="10"/>
     </row>
     <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="22">
+      <c r="A66" s="21">
         <v>1806</v>
       </c>
-      <c r="B66" s="17">
+      <c r="B66" s="16">
         <v>2</v>
       </c>
-      <c r="C66" s="17">
-        <v>1</v>
-      </c>
-      <c r="D66" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="17">
+      <c r="C66" s="16">
+        <v>1</v>
+      </c>
+      <c r="D66" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="16">
         <v>4055246</v>
       </c>
-      <c r="F66" s="17"/>
-      <c r="G66" s="23" t="s">
+      <c r="F66" s="16"/>
+      <c r="G66" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11"/>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
+      <c r="L66" s="10"/>
     </row>
     <row r="67" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="22">
+      <c r="A67" s="21">
         <v>1807</v>
       </c>
-      <c r="B67" s="17">
+      <c r="B67" s="16">
         <v>2</v>
       </c>
-      <c r="C67" s="17">
-        <v>1</v>
-      </c>
-      <c r="D67" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="17">
+      <c r="C67" s="16">
+        <v>1</v>
+      </c>
+      <c r="D67" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="16">
         <v>4055247</v>
       </c>
-      <c r="F67" s="17"/>
-      <c r="G67" s="23" t="s">
+      <c r="F67" s="16"/>
+      <c r="G67" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H67" s="11" t="s">
+      <c r="H67" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I67" s="11"/>
-      <c r="J67" s="11"/>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10"/>
+      <c r="L67" s="10"/>
     </row>
     <row r="68" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="15">
+      <c r="A68" s="14">
         <v>1901</v>
       </c>
-      <c r="B68" s="16"/>
-      <c r="C68" s="16">
-        <v>1</v>
-      </c>
-      <c r="D68" s="25" t="b">
+      <c r="B68" s="15"/>
+      <c r="C68" s="15">
+        <v>1</v>
+      </c>
+      <c r="D68" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="24" t="s">
+      <c r="E68" s="15"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H68" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I68" s="18"/>
-      <c r="J68" s="18"/>
-      <c r="K68" s="18"/>
-      <c r="L68" s="18"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
+      <c r="L68" s="17"/>
     </row>
     <row r="69" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A69" s="15">
+      <c r="A69" s="14">
         <v>1902</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="15">
         <v>2</v>
       </c>
-      <c r="C69" s="16">
-        <v>1</v>
-      </c>
-      <c r="D69" s="25" t="b">
+      <c r="C69" s="15">
+        <v>1</v>
+      </c>
+      <c r="D69" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E69" s="16">
+      <c r="E69" s="15">
         <v>4055263</v>
       </c>
-      <c r="F69" s="16"/>
-      <c r="G69" s="24" t="s">
+      <c r="F69" s="15"/>
+      <c r="G69" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="H69" s="11" t="s">
+      <c r="H69" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="I69" s="18"/>
-      <c r="J69" s="18"/>
-      <c r="K69" s="18"/>
-      <c r="L69" s="18"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="17"/>
+      <c r="K69" s="17"/>
+      <c r="L69" s="17"/>
     </row>
     <row r="70" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="15">
+      <c r="A70" s="14">
         <v>1903</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="15">
         <v>2</v>
       </c>
-      <c r="C70" s="16">
-        <v>1</v>
-      </c>
-      <c r="D70" s="25" t="b">
+      <c r="C70" s="15">
+        <v>1</v>
+      </c>
+      <c r="D70" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="15">
         <v>4055264</v>
       </c>
-      <c r="F70" s="16"/>
-      <c r="G70" s="24" t="s">
+      <c r="F70" s="15"/>
+      <c r="G70" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="I70" s="18"/>
-      <c r="J70" s="18"/>
-      <c r="K70" s="18"/>
-      <c r="L70" s="18"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="17"/>
+      <c r="K70" s="17"/>
+      <c r="L70" s="17"/>
     </row>
     <row r="71" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="22">
+      <c r="A71" s="21">
         <v>1981</v>
       </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17">
-        <v>1</v>
-      </c>
-      <c r="D71" s="25" t="b">
+      <c r="B71" s="16"/>
+      <c r="C71" s="16">
+        <v>1</v>
+      </c>
+      <c r="D71" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
-      <c r="G71" s="23" t="s">
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="10"/>
     </row>
     <row r="72" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="22">
+      <c r="A72" s="21">
         <v>1982</v>
       </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="17">
-        <v>1</v>
-      </c>
-      <c r="D72" s="25" t="b">
+      <c r="B72" s="16"/>
+      <c r="C72" s="16">
+        <v>1</v>
+      </c>
+      <c r="D72" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="23" t="s">
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H72" s="11" t="s">
+      <c r="H72" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
+      <c r="I72" s="10"/>
+      <c r="J72" s="10"/>
+      <c r="K72" s="10"/>
+      <c r="L72" s="10"/>
     </row>
     <row r="73" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A73" s="22">
+      <c r="A73" s="21">
         <v>1983</v>
       </c>
-      <c r="B73" s="17">
+      <c r="B73" s="16">
         <v>2</v>
       </c>
-      <c r="C73" s="17">
-        <v>1</v>
-      </c>
-      <c r="D73" s="25" t="b">
+      <c r="C73" s="16">
+        <v>1</v>
+      </c>
+      <c r="D73" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E73" s="17">
+      <c r="E73" s="16">
         <v>4055321</v>
       </c>
-      <c r="F73" s="17"/>
-      <c r="G73" s="23" t="s">
+      <c r="F73" s="16"/>
+      <c r="G73" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H73" s="11" t="s">
+      <c r="H73" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11"/>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
+      <c r="I73" s="10"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="10"/>
+      <c r="L73" s="10"/>
     </row>
     <row r="74" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="15">
+      <c r="A74" s="14">
         <v>2001</v>
       </c>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16">
-        <v>1</v>
-      </c>
-      <c r="D74" s="25" t="b">
+      <c r="B74" s="15"/>
+      <c r="C74" s="15">
+        <v>1</v>
+      </c>
+      <c r="D74" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="24" t="s">
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H74" s="11" t="s">
+      <c r="H74" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I74" s="18"/>
-      <c r="J74" s="18"/>
-      <c r="K74" s="18"/>
-      <c r="L74" s="18"/>
+      <c r="I74" s="17"/>
+      <c r="J74" s="17"/>
+      <c r="K74" s="17"/>
+      <c r="L74" s="17"/>
     </row>
     <row r="75" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="15">
+      <c r="A75" s="14">
         <v>2002</v>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="15">
         <v>2</v>
       </c>
-      <c r="C75" s="16">
-        <v>1</v>
-      </c>
-      <c r="D75" s="25" t="b">
+      <c r="C75" s="15">
+        <v>1</v>
+      </c>
+      <c r="D75" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E75" s="16">
+      <c r="E75" s="15">
         <v>4055281</v>
       </c>
-      <c r="F75" s="16"/>
-      <c r="G75" s="24" t="s">
+      <c r="F75" s="15"/>
+      <c r="G75" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H75" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="18"/>
-      <c r="J75" s="18"/>
-      <c r="K75" s="18"/>
-      <c r="L75" s="18"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
+      <c r="L75" s="17"/>
     </row>
     <row r="76" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A76" s="15">
+      <c r="A76" s="14">
         <v>2003</v>
       </c>
-      <c r="B76" s="16">
+      <c r="B76" s="15">
         <v>2</v>
       </c>
-      <c r="C76" s="16">
-        <v>1</v>
-      </c>
-      <c r="D76" s="25" t="b">
+      <c r="C76" s="15">
+        <v>1</v>
+      </c>
+      <c r="D76" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E76" s="16">
+      <c r="E76" s="15">
         <v>4055282</v>
       </c>
-      <c r="F76" s="16"/>
-      <c r="G76" s="24" t="s">
+      <c r="F76" s="15"/>
+      <c r="G76" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H76" s="11" t="s">
+      <c r="H76" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I76" s="18"/>
-      <c r="J76" s="18"/>
-      <c r="K76" s="18"/>
-      <c r="L76" s="18"/>
+      <c r="I76" s="17"/>
+      <c r="J76" s="17"/>
+      <c r="K76" s="17"/>
+      <c r="L76" s="17"/>
     </row>
     <row r="77" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A77" s="15">
+      <c r="A77" s="14">
         <v>2004</v>
       </c>
-      <c r="B77" s="16">
+      <c r="B77" s="15">
         <v>2</v>
       </c>
-      <c r="C77" s="16">
-        <v>1</v>
-      </c>
-      <c r="D77" s="25" t="b">
+      <c r="C77" s="15">
+        <v>1</v>
+      </c>
+      <c r="D77" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E77" s="16">
+      <c r="E77" s="15">
         <v>4055283</v>
       </c>
-      <c r="F77" s="16"/>
-      <c r="G77" s="24" t="s">
+      <c r="F77" s="15"/>
+      <c r="G77" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H77" s="11" t="s">
+      <c r="H77" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I77" s="18"/>
-      <c r="J77" s="18"/>
-      <c r="K77" s="18"/>
-      <c r="L77" s="18"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
+      <c r="K77" s="17"/>
+      <c r="L77" s="17"/>
     </row>
     <row r="78" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A78" s="15">
+      <c r="A78" s="14">
         <v>2005</v>
       </c>
-      <c r="B78" s="16">
+      <c r="B78" s="15">
         <v>2</v>
       </c>
-      <c r="C78" s="16">
-        <v>1</v>
-      </c>
-      <c r="D78" s="25" t="b">
+      <c r="C78" s="15">
+        <v>1</v>
+      </c>
+      <c r="D78" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E78" s="16">
+      <c r="E78" s="15">
         <v>4055284</v>
       </c>
-      <c r="F78" s="16"/>
-      <c r="G78" s="24" t="s">
+      <c r="F78" s="15"/>
+      <c r="G78" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H78" s="11" t="s">
+      <c r="H78" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I78" s="18"/>
-      <c r="J78" s="18"/>
-      <c r="K78" s="18"/>
-      <c r="L78" s="18"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="17"/>
+      <c r="K78" s="17"/>
+      <c r="L78" s="17"/>
     </row>
     <row r="79" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="15">
+      <c r="A79" s="14">
         <v>2006</v>
       </c>
-      <c r="B79" s="16">
+      <c r="B79" s="15">
         <v>2</v>
       </c>
-      <c r="C79" s="16">
-        <v>1</v>
-      </c>
-      <c r="D79" s="25" t="b">
+      <c r="C79" s="15">
+        <v>1</v>
+      </c>
+      <c r="D79" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E79" s="16">
+      <c r="E79" s="15">
         <v>4055285</v>
       </c>
-      <c r="F79" s="16"/>
-      <c r="G79" s="24" t="s">
+      <c r="F79" s="15"/>
+      <c r="G79" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H79" s="11" t="s">
+      <c r="H79" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I79" s="18"/>
-      <c r="J79" s="18"/>
-      <c r="K79" s="18"/>
-      <c r="L79" s="18"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="17"/>
+      <c r="K79" s="17"/>
+      <c r="L79" s="17"/>
     </row>
     <row r="80" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="15">
+      <c r="A80" s="14">
         <v>2007</v>
       </c>
-      <c r="B80" s="16">
+      <c r="B80" s="15">
         <v>2</v>
       </c>
-      <c r="C80" s="16">
-        <v>1</v>
-      </c>
-      <c r="D80" s="25" t="b">
+      <c r="C80" s="15">
+        <v>1</v>
+      </c>
+      <c r="D80" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E80" s="16">
+      <c r="E80" s="15">
         <v>4055286</v>
       </c>
-      <c r="F80" s="16"/>
-      <c r="G80" s="24" t="s">
+      <c r="F80" s="15"/>
+      <c r="G80" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H80" s="11" t="s">
+      <c r="H80" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I80" s="18"/>
-      <c r="J80" s="18"/>
-      <c r="K80" s="18"/>
-      <c r="L80" s="18"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="17"/>
+      <c r="K80" s="17"/>
+      <c r="L80" s="17"/>
     </row>
     <row r="81" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="26">
+      <c r="A81" s="25">
         <v>2101</v>
       </c>
-      <c r="B81" s="26">
+      <c r="B81" s="25">
         <v>2</v>
       </c>
-      <c r="C81" s="26">
-        <v>1</v>
-      </c>
-      <c r="D81" s="25" t="b">
+      <c r="C81" s="25">
+        <v>1</v>
+      </c>
+      <c r="D81" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E81" s="26">
+      <c r="E81" s="25">
         <v>4055301</v>
       </c>
-      <c r="F81" s="26"/>
+      <c r="F81" s="25"/>
       <c r="G81" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H81" s="11" t="s">
+      <c r="H81" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I81" s="11"/>
-      <c r="J81" s="11"/>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="10"/>
+      <c r="L81" s="10"/>
     </row>
     <row r="82" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="26">
+      <c r="A82" s="25">
         <v>2102</v>
       </c>
-      <c r="B82" s="26">
-        <v>1</v>
-      </c>
-      <c r="C82" s="26">
-        <v>1</v>
-      </c>
-      <c r="D82" s="25" t="b">
+      <c r="B82" s="25">
+        <v>1</v>
+      </c>
+      <c r="C82" s="25">
+        <v>1</v>
+      </c>
+      <c r="D82" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E82" s="26">
+      <c r="E82" s="25">
         <v>4055303</v>
       </c>
-      <c r="F82" s="26"/>
+      <c r="F82" s="25"/>
       <c r="G82" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H82" s="11" t="s">
+      <c r="H82" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I82" s="11"/>
-      <c r="J82" s="11"/>
-      <c r="K82" s="11"/>
-      <c r="L82" s="11"/>
+      <c r="I82" s="10"/>
+      <c r="J82" s="10"/>
+      <c r="K82" s="10"/>
+      <c r="L82" s="10"/>
     </row>
     <row r="83" s="9" customFormat="1" customHeight="1" spans="1:12">
       <c r="A83" s="9">
@@ -3916,7 +3918,7 @@
       <c r="C83" s="9">
         <v>2</v>
       </c>
-      <c r="D83" s="27" t="b">
+      <c r="D83" s="26" t="b">
         <v>1</v>
       </c>
       <c r="E83" s="9">
@@ -3926,11 +3928,12 @@
       <c r="G83" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="H83" s="28"/>
-      <c r="I83" s="29"/>
-      <c r="J83" s="29"/>
-      <c r="K83" s="29"/>
-      <c r="L83" s="29"/>
+      <c r="H83" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="J83" s="27"/>
+      <c r="K83" s="27"/>
+      <c r="L83" s="27"/>
     </row>
     <row r="84" customHeight="1" spans="1:12">
       <c r="A84" s="9">
@@ -3942,7 +3945,7 @@
       <c r="C84" s="1">
         <v>1</v>
       </c>
-      <c r="D84" s="27" t="b">
+      <c r="D84" s="26" t="b">
         <v>1</v>
       </c>
       <c r="E84" s="1">
@@ -3950,6 +3953,9 @@
       </c>
       <c r="G84" s="9" t="s">
         <v>80</v>
+      </c>
+      <c r="H84" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:12">
@@ -3962,7 +3968,7 @@
       <c r="C85" s="1">
         <v>1</v>
       </c>
-      <c r="D85" s="27" t="b">
+      <c r="D85" s="26" t="b">
         <v>1</v>
       </c>
       <c r="E85" s="1">
@@ -3971,222 +3977,320 @@
       <c r="G85" s="9" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="86" customHeight="1" spans="1:12">
-      <c r="A86" s="9">
+      <c r="H85" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A86" s="26">
         <v>2204</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="6">
         <v>4</v>
       </c>
-      <c r="C86" s="1">
-        <v>1</v>
-      </c>
-      <c r="D86" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" s="1">
+      <c r="C86" s="6">
+        <v>1</v>
+      </c>
+      <c r="D86" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="6">
         <v>4055344</v>
       </c>
-      <c r="G86" s="9" t="s">
+      <c r="F86" s="6"/>
+      <c r="G86" s="26" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="87" customHeight="1" spans="1:12">
-      <c r="A87" s="9">
+      <c r="H86" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I86" s="28"/>
+      <c r="J86" s="28"/>
+      <c r="K86" s="28"/>
+      <c r="L86" s="28"/>
+    </row>
+    <row r="87" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A87" s="26">
         <v>2205</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="6">
         <v>5</v>
       </c>
-      <c r="C87" s="1">
-        <v>1</v>
-      </c>
-      <c r="D87" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="1">
+      <c r="C87" s="6">
+        <v>1</v>
+      </c>
+      <c r="D87" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="6">
         <v>4055345</v>
       </c>
-      <c r="G87" s="9" t="s">
+      <c r="F87" s="6"/>
+      <c r="G87" s="26" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="88" customHeight="1" spans="1:12">
-      <c r="A88" s="9">
+      <c r="H87" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I87" s="28"/>
+      <c r="J87" s="28"/>
+      <c r="K87" s="28"/>
+      <c r="L87" s="28"/>
+    </row>
+    <row r="88" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A88" s="26">
         <v>2206</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88" s="6">
         <v>6</v>
       </c>
-      <c r="C88" s="1">
-        <v>1</v>
-      </c>
-      <c r="D88" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" s="1">
+      <c r="C88" s="6">
+        <v>1</v>
+      </c>
+      <c r="D88" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="6">
         <v>4055346</v>
       </c>
-      <c r="G88" s="9" t="s">
+      <c r="F88" s="6"/>
+      <c r="G88" s="26" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="89" customHeight="1" spans="1:12">
-      <c r="A89" s="9">
+      <c r="H88" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I88" s="28"/>
+      <c r="J88" s="28"/>
+      <c r="K88" s="28"/>
+      <c r="L88" s="28"/>
+    </row>
+    <row r="89" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A89" s="26">
         <v>2207</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89" s="6">
         <v>7</v>
       </c>
-      <c r="C89" s="1">
-        <v>1</v>
-      </c>
-      <c r="D89" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" s="1">
+      <c r="C89" s="6">
+        <v>1</v>
+      </c>
+      <c r="D89" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="6">
         <v>4055347</v>
       </c>
-      <c r="G89" s="9" t="s">
+      <c r="F89" s="6"/>
+      <c r="G89" s="26" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="90" customHeight="1" spans="1:12">
-      <c r="A90" s="9">
+      <c r="H89" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I89" s="28"/>
+      <c r="J89" s="28"/>
+      <c r="K89" s="28"/>
+      <c r="L89" s="28"/>
+    </row>
+    <row r="90" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A90" s="26">
         <v>2208</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90" s="6">
         <v>8</v>
       </c>
-      <c r="C90" s="1">
-        <v>1</v>
-      </c>
-      <c r="D90" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G90" s="9" t="s">
+      <c r="C90" s="6">
+        <v>1</v>
+      </c>
+      <c r="D90" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="6">
+        <v>4055348</v>
+      </c>
+      <c r="F90" s="6"/>
+      <c r="G90" s="26" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="91" customHeight="1" spans="1:12">
-      <c r="A91" s="9">
+      <c r="H90" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I90" s="28"/>
+      <c r="J90" s="28"/>
+      <c r="K90" s="28"/>
+      <c r="L90" s="28"/>
+    </row>
+    <row r="91" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A91" s="26">
         <v>2209</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91" s="6">
         <v>9</v>
       </c>
-      <c r="C91" s="1">
-        <v>1</v>
-      </c>
-      <c r="D91" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" s="1">
-        <v>4055349</v>
-      </c>
-      <c r="G91" s="9" t="s">
+      <c r="C91" s="6">
+        <v>1</v>
+      </c>
+      <c r="D91" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="26" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="92" s="10" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A92" s="30">
+      <c r="H91" s="28"/>
+      <c r="I91" s="28"/>
+      <c r="J91" s="28"/>
+      <c r="K91" s="28"/>
+      <c r="L91" s="28"/>
+    </row>
+    <row r="92" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A92" s="26">
         <v>2210</v>
       </c>
-      <c r="B92" s="10">
+      <c r="B92" s="6">
         <v>10</v>
       </c>
-      <c r="C92" s="10">
-        <v>1</v>
-      </c>
-      <c r="D92" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" s="10">
+      <c r="C92" s="6">
+        <v>1</v>
+      </c>
+      <c r="D92" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="6">
         <v>4055350</v>
       </c>
-      <c r="F92" s="10"/>
-      <c r="G92" s="30" t="s">
+      <c r="F92" s="6"/>
+      <c r="G92" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="H92" s="31"/>
-      <c r="I92" s="31"/>
-      <c r="J92" s="31"/>
-      <c r="K92" s="31"/>
-      <c r="L92" s="31"/>
-    </row>
-    <row r="93" customHeight="1" spans="1:12">
-      <c r="A93" s="9">
+      <c r="H92" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="J92" s="10"/>
+      <c r="K92" s="10"/>
+      <c r="L92" s="10"/>
+    </row>
+    <row r="93" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A93" s="26">
         <v>2211</v>
       </c>
-      <c r="B93" s="1">
-        <v>11</v>
-      </c>
-      <c r="C93" s="1">
-        <v>1</v>
-      </c>
-      <c r="D93" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="1">
+      <c r="B93" s="6">
+        <v>12</v>
+      </c>
+      <c r="C93" s="6">
+        <v>1</v>
+      </c>
+      <c r="D93" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="6">
         <v>4055351</v>
       </c>
-      <c r="G93" s="9" t="s">
+      <c r="F93" s="6"/>
+      <c r="G93" s="26" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="94" customHeight="1" spans="1:12">
-      <c r="A94" s="9">
+      <c r="H93" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I93" s="28"/>
+      <c r="J93" s="28"/>
+      <c r="K93" s="28"/>
+      <c r="L93" s="28"/>
+    </row>
+    <row r="94" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A94" s="26">
         <v>2212</v>
       </c>
-      <c r="B94" s="1">
-        <v>12</v>
-      </c>
-      <c r="C94" s="1">
-        <v>1</v>
-      </c>
-      <c r="D94" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G94" s="9" t="s">
+      <c r="B94" s="6">
+        <v>13</v>
+      </c>
+      <c r="C94" s="6">
+        <v>1</v>
+      </c>
+      <c r="D94" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="6">
+        <v>4055352</v>
+      </c>
+      <c r="F94" s="6"/>
+      <c r="G94" s="26" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="95" customHeight="1" spans="1:12">
-      <c r="A95" s="9">
+      <c r="H94" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J94" s="10"/>
+      <c r="K94" s="10"/>
+      <c r="L94" s="10"/>
+    </row>
+    <row r="95" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A95" s="26">
         <v>2213</v>
       </c>
-      <c r="B95" s="1">
-        <v>13</v>
-      </c>
-      <c r="C95" s="1">
-        <v>1</v>
-      </c>
-      <c r="D95" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G95" s="9" t="s">
+      <c r="B95" s="6">
+        <v>14</v>
+      </c>
+      <c r="C95" s="6">
+        <v>1</v>
+      </c>
+      <c r="D95" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="26" t="s">
         <v>80</v>
       </c>
+      <c r="H95" s="28"/>
+      <c r="I95" s="28"/>
+      <c r="J95" s="28"/>
+      <c r="K95" s="28"/>
+      <c r="L95" s="28"/>
     </row>
     <row r="96" customHeight="1" spans="1:12">
       <c r="A96" s="9">
         <v>2214</v>
       </c>
       <c r="B96" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C96" s="1">
         <v>1</v>
       </c>
-      <c r="D96" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E96" s="1">
-        <v>4055354</v>
-      </c>
+      <c r="D96" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" s="1"/>
       <c r="G96" s="9" t="s">
         <v>80</v>
+      </c>
+      <c r="H96"/>
+    </row>
+    <row r="97" customHeight="1" spans="1:8">
+      <c r="A97" s="9">
+        <v>2215</v>
+      </c>
+      <c r="B97" s="1">
+        <v>14</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1</v>
+      </c>
+      <c r="D97" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" s="1">
+        <v>4055355</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H97" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -4247,14 +4351,14 @@
         <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -4263,7 +4367,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4273,14 +4377,14 @@
         <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4288,14 +4392,14 @@
         <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4303,14 +4407,14 @@
         <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4318,14 +4422,14 @@
         <v>2205</v>
       </c>
       <c r="J9" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
         <v>2205_</v>
       </c>
       <c r="M9" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4333,14 +4437,14 @@
         <v>2206</v>
       </c>
       <c r="J10" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>2206_</v>
       </c>
       <c r="M10" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4348,14 +4452,14 @@
         <v>2207</v>
       </c>
       <c r="J11" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>2207_</v>
       </c>
       <c r="M11" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4363,14 +4467,14 @@
         <v>2208</v>
       </c>
       <c r="J12" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>2208_</v>
       </c>
       <c r="M12" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4378,32 +4482,32 @@
         <v>2209</v>
       </c>
       <c r="J13" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>2209_</v>
       </c>
       <c r="M13" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>2210</v>
       </c>
       <c r="J14" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>2210_</v>
       </c>
       <c r="M14" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4411,14 +4515,14 @@
         <v>2211</v>
       </c>
       <c r="J15" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>2211_</v>
       </c>
       <c r="M15" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4426,14 +4530,14 @@
         <v>2212</v>
       </c>
       <c r="J16" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>2212_</v>
       </c>
       <c r="M16" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4441,14 +4545,14 @@
         <v>2213</v>
       </c>
       <c r="J17" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>2213_</v>
       </c>
       <c r="M17" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4456,29 +4560,29 @@
         <v>2214</v>
       </c>
       <c r="J18" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>2214_</v>
       </c>
       <c r="M18" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="111">
   <si>
     <t>序号</t>
   </si>
@@ -448,6 +448,12 @@
   </si>
   <si>
     <t>在&lt;color=#00bfff&gt;萌宠小队&lt;/color&gt;游戏中概率&lt;color=#00bfff&gt;中奖SWEET WIN 大奖&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>在线购买资源</t>
+  </si>
+  <si>
+    <t>在这里可以&lt;color=#00bfff&gt;快速获得金币、娱乐城经验&lt;/color&gt;等资源</t>
   </si>
   <si>
     <t>_</t>
@@ -746,12 +752,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1084,7 +1096,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
@@ -1108,16 +1120,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
@@ -1126,89 +1138,89 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1284,7 +1296,10 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1293,8 +1308,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1780,7 +1795,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -3560,180 +3575,165 @@
       <c r="A70" s="14">
         <v>1903</v>
       </c>
-      <c r="B70" s="15">
-        <v>2</v>
-      </c>
-      <c r="C70" s="15">
-        <v>1</v>
-      </c>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
       <c r="D70" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E70" s="15">
-        <v>4055264</v>
-      </c>
+      <c r="E70" s="25"/>
       <c r="F70" s="15"/>
       <c r="G70" s="23" t="s">
         <v>67</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>69</v>
       </c>
       <c r="I70" s="17"/>
       <c r="J70" s="17"/>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
     </row>
-    <row r="71" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="21">
-        <v>1981</v>
-      </c>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16">
+    <row r="71" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A71" s="14">
+        <v>1904</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15">
         <v>1</v>
       </c>
       <c r="D71" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="10"/>
-    </row>
-    <row r="72" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="21">
-        <v>1982</v>
-      </c>
-      <c r="B72" s="16"/>
-      <c r="C72" s="16">
+      <c r="E71" s="15"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="H71" s="10"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+      <c r="L71" s="17"/>
+    </row>
+    <row r="72" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A72" s="14">
+        <v>1905</v>
+      </c>
+      <c r="B72" s="15">
+        <v>2</v>
+      </c>
+      <c r="C72" s="15">
         <v>1</v>
       </c>
       <c r="D72" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="22" t="s">
-        <v>70</v>
+      <c r="E72" s="15">
+        <v>4055264</v>
+      </c>
+      <c r="F72" s="15"/>
+      <c r="G72" s="23" t="s">
+        <v>67</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I72" s="10"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="10"/>
-      <c r="L72" s="10"/>
+        <v>69</v>
+      </c>
+      <c r="I72" s="17"/>
+      <c r="J72" s="17"/>
+      <c r="K72" s="17"/>
+      <c r="L72" s="17"/>
     </row>
     <row r="73" s="7" customFormat="1" customHeight="1" spans="1:12">
       <c r="A73" s="21">
-        <v>1983</v>
-      </c>
-      <c r="B73" s="16">
-        <v>2</v>
-      </c>
+        <v>1981</v>
+      </c>
+      <c r="B73" s="16"/>
       <c r="C73" s="16">
         <v>1</v>
       </c>
       <c r="D73" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E73" s="16">
-        <v>4055321</v>
-      </c>
+      <c r="E73" s="16"/>
       <c r="F73" s="16"/>
       <c r="G73" s="22" t="s">
         <v>70</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
       <c r="L73" s="10"/>
     </row>
-    <row r="74" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="14">
-        <v>2001</v>
-      </c>
-      <c r="B74" s="15"/>
-      <c r="C74" s="15">
+    <row r="74" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A74" s="21">
+        <v>1982</v>
+      </c>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16">
         <v>1</v>
       </c>
       <c r="D74" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="23" t="s">
-        <v>72</v>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="22" t="s">
+        <v>70</v>
       </c>
       <c r="H74" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I74" s="17"/>
-      <c r="J74" s="17"/>
-      <c r="K74" s="17"/>
-      <c r="L74" s="17"/>
-    </row>
-    <row r="75" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="14">
-        <v>2002</v>
-      </c>
-      <c r="B75" s="15">
+      <c r="I74" s="10"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="10"/>
+      <c r="L74" s="10"/>
+    </row>
+    <row r="75" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A75" s="21">
+        <v>1983</v>
+      </c>
+      <c r="B75" s="16">
         <v>2</v>
       </c>
-      <c r="C75" s="15">
+      <c r="C75" s="16">
         <v>1</v>
       </c>
       <c r="D75" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E75" s="15">
-        <v>4055281</v>
-      </c>
-      <c r="F75" s="15"/>
-      <c r="G75" s="23" t="s">
-        <v>72</v>
+      <c r="E75" s="16">
+        <v>4055321</v>
+      </c>
+      <c r="F75" s="16"/>
+      <c r="G75" s="22" t="s">
+        <v>70</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I75" s="17"/>
-      <c r="J75" s="17"/>
-      <c r="K75" s="17"/>
-      <c r="L75" s="17"/>
+        <v>71</v>
+      </c>
+      <c r="I75" s="10"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="10"/>
+      <c r="L75" s="10"/>
     </row>
     <row r="76" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A76" s="14">
-        <v>2003</v>
-      </c>
-      <c r="B76" s="15">
-        <v>2</v>
-      </c>
+        <v>2001</v>
+      </c>
+      <c r="B76" s="15"/>
       <c r="C76" s="15">
         <v>1</v>
       </c>
       <c r="D76" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E76" s="15">
-        <v>4055282</v>
-      </c>
+      <c r="E76" s="15"/>
       <c r="F76" s="15"/>
       <c r="G76" s="23" t="s">
         <v>72</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="I76" s="17"/>
       <c r="J76" s="17"/>
@@ -3742,7 +3742,7 @@
     </row>
     <row r="77" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A77" s="14">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B77" s="15">
         <v>2</v>
@@ -3754,14 +3754,14 @@
         <v>0</v>
       </c>
       <c r="E77" s="15">
-        <v>4055283</v>
+        <v>4055281</v>
       </c>
       <c r="F77" s="15"/>
       <c r="G77" s="23" t="s">
         <v>72</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -3770,7 +3770,7 @@
     </row>
     <row r="78" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A78" s="14">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B78" s="15">
         <v>2</v>
@@ -3782,7 +3782,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="15">
-        <v>4055284</v>
+        <v>4055282</v>
       </c>
       <c r="F78" s="15"/>
       <c r="G78" s="23" t="s">
@@ -3798,7 +3798,7 @@
     </row>
     <row r="79" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A79" s="14">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B79" s="15">
         <v>2</v>
@@ -3810,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="15">
-        <v>4055285</v>
+        <v>4055283</v>
       </c>
       <c r="F79" s="15"/>
       <c r="G79" s="23" t="s">
@@ -3826,7 +3826,7 @@
     </row>
     <row r="80" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A80" s="14">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B80" s="15">
         <v>2</v>
@@ -3838,459 +3838,574 @@
         <v>0</v>
       </c>
       <c r="E80" s="15">
-        <v>4055286</v>
+        <v>4055284</v>
       </c>
       <c r="F80" s="15"/>
       <c r="G80" s="23" t="s">
         <v>72</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I80" s="17"/>
       <c r="J80" s="17"/>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
     </row>
-    <row r="81" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="25">
-        <v>2101</v>
-      </c>
-      <c r="B81" s="25">
+    <row r="81" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A81" s="14">
+        <v>2006</v>
+      </c>
+      <c r="B81" s="15">
         <v>2</v>
       </c>
-      <c r="C81" s="25">
+      <c r="C81" s="15">
         <v>1</v>
       </c>
       <c r="D81" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E81" s="25">
-        <v>4055301</v>
-      </c>
-      <c r="F81" s="25"/>
-      <c r="G81" s="6" t="s">
-        <v>77</v>
+      <c r="E81" s="15">
+        <v>4055285</v>
+      </c>
+      <c r="F81" s="15"/>
+      <c r="G81" s="23" t="s">
+        <v>72</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="10"/>
-      <c r="L81" s="10"/>
-    </row>
-    <row r="82" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="25">
-        <v>2102</v>
-      </c>
-      <c r="B82" s="25">
-        <v>1</v>
-      </c>
-      <c r="C82" s="25">
+        <v>75</v>
+      </c>
+      <c r="I81" s="17"/>
+      <c r="J81" s="17"/>
+      <c r="K81" s="17"/>
+      <c r="L81" s="17"/>
+    </row>
+    <row r="82" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A82" s="14">
+        <v>2007</v>
+      </c>
+      <c r="B82" s="15">
+        <v>2</v>
+      </c>
+      <c r="C82" s="15">
         <v>1</v>
       </c>
       <c r="D82" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E82" s="25">
+      <c r="E82" s="15">
+        <v>4055286</v>
+      </c>
+      <c r="F82" s="15"/>
+      <c r="G82" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I82" s="17"/>
+      <c r="J82" s="17"/>
+      <c r="K82" s="17"/>
+      <c r="L82" s="17"/>
+    </row>
+    <row r="83" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A83" s="26">
+        <v>2101</v>
+      </c>
+      <c r="B83" s="26">
+        <v>2</v>
+      </c>
+      <c r="C83" s="26">
+        <v>1</v>
+      </c>
+      <c r="D83" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" s="26">
+        <v>4055301</v>
+      </c>
+      <c r="F83" s="26"/>
+      <c r="G83" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I83" s="10"/>
+      <c r="J83" s="10"/>
+      <c r="K83" s="10"/>
+      <c r="L83" s="10"/>
+    </row>
+    <row r="84" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A84" s="26">
+        <v>2102</v>
+      </c>
+      <c r="B84" s="26">
+        <v>1</v>
+      </c>
+      <c r="C84" s="26">
+        <v>1</v>
+      </c>
+      <c r="D84" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84" s="26">
         <v>4055303</v>
       </c>
-      <c r="F82" s="25"/>
-      <c r="G82" s="6" t="s">
+      <c r="F84" s="26"/>
+      <c r="G84" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H82" s="10" t="s">
+      <c r="H84" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I82" s="10"/>
-      <c r="J82" s="10"/>
-      <c r="K82" s="10"/>
-      <c r="L82" s="10"/>
-    </row>
-    <row r="83" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A83" s="9">
+      <c r="I84" s="10"/>
+      <c r="J84" s="10"/>
+      <c r="K84" s="10"/>
+      <c r="L84" s="10"/>
+    </row>
+    <row r="85" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A85" s="9">
         <v>2201</v>
       </c>
-      <c r="B83" s="9">
-        <v>1</v>
-      </c>
-      <c r="C83" s="9">
+      <c r="B85" s="9">
+        <v>1</v>
+      </c>
+      <c r="C85" s="9">
         <v>2</v>
       </c>
-      <c r="D83" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="9">
+      <c r="D85" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="9">
         <v>4055341</v>
       </c>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H83" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="J83" s="27"/>
-      <c r="K83" s="27"/>
-      <c r="L83" s="27"/>
-    </row>
-    <row r="84" customHeight="1" spans="1:12">
-      <c r="A84" s="9">
-        <v>2202</v>
-      </c>
-      <c r="B84" s="1">
-        <v>2</v>
-      </c>
-      <c r="C84" s="1">
-        <v>1</v>
-      </c>
-      <c r="D84" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" s="1">
-        <v>4055342</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H84" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="1:12">
-      <c r="A85" s="9">
-        <v>2203</v>
-      </c>
-      <c r="B85" s="1">
-        <v>3</v>
-      </c>
-      <c r="C85" s="1">
-        <v>1</v>
-      </c>
-      <c r="D85" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" s="1">
-        <v>4055343</v>
-      </c>
+      <c r="F85" s="9"/>
       <c r="G85" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="J85" s="28"/>
+      <c r="K85" s="28"/>
+      <c r="L85" s="28"/>
+    </row>
+    <row r="86" customHeight="1" spans="1:12">
+      <c r="A86" s="9">
+        <v>2202</v>
+      </c>
+      <c r="B86" s="1">
+        <v>2</v>
+      </c>
+      <c r="C86" s="1">
+        <v>1</v>
+      </c>
+      <c r="D86" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="1">
+        <v>4055342</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H86" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:12">
+      <c r="A87" s="9">
+        <v>2203</v>
+      </c>
+      <c r="B87" s="1">
+        <v>3</v>
+      </c>
+      <c r="C87" s="1">
+        <v>1</v>
+      </c>
+      <c r="D87" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="1">
+        <v>4055343</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H87" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="86" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A86" s="26">
+    <row r="88" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A88" s="27">
         <v>2204</v>
       </c>
-      <c r="B86" s="6">
+      <c r="B88" s="6">
         <v>4</v>
       </c>
-      <c r="C86" s="6">
-        <v>1</v>
-      </c>
-      <c r="D86" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" s="6">
+      <c r="C88" s="6">
+        <v>1</v>
+      </c>
+      <c r="D88" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="6">
         <v>4055344</v>
       </c>
-      <c r="F86" s="6"/>
-      <c r="G86" s="26" t="s">
+      <c r="F88" s="6"/>
+      <c r="G88" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="H86" s="10" t="s">
+      <c r="H88" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I86" s="28"/>
-      <c r="J86" s="28"/>
-      <c r="K86" s="28"/>
-      <c r="L86" s="28"/>
-    </row>
-    <row r="87" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A87" s="26">
+      <c r="I88" s="10"/>
+      <c r="J88" s="10"/>
+      <c r="K88" s="10"/>
+      <c r="L88" s="10"/>
+    </row>
+    <row r="89" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A89" s="27">
         <v>2205</v>
       </c>
-      <c r="B87" s="6">
+      <c r="B89" s="6">
         <v>5</v>
       </c>
-      <c r="C87" s="6">
-        <v>1</v>
-      </c>
-      <c r="D87" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="6">
+      <c r="C89" s="6">
+        <v>1</v>
+      </c>
+      <c r="D89" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="6">
         <v>4055345</v>
       </c>
-      <c r="F87" s="6"/>
-      <c r="G87" s="26" t="s">
+      <c r="F89" s="6"/>
+      <c r="G89" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="H87" s="10" t="s">
+      <c r="H89" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="I87" s="28"/>
-      <c r="J87" s="28"/>
-      <c r="K87" s="28"/>
-      <c r="L87" s="28"/>
-    </row>
-    <row r="88" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A88" s="26">
+      <c r="I89" s="10"/>
+      <c r="J89" s="10"/>
+      <c r="K89" s="10"/>
+      <c r="L89" s="10"/>
+    </row>
+    <row r="90" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A90" s="27">
         <v>2206</v>
       </c>
-      <c r="B88" s="6">
+      <c r="B90" s="6">
         <v>6</v>
       </c>
-      <c r="C88" s="6">
-        <v>1</v>
-      </c>
-      <c r="D88" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" s="6">
+      <c r="C90" s="6">
+        <v>1</v>
+      </c>
+      <c r="D90" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="6">
         <v>4055346</v>
       </c>
-      <c r="F88" s="6"/>
-      <c r="G88" s="26" t="s">
+      <c r="F90" s="6"/>
+      <c r="G90" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="H88" s="10" t="s">
+      <c r="H90" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="I88" s="28"/>
-      <c r="J88" s="28"/>
-      <c r="K88" s="28"/>
-      <c r="L88" s="28"/>
-    </row>
-    <row r="89" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A89" s="26">
+      <c r="I90" s="10"/>
+      <c r="J90" s="10"/>
+      <c r="K90" s="10"/>
+      <c r="L90" s="10"/>
+    </row>
+    <row r="91" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A91" s="27">
         <v>2207</v>
       </c>
-      <c r="B89" s="6">
+      <c r="B91" s="6">
         <v>7</v>
       </c>
-      <c r="C89" s="6">
-        <v>1</v>
-      </c>
-      <c r="D89" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" s="6">
+      <c r="C91" s="6">
+        <v>1</v>
+      </c>
+      <c r="D91" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="6">
         <v>4055347</v>
       </c>
-      <c r="F89" s="6"/>
-      <c r="G89" s="26" t="s">
+      <c r="F91" s="6"/>
+      <c r="G91" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="H89" s="10" t="s">
+      <c r="H91" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I89" s="28"/>
-      <c r="J89" s="28"/>
-      <c r="K89" s="28"/>
-      <c r="L89" s="28"/>
-    </row>
-    <row r="90" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A90" s="26">
+      <c r="I91" s="10"/>
+      <c r="J91" s="10"/>
+      <c r="K91" s="10"/>
+      <c r="L91" s="10"/>
+    </row>
+    <row r="92" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A92" s="27">
         <v>2208</v>
       </c>
-      <c r="B90" s="6">
+      <c r="B92" s="6">
         <v>8</v>
       </c>
-      <c r="C90" s="6">
-        <v>1</v>
-      </c>
-      <c r="D90" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E90" s="6">
+      <c r="C92" s="6">
+        <v>1</v>
+      </c>
+      <c r="D92" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="6">
         <v>4055348</v>
       </c>
-      <c r="F90" s="6"/>
-      <c r="G90" s="26" t="s">
+      <c r="F92" s="6"/>
+      <c r="G92" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="H90" s="10" t="s">
+      <c r="H92" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="I90" s="28"/>
-      <c r="J90" s="28"/>
-      <c r="K90" s="28"/>
-      <c r="L90" s="28"/>
-    </row>
-    <row r="91" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A91" s="26">
-        <v>2209</v>
-      </c>
-      <c r="B91" s="6">
-        <v>9</v>
-      </c>
-      <c r="C91" s="6">
-        <v>1</v>
-      </c>
-      <c r="D91" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="H91" s="28"/>
-      <c r="I91" s="28"/>
-      <c r="J91" s="28"/>
-      <c r="K91" s="28"/>
-      <c r="L91" s="28"/>
-    </row>
-    <row r="92" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A92" s="26">
-        <v>2210</v>
-      </c>
-      <c r="B92" s="6">
-        <v>10</v>
-      </c>
-      <c r="C92" s="6">
-        <v>1</v>
-      </c>
-      <c r="D92" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" s="6">
-        <v>4055350</v>
-      </c>
-      <c r="F92" s="6"/>
-      <c r="G92" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="H92" s="10" t="s">
-        <v>82</v>
-      </c>
+      <c r="I92" s="10"/>
       <c r="J92" s="10"/>
       <c r="K92" s="10"/>
       <c r="L92" s="10"/>
     </row>
     <row r="93" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A93" s="26">
-        <v>2211</v>
+      <c r="A93" s="27">
+        <v>2209</v>
       </c>
       <c r="B93" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C93" s="6">
         <v>1</v>
       </c>
-      <c r="D93" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="6">
-        <v>4055351</v>
-      </c>
+      <c r="D93" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="6"/>
       <c r="F93" s="6"/>
-      <c r="G93" s="26" t="s">
+      <c r="G93" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="H93" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I93" s="28"/>
-      <c r="J93" s="28"/>
-      <c r="K93" s="28"/>
-      <c r="L93" s="28"/>
+      <c r="H93" s="10"/>
+      <c r="I93" s="10"/>
+      <c r="J93" s="10"/>
+      <c r="K93" s="10"/>
+      <c r="L93" s="10"/>
     </row>
     <row r="94" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A94" s="26">
-        <v>2212</v>
+      <c r="A94" s="27">
+        <v>2210</v>
       </c>
       <c r="B94" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C94" s="6">
         <v>1</v>
       </c>
-      <c r="D94" s="26" t="b">
+      <c r="D94" s="27" t="b">
         <v>1</v>
       </c>
       <c r="E94" s="6">
-        <v>4055352</v>
+        <v>4055350</v>
       </c>
       <c r="F94" s="6"/>
-      <c r="G94" s="26" t="s">
+      <c r="G94" s="27" t="s">
         <v>80</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J94" s="10"/>
       <c r="K94" s="10"/>
       <c r="L94" s="10"/>
     </row>
     <row r="95" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A95" s="26">
+      <c r="A95" s="27">
+        <v>2211</v>
+      </c>
+      <c r="B95" s="6">
+        <v>12</v>
+      </c>
+      <c r="C95" s="6">
+        <v>1</v>
+      </c>
+      <c r="D95" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="6">
+        <v>4055351</v>
+      </c>
+      <c r="F95" s="6"/>
+      <c r="G95" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I95" s="10"/>
+      <c r="J95" s="10"/>
+      <c r="K95" s="10"/>
+      <c r="L95" s="10"/>
+    </row>
+    <row r="96" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A96" s="27">
+        <v>2212</v>
+      </c>
+      <c r="B96" s="6">
+        <v>13</v>
+      </c>
+      <c r="C96" s="6">
+        <v>1</v>
+      </c>
+      <c r="D96" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" s="6">
+        <v>4055352</v>
+      </c>
+      <c r="F96" s="6"/>
+      <c r="G96" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="H96" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J96" s="10"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="10"/>
+    </row>
+    <row r="97" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A97" s="27">
         <v>2213</v>
       </c>
-      <c r="B95" s="6">
+      <c r="B97" s="6">
         <v>14</v>
       </c>
-      <c r="C95" s="6">
-        <v>1</v>
-      </c>
-      <c r="D95" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="26" t="s">
+      <c r="C97" s="6">
+        <v>1</v>
+      </c>
+      <c r="D97" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="H95" s="28"/>
-      <c r="I95" s="28"/>
-      <c r="J95" s="28"/>
-      <c r="K95" s="28"/>
-      <c r="L95" s="28"/>
-    </row>
-    <row r="96" customHeight="1" spans="1:12">
-      <c r="A96" s="9">
+      <c r="H97" s="10"/>
+      <c r="I97" s="10"/>
+      <c r="J97" s="10"/>
+      <c r="K97" s="10"/>
+      <c r="L97" s="10"/>
+    </row>
+    <row r="98" customHeight="1" spans="1:12">
+      <c r="A98" s="9">
         <v>2214</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B98" s="1">
         <v>13</v>
       </c>
-      <c r="C96" s="1">
-        <v>1</v>
-      </c>
-      <c r="D96" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E96" s="1"/>
-      <c r="G96" s="9" t="s">
+      <c r="C98" s="1">
+        <v>1</v>
+      </c>
+      <c r="D98" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G98" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="H96"/>
-    </row>
-    <row r="97" customHeight="1" spans="1:8">
-      <c r="A97" s="9">
+      <c r="H98"/>
+    </row>
+    <row r="99" customHeight="1" spans="1:12">
+      <c r="A99" s="9">
         <v>2215</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B99" s="1">
         <v>14</v>
       </c>
-      <c r="C97" s="1">
-        <v>1</v>
-      </c>
-      <c r="D97" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E97" s="1">
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" s="1">
         <v>4055355</v>
       </c>
-      <c r="G97" s="9" t="s">
+      <c r="G99" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H99" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="1:12">
+      <c r="A100" s="29">
+        <v>2301</v>
+      </c>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29">
+        <v>2</v>
+      </c>
+      <c r="D100" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E100" s="29"/>
+      <c r="F100" s="29"/>
+      <c r="G100" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="1:12">
+      <c r="A101" s="29">
+        <v>2302</v>
+      </c>
+      <c r="B101" s="29">
+        <v>1</v>
+      </c>
+      <c r="C101" s="29">
+        <v>1</v>
+      </c>
+      <c r="D101" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E101" s="29"/>
+      <c r="F101" s="29"/>
+      <c r="G101" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="1:12">
+      <c r="A102" s="29">
+        <v>2303</v>
+      </c>
+      <c r="B102" s="29">
+        <v>1</v>
+      </c>
+      <c r="C102" s="29">
+        <v>1</v>
+      </c>
+      <c r="D102" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102" s="29">
+        <v>4055371</v>
+      </c>
+      <c r="F102" s="29"/>
+      <c r="G102" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -4351,14 +4466,14 @@
         <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -4367,7 +4482,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4377,14 +4492,14 @@
         <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4392,14 +4507,14 @@
         <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4407,14 +4522,14 @@
         <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4422,14 +4537,14 @@
         <v>2205</v>
       </c>
       <c r="J9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
         <v>2205_</v>
       </c>
       <c r="M9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4437,14 +4552,14 @@
         <v>2206</v>
       </c>
       <c r="J10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>2206_</v>
       </c>
       <c r="M10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4452,14 +4567,14 @@
         <v>2207</v>
       </c>
       <c r="J11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>2207_</v>
       </c>
       <c r="M11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4467,14 +4582,14 @@
         <v>2208</v>
       </c>
       <c r="J12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>2208_</v>
       </c>
       <c r="M12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4482,32 +4597,32 @@
         <v>2209</v>
       </c>
       <c r="J13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>2209_</v>
       </c>
       <c r="M13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I14">
         <v>2210</v>
       </c>
       <c r="J14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>2210_</v>
       </c>
       <c r="M14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4515,14 +4630,14 @@
         <v>2211</v>
       </c>
       <c r="J15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>2211_</v>
       </c>
       <c r="M15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4530,14 +4645,14 @@
         <v>2212</v>
       </c>
       <c r="J16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>2212_</v>
       </c>
       <c r="M16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4545,14 +4660,14 @@
         <v>2213</v>
       </c>
       <c r="J17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>2213_</v>
       </c>
       <c r="M17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4560,29 +4675,29 @@
         <v>2214</v>
       </c>
       <c r="J18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>2214_</v>
       </c>
       <c r="M18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="112">
   <si>
     <t>序号</t>
   </si>
@@ -412,6 +412,9 @@
   </si>
   <si>
     <t>在未提牌时，点击区域内的牌可将牌&lt;color=#00bfff&gt;取回&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>联盟-触发</t>
   </si>
   <si>
     <t>联盟</t>
@@ -752,18 +755,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.05"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1096,7 +1093,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
@@ -1120,16 +1117,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
@@ -1138,89 +1135,89 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1296,10 +1293,16 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1308,7 +1311,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1795,7 +1798,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -3908,53 +3911,49 @@
       <c r="K82" s="17"/>
       <c r="L82" s="17"/>
     </row>
-    <row r="83" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="83" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A83" s="26">
-        <v>2101</v>
-      </c>
-      <c r="B83" s="26">
+        <v>2100</v>
+      </c>
+      <c r="B83" s="27">
         <v>2</v>
       </c>
-      <c r="C83" s="26">
+      <c r="C83" s="27">
         <v>1</v>
       </c>
       <c r="D83" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E83" s="26">
-        <v>4055301</v>
-      </c>
-      <c r="F83" s="26"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
       <c r="G83" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H83" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="10"/>
-      <c r="L83" s="10"/>
+      <c r="H83" s="10"/>
+      <c r="I83" s="17"/>
+      <c r="J83" s="17"/>
+      <c r="K83" s="17"/>
+      <c r="L83" s="17"/>
     </row>
     <row r="84" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A84" s="26">
-        <v>2102</v>
-      </c>
-      <c r="B84" s="26">
-        <v>1</v>
-      </c>
-      <c r="C84" s="26">
+      <c r="A84" s="28">
+        <v>2101</v>
+      </c>
+      <c r="B84" s="28">
+        <v>2</v>
+      </c>
+      <c r="C84" s="28">
         <v>1</v>
       </c>
       <c r="D84" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="E84" s="26">
-        <v>4055303</v>
-      </c>
-      <c r="F84" s="26"/>
+      <c r="E84" s="28">
+        <v>4055301</v>
+      </c>
+      <c r="F84" s="28"/>
       <c r="G84" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H84" s="10" t="s">
         <v>79</v>
@@ -3964,126 +3963,126 @@
       <c r="K84" s="10"/>
       <c r="L84" s="10"/>
     </row>
-    <row r="85" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A85" s="9">
+    <row r="85" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A85" s="28">
+        <v>2102</v>
+      </c>
+      <c r="B85" s="28">
+        <v>1</v>
+      </c>
+      <c r="C85" s="28">
+        <v>1</v>
+      </c>
+      <c r="D85" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" s="28">
+        <v>4055303</v>
+      </c>
+      <c r="F85" s="28"/>
+      <c r="G85" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I85" s="10"/>
+      <c r="J85" s="10"/>
+      <c r="K85" s="10"/>
+      <c r="L85" s="10"/>
+    </row>
+    <row r="86" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A86" s="9">
         <v>2201</v>
       </c>
-      <c r="B85" s="9">
-        <v>1</v>
-      </c>
-      <c r="C85" s="9">
+      <c r="B86" s="9">
+        <v>1</v>
+      </c>
+      <c r="C86" s="9">
         <v>2</v>
       </c>
-      <c r="D85" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" s="9">
+      <c r="D86" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="9">
         <v>4055341</v>
       </c>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H85" s="28" t="s">
+      <c r="F86" s="9"/>
+      <c r="G86" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="J85" s="28"/>
-      <c r="K85" s="28"/>
-      <c r="L85" s="28"/>
-    </row>
-    <row r="86" customHeight="1" spans="1:12">
-      <c r="A86" s="9">
-        <v>2202</v>
-      </c>
-      <c r="B86" s="1">
-        <v>2</v>
-      </c>
-      <c r="C86" s="1">
-        <v>1</v>
-      </c>
-      <c r="D86" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" s="1">
-        <v>4055342</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H86" t="s">
+      <c r="H86" s="30" t="s">
         <v>82</v>
       </c>
+      <c r="J86" s="30"/>
+      <c r="K86" s="30"/>
+      <c r="L86" s="30"/>
     </row>
     <row r="87" customHeight="1" spans="1:12">
       <c r="A87" s="9">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B87" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87" s="1">
         <v>1</v>
       </c>
-      <c r="D87" s="27" t="b">
+      <c r="D87" s="29" t="b">
         <v>1</v>
       </c>
       <c r="E87" s="1">
-        <v>4055343</v>
+        <v>4055342</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="88" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A88" s="27">
+    <row r="88" customHeight="1" spans="1:12">
+      <c r="A88" s="9">
+        <v>2203</v>
+      </c>
+      <c r="B88" s="1">
+        <v>3</v>
+      </c>
+      <c r="C88" s="1">
+        <v>1</v>
+      </c>
+      <c r="D88" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="1">
+        <v>4055343</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H88" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A89" s="29">
         <v>2204</v>
       </c>
-      <c r="B88" s="6">
+      <c r="B89" s="6">
         <v>4</v>
       </c>
-      <c r="C88" s="6">
-        <v>1</v>
-      </c>
-      <c r="D88" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" s="6">
+      <c r="C89" s="6">
+        <v>1</v>
+      </c>
+      <c r="D89" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="6">
         <v>4055344</v>
       </c>
-      <c r="F88" s="6"/>
-      <c r="G88" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="I88" s="10"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="10"/>
-      <c r="L88" s="10"/>
-    </row>
-    <row r="89" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A89" s="27">
-        <v>2205</v>
-      </c>
-      <c r="B89" s="6">
-        <v>5</v>
-      </c>
-      <c r="C89" s="6">
-        <v>1</v>
-      </c>
-      <c r="D89" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" s="6">
-        <v>4055345</v>
-      </c>
       <c r="F89" s="6"/>
-      <c r="G89" s="27" t="s">
-        <v>80</v>
+      <c r="G89" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="H89" s="10" t="s">
         <v>85</v>
@@ -4094,24 +4093,24 @@
       <c r="L89" s="10"/>
     </row>
     <row r="90" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A90" s="27">
-        <v>2206</v>
+      <c r="A90" s="29">
+        <v>2205</v>
       </c>
       <c r="B90" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C90" s="6">
         <v>1</v>
       </c>
-      <c r="D90" s="27" t="b">
+      <c r="D90" s="29" t="b">
         <v>1</v>
       </c>
       <c r="E90" s="6">
-        <v>4055346</v>
+        <v>4055345</v>
       </c>
       <c r="F90" s="6"/>
-      <c r="G90" s="27" t="s">
-        <v>80</v>
+      <c r="G90" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="H90" s="10" t="s">
         <v>86</v>
@@ -4122,27 +4121,27 @@
       <c r="L90" s="10"/>
     </row>
     <row r="91" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A91" s="27">
-        <v>2207</v>
+      <c r="A91" s="29">
+        <v>2206</v>
       </c>
       <c r="B91" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C91" s="6">
         <v>1</v>
       </c>
-      <c r="D91" s="27" t="b">
+      <c r="D91" s="29" t="b">
         <v>1</v>
       </c>
       <c r="E91" s="6">
-        <v>4055347</v>
+        <v>4055346</v>
       </c>
       <c r="F91" s="6"/>
-      <c r="G91" s="27" t="s">
-        <v>80</v>
+      <c r="G91" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="10"/>
@@ -4150,24 +4149,24 @@
       <c r="L91" s="10"/>
     </row>
     <row r="92" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A92" s="27">
-        <v>2208</v>
+      <c r="A92" s="29">
+        <v>2207</v>
       </c>
       <c r="B92" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C92" s="6">
         <v>1</v>
       </c>
-      <c r="D92" s="27" t="b">
+      <c r="D92" s="29" t="b">
         <v>1</v>
       </c>
       <c r="E92" s="6">
-        <v>4055348</v>
+        <v>4055347</v>
       </c>
       <c r="F92" s="6"/>
-      <c r="G92" s="27" t="s">
-        <v>80</v>
+      <c r="G92" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="H92" s="10" t="s">
         <v>85</v>
@@ -4178,234 +4177,262 @@
       <c r="L92" s="10"/>
     </row>
     <row r="93" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A93" s="27">
-        <v>2209</v>
+      <c r="A93" s="29">
+        <v>2208</v>
       </c>
       <c r="B93" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C93" s="6">
         <v>1</v>
       </c>
-      <c r="D93" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="6"/>
+      <c r="D93" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="6">
+        <v>4055348</v>
+      </c>
       <c r="F93" s="6"/>
-      <c r="G93" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="H93" s="10"/>
+      <c r="G93" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>86</v>
+      </c>
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
       <c r="K93" s="10"/>
       <c r="L93" s="10"/>
     </row>
     <row r="94" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A94" s="27">
-        <v>2210</v>
+      <c r="A94" s="29">
+        <v>2209</v>
       </c>
       <c r="B94" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C94" s="6">
         <v>1</v>
       </c>
-      <c r="D94" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E94" s="6">
-        <v>4055350</v>
-      </c>
+      <c r="D94" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="6"/>
       <c r="F94" s="6"/>
-      <c r="G94" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>82</v>
-      </c>
+      <c r="G94" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="H94" s="10"/>
+      <c r="I94" s="10"/>
       <c r="J94" s="10"/>
       <c r="K94" s="10"/>
       <c r="L94" s="10"/>
     </row>
     <row r="95" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A95" s="27">
-        <v>2211</v>
+      <c r="A95" s="29">
+        <v>2210</v>
       </c>
       <c r="B95" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C95" s="6">
         <v>1</v>
       </c>
-      <c r="D95" s="27" t="b">
+      <c r="D95" s="29" t="b">
         <v>1</v>
       </c>
       <c r="E95" s="6">
-        <v>4055351</v>
+        <v>4055350</v>
       </c>
       <c r="F95" s="6"/>
-      <c r="G95" s="27" t="s">
-        <v>80</v>
+      <c r="G95" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I95" s="10"/>
+        <v>83</v>
+      </c>
       <c r="J95" s="10"/>
       <c r="K95" s="10"/>
       <c r="L95" s="10"/>
     </row>
     <row r="96" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A96" s="27">
-        <v>2212</v>
+      <c r="A96" s="29">
+        <v>2211</v>
       </c>
       <c r="B96" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C96" s="6">
         <v>1</v>
       </c>
-      <c r="D96" s="27" t="b">
+      <c r="D96" s="29" t="b">
         <v>1</v>
       </c>
       <c r="E96" s="6">
-        <v>4055352</v>
+        <v>4055351</v>
       </c>
       <c r="F96" s="6"/>
-      <c r="G96" s="27" t="s">
-        <v>80</v>
+      <c r="G96" s="29" t="s">
+        <v>81</v>
       </c>
       <c r="H96" s="10" t="s">
         <v>88</v>
       </c>
+      <c r="I96" s="10"/>
       <c r="J96" s="10"/>
       <c r="K96" s="10"/>
       <c r="L96" s="10"/>
     </row>
     <row r="97" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A97" s="27">
-        <v>2213</v>
+      <c r="A97" s="29">
+        <v>2212</v>
       </c>
       <c r="B97" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C97" s="6">
         <v>1</v>
       </c>
-      <c r="D97" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E97" s="6"/>
+      <c r="D97" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" s="6">
+        <v>4055352</v>
+      </c>
       <c r="F97" s="6"/>
-      <c r="G97" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="H97" s="10"/>
-      <c r="I97" s="10"/>
+      <c r="G97" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>89</v>
+      </c>
       <c r="J97" s="10"/>
       <c r="K97" s="10"/>
       <c r="L97" s="10"/>
     </row>
-    <row r="98" customHeight="1" spans="1:12">
-      <c r="A98" s="9">
-        <v>2214</v>
-      </c>
-      <c r="B98" s="1">
-        <v>13</v>
-      </c>
-      <c r="C98" s="1">
-        <v>1</v>
-      </c>
-      <c r="D98" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H98"/>
+    <row r="98" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A98" s="29">
+        <v>2213</v>
+      </c>
+      <c r="B98" s="6">
+        <v>14</v>
+      </c>
+      <c r="C98" s="6">
+        <v>1</v>
+      </c>
+      <c r="D98" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="H98" s="10"/>
+      <c r="I98" s="10"/>
+      <c r="J98" s="10"/>
+      <c r="K98" s="10"/>
+      <c r="L98" s="10"/>
     </row>
     <row r="99" customHeight="1" spans="1:12">
       <c r="A99" s="9">
+        <v>2214</v>
+      </c>
+      <c r="B99" s="1">
+        <v>13</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H99"/>
+    </row>
+    <row r="100" customHeight="1" spans="1:12">
+      <c r="A100" s="9">
         <v>2215</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B100" s="1">
         <v>14</v>
       </c>
-      <c r="C99" s="1">
-        <v>1</v>
-      </c>
-      <c r="D99" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E99" s="1">
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" s="1">
         <v>4055355</v>
       </c>
-      <c r="G99" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H99" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="1:12">
-      <c r="A100" s="29">
+      <c r="G100" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H100" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="1:12">
+      <c r="A101" s="31">
         <v>2301</v>
       </c>
-      <c r="B100" s="29"/>
-      <c r="C100" s="29">
+      <c r="B101" s="31"/>
+      <c r="C101" s="31">
         <v>2</v>
       </c>
-      <c r="D100" s="29" t="b">
+      <c r="D101" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="E100" s="29"/>
-      <c r="F100" s="29"/>
-      <c r="G100" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="1:12">
-      <c r="A101" s="29">
+      <c r="E101" s="31"/>
+      <c r="F101" s="31"/>
+      <c r="G101" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="1:12">
+      <c r="A102" s="31">
         <v>2302</v>
       </c>
-      <c r="B101" s="29">
-        <v>1</v>
-      </c>
-      <c r="C101" s="29">
-        <v>1</v>
-      </c>
-      <c r="D101" s="29" t="b">
+      <c r="B102" s="31">
+        <v>1</v>
+      </c>
+      <c r="C102" s="31">
+        <v>1</v>
+      </c>
+      <c r="D102" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="E101" s="29"/>
-      <c r="F101" s="29"/>
-      <c r="G101" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" spans="1:12">
-      <c r="A102" s="29">
+      <c r="E102" s="31"/>
+      <c r="F102" s="31"/>
+      <c r="G102" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="1:12">
+      <c r="A103" s="31">
         <v>2303</v>
       </c>
-      <c r="B102" s="29">
-        <v>1</v>
-      </c>
-      <c r="C102" s="29">
-        <v>1</v>
-      </c>
-      <c r="D102" s="29" t="b">
+      <c r="B103" s="31">
+        <v>1</v>
+      </c>
+      <c r="C103" s="31">
+        <v>1</v>
+      </c>
+      <c r="D103" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="E102" s="29">
+      <c r="E103" s="31">
         <v>4055371</v>
       </c>
-      <c r="F102" s="29"/>
-      <c r="G102" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H102" s="10" t="s">
+      <c r="F103" s="31"/>
+      <c r="G103" s="1" t="s">
         <v>90</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -4466,14 +4493,14 @@
         <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -4482,7 +4509,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4492,14 +4519,14 @@
         <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4507,14 +4534,14 @@
         <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4522,14 +4549,14 @@
         <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4537,14 +4564,14 @@
         <v>2205</v>
       </c>
       <c r="J9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
         <v>2205_</v>
       </c>
       <c r="M9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4552,14 +4579,14 @@
         <v>2206</v>
       </c>
       <c r="J10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>2206_</v>
       </c>
       <c r="M10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4567,14 +4594,14 @@
         <v>2207</v>
       </c>
       <c r="J11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>2207_</v>
       </c>
       <c r="M11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4582,14 +4609,14 @@
         <v>2208</v>
       </c>
       <c r="J12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>2208_</v>
       </c>
       <c r="M12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4597,32 +4624,32 @@
         <v>2209</v>
       </c>
       <c r="J13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>2209_</v>
       </c>
       <c r="M13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I14">
         <v>2210</v>
       </c>
       <c r="J14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>2210_</v>
       </c>
       <c r="M14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4630,14 +4657,14 @@
         <v>2211</v>
       </c>
       <c r="J15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>2211_</v>
       </c>
       <c r="M15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4645,14 +4672,14 @@
         <v>2212</v>
       </c>
       <c r="J16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>2212_</v>
       </c>
       <c r="M16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4660,14 +4687,14 @@
         <v>2213</v>
       </c>
       <c r="J17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>2213_</v>
       </c>
       <c r="M17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4675,29 +4702,29 @@
         <v>2214</v>
       </c>
       <c r="J18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>2214_</v>
       </c>
       <c r="M18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="113">
   <si>
     <t>序号</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>游戏操作已教学完成，剩下的就交给您自由探索了！</t>
   </si>
   <si>
     <t>建筑-愤怒的小鸟-升到2级</t>
@@ -2427,13 +2430,15 @@
       <c r="D26" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="E26" s="15"/>
+      <c r="E26" s="15">
+        <v>4055144</v>
+      </c>
       <c r="F26" s="15"/>
       <c r="G26" s="23" t="s">
         <v>31</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
@@ -2458,10 +2463,10 @@
       </c>
       <c r="F27" s="16"/>
       <c r="G27" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
@@ -2486,10 +2491,10 @@
       </c>
       <c r="F28" s="16"/>
       <c r="G28" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
@@ -2514,10 +2519,10 @@
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
@@ -2542,10 +2547,10 @@
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
@@ -2566,7 +2571,7 @@
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
       <c r="G31" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>35</v>
@@ -2594,10 +2599,10 @@
       </c>
       <c r="F32" s="16"/>
       <c r="G32" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
@@ -2622,10 +2627,10 @@
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I33" s="17"/>
       <c r="J33" s="17"/>
@@ -2650,10 +2655,10 @@
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I34" s="17"/>
       <c r="J34" s="17"/>
@@ -2674,7 +2679,7 @@
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
       <c r="G35" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>35</v>
@@ -2698,7 +2703,7 @@
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
       <c r="G36" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>35</v>
@@ -2722,7 +2727,7 @@
       <c r="E37" s="16"/>
       <c r="F37" s="16"/>
       <c r="G37" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>35</v>
@@ -2746,7 +2751,7 @@
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
       <c r="G38" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>35</v>
@@ -2772,10 +2777,10 @@
       </c>
       <c r="F39" s="15"/>
       <c r="G39" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -2796,7 +2801,7 @@
       <c r="E40" s="16"/>
       <c r="F40" s="16"/>
       <c r="G40" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>35</v>
@@ -2824,10 +2829,10 @@
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
@@ -2848,7 +2853,7 @@
       <c r="E42" s="16"/>
       <c r="F42" s="16"/>
       <c r="G42" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>35</v>
@@ -2874,7 +2879,7 @@
       <c r="E43" s="16"/>
       <c r="F43" s="16"/>
       <c r="G43" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>35</v>
@@ -2900,10 +2905,10 @@
       </c>
       <c r="F44" s="15"/>
       <c r="G44" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
@@ -2926,10 +2931,10 @@
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
@@ -2954,10 +2959,10 @@
       </c>
       <c r="F46" s="15"/>
       <c r="G46" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
@@ -2982,10 +2987,10 @@
       </c>
       <c r="F47" s="15"/>
       <c r="G47" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -3010,10 +3015,10 @@
       </c>
       <c r="F48" s="15"/>
       <c r="G48" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
@@ -3034,7 +3039,7 @@
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
       <c r="G49" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>35</v>
@@ -3056,7 +3061,7 @@
       </c>
       <c r="F50" s="15"/>
       <c r="G50" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>35</v>
@@ -3084,10 +3089,10 @@
       </c>
       <c r="F51" s="15"/>
       <c r="G51" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="17"/>
@@ -3112,10 +3117,10 @@
       </c>
       <c r="F52" s="15"/>
       <c r="G52" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="17"/>
@@ -3140,10 +3145,10 @@
       </c>
       <c r="F53" s="15"/>
       <c r="G53" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17"/>
@@ -3164,7 +3169,7 @@
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
       <c r="G54" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>35</v>
@@ -3192,10 +3197,10 @@
       </c>
       <c r="F55" s="15"/>
       <c r="G55" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="17"/>
@@ -3220,10 +3225,10 @@
       </c>
       <c r="F56" s="15"/>
       <c r="G56" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I56" s="17"/>
       <c r="J56" s="17"/>
@@ -3244,7 +3249,7 @@
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H57" s="10" t="s">
         <v>35</v>
@@ -3268,7 +3273,7 @@
       <c r="E58" s="15"/>
       <c r="F58" s="15"/>
       <c r="G58" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>35</v>
@@ -3296,10 +3301,10 @@
       </c>
       <c r="F59" s="15"/>
       <c r="G59" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I59" s="17"/>
       <c r="J59" s="17"/>
@@ -3324,10 +3329,10 @@
       </c>
       <c r="F60" s="15"/>
       <c r="G60" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
@@ -3348,7 +3353,7 @@
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
       <c r="G61" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>35</v>
@@ -3372,7 +3377,7 @@
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
       <c r="G62" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>35</v>
@@ -3400,10 +3405,10 @@
       </c>
       <c r="F63" s="16"/>
       <c r="G63" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
@@ -3428,10 +3433,10 @@
       </c>
       <c r="F64" s="16"/>
       <c r="G64" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
@@ -3456,10 +3461,10 @@
       </c>
       <c r="F65" s="16"/>
       <c r="G65" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
@@ -3484,10 +3489,10 @@
       </c>
       <c r="F66" s="16"/>
       <c r="G66" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
@@ -3512,10 +3517,10 @@
       </c>
       <c r="F67" s="16"/>
       <c r="G67" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
@@ -3536,7 +3541,7 @@
       <c r="E68" s="15"/>
       <c r="F68" s="15"/>
       <c r="G68" s="23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H68" s="10" t="s">
         <v>35</v>
@@ -3564,10 +3569,10 @@
       </c>
       <c r="F69" s="15"/>
       <c r="G69" s="23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I69" s="17"/>
       <c r="J69" s="17"/>
@@ -3586,7 +3591,7 @@
       <c r="E70" s="25"/>
       <c r="F70" s="15"/>
       <c r="G70" s="23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I70" s="17"/>
       <c r="J70" s="17"/>
@@ -3607,7 +3612,7 @@
       <c r="E71" s="15"/>
       <c r="F71" s="15"/>
       <c r="G71" s="23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H71" s="10"/>
       <c r="I71" s="17"/>
@@ -3633,10 +3638,10 @@
       </c>
       <c r="F72" s="15"/>
       <c r="G72" s="23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I72" s="17"/>
       <c r="J72" s="17"/>
@@ -3657,7 +3662,7 @@
       <c r="E73" s="16"/>
       <c r="F73" s="16"/>
       <c r="G73" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>35</v>
@@ -3681,7 +3686,7 @@
       <c r="E74" s="16"/>
       <c r="F74" s="16"/>
       <c r="G74" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H74" s="10" t="s">
         <v>35</v>
@@ -3709,10 +3714,10 @@
       </c>
       <c r="F75" s="16"/>
       <c r="G75" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
@@ -3733,7 +3738,7 @@
       <c r="E76" s="15"/>
       <c r="F76" s="15"/>
       <c r="G76" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H76" s="10" t="s">
         <v>35</v>
@@ -3761,10 +3766,10 @@
       </c>
       <c r="F77" s="15"/>
       <c r="G77" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
@@ -3789,10 +3794,10 @@
       </c>
       <c r="F78" s="15"/>
       <c r="G78" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I78" s="17"/>
       <c r="J78" s="17"/>
@@ -3817,10 +3822,10 @@
       </c>
       <c r="F79" s="15"/>
       <c r="G79" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I79" s="17"/>
       <c r="J79" s="17"/>
@@ -3845,10 +3850,10 @@
       </c>
       <c r="F80" s="15"/>
       <c r="G80" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I80" s="17"/>
       <c r="J80" s="17"/>
@@ -3873,10 +3878,10 @@
       </c>
       <c r="F81" s="15"/>
       <c r="G81" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I81" s="17"/>
       <c r="J81" s="17"/>
@@ -3901,10 +3906,10 @@
       </c>
       <c r="F82" s="15"/>
       <c r="G82" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I82" s="17"/>
       <c r="J82" s="17"/>
@@ -3927,7 +3932,7 @@
       <c r="E83" s="27"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H83" s="10"/>
       <c r="I83" s="17"/>
@@ -3953,10 +3958,10 @@
       </c>
       <c r="F84" s="28"/>
       <c r="G84" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
@@ -3981,10 +3986,10 @@
       </c>
       <c r="F85" s="28"/>
       <c r="G85" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
@@ -4009,10 +4014,10 @@
       </c>
       <c r="F86" s="9"/>
       <c r="G86" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H86" s="30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
@@ -4035,10 +4040,10 @@
         <v>4055342</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:12">
@@ -4058,10 +4063,10 @@
         <v>4055343</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89" s="6" customFormat="1" customHeight="1" spans="1:12">
@@ -4082,10 +4087,10 @@
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="10"/>
@@ -4110,10 +4115,10 @@
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
@@ -4138,10 +4143,10 @@
       </c>
       <c r="F91" s="6"/>
       <c r="G91" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="10"/>
@@ -4166,10 +4171,10 @@
       </c>
       <c r="F92" s="6"/>
       <c r="G92" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="10"/>
@@ -4194,10 +4199,10 @@
       </c>
       <c r="F93" s="6"/>
       <c r="G93" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
@@ -4220,7 +4225,7 @@
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
       <c r="G94" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H94" s="10"/>
       <c r="I94" s="10"/>
@@ -4246,10 +4251,10 @@
       </c>
       <c r="F95" s="6"/>
       <c r="G95" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J95" s="10"/>
       <c r="K95" s="10"/>
@@ -4273,10 +4278,10 @@
       </c>
       <c r="F96" s="6"/>
       <c r="G96" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="10"/>
@@ -4301,10 +4306,10 @@
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J97" s="10"/>
       <c r="K97" s="10"/>
@@ -4326,7 +4331,7 @@
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
       <c r="G98" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H98" s="10"/>
       <c r="I98" s="10"/>
@@ -4348,7 +4353,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H99"/>
     </row>
@@ -4369,10 +4374,10 @@
         <v>4055355</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H100" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:12">
@@ -4389,7 +4394,7 @@
       <c r="E101" s="31"/>
       <c r="F101" s="31"/>
       <c r="G101" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:12">
@@ -4408,7 +4413,7 @@
       <c r="E102" s="31"/>
       <c r="F102" s="31"/>
       <c r="G102" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:12">
@@ -4429,10 +4434,10 @@
       </c>
       <c r="F103" s="31"/>
       <c r="G103" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -4493,14 +4498,14 @@
         <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -4509,7 +4514,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4519,14 +4524,14 @@
         <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4534,14 +4539,14 @@
         <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4549,14 +4554,14 @@
         <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4564,14 +4569,14 @@
         <v>2205</v>
       </c>
       <c r="J9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
         <v>2205_</v>
       </c>
       <c r="M9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4579,14 +4584,14 @@
         <v>2206</v>
       </c>
       <c r="J10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>2206_</v>
       </c>
       <c r="M10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4594,14 +4599,14 @@
         <v>2207</v>
       </c>
       <c r="J11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>2207_</v>
       </c>
       <c r="M11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4609,14 +4614,14 @@
         <v>2208</v>
       </c>
       <c r="J12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>2208_</v>
       </c>
       <c r="M12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4624,32 +4629,32 @@
         <v>2209</v>
       </c>
       <c r="J13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>2209_</v>
       </c>
       <c r="M13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I14">
         <v>2210</v>
       </c>
       <c r="J14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>2210_</v>
       </c>
       <c r="M14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4657,14 +4662,14 @@
         <v>2211</v>
       </c>
       <c r="J15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>2211_</v>
       </c>
       <c r="M15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4672,14 +4677,14 @@
         <v>2212</v>
       </c>
       <c r="J16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>2212_</v>
       </c>
       <c r="M16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4687,14 +4692,14 @@
         <v>2213</v>
       </c>
       <c r="J17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>2213_</v>
       </c>
       <c r="M17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4702,29 +4707,29 @@
         <v>2214</v>
       </c>
       <c r="J18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>2214_</v>
       </c>
       <c r="M18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -4007,7 +4007,7 @@
         <v>2</v>
       </c>
       <c r="D86" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="9">
         <v>4055341</v>
@@ -4034,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="D87" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" s="1">
         <v>4055342</v>
@@ -4057,7 +4057,7 @@
         <v>1</v>
       </c>
       <c r="D88" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" s="1">
         <v>4055343</v>
@@ -4080,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="D89" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" s="6">
         <v>4055344</v>
@@ -4108,7 +4108,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" s="6">
         <v>4055345</v>
@@ -4136,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="D91" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" s="6">
         <v>4055346</v>
@@ -4164,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="D92" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" s="6">
         <v>4055347</v>
@@ -4192,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" s="6">
         <v>4055348</v>
@@ -4220,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="D94" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -4244,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="D95" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" s="6">
         <v>4055350</v>
@@ -4271,7 +4271,7 @@
         <v>1</v>
       </c>
       <c r="D96" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" s="6">
         <v>4055351</v>
@@ -4299,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="D97" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" s="6">
         <v>4055352</v>
@@ -4326,7 +4326,7 @@
         <v>1</v>
       </c>
       <c r="D98" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
@@ -4350,7 +4350,7 @@
         <v>1</v>
       </c>
       <c r="D99" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" s="9" t="s">
         <v>82</v>
@@ -4368,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" s="1">
         <v>4055355</v>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="114">
   <si>
     <t>序号</t>
   </si>
@@ -233,13 +233,13 @@
     <t>初入游戏-创建新号到经营大厅</t>
   </si>
   <si>
-    <t>欢迎来到GECA黄金星娱乐城，梦想由此启航</t>
-  </si>
-  <si>
-    <t>娱乐城处处是机遇</t>
-  </si>
-  <si>
-    <t>先前往SLOT区试试手气</t>
+    <t>欢迎来到GECA黄金星娱乐城，我是面试官Miss.wang，你是来参加面试的嘛？</t>
+  </si>
+  <si>
+    <t>是的，我会让你大吃一惊的</t>
+  </si>
+  <si>
+    <t>好的，你展示你的技术吧</t>
   </si>
   <si>
     <t>点击&lt;color=#00bfff&gt;旋转&lt;/color&gt;按钮，赢得大奖</t>
@@ -251,10 +251,13 @@
     <t>恭喜！将聘请您成为GECA黄金星娱乐城经理人</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>很高兴加入，我会把娱乐城发展为全球第一城</t>
   </si>
   <si>
-    <t>持续研发游戏、扩建新区，提升收益发展娱乐城</t>
+    <t>接下来我带你熟悉一下你的工作</t>
   </si>
   <si>
     <t>开始经营娱乐城</t>
@@ -532,7 +535,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,6 +581,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1090,137 +1100,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1275,13 +1285,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1293,7 +1309,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1919,13 +1935,13 @@
       <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A6" s="14">
@@ -1943,13 +1959,13 @@
       <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A7" s="14">
@@ -1967,13 +1983,13 @@
       <c r="G7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A8" s="14">
@@ -1994,10 +2010,10 @@
       <c r="H8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A9" s="14">
@@ -2018,10 +2034,10 @@
       <c r="H9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A10" s="14">
@@ -2039,13 +2055,14 @@
       <c r="G10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
+      <c r="J10" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A11" s="14">
@@ -2064,12 +2081,12 @@
         <v>16</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
+        <v>24</v>
+      </c>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A12" s="14">
@@ -2087,13 +2104,12 @@
       <c r="G12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
+      <c r="H12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A13" s="14">
@@ -2111,96 +2127,96 @@
       <c r="G13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
+      <c r="H13" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
     </row>
     <row r="14" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="18">
+      <c r="A14" s="20">
         <v>1010</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="18">
+      <c r="A15" s="20">
         <v>1011</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="18">
+      <c r="A16" s="20">
         <v>1012</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
       <c r="G16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="18">
+      <c r="A17" s="20">
         <v>1013</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
       <c r="G17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="21">
+      <c r="A18" s="23">
         <v>1201</v>
       </c>
       <c r="B18" s="16">
@@ -2216,11 +2232,11 @@
         <v>4055121</v>
       </c>
       <c r="F18" s="16"/>
-      <c r="G18" s="22" t="s">
-        <v>26</v>
+      <c r="G18" s="24" t="s">
+        <v>27</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
@@ -2228,7 +2244,7 @@
       <c r="L18" s="10"/>
     </row>
     <row r="19" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="21">
+      <c r="A19" s="23">
         <v>1202</v>
       </c>
       <c r="B19" s="16">
@@ -2244,11 +2260,11 @@
         <v>4055122</v>
       </c>
       <c r="F19" s="16"/>
-      <c r="G19" s="22" t="s">
-        <v>26</v>
+      <c r="G19" s="24" t="s">
+        <v>27</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
@@ -2256,7 +2272,7 @@
       <c r="L19" s="10"/>
     </row>
     <row r="20" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="21">
+      <c r="A20" s="23">
         <v>1203</v>
       </c>
       <c r="B20" s="16">
@@ -2272,11 +2288,11 @@
         <v>4055123</v>
       </c>
       <c r="F20" s="16"/>
-      <c r="G20" s="22" t="s">
-        <v>26</v>
+      <c r="G20" s="24" t="s">
+        <v>27</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
@@ -2284,7 +2300,7 @@
       <c r="L20" s="10"/>
     </row>
     <row r="21" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="21">
+      <c r="A21" s="23">
         <v>1204</v>
       </c>
       <c r="B21" s="16">
@@ -2300,11 +2316,11 @@
         <v>4055124</v>
       </c>
       <c r="F21" s="16"/>
-      <c r="G21" s="22" t="s">
-        <v>26</v>
+      <c r="G21" s="24" t="s">
+        <v>27</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
@@ -2328,16 +2344,16 @@
         <v>4055141</v>
       </c>
       <c r="F22" s="15"/>
-      <c r="G22" s="23" t="s">
-        <v>31</v>
+      <c r="G22" s="25" t="s">
+        <v>32</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
+        <v>33</v>
+      </c>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
     </row>
     <row r="23" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A23" s="14">
@@ -2356,16 +2372,16 @@
         <v>4055142</v>
       </c>
       <c r="F23" s="15"/>
-      <c r="G23" s="23" t="s">
-        <v>31</v>
+      <c r="G23" s="25" t="s">
+        <v>32</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
+        <v>34</v>
+      </c>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
     </row>
     <row r="24" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A24" s="14">
@@ -2384,16 +2400,16 @@
         <v>4055143</v>
       </c>
       <c r="F24" s="15"/>
-      <c r="G24" s="23" t="s">
-        <v>31</v>
+      <c r="G24" s="25" t="s">
+        <v>32</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
+        <v>35</v>
+      </c>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
     </row>
     <row r="25" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A25" s="14">
@@ -2408,16 +2424,16 @@
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="15"/>
-      <c r="G25" s="23" t="s">
-        <v>31</v>
+      <c r="G25" s="25" t="s">
+        <v>32</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
     </row>
     <row r="26" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A26" s="14">
@@ -2434,19 +2450,19 @@
         <v>4055144</v>
       </c>
       <c r="F26" s="15"/>
-      <c r="G26" s="23" t="s">
-        <v>31</v>
+      <c r="G26" s="25" t="s">
+        <v>32</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
+        <v>37</v>
+      </c>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
     </row>
     <row r="27" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="21">
+      <c r="A27" s="23">
         <v>1401</v>
       </c>
       <c r="B27" s="16">
@@ -2462,11 +2478,11 @@
         <v>4055161</v>
       </c>
       <c r="F27" s="16"/>
-      <c r="G27" s="22" t="s">
-        <v>37</v>
+      <c r="G27" s="24" t="s">
+        <v>38</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
@@ -2474,7 +2490,7 @@
       <c r="L27" s="10"/>
     </row>
     <row r="28" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="21">
+      <c r="A28" s="23">
         <v>1402</v>
       </c>
       <c r="B28" s="16">
@@ -2490,11 +2506,11 @@
         <v>4055162</v>
       </c>
       <c r="F28" s="16"/>
-      <c r="G28" s="22" t="s">
-        <v>37</v>
+      <c r="G28" s="24" t="s">
+        <v>38</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
@@ -2502,7 +2518,7 @@
       <c r="L28" s="10"/>
     </row>
     <row r="29" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="21">
+      <c r="A29" s="23">
         <v>1403</v>
       </c>
       <c r="B29" s="16">
@@ -2518,11 +2534,11 @@
         <v>4055163</v>
       </c>
       <c r="F29" s="16"/>
-      <c r="G29" s="22" t="s">
-        <v>37</v>
+      <c r="G29" s="24" t="s">
+        <v>38</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
@@ -2530,7 +2546,7 @@
       <c r="L29" s="10"/>
     </row>
     <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="21">
+      <c r="A30" s="23">
         <v>1404</v>
       </c>
       <c r="B30" s="16">
@@ -2546,11 +2562,11 @@
         <v>4055164</v>
       </c>
       <c r="F30" s="16"/>
-      <c r="G30" s="22" t="s">
-        <v>37</v>
+      <c r="G30" s="24" t="s">
+        <v>38</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
@@ -2558,7 +2574,7 @@
       <c r="L30" s="10"/>
     </row>
     <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="21">
+      <c r="A31" s="23">
         <v>1405</v>
       </c>
       <c r="B31" s="16"/>
@@ -2570,11 +2586,11 @@
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
-      <c r="G31" s="22" t="s">
-        <v>37</v>
+      <c r="G31" s="24" t="s">
+        <v>38</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I31" s="10"/>
       <c r="J31" s="10"/>
@@ -2582,7 +2598,7 @@
       <c r="L31" s="10"/>
     </row>
     <row r="32" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="21">
+      <c r="A32" s="23">
         <v>1406</v>
       </c>
       <c r="B32" s="16">
@@ -2598,11 +2614,11 @@
         <v>4055165</v>
       </c>
       <c r="F32" s="16"/>
-      <c r="G32" s="22" t="s">
-        <v>37</v>
+      <c r="G32" s="24" t="s">
+        <v>38</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
@@ -2626,16 +2642,16 @@
         <v>4055181</v>
       </c>
       <c r="F33" s="15"/>
-      <c r="G33" s="23" t="s">
-        <v>43</v>
+      <c r="G33" s="25" t="s">
+        <v>44</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
+        <v>45</v>
+      </c>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
     </row>
     <row r="34" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A34" s="14">
@@ -2654,16 +2670,16 @@
         <v>4055182</v>
       </c>
       <c r="F34" s="15"/>
-      <c r="G34" s="23" t="s">
-        <v>43</v>
+      <c r="G34" s="25" t="s">
+        <v>44</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
+        <v>46</v>
+      </c>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
     </row>
     <row r="35" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A35" s="14">
@@ -2678,16 +2694,16 @@
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
-      <c r="G35" s="23" t="s">
-        <v>43</v>
+      <c r="G35" s="25" t="s">
+        <v>44</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
     </row>
     <row r="36" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A36" s="14">
@@ -2702,19 +2718,19 @@
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
-      <c r="G36" s="23" t="s">
-        <v>43</v>
+      <c r="G36" s="25" t="s">
+        <v>44</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
     </row>
     <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="21">
+      <c r="A37" s="23">
         <v>1601</v>
       </c>
       <c r="B37" s="16"/>
@@ -2726,11 +2742,11 @@
       </c>
       <c r="E37" s="16"/>
       <c r="F37" s="16"/>
-      <c r="G37" s="22" t="s">
-        <v>46</v>
+      <c r="G37" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -2738,7 +2754,7 @@
       <c r="L37" s="10"/>
     </row>
     <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="21">
+      <c r="A38" s="23">
         <v>1602</v>
       </c>
       <c r="B38" s="16"/>
@@ -2750,11 +2766,11 @@
       </c>
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
-      <c r="G38" s="22" t="s">
-        <v>46</v>
+      <c r="G38" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
@@ -2762,7 +2778,7 @@
       <c r="L38" s="10"/>
     </row>
     <row r="39" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A39" s="21">
+      <c r="A39" s="23">
         <v>1603</v>
       </c>
       <c r="B39" s="16"/>
@@ -2776,11 +2792,11 @@
         <v>4055203</v>
       </c>
       <c r="F39" s="15"/>
-      <c r="G39" s="22" t="s">
-        <v>46</v>
+      <c r="G39" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -2788,7 +2804,7 @@
       <c r="L39" s="10"/>
     </row>
     <row r="40" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="21">
+      <c r="A40" s="23">
         <v>1604</v>
       </c>
       <c r="B40" s="16"/>
@@ -2800,11 +2816,11 @@
       </c>
       <c r="E40" s="16"/>
       <c r="F40" s="16"/>
-      <c r="G40" s="22" t="s">
-        <v>46</v>
+      <c r="G40" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
@@ -2812,7 +2828,7 @@
       <c r="L40" s="10"/>
     </row>
     <row r="41" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="21">
+      <c r="A41" s="23">
         <v>1605</v>
       </c>
       <c r="B41" s="16">
@@ -2828,11 +2844,11 @@
         <v>4055204</v>
       </c>
       <c r="F41" s="15"/>
-      <c r="G41" s="22" t="s">
-        <v>46</v>
+      <c r="G41" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
@@ -2840,7 +2856,7 @@
       <c r="L41" s="10"/>
     </row>
     <row r="42" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="21">
+      <c r="A42" s="23">
         <v>1606</v>
       </c>
       <c r="B42" s="16"/>
@@ -2852,11 +2868,11 @@
       </c>
       <c r="E42" s="16"/>
       <c r="F42" s="16"/>
-      <c r="G42" s="22" t="s">
-        <v>46</v>
+      <c r="G42" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
@@ -2864,7 +2880,7 @@
       <c r="L42" s="10"/>
     </row>
     <row r="43" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="21">
+      <c r="A43" s="23">
         <v>1607</v>
       </c>
       <c r="B43" s="16">
@@ -2878,11 +2894,11 @@
       </c>
       <c r="E43" s="16"/>
       <c r="F43" s="16"/>
-      <c r="G43" s="22" t="s">
-        <v>46</v>
+      <c r="G43" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
@@ -2890,7 +2906,7 @@
       <c r="L43" s="10"/>
     </row>
     <row r="44" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="21">
+      <c r="A44" s="23">
         <v>1608</v>
       </c>
       <c r="B44" s="16"/>
@@ -2904,11 +2920,11 @@
         <v>4055205</v>
       </c>
       <c r="F44" s="15"/>
-      <c r="G44" s="22" t="s">
-        <v>46</v>
+      <c r="G44" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
@@ -2916,7 +2932,7 @@
       <c r="L44" s="10"/>
     </row>
     <row r="45" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="21">
+      <c r="A45" s="23">
         <v>1609</v>
       </c>
       <c r="B45" s="16"/>
@@ -2930,11 +2946,11 @@
         <v>4055206</v>
       </c>
       <c r="F45" s="15"/>
-      <c r="G45" s="22" t="s">
-        <v>46</v>
+      <c r="G45" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
@@ -2942,7 +2958,7 @@
       <c r="L45" s="10"/>
     </row>
     <row r="46" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="21">
+      <c r="A46" s="23">
         <v>1610</v>
       </c>
       <c r="B46" s="16">
@@ -2958,11 +2974,11 @@
         <v>4055207</v>
       </c>
       <c r="F46" s="15"/>
-      <c r="G46" s="22" t="s">
-        <v>46</v>
+      <c r="G46" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
@@ -2970,7 +2986,7 @@
       <c r="L46" s="10"/>
     </row>
     <row r="47" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="21">
+      <c r="A47" s="23">
         <v>1611</v>
       </c>
       <c r="B47" s="16">
@@ -2986,11 +3002,11 @@
         <v>4055208</v>
       </c>
       <c r="F47" s="15"/>
-      <c r="G47" s="22" t="s">
-        <v>46</v>
+      <c r="G47" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -2998,7 +3014,7 @@
       <c r="L47" s="10"/>
     </row>
     <row r="48" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="21">
+      <c r="A48" s="23">
         <v>1612</v>
       </c>
       <c r="B48" s="16">
@@ -3014,11 +3030,11 @@
         <v>4055209</v>
       </c>
       <c r="F48" s="15"/>
-      <c r="G48" s="22" t="s">
-        <v>46</v>
+      <c r="G48" s="24" t="s">
+        <v>47</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
@@ -3038,16 +3054,16 @@
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
-      <c r="G49" s="23" t="s">
-        <v>54</v>
+      <c r="G49" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
     </row>
     <row r="50" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A50" s="14">
@@ -3060,16 +3076,16 @@
         <v>1</v>
       </c>
       <c r="F50" s="15"/>
-      <c r="G50" s="23" t="s">
-        <v>54</v>
+      <c r="G50" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
     </row>
     <row r="51" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A51" s="14">
@@ -3088,16 +3104,16 @@
         <v>4055222</v>
       </c>
       <c r="F51" s="15"/>
-      <c r="G51" s="23" t="s">
-        <v>54</v>
+      <c r="G51" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
+        <v>56</v>
+      </c>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="18"/>
     </row>
     <row r="52" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A52" s="14">
@@ -3116,16 +3132,16 @@
         <v>4055223</v>
       </c>
       <c r="F52" s="15"/>
-      <c r="G52" s="23" t="s">
-        <v>54</v>
+      <c r="G52" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
+        <v>57</v>
+      </c>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
     </row>
     <row r="53" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A53" s="14">
@@ -3144,16 +3160,16 @@
         <v>4055224</v>
       </c>
       <c r="F53" s="15"/>
-      <c r="G53" s="23" t="s">
-        <v>54</v>
+      <c r="G53" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
+        <v>58</v>
+      </c>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
     </row>
     <row r="54" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A54" s="14">
@@ -3168,16 +3184,16 @@
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
-      <c r="G54" s="23" t="s">
-        <v>54</v>
+      <c r="G54" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
     </row>
     <row r="55" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A55" s="14">
@@ -3196,16 +3212,16 @@
         <v>4055225</v>
       </c>
       <c r="F55" s="15"/>
-      <c r="G55" s="23" t="s">
-        <v>54</v>
+      <c r="G55" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
+        <v>59</v>
+      </c>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
     </row>
     <row r="56" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A56" s="14">
@@ -3224,16 +3240,16 @@
         <v>4055226</v>
       </c>
       <c r="F56" s="15"/>
-      <c r="G56" s="23" t="s">
-        <v>54</v>
+      <c r="G56" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
     </row>
     <row r="57" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A57" s="14">
@@ -3248,16 +3264,16 @@
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
-      <c r="G57" s="23" t="s">
-        <v>54</v>
+      <c r="G57" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
     </row>
     <row r="58" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A58" s="14">
@@ -3272,16 +3288,16 @@
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="15"/>
-      <c r="G58" s="23" t="s">
-        <v>54</v>
+      <c r="G58" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="18"/>
     </row>
     <row r="59" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A59" s="14">
@@ -3300,16 +3316,16 @@
         <v>4055227</v>
       </c>
       <c r="F59" s="15"/>
-      <c r="G59" s="23" t="s">
-        <v>54</v>
+      <c r="G59" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
+        <v>61</v>
+      </c>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
+      <c r="L59" s="18"/>
     </row>
     <row r="60" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A60" s="14">
@@ -3328,19 +3344,19 @@
         <v>4055228</v>
       </c>
       <c r="F60" s="15"/>
-      <c r="G60" s="23" t="s">
-        <v>54</v>
+      <c r="G60" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
+        <v>62</v>
+      </c>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
     </row>
     <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="21">
+      <c r="A61" s="23">
         <v>1801</v>
       </c>
       <c r="B61" s="16"/>
@@ -3352,11 +3368,11 @@
       </c>
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
-      <c r="G61" s="22" t="s">
-        <v>62</v>
+      <c r="G61" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
@@ -3364,7 +3380,7 @@
       <c r="L61" s="10"/>
     </row>
     <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A62" s="21">
+      <c r="A62" s="23">
         <v>1802</v>
       </c>
       <c r="B62" s="16"/>
@@ -3376,11 +3392,11 @@
       </c>
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
-      <c r="G62" s="22" t="s">
-        <v>62</v>
+      <c r="G62" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
@@ -3388,7 +3404,7 @@
       <c r="L62" s="10"/>
     </row>
     <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A63" s="21">
+      <c r="A63" s="23">
         <v>1803</v>
       </c>
       <c r="B63" s="16">
@@ -3404,11 +3420,11 @@
         <v>4055243</v>
       </c>
       <c r="F63" s="16"/>
-      <c r="G63" s="22" t="s">
-        <v>62</v>
+      <c r="G63" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
@@ -3416,7 +3432,7 @@
       <c r="L63" s="10"/>
     </row>
     <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A64" s="21">
+      <c r="A64" s="23">
         <v>1804</v>
       </c>
       <c r="B64" s="16">
@@ -3432,11 +3448,11 @@
         <v>4055244</v>
       </c>
       <c r="F64" s="16"/>
-      <c r="G64" s="22" t="s">
-        <v>62</v>
+      <c r="G64" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
@@ -3444,7 +3460,7 @@
       <c r="L64" s="10"/>
     </row>
     <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A65" s="21">
+      <c r="A65" s="23">
         <v>1805</v>
       </c>
       <c r="B65" s="16">
@@ -3460,11 +3476,11 @@
         <v>4055245</v>
       </c>
       <c r="F65" s="16"/>
-      <c r="G65" s="22" t="s">
-        <v>62</v>
+      <c r="G65" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
@@ -3472,7 +3488,7 @@
       <c r="L65" s="10"/>
     </row>
     <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="21">
+      <c r="A66" s="23">
         <v>1806</v>
       </c>
       <c r="B66" s="16">
@@ -3488,11 +3504,11 @@
         <v>4055246</v>
       </c>
       <c r="F66" s="16"/>
-      <c r="G66" s="22" t="s">
-        <v>62</v>
+      <c r="G66" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
@@ -3500,7 +3516,7 @@
       <c r="L66" s="10"/>
     </row>
     <row r="67" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="21">
+      <c r="A67" s="23">
         <v>1807</v>
       </c>
       <c r="B67" s="16">
@@ -3516,11 +3532,11 @@
         <v>4055247</v>
       </c>
       <c r="F67" s="16"/>
-      <c r="G67" s="22" t="s">
-        <v>62</v>
+      <c r="G67" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
@@ -3535,21 +3551,21 @@
       <c r="C68" s="15">
         <v>1</v>
       </c>
-      <c r="D68" s="24" t="b">
+      <c r="D68" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E68" s="15"/>
       <c r="F68" s="15"/>
-      <c r="G68" s="23" t="s">
-        <v>68</v>
+      <c r="G68" s="25" t="s">
+        <v>69</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I68" s="17"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="17"/>
-      <c r="L68" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="18"/>
+      <c r="L68" s="18"/>
     </row>
     <row r="69" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A69" s="14">
@@ -3561,23 +3577,23 @@
       <c r="C69" s="15">
         <v>1</v>
       </c>
-      <c r="D69" s="24" t="b">
+      <c r="D69" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E69" s="15">
         <v>4055263</v>
       </c>
       <c r="F69" s="15"/>
-      <c r="G69" s="23" t="s">
-        <v>68</v>
+      <c r="G69" s="25" t="s">
+        <v>69</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I69" s="17"/>
-      <c r="J69" s="17"/>
-      <c r="K69" s="17"/>
-      <c r="L69" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
+      <c r="L69" s="18"/>
     </row>
     <row r="70" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A70" s="14">
@@ -3585,18 +3601,18 @@
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
-      <c r="D70" s="24" t="b">
+      <c r="D70" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="E70" s="25"/>
+      <c r="E70" s="27"/>
       <c r="F70" s="15"/>
-      <c r="G70" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="I70" s="17"/>
-      <c r="J70" s="17"/>
-      <c r="K70" s="17"/>
-      <c r="L70" s="17"/>
+      <c r="G70" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
     </row>
     <row r="71" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A71" s="14">
@@ -3606,19 +3622,19 @@
       <c r="C71" s="15">
         <v>1</v>
       </c>
-      <c r="D71" s="24" t="b">
+      <c r="D71" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="15"/>
-      <c r="G71" s="23" t="s">
-        <v>68</v>
+      <c r="G71" s="25" t="s">
+        <v>69</v>
       </c>
       <c r="H71" s="10"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="17"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
+      <c r="L71" s="18"/>
     </row>
     <row r="72" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A72" s="14">
@@ -3630,42 +3646,42 @@
       <c r="C72" s="15">
         <v>1</v>
       </c>
-      <c r="D72" s="24" t="b">
+      <c r="D72" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E72" s="15">
         <v>4055264</v>
       </c>
       <c r="F72" s="15"/>
-      <c r="G72" s="23" t="s">
-        <v>68</v>
+      <c r="G72" s="25" t="s">
+        <v>69</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="I72" s="17"/>
-      <c r="J72" s="17"/>
-      <c r="K72" s="17"/>
-      <c r="L72" s="17"/>
+        <v>71</v>
+      </c>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="18"/>
+      <c r="L72" s="18"/>
     </row>
     <row r="73" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A73" s="21">
+      <c r="A73" s="23">
         <v>1981</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16">
         <v>1</v>
       </c>
-      <c r="D73" s="24" t="b">
+      <c r="D73" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E73" s="16"/>
       <c r="F73" s="16"/>
-      <c r="G73" s="22" t="s">
-        <v>71</v>
+      <c r="G73" s="24" t="s">
+        <v>72</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
@@ -3673,23 +3689,23 @@
       <c r="L73" s="10"/>
     </row>
     <row r="74" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="21">
+      <c r="A74" s="23">
         <v>1982</v>
       </c>
       <c r="B74" s="16"/>
       <c r="C74" s="16">
         <v>1</v>
       </c>
-      <c r="D74" s="24" t="b">
+      <c r="D74" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E74" s="16"/>
       <c r="F74" s="16"/>
-      <c r="G74" s="22" t="s">
-        <v>71</v>
+      <c r="G74" s="24" t="s">
+        <v>72</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I74" s="10"/>
       <c r="J74" s="10"/>
@@ -3697,7 +3713,7 @@
       <c r="L74" s="10"/>
     </row>
     <row r="75" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="21">
+      <c r="A75" s="23">
         <v>1983</v>
       </c>
       <c r="B75" s="16">
@@ -3706,18 +3722,18 @@
       <c r="C75" s="16">
         <v>1</v>
       </c>
-      <c r="D75" s="24" t="b">
+      <c r="D75" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E75" s="16">
         <v>4055321</v>
       </c>
       <c r="F75" s="16"/>
-      <c r="G75" s="22" t="s">
-        <v>71</v>
+      <c r="G75" s="24" t="s">
+        <v>72</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
@@ -3732,21 +3748,21 @@
       <c r="C76" s="15">
         <v>1</v>
       </c>
-      <c r="D76" s="24" t="b">
+      <c r="D76" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E76" s="15"/>
       <c r="F76" s="15"/>
-      <c r="G76" s="23" t="s">
-        <v>73</v>
+      <c r="G76" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I76" s="17"/>
-      <c r="J76" s="17"/>
-      <c r="K76" s="17"/>
-      <c r="L76" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="I76" s="18"/>
+      <c r="J76" s="18"/>
+      <c r="K76" s="18"/>
+      <c r="L76" s="18"/>
     </row>
     <row r="77" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A77" s="14">
@@ -3758,23 +3774,23 @@
       <c r="C77" s="15">
         <v>1</v>
       </c>
-      <c r="D77" s="24" t="b">
+      <c r="D77" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E77" s="15">
         <v>4055281</v>
       </c>
       <c r="F77" s="15"/>
-      <c r="G77" s="23" t="s">
-        <v>73</v>
+      <c r="G77" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
-      <c r="K77" s="17"/>
-      <c r="L77" s="17"/>
+        <v>75</v>
+      </c>
+      <c r="I77" s="18"/>
+      <c r="J77" s="18"/>
+      <c r="K77" s="18"/>
+      <c r="L77" s="18"/>
     </row>
     <row r="78" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A78" s="14">
@@ -3786,23 +3802,23 @@
       <c r="C78" s="15">
         <v>1</v>
       </c>
-      <c r="D78" s="24" t="b">
+      <c r="D78" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E78" s="15">
         <v>4055282</v>
       </c>
       <c r="F78" s="15"/>
-      <c r="G78" s="23" t="s">
-        <v>73</v>
+      <c r="G78" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I78" s="17"/>
-      <c r="J78" s="17"/>
-      <c r="K78" s="17"/>
-      <c r="L78" s="17"/>
+        <v>76</v>
+      </c>
+      <c r="I78" s="18"/>
+      <c r="J78" s="18"/>
+      <c r="K78" s="18"/>
+      <c r="L78" s="18"/>
     </row>
     <row r="79" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A79" s="14">
@@ -3814,23 +3830,23 @@
       <c r="C79" s="15">
         <v>1</v>
       </c>
-      <c r="D79" s="24" t="b">
+      <c r="D79" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E79" s="15">
         <v>4055283</v>
       </c>
       <c r="F79" s="15"/>
-      <c r="G79" s="23" t="s">
-        <v>73</v>
+      <c r="G79" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I79" s="17"/>
-      <c r="J79" s="17"/>
-      <c r="K79" s="17"/>
-      <c r="L79" s="17"/>
+        <v>77</v>
+      </c>
+      <c r="I79" s="18"/>
+      <c r="J79" s="18"/>
+      <c r="K79" s="18"/>
+      <c r="L79" s="18"/>
     </row>
     <row r="80" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A80" s="14">
@@ -3842,23 +3858,23 @@
       <c r="C80" s="15">
         <v>1</v>
       </c>
-      <c r="D80" s="24" t="b">
+      <c r="D80" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E80" s="15">
         <v>4055284</v>
       </c>
       <c r="F80" s="15"/>
-      <c r="G80" s="23" t="s">
-        <v>73</v>
+      <c r="G80" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I80" s="17"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="17"/>
-      <c r="L80" s="17"/>
+        <v>76</v>
+      </c>
+      <c r="I80" s="18"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="18"/>
+      <c r="L80" s="18"/>
     </row>
     <row r="81" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A81" s="14">
@@ -3870,23 +3886,23 @@
       <c r="C81" s="15">
         <v>1</v>
       </c>
-      <c r="D81" s="24" t="b">
+      <c r="D81" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E81" s="15">
         <v>4055285</v>
       </c>
       <c r="F81" s="15"/>
-      <c r="G81" s="23" t="s">
-        <v>73</v>
+      <c r="G81" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
-      <c r="K81" s="17"/>
-      <c r="L81" s="17"/>
+        <v>77</v>
+      </c>
+      <c r="I81" s="18"/>
+      <c r="J81" s="18"/>
+      <c r="K81" s="18"/>
+      <c r="L81" s="18"/>
     </row>
     <row r="82" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A82" s="14">
@@ -3898,70 +3914,70 @@
       <c r="C82" s="15">
         <v>1</v>
       </c>
-      <c r="D82" s="24" t="b">
+      <c r="D82" s="26" t="b">
         <v>0</v>
       </c>
       <c r="E82" s="15">
         <v>4055286</v>
       </c>
       <c r="F82" s="15"/>
-      <c r="G82" s="23" t="s">
-        <v>73</v>
+      <c r="G82" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I82" s="17"/>
-      <c r="J82" s="17"/>
-      <c r="K82" s="17"/>
-      <c r="L82" s="17"/>
+        <v>78</v>
+      </c>
+      <c r="I82" s="18"/>
+      <c r="J82" s="18"/>
+      <c r="K82" s="18"/>
+      <c r="L82" s="18"/>
     </row>
     <row r="83" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A83" s="26">
+      <c r="A83" s="28">
         <v>2100</v>
       </c>
-      <c r="B83" s="27">
+      <c r="B83" s="29">
         <v>2</v>
       </c>
-      <c r="C83" s="27">
-        <v>1</v>
-      </c>
-      <c r="D83" s="24" t="b">
+      <c r="C83" s="29">
+        <v>1</v>
+      </c>
+      <c r="D83" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="E83" s="27"/>
-      <c r="F83" s="27"/>
+      <c r="E83" s="29"/>
+      <c r="F83" s="29"/>
       <c r="G83" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H83" s="10"/>
-      <c r="I83" s="17"/>
-      <c r="J83" s="17"/>
-      <c r="K83" s="17"/>
-      <c r="L83" s="17"/>
+      <c r="I83" s="18"/>
+      <c r="J83" s="18"/>
+      <c r="K83" s="18"/>
+      <c r="L83" s="18"/>
     </row>
     <row r="84" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A84" s="28">
+      <c r="A84" s="30">
         <v>2101</v>
       </c>
-      <c r="B84" s="28">
+      <c r="B84" s="30">
         <v>2</v>
       </c>
-      <c r="C84" s="28">
-        <v>1</v>
-      </c>
-      <c r="D84" s="24" t="b">
+      <c r="C84" s="30">
+        <v>1</v>
+      </c>
+      <c r="D84" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="E84" s="28">
+      <c r="E84" s="30">
         <v>4055301</v>
       </c>
-      <c r="F84" s="28"/>
+      <c r="F84" s="30"/>
       <c r="G84" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
@@ -3969,27 +3985,27 @@
       <c r="L84" s="10"/>
     </row>
     <row r="85" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A85" s="28">
+      <c r="A85" s="30">
         <v>2102</v>
       </c>
-      <c r="B85" s="28">
-        <v>1</v>
-      </c>
-      <c r="C85" s="28">
-        <v>1</v>
-      </c>
-      <c r="D85" s="24" t="b">
+      <c r="B85" s="30">
+        <v>1</v>
+      </c>
+      <c r="C85" s="30">
+        <v>1</v>
+      </c>
+      <c r="D85" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="E85" s="28">
+      <c r="E85" s="30">
         <v>4055303</v>
       </c>
-      <c r="F85" s="28"/>
+      <c r="F85" s="30"/>
       <c r="G85" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
@@ -4006,7 +4022,7 @@
       <c r="C86" s="9">
         <v>2</v>
       </c>
-      <c r="D86" s="29" t="b">
+      <c r="D86" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E86" s="9">
@@ -4014,14 +4030,14 @@
       </c>
       <c r="F86" s="9"/>
       <c r="G86" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H86" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="J86" s="30"/>
-      <c r="K86" s="30"/>
-      <c r="L86" s="30"/>
+      <c r="H86" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="J86" s="32"/>
+      <c r="K86" s="32"/>
+      <c r="L86" s="32"/>
     </row>
     <row r="87" customHeight="1" spans="1:12">
       <c r="A87" s="9">
@@ -4033,17 +4049,17 @@
       <c r="C87" s="1">
         <v>1</v>
       </c>
-      <c r="D87" s="29" t="b">
+      <c r="D87" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E87" s="1">
         <v>4055342</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H87" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:12">
@@ -4056,21 +4072,21 @@
       <c r="C88" s="1">
         <v>1</v>
       </c>
-      <c r="D88" s="29" t="b">
+      <c r="D88" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E88" s="1">
         <v>4055343</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H88" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A89" s="29">
+      <c r="A89" s="31">
         <v>2204</v>
       </c>
       <c r="B89" s="6">
@@ -4079,18 +4095,18 @@
       <c r="C89" s="6">
         <v>1</v>
       </c>
-      <c r="D89" s="29" t="b">
+      <c r="D89" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E89" s="6">
         <v>4055344</v>
       </c>
       <c r="F89" s="6"/>
-      <c r="G89" s="29" t="s">
-        <v>82</v>
+      <c r="G89" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="10"/>
@@ -4098,7 +4114,7 @@
       <c r="L89" s="10"/>
     </row>
     <row r="90" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A90" s="29">
+      <c r="A90" s="31">
         <v>2205</v>
       </c>
       <c r="B90" s="6">
@@ -4107,18 +4123,18 @@
       <c r="C90" s="6">
         <v>1</v>
       </c>
-      <c r="D90" s="29" t="b">
+      <c r="D90" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E90" s="6">
         <v>4055345</v>
       </c>
       <c r="F90" s="6"/>
-      <c r="G90" s="29" t="s">
-        <v>82</v>
+      <c r="G90" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
@@ -4126,7 +4142,7 @@
       <c r="L90" s="10"/>
     </row>
     <row r="91" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A91" s="29">
+      <c r="A91" s="31">
         <v>2206</v>
       </c>
       <c r="B91" s="6">
@@ -4135,18 +4151,18 @@
       <c r="C91" s="6">
         <v>1</v>
       </c>
-      <c r="D91" s="29" t="b">
+      <c r="D91" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E91" s="6">
         <v>4055346</v>
       </c>
       <c r="F91" s="6"/>
-      <c r="G91" s="29" t="s">
-        <v>82</v>
+      <c r="G91" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="10"/>
@@ -4154,7 +4170,7 @@
       <c r="L91" s="10"/>
     </row>
     <row r="92" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A92" s="29">
+      <c r="A92" s="31">
         <v>2207</v>
       </c>
       <c r="B92" s="6">
@@ -4163,18 +4179,18 @@
       <c r="C92" s="6">
         <v>1</v>
       </c>
-      <c r="D92" s="29" t="b">
+      <c r="D92" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E92" s="6">
         <v>4055347</v>
       </c>
       <c r="F92" s="6"/>
-      <c r="G92" s="29" t="s">
-        <v>82</v>
+      <c r="G92" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="10"/>
@@ -4182,7 +4198,7 @@
       <c r="L92" s="10"/>
     </row>
     <row r="93" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A93" s="29">
+      <c r="A93" s="31">
         <v>2208</v>
       </c>
       <c r="B93" s="6">
@@ -4191,18 +4207,18 @@
       <c r="C93" s="6">
         <v>1</v>
       </c>
-      <c r="D93" s="29" t="b">
+      <c r="D93" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E93" s="6">
         <v>4055348</v>
       </c>
       <c r="F93" s="6"/>
-      <c r="G93" s="29" t="s">
-        <v>82</v>
+      <c r="G93" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
@@ -4210,7 +4226,7 @@
       <c r="L93" s="10"/>
     </row>
     <row r="94" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A94" s="29">
+      <c r="A94" s="31">
         <v>2209</v>
       </c>
       <c r="B94" s="6">
@@ -4219,13 +4235,13 @@
       <c r="C94" s="6">
         <v>1</v>
       </c>
-      <c r="D94" s="29" t="b">
+      <c r="D94" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
-      <c r="G94" s="29" t="s">
-        <v>82</v>
+      <c r="G94" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="H94" s="10"/>
       <c r="I94" s="10"/>
@@ -4234,7 +4250,7 @@
       <c r="L94" s="10"/>
     </row>
     <row r="95" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A95" s="29">
+      <c r="A95" s="31">
         <v>2210</v>
       </c>
       <c r="B95" s="6">
@@ -4243,25 +4259,25 @@
       <c r="C95" s="6">
         <v>1</v>
       </c>
-      <c r="D95" s="29" t="b">
+      <c r="D95" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E95" s="6">
         <v>4055350</v>
       </c>
       <c r="F95" s="6"/>
-      <c r="G95" s="29" t="s">
-        <v>82</v>
+      <c r="G95" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J95" s="10"/>
       <c r="K95" s="10"/>
       <c r="L95" s="10"/>
     </row>
     <row r="96" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A96" s="29">
+      <c r="A96" s="31">
         <v>2211</v>
       </c>
       <c r="B96" s="6">
@@ -4270,18 +4286,18 @@
       <c r="C96" s="6">
         <v>1</v>
       </c>
-      <c r="D96" s="29" t="b">
+      <c r="D96" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E96" s="6">
         <v>4055351</v>
       </c>
       <c r="F96" s="6"/>
-      <c r="G96" s="29" t="s">
-        <v>82</v>
+      <c r="G96" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="10"/>
@@ -4289,7 +4305,7 @@
       <c r="L96" s="10"/>
     </row>
     <row r="97" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A97" s="29">
+      <c r="A97" s="31">
         <v>2212</v>
       </c>
       <c r="B97" s="6">
@@ -4298,25 +4314,25 @@
       <c r="C97" s="6">
         <v>1</v>
       </c>
-      <c r="D97" s="29" t="b">
+      <c r="D97" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E97" s="6">
         <v>4055352</v>
       </c>
       <c r="F97" s="6"/>
-      <c r="G97" s="29" t="s">
-        <v>82</v>
+      <c r="G97" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J97" s="10"/>
       <c r="K97" s="10"/>
       <c r="L97" s="10"/>
     </row>
     <row r="98" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A98" s="29">
+      <c r="A98" s="31">
         <v>2213</v>
       </c>
       <c r="B98" s="6">
@@ -4325,13 +4341,13 @@
       <c r="C98" s="6">
         <v>1</v>
       </c>
-      <c r="D98" s="29" t="b">
+      <c r="D98" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
-      <c r="G98" s="29" t="s">
-        <v>82</v>
+      <c r="G98" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="H98" s="10"/>
       <c r="I98" s="10"/>
@@ -4349,11 +4365,11 @@
       <c r="C99" s="1">
         <v>1</v>
       </c>
-      <c r="D99" s="29" t="b">
+      <c r="D99" s="31" t="b">
         <v>0</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H99"/>
     </row>
@@ -4367,77 +4383,77 @@
       <c r="C100" s="1">
         <v>1</v>
       </c>
-      <c r="D100" s="29" t="b">
+      <c r="D100" s="31" t="b">
         <v>0</v>
       </c>
       <c r="E100" s="1">
         <v>4055355</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H100" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:12">
-      <c r="A101" s="31">
+      <c r="A101" s="33">
         <v>2301</v>
       </c>
-      <c r="B101" s="31"/>
-      <c r="C101" s="31">
+      <c r="B101" s="33"/>
+      <c r="C101" s="33">
         <v>2</v>
       </c>
-      <c r="D101" s="31" t="b">
+      <c r="D101" s="33" t="b">
         <v>0</v>
       </c>
-      <c r="E101" s="31"/>
-      <c r="F101" s="31"/>
+      <c r="E101" s="33"/>
+      <c r="F101" s="33"/>
       <c r="G101" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:12">
-      <c r="A102" s="31">
+      <c r="A102" s="33">
         <v>2302</v>
       </c>
-      <c r="B102" s="31">
-        <v>1</v>
-      </c>
-      <c r="C102" s="31">
-        <v>1</v>
-      </c>
-      <c r="D102" s="31" t="b">
+      <c r="B102" s="33">
+        <v>1</v>
+      </c>
+      <c r="C102" s="33">
+        <v>1</v>
+      </c>
+      <c r="D102" s="33" t="b">
         <v>0</v>
       </c>
-      <c r="E102" s="31"/>
-      <c r="F102" s="31"/>
+      <c r="E102" s="33"/>
+      <c r="F102" s="33"/>
       <c r="G102" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:12">
-      <c r="A103" s="31">
+      <c r="A103" s="33">
         <v>2303</v>
       </c>
-      <c r="B103" s="31">
-        <v>1</v>
-      </c>
-      <c r="C103" s="31">
-        <v>1</v>
-      </c>
-      <c r="D103" s="31" t="b">
+      <c r="B103" s="33">
+        <v>1</v>
+      </c>
+      <c r="C103" s="33">
+        <v>1</v>
+      </c>
+      <c r="D103" s="33" t="b">
         <v>0</v>
       </c>
-      <c r="E103" s="31">
+      <c r="E103" s="33">
         <v>4055371</v>
       </c>
-      <c r="F103" s="31"/>
+      <c r="F103" s="33"/>
       <c r="G103" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -4498,14 +4514,14 @@
         <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -4514,7 +4530,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4524,14 +4540,14 @@
         <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4539,14 +4555,14 @@
         <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4554,14 +4570,14 @@
         <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4569,14 +4585,14 @@
         <v>2205</v>
       </c>
       <c r="J9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
         <v>2205_</v>
       </c>
       <c r="M9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4584,14 +4600,14 @@
         <v>2206</v>
       </c>
       <c r="J10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>2206_</v>
       </c>
       <c r="M10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4599,14 +4615,14 @@
         <v>2207</v>
       </c>
       <c r="J11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>2207_</v>
       </c>
       <c r="M11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4614,14 +4630,14 @@
         <v>2208</v>
       </c>
       <c r="J12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>2208_</v>
       </c>
       <c r="M12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4629,32 +4645,32 @@
         <v>2209</v>
       </c>
       <c r="J13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>2209_</v>
       </c>
       <c r="M13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I14">
         <v>2210</v>
       </c>
       <c r="J14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>2210_</v>
       </c>
       <c r="M14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4662,14 +4678,14 @@
         <v>2211</v>
       </c>
       <c r="J15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>2211_</v>
       </c>
       <c r="M15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4677,14 +4693,14 @@
         <v>2212</v>
       </c>
       <c r="J16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>2212_</v>
       </c>
       <c r="M16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4692,14 +4708,14 @@
         <v>2213</v>
       </c>
       <c r="J17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>2213_</v>
       </c>
       <c r="M17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4707,29 +4723,29 @@
         <v>2214</v>
       </c>
       <c r="J18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>2214_</v>
       </c>
       <c r="M18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="115">
   <si>
     <t>序号</t>
   </si>
@@ -453,10 +453,13 @@
     <t>娱乐城已&lt;color=#00bfff&gt;提升到2级&lt;/color&gt;，解锁了一些&lt;color=#00bfff&gt;新功能&lt;/color&gt;</t>
   </si>
   <si>
+    <t>点击打开&lt;color=#00bfff&gt;游戏技能&lt;/color&gt;界面</t>
+  </si>
+  <si>
     <t>解锁 &lt;color=#00bfff&gt;SWEET WIN 大奖&lt;/color&gt;技能</t>
   </si>
   <si>
-    <t>在&lt;color=#00bfff&gt;萌宠小队&lt;/color&gt;游戏中概率&lt;color=#00bfff&gt;中奖SWEET WIN 大奖&lt;/color&gt;</t>
+    <t>在&lt;color=#00bfff&gt;萌宠小队&lt;/color&gt;游戏中有概率&lt;color=#00bfff&gt;中奖SWEET WIN 大奖&lt;/color&gt;</t>
   </si>
   <si>
     <t>在线购买资源</t>
@@ -535,7 +538,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,6 +614,13 @@
       <color theme="0" tint="-0.5"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF92D050"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1100,137 +1110,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1327,7 +1337,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1817,7 +1833,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -4035,9 +4051,9 @@
       <c r="H86" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="J86" s="32"/>
-      <c r="K86" s="32"/>
-      <c r="L86" s="32"/>
+      <c r="J86" s="33"/>
+      <c r="K86" s="33"/>
+      <c r="L86" s="33"/>
     </row>
     <row r="87" customHeight="1" spans="1:12">
       <c r="A87" s="9">
@@ -4058,7 +4074,7 @@
       <c r="G87" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H87" s="34" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4067,7 +4083,7 @@
         <v>2203</v>
       </c>
       <c r="B88" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C88" s="1">
         <v>1</v>
@@ -4081,7 +4097,7 @@
       <c r="G88" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H88" s="34" t="s">
         <v>86</v>
       </c>
     </row>
@@ -4089,8 +4105,8 @@
       <c r="A89" s="31">
         <v>2204</v>
       </c>
-      <c r="B89" s="6">
-        <v>4</v>
+      <c r="B89" s="1">
+        <v>2</v>
       </c>
       <c r="C89" s="6">
         <v>1</v>
@@ -4105,7 +4121,7 @@
       <c r="G89" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="H89" s="10" t="s">
+      <c r="H89" s="34" t="s">
         <v>87</v>
       </c>
       <c r="I89" s="10"/>
@@ -4117,8 +4133,8 @@
       <c r="A90" s="31">
         <v>2205</v>
       </c>
-      <c r="B90" s="6">
-        <v>5</v>
+      <c r="B90" s="1">
+        <v>2</v>
       </c>
       <c r="C90" s="6">
         <v>1</v>
@@ -4133,7 +4149,7 @@
       <c r="G90" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="H90" s="10" t="s">
+      <c r="H90" s="34" t="s">
         <v>88</v>
       </c>
       <c r="I90" s="10"/>
@@ -4145,8 +4161,8 @@
       <c r="A91" s="31">
         <v>2206</v>
       </c>
-      <c r="B91" s="6">
-        <v>6</v>
+      <c r="B91" s="1">
+        <v>2</v>
       </c>
       <c r="C91" s="6">
         <v>1</v>
@@ -4161,7 +4177,7 @@
       <c r="G91" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="H91" s="10" t="s">
+      <c r="H91" s="34" t="s">
         <v>89</v>
       </c>
       <c r="I91" s="10"/>
@@ -4173,8 +4189,8 @@
       <c r="A92" s="31">
         <v>2207</v>
       </c>
-      <c r="B92" s="6">
-        <v>7</v>
+      <c r="B92" s="1">
+        <v>2</v>
       </c>
       <c r="C92" s="6">
         <v>1</v>
@@ -4189,7 +4205,7 @@
       <c r="G92" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="H92" s="10" t="s">
+      <c r="H92" s="34" t="s">
         <v>87</v>
       </c>
       <c r="I92" s="10"/>
@@ -4201,8 +4217,8 @@
       <c r="A93" s="31">
         <v>2208</v>
       </c>
-      <c r="B93" s="6">
-        <v>8</v>
+      <c r="B93" s="1">
+        <v>2</v>
       </c>
       <c r="C93" s="6">
         <v>1</v>
@@ -4217,7 +4233,7 @@
       <c r="G93" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="H93" s="10" t="s">
+      <c r="H93" s="34" t="s">
         <v>88</v>
       </c>
       <c r="I93" s="10"/>
@@ -4229,8 +4245,8 @@
       <c r="A94" s="31">
         <v>2209</v>
       </c>
-      <c r="B94" s="6">
-        <v>9</v>
+      <c r="B94" s="1">
+        <v>2</v>
       </c>
       <c r="C94" s="6">
         <v>1</v>
@@ -4253,8 +4269,8 @@
       <c r="A95" s="31">
         <v>2210</v>
       </c>
-      <c r="B95" s="6">
-        <v>10</v>
+      <c r="B95" s="1">
+        <v>2</v>
       </c>
       <c r="C95" s="6">
         <v>1</v>
@@ -4269,7 +4285,7 @@
       <c r="G95" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="H95" s="10" t="s">
+      <c r="H95" s="34" t="s">
         <v>85</v>
       </c>
       <c r="J95" s="10"/>
@@ -4280,8 +4296,8 @@
       <c r="A96" s="31">
         <v>2211</v>
       </c>
-      <c r="B96" s="6">
-        <v>12</v>
+      <c r="B96" s="1">
+        <v>2</v>
       </c>
       <c r="C96" s="6">
         <v>1</v>
@@ -4289,17 +4305,16 @@
       <c r="D96" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="E96" s="6">
-        <v>4055351</v>
-      </c>
-      <c r="F96" s="6"/>
+      <c r="E96" s="1">
+        <v>4055356</v>
+      </c>
       <c r="G96" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="H96" s="10" t="s">
+      <c r="H96" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="I96" s="10"/>
+      <c r="I96" s="7"/>
       <c r="J96" s="10"/>
       <c r="K96" s="10"/>
       <c r="L96" s="10"/>
@@ -4308,8 +4323,8 @@
       <c r="A97" s="31">
         <v>2212</v>
       </c>
-      <c r="B97" s="6">
-        <v>13</v>
+      <c r="B97" s="1">
+        <v>2</v>
       </c>
       <c r="C97" s="6">
         <v>1</v>
@@ -4318,15 +4333,16 @@
         <v>0</v>
       </c>
       <c r="E97" s="6">
-        <v>4055352</v>
+        <v>4055351</v>
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="H97" s="10" t="s">
+      <c r="H97" s="34" t="s">
         <v>91</v>
       </c>
+      <c r="I97" s="10"/>
       <c r="J97" s="10"/>
       <c r="K97" s="10"/>
       <c r="L97" s="10"/>
@@ -4335,8 +4351,8 @@
       <c r="A98" s="31">
         <v>2213</v>
       </c>
-      <c r="B98" s="6">
-        <v>14</v>
+      <c r="B98" s="1">
+        <v>2</v>
       </c>
       <c r="C98" s="6">
         <v>1</v>
@@ -4344,41 +4360,50 @@
       <c r="D98" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="E98" s="6"/>
+      <c r="E98" s="6">
+        <v>4055352</v>
+      </c>
       <c r="F98" s="6"/>
       <c r="G98" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="H98" s="10"/>
-      <c r="I98" s="10"/>
+      <c r="H98" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="J98" s="10"/>
       <c r="K98" s="10"/>
       <c r="L98" s="10"/>
     </row>
-    <row r="99" customHeight="1" spans="1:12">
+    <row r="99" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A99" s="9">
         <v>2214</v>
       </c>
       <c r="B99" s="1">
-        <v>13</v>
-      </c>
-      <c r="C99" s="1">
+        <v>2</v>
+      </c>
+      <c r="C99" s="6">
         <v>1</v>
       </c>
       <c r="D99" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="G99" s="9" t="s">
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="H99"/>
+      <c r="H99" s="10"/>
+      <c r="I99" s="10"/>
+      <c r="J99" s="10"/>
+      <c r="K99" s="10"/>
+      <c r="L99" s="10"/>
     </row>
     <row r="100" customHeight="1" spans="1:12">
-      <c r="A100" s="9">
+      <c r="A100" s="31">
         <v>2215</v>
       </c>
       <c r="B100" s="1">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C100" s="1">
         <v>1</v>
@@ -4386,74 +4411,92 @@
       <c r="D100" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="E100" s="1">
-        <v>4055355</v>
-      </c>
       <c r="G100" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H100"/>
+    </row>
+    <row r="101" customHeight="1" spans="1:12">
+      <c r="A101" s="9">
+        <v>2216</v>
+      </c>
+      <c r="B101" s="1">
+        <v>2</v>
+      </c>
+      <c r="C101" s="1">
+        <v>1</v>
+      </c>
+      <c r="D101" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="E101" s="1">
+        <v>4055355</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H101" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="1:12">
-      <c r="A101" s="33">
+    <row r="102" customHeight="1" spans="1:12">
+      <c r="A102" s="35">
         <v>2301</v>
       </c>
-      <c r="B101" s="33"/>
-      <c r="C101" s="33">
-        <v>2</v>
-      </c>
-      <c r="D101" s="33" t="b">
+      <c r="B102" s="35"/>
+      <c r="C102" s="35">
+        <v>2</v>
+      </c>
+      <c r="D102" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="E101" s="33"/>
-      <c r="F101" s="33"/>
-      <c r="G101" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" spans="1:12">
-      <c r="A102" s="33">
+      <c r="E102" s="35"/>
+      <c r="F102" s="35"/>
+      <c r="G102" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="1:12">
+      <c r="A103" s="35">
         <v>2302</v>
       </c>
-      <c r="B102" s="33">
-        <v>1</v>
-      </c>
-      <c r="C102" s="33">
-        <v>1</v>
-      </c>
-      <c r="D102" s="33" t="b">
+      <c r="B103" s="35">
+        <v>1</v>
+      </c>
+      <c r="C103" s="35">
+        <v>1</v>
+      </c>
+      <c r="D103" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="E102" s="33"/>
-      <c r="F102" s="33"/>
-      <c r="G102" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" spans="1:12">
-      <c r="A103" s="33">
+      <c r="E103" s="35"/>
+      <c r="F103" s="35"/>
+      <c r="G103" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="1:12">
+      <c r="A104" s="35">
         <v>2303</v>
       </c>
-      <c r="B103" s="33">
-        <v>1</v>
-      </c>
-      <c r="C103" s="33">
-        <v>1</v>
-      </c>
-      <c r="D103" s="33" t="b">
+      <c r="B104" s="35">
+        <v>1</v>
+      </c>
+      <c r="C104" s="35">
+        <v>1</v>
+      </c>
+      <c r="D104" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="E103" s="33">
+      <c r="E104" s="35">
         <v>4055371</v>
       </c>
-      <c r="F103" s="33"/>
-      <c r="G103" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H103" s="10" t="s">
+      <c r="F104" s="35"/>
+      <c r="G104" s="1" t="s">
         <v>93</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4514,14 +4557,14 @@
         <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -4530,7 +4573,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4540,14 +4583,14 @@
         <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4555,14 +4598,14 @@
         <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4570,14 +4613,14 @@
         <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4585,14 +4628,14 @@
         <v>2205</v>
       </c>
       <c r="J9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
         <v>2205_</v>
       </c>
       <c r="M9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4600,14 +4643,14 @@
         <v>2206</v>
       </c>
       <c r="J10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>2206_</v>
       </c>
       <c r="M10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4615,14 +4658,14 @@
         <v>2207</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>2207_</v>
       </c>
       <c r="M11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4630,14 +4673,14 @@
         <v>2208</v>
       </c>
       <c r="J12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>2208_</v>
       </c>
       <c r="M12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4645,32 +4688,32 @@
         <v>2209</v>
       </c>
       <c r="J13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>2209_</v>
       </c>
       <c r="M13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I14">
         <v>2210</v>
       </c>
       <c r="J14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>2210_</v>
       </c>
       <c r="M14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4678,14 +4721,14 @@
         <v>2211</v>
       </c>
       <c r="J15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>2211_</v>
       </c>
       <c r="M15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4693,14 +4736,14 @@
         <v>2212</v>
       </c>
       <c r="J16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>2212_</v>
       </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4708,14 +4751,14 @@
         <v>2213</v>
       </c>
       <c r="J17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>2213_</v>
       </c>
       <c r="M17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4723,29 +4766,29 @@
         <v>2214</v>
       </c>
       <c r="J18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>2214_</v>
       </c>
       <c r="M18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -4039,7 +4039,7 @@
         <v>2</v>
       </c>
       <c r="D86" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="9">
         <v>4055341</v>
@@ -4066,7 +4066,7 @@
         <v>1</v>
       </c>
       <c r="D87" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="1">
         <v>4055342</v>
@@ -4089,7 +4089,7 @@
         <v>1</v>
       </c>
       <c r="D88" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" s="1">
         <v>4055343</v>
@@ -4112,7 +4112,7 @@
         <v>1</v>
       </c>
       <c r="D89" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" s="6">
         <v>4055344</v>
@@ -4140,7 +4140,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" s="6">
         <v>4055345</v>
@@ -4168,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="D91" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" s="6">
         <v>4055346</v>
@@ -4196,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="D92" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6">
         <v>4055347</v>
@@ -4224,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" s="6">
         <v>4055348</v>
@@ -4252,7 +4252,7 @@
         <v>1</v>
       </c>
       <c r="D94" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -4276,7 +4276,7 @@
         <v>1</v>
       </c>
       <c r="D95" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="6">
         <v>4055350</v>
@@ -4303,7 +4303,7 @@
         <v>1</v>
       </c>
       <c r="D96" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" s="1">
         <v>4055356</v>
@@ -4330,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="D97" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="6">
         <v>4055351</v>
@@ -4358,7 +4358,7 @@
         <v>1</v>
       </c>
       <c r="D98" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="6">
         <v>4055352</v>
@@ -4385,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="D99" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
@@ -4409,7 +4409,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="9" t="s">
         <v>83</v>
@@ -4427,7 +4427,7 @@
         <v>1</v>
       </c>
       <c r="D101" s="31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="1">
         <v>4055355</v>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -263,7 +263,7 @@
     <t>开始经营娱乐城</t>
   </si>
   <si>
-    <t>建筑-愤怒的小鸟-升级1次</t>
+    <t>建筑-愤怒的小鸟-升级2次</t>
   </si>
   <si>
     <t>点击[+]图标解锁SLOT游戏&lt;color=#00bfff&gt;萌宠小队&lt;/color&gt;</t>
@@ -590,6 +590,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0" tint="-0.5"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -608,12 +614,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.5"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1289,39 +1289,39 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1334,17 +1334,17 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1942,7 +1942,7 @@
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
       <c r="D5" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="15">
         <v>4055101</v>
@@ -1966,7 +1966,7 @@
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="15">
         <v>4055102</v>
@@ -1990,7 +1990,7 @@
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="15">
         <v>4055103</v>
@@ -2014,7 +2014,7 @@
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="15">
         <v>4055104</v>
@@ -2038,7 +2038,7 @@
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
       <c r="D9" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="15">
         <v>4055109</v>
@@ -2062,7 +2062,7 @@
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
       <c r="D10" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="15">
         <v>4055105</v>
@@ -2087,7 +2087,7 @@
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="15">
         <v>4055106</v>
@@ -2111,7 +2111,7 @@
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
       <c r="D12" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="15">
         <v>4055107</v>
@@ -2134,7 +2134,7 @@
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
       <c r="D13" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="15">
         <v>4055108</v>
@@ -2157,8 +2157,8 @@
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
-      <c r="D14" s="21" t="b">
-        <v>1</v>
+      <c r="D14" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
@@ -2177,8 +2177,8 @@
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
-      <c r="D15" s="21" t="b">
-        <v>1</v>
+      <c r="D15" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
@@ -2197,8 +2197,8 @@
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
-      <c r="D16" s="21" t="b">
-        <v>1</v>
+      <c r="D16" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
@@ -2217,8 +2217,8 @@
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
-      <c r="D17" s="21" t="b">
-        <v>1</v>
+      <c r="D17" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
@@ -2235,20 +2235,20 @@
       <c r="A18" s="23">
         <v>1201</v>
       </c>
-      <c r="B18" s="16">
-        <v>2</v>
-      </c>
-      <c r="C18" s="16">
+      <c r="B18" s="24">
+        <v>2</v>
+      </c>
+      <c r="C18" s="24">
         <v>2</v>
       </c>
       <c r="D18" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="16">
+        <v>0</v>
+      </c>
+      <c r="E18" s="24">
         <v>4055121</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="24" t="s">
+      <c r="F18" s="24"/>
+      <c r="G18" s="25" t="s">
         <v>27</v>
       </c>
       <c r="H18" s="10" t="s">
@@ -2263,20 +2263,20 @@
       <c r="A19" s="23">
         <v>1202</v>
       </c>
-      <c r="B19" s="16">
-        <v>2</v>
-      </c>
-      <c r="C19" s="16">
+      <c r="B19" s="24">
+        <v>2</v>
+      </c>
+      <c r="C19" s="24">
         <v>2</v>
       </c>
       <c r="D19" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="16">
+        <v>0</v>
+      </c>
+      <c r="E19" s="24">
         <v>4055122</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="24" t="s">
+      <c r="F19" s="24"/>
+      <c r="G19" s="25" t="s">
         <v>27</v>
       </c>
       <c r="H19" s="10" t="s">
@@ -2291,20 +2291,20 @@
       <c r="A20" s="23">
         <v>1203</v>
       </c>
-      <c r="B20" s="16">
-        <v>2</v>
-      </c>
-      <c r="C20" s="16">
+      <c r="B20" s="24">
+        <v>2</v>
+      </c>
+      <c r="C20" s="24">
         <v>1</v>
       </c>
       <c r="D20" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="16">
+        <v>0</v>
+      </c>
+      <c r="E20" s="24">
         <v>4055123</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="24" t="s">
+      <c r="F20" s="24"/>
+      <c r="G20" s="25" t="s">
         <v>27</v>
       </c>
       <c r="H20" s="10" t="s">
@@ -2319,20 +2319,20 @@
       <c r="A21" s="23">
         <v>1204</v>
       </c>
-      <c r="B21" s="16">
-        <v>2</v>
-      </c>
-      <c r="C21" s="16">
+      <c r="B21" s="24">
+        <v>2</v>
+      </c>
+      <c r="C21" s="24">
         <v>1</v>
       </c>
       <c r="D21" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="16">
+        <v>0</v>
+      </c>
+      <c r="E21" s="24">
         <v>4055124</v>
       </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="24" t="s">
+      <c r="F21" s="24"/>
+      <c r="G21" s="25" t="s">
         <v>27</v>
       </c>
       <c r="H21" s="10" t="s">
@@ -2354,13 +2354,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="15">
         <v>4055141</v>
       </c>
       <c r="F22" s="15"/>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="26" t="s">
         <v>32</v>
       </c>
       <c r="H22" s="10" t="s">
@@ -2382,13 +2382,13 @@
         <v>1</v>
       </c>
       <c r="D23" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="15">
         <v>4055142</v>
       </c>
       <c r="F23" s="15"/>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="26" t="s">
         <v>32</v>
       </c>
       <c r="H23" s="10" t="s">
@@ -2410,13 +2410,13 @@
         <v>1</v>
       </c>
       <c r="D24" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="15">
         <v>4055143</v>
       </c>
       <c r="F24" s="15"/>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="26" t="s">
         <v>32</v>
       </c>
       <c r="H24" s="10" t="s">
@@ -2436,11 +2436,11 @@
         <v>1</v>
       </c>
       <c r="D25" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="15"/>
-      <c r="G25" s="25" t="s">
+      <c r="G25" s="26" t="s">
         <v>32</v>
       </c>
       <c r="H25" s="10" t="s">
@@ -2460,13 +2460,13 @@
         <v>1</v>
       </c>
       <c r="D26" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="15">
         <v>4055144</v>
       </c>
       <c r="F26" s="15"/>
-      <c r="G26" s="25" t="s">
+      <c r="G26" s="26" t="s">
         <v>32</v>
       </c>
       <c r="H26" s="10" t="s">
@@ -2481,20 +2481,20 @@
       <c r="A27" s="23">
         <v>1401</v>
       </c>
-      <c r="B27" s="16">
-        <v>2</v>
-      </c>
-      <c r="C27" s="16">
+      <c r="B27" s="24">
+        <v>2</v>
+      </c>
+      <c r="C27" s="24">
         <v>1</v>
       </c>
       <c r="D27" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="16">
+        <v>0</v>
+      </c>
+      <c r="E27" s="24">
         <v>4055161</v>
       </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="24" t="s">
+      <c r="F27" s="24"/>
+      <c r="G27" s="25" t="s">
         <v>38</v>
       </c>
       <c r="H27" s="10" t="s">
@@ -2509,20 +2509,20 @@
       <c r="A28" s="23">
         <v>1402</v>
       </c>
-      <c r="B28" s="16">
-        <v>2</v>
-      </c>
-      <c r="C28" s="16">
+      <c r="B28" s="24">
+        <v>2</v>
+      </c>
+      <c r="C28" s="24">
         <v>1</v>
       </c>
       <c r="D28" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="16">
+        <v>0</v>
+      </c>
+      <c r="E28" s="24">
         <v>4055162</v>
       </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="24" t="s">
+      <c r="F28" s="24"/>
+      <c r="G28" s="25" t="s">
         <v>38</v>
       </c>
       <c r="H28" s="10" t="s">
@@ -2537,20 +2537,20 @@
       <c r="A29" s="23">
         <v>1403</v>
       </c>
-      <c r="B29" s="16">
-        <v>2</v>
-      </c>
-      <c r="C29" s="16">
+      <c r="B29" s="24">
+        <v>2</v>
+      </c>
+      <c r="C29" s="24">
         <v>1</v>
       </c>
       <c r="D29" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="16">
+        <v>0</v>
+      </c>
+      <c r="E29" s="24">
         <v>4055163</v>
       </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="24" t="s">
+      <c r="F29" s="24"/>
+      <c r="G29" s="25" t="s">
         <v>38</v>
       </c>
       <c r="H29" s="10" t="s">
@@ -2565,20 +2565,20 @@
       <c r="A30" s="23">
         <v>1404</v>
       </c>
-      <c r="B30" s="16">
-        <v>2</v>
-      </c>
-      <c r="C30" s="16">
+      <c r="B30" s="24">
+        <v>2</v>
+      </c>
+      <c r="C30" s="24">
         <v>1</v>
       </c>
       <c r="D30" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="16">
+        <v>0</v>
+      </c>
+      <c r="E30" s="24">
         <v>4055164</v>
       </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="24" t="s">
+      <c r="F30" s="24"/>
+      <c r="G30" s="25" t="s">
         <v>38</v>
       </c>
       <c r="H30" s="10" t="s">
@@ -2593,16 +2593,16 @@
       <c r="A31" s="23">
         <v>1405</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16">
+      <c r="B31" s="24"/>
+      <c r="C31" s="24">
         <v>1</v>
       </c>
       <c r="D31" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="25" t="s">
         <v>38</v>
       </c>
       <c r="H31" s="10" t="s">
@@ -2617,20 +2617,20 @@
       <c r="A32" s="23">
         <v>1406</v>
       </c>
-      <c r="B32" s="16">
-        <v>2</v>
-      </c>
-      <c r="C32" s="16">
+      <c r="B32" s="24">
+        <v>2</v>
+      </c>
+      <c r="C32" s="24">
         <v>1</v>
       </c>
       <c r="D32" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="16">
+        <v>0</v>
+      </c>
+      <c r="E32" s="24">
         <v>4055165</v>
       </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="24" t="s">
+      <c r="F32" s="24"/>
+      <c r="G32" s="25" t="s">
         <v>38</v>
       </c>
       <c r="H32" s="10" t="s">
@@ -2652,13 +2652,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="15">
         <v>4055181</v>
       </c>
       <c r="F33" s="15"/>
-      <c r="G33" s="25" t="s">
+      <c r="G33" s="26" t="s">
         <v>44</v>
       </c>
       <c r="H33" s="10" t="s">
@@ -2680,13 +2680,13 @@
         <v>1</v>
       </c>
       <c r="D34" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="15">
         <v>4055182</v>
       </c>
       <c r="F34" s="15"/>
-      <c r="G34" s="25" t="s">
+      <c r="G34" s="26" t="s">
         <v>44</v>
       </c>
       <c r="H34" s="10" t="s">
@@ -2706,11 +2706,11 @@
         <v>1</v>
       </c>
       <c r="D35" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
-      <c r="G35" s="25" t="s">
+      <c r="G35" s="26" t="s">
         <v>44</v>
       </c>
       <c r="H35" s="10" t="s">
@@ -2730,11 +2730,11 @@
         <v>1</v>
       </c>
       <c r="D36" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
-      <c r="G36" s="25" t="s">
+      <c r="G36" s="26" t="s">
         <v>44</v>
       </c>
       <c r="H36" s="10" t="s">
@@ -2749,16 +2749,16 @@
       <c r="A37" s="23">
         <v>1601</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16">
+      <c r="B37" s="24"/>
+      <c r="C37" s="24">
         <v>1</v>
       </c>
       <c r="D37" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H37" s="10" t="s">
@@ -2773,16 +2773,16 @@
       <c r="A38" s="23">
         <v>1602</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16">
+      <c r="B38" s="24"/>
+      <c r="C38" s="24">
         <v>1</v>
       </c>
       <c r="D38" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H38" s="10" t="s">
@@ -2797,18 +2797,18 @@
       <c r="A39" s="23">
         <v>1603</v>
       </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16">
+      <c r="B39" s="24"/>
+      <c r="C39" s="24">
         <v>1</v>
       </c>
       <c r="D39" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="16">
+        <v>0</v>
+      </c>
+      <c r="E39" s="24">
         <v>4055203</v>
       </c>
       <c r="F39" s="15"/>
-      <c r="G39" s="24" t="s">
+      <c r="G39" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H39" s="10" t="s">
@@ -2823,16 +2823,16 @@
       <c r="A40" s="23">
         <v>1604</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16">
+      <c r="B40" s="24"/>
+      <c r="C40" s="24">
         <v>1</v>
       </c>
       <c r="D40" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H40" s="10" t="s">
@@ -2847,20 +2847,20 @@
       <c r="A41" s="23">
         <v>1605</v>
       </c>
-      <c r="B41" s="16">
-        <v>2</v>
-      </c>
-      <c r="C41" s="16">
+      <c r="B41" s="24">
+        <v>2</v>
+      </c>
+      <c r="C41" s="24">
         <v>1</v>
       </c>
       <c r="D41" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="16">
+        <v>0</v>
+      </c>
+      <c r="E41" s="24">
         <v>4055204</v>
       </c>
       <c r="F41" s="15"/>
-      <c r="G41" s="24" t="s">
+      <c r="G41" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H41" s="10" t="s">
@@ -2875,16 +2875,16 @@
       <c r="A42" s="23">
         <v>1606</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16">
+      <c r="B42" s="24"/>
+      <c r="C42" s="24">
         <v>1</v>
       </c>
       <c r="D42" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H42" s="10" t="s">
@@ -2899,18 +2899,18 @@
       <c r="A43" s="23">
         <v>1607</v>
       </c>
-      <c r="B43" s="16">
-        <v>2</v>
-      </c>
-      <c r="C43" s="16">
+      <c r="B43" s="24">
+        <v>2</v>
+      </c>
+      <c r="C43" s="24">
         <v>1</v>
       </c>
       <c r="D43" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H43" s="10" t="s">
@@ -2925,18 +2925,18 @@
       <c r="A44" s="23">
         <v>1608</v>
       </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16">
+      <c r="B44" s="24"/>
+      <c r="C44" s="24">
         <v>1</v>
       </c>
       <c r="D44" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="16">
+        <v>0</v>
+      </c>
+      <c r="E44" s="24">
         <v>4055205</v>
       </c>
       <c r="F44" s="15"/>
-      <c r="G44" s="24" t="s">
+      <c r="G44" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H44" s="10" t="s">
@@ -2951,18 +2951,18 @@
       <c r="A45" s="23">
         <v>1609</v>
       </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16">
+      <c r="B45" s="24"/>
+      <c r="C45" s="24">
         <v>1</v>
       </c>
       <c r="D45" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="16">
+        <v>0</v>
+      </c>
+      <c r="E45" s="24">
         <v>4055206</v>
       </c>
       <c r="F45" s="15"/>
-      <c r="G45" s="24" t="s">
+      <c r="G45" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H45" s="10" t="s">
@@ -2977,20 +2977,20 @@
       <c r="A46" s="23">
         <v>1610</v>
       </c>
-      <c r="B46" s="16">
-        <v>2</v>
-      </c>
-      <c r="C46" s="16">
+      <c r="B46" s="24">
+        <v>2</v>
+      </c>
+      <c r="C46" s="24">
         <v>1</v>
       </c>
       <c r="D46" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="16">
+        <v>0</v>
+      </c>
+      <c r="E46" s="24">
         <v>4055207</v>
       </c>
       <c r="F46" s="15"/>
-      <c r="G46" s="24" t="s">
+      <c r="G46" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H46" s="10" t="s">
@@ -3005,20 +3005,20 @@
       <c r="A47" s="23">
         <v>1611</v>
       </c>
-      <c r="B47" s="16">
-        <v>2</v>
-      </c>
-      <c r="C47" s="16">
+      <c r="B47" s="24">
+        <v>2</v>
+      </c>
+      <c r="C47" s="24">
         <v>1</v>
       </c>
       <c r="D47" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="16">
+        <v>0</v>
+      </c>
+      <c r="E47" s="24">
         <v>4055208</v>
       </c>
       <c r="F47" s="15"/>
-      <c r="G47" s="24" t="s">
+      <c r="G47" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H47" s="10" t="s">
@@ -3033,20 +3033,20 @@
       <c r="A48" s="23">
         <v>1612</v>
       </c>
-      <c r="B48" s="16">
-        <v>2</v>
-      </c>
-      <c r="C48" s="16">
+      <c r="B48" s="24">
+        <v>2</v>
+      </c>
+      <c r="C48" s="24">
         <v>1</v>
       </c>
       <c r="D48" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="16">
+        <v>0</v>
+      </c>
+      <c r="E48" s="24">
         <v>4055209</v>
       </c>
       <c r="F48" s="15"/>
-      <c r="G48" s="24" t="s">
+      <c r="G48" s="25" t="s">
         <v>47</v>
       </c>
       <c r="H48" s="10" t="s">
@@ -3066,11 +3066,11 @@
         <v>1</v>
       </c>
       <c r="D49" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
-      <c r="G49" s="25" t="s">
+      <c r="G49" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H49" s="10" t="s">
@@ -3089,10 +3089,10 @@
         <v>1</v>
       </c>
       <c r="D50" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="15"/>
-      <c r="G50" s="25" t="s">
+      <c r="G50" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H50" s="10" t="s">
@@ -3114,13 +3114,13 @@
         <v>1</v>
       </c>
       <c r="D51" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="15">
         <v>4055222</v>
       </c>
       <c r="F51" s="15"/>
-      <c r="G51" s="25" t="s">
+      <c r="G51" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H51" s="10" t="s">
@@ -3142,13 +3142,13 @@
         <v>1</v>
       </c>
       <c r="D52" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="15">
         <v>4055223</v>
       </c>
       <c r="F52" s="15"/>
-      <c r="G52" s="25" t="s">
+      <c r="G52" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H52" s="10" t="s">
@@ -3170,13 +3170,13 @@
         <v>1</v>
       </c>
       <c r="D53" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="15">
         <v>4055224</v>
       </c>
       <c r="F53" s="15"/>
-      <c r="G53" s="25" t="s">
+      <c r="G53" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H53" s="10" t="s">
@@ -3196,11 +3196,11 @@
         <v>1</v>
       </c>
       <c r="D54" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
-      <c r="G54" s="25" t="s">
+      <c r="G54" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H54" s="10" t="s">
@@ -3222,13 +3222,13 @@
         <v>1</v>
       </c>
       <c r="D55" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="15">
         <v>4055225</v>
       </c>
       <c r="F55" s="15"/>
-      <c r="G55" s="25" t="s">
+      <c r="G55" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H55" s="10" t="s">
@@ -3250,13 +3250,13 @@
         <v>1</v>
       </c>
       <c r="D56" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="15">
         <v>4055226</v>
       </c>
       <c r="F56" s="15"/>
-      <c r="G56" s="25" t="s">
+      <c r="G56" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H56" s="10" t="s">
@@ -3276,11 +3276,11 @@
         <v>1</v>
       </c>
       <c r="D57" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
-      <c r="G57" s="25" t="s">
+      <c r="G57" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H57" s="10" t="s">
@@ -3300,11 +3300,11 @@
         <v>1</v>
       </c>
       <c r="D58" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="15"/>
-      <c r="G58" s="25" t="s">
+      <c r="G58" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H58" s="10" t="s">
@@ -3326,13 +3326,13 @@
         <v>1</v>
       </c>
       <c r="D59" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="15">
         <v>4055227</v>
       </c>
       <c r="F59" s="15"/>
-      <c r="G59" s="25" t="s">
+      <c r="G59" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H59" s="10" t="s">
@@ -3354,13 +3354,13 @@
         <v>1</v>
       </c>
       <c r="D60" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="15">
         <v>4055228</v>
       </c>
       <c r="F60" s="15"/>
-      <c r="G60" s="25" t="s">
+      <c r="G60" s="26" t="s">
         <v>55</v>
       </c>
       <c r="H60" s="10" t="s">
@@ -3375,16 +3375,16 @@
       <c r="A61" s="23">
         <v>1801</v>
       </c>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16">
+      <c r="B61" s="24"/>
+      <c r="C61" s="24">
         <v>1</v>
       </c>
       <c r="D61" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="25" t="s">
         <v>63</v>
       </c>
       <c r="H61" s="10" t="s">
@@ -3399,16 +3399,16 @@
       <c r="A62" s="23">
         <v>1802</v>
       </c>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16">
+      <c r="B62" s="24"/>
+      <c r="C62" s="24">
         <v>1</v>
       </c>
       <c r="D62" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="25" t="s">
         <v>63</v>
       </c>
       <c r="H62" s="10" t="s">
@@ -3423,20 +3423,20 @@
       <c r="A63" s="23">
         <v>1803</v>
       </c>
-      <c r="B63" s="16">
-        <v>2</v>
-      </c>
-      <c r="C63" s="16">
+      <c r="B63" s="24">
+        <v>2</v>
+      </c>
+      <c r="C63" s="24">
         <v>1</v>
       </c>
       <c r="D63" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="16">
+        <v>0</v>
+      </c>
+      <c r="E63" s="24">
         <v>4055243</v>
       </c>
-      <c r="F63" s="16"/>
-      <c r="G63" s="24" t="s">
+      <c r="F63" s="24"/>
+      <c r="G63" s="25" t="s">
         <v>63</v>
       </c>
       <c r="H63" s="10" t="s">
@@ -3451,20 +3451,20 @@
       <c r="A64" s="23">
         <v>1804</v>
       </c>
-      <c r="B64" s="16">
-        <v>2</v>
-      </c>
-      <c r="C64" s="16">
+      <c r="B64" s="24">
+        <v>2</v>
+      </c>
+      <c r="C64" s="24">
         <v>1</v>
       </c>
       <c r="D64" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="16">
+        <v>0</v>
+      </c>
+      <c r="E64" s="24">
         <v>4055244</v>
       </c>
-      <c r="F64" s="16"/>
-      <c r="G64" s="24" t="s">
+      <c r="F64" s="24"/>
+      <c r="G64" s="25" t="s">
         <v>63</v>
       </c>
       <c r="H64" s="10" t="s">
@@ -3479,20 +3479,20 @@
       <c r="A65" s="23">
         <v>1805</v>
       </c>
-      <c r="B65" s="16">
-        <v>2</v>
-      </c>
-      <c r="C65" s="16">
+      <c r="B65" s="24">
+        <v>2</v>
+      </c>
+      <c r="C65" s="24">
         <v>1</v>
       </c>
       <c r="D65" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="16">
+        <v>0</v>
+      </c>
+      <c r="E65" s="24">
         <v>4055245</v>
       </c>
-      <c r="F65" s="16"/>
-      <c r="G65" s="24" t="s">
+      <c r="F65" s="24"/>
+      <c r="G65" s="25" t="s">
         <v>63</v>
       </c>
       <c r="H65" s="10" t="s">
@@ -3507,20 +3507,20 @@
       <c r="A66" s="23">
         <v>1806</v>
       </c>
-      <c r="B66" s="16">
-        <v>2</v>
-      </c>
-      <c r="C66" s="16">
+      <c r="B66" s="24">
+        <v>2</v>
+      </c>
+      <c r="C66" s="24">
         <v>1</v>
       </c>
       <c r="D66" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="16">
+        <v>0</v>
+      </c>
+      <c r="E66" s="24">
         <v>4055246</v>
       </c>
-      <c r="F66" s="16"/>
-      <c r="G66" s="24" t="s">
+      <c r="F66" s="24"/>
+      <c r="G66" s="25" t="s">
         <v>63</v>
       </c>
       <c r="H66" s="10" t="s">
@@ -3535,20 +3535,20 @@
       <c r="A67" s="23">
         <v>1807</v>
       </c>
-      <c r="B67" s="16">
-        <v>2</v>
-      </c>
-      <c r="C67" s="16">
+      <c r="B67" s="24">
+        <v>2</v>
+      </c>
+      <c r="C67" s="24">
         <v>1</v>
       </c>
       <c r="D67" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="16">
+        <v>0</v>
+      </c>
+      <c r="E67" s="24">
         <v>4055247</v>
       </c>
-      <c r="F67" s="16"/>
-      <c r="G67" s="24" t="s">
+      <c r="F67" s="24"/>
+      <c r="G67" s="25" t="s">
         <v>63</v>
       </c>
       <c r="H67" s="10" t="s">
@@ -3567,12 +3567,12 @@
       <c r="C68" s="15">
         <v>1</v>
       </c>
-      <c r="D68" s="26" t="b">
+      <c r="D68" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E68" s="15"/>
       <c r="F68" s="15"/>
-      <c r="G68" s="25" t="s">
+      <c r="G68" s="26" t="s">
         <v>69</v>
       </c>
       <c r="H68" s="10" t="s">
@@ -3593,14 +3593,14 @@
       <c r="C69" s="15">
         <v>1</v>
       </c>
-      <c r="D69" s="26" t="b">
+      <c r="D69" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E69" s="15">
         <v>4055263</v>
       </c>
       <c r="F69" s="15"/>
-      <c r="G69" s="25" t="s">
+      <c r="G69" s="26" t="s">
         <v>69</v>
       </c>
       <c r="H69" s="10" t="s">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
-      <c r="D70" s="26" t="b">
+      <c r="D70" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E70" s="27"/>
       <c r="F70" s="15"/>
-      <c r="G70" s="25" t="s">
+      <c r="G70" s="26" t="s">
         <v>69</v>
       </c>
       <c r="I70" s="18"/>
@@ -3638,12 +3638,12 @@
       <c r="C71" s="15">
         <v>1</v>
       </c>
-      <c r="D71" s="26" t="b">
+      <c r="D71" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="15"/>
-      <c r="G71" s="25" t="s">
+      <c r="G71" s="26" t="s">
         <v>69</v>
       </c>
       <c r="H71" s="10"/>
@@ -3662,14 +3662,14 @@
       <c r="C72" s="15">
         <v>1</v>
       </c>
-      <c r="D72" s="26" t="b">
+      <c r="D72" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E72" s="15">
         <v>4055264</v>
       </c>
       <c r="F72" s="15"/>
-      <c r="G72" s="25" t="s">
+      <c r="G72" s="26" t="s">
         <v>69</v>
       </c>
       <c r="H72" s="10" t="s">
@@ -3684,16 +3684,16 @@
       <c r="A73" s="23">
         <v>1981</v>
       </c>
-      <c r="B73" s="16"/>
-      <c r="C73" s="16">
-        <v>1</v>
-      </c>
-      <c r="D73" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="24" t="s">
+      <c r="B73" s="24"/>
+      <c r="C73" s="24">
+        <v>1</v>
+      </c>
+      <c r="D73" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="25" t="s">
         <v>72</v>
       </c>
       <c r="H73" s="10" t="s">
@@ -3708,16 +3708,16 @@
       <c r="A74" s="23">
         <v>1982</v>
       </c>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16">
-        <v>1</v>
-      </c>
-      <c r="D74" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="24" t="s">
+      <c r="B74" s="24"/>
+      <c r="C74" s="24">
+        <v>1</v>
+      </c>
+      <c r="D74" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="25" t="s">
         <v>72</v>
       </c>
       <c r="H74" s="10" t="s">
@@ -3732,20 +3732,20 @@
       <c r="A75" s="23">
         <v>1983</v>
       </c>
-      <c r="B75" s="16">
-        <v>2</v>
-      </c>
-      <c r="C75" s="16">
-        <v>1</v>
-      </c>
-      <c r="D75" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E75" s="16">
+      <c r="B75" s="24">
+        <v>2</v>
+      </c>
+      <c r="C75" s="24">
+        <v>1</v>
+      </c>
+      <c r="D75" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" s="24">
         <v>4055321</v>
       </c>
-      <c r="F75" s="16"/>
-      <c r="G75" s="24" t="s">
+      <c r="F75" s="24"/>
+      <c r="G75" s="25" t="s">
         <v>72</v>
       </c>
       <c r="H75" s="10" t="s">
@@ -3764,12 +3764,12 @@
       <c r="C76" s="15">
         <v>1</v>
       </c>
-      <c r="D76" s="26" t="b">
+      <c r="D76" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E76" s="15"/>
       <c r="F76" s="15"/>
-      <c r="G76" s="25" t="s">
+      <c r="G76" s="26" t="s">
         <v>74</v>
       </c>
       <c r="H76" s="10" t="s">
@@ -3790,14 +3790,14 @@
       <c r="C77" s="15">
         <v>1</v>
       </c>
-      <c r="D77" s="26" t="b">
+      <c r="D77" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E77" s="15">
         <v>4055281</v>
       </c>
       <c r="F77" s="15"/>
-      <c r="G77" s="25" t="s">
+      <c r="G77" s="26" t="s">
         <v>74</v>
       </c>
       <c r="H77" s="10" t="s">
@@ -3818,14 +3818,14 @@
       <c r="C78" s="15">
         <v>1</v>
       </c>
-      <c r="D78" s="26" t="b">
+      <c r="D78" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E78" s="15">
         <v>4055282</v>
       </c>
       <c r="F78" s="15"/>
-      <c r="G78" s="25" t="s">
+      <c r="G78" s="26" t="s">
         <v>74</v>
       </c>
       <c r="H78" s="10" t="s">
@@ -3846,14 +3846,14 @@
       <c r="C79" s="15">
         <v>1</v>
       </c>
-      <c r="D79" s="26" t="b">
+      <c r="D79" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E79" s="15">
         <v>4055283</v>
       </c>
       <c r="F79" s="15"/>
-      <c r="G79" s="25" t="s">
+      <c r="G79" s="26" t="s">
         <v>74</v>
       </c>
       <c r="H79" s="10" t="s">
@@ -3874,14 +3874,14 @@
       <c r="C80" s="15">
         <v>1</v>
       </c>
-      <c r="D80" s="26" t="b">
+      <c r="D80" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E80" s="15">
         <v>4055284</v>
       </c>
       <c r="F80" s="15"/>
-      <c r="G80" s="25" t="s">
+      <c r="G80" s="26" t="s">
         <v>74</v>
       </c>
       <c r="H80" s="10" t="s">
@@ -3902,14 +3902,14 @@
       <c r="C81" s="15">
         <v>1</v>
       </c>
-      <c r="D81" s="26" t="b">
+      <c r="D81" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E81" s="15">
         <v>4055285</v>
       </c>
       <c r="F81" s="15"/>
-      <c r="G81" s="25" t="s">
+      <c r="G81" s="26" t="s">
         <v>74</v>
       </c>
       <c r="H81" s="10" t="s">
@@ -3930,14 +3930,14 @@
       <c r="C82" s="15">
         <v>1</v>
       </c>
-      <c r="D82" s="26" t="b">
+      <c r="D82" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E82" s="15">
         <v>4055286</v>
       </c>
       <c r="F82" s="15"/>
-      <c r="G82" s="25" t="s">
+      <c r="G82" s="26" t="s">
         <v>74</v>
       </c>
       <c r="H82" s="10" t="s">
@@ -3958,7 +3958,7 @@
       <c r="C83" s="29">
         <v>1</v>
       </c>
-      <c r="D83" s="26" t="b">
+      <c r="D83" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E83" s="29"/>
@@ -3982,7 +3982,7 @@
       <c r="C84" s="30">
         <v>1</v>
       </c>
-      <c r="D84" s="26" t="b">
+      <c r="D84" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E84" s="30">
@@ -4010,7 +4010,7 @@
       <c r="C85" s="30">
         <v>1</v>
       </c>
-      <c r="D85" s="26" t="b">
+      <c r="D85" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E85" s="30">
@@ -4038,8 +4038,8 @@
       <c r="C86" s="9">
         <v>2</v>
       </c>
-      <c r="D86" s="31" t="b">
-        <v>1</v>
+      <c r="D86" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E86" s="9">
         <v>4055341</v>
@@ -4048,12 +4048,12 @@
       <c r="G86" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H86" s="32" t="s">
+      <c r="H86" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="J86" s="33"/>
-      <c r="K86" s="33"/>
-      <c r="L86" s="33"/>
+      <c r="J86" s="32"/>
+      <c r="K86" s="32"/>
+      <c r="L86" s="32"/>
     </row>
     <row r="87" customHeight="1" spans="1:12">
       <c r="A87" s="9">
@@ -4065,8 +4065,8 @@
       <c r="C87" s="1">
         <v>1</v>
       </c>
-      <c r="D87" s="31" t="b">
-        <v>1</v>
+      <c r="D87" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E87" s="1">
         <v>4055342</v>
@@ -4074,7 +4074,7 @@
       <c r="G87" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H87" s="34" t="s">
+      <c r="H87" s="33" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4088,8 +4088,8 @@
       <c r="C88" s="1">
         <v>1</v>
       </c>
-      <c r="D88" s="31" t="b">
-        <v>1</v>
+      <c r="D88" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E88" s="1">
         <v>4055343</v>
@@ -4097,12 +4097,12 @@
       <c r="G88" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H88" s="34" t="s">
+      <c r="H88" s="33" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="89" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A89" s="31">
+      <c r="A89" s="34">
         <v>2204</v>
       </c>
       <c r="B89" s="1">
@@ -4111,17 +4111,17 @@
       <c r="C89" s="6">
         <v>1</v>
       </c>
-      <c r="D89" s="31" t="b">
-        <v>1</v>
+      <c r="D89" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E89" s="6">
         <v>4055344</v>
       </c>
       <c r="F89" s="6"/>
-      <c r="G89" s="31" t="s">
+      <c r="G89" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H89" s="34" t="s">
+      <c r="H89" s="33" t="s">
         <v>87</v>
       </c>
       <c r="I89" s="10"/>
@@ -4130,7 +4130,7 @@
       <c r="L89" s="10"/>
     </row>
     <row r="90" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A90" s="31">
+      <c r="A90" s="34">
         <v>2205</v>
       </c>
       <c r="B90" s="1">
@@ -4139,17 +4139,17 @@
       <c r="C90" s="6">
         <v>1</v>
       </c>
-      <c r="D90" s="31" t="b">
-        <v>1</v>
+      <c r="D90" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E90" s="6">
         <v>4055345</v>
       </c>
       <c r="F90" s="6"/>
-      <c r="G90" s="31" t="s">
+      <c r="G90" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H90" s="34" t="s">
+      <c r="H90" s="33" t="s">
         <v>88</v>
       </c>
       <c r="I90" s="10"/>
@@ -4158,7 +4158,7 @@
       <c r="L90" s="10"/>
     </row>
     <row r="91" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A91" s="31">
+      <c r="A91" s="34">
         <v>2206</v>
       </c>
       <c r="B91" s="1">
@@ -4167,17 +4167,17 @@
       <c r="C91" s="6">
         <v>1</v>
       </c>
-      <c r="D91" s="31" t="b">
-        <v>1</v>
+      <c r="D91" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E91" s="6">
         <v>4055346</v>
       </c>
       <c r="F91" s="6"/>
-      <c r="G91" s="31" t="s">
+      <c r="G91" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H91" s="34" t="s">
+      <c r="H91" s="33" t="s">
         <v>89</v>
       </c>
       <c r="I91" s="10"/>
@@ -4186,7 +4186,7 @@
       <c r="L91" s="10"/>
     </row>
     <row r="92" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A92" s="31">
+      <c r="A92" s="34">
         <v>2207</v>
       </c>
       <c r="B92" s="1">
@@ -4195,17 +4195,17 @@
       <c r="C92" s="6">
         <v>1</v>
       </c>
-      <c r="D92" s="31" t="b">
-        <v>1</v>
+      <c r="D92" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E92" s="6">
         <v>4055347</v>
       </c>
       <c r="F92" s="6"/>
-      <c r="G92" s="31" t="s">
+      <c r="G92" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H92" s="34" t="s">
+      <c r="H92" s="33" t="s">
         <v>87</v>
       </c>
       <c r="I92" s="10"/>
@@ -4214,7 +4214,7 @@
       <c r="L92" s="10"/>
     </row>
     <row r="93" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A93" s="31">
+      <c r="A93" s="34">
         <v>2208</v>
       </c>
       <c r="B93" s="1">
@@ -4223,17 +4223,17 @@
       <c r="C93" s="6">
         <v>1</v>
       </c>
-      <c r="D93" s="31" t="b">
-        <v>1</v>
+      <c r="D93" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E93" s="6">
         <v>4055348</v>
       </c>
       <c r="F93" s="6"/>
-      <c r="G93" s="31" t="s">
+      <c r="G93" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H93" s="34" t="s">
+      <c r="H93" s="33" t="s">
         <v>88</v>
       </c>
       <c r="I93" s="10"/>
@@ -4242,7 +4242,7 @@
       <c r="L93" s="10"/>
     </row>
     <row r="94" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A94" s="31">
+      <c r="A94" s="34">
         <v>2209</v>
       </c>
       <c r="B94" s="1">
@@ -4251,12 +4251,12 @@
       <c r="C94" s="6">
         <v>1</v>
       </c>
-      <c r="D94" s="31" t="b">
-        <v>1</v>
+      <c r="D94" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
-      <c r="G94" s="31" t="s">
+      <c r="G94" s="34" t="s">
         <v>83</v>
       </c>
       <c r="H94" s="10"/>
@@ -4266,7 +4266,7 @@
       <c r="L94" s="10"/>
     </row>
     <row r="95" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A95" s="31">
+      <c r="A95" s="34">
         <v>2210</v>
       </c>
       <c r="B95" s="1">
@@ -4275,17 +4275,17 @@
       <c r="C95" s="6">
         <v>1</v>
       </c>
-      <c r="D95" s="31" t="b">
-        <v>1</v>
+      <c r="D95" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E95" s="6">
         <v>4055350</v>
       </c>
       <c r="F95" s="6"/>
-      <c r="G95" s="31" t="s">
+      <c r="G95" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H95" s="34" t="s">
+      <c r="H95" s="33" t="s">
         <v>85</v>
       </c>
       <c r="J95" s="10"/>
@@ -4293,7 +4293,7 @@
       <c r="L95" s="10"/>
     </row>
     <row r="96" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A96" s="31">
+      <c r="A96" s="34">
         <v>2211</v>
       </c>
       <c r="B96" s="1">
@@ -4302,16 +4302,16 @@
       <c r="C96" s="6">
         <v>1</v>
       </c>
-      <c r="D96" s="31" t="b">
-        <v>1</v>
+      <c r="D96" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E96" s="1">
         <v>4055356</v>
       </c>
-      <c r="G96" s="31" t="s">
+      <c r="G96" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H96" s="34" t="s">
+      <c r="H96" s="33" t="s">
         <v>90</v>
       </c>
       <c r="I96" s="7"/>
@@ -4320,7 +4320,7 @@
       <c r="L96" s="10"/>
     </row>
     <row r="97" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A97" s="31">
+      <c r="A97" s="34">
         <v>2212</v>
       </c>
       <c r="B97" s="1">
@@ -4329,17 +4329,17 @@
       <c r="C97" s="6">
         <v>1</v>
       </c>
-      <c r="D97" s="31" t="b">
-        <v>1</v>
+      <c r="D97" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E97" s="6">
         <v>4055351</v>
       </c>
       <c r="F97" s="6"/>
-      <c r="G97" s="31" t="s">
+      <c r="G97" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H97" s="34" t="s">
+      <c r="H97" s="33" t="s">
         <v>91</v>
       </c>
       <c r="I97" s="10"/>
@@ -4348,7 +4348,7 @@
       <c r="L97" s="10"/>
     </row>
     <row r="98" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A98" s="31">
+      <c r="A98" s="34">
         <v>2213</v>
       </c>
       <c r="B98" s="1">
@@ -4357,14 +4357,14 @@
       <c r="C98" s="6">
         <v>1</v>
       </c>
-      <c r="D98" s="31" t="b">
-        <v>1</v>
+      <c r="D98" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E98" s="6">
         <v>4055352</v>
       </c>
       <c r="F98" s="6"/>
-      <c r="G98" s="31" t="s">
+      <c r="G98" s="34" t="s">
         <v>83</v>
       </c>
       <c r="H98" s="10" t="s">
@@ -4384,12 +4384,12 @@
       <c r="C99" s="6">
         <v>1</v>
       </c>
-      <c r="D99" s="31" t="b">
-        <v>1</v>
+      <c r="D99" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
-      <c r="G99" s="31" t="s">
+      <c r="G99" s="34" t="s">
         <v>83</v>
       </c>
       <c r="H99" s="10"/>
@@ -4399,7 +4399,7 @@
       <c r="L99" s="10"/>
     </row>
     <row r="100" customHeight="1" spans="1:12">
-      <c r="A100" s="31">
+      <c r="A100" s="34">
         <v>2215</v>
       </c>
       <c r="B100" s="1">
@@ -4408,8 +4408,8 @@
       <c r="C100" s="1">
         <v>1</v>
       </c>
-      <c r="D100" s="31" t="b">
-        <v>1</v>
+      <c r="D100" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="G100" s="9" t="s">
         <v>83</v>
@@ -4426,8 +4426,8 @@
       <c r="C101" s="1">
         <v>1</v>
       </c>
-      <c r="D101" s="31" t="b">
-        <v>1</v>
+      <c r="D101" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="E101" s="1">
         <v>4055355</v>
@@ -4447,7 +4447,7 @@
       <c r="C102" s="35">
         <v>2</v>
       </c>
-      <c r="D102" s="35" t="b">
+      <c r="D102" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E102" s="35"/>
@@ -4466,7 +4466,7 @@
       <c r="C103" s="35">
         <v>1</v>
       </c>
-      <c r="D103" s="35" t="b">
+      <c r="D103" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E103" s="35"/>
@@ -4485,7 +4485,7 @@
       <c r="C104" s="35">
         <v>1</v>
       </c>
-      <c r="D104" s="35" t="b">
+      <c r="D104" s="16" t="b">
         <v>0</v>
       </c>
       <c r="E104" s="35">

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="116">
   <si>
     <t>序号</t>
   </si>
@@ -460,6 +460,9 @@
   </si>
   <si>
     <t>在&lt;color=#00bfff&gt;萌宠小队&lt;/color&gt;游戏中有概率&lt;color=#00bfff&gt;中奖SWEET WIN 大奖&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>点击前往&lt;color=#00bfff&gt;游戏界面&lt;/color&gt;</t>
   </si>
   <si>
     <t>在线购买资源</t>
@@ -1833,7 +1836,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -4440,31 +4443,35 @@
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:12">
-      <c r="A102" s="35">
-        <v>2301</v>
-      </c>
-      <c r="B102" s="35"/>
-      <c r="C102" s="35">
-        <v>2</v>
+      <c r="A102" s="34">
+        <v>2217</v>
+      </c>
+      <c r="B102" s="1">
+        <v>2</v>
+      </c>
+      <c r="C102" s="1">
+        <v>1</v>
       </c>
       <c r="D102" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E102" s="35"/>
-      <c r="F102" s="35"/>
-      <c r="G102" s="1" t="s">
+      <c r="E102" s="1">
+        <v>4055357</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H102" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:12">
       <c r="A103" s="35">
-        <v>2302</v>
-      </c>
-      <c r="B103" s="35">
-        <v>1</v>
-      </c>
+        <v>2301</v>
+      </c>
+      <c r="B103" s="35"/>
       <c r="C103" s="35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103" s="16" t="b">
         <v>0</v>
@@ -4472,12 +4479,12 @@
       <c r="E103" s="35"/>
       <c r="F103" s="35"/>
       <c r="G103" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="1:12">
       <c r="A104" s="35">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="B104" s="35">
         <v>1</v>
@@ -4488,15 +4495,34 @@
       <c r="D104" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E104" s="35">
-        <v>4055371</v>
-      </c>
+      <c r="E104" s="35"/>
       <c r="F104" s="35"/>
       <c r="G104" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H104" s="10" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="1:12">
+      <c r="A105" s="35">
+        <v>2303</v>
+      </c>
+      <c r="B105" s="35">
+        <v>1</v>
+      </c>
+      <c r="C105" s="35">
+        <v>1</v>
+      </c>
+      <c r="D105" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E105" s="35">
+        <v>4055371</v>
+      </c>
+      <c r="F105" s="35"/>
+      <c r="G105" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -4557,14 +4583,14 @@
         <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -4573,7 +4599,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4583,14 +4609,14 @@
         <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4598,14 +4624,14 @@
         <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4613,14 +4639,14 @@
         <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4628,14 +4654,14 @@
         <v>2205</v>
       </c>
       <c r="J9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
         <v>2205_</v>
       </c>
       <c r="M9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4643,14 +4669,14 @@
         <v>2206</v>
       </c>
       <c r="J10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>2206_</v>
       </c>
       <c r="M10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4658,14 +4684,14 @@
         <v>2207</v>
       </c>
       <c r="J11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>2207_</v>
       </c>
       <c r="M11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4673,14 +4699,14 @@
         <v>2208</v>
       </c>
       <c r="J12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>2208_</v>
       </c>
       <c r="M12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4688,32 +4714,32 @@
         <v>2209</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>2209_</v>
       </c>
       <c r="M13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I14">
         <v>2210</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>2210_</v>
       </c>
       <c r="M14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4721,14 +4747,14 @@
         <v>2211</v>
       </c>
       <c r="J15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>2211_</v>
       </c>
       <c r="M15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4736,14 +4762,14 @@
         <v>2212</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>2212_</v>
       </c>
       <c r="M16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4751,14 +4777,14 @@
         <v>2213</v>
       </c>
       <c r="J17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>2213_</v>
       </c>
       <c r="M17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4766,29 +4792,29 @@
         <v>2214</v>
       </c>
       <c r="J18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>2214_</v>
       </c>
       <c r="M18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -171,7 +171,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-只有“小助手\气泡框”才有，没配置就没有语言</t>
+只有“小助手\气泡框”有文本的才有，没配置就没有语言
+语音路径：...\Assets\AssetsPackage\Common\GameArtsCommon\Common\audio</t>
         </r>
       </text>
     </comment>
@@ -180,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="116">
   <si>
     <t>序号</t>
   </si>
@@ -251,9 +252,6 @@
     <t>恭喜！将聘请您成为GECA黄金星娱乐城经理人</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>很高兴加入，我会把娱乐城发展为全球第一城</t>
   </si>
   <si>
@@ -261,6 +259,9 @@
   </si>
   <si>
     <t>开始经营娱乐城</t>
+  </si>
+  <si>
+    <t>welcome_test.mp3</t>
   </si>
   <si>
     <t>建筑-愤怒的小鸟-升级2次</t>
@@ -770,12 +771,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1844,7 +1845,7 @@
     <col min="3" max="3" width="16.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="85.2916666666667" style="10" customWidth="1"/>
     <col min="13" max="16384" width="15.625" style="1"/>
@@ -2077,9 +2078,7 @@
       <c r="H10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="18" t="s">
-        <v>23</v>
-      </c>
+      <c r="J10" s="18"/>
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
     </row>
@@ -2100,7 +2099,7 @@
         <v>16</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
@@ -2124,7 +2123,7 @@
         <v>16</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -2147,7 +2146,7 @@
         <v>16</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
@@ -2250,7 +2249,9 @@
       <c r="E18" s="24">
         <v>4055121</v>
       </c>
-      <c r="F18" s="24"/>
+      <c r="F18" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G18" s="25" t="s">
         <v>27</v>
       </c>
@@ -2278,7 +2279,9 @@
       <c r="E19" s="24">
         <v>4055122</v>
       </c>
-      <c r="F19" s="24"/>
+      <c r="F19" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G19" s="25" t="s">
         <v>27</v>
       </c>
@@ -2306,7 +2309,9 @@
       <c r="E20" s="24">
         <v>4055123</v>
       </c>
-      <c r="F20" s="24"/>
+      <c r="F20" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G20" s="25" t="s">
         <v>27</v>
       </c>
@@ -2334,7 +2339,9 @@
       <c r="E21" s="24">
         <v>4055124</v>
       </c>
-      <c r="F21" s="24"/>
+      <c r="F21" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G21" s="25" t="s">
         <v>27</v>
       </c>
@@ -2362,7 +2369,9 @@
       <c r="E22" s="15">
         <v>4055141</v>
       </c>
-      <c r="F22" s="15"/>
+      <c r="F22" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G22" s="26" t="s">
         <v>32</v>
       </c>
@@ -2390,7 +2399,9 @@
       <c r="E23" s="15">
         <v>4055142</v>
       </c>
-      <c r="F23" s="15"/>
+      <c r="F23" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G23" s="26" t="s">
         <v>32</v>
       </c>
@@ -2418,7 +2429,9 @@
       <c r="E24" s="15">
         <v>4055143</v>
       </c>
-      <c r="F24" s="15"/>
+      <c r="F24" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G24" s="26" t="s">
         <v>32</v>
       </c>
@@ -2468,7 +2481,9 @@
       <c r="E26" s="15">
         <v>4055144</v>
       </c>
-      <c r="F26" s="15"/>
+      <c r="F26" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G26" s="26" t="s">
         <v>32</v>
       </c>
@@ -2496,7 +2511,9 @@
       <c r="E27" s="24">
         <v>4055161</v>
       </c>
-      <c r="F27" s="24"/>
+      <c r="F27" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G27" s="25" t="s">
         <v>38</v>
       </c>
@@ -2524,7 +2541,9 @@
       <c r="E28" s="24">
         <v>4055162</v>
       </c>
-      <c r="F28" s="24"/>
+      <c r="F28" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G28" s="25" t="s">
         <v>38</v>
       </c>
@@ -2552,7 +2571,9 @@
       <c r="E29" s="24">
         <v>4055163</v>
       </c>
-      <c r="F29" s="24"/>
+      <c r="F29" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G29" s="25" t="s">
         <v>38</v>
       </c>
@@ -2580,7 +2601,9 @@
       <c r="E30" s="24">
         <v>4055164</v>
       </c>
-      <c r="F30" s="24"/>
+      <c r="F30" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G30" s="25" t="s">
         <v>38</v>
       </c>
@@ -4047,7 +4070,9 @@
       <c r="E86" s="9">
         <v>4055341</v>
       </c>
-      <c r="F86" s="9"/>
+      <c r="F86" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G86" s="9" t="s">
         <v>83</v>
       </c>
@@ -4074,6 +4099,9 @@
       <c r="E87" s="1">
         <v>4055342</v>
       </c>
+      <c r="F87" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G87" s="9" t="s">
         <v>83</v>
       </c>
@@ -4097,6 +4125,9 @@
       <c r="E88" s="1">
         <v>4055343</v>
       </c>
+      <c r="F88" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G88" s="9" t="s">
         <v>83</v>
       </c>
@@ -4120,7 +4151,9 @@
       <c r="E89" s="6">
         <v>4055344</v>
       </c>
-      <c r="F89" s="6"/>
+      <c r="F89" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G89" s="34" t="s">
         <v>83</v>
       </c>
@@ -4148,7 +4181,9 @@
       <c r="E90" s="6">
         <v>4055345</v>
       </c>
-      <c r="F90" s="6"/>
+      <c r="F90" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G90" s="34" t="s">
         <v>83</v>
       </c>
@@ -4176,7 +4211,9 @@
       <c r="E91" s="6">
         <v>4055346</v>
       </c>
-      <c r="F91" s="6"/>
+      <c r="F91" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G91" s="34" t="s">
         <v>83</v>
       </c>
@@ -4204,7 +4241,9 @@
       <c r="E92" s="6">
         <v>4055347</v>
       </c>
-      <c r="F92" s="6"/>
+      <c r="F92" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G92" s="34" t="s">
         <v>83</v>
       </c>
@@ -4232,7 +4271,9 @@
       <c r="E93" s="6">
         <v>4055348</v>
       </c>
-      <c r="F93" s="6"/>
+      <c r="F93" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G93" s="34" t="s">
         <v>83</v>
       </c>
@@ -4284,7 +4325,9 @@
       <c r="E95" s="6">
         <v>4055350</v>
       </c>
-      <c r="F95" s="6"/>
+      <c r="F95" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G95" s="34" t="s">
         <v>83</v>
       </c>
@@ -4310,6 +4353,9 @@
       </c>
       <c r="E96" s="1">
         <v>4055356</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="G96" s="34" t="s">
         <v>83</v>
@@ -4338,7 +4384,9 @@
       <c r="E97" s="6">
         <v>4055351</v>
       </c>
-      <c r="F97" s="6"/>
+      <c r="F97" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G97" s="34" t="s">
         <v>83</v>
       </c>
@@ -4366,7 +4414,9 @@
       <c r="E98" s="6">
         <v>4055352</v>
       </c>
-      <c r="F98" s="6"/>
+      <c r="F98" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G98" s="34" t="s">
         <v>83</v>
       </c>
@@ -4435,6 +4485,9 @@
       <c r="E101" s="1">
         <v>4055355</v>
       </c>
+      <c r="F101" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="G101" s="9" t="s">
         <v>83</v>
       </c>
@@ -4457,6 +4510,9 @@
       </c>
       <c r="E102" s="1">
         <v>4055357</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="G102" s="9" t="s">
         <v>83</v>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="188">
   <si>
     <t>序号</t>
   </si>
@@ -231,242 +231,457 @@
     <t>SoundFile</t>
   </si>
   <si>
+    <t>1001.mp3</t>
+  </si>
+  <si>
     <t>初入游戏-创建新号到经营大厅</t>
   </si>
   <si>
-    <t>欢迎来到GECA黄金星娱乐城，我是面试官Miss.wang，你是来参加面试的嘛？</t>
-  </si>
-  <si>
-    <t>是的，我会让你大吃一惊的</t>
-  </si>
-  <si>
-    <t>好的，你展示你的技术吧</t>
+    <t>欢迎来到GECA黄金星娱乐城。我是面试官，AURORA 。</t>
+  </si>
+  <si>
+    <t>1002.mp3</t>
+  </si>
+  <si>
+    <t>您好，我是来面试经理人的。听说这里需要一个能把"废铁"变黄金的人 。</t>
+  </si>
+  <si>
+    <t>1003.mp3</t>
+  </si>
+  <si>
+    <t>简历很漂亮——但我不看那个。那里有台机器，看你表现 。</t>
+  </si>
+  <si>
+    <t>1004.mp3</t>
   </si>
   <si>
     <t>点击&lt;color=#00bfff&gt;旋转&lt;/color&gt;按钮，赢得大奖</t>
   </si>
   <si>
-    <t>哇，真的爆大奖了</t>
-  </si>
-  <si>
-    <t>恭喜！将聘请您成为GECA黄金星娱乐城经理人</t>
-  </si>
-  <si>
-    <t>很高兴加入，我会把娱乐城发展为全球第一城</t>
-  </si>
-  <si>
-    <t>接下来我带你熟悉一下你的工作</t>
+    <t>1005.mp3</t>
+  </si>
+  <si>
+    <t>看来这台机器已经替我交了一份满意的答卷 。</t>
+  </si>
+  <si>
+    <t>1006.mp3</t>
+  </si>
+  <si>
+    <t>您做得很好，欢迎加入GECA 。</t>
+  </si>
+  <si>
+    <t>1007.mp3</t>
+  </si>
+  <si>
+    <t>接下来做什么 ？</t>
+  </si>
+  <si>
+    <t>1008.mp3</t>
+  </si>
+  <si>
+    <t>我先带你了解一下工作内容 。</t>
+  </si>
+  <si>
+    <t>1009.mp3</t>
   </si>
   <si>
     <t>开始经营娱乐城</t>
   </si>
   <si>
-    <t>welcome_test.mp3</t>
+    <t>1010.mp3</t>
+  </si>
+  <si>
+    <t>1011.mp3</t>
+  </si>
+  <si>
+    <t>1012.mp3</t>
+  </si>
+  <si>
+    <t>1013.mp3</t>
+  </si>
+  <si>
+    <t>1201.mp3</t>
   </si>
   <si>
     <t>建筑-愤怒的小鸟-升级2次</t>
   </si>
   <si>
-    <t>点击[+]图标解锁SLOT游戏&lt;color=#00bfff&gt;萌宠小队&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>点击&lt;color=#00bfff&gt;游戏建筑&lt;/color&gt;进行升级提升收益。</t>
-  </si>
-  <si>
-    <t>点击&lt;color=#00bfff&gt;升级&lt;/color&gt;按钮，对建筑进行升级。</t>
-  </si>
-  <si>
-    <t>点击&lt;color=#00bfff&gt;开始游戏&lt;/color&gt;进入SLOT游戏，探索新玩法。</t>
+    <t>1202.mp3</t>
+  </si>
+  <si>
+    <t>1203.mp3</t>
+  </si>
+  <si>
+    <t>1204.mp3</t>
+  </si>
+  <si>
+    <t>1301.mp3</t>
   </si>
   <si>
     <t>建筑-愤怒的小鸟-SLOT</t>
   </si>
   <si>
-    <t>消耗&lt;sprite name="tiliIcon"&gt;赢奖有机会获得研究值
-[&lt;sprite name="yjdIcon"&gt;研究点：用于升级提升爆奖属性和经营收益</t>
-  </si>
-  <si>
-    <t>点击&lt;color=#00bfff&gt;旋转&lt;/color&gt;按钮，开启SLOT游戏旅程！</t>
-  </si>
-  <si>
-    <t>请&lt;color=#00bfff&gt;再次旋转&lt;/color&gt;游戏</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>游戏操作已教学完成，剩下的就交给您自由探索了！</t>
+    <t>1302.mp3</t>
+  </si>
+  <si>
+    <t>点击&lt;color=#00bfff&gt;旋转&lt;/color&gt;按钮，开启旅程！</t>
+  </si>
+  <si>
+    <t>1303.mp3</t>
+  </si>
+  <si>
+    <t>1304.mp3</t>
+  </si>
+  <si>
+    <t>1305.mp3</t>
+  </si>
+  <si>
+    <t>1401.mp3</t>
   </si>
   <si>
     <t>建筑-愤怒的小鸟-升到2级</t>
   </si>
   <si>
-    <t>请再次&lt;color=#00bfff&gt;连续点击&lt;/color&gt;升级按钮</t>
-  </si>
-  <si>
-    <t>建筑升级需要时间，使用&lt;color=#00bfff&gt;加速卡、钻石或观看广告&lt;/color&gt;可以加速完成</t>
-  </si>
-  <si>
-    <t>提高爆率赢取大奖需要提升科研等级！点击&lt;color=#00bfff&gt;科研&lt;/color&gt;进行升级</t>
-  </si>
-  <si>
-    <t>每个游戏可以进行多项科研，科研等级越高，中奖概率越大！</t>
-  </si>
-  <si>
-    <t>科研升级成功！进入游戏体验爆奖效果。</t>
+    <t>1402.mp3</t>
+  </si>
+  <si>
+    <t>1403.mp3</t>
+  </si>
+  <si>
+    <t>1404.mp3</t>
+  </si>
+  <si>
+    <t>1405.mp3</t>
+  </si>
+  <si>
+    <t>1406.mp3</t>
+  </si>
+  <si>
+    <t>1501.mp3</t>
   </si>
   <si>
     <t>建筑-愤怒的小鸟-SLOT2</t>
   </si>
   <si>
-    <t>请点击&lt;color=#00bfff&gt;旋转按钮&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>请&lt;color=#00bfff&gt;再次旋转游戏&lt;/color&gt;</t>
+    <t>1502.mp3</t>
+  </si>
+  <si>
+    <t>1503.mp3</t>
+  </si>
+  <si>
+    <t>1504.mp3</t>
+  </si>
+  <si>
+    <t>1601.mp3</t>
   </si>
   <si>
     <t>雇员-抽卡-升级-升星</t>
   </si>
   <si>
+    <t>1602.mp3</t>
+  </si>
+  <si>
+    <t>1603.mp3</t>
+  </si>
+  <si>
     <t>前往招募管理人才！</t>
   </si>
   <si>
-    <t>点击&lt;color=#00bfff&gt;按钮&lt;/color&gt;开始招募！</t>
+    <t>1604.mp3</t>
+  </si>
+  <si>
+    <t>1605.mp3</t>
+  </si>
+  <si>
+    <t>点击&lt;color=#00bfff&gt;按钮&lt;/color&gt;开始招募</t>
+  </si>
+  <si>
+    <t>1606.mp3</t>
+  </si>
+  <si>
+    <t>1607.mp3</t>
+  </si>
+  <si>
+    <t>1608.mp3</t>
   </si>
   <si>
     <t>选择雇员类型&lt;color=#00bfff&gt;游戏经理&lt;/color&gt;</t>
   </si>
   <si>
-    <t>游戏经理可为建筑增加收益加成。每类建筑可任命一名雇员作为主管。</t>
-  </si>
-  <si>
-    <t>将雇员任命为主管，雇员特殊属性才会生效。</t>
-  </si>
-  <si>
-    <t>雇员等级越高，固定加成越多。培训可提升等级！</t>
-  </si>
-  <si>
-    <t>任命主管人员星级越高，建筑加成比例越高，需重点培养！</t>
+    <t>1609.mp3</t>
+  </si>
+  <si>
+    <t>游戏经理可以给游戏建筑增加基础收益。每个类型的游戏建筑可以任命一名雇员作为主管。</t>
+  </si>
+  <si>
+    <t>1610.mp3</t>
+  </si>
+  <si>
+    <t>将雇员任命为游戏建筑的主管后，雇员的专属技能才会生效。</t>
+  </si>
+  <si>
+    <t>1611.mp3</t>
+  </si>
+  <si>
+    <t>雇员等级和星级越高，对游戏建筑的基础加成越多！</t>
+  </si>
+  <si>
+    <t>1612.mp3</t>
+  </si>
+  <si>
+    <t>1701.mp3</t>
   </si>
   <si>
     <t>游客-抽卡-升星</t>
   </si>
   <si>
-    <t>点击这里进入&lt;color=#00bfff&gt;邀请特殊游客&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>点击这里查看并使用已获得的&lt;color=#00bfff&gt;游客特邀卡&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>特邀卡支持一键邀请或单个邀请，邀请后游客会带来丰厚的收益。</t>
-  </si>
-  <si>
-    <t>成功邀请特殊游客！继续解锁新游客！</t>
-  </si>
-  <si>
-    <t>请点击&lt;color=#00bfff&gt;游客&lt;/color&gt;按钮</t>
-  </si>
-  <si>
-    <t>获得特殊游客！&lt;color=#00bfff&gt;升星&lt;/color&gt;可提升游客价值。</t>
-  </si>
-  <si>
-    <t>游客升星提升游客价值增加运营收益，有&lt;color=#00bfff&gt;概率掉落稀有道具&lt;/color&gt;</t>
+    <t>1702.mp3</t>
+  </si>
+  <si>
+    <t>1703.mp3</t>
+  </si>
+  <si>
+    <t>1704.mp3</t>
+  </si>
+  <si>
+    <t>1705.mp3</t>
+  </si>
+  <si>
+    <t>1706.mp3</t>
+  </si>
+  <si>
+    <t>1707.mp3</t>
+  </si>
+  <si>
+    <t>1708.mp3</t>
+  </si>
+  <si>
+    <t>1709.mp3</t>
+  </si>
+  <si>
+    <t>1710.mp3</t>
+  </si>
+  <si>
+    <t>1711.mp3</t>
+  </si>
+  <si>
+    <t>1712.mp3</t>
+  </si>
+  <si>
+    <t>1801.mp3</t>
   </si>
   <si>
     <t>建筑-象财神-升级</t>
   </si>
   <si>
-    <t>新建筑需解锁后才能激活新游戏！</t>
-  </si>
-  <si>
-    <t>请及时对建筑进行升级，提高运营收益。</t>
-  </si>
-  <si>
-    <t>&lt;color=#00bfff&gt;连续点击&lt;/color&gt;对当前建筑进行升级</t>
-  </si>
-  <si>
-    <t>建筑升级需要等待，使用&lt;color=#00bfff&gt;加速卡、钻石或观看广告&lt;/color&gt;可加速完成</t>
-  </si>
-  <si>
-    <t>游戏&lt;color=#00bfff&gt;象财神&lt;/color&gt;已解锁，前往体验！</t>
+    <t>1802.mp3</t>
+  </si>
+  <si>
+    <t>1803.mp3</t>
+  </si>
+  <si>
+    <t>1804.mp3</t>
+  </si>
+  <si>
+    <t>1805.mp3</t>
+  </si>
+  <si>
+    <t>1806.mp3</t>
+  </si>
+  <si>
+    <t>1807.mp3</t>
+  </si>
+  <si>
+    <t>1901.mp3</t>
   </si>
   <si>
     <t>赛季-界面-SLOT</t>
   </si>
   <si>
-    <t>点击这里进入&lt;color=#00bfff&gt;赛季&lt;/color&gt;界面</t>
-  </si>
-  <si>
-    <t>体验经典游戏！游戏需消耗&lt;color=#00bfff&gt;赛季币&lt;/color&gt;，赚取赛季币也是重要目标。</t>
+    <t>1902.mp3</t>
+  </si>
+  <si>
+    <t>点击进入&lt;color=#00bfff&gt;赛季&lt;/color&gt;界面</t>
+  </si>
+  <si>
+    <t>1903.mp3</t>
+  </si>
+  <si>
+    <t>1904.mp3</t>
+  </si>
+  <si>
+    <t>1905.mp3</t>
+  </si>
+  <si>
+    <t>体验游戏需消耗&lt;color=#00bfff&gt;赛季币&lt;/color&gt;，赚取赛季币也是重要目标之一。</t>
+  </si>
+  <si>
+    <t>1981.mp3</t>
   </si>
   <si>
     <t>赛季-斗仙牌-前置</t>
   </si>
   <si>
-    <t>【Aether Trial】是赛季核心&lt;color=#00bfff&gt;多人竞技玩法&lt;/color&gt;，使用赛季币参与。</t>
+    <t>1982.mp3</t>
+  </si>
+  <si>
+    <t>1983.mp3</t>
+  </si>
+  <si>
+    <t>【Aether Trial】是赛季&lt;color=#00bfff&gt;多人竞技玩法&lt;/color&gt;，使用赛季币参与。</t>
+  </si>
+  <si>
+    <t>2001.mp3</t>
   </si>
   <si>
     <t>赛季-斗仙牌</t>
   </si>
   <si>
-    <t>准备好了吗？开始游戏！</t>
+    <t>2002.mp3</t>
+  </si>
+  <si>
+    <t>准备好了吗？请开始游戏！</t>
+  </si>
+  <si>
+    <t>2003.mp3</t>
   </si>
   <si>
     <t>点击区域可以快速提起该区域最大牌型</t>
   </si>
   <si>
+    <t>2004.mp3</t>
+  </si>
+  <si>
     <t>点击&lt;color=#00bfff&gt;放入&lt;/color&gt;牌型到指定区域内</t>
   </si>
   <si>
+    <t>2005.mp3</t>
+  </si>
+  <si>
+    <t>2006.mp3</t>
+  </si>
+  <si>
+    <t>2007.mp3</t>
+  </si>
+  <si>
     <t>在未提牌时，点击区域内的牌可将牌&lt;color=#00bfff&gt;取回&lt;/color&gt;</t>
   </si>
   <si>
+    <t>2100.mp3</t>
+  </si>
+  <si>
     <t>联盟-触发</t>
   </si>
   <si>
+    <t>2101.mp3</t>
+  </si>
+  <si>
     <t>联盟</t>
   </si>
   <si>
     <t>和好友完成联盟任务与每日捐献，可获得稀有联盟道具！</t>
   </si>
   <si>
+    <t>2102.mp3</t>
+  </si>
+  <si>
     <t>加入联盟有两种方式：加入他人联盟或自己创建，和好友共同赚取收益！</t>
   </si>
   <si>
+    <t>2201.mp3</t>
+  </si>
+  <si>
     <t>小鸟建筑升级</t>
   </si>
   <si>
     <t>点击[+]图标解锁&lt;color=#00bfff&gt;萌宠小队&lt;/color&gt;游戏</t>
   </si>
   <si>
+    <t>2202.mp3</t>
+  </si>
+  <si>
     <t>点击去完成&lt;color=#00bfff&gt;主线任务&lt;/color&gt;</t>
   </si>
   <si>
+    <t>2203.mp3</t>
+  </si>
+  <si>
     <t>点击按钮&lt;color=#00bfff&gt;进行升级&lt;/color&gt;</t>
   </si>
   <si>
+    <t>2204.mp3</t>
+  </si>
+  <si>
     <t>&lt;color=#00bfff&gt;连续点击或长按&lt;/color&gt;升级至进度条完成</t>
   </si>
   <si>
-    <t>建筑升级期间会有一定的等待时间，&lt;color=#00bfff&gt;使用加速卡、钻石或观看广告&lt;/color&gt;可以快速清除等待时间</t>
+    <t>2205.mp3</t>
+  </si>
+  <si>
+    <t>建筑升级期间会有一定的等待时间，&lt;color=#00bfff&gt;使用加速卡、钻石或观看广告&lt;/color&gt;可以快速消除等待时间</t>
+  </si>
+  <si>
+    <t>2206.mp3</t>
   </si>
   <si>
     <t>娱乐城已&lt;color=#00bfff&gt;提升到2级&lt;/color&gt;，解锁了一些&lt;color=#00bfff&gt;新功能&lt;/color&gt;</t>
   </si>
   <si>
-    <t>点击打开&lt;color=#00bfff&gt;游戏技能&lt;/color&gt;界面</t>
+    <t>2207.mp3</t>
+  </si>
+  <si>
+    <t>2208.mp3</t>
+  </si>
+  <si>
+    <t>2209.mp3</t>
+  </si>
+  <si>
+    <t>2210.mp3</t>
+  </si>
+  <si>
+    <t>2211.mp3</t>
+  </si>
+  <si>
+    <t>点击前往&lt;color=#00bfff&gt;解锁游戏技能&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>2212.mp3</t>
   </si>
   <si>
     <t>解锁 &lt;color=#00bfff&gt;SWEET WIN 大奖&lt;/color&gt;技能</t>
   </si>
   <si>
+    <t>2213.mp3</t>
+  </si>
+  <si>
     <t>在&lt;color=#00bfff&gt;萌宠小队&lt;/color&gt;游戏中有概率&lt;color=#00bfff&gt;中奖SWEET WIN 大奖&lt;/color&gt;</t>
   </si>
   <si>
+    <t>2214.mp3</t>
+  </si>
+  <si>
+    <t>2215.mp3</t>
+  </si>
+  <si>
+    <t>2216.mp3</t>
+  </si>
+  <si>
+    <t>2217.mp3</t>
+  </si>
+  <si>
     <t>点击前往&lt;color=#00bfff&gt;游戏界面&lt;/color&gt;</t>
   </si>
   <si>
+    <t>2301.mp3</t>
+  </si>
+  <si>
     <t>在线购买资源</t>
+  </si>
+  <si>
+    <t>2302.mp3</t>
+  </si>
+  <si>
+    <t>2303.mp3</t>
   </si>
   <si>
     <t>在这里可以&lt;color=#00bfff&gt;快速获得金币、娱乐城经验&lt;/color&gt;等资源</t>
@@ -542,7 +757,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -594,12 +809,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.5"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -615,13 +824,6 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.25"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF92D050"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -771,18 +973,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -791,13 +993,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.05"/>
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1114,137 +1322,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1263,15 +1471,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1287,70 +1498,52 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1847,40 +2040,40 @@
     <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="85.2916666666667" style="10" customWidth="1"/>
+    <col min="8" max="8" width="100.883333333333" style="11" customWidth="1"/>
     <col min="13" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10"/>
+      <c r="H1" s="11"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
       <c r="L1"/>
     </row>
     <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1892,71 +2085,73 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="10"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="11"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="10"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="11"/>
       <c r="I3"/>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="13"/>
-      <c r="H4" s="10"/>
+      <c r="A4" s="14"/>
+      <c r="H4" s="11"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
     </row>
     <row r="5" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="14">
+      <c r="A5" s="15">
         <v>1001</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
       <c r="D5" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="16">
         <v>4055101</v>
       </c>
-      <c r="F5" s="15"/>
+      <c r="F5" s="16" t="s">
+        <v>16</v>
+      </c>
       <c r="G5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
@@ -1964,23 +2159,25 @@
       <c r="L5" s="18"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <v>1002</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="16">
         <v>4055102</v>
       </c>
-      <c r="F6" s="15"/>
+      <c r="F6" s="16" t="s">
+        <v>19</v>
+      </c>
       <c r="G6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
@@ -1988,23 +2185,25 @@
       <c r="L6" s="18"/>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <v>1003</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
       <c r="D7" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="16">
         <v>4055103</v>
       </c>
-      <c r="F7" s="15"/>
+      <c r="F7" s="16" t="s">
+        <v>21</v>
+      </c>
       <c r="G7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>22</v>
       </c>
       <c r="I7" s="18"/>
       <c r="J7" s="18"/>
@@ -2012,23 +2211,25 @@
       <c r="L7" s="18"/>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="14">
+      <c r="A8" s="15">
         <v>1004</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="16">
         <v>4055104</v>
       </c>
-      <c r="F8" s="15"/>
+      <c r="F8" s="16" t="s">
+        <v>23</v>
+      </c>
       <c r="G8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="I8" s="18"/>
       <c r="J8" s="18"/>
@@ -2036,23 +2237,25 @@
       <c r="L8" s="18"/>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <v>1005</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="16">
         <v>4055109</v>
       </c>
-      <c r="F9" s="15"/>
+      <c r="F9" s="16" t="s">
+        <v>25</v>
+      </c>
       <c r="G9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
@@ -2060,46 +2263,50 @@
       <c r="L9" s="18"/>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <v>1006</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="16">
         <v>4055105</v>
       </c>
-      <c r="F10" s="15"/>
+      <c r="F10" s="16" t="s">
+        <v>27</v>
+      </c>
       <c r="G10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J10" s="18"/>
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <v>1007</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="16">
         <v>4055106</v>
       </c>
-      <c r="F11" s="15"/>
+      <c r="F11" s="16" t="s">
+        <v>29</v>
+      </c>
       <c r="G11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>23</v>
+        <v>17</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
@@ -2107,46 +2314,50 @@
       <c r="L11" s="18"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="14">
+      <c r="A12" s="15">
         <v>1008</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
       <c r="D12" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="16">
         <v>4055107</v>
       </c>
-      <c r="F12" s="15"/>
+      <c r="F12" s="16" t="s">
+        <v>31</v>
+      </c>
       <c r="G12" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="14">
+      <c r="A13" s="15">
         <v>1009</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
       <c r="D13" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="16">
         <v>4055108</v>
       </c>
-      <c r="F13" s="15"/>
+      <c r="F13" s="16" t="s">
+        <v>33</v>
+      </c>
       <c r="G13" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
@@ -2154,1559 +2365,1568 @@
       <c r="L13" s="18"/>
     </row>
     <row r="14" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="20">
+      <c r="A14" s="19">
         <v>1010</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20" t="s">
+        <v>35</v>
+      </c>
       <c r="G14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+        <v>17</v>
+      </c>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
     </row>
     <row r="15" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="20">
+      <c r="A15" s="19">
         <v>1011</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20" t="s">
+        <v>36</v>
+      </c>
       <c r="G15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+        <v>17</v>
+      </c>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
     </row>
     <row r="16" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="20">
+      <c r="A16" s="19">
         <v>1012</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20" t="s">
+        <v>37</v>
+      </c>
       <c r="G16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
+        <v>17</v>
+      </c>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
     </row>
     <row r="17" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="20">
+      <c r="A17" s="19">
         <v>1013</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20" t="s">
+        <v>38</v>
+      </c>
       <c r="G17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-    </row>
-    <row r="18" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="23">
+        <v>17</v>
+      </c>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+    </row>
+    <row r="18" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A18" s="19">
         <v>1201</v>
       </c>
-      <c r="B18" s="24">
-        <v>2</v>
-      </c>
-      <c r="C18" s="24">
-        <v>2</v>
-      </c>
-      <c r="D18" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="24">
+      <c r="B18" s="20">
+        <v>2</v>
+      </c>
+      <c r="C18" s="20">
+        <v>2</v>
+      </c>
+      <c r="D18" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="20">
         <v>4055121</v>
       </c>
-      <c r="F18" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="23">
+      <c r="F18" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+    </row>
+    <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A19" s="19">
         <v>1202</v>
       </c>
-      <c r="B19" s="24">
-        <v>2</v>
-      </c>
-      <c r="C19" s="24">
-        <v>2</v>
-      </c>
-      <c r="D19" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="24">
+      <c r="B19" s="20">
+        <v>2</v>
+      </c>
+      <c r="C19" s="20">
+        <v>2</v>
+      </c>
+      <c r="D19" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="20">
         <v>4055122</v>
       </c>
-      <c r="F19" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-    </row>
-    <row r="20" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="23">
+      <c r="F19" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+    </row>
+    <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A20" s="19">
         <v>1203</v>
       </c>
-      <c r="B20" s="24">
-        <v>2</v>
-      </c>
-      <c r="C20" s="24">
-        <v>1</v>
-      </c>
-      <c r="D20" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="24">
+      <c r="B20" s="20">
+        <v>2</v>
+      </c>
+      <c r="C20" s="20">
+        <v>1</v>
+      </c>
+      <c r="D20" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="20">
         <v>4055123</v>
       </c>
-      <c r="F20" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-    </row>
-    <row r="21" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="23">
+      <c r="F20" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+    </row>
+    <row r="21" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A21" s="19">
         <v>1204</v>
       </c>
-      <c r="B21" s="24">
-        <v>2</v>
-      </c>
-      <c r="C21" s="24">
-        <v>1</v>
-      </c>
-      <c r="D21" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="24">
+      <c r="B21" s="20">
+        <v>2</v>
+      </c>
+      <c r="C21" s="20">
+        <v>1</v>
+      </c>
+      <c r="D21" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="20">
         <v>4055124</v>
       </c>
-      <c r="F21" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-    </row>
-    <row r="22" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="14">
+      <c r="F21" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
+    </row>
+    <row r="22" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A22" s="19">
         <v>1301</v>
       </c>
-      <c r="B22" s="15">
-        <v>2</v>
-      </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" s="15">
+      <c r="B22" s="20">
+        <v>2</v>
+      </c>
+      <c r="C22" s="20">
+        <v>1</v>
+      </c>
+      <c r="D22" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="20">
         <v>4055141</v>
       </c>
-      <c r="F22" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-    </row>
-    <row r="23" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A23" s="14">
+      <c r="F22" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+    </row>
+    <row r="23" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A23" s="23">
         <v>1302</v>
       </c>
-      <c r="B23" s="15">
-        <v>2</v>
-      </c>
-      <c r="C23" s="15">
-        <v>1</v>
-      </c>
-      <c r="D23" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="15">
+      <c r="B23" s="24">
+        <v>2</v>
+      </c>
+      <c r="C23" s="24">
+        <v>1</v>
+      </c>
+      <c r="D23" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="24">
         <v>4055142</v>
       </c>
       <c r="F23" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>34</v>
+        <v>46</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>47</v>
       </c>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
       <c r="L23" s="18"/>
     </row>
-    <row r="24" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A24" s="14">
+    <row r="24" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A24" s="19">
         <v>1303</v>
       </c>
-      <c r="B24" s="15">
-        <v>2</v>
-      </c>
-      <c r="C24" s="15">
-        <v>1</v>
-      </c>
-      <c r="D24" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" s="15">
+      <c r="B24" s="20">
+        <v>2</v>
+      </c>
+      <c r="C24" s="20">
+        <v>1</v>
+      </c>
+      <c r="D24" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="20">
         <v>4055143</v>
       </c>
-      <c r="F24" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
-    </row>
-    <row r="25" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="14">
+      <c r="F24" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+    </row>
+    <row r="25" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="19">
         <v>1304</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15">
-        <v>1</v>
-      </c>
-      <c r="D25" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-    </row>
-    <row r="26" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="14">
+      <c r="B25" s="20"/>
+      <c r="C25" s="20">
+        <v>1</v>
+      </c>
+      <c r="D25" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+    </row>
+    <row r="26" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A26" s="19">
         <v>1305</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15">
-        <v>1</v>
-      </c>
-      <c r="D26" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="15">
+      <c r="B26" s="20"/>
+      <c r="C26" s="20">
+        <v>1</v>
+      </c>
+      <c r="D26" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="20">
         <v>4055144</v>
       </c>
-      <c r="F26" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-    </row>
-    <row r="27" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="23">
+      <c r="F26" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+    </row>
+    <row r="27" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A27" s="19">
         <v>1401</v>
       </c>
-      <c r="B27" s="24">
-        <v>2</v>
-      </c>
-      <c r="C27" s="24">
-        <v>1</v>
-      </c>
-      <c r="D27" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="24">
+      <c r="B27" s="20">
+        <v>2</v>
+      </c>
+      <c r="C27" s="20">
+        <v>1</v>
+      </c>
+      <c r="D27" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="20">
         <v>4055161</v>
       </c>
-      <c r="F27" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-    </row>
-    <row r="28" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="23">
+      <c r="F27" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+    </row>
+    <row r="28" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A28" s="19">
         <v>1402</v>
       </c>
-      <c r="B28" s="24">
-        <v>2</v>
-      </c>
-      <c r="C28" s="24">
-        <v>1</v>
-      </c>
-      <c r="D28" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="24">
+      <c r="B28" s="20">
+        <v>2</v>
+      </c>
+      <c r="C28" s="20">
+        <v>1</v>
+      </c>
+      <c r="D28" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="20">
         <v>4055162</v>
       </c>
-      <c r="F28" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-    </row>
-    <row r="29" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="23">
+      <c r="F28" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+    </row>
+    <row r="29" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A29" s="19">
         <v>1403</v>
       </c>
-      <c r="B29" s="24">
-        <v>2</v>
-      </c>
-      <c r="C29" s="24">
-        <v>1</v>
-      </c>
-      <c r="D29" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="24">
+      <c r="B29" s="20">
+        <v>2</v>
+      </c>
+      <c r="C29" s="20">
+        <v>1</v>
+      </c>
+      <c r="D29" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="20">
         <v>4055163</v>
       </c>
-      <c r="F29" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-    </row>
-    <row r="30" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="23">
+      <c r="F29" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+    </row>
+    <row r="30" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A30" s="19">
         <v>1404</v>
       </c>
-      <c r="B30" s="24">
-        <v>2</v>
-      </c>
-      <c r="C30" s="24">
-        <v>1</v>
-      </c>
-      <c r="D30" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="24">
+      <c r="B30" s="20">
+        <v>2</v>
+      </c>
+      <c r="C30" s="20">
+        <v>1</v>
+      </c>
+      <c r="D30" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="20">
         <v>4055164</v>
       </c>
-      <c r="F30" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-    </row>
-    <row r="31" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="23">
+      <c r="F30" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+    </row>
+    <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A31" s="19">
         <v>1405</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24">
-        <v>1</v>
-      </c>
-      <c r="D31" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-    </row>
-    <row r="32" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="23">
+      <c r="B31" s="20"/>
+      <c r="C31" s="20">
+        <v>1</v>
+      </c>
+      <c r="D31" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+    </row>
+    <row r="32" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A32" s="19">
         <v>1406</v>
       </c>
-      <c r="B32" s="24">
-        <v>2</v>
-      </c>
-      <c r="C32" s="24">
-        <v>1</v>
-      </c>
-      <c r="D32" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" s="24">
+      <c r="B32" s="20">
+        <v>2</v>
+      </c>
+      <c r="C32" s="20">
+        <v>1</v>
+      </c>
+      <c r="D32" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="20">
         <v>4055165</v>
       </c>
-      <c r="F32" s="24"/>
-      <c r="G32" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-    </row>
-    <row r="33" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="14">
+      <c r="F32" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+    </row>
+    <row r="33" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A33" s="19">
         <v>1501</v>
       </c>
-      <c r="B33" s="15">
-        <v>2</v>
-      </c>
-      <c r="C33" s="15">
-        <v>1</v>
-      </c>
-      <c r="D33" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" s="15">
+      <c r="B33" s="20">
+        <v>2</v>
+      </c>
+      <c r="C33" s="20">
+        <v>1</v>
+      </c>
+      <c r="D33" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="20">
         <v>4055181</v>
       </c>
-      <c r="F33" s="15"/>
-      <c r="G33" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-    </row>
-    <row r="34" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="14">
+      <c r="F33" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+    </row>
+    <row r="34" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A34" s="19">
         <v>1502</v>
       </c>
-      <c r="B34" s="15">
-        <v>2</v>
-      </c>
-      <c r="C34" s="15">
-        <v>1</v>
-      </c>
-      <c r="D34" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" s="15">
+      <c r="B34" s="20">
+        <v>2</v>
+      </c>
+      <c r="C34" s="20">
+        <v>1</v>
+      </c>
+      <c r="D34" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="20">
         <v>4055182</v>
       </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-    </row>
-    <row r="35" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="14">
+      <c r="F34" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+    </row>
+    <row r="35" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A35" s="19">
         <v>1503</v>
       </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15">
-        <v>1</v>
-      </c>
-      <c r="D35" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-    </row>
-    <row r="36" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="14">
+      <c r="B35" s="20"/>
+      <c r="C35" s="20">
+        <v>1</v>
+      </c>
+      <c r="D35" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+    </row>
+    <row r="36" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A36" s="19">
         <v>1504</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15">
-        <v>1</v>
-      </c>
-      <c r="D36" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-    </row>
-    <row r="37" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="23">
+      <c r="B36" s="20"/>
+      <c r="C36" s="20">
+        <v>1</v>
+      </c>
+      <c r="D36" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+    </row>
+    <row r="37" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A37" s="15">
         <v>1601</v>
       </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24">
+      <c r="B37" s="16"/>
+      <c r="C37" s="16">
         <v>1</v>
       </c>
       <c r="D37" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-    </row>
-    <row r="38" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="23">
+      <c r="E37" s="16"/>
+      <c r="F37" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G37" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37" s="17"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+    </row>
+    <row r="38" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A38" s="15">
         <v>1602</v>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24">
+      <c r="B38" s="16"/>
+      <c r="C38" s="16">
         <v>1</v>
       </c>
       <c r="D38" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-    </row>
-    <row r="39" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A39" s="23">
+      <c r="E38" s="16"/>
+      <c r="F38" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" s="17"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+    </row>
+    <row r="39" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A39" s="15">
         <v>1603</v>
       </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24">
+      <c r="B39" s="16"/>
+      <c r="C39" s="16">
         <v>1</v>
       </c>
       <c r="D39" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="16">
         <v>4055203</v>
       </c>
-      <c r="F39" s="15"/>
-      <c r="G39" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-    </row>
-    <row r="40" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="23">
+      <c r="F39" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="G39" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+    </row>
+    <row r="40" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A40" s="15">
         <v>1604</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24">
+      <c r="B40" s="16"/>
+      <c r="C40" s="16">
         <v>1</v>
       </c>
       <c r="D40" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-    </row>
-    <row r="41" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="23">
+      <c r="E40" s="16"/>
+      <c r="F40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G40" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H40" s="17"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+    </row>
+    <row r="41" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A41" s="15">
         <v>1605</v>
       </c>
-      <c r="B41" s="24">
-        <v>2</v>
-      </c>
-      <c r="C41" s="24">
+      <c r="B41" s="16">
+        <v>2</v>
+      </c>
+      <c r="C41" s="16">
         <v>1</v>
       </c>
       <c r="D41" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="16">
         <v>4055204</v>
       </c>
-      <c r="F41" s="15"/>
-      <c r="G41" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-    </row>
-    <row r="42" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="23">
+      <c r="F41" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+    </row>
+    <row r="42" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A42" s="15">
         <v>1606</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24">
+      <c r="B42" s="16"/>
+      <c r="C42" s="16">
         <v>1</v>
       </c>
       <c r="D42" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-    </row>
-    <row r="43" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="23">
+      <c r="E42" s="16"/>
+      <c r="F42" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G42" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H42" s="17"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+    </row>
+    <row r="43" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A43" s="15">
         <v>1607</v>
       </c>
-      <c r="B43" s="24">
-        <v>2</v>
-      </c>
-      <c r="C43" s="24">
+      <c r="B43" s="16">
+        <v>2</v>
+      </c>
+      <c r="C43" s="16">
         <v>1</v>
       </c>
       <c r="D43" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-    </row>
-    <row r="44" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="23">
+      <c r="E43" s="16"/>
+      <c r="F43" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G43" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H43" s="17"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+    </row>
+    <row r="44" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A44" s="15">
         <v>1608</v>
       </c>
-      <c r="B44" s="24"/>
-      <c r="C44" s="24">
+      <c r="B44" s="16"/>
+      <c r="C44" s="16">
         <v>1</v>
       </c>
       <c r="D44" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E44" s="24">
+      <c r="E44" s="16">
         <v>4055205</v>
       </c>
-      <c r="F44" s="15"/>
-      <c r="G44" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-    </row>
-    <row r="45" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="23">
+      <c r="F44" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G44" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+    </row>
+    <row r="45" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A45" s="15">
         <v>1609</v>
       </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24">
+      <c r="B45" s="16"/>
+      <c r="C45" s="16">
         <v>1</v>
       </c>
       <c r="D45" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E45" s="24">
+      <c r="E45" s="16">
         <v>4055206</v>
       </c>
-      <c r="F45" s="15"/>
-      <c r="G45" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-    </row>
-    <row r="46" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="23">
+      <c r="F45" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G45" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+    </row>
+    <row r="46" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A46" s="15">
         <v>1610</v>
       </c>
-      <c r="B46" s="24">
-        <v>2</v>
-      </c>
-      <c r="C46" s="24">
+      <c r="B46" s="16">
+        <v>2</v>
+      </c>
+      <c r="C46" s="16">
         <v>1</v>
       </c>
       <c r="D46" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E46" s="24">
+      <c r="E46" s="16">
         <v>4055207</v>
       </c>
-      <c r="F46" s="15"/>
-      <c r="G46" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-    </row>
-    <row r="47" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="23">
+      <c r="F46" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G46" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H46" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+    </row>
+    <row r="47" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A47" s="15">
         <v>1611</v>
       </c>
-      <c r="B47" s="24">
-        <v>2</v>
-      </c>
-      <c r="C47" s="24">
+      <c r="B47" s="16">
+        <v>2</v>
+      </c>
+      <c r="C47" s="16">
         <v>1</v>
       </c>
       <c r="D47" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E47" s="24">
+      <c r="E47" s="16">
         <v>4055208</v>
       </c>
-      <c r="F47" s="15"/>
-      <c r="G47" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-    </row>
-    <row r="48" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="23">
+      <c r="F47" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G47" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+    </row>
+    <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="19">
         <v>1612</v>
       </c>
-      <c r="B48" s="24">
-        <v>2</v>
-      </c>
-      <c r="C48" s="24">
-        <v>1</v>
-      </c>
-      <c r="D48" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E48" s="24">
+      <c r="B48" s="20">
+        <v>2</v>
+      </c>
+      <c r="C48" s="20">
+        <v>1</v>
+      </c>
+      <c r="D48" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="20">
         <v>4055209</v>
       </c>
-      <c r="F48" s="15"/>
-      <c r="G48" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-    </row>
-    <row r="49" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="14">
+      <c r="F48" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G48" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="H48" s="21"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="21"/>
+      <c r="K48" s="21"/>
+      <c r="L48" s="21"/>
+    </row>
+    <row r="49" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A49" s="19">
         <v>1701</v>
       </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15">
-        <v>1</v>
-      </c>
-      <c r="D49" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I49" s="18"/>
-      <c r="J49" s="18"/>
-      <c r="K49" s="18"/>
-      <c r="L49" s="18"/>
-    </row>
-    <row r="50" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A50" s="14">
+      <c r="B49" s="20"/>
+      <c r="C49" s="20">
+        <v>1</v>
+      </c>
+      <c r="D49" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="21"/>
+    </row>
+    <row r="50" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A50" s="19">
         <v>1702</v>
       </c>
-      <c r="C50" s="15">
-        <v>1</v>
-      </c>
-      <c r="D50" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="15"/>
-      <c r="G50" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I50" s="18"/>
-      <c r="J50" s="18"/>
-      <c r="K50" s="18"/>
-      <c r="L50" s="18"/>
-    </row>
-    <row r="51" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A51" s="14">
+      <c r="B50" s="27"/>
+      <c r="C50" s="20">
+        <v>1</v>
+      </c>
+      <c r="D50" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="27"/>
+      <c r="F50" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G50" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H50" s="21"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="21"/>
+      <c r="L50" s="21"/>
+    </row>
+    <row r="51" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A51" s="19">
         <v>1703</v>
       </c>
-      <c r="B51" s="15">
-        <v>2</v>
-      </c>
-      <c r="C51" s="15">
-        <v>1</v>
-      </c>
-      <c r="D51" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E51" s="15">
+      <c r="B51" s="20">
+        <v>2</v>
+      </c>
+      <c r="C51" s="20">
+        <v>1</v>
+      </c>
+      <c r="D51" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" s="20">
         <v>4055222</v>
       </c>
-      <c r="F51" s="15"/>
-      <c r="G51" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="I51" s="18"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="18"/>
-    </row>
-    <row r="52" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A52" s="14">
+      <c r="F51" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G51" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+    </row>
+    <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A52" s="19">
         <v>1704</v>
       </c>
-      <c r="B52" s="15">
-        <v>2</v>
-      </c>
-      <c r="C52" s="15">
-        <v>1</v>
-      </c>
-      <c r="D52" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E52" s="15">
+      <c r="B52" s="20">
+        <v>2</v>
+      </c>
+      <c r="C52" s="20">
+        <v>1</v>
+      </c>
+      <c r="D52" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" s="20">
         <v>4055223</v>
       </c>
-      <c r="F52" s="15"/>
-      <c r="G52" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="I52" s="18"/>
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="18"/>
-    </row>
-    <row r="53" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A53" s="14">
+      <c r="F52" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="G52" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H52" s="21"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+    </row>
+    <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A53" s="19">
         <v>1705</v>
       </c>
-      <c r="B53" s="15">
-        <v>2</v>
-      </c>
-      <c r="C53" s="15">
-        <v>1</v>
-      </c>
-      <c r="D53" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E53" s="15">
+      <c r="B53" s="20">
+        <v>2</v>
+      </c>
+      <c r="C53" s="20">
+        <v>1</v>
+      </c>
+      <c r="D53" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" s="20">
         <v>4055224</v>
       </c>
-      <c r="F53" s="15"/>
-      <c r="G53" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-    </row>
-    <row r="54" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A54" s="14">
+      <c r="F53" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="G53" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H53" s="21"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="21"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+    </row>
+    <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A54" s="19">
         <v>1706</v>
       </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15">
-        <v>1</v>
-      </c>
-      <c r="D54" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I54" s="18"/>
-      <c r="J54" s="18"/>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
-    </row>
-    <row r="55" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A55" s="14">
+      <c r="B54" s="20"/>
+      <c r="C54" s="20">
+        <v>1</v>
+      </c>
+      <c r="D54" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G54" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+    </row>
+    <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A55" s="19">
         <v>1707</v>
       </c>
-      <c r="B55" s="15">
-        <v>2</v>
-      </c>
-      <c r="C55" s="15">
-        <v>1</v>
-      </c>
-      <c r="D55" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E55" s="15">
+      <c r="B55" s="20">
+        <v>2</v>
+      </c>
+      <c r="C55" s="20">
+        <v>1</v>
+      </c>
+      <c r="D55" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" s="20">
         <v>4055225</v>
       </c>
-      <c r="F55" s="15"/>
-      <c r="G55" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I55" s="18"/>
-      <c r="J55" s="18"/>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
-    </row>
-    <row r="56" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A56" s="14">
+      <c r="F55" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G55" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+    </row>
+    <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A56" s="19">
         <v>1708</v>
       </c>
-      <c r="B56" s="15">
-        <v>2</v>
-      </c>
-      <c r="C56" s="15">
-        <v>1</v>
-      </c>
-      <c r="D56" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" s="15">
+      <c r="B56" s="20">
+        <v>2</v>
+      </c>
+      <c r="C56" s="20">
+        <v>1</v>
+      </c>
+      <c r="D56" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" s="20">
         <v>4055226</v>
       </c>
-      <c r="F56" s="15"/>
-      <c r="G56" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
-      <c r="L56" s="18"/>
-    </row>
-    <row r="57" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A57" s="14">
+      <c r="F56" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G56" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H56" s="21"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="21"/>
+      <c r="K56" s="21"/>
+      <c r="L56" s="21"/>
+    </row>
+    <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A57" s="19">
         <v>1709</v>
       </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15">
-        <v>1</v>
-      </c>
-      <c r="D57" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="18"/>
-      <c r="L57" s="18"/>
-    </row>
-    <row r="58" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A58" s="14">
+      <c r="B57" s="20"/>
+      <c r="C57" s="20">
+        <v>1</v>
+      </c>
+      <c r="D57" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G57" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H57" s="21"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="21"/>
+      <c r="K57" s="21"/>
+      <c r="L57" s="21"/>
+    </row>
+    <row r="58" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A58" s="19">
         <v>1710</v>
       </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15">
-        <v>1</v>
-      </c>
-      <c r="D58" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I58" s="18"/>
-      <c r="J58" s="18"/>
-      <c r="K58" s="18"/>
-      <c r="L58" s="18"/>
-    </row>
-    <row r="59" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="14">
+      <c r="B58" s="20"/>
+      <c r="C58" s="20">
+        <v>1</v>
+      </c>
+      <c r="D58" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G58" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
+      <c r="J58" s="21"/>
+      <c r="K58" s="21"/>
+      <c r="L58" s="21"/>
+    </row>
+    <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A59" s="19">
         <v>1711</v>
       </c>
-      <c r="B59" s="15">
-        <v>2</v>
-      </c>
-      <c r="C59" s="15">
-        <v>1</v>
-      </c>
-      <c r="D59" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" s="15">
+      <c r="B59" s="20">
+        <v>2</v>
+      </c>
+      <c r="C59" s="20">
+        <v>1</v>
+      </c>
+      <c r="D59" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" s="20">
         <v>4055227</v>
       </c>
-      <c r="F59" s="15"/>
-      <c r="G59" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
-    </row>
-    <row r="60" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="14">
+      <c r="F59" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G59" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H59" s="21"/>
+      <c r="I59" s="21"/>
+      <c r="J59" s="21"/>
+      <c r="K59" s="21"/>
+      <c r="L59" s="21"/>
+    </row>
+    <row r="60" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A60" s="19">
         <v>1712</v>
       </c>
-      <c r="B60" s="15">
-        <v>2</v>
-      </c>
-      <c r="C60" s="15">
-        <v>1</v>
-      </c>
-      <c r="D60" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E60" s="15">
+      <c r="B60" s="20">
+        <v>2</v>
+      </c>
+      <c r="C60" s="20">
+        <v>1</v>
+      </c>
+      <c r="D60" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" s="20">
         <v>4055228</v>
       </c>
-      <c r="F60" s="15"/>
-      <c r="G60" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="I60" s="18"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
-      <c r="L60" s="18"/>
-    </row>
-    <row r="61" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="23">
+      <c r="F60" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G60" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H60" s="21"/>
+      <c r="I60" s="21"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
+      <c r="L60" s="21"/>
+    </row>
+    <row r="61" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A61" s="19">
         <v>1801</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24">
-        <v>1</v>
-      </c>
-      <c r="D61" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-    </row>
-    <row r="62" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A62" s="23">
+      <c r="B61" s="20"/>
+      <c r="C61" s="20">
+        <v>1</v>
+      </c>
+      <c r="D61" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G61" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H61" s="21"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="21"/>
+      <c r="L61" s="21"/>
+    </row>
+    <row r="62" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A62" s="19">
         <v>1802</v>
       </c>
-      <c r="B62" s="24"/>
-      <c r="C62" s="24">
-        <v>1</v>
-      </c>
-      <c r="D62" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
-    </row>
-    <row r="63" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A63" s="23">
+      <c r="B62" s="20"/>
+      <c r="C62" s="20">
+        <v>1</v>
+      </c>
+      <c r="D62" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G62" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="21"/>
+      <c r="L62" s="21"/>
+    </row>
+    <row r="63" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A63" s="19">
         <v>1803</v>
       </c>
-      <c r="B63" s="24">
-        <v>2</v>
-      </c>
-      <c r="C63" s="24">
-        <v>1</v>
-      </c>
-      <c r="D63" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E63" s="24">
+      <c r="B63" s="20">
+        <v>2</v>
+      </c>
+      <c r="C63" s="20">
+        <v>1</v>
+      </c>
+      <c r="D63" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" s="20">
         <v>4055243</v>
       </c>
-      <c r="F63" s="24"/>
-      <c r="G63" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="10"/>
-    </row>
-    <row r="64" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A64" s="23">
+      <c r="F63" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G63" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H63" s="21"/>
+      <c r="I63" s="21"/>
+      <c r="J63" s="21"/>
+      <c r="K63" s="21"/>
+      <c r="L63" s="21"/>
+    </row>
+    <row r="64" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A64" s="19">
         <v>1804</v>
       </c>
-      <c r="B64" s="24">
-        <v>2</v>
-      </c>
-      <c r="C64" s="24">
-        <v>1</v>
-      </c>
-      <c r="D64" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E64" s="24">
+      <c r="B64" s="20">
+        <v>2</v>
+      </c>
+      <c r="C64" s="20">
+        <v>1</v>
+      </c>
+      <c r="D64" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" s="20">
         <v>4055244</v>
       </c>
-      <c r="F64" s="24"/>
-      <c r="G64" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="10"/>
-    </row>
-    <row r="65" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A65" s="23">
+      <c r="F64" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G64" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H64" s="21"/>
+      <c r="I64" s="21"/>
+      <c r="J64" s="21"/>
+      <c r="K64" s="21"/>
+      <c r="L64" s="21"/>
+    </row>
+    <row r="65" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A65" s="19">
         <v>1805</v>
       </c>
-      <c r="B65" s="24">
-        <v>2</v>
-      </c>
-      <c r="C65" s="24">
-        <v>1</v>
-      </c>
-      <c r="D65" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E65" s="24">
+      <c r="B65" s="20">
+        <v>2</v>
+      </c>
+      <c r="C65" s="20">
+        <v>1</v>
+      </c>
+      <c r="D65" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" s="20">
         <v>4055245</v>
       </c>
-      <c r="F65" s="24"/>
-      <c r="G65" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
-    </row>
-    <row r="66" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="23">
+      <c r="F65" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G65" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H65" s="21"/>
+      <c r="I65" s="21"/>
+      <c r="J65" s="21"/>
+      <c r="K65" s="21"/>
+      <c r="L65" s="21"/>
+    </row>
+    <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A66" s="19">
         <v>1806</v>
       </c>
-      <c r="B66" s="24">
-        <v>2</v>
-      </c>
-      <c r="C66" s="24">
-        <v>1</v>
-      </c>
-      <c r="D66" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E66" s="24">
+      <c r="B66" s="20">
+        <v>2</v>
+      </c>
+      <c r="C66" s="20">
+        <v>1</v>
+      </c>
+      <c r="D66" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" s="20">
         <v>4055246</v>
       </c>
-      <c r="F66" s="24"/>
-      <c r="G66" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="10"/>
-    </row>
-    <row r="67" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="23">
+      <c r="F66" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G66" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H66" s="21"/>
+      <c r="I66" s="21"/>
+      <c r="J66" s="21"/>
+      <c r="K66" s="21"/>
+      <c r="L66" s="21"/>
+    </row>
+    <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A67" s="19">
         <v>1807</v>
       </c>
-      <c r="B67" s="24">
-        <v>2</v>
-      </c>
-      <c r="C67" s="24">
-        <v>1</v>
-      </c>
-      <c r="D67" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E67" s="24">
+      <c r="B67" s="20">
+        <v>2</v>
+      </c>
+      <c r="C67" s="20">
+        <v>1</v>
+      </c>
+      <c r="D67" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" s="20">
         <v>4055247</v>
       </c>
-      <c r="F67" s="24"/>
-      <c r="G67" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="10"/>
-    </row>
-    <row r="68" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="14">
+      <c r="F67" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G67" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H67" s="21"/>
+      <c r="I67" s="21"/>
+      <c r="J67" s="21"/>
+      <c r="K67" s="21"/>
+      <c r="L67" s="21"/>
+    </row>
+    <row r="68" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A68" s="15">
         <v>1901</v>
       </c>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15">
+      <c r="B68" s="16"/>
+      <c r="C68" s="16">
         <v>1</v>
       </c>
       <c r="D68" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G68" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="H68" s="17"/>
       <c r="I68" s="18"/>
       <c r="J68" s="18"/>
       <c r="K68" s="18"/>
       <c r="L68" s="18"/>
     </row>
-    <row r="69" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A69" s="14">
+    <row r="69" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A69" s="15">
         <v>1902</v>
       </c>
-      <c r="B69" s="15">
-        <v>2</v>
-      </c>
-      <c r="C69" s="15">
+      <c r="B69" s="16">
+        <v>2</v>
+      </c>
+      <c r="C69" s="16">
         <v>1</v>
       </c>
       <c r="D69" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E69" s="15">
+      <c r="E69" s="16">
         <v>4055263</v>
       </c>
-      <c r="F69" s="15"/>
-      <c r="G69" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>70</v>
+      <c r="F69" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="G69" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="H69" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="I69" s="18"/>
       <c r="J69" s="18"/>
       <c r="K69" s="18"/>
       <c r="L69" s="18"/>
     </row>
-    <row r="70" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="14">
+    <row r="70" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A70" s="15">
         <v>1903</v>
       </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
       <c r="D70" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E70" s="27"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="26" t="s">
-        <v>69</v>
-      </c>
+      <c r="E70" s="28"/>
+      <c r="F70" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="G70" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="H70" s="17"/>
       <c r="I70" s="18"/>
       <c r="J70" s="18"/>
       <c r="K70" s="18"/>
       <c r="L70" s="18"/>
     </row>
-    <row r="71" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="14">
+    <row r="71" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A71" s="15">
         <v>1904</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15">
+      <c r="B71" s="16"/>
+      <c r="C71" s="16">
         <v>1</v>
       </c>
       <c r="D71" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="H71" s="10"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="G71" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="H71" s="17"/>
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
       <c r="K71" s="18"/>
       <c r="L71" s="18"/>
     </row>
-    <row r="72" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="14">
+    <row r="72" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A72" s="15">
         <v>1905</v>
       </c>
-      <c r="B72" s="15">
-        <v>2</v>
-      </c>
-      <c r="C72" s="15">
+      <c r="B72" s="16">
+        <v>2</v>
+      </c>
+      <c r="C72" s="16">
         <v>1</v>
       </c>
       <c r="D72" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="15">
+      <c r="E72" s="16">
         <v>4055264</v>
       </c>
-      <c r="F72" s="15"/>
-      <c r="G72" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="H72" s="10" t="s">
-        <v>71</v>
+      <c r="F72" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="G72" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="H72" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="I72" s="18"/>
       <c r="J72" s="18"/>
       <c r="K72" s="18"/>
       <c r="L72" s="18"/>
     </row>
-    <row r="73" s="7" customFormat="1" customHeight="1" spans="1:12">
+    <row r="73" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A73" s="23">
         <v>1981</v>
       </c>
@@ -3714,23 +3934,23 @@
       <c r="C73" s="24">
         <v>1</v>
       </c>
-      <c r="D73" s="16" t="b">
+      <c r="D73" s="24" t="b">
         <v>0</v>
       </c>
       <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10"/>
-      <c r="K73" s="10"/>
-      <c r="L73" s="10"/>
-    </row>
-    <row r="74" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="F73" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="G73" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H73" s="17"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+    </row>
+    <row r="74" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A74" s="23">
         <v>1982</v>
       </c>
@@ -3738,23 +3958,23 @@
       <c r="C74" s="24">
         <v>1</v>
       </c>
-      <c r="D74" s="16" t="b">
+      <c r="D74" s="24" t="b">
         <v>0</v>
       </c>
       <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="10"/>
-    </row>
-    <row r="75" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="F74" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="G74" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H74" s="17"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+    </row>
+    <row r="75" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A75" s="23">
         <v>1983</v>
       </c>
@@ -3764,821 +3984,857 @@
       <c r="C75" s="24">
         <v>1</v>
       </c>
-      <c r="D75" s="16" t="b">
+      <c r="D75" s="24" t="b">
         <v>0</v>
       </c>
       <c r="E75" s="24">
         <v>4055321</v>
       </c>
-      <c r="F75" s="24"/>
-      <c r="G75" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="10"/>
-      <c r="L75" s="10"/>
-    </row>
-    <row r="76" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A76" s="14">
+      <c r="F75" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="G75" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H75" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+    </row>
+    <row r="76" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A76" s="15">
         <v>2001</v>
       </c>
-      <c r="B76" s="15"/>
-      <c r="C76" s="15">
+      <c r="B76" s="16"/>
+      <c r="C76" s="16">
         <v>1</v>
       </c>
       <c r="D76" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G76" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H76" s="17"/>
       <c r="I76" s="18"/>
       <c r="J76" s="18"/>
       <c r="K76" s="18"/>
       <c r="L76" s="18"/>
     </row>
-    <row r="77" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A77" s="14">
+    <row r="77" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A77" s="15">
         <v>2002</v>
       </c>
-      <c r="B77" s="15">
-        <v>2</v>
-      </c>
-      <c r="C77" s="15">
+      <c r="B77" s="16">
+        <v>2</v>
+      </c>
+      <c r="C77" s="16">
         <v>1</v>
       </c>
       <c r="D77" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E77" s="15">
+      <c r="E77" s="16">
         <v>4055281</v>
       </c>
-      <c r="F77" s="15"/>
-      <c r="G77" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>75</v>
+      <c r="F77" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="G77" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H77" s="17" t="s">
+        <v>119</v>
       </c>
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
       <c r="K77" s="18"/>
       <c r="L77" s="18"/>
     </row>
-    <row r="78" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A78" s="14">
+    <row r="78" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A78" s="15">
         <v>2003</v>
       </c>
-      <c r="B78" s="15">
-        <v>2</v>
-      </c>
-      <c r="C78" s="15">
+      <c r="B78" s="16">
+        <v>2</v>
+      </c>
+      <c r="C78" s="16">
         <v>1</v>
       </c>
       <c r="D78" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E78" s="15">
+      <c r="E78" s="16">
         <v>4055282</v>
       </c>
-      <c r="F78" s="15"/>
-      <c r="G78" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>76</v>
+      <c r="F78" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G78" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H78" s="17" t="s">
+        <v>121</v>
       </c>
       <c r="I78" s="18"/>
       <c r="J78" s="18"/>
       <c r="K78" s="18"/>
       <c r="L78" s="18"/>
     </row>
-    <row r="79" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="14">
+    <row r="79" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A79" s="15">
         <v>2004</v>
       </c>
-      <c r="B79" s="15">
-        <v>2</v>
-      </c>
-      <c r="C79" s="15">
+      <c r="B79" s="16">
+        <v>2</v>
+      </c>
+      <c r="C79" s="16">
         <v>1</v>
       </c>
       <c r="D79" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E79" s="15">
+      <c r="E79" s="16">
         <v>4055283</v>
       </c>
-      <c r="F79" s="15"/>
-      <c r="G79" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>77</v>
+      <c r="F79" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G79" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="I79" s="18"/>
       <c r="J79" s="18"/>
       <c r="K79" s="18"/>
       <c r="L79" s="18"/>
     </row>
-    <row r="80" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="14">
+    <row r="80" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="15">
         <v>2005</v>
       </c>
-      <c r="B80" s="15">
-        <v>2</v>
-      </c>
-      <c r="C80" s="15">
+      <c r="B80" s="16">
+        <v>2</v>
+      </c>
+      <c r="C80" s="16">
         <v>1</v>
       </c>
       <c r="D80" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E80" s="15">
+      <c r="E80" s="16">
         <v>4055284</v>
       </c>
-      <c r="F80" s="15"/>
-      <c r="G80" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H80" s="10" t="s">
-        <v>76</v>
+      <c r="F80" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="G80" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H80" s="17" t="s">
+        <v>121</v>
       </c>
       <c r="I80" s="18"/>
       <c r="J80" s="18"/>
       <c r="K80" s="18"/>
       <c r="L80" s="18"/>
     </row>
-    <row r="81" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="14">
+    <row r="81" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A81" s="15">
         <v>2006</v>
       </c>
-      <c r="B81" s="15">
-        <v>2</v>
-      </c>
-      <c r="C81" s="15">
+      <c r="B81" s="16">
+        <v>2</v>
+      </c>
+      <c r="C81" s="16">
         <v>1</v>
       </c>
       <c r="D81" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E81" s="15">
+      <c r="E81" s="16">
         <v>4055285</v>
       </c>
-      <c r="F81" s="15"/>
-      <c r="G81" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>77</v>
+      <c r="F81" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="G81" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H81" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
       <c r="K81" s="18"/>
       <c r="L81" s="18"/>
     </row>
-    <row r="82" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="14">
+    <row r="82" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A82" s="15">
         <v>2007</v>
       </c>
-      <c r="B82" s="15">
-        <v>2</v>
-      </c>
-      <c r="C82" s="15">
+      <c r="B82" s="16">
+        <v>2</v>
+      </c>
+      <c r="C82" s="16">
         <v>1</v>
       </c>
       <c r="D82" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E82" s="15">
+      <c r="E82" s="16">
         <v>4055286</v>
       </c>
-      <c r="F82" s="15"/>
-      <c r="G82" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H82" s="10" t="s">
-        <v>78</v>
+      <c r="F82" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="G82" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H82" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="I82" s="18"/>
       <c r="J82" s="18"/>
       <c r="K82" s="18"/>
       <c r="L82" s="18"/>
     </row>
-    <row r="83" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A83" s="28">
+    <row r="83" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A83" s="15">
         <v>2100</v>
       </c>
-      <c r="B83" s="29">
-        <v>2</v>
-      </c>
-      <c r="C83" s="29">
+      <c r="B83" s="16">
+        <v>2</v>
+      </c>
+      <c r="C83" s="16">
         <v>1</v>
       </c>
       <c r="D83" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E83" s="29"/>
-      <c r="F83" s="29"/>
-      <c r="G83" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H83" s="10"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H83" s="17"/>
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
       <c r="K83" s="18"/>
       <c r="L83" s="18"/>
     </row>
-    <row r="84" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A84" s="30">
+    <row r="84" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A84" s="16">
         <v>2101</v>
       </c>
-      <c r="B84" s="30">
-        <v>2</v>
-      </c>
-      <c r="C84" s="30">
+      <c r="B84" s="16">
+        <v>2</v>
+      </c>
+      <c r="C84" s="16">
         <v>1</v>
       </c>
       <c r="D84" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E84" s="30">
+      <c r="E84" s="16">
         <v>4055301</v>
       </c>
-      <c r="F84" s="30"/>
-      <c r="G84" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="I84" s="10"/>
-      <c r="J84" s="10"/>
-      <c r="K84" s="10"/>
-      <c r="L84" s="10"/>
-    </row>
-    <row r="85" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A85" s="30">
+      <c r="F84" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H84" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="I84" s="11"/>
+      <c r="J84" s="11"/>
+      <c r="K84" s="11"/>
+      <c r="L84" s="11"/>
+    </row>
+    <row r="85" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A85" s="16">
         <v>2102</v>
       </c>
-      <c r="B85" s="30">
-        <v>1</v>
-      </c>
-      <c r="C85" s="30">
+      <c r="B85" s="16">
+        <v>1</v>
+      </c>
+      <c r="C85" s="16">
         <v>1</v>
       </c>
       <c r="D85" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E85" s="30">
+      <c r="E85" s="16">
         <v>4055303</v>
       </c>
-      <c r="F85" s="30"/>
-      <c r="G85" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="10"/>
-    </row>
-    <row r="86" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A86" s="9">
+      <c r="F85" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H85" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="11"/>
+      <c r="L85" s="11"/>
+    </row>
+    <row r="86" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A86" s="24">
         <v>2201</v>
       </c>
-      <c r="B86" s="9">
-        <v>1</v>
-      </c>
-      <c r="C86" s="9">
-        <v>2</v>
-      </c>
-      <c r="D86" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E86" s="9">
+      <c r="B86" s="24">
+        <v>1</v>
+      </c>
+      <c r="C86" s="24">
+        <v>2</v>
+      </c>
+      <c r="D86" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86" s="24">
         <v>4055341</v>
       </c>
-      <c r="F86" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H86" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="J86" s="32"/>
-      <c r="K86" s="32"/>
-      <c r="L86" s="32"/>
+      <c r="F86" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H86" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="J86" s="29"/>
+      <c r="K86" s="29"/>
+      <c r="L86" s="29"/>
     </row>
     <row r="87" customHeight="1" spans="1:12">
-      <c r="A87" s="9">
+      <c r="A87" s="24">
         <v>2202</v>
       </c>
-      <c r="B87" s="1">
-        <v>2</v>
-      </c>
-      <c r="C87" s="1">
-        <v>1</v>
-      </c>
-      <c r="D87" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E87" s="1">
+      <c r="B87" s="24">
+        <v>2</v>
+      </c>
+      <c r="C87" s="24">
+        <v>1</v>
+      </c>
+      <c r="D87" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E87" s="24">
         <v>4055342</v>
       </c>
-      <c r="F87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H87" s="33" t="s">
-        <v>85</v>
+      <c r="F87" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H87" s="17" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:12">
-      <c r="A88" s="9">
+      <c r="A88" s="24">
         <v>2203</v>
       </c>
-      <c r="B88" s="1">
-        <v>2</v>
-      </c>
-      <c r="C88" s="1">
-        <v>1</v>
-      </c>
-      <c r="D88" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E88" s="1">
+      <c r="B88" s="24">
+        <v>2</v>
+      </c>
+      <c r="C88" s="24">
+        <v>1</v>
+      </c>
+      <c r="D88" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88" s="24">
         <v>4055343</v>
       </c>
-      <c r="F88" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H88" s="33" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A89" s="34">
+      <c r="F88" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H88" s="17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="89" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A89" s="24">
         <v>2204</v>
       </c>
-      <c r="B89" s="1">
-        <v>2</v>
-      </c>
-      <c r="C89" s="6">
-        <v>1</v>
-      </c>
-      <c r="D89" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E89" s="6">
+      <c r="B89" s="24">
+        <v>2</v>
+      </c>
+      <c r="C89" s="24">
+        <v>1</v>
+      </c>
+      <c r="D89" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E89" s="24">
         <v>4055344</v>
       </c>
-      <c r="F89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H89" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="I89" s="10"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="10"/>
-      <c r="L89" s="10"/>
-    </row>
-    <row r="90" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A90" s="34">
+      <c r="F89" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="G89" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H89" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I89" s="11"/>
+      <c r="J89" s="11"/>
+      <c r="K89" s="11"/>
+      <c r="L89" s="11"/>
+    </row>
+    <row r="90" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A90" s="24">
         <v>2205</v>
       </c>
-      <c r="B90" s="1">
-        <v>2</v>
-      </c>
-      <c r="C90" s="6">
-        <v>1</v>
-      </c>
-      <c r="D90" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E90" s="6">
+      <c r="B90" s="24">
+        <v>2</v>
+      </c>
+      <c r="C90" s="24">
+        <v>1</v>
+      </c>
+      <c r="D90" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E90" s="24">
         <v>4055345</v>
       </c>
-      <c r="F90" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G90" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H90" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="I90" s="10"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="10"/>
-      <c r="L90" s="10"/>
-    </row>
-    <row r="91" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A91" s="34">
+      <c r="F90" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="G90" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H90" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I90" s="11"/>
+      <c r="J90" s="11"/>
+      <c r="K90" s="11"/>
+      <c r="L90" s="11"/>
+    </row>
+    <row r="91" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A91" s="24">
         <v>2206</v>
       </c>
-      <c r="B91" s="1">
-        <v>2</v>
-      </c>
-      <c r="C91" s="6">
-        <v>1</v>
-      </c>
-      <c r="D91" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E91" s="6">
+      <c r="B91" s="24">
+        <v>2</v>
+      </c>
+      <c r="C91" s="24">
+        <v>1</v>
+      </c>
+      <c r="D91" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E91" s="24">
         <v>4055346</v>
       </c>
-      <c r="F91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H91" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="I91" s="10"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="10"/>
-    </row>
-    <row r="92" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A92" s="34">
+      <c r="F91" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="G91" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H91" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="I91" s="11"/>
+      <c r="J91" s="11"/>
+      <c r="K91" s="11"/>
+      <c r="L91" s="11"/>
+    </row>
+    <row r="92" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A92" s="24">
         <v>2207</v>
       </c>
-      <c r="B92" s="1">
-        <v>2</v>
-      </c>
-      <c r="C92" s="6">
-        <v>1</v>
-      </c>
-      <c r="D92" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E92" s="6">
+      <c r="B92" s="24">
+        <v>2</v>
+      </c>
+      <c r="C92" s="24">
+        <v>1</v>
+      </c>
+      <c r="D92" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92" s="24">
         <v>4055347</v>
       </c>
-      <c r="F92" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G92" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H92" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="I92" s="10"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="10"/>
-    </row>
-    <row r="93" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A93" s="34">
+      <c r="F92" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="G92" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H92" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I92" s="11"/>
+      <c r="J92" s="11"/>
+      <c r="K92" s="11"/>
+      <c r="L92" s="11"/>
+    </row>
+    <row r="93" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A93" s="24">
         <v>2208</v>
       </c>
-      <c r="B93" s="1">
-        <v>2</v>
-      </c>
-      <c r="C93" s="6">
-        <v>1</v>
-      </c>
-      <c r="D93" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E93" s="6">
+      <c r="B93" s="24">
+        <v>2</v>
+      </c>
+      <c r="C93" s="24">
+        <v>1</v>
+      </c>
+      <c r="D93" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E93" s="24">
         <v>4055348</v>
       </c>
-      <c r="F93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H93" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="I93" s="10"/>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10"/>
-      <c r="L93" s="10"/>
-    </row>
-    <row r="94" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A94" s="34">
+      <c r="F93" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="G93" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H93" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="I93" s="11"/>
+      <c r="J93" s="11"/>
+      <c r="K93" s="11"/>
+      <c r="L93" s="11"/>
+    </row>
+    <row r="94" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A94" s="24">
         <v>2209</v>
       </c>
-      <c r="B94" s="1">
-        <v>2</v>
-      </c>
-      <c r="C94" s="6">
-        <v>1</v>
-      </c>
-      <c r="D94" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-    </row>
-    <row r="95" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A95" s="34">
+      <c r="B94" s="24">
+        <v>2</v>
+      </c>
+      <c r="C94" s="24">
+        <v>1</v>
+      </c>
+      <c r="D94" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="G94" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H94" s="17"/>
+      <c r="I94" s="11"/>
+      <c r="J94" s="11"/>
+      <c r="K94" s="11"/>
+      <c r="L94" s="11"/>
+    </row>
+    <row r="95" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A95" s="24">
         <v>2210</v>
       </c>
-      <c r="B95" s="1">
-        <v>2</v>
-      </c>
-      <c r="C95" s="6">
-        <v>1</v>
-      </c>
-      <c r="D95" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E95" s="6">
+      <c r="B95" s="24">
+        <v>2</v>
+      </c>
+      <c r="C95" s="24">
+        <v>1</v>
+      </c>
+      <c r="D95" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E95" s="24">
         <v>4055350</v>
       </c>
-      <c r="F95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H95" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="J95" s="10"/>
-      <c r="K95" s="10"/>
-      <c r="L95" s="10"/>
-    </row>
-    <row r="96" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A96" s="34">
+      <c r="F95" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="G95" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H95" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="J95" s="11"/>
+      <c r="K95" s="11"/>
+      <c r="L95" s="11"/>
+    </row>
+    <row r="96" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A96" s="24">
         <v>2211</v>
       </c>
-      <c r="B96" s="1">
-        <v>2</v>
-      </c>
-      <c r="C96" s="6">
-        <v>1</v>
-      </c>
-      <c r="D96" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E96" s="1">
+      <c r="B96" s="24">
+        <v>2</v>
+      </c>
+      <c r="C96" s="24">
+        <v>1</v>
+      </c>
+      <c r="D96" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E96" s="24">
         <v>4055356</v>
       </c>
-      <c r="F96" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G96" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H96" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="I96" s="7"/>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="10"/>
-    </row>
-    <row r="97" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A97" s="34">
+      <c r="F96" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="G96" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H96" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="I96" s="8"/>
+      <c r="J96" s="11"/>
+      <c r="K96" s="11"/>
+      <c r="L96" s="11"/>
+    </row>
+    <row r="97" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A97" s="24">
         <v>2212</v>
       </c>
-      <c r="B97" s="1">
-        <v>2</v>
-      </c>
-      <c r="C97" s="6">
-        <v>1</v>
-      </c>
-      <c r="D97" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E97" s="6">
+      <c r="B97" s="24">
+        <v>2</v>
+      </c>
+      <c r="C97" s="24">
+        <v>1</v>
+      </c>
+      <c r="D97" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E97" s="24">
         <v>4055351</v>
       </c>
-      <c r="F97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H97" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="I97" s="10"/>
-      <c r="J97" s="10"/>
-      <c r="K97" s="10"/>
-      <c r="L97" s="10"/>
-    </row>
-    <row r="98" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A98" s="34">
+      <c r="F97" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="G97" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H97" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="I97" s="11"/>
+      <c r="J97" s="11"/>
+      <c r="K97" s="11"/>
+      <c r="L97" s="11"/>
+    </row>
+    <row r="98" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A98" s="24">
         <v>2213</v>
       </c>
-      <c r="B98" s="1">
-        <v>2</v>
-      </c>
-      <c r="C98" s="6">
-        <v>1</v>
-      </c>
-      <c r="D98" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E98" s="6">
+      <c r="B98" s="24">
+        <v>2</v>
+      </c>
+      <c r="C98" s="24">
+        <v>1</v>
+      </c>
+      <c r="D98" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E98" s="24">
         <v>4055352</v>
       </c>
-      <c r="F98" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G98" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H98" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="J98" s="10"/>
-      <c r="K98" s="10"/>
-      <c r="L98" s="10"/>
-    </row>
-    <row r="99" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A99" s="9">
+      <c r="F98" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="G98" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H98" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="J98" s="11"/>
+      <c r="K98" s="11"/>
+      <c r="L98" s="11"/>
+    </row>
+    <row r="99" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A99" s="24">
         <v>2214</v>
       </c>
-      <c r="B99" s="1">
-        <v>2</v>
-      </c>
-      <c r="C99" s="6">
-        <v>1</v>
-      </c>
-      <c r="D99" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H99" s="10"/>
-      <c r="I99" s="10"/>
-      <c r="J99" s="10"/>
-      <c r="K99" s="10"/>
-      <c r="L99" s="10"/>
+      <c r="B99" s="24">
+        <v>2</v>
+      </c>
+      <c r="C99" s="24">
+        <v>1</v>
+      </c>
+      <c r="D99" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="G99" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H99" s="17"/>
+      <c r="I99" s="11"/>
+      <c r="J99" s="11"/>
+      <c r="K99" s="11"/>
+      <c r="L99" s="11"/>
     </row>
     <row r="100" customHeight="1" spans="1:12">
-      <c r="A100" s="34">
+      <c r="A100" s="24">
         <v>2215</v>
       </c>
-      <c r="B100" s="1">
-        <v>2</v>
-      </c>
-      <c r="C100" s="1">
-        <v>1</v>
-      </c>
-      <c r="D100" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G100" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H100"/>
+      <c r="B100" s="24">
+        <v>2</v>
+      </c>
+      <c r="C100" s="24">
+        <v>1</v>
+      </c>
+      <c r="D100" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E100" s="24"/>
+      <c r="F100" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H100" s="17"/>
     </row>
     <row r="101" customHeight="1" spans="1:12">
-      <c r="A101" s="9">
+      <c r="A101" s="24">
         <v>2216</v>
       </c>
-      <c r="B101" s="1">
-        <v>2</v>
-      </c>
-      <c r="C101" s="1">
-        <v>1</v>
-      </c>
-      <c r="D101" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E101" s="1">
+      <c r="B101" s="24">
+        <v>2</v>
+      </c>
+      <c r="C101" s="24">
+        <v>1</v>
+      </c>
+      <c r="D101" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E101" s="24">
         <v>4055355</v>
       </c>
-      <c r="F101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G101" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H101" t="s">
-        <v>85</v>
+      <c r="F101" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H101" s="17" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:12">
-      <c r="A102" s="34">
+      <c r="A102" s="24">
         <v>2217</v>
       </c>
-      <c r="B102" s="1">
-        <v>2</v>
-      </c>
-      <c r="C102" s="1">
-        <v>1</v>
-      </c>
-      <c r="D102" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E102" s="1">
+      <c r="B102" s="24">
+        <v>2</v>
+      </c>
+      <c r="C102" s="24">
+        <v>1</v>
+      </c>
+      <c r="D102" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102" s="24">
         <v>4055357</v>
       </c>
-      <c r="F102" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G102" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H102" t="s">
-        <v>93</v>
+      <c r="F102" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H102" s="17" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:12">
-      <c r="A103" s="35">
+      <c r="A103" s="16">
         <v>2301</v>
       </c>
-      <c r="B103" s="35"/>
-      <c r="C103" s="35">
+      <c r="B103" s="16"/>
+      <c r="C103" s="16">
         <v>2</v>
       </c>
       <c r="D103" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E103" s="35"/>
-      <c r="F103" s="35"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="16" t="s">
+        <v>163</v>
+      </c>
       <c r="G103" s="1" t="s">
-        <v>94</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="H103" s="17"/>
     </row>
     <row r="104" customHeight="1" spans="1:12">
-      <c r="A104" s="35">
+      <c r="A104" s="16">
         <v>2302</v>
       </c>
-      <c r="B104" s="35">
-        <v>1</v>
-      </c>
-      <c r="C104" s="35">
+      <c r="B104" s="16">
+        <v>1</v>
+      </c>
+      <c r="C104" s="16">
         <v>1</v>
       </c>
       <c r="D104" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E104" s="35"/>
-      <c r="F104" s="35"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="16" t="s">
+        <v>165</v>
+      </c>
       <c r="G104" s="1" t="s">
-        <v>94</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="H104" s="17"/>
     </row>
     <row r="105" customHeight="1" spans="1:12">
-      <c r="A105" s="35">
+      <c r="A105" s="16">
         <v>2303</v>
       </c>
-      <c r="B105" s="35">
-        <v>1</v>
-      </c>
-      <c r="C105" s="35">
+      <c r="B105" s="16">
+        <v>1</v>
+      </c>
+      <c r="C105" s="16">
         <v>1</v>
       </c>
       <c r="D105" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="E105" s="35">
+      <c r="E105" s="16">
         <v>4055371</v>
       </c>
-      <c r="F105" s="35"/>
+      <c r="F105" s="16" t="s">
+        <v>166</v>
+      </c>
       <c r="G105" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>95</v>
+        <v>164</v>
+      </c>
+      <c r="H105" s="17" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -4639,14 +4895,14 @@
         <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -4655,7 +4911,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4665,14 +4921,14 @@
         <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>99</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4680,14 +4936,14 @@
         <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>100</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4695,14 +4951,14 @@
         <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4710,14 +4966,14 @@
         <v>2205</v>
       </c>
       <c r="J9" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
         <v>2205_</v>
       </c>
       <c r="M9" t="s">
-        <v>102</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4725,14 +4981,14 @@
         <v>2206</v>
       </c>
       <c r="J10" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>2206_</v>
       </c>
       <c r="M10" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4740,14 +4996,14 @@
         <v>2207</v>
       </c>
       <c r="J11" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>2207_</v>
       </c>
       <c r="M11" t="s">
-        <v>104</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4755,14 +5011,14 @@
         <v>2208</v>
       </c>
       <c r="J12" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>2208_</v>
       </c>
       <c r="M12" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4770,32 +5026,32 @@
         <v>2209</v>
       </c>
       <c r="J13" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>2209_</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="I14">
         <v>2210</v>
       </c>
       <c r="J14" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>2210_</v>
       </c>
       <c r="M14" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4803,14 +5059,14 @@
         <v>2211</v>
       </c>
       <c r="J15" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>2211_</v>
       </c>
       <c r="M15" t="s">
-        <v>109</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4818,14 +5074,14 @@
         <v>2212</v>
       </c>
       <c r="J16" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>2212_</v>
       </c>
       <c r="M16" t="s">
-        <v>110</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4833,14 +5089,14 @@
         <v>2213</v>
       </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>2213_</v>
       </c>
       <c r="M17" t="s">
-        <v>111</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4848,29 +5104,29 @@
         <v>2214</v>
       </c>
       <c r="J18" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>2214_</v>
       </c>
       <c r="M18" t="s">
-        <v>112</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>113</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>115</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="191">
   <si>
     <t>序号</t>
   </si>
@@ -303,7 +303,7 @@
     <t>1201.mp3</t>
   </si>
   <si>
-    <t>建筑-愤怒的小鸟-升级2次</t>
+    <t>建筑-萌宠小队-升级2次</t>
   </si>
   <si>
     <t>1202.mp3</t>
@@ -318,7 +318,7 @@
     <t>1301.mp3</t>
   </si>
   <si>
-    <t>建筑-愤怒的小鸟-SLOT</t>
+    <t>建筑-萌宠小队-SLOT</t>
   </si>
   <si>
     <t>1302.mp3</t>
@@ -336,10 +336,22 @@
     <t>1305.mp3</t>
   </si>
   <si>
+    <t>1311.mp3</t>
+  </si>
+  <si>
+    <t>1312.mp3</t>
+  </si>
+  <si>
+    <t>1313.mp3</t>
+  </si>
+  <si>
+    <t>1314.mp3</t>
+  </si>
+  <si>
     <t>1401.mp3</t>
   </si>
   <si>
-    <t>建筑-愤怒的小鸟-升到2级</t>
+    <t>建筑-萌宠小队-升到2级</t>
   </si>
   <si>
     <t>1402.mp3</t>
@@ -360,7 +372,7 @@
     <t>1501.mp3</t>
   </si>
   <si>
-    <t>建筑-愤怒的小鸟-SLOT2</t>
+    <t>建筑-萌宠小队-SLOT2</t>
   </si>
   <si>
     <t>1502.mp3</t>
@@ -372,36 +384,21 @@
     <t>1504.mp3</t>
   </si>
   <si>
-    <t>1601.mp3</t>
-  </si>
-  <si>
     <t>雇员-抽卡-升级-升星</t>
   </si>
   <si>
-    <t>1602.mp3</t>
-  </si>
-  <si>
     <t>1603.mp3</t>
   </si>
   <si>
     <t>前往招募管理人才！</t>
   </si>
   <si>
-    <t>1604.mp3</t>
-  </si>
-  <si>
     <t>1605.mp3</t>
   </si>
   <si>
     <t>点击&lt;color=#00bfff&gt;按钮&lt;/color&gt;开始招募</t>
   </si>
   <si>
-    <t>1606.mp3</t>
-  </si>
-  <si>
-    <t>1607.mp3</t>
-  </si>
-  <si>
     <t>1608.mp3</t>
   </si>
   <si>
@@ -685,6 +682,18 @@
   </si>
   <si>
     <t>在这里可以&lt;color=#00bfff&gt;快速获得金币、娱乐城经验&lt;/color&gt;等资源</t>
+  </si>
+  <si>
+    <t>引导主线离开游戏</t>
+  </si>
+  <si>
+    <t>当前主线任务已完成，请退出游戏继续主线任务 .</t>
+  </si>
+  <si>
+    <t>点击退出游戏进入经营大厅</t>
+  </si>
+  <si>
+    <t>点击主线界面继续任务</t>
   </si>
   <si>
     <t>_</t>
@@ -973,18 +982,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -994,12 +1003,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1328,7 +1331,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
@@ -1352,16 +1355,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
@@ -1370,89 +1373,89 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1477,6 +1480,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1531,10 +1537,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1542,9 +1563,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2030,7 +2048,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
@@ -2040,40 +2058,40 @@
     <col min="5" max="5" width="9.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="100.883333333333" style="11" customWidth="1"/>
+    <col min="8" max="8" width="100.883333333333" style="12" customWidth="1"/>
     <col min="13" max="16384" width="15.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
       <c r="L1"/>
     </row>
     <row r="2" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -2085,2756 +2103,2918 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="11"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="12"/>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="11"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="12"/>
       <c r="I3"/>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="14"/>
-      <c r="H4" s="11"/>
+      <c r="A4" s="15"/>
+      <c r="H4" s="12"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
     </row>
     <row r="5" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <v>1001</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="16">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17">
         <v>4055101</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="15">
+      <c r="A6" s="16">
         <v>1002</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="16">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="17">
         <v>4055102</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="15">
+      <c r="A7" s="16">
         <v>1003</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="16">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="17">
         <v>4055103</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="17" t="s">
         <v>21</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="15">
+      <c r="A8" s="16">
         <v>1004</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="16">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="17">
         <v>4055104</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="17" t="s">
         <v>23</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="15">
+      <c r="A9" s="16">
         <v>1005</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="16">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="17">
         <v>4055109</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="17" t="s">
         <v>25</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="15">
+      <c r="A10" s="16">
         <v>1006</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="17">
         <v>4055105</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="17" t="s">
         <v>27</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
     </row>
     <row r="11" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="15">
+      <c r="A11" s="16">
         <v>1007</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="16">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="17">
         <v>4055106</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="17" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="15">
+      <c r="A12" s="16">
         <v>1008</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="16">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="17">
         <v>4055107</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="17" t="s">
         <v>31</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="15">
+      <c r="A13" s="16">
         <v>1009</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
         <v>4055108</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="17" t="s">
         <v>33</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
     </row>
     <row r="14" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="19">
+      <c r="A14" s="20">
         <v>1010</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21" t="s">
         <v>35</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="19">
+      <c r="A15" s="20">
         <v>1011</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20" t="s">
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21" t="s">
         <v>36</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="19">
+      <c r="A16" s="20">
         <v>1012</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20" t="s">
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="19">
+      <c r="A17" s="20">
         <v>1013</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20" t="s">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21" t="s">
         <v>38</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="19">
+      <c r="A18" s="20">
         <v>1201</v>
       </c>
-      <c r="B18" s="20">
-        <v>2</v>
-      </c>
-      <c r="C18" s="20">
-        <v>2</v>
-      </c>
-      <c r="D18" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="20">
+      <c r="B18" s="21">
+        <v>2</v>
+      </c>
+      <c r="C18" s="21">
+        <v>2</v>
+      </c>
+      <c r="D18" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="21">
         <v>4055121</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="19">
+      <c r="A19" s="20">
         <v>1202</v>
       </c>
-      <c r="B19" s="20">
-        <v>2</v>
-      </c>
-      <c r="C19" s="20">
-        <v>2</v>
-      </c>
-      <c r="D19" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="20">
+      <c r="B19" s="21">
+        <v>2</v>
+      </c>
+      <c r="C19" s="21">
+        <v>2</v>
+      </c>
+      <c r="D19" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="21">
         <v>4055122</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
     </row>
     <row r="20" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="19">
+      <c r="A20" s="20">
         <v>1203</v>
       </c>
-      <c r="B20" s="20">
-        <v>2</v>
-      </c>
-      <c r="C20" s="20">
-        <v>1</v>
-      </c>
-      <c r="D20" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="20">
+      <c r="B20" s="21">
+        <v>2</v>
+      </c>
+      <c r="C20" s="21">
+        <v>1</v>
+      </c>
+      <c r="D20" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="21">
         <v>4055123</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
     </row>
     <row r="21" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="19">
+      <c r="A21" s="20">
         <v>1204</v>
       </c>
-      <c r="B21" s="20">
-        <v>2</v>
-      </c>
-      <c r="C21" s="20">
-        <v>1</v>
-      </c>
-      <c r="D21" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="20">
+      <c r="B21" s="21">
+        <v>2</v>
+      </c>
+      <c r="C21" s="21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="21">
         <v>4055124</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="19">
+      <c r="A22" s="20">
         <v>1301</v>
       </c>
-      <c r="B22" s="20">
-        <v>2</v>
-      </c>
-      <c r="C22" s="20">
-        <v>1</v>
-      </c>
-      <c r="D22" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" s="20">
+      <c r="B22" s="21">
+        <v>2</v>
+      </c>
+      <c r="C22" s="21">
+        <v>1</v>
+      </c>
+      <c r="D22" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="21">
         <v>4055141</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
     </row>
     <row r="23" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A23" s="23">
+      <c r="A23" s="24">
         <v>1302</v>
       </c>
-      <c r="B23" s="24">
-        <v>2</v>
-      </c>
-      <c r="C23" s="24">
-        <v>1</v>
-      </c>
-      <c r="D23" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="24">
+      <c r="B23" s="25">
+        <v>2</v>
+      </c>
+      <c r="C23" s="25">
+        <v>1</v>
+      </c>
+      <c r="D23" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="25">
         <v>4055142</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
     </row>
     <row r="24" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A24" s="19">
+      <c r="A24" s="20">
         <v>1303</v>
       </c>
-      <c r="B24" s="20">
-        <v>2</v>
-      </c>
-      <c r="C24" s="20">
-        <v>1</v>
-      </c>
-      <c r="D24" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" s="20">
+      <c r="B24" s="21">
+        <v>2</v>
+      </c>
+      <c r="C24" s="21">
+        <v>1</v>
+      </c>
+      <c r="D24" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="21">
         <v>4055143</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
     </row>
     <row r="25" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="19">
+      <c r="A25" s="20">
         <v>1304</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20">
-        <v>1</v>
-      </c>
-      <c r="D25" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20" t="s">
+      <c r="B25" s="21"/>
+      <c r="C25" s="21">
+        <v>1</v>
+      </c>
+      <c r="D25" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G25" s="22" t="s">
+      <c r="G25" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
     </row>
     <row r="26" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="19">
+      <c r="A26" s="20">
         <v>1305</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20">
-        <v>1</v>
-      </c>
-      <c r="D26" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="20">
+      <c r="B26" s="21"/>
+      <c r="C26" s="21">
+        <v>1</v>
+      </c>
+      <c r="D26" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="21">
         <v>4055144</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="G26" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-    </row>
-    <row r="27" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="19">
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+    </row>
+    <row r="27" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A27" s="27">
+        <v>1311</v>
+      </c>
+      <c r="B27" s="28">
+        <v>2</v>
+      </c>
+      <c r="C27" s="28">
+        <v>1</v>
+      </c>
+      <c r="D27" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="28">
+        <v>4055145</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+    </row>
+    <row r="28" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A28" s="27">
+        <v>1312</v>
+      </c>
+      <c r="B28" s="28">
+        <v>2</v>
+      </c>
+      <c r="C28" s="28">
+        <v>1</v>
+      </c>
+      <c r="D28" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="28">
+        <v>4055146</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+    </row>
+    <row r="29" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A29" s="27">
+        <v>1313</v>
+      </c>
+      <c r="B29" s="28">
+        <v>2</v>
+      </c>
+      <c r="C29" s="28">
+        <v>1</v>
+      </c>
+      <c r="D29" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="28">
+        <v>4055147</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+    </row>
+    <row r="30" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A30" s="27">
+        <v>1314</v>
+      </c>
+      <c r="B30" s="28">
+        <v>2</v>
+      </c>
+      <c r="C30" s="28">
+        <v>1</v>
+      </c>
+      <c r="D30" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="28">
+        <v>4055148</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+    </row>
+    <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A31" s="20">
         <v>1401</v>
       </c>
-      <c r="B27" s="20">
-        <v>2</v>
-      </c>
-      <c r="C27" s="20">
-        <v>1</v>
-      </c>
-      <c r="D27" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="20">
+      <c r="B31" s="21">
+        <v>2</v>
+      </c>
+      <c r="C31" s="21">
+        <v>1</v>
+      </c>
+      <c r="D31" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="21">
         <v>4055161</v>
       </c>
-      <c r="F27" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-    </row>
-    <row r="28" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="19">
+      <c r="F31" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A32" s="20">
         <v>1402</v>
       </c>
-      <c r="B28" s="20">
-        <v>2</v>
-      </c>
-      <c r="C28" s="20">
-        <v>1</v>
-      </c>
-      <c r="D28" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="20">
+      <c r="B32" s="21">
+        <v>2</v>
+      </c>
+      <c r="C32" s="21">
+        <v>1</v>
+      </c>
+      <c r="D32" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="21">
         <v>4055162</v>
       </c>
-      <c r="F28" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-    </row>
-    <row r="29" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="19">
+      <c r="F32" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A33" s="20">
         <v>1403</v>
       </c>
-      <c r="B29" s="20">
-        <v>2</v>
-      </c>
-      <c r="C29" s="20">
-        <v>1</v>
-      </c>
-      <c r="D29" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="20">
+      <c r="B33" s="21">
+        <v>2</v>
+      </c>
+      <c r="C33" s="21">
+        <v>1</v>
+      </c>
+      <c r="D33" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="21">
         <v>4055163</v>
       </c>
-      <c r="F29" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-    </row>
-    <row r="30" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="19">
+      <c r="F33" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A34" s="20">
         <v>1404</v>
       </c>
-      <c r="B30" s="20">
-        <v>2</v>
-      </c>
-      <c r="C30" s="20">
-        <v>1</v>
-      </c>
-      <c r="D30" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="20">
+      <c r="B34" s="21">
+        <v>2</v>
+      </c>
+      <c r="C34" s="21">
+        <v>1</v>
+      </c>
+      <c r="D34" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="21">
         <v>4055164</v>
       </c>
-      <c r="F30" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-    </row>
-    <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="19">
+      <c r="F34" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A35" s="20">
         <v>1405</v>
       </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20">
-        <v>1</v>
-      </c>
-      <c r="D31" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20" t="s">
+      <c r="B35" s="21"/>
+      <c r="C35" s="21">
+        <v>1</v>
+      </c>
+      <c r="D35" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-    </row>
-    <row r="32" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="19">
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A36" s="20">
         <v>1406</v>
       </c>
-      <c r="B32" s="20">
-        <v>2</v>
-      </c>
-      <c r="C32" s="20">
-        <v>1</v>
-      </c>
-      <c r="D32" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" s="20">
+      <c r="B36" s="21">
+        <v>2</v>
+      </c>
+      <c r="C36" s="21">
+        <v>1</v>
+      </c>
+      <c r="D36" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="21">
         <v>4055165</v>
       </c>
-      <c r="F32" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G32" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
-    </row>
-    <row r="33" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="19">
+      <c r="F36" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A37" s="20">
         <v>1501</v>
       </c>
-      <c r="B33" s="20">
-        <v>2</v>
-      </c>
-      <c r="C33" s="20">
-        <v>1</v>
-      </c>
-      <c r="D33" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" s="20">
+      <c r="B37" s="21">
+        <v>2</v>
+      </c>
+      <c r="C37" s="21">
+        <v>1</v>
+      </c>
+      <c r="D37" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="21">
         <v>4055181</v>
       </c>
-      <c r="F33" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-    </row>
-    <row r="34" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="19">
+      <c r="F37" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A38" s="20">
         <v>1502</v>
       </c>
-      <c r="B34" s="20">
-        <v>2</v>
-      </c>
-      <c r="C34" s="20">
-        <v>1</v>
-      </c>
-      <c r="D34" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" s="20">
+      <c r="B38" s="21">
+        <v>2</v>
+      </c>
+      <c r="C38" s="21">
+        <v>1</v>
+      </c>
+      <c r="D38" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="21">
         <v>4055182</v>
       </c>
-      <c r="F34" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-    </row>
-    <row r="35" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="19">
+      <c r="F38" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G38" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+    </row>
+    <row r="39" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A39" s="20">
         <v>1503</v>
       </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20">
-        <v>1</v>
-      </c>
-      <c r="D35" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G35" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
-    </row>
-    <row r="36" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="19">
+      <c r="B39" s="21"/>
+      <c r="C39" s="21">
+        <v>1</v>
+      </c>
+      <c r="D39" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G39" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+    </row>
+    <row r="40" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A40" s="20">
         <v>1504</v>
       </c>
-      <c r="B36" s="20"/>
-      <c r="C36" s="20">
-        <v>1</v>
-      </c>
-      <c r="D36" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-    </row>
-    <row r="37" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="15">
+      <c r="B40" s="21"/>
+      <c r="C40" s="21">
+        <v>1</v>
+      </c>
+      <c r="D40" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+    </row>
+    <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A41" s="30">
         <v>1601</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16">
-        <v>1</v>
-      </c>
-      <c r="D37" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G37" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H37" s="17"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-    </row>
-    <row r="38" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="15">
+      <c r="B41" s="31"/>
+      <c r="C41" s="31">
+        <v>1</v>
+      </c>
+      <c r="D41" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+    </row>
+    <row r="42" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A42" s="16">
         <v>1602</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16">
-        <v>1</v>
-      </c>
-      <c r="D38" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H38" s="17"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-    </row>
-    <row r="39" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A39" s="15">
+      <c r="B42" s="17"/>
+      <c r="C42" s="17">
+        <v>1</v>
+      </c>
+      <c r="D42" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+    </row>
+    <row r="43" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A43" s="16">
         <v>1603</v>
       </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16">
-        <v>1</v>
-      </c>
-      <c r="D39" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="16">
+      <c r="B43" s="17"/>
+      <c r="C43" s="17">
+        <v>1</v>
+      </c>
+      <c r="D43" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="17">
         <v>4055203</v>
       </c>
-      <c r="F39" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G39" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H39" s="17" t="s">
+      <c r="F43" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G43" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-    </row>
-    <row r="40" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="15">
+      <c r="H43" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+    </row>
+    <row r="44" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A44" s="16">
         <v>1604</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16">
-        <v>1</v>
-      </c>
-      <c r="D40" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H40" s="17"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-    </row>
-    <row r="41" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="15">
+      <c r="B44" s="17"/>
+      <c r="C44" s="17">
+        <v>1</v>
+      </c>
+      <c r="D44" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H44" s="18"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
+    </row>
+    <row r="45" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A45" s="16">
         <v>1605</v>
       </c>
-      <c r="B41" s="16">
-        <v>2</v>
-      </c>
-      <c r="C41" s="16">
-        <v>1</v>
-      </c>
-      <c r="D41" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" s="16">
+      <c r="B45" s="17">
+        <v>2</v>
+      </c>
+      <c r="C45" s="17">
+        <v>1</v>
+      </c>
+      <c r="D45" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="17">
         <v>4055204</v>
       </c>
-      <c r="F41" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H41" s="17" t="s">
+      <c r="F45" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-    </row>
-    <row r="42" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="15">
+      <c r="G45" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+    </row>
+    <row r="46" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A46" s="16">
         <v>1606</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16">
-        <v>1</v>
-      </c>
-      <c r="D42" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H42" s="17"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-    </row>
-    <row r="43" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="15">
+      <c r="B46" s="17"/>
+      <c r="C46" s="17">
+        <v>1</v>
+      </c>
+      <c r="D46" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H46" s="18"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+    </row>
+    <row r="47" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A47" s="16">
         <v>1607</v>
       </c>
-      <c r="B43" s="16">
-        <v>2</v>
-      </c>
-      <c r="C43" s="16">
-        <v>1</v>
-      </c>
-      <c r="D43" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16" t="s">
+      <c r="B47" s="17">
+        <v>2</v>
+      </c>
+      <c r="C47" s="17">
+        <v>1</v>
+      </c>
+      <c r="D47" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H47" s="18"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+    </row>
+    <row r="48" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="16">
+        <v>1608</v>
+      </c>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17">
+        <v>1</v>
+      </c>
+      <c r="D48" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="17">
+        <v>4055205</v>
+      </c>
+      <c r="F48" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="G43" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H43" s="17"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-    </row>
-    <row r="44" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="15">
-        <v>1608</v>
-      </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16">
-        <v>1</v>
-      </c>
-      <c r="D44" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E44" s="16">
-        <v>4055205</v>
-      </c>
-      <c r="F44" s="16" t="s">
+      <c r="G48" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H48" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="G44" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H44" s="17" t="s">
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+    </row>
+    <row r="49" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A49" s="16">
+        <v>1609</v>
+      </c>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17">
+        <v>1</v>
+      </c>
+      <c r="D49" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="17">
+        <v>4055206</v>
+      </c>
+      <c r="F49" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-    </row>
-    <row r="45" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="15">
-        <v>1609</v>
-      </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16">
-        <v>1</v>
-      </c>
-      <c r="D45" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" s="16">
-        <v>4055206</v>
-      </c>
-      <c r="F45" s="16" t="s">
+      <c r="G49" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H49" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="G45" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H45" s="17" t="s">
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="12"/>
+    </row>
+    <row r="50" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A50" s="16">
+        <v>1610</v>
+      </c>
+      <c r="B50" s="17">
+        <v>2</v>
+      </c>
+      <c r="C50" s="17">
+        <v>1</v>
+      </c>
+      <c r="D50" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="17">
+        <v>4055207</v>
+      </c>
+      <c r="F50" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-    </row>
-    <row r="46" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="15">
-        <v>1610</v>
-      </c>
-      <c r="B46" s="16">
-        <v>2</v>
-      </c>
-      <c r="C46" s="16">
-        <v>1</v>
-      </c>
-      <c r="D46" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" s="16">
-        <v>4055207</v>
-      </c>
-      <c r="F46" s="16" t="s">
+      <c r="G50" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H50" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="G46" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H46" s="17" t="s">
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="12"/>
+    </row>
+    <row r="51" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A51" s="16">
+        <v>1611</v>
+      </c>
+      <c r="B51" s="17">
+        <v>2</v>
+      </c>
+      <c r="C51" s="17">
+        <v>1</v>
+      </c>
+      <c r="D51" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" s="17">
+        <v>4055208</v>
+      </c>
+      <c r="F51" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-    </row>
-    <row r="47" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="15">
-        <v>1611</v>
-      </c>
-      <c r="B47" s="16">
-        <v>2</v>
-      </c>
-      <c r="C47" s="16">
-        <v>1</v>
-      </c>
-      <c r="D47" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" s="16">
-        <v>4055208</v>
-      </c>
-      <c r="F47" s="16" t="s">
+      <c r="G51" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H51" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="G47" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H47" s="17" t="s">
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="12"/>
+    </row>
+    <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A52" s="20">
+        <v>1612</v>
+      </c>
+      <c r="B52" s="21">
+        <v>2</v>
+      </c>
+      <c r="C52" s="21">
+        <v>1</v>
+      </c>
+      <c r="D52" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" s="21">
+        <v>4055209</v>
+      </c>
+      <c r="F52" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-    </row>
-    <row r="48" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="19">
-        <v>1612</v>
-      </c>
-      <c r="B48" s="20">
-        <v>2</v>
-      </c>
-      <c r="C48" s="20">
-        <v>1</v>
-      </c>
-      <c r="D48" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E48" s="20">
-        <v>4055209</v>
-      </c>
-      <c r="F48" s="20" t="s">
+      <c r="G52" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+    </row>
+    <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A53" s="20">
+        <v>1701</v>
+      </c>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21">
+        <v>1</v>
+      </c>
+      <c r="D53" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="G48" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="H48" s="21"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21"/>
-      <c r="K48" s="21"/>
-      <c r="L48" s="21"/>
-    </row>
-    <row r="49" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="19">
-        <v>1701</v>
-      </c>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20">
-        <v>1</v>
-      </c>
-      <c r="D49" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20" t="s">
+      <c r="G53" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="G49" s="22" t="s">
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+    </row>
+    <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A54" s="20">
+        <v>1702</v>
+      </c>
+      <c r="B54" s="33"/>
+      <c r="C54" s="21">
+        <v>1</v>
+      </c>
+      <c r="D54" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" s="33"/>
+      <c r="F54" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21"/>
-      <c r="K49" s="21"/>
-      <c r="L49" s="21"/>
-    </row>
-    <row r="50" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A50" s="19">
-        <v>1702</v>
-      </c>
-      <c r="B50" s="27"/>
-      <c r="C50" s="20">
-        <v>1</v>
-      </c>
-      <c r="D50" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E50" s="27"/>
-      <c r="F50" s="20" t="s">
+      <c r="G54" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H54" s="22"/>
+      <c r="I54" s="22"/>
+      <c r="J54" s="22"/>
+      <c r="K54" s="22"/>
+      <c r="L54" s="22"/>
+    </row>
+    <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A55" s="20">
+        <v>1703</v>
+      </c>
+      <c r="B55" s="21">
+        <v>2</v>
+      </c>
+      <c r="C55" s="21">
+        <v>1</v>
+      </c>
+      <c r="D55" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" s="21">
+        <v>4055222</v>
+      </c>
+      <c r="F55" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="G50" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21"/>
-      <c r="K50" s="21"/>
-      <c r="L50" s="21"/>
-    </row>
-    <row r="51" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A51" s="19">
-        <v>1703</v>
-      </c>
-      <c r="B51" s="20">
-        <v>2</v>
-      </c>
-      <c r="C51" s="20">
-        <v>1</v>
-      </c>
-      <c r="D51" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E51" s="20">
-        <v>4055222</v>
-      </c>
-      <c r="F51" s="20" t="s">
+      <c r="G55" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="22"/>
+      <c r="L55" s="22"/>
+    </row>
+    <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A56" s="20">
+        <v>1704</v>
+      </c>
+      <c r="B56" s="21">
+        <v>2</v>
+      </c>
+      <c r="C56" s="21">
+        <v>1</v>
+      </c>
+      <c r="D56" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" s="21">
+        <v>4055223</v>
+      </c>
+      <c r="F56" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="G51" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="21"/>
-      <c r="L51" s="21"/>
-    </row>
-    <row r="52" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A52" s="19">
-        <v>1704</v>
-      </c>
-      <c r="B52" s="20">
-        <v>2</v>
-      </c>
-      <c r="C52" s="20">
-        <v>1</v>
-      </c>
-      <c r="D52" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E52" s="20">
-        <v>4055223</v>
-      </c>
-      <c r="F52" s="20" t="s">
+      <c r="G56" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H56" s="22"/>
+      <c r="I56" s="22"/>
+      <c r="J56" s="22"/>
+      <c r="K56" s="22"/>
+      <c r="L56" s="22"/>
+    </row>
+    <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A57" s="20">
+        <v>1705</v>
+      </c>
+      <c r="B57" s="21">
+        <v>2</v>
+      </c>
+      <c r="C57" s="21">
+        <v>1</v>
+      </c>
+      <c r="D57" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="21">
+        <v>4055224</v>
+      </c>
+      <c r="F57" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="G52" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21"/>
-      <c r="K52" s="21"/>
-      <c r="L52" s="21"/>
-    </row>
-    <row r="53" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A53" s="19">
-        <v>1705</v>
-      </c>
-      <c r="B53" s="20">
-        <v>2</v>
-      </c>
-      <c r="C53" s="20">
-        <v>1</v>
-      </c>
-      <c r="D53" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E53" s="20">
-        <v>4055224</v>
-      </c>
-      <c r="F53" s="20" t="s">
+      <c r="G57" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="22"/>
+      <c r="K57" s="22"/>
+      <c r="L57" s="22"/>
+    </row>
+    <row r="58" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A58" s="20">
+        <v>1706</v>
+      </c>
+      <c r="B58" s="21"/>
+      <c r="C58" s="21">
+        <v>1</v>
+      </c>
+      <c r="D58" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="G53" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21"/>
-      <c r="K53" s="21"/>
-      <c r="L53" s="21"/>
-    </row>
-    <row r="54" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A54" s="19">
-        <v>1706</v>
-      </c>
-      <c r="B54" s="20"/>
-      <c r="C54" s="20">
-        <v>1</v>
-      </c>
-      <c r="D54" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20" t="s">
+      <c r="G58" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+    </row>
+    <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A59" s="20">
+        <v>1707</v>
+      </c>
+      <c r="B59" s="21">
+        <v>2</v>
+      </c>
+      <c r="C59" s="21">
+        <v>1</v>
+      </c>
+      <c r="D59" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" s="21">
+        <v>4055225</v>
+      </c>
+      <c r="F59" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="G54" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="21"/>
-      <c r="K54" s="21"/>
-      <c r="L54" s="21"/>
-    </row>
-    <row r="55" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A55" s="19">
-        <v>1707</v>
-      </c>
-      <c r="B55" s="20">
-        <v>2</v>
-      </c>
-      <c r="C55" s="20">
-        <v>1</v>
-      </c>
-      <c r="D55" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E55" s="20">
-        <v>4055225</v>
-      </c>
-      <c r="F55" s="20" t="s">
+      <c r="G59" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="22"/>
+    </row>
+    <row r="60" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A60" s="20">
+        <v>1708</v>
+      </c>
+      <c r="B60" s="21">
+        <v>2</v>
+      </c>
+      <c r="C60" s="21">
+        <v>1</v>
+      </c>
+      <c r="D60" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" s="21">
+        <v>4055226</v>
+      </c>
+      <c r="F60" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="G55" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
-      <c r="K55" s="21"/>
-      <c r="L55" s="21"/>
-    </row>
-    <row r="56" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A56" s="19">
-        <v>1708</v>
-      </c>
-      <c r="B56" s="20">
-        <v>2</v>
-      </c>
-      <c r="C56" s="20">
-        <v>1</v>
-      </c>
-      <c r="D56" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" s="20">
-        <v>4055226</v>
-      </c>
-      <c r="F56" s="20" t="s">
+      <c r="G60" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H60" s="22"/>
+      <c r="I60" s="22"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="22"/>
+    </row>
+    <row r="61" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A61" s="20">
+        <v>1709</v>
+      </c>
+      <c r="B61" s="21"/>
+      <c r="C61" s="21">
+        <v>1</v>
+      </c>
+      <c r="D61" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="G56" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H56" s="21"/>
-      <c r="I56" s="21"/>
-      <c r="J56" s="21"/>
-      <c r="K56" s="21"/>
-      <c r="L56" s="21"/>
-    </row>
-    <row r="57" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A57" s="19">
-        <v>1709</v>
-      </c>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20">
-        <v>1</v>
-      </c>
-      <c r="D57" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20" t="s">
+      <c r="G61" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="22"/>
+    </row>
+    <row r="62" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A62" s="20">
+        <v>1710</v>
+      </c>
+      <c r="B62" s="21"/>
+      <c r="C62" s="21">
+        <v>1</v>
+      </c>
+      <c r="D62" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="G57" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
-      <c r="J57" s="21"/>
-      <c r="K57" s="21"/>
-      <c r="L57" s="21"/>
-    </row>
-    <row r="58" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A58" s="19">
-        <v>1710</v>
-      </c>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20">
-        <v>1</v>
-      </c>
-      <c r="D58" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20" t="s">
+      <c r="G62" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
+    </row>
+    <row r="63" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A63" s="20">
+        <v>1711</v>
+      </c>
+      <c r="B63" s="21">
+        <v>2</v>
+      </c>
+      <c r="C63" s="21">
+        <v>1</v>
+      </c>
+      <c r="D63" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" s="21">
+        <v>4055227</v>
+      </c>
+      <c r="F63" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="G58" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="21"/>
-      <c r="K58" s="21"/>
-      <c r="L58" s="21"/>
-    </row>
-    <row r="59" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="19">
-        <v>1711</v>
-      </c>
-      <c r="B59" s="20">
-        <v>2</v>
-      </c>
-      <c r="C59" s="20">
-        <v>1</v>
-      </c>
-      <c r="D59" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" s="20">
-        <v>4055227</v>
-      </c>
-      <c r="F59" s="20" t="s">
+      <c r="G63" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="22"/>
+      <c r="K63" s="22"/>
+      <c r="L63" s="22"/>
+    </row>
+    <row r="64" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A64" s="20">
+        <v>1712</v>
+      </c>
+      <c r="B64" s="21">
+        <v>2</v>
+      </c>
+      <c r="C64" s="21">
+        <v>1</v>
+      </c>
+      <c r="D64" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" s="21">
+        <v>4055228</v>
+      </c>
+      <c r="F64" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G59" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H59" s="21"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
-      <c r="K59" s="21"/>
-      <c r="L59" s="21"/>
-    </row>
-    <row r="60" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="19">
-        <v>1712</v>
-      </c>
-      <c r="B60" s="20">
-        <v>2</v>
-      </c>
-      <c r="C60" s="20">
-        <v>1</v>
-      </c>
-      <c r="D60" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E60" s="20">
-        <v>4055228</v>
-      </c>
-      <c r="F60" s="20" t="s">
+      <c r="G64" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H64" s="22"/>
+      <c r="I64" s="22"/>
+      <c r="J64" s="22"/>
+      <c r="K64" s="22"/>
+      <c r="L64" s="22"/>
+    </row>
+    <row r="65" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A65" s="20">
+        <v>1801</v>
+      </c>
+      <c r="B65" s="21"/>
+      <c r="C65" s="21">
+        <v>1</v>
+      </c>
+      <c r="D65" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="G60" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="21"/>
-      <c r="K60" s="21"/>
-      <c r="L60" s="21"/>
-    </row>
-    <row r="61" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="19">
-        <v>1801</v>
-      </c>
-      <c r="B61" s="20"/>
-      <c r="C61" s="20">
-        <v>1</v>
-      </c>
-      <c r="D61" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20" t="s">
+      <c r="G65" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="G61" s="22" t="s">
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="22"/>
+      <c r="K65" s="22"/>
+      <c r="L65" s="22"/>
+    </row>
+    <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A66" s="20">
+        <v>1802</v>
+      </c>
+      <c r="B66" s="21"/>
+      <c r="C66" s="21">
+        <v>1</v>
+      </c>
+      <c r="D66" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="H61" s="21"/>
-      <c r="I61" s="21"/>
-      <c r="J61" s="21"/>
-      <c r="K61" s="21"/>
-      <c r="L61" s="21"/>
-    </row>
-    <row r="62" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A62" s="19">
-        <v>1802</v>
-      </c>
-      <c r="B62" s="20"/>
-      <c r="C62" s="20">
-        <v>1</v>
-      </c>
-      <c r="D62" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20" t="s">
+      <c r="G66" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H66" s="22"/>
+      <c r="I66" s="22"/>
+      <c r="J66" s="22"/>
+      <c r="K66" s="22"/>
+      <c r="L66" s="22"/>
+    </row>
+    <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A67" s="20">
+        <v>1803</v>
+      </c>
+      <c r="B67" s="21">
+        <v>2</v>
+      </c>
+      <c r="C67" s="21">
+        <v>1</v>
+      </c>
+      <c r="D67" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" s="21">
+        <v>4055243</v>
+      </c>
+      <c r="F67" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="G62" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="21"/>
-      <c r="L62" s="21"/>
-    </row>
-    <row r="63" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A63" s="19">
-        <v>1803</v>
-      </c>
-      <c r="B63" s="20">
-        <v>2</v>
-      </c>
-      <c r="C63" s="20">
-        <v>1</v>
-      </c>
-      <c r="D63" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E63" s="20">
-        <v>4055243</v>
-      </c>
-      <c r="F63" s="20" t="s">
+      <c r="G67" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="22"/>
+      <c r="K67" s="22"/>
+      <c r="L67" s="22"/>
+    </row>
+    <row r="68" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A68" s="20">
+        <v>1804</v>
+      </c>
+      <c r="B68" s="21">
+        <v>2</v>
+      </c>
+      <c r="C68" s="21">
+        <v>1</v>
+      </c>
+      <c r="D68" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" s="21">
+        <v>4055244</v>
+      </c>
+      <c r="F68" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="G63" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
-      <c r="K63" s="21"/>
-      <c r="L63" s="21"/>
-    </row>
-    <row r="64" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A64" s="19">
-        <v>1804</v>
-      </c>
-      <c r="B64" s="20">
-        <v>2</v>
-      </c>
-      <c r="C64" s="20">
-        <v>1</v>
-      </c>
-      <c r="D64" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E64" s="20">
-        <v>4055244</v>
-      </c>
-      <c r="F64" s="20" t="s">
+      <c r="G68" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+    </row>
+    <row r="69" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A69" s="20">
+        <v>1805</v>
+      </c>
+      <c r="B69" s="21">
+        <v>2</v>
+      </c>
+      <c r="C69" s="21">
+        <v>1</v>
+      </c>
+      <c r="D69" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" s="21">
+        <v>4055245</v>
+      </c>
+      <c r="F69" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="G64" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="H64" s="21"/>
-      <c r="I64" s="21"/>
-      <c r="J64" s="21"/>
-      <c r="K64" s="21"/>
-      <c r="L64" s="21"/>
-    </row>
-    <row r="65" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A65" s="19">
-        <v>1805</v>
-      </c>
-      <c r="B65" s="20">
-        <v>2</v>
-      </c>
-      <c r="C65" s="20">
-        <v>1</v>
-      </c>
-      <c r="D65" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E65" s="20">
-        <v>4055245</v>
-      </c>
-      <c r="F65" s="20" t="s">
+      <c r="G69" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+      <c r="L69" s="22"/>
+    </row>
+    <row r="70" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A70" s="20">
+        <v>1806</v>
+      </c>
+      <c r="B70" s="21">
+        <v>2</v>
+      </c>
+      <c r="C70" s="21">
+        <v>1</v>
+      </c>
+      <c r="D70" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" s="21">
+        <v>4055246</v>
+      </c>
+      <c r="F70" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="G65" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21"/>
-      <c r="K65" s="21"/>
-      <c r="L65" s="21"/>
-    </row>
-    <row r="66" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A66" s="19">
-        <v>1806</v>
-      </c>
-      <c r="B66" s="20">
-        <v>2</v>
-      </c>
-      <c r="C66" s="20">
-        <v>1</v>
-      </c>
-      <c r="D66" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E66" s="20">
-        <v>4055246</v>
-      </c>
-      <c r="F66" s="20" t="s">
+      <c r="G70" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+    </row>
+    <row r="71" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A71" s="20">
+        <v>1807</v>
+      </c>
+      <c r="B71" s="21">
+        <v>2</v>
+      </c>
+      <c r="C71" s="21">
+        <v>1</v>
+      </c>
+      <c r="D71" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" s="21">
+        <v>4055247</v>
+      </c>
+      <c r="F71" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="G66" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="H66" s="21"/>
-      <c r="I66" s="21"/>
-      <c r="J66" s="21"/>
-      <c r="K66" s="21"/>
-      <c r="L66" s="21"/>
-    </row>
-    <row r="67" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A67" s="19">
-        <v>1807</v>
-      </c>
-      <c r="B67" s="20">
-        <v>2</v>
-      </c>
-      <c r="C67" s="20">
-        <v>1</v>
-      </c>
-      <c r="D67" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E67" s="20">
-        <v>4055247</v>
-      </c>
-      <c r="F67" s="20" t="s">
+      <c r="G71" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
+      <c r="K71" s="22"/>
+      <c r="L71" s="22"/>
+    </row>
+    <row r="72" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A72" s="16">
+        <v>1901</v>
+      </c>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17">
+        <v>1</v>
+      </c>
+      <c r="D72" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G67" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="H67" s="21"/>
-      <c r="I67" s="21"/>
-      <c r="J67" s="21"/>
-      <c r="K67" s="21"/>
-      <c r="L67" s="21"/>
-    </row>
-    <row r="68" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A68" s="15">
-        <v>1901</v>
-      </c>
-      <c r="B68" s="16"/>
-      <c r="C68" s="16">
-        <v>1</v>
-      </c>
-      <c r="D68" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16" t="s">
+      <c r="G72" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="G68" s="25" t="s">
+      <c r="H72" s="18"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="19"/>
+      <c r="K72" s="19"/>
+      <c r="L72" s="19"/>
+    </row>
+    <row r="73" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A73" s="16">
+        <v>1902</v>
+      </c>
+      <c r="B73" s="17">
+        <v>2</v>
+      </c>
+      <c r="C73" s="17">
+        <v>1</v>
+      </c>
+      <c r="D73" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" s="17">
+        <v>4055263</v>
+      </c>
+      <c r="F73" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="H68" s="17"/>
-      <c r="I68" s="18"/>
-      <c r="J68" s="18"/>
-      <c r="K68" s="18"/>
-      <c r="L68" s="18"/>
-    </row>
-    <row r="69" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A69" s="15">
-        <v>1902</v>
-      </c>
-      <c r="B69" s="16">
-        <v>2</v>
-      </c>
-      <c r="C69" s="16">
-        <v>1</v>
-      </c>
-      <c r="D69" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E69" s="16">
-        <v>4055263</v>
-      </c>
-      <c r="F69" s="16" t="s">
+      <c r="G73" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H73" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="G69" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="H69" s="17" t="s">
+      <c r="I73" s="19"/>
+      <c r="J73" s="19"/>
+      <c r="K73" s="19"/>
+      <c r="L73" s="19"/>
+    </row>
+    <row r="74" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A74" s="16">
+        <v>1903</v>
+      </c>
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" s="34"/>
+      <c r="F74" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="I69" s="18"/>
-      <c r="J69" s="18"/>
-      <c r="K69" s="18"/>
-      <c r="L69" s="18"/>
-    </row>
-    <row r="70" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A70" s="15">
-        <v>1903</v>
-      </c>
-      <c r="B70" s="16"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E70" s="28"/>
-      <c r="F70" s="16" t="s">
+      <c r="G74" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H74" s="18"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="19"/>
+      <c r="K74" s="19"/>
+      <c r="L74" s="19"/>
+    </row>
+    <row r="75" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A75" s="16">
+        <v>1904</v>
+      </c>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17">
+        <v>1</v>
+      </c>
+      <c r="D75" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="G70" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="H70" s="17"/>
-      <c r="I70" s="18"/>
-      <c r="J70" s="18"/>
-      <c r="K70" s="18"/>
-      <c r="L70" s="18"/>
-    </row>
-    <row r="71" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A71" s="15">
-        <v>1904</v>
-      </c>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16">
-        <v>1</v>
-      </c>
-      <c r="D71" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16" t="s">
+      <c r="G75" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H75" s="18"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="19"/>
+      <c r="K75" s="19"/>
+      <c r="L75" s="19"/>
+    </row>
+    <row r="76" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A76" s="16">
+        <v>1905</v>
+      </c>
+      <c r="B76" s="17">
+        <v>2</v>
+      </c>
+      <c r="C76" s="17">
+        <v>1</v>
+      </c>
+      <c r="D76" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" s="17">
+        <v>4055264</v>
+      </c>
+      <c r="F76" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G71" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="H71" s="17"/>
-      <c r="I71" s="18"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="18"/>
-      <c r="L71" s="18"/>
-    </row>
-    <row r="72" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A72" s="15">
-        <v>1905</v>
-      </c>
-      <c r="B72" s="16">
-        <v>2</v>
-      </c>
-      <c r="C72" s="16">
-        <v>1</v>
-      </c>
-      <c r="D72" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E72" s="16">
-        <v>4055264</v>
-      </c>
-      <c r="F72" s="16" t="s">
+      <c r="G76" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H76" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="G72" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="H72" s="17" t="s">
+      <c r="I76" s="19"/>
+      <c r="J76" s="19"/>
+      <c r="K76" s="19"/>
+      <c r="L76" s="19"/>
+    </row>
+    <row r="77" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A77" s="24">
+        <v>1981</v>
+      </c>
+      <c r="B77" s="25"/>
+      <c r="C77" s="25">
+        <v>1</v>
+      </c>
+      <c r="D77" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="I72" s="18"/>
-      <c r="J72" s="18"/>
-      <c r="K72" s="18"/>
-      <c r="L72" s="18"/>
-    </row>
-    <row r="73" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A73" s="23">
-        <v>1981</v>
-      </c>
-      <c r="B73" s="24"/>
-      <c r="C73" s="24">
-        <v>1</v>
-      </c>
-      <c r="D73" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24" t="s">
+      <c r="G77" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="G73" s="26" t="s">
+      <c r="H77" s="18"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="12"/>
+    </row>
+    <row r="78" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A78" s="24">
+        <v>1982</v>
+      </c>
+      <c r="B78" s="25"/>
+      <c r="C78" s="25">
+        <v>1</v>
+      </c>
+      <c r="D78" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="H73" s="17"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11"/>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-    </row>
-    <row r="74" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A74" s="23">
-        <v>1982</v>
-      </c>
-      <c r="B74" s="24"/>
-      <c r="C74" s="24">
-        <v>1</v>
-      </c>
-      <c r="D74" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24" t="s">
+      <c r="G78" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="H78" s="18"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="12"/>
+      <c r="L78" s="12"/>
+    </row>
+    <row r="79" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A79" s="24">
+        <v>1983</v>
+      </c>
+      <c r="B79" s="25">
+        <v>2</v>
+      </c>
+      <c r="C79" s="25">
+        <v>1</v>
+      </c>
+      <c r="D79" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79" s="25">
+        <v>4055321</v>
+      </c>
+      <c r="F79" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="G74" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="H74" s="17"/>
-      <c r="I74" s="11"/>
-      <c r="J74" s="11"/>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-    </row>
-    <row r="75" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A75" s="23">
-        <v>1983</v>
-      </c>
-      <c r="B75" s="24">
-        <v>2</v>
-      </c>
-      <c r="C75" s="24">
-        <v>1</v>
-      </c>
-      <c r="D75" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E75" s="24">
-        <v>4055321</v>
-      </c>
-      <c r="F75" s="24" t="s">
+      <c r="G79" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="H79" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="G75" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="H75" s="17" t="s">
+      <c r="I79" s="12"/>
+      <c r="J79" s="12"/>
+      <c r="K79" s="12"/>
+      <c r="L79" s="12"/>
+    </row>
+    <row r="80" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A80" s="16">
+        <v>2001</v>
+      </c>
+      <c r="B80" s="17"/>
+      <c r="C80" s="17">
+        <v>1</v>
+      </c>
+      <c r="D80" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="I75" s="11"/>
-      <c r="J75" s="11"/>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-    </row>
-    <row r="76" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A76" s="15">
-        <v>2001</v>
-      </c>
-      <c r="B76" s="16"/>
-      <c r="C76" s="16">
-        <v>1</v>
-      </c>
-      <c r="D76" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16" t="s">
+      <c r="G80" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="G76" s="25" t="s">
+      <c r="H80" s="18"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="19"/>
+      <c r="K80" s="19"/>
+      <c r="L80" s="19"/>
+    </row>
+    <row r="81" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A81" s="16">
+        <v>2002</v>
+      </c>
+      <c r="B81" s="17">
+        <v>2</v>
+      </c>
+      <c r="C81" s="17">
+        <v>1</v>
+      </c>
+      <c r="D81" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" s="17">
+        <v>4055281</v>
+      </c>
+      <c r="F81" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="H76" s="17"/>
-      <c r="I76" s="18"/>
-      <c r="J76" s="18"/>
-      <c r="K76" s="18"/>
-      <c r="L76" s="18"/>
-    </row>
-    <row r="77" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A77" s="15">
-        <v>2002</v>
-      </c>
-      <c r="B77" s="16">
-        <v>2</v>
-      </c>
-      <c r="C77" s="16">
-        <v>1</v>
-      </c>
-      <c r="D77" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E77" s="16">
-        <v>4055281</v>
-      </c>
-      <c r="F77" s="16" t="s">
+      <c r="G81" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H81" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="G77" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="H77" s="17" t="s">
+      <c r="I81" s="19"/>
+      <c r="J81" s="19"/>
+      <c r="K81" s="19"/>
+      <c r="L81" s="19"/>
+    </row>
+    <row r="82" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A82" s="16">
+        <v>2003</v>
+      </c>
+      <c r="B82" s="17">
+        <v>2</v>
+      </c>
+      <c r="C82" s="17">
+        <v>1</v>
+      </c>
+      <c r="D82" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" s="17">
+        <v>4055282</v>
+      </c>
+      <c r="F82" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="I77" s="18"/>
-      <c r="J77" s="18"/>
-      <c r="K77" s="18"/>
-      <c r="L77" s="18"/>
-    </row>
-    <row r="78" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A78" s="15">
-        <v>2003</v>
-      </c>
-      <c r="B78" s="16">
-        <v>2</v>
-      </c>
-      <c r="C78" s="16">
-        <v>1</v>
-      </c>
-      <c r="D78" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E78" s="16">
-        <v>4055282</v>
-      </c>
-      <c r="F78" s="16" t="s">
+      <c r="G82" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H82" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G78" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="H78" s="17" t="s">
+      <c r="I82" s="19"/>
+      <c r="J82" s="19"/>
+      <c r="K82" s="19"/>
+      <c r="L82" s="19"/>
+    </row>
+    <row r="83" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A83" s="16">
+        <v>2004</v>
+      </c>
+      <c r="B83" s="17">
+        <v>2</v>
+      </c>
+      <c r="C83" s="17">
+        <v>1</v>
+      </c>
+      <c r="D83" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" s="17">
+        <v>4055283</v>
+      </c>
+      <c r="F83" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="I78" s="18"/>
-      <c r="J78" s="18"/>
-      <c r="K78" s="18"/>
-      <c r="L78" s="18"/>
-    </row>
-    <row r="79" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A79" s="15">
-        <v>2004</v>
-      </c>
-      <c r="B79" s="16">
-        <v>2</v>
-      </c>
-      <c r="C79" s="16">
-        <v>1</v>
-      </c>
-      <c r="D79" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E79" s="16">
-        <v>4055283</v>
-      </c>
-      <c r="F79" s="16" t="s">
+      <c r="G83" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H83" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="G79" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="H79" s="17" t="s">
+      <c r="I83" s="19"/>
+      <c r="J83" s="19"/>
+      <c r="K83" s="19"/>
+      <c r="L83" s="19"/>
+    </row>
+    <row r="84" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A84" s="16">
+        <v>2005</v>
+      </c>
+      <c r="B84" s="17">
+        <v>2</v>
+      </c>
+      <c r="C84" s="17">
+        <v>1</v>
+      </c>
+      <c r="D84" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E84" s="17">
+        <v>4055284</v>
+      </c>
+      <c r="F84" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="I79" s="18"/>
-      <c r="J79" s="18"/>
-      <c r="K79" s="18"/>
-      <c r="L79" s="18"/>
-    </row>
-    <row r="80" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A80" s="15">
-        <v>2005</v>
-      </c>
-      <c r="B80" s="16">
-        <v>2</v>
-      </c>
-      <c r="C80" s="16">
-        <v>1</v>
-      </c>
-      <c r="D80" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E80" s="16">
-        <v>4055284</v>
-      </c>
-      <c r="F80" s="16" t="s">
+      <c r="G84" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H84" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="I84" s="19"/>
+      <c r="J84" s="19"/>
+      <c r="K84" s="19"/>
+      <c r="L84" s="19"/>
+    </row>
+    <row r="85" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A85" s="16">
+        <v>2006</v>
+      </c>
+      <c r="B85" s="17">
+        <v>2</v>
+      </c>
+      <c r="C85" s="17">
+        <v>1</v>
+      </c>
+      <c r="D85" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" s="17">
+        <v>4055285</v>
+      </c>
+      <c r="F85" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="G80" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="H80" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="I80" s="18"/>
-      <c r="J80" s="18"/>
-      <c r="K80" s="18"/>
-      <c r="L80" s="18"/>
-    </row>
-    <row r="81" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="15">
-        <v>2006</v>
-      </c>
-      <c r="B81" s="16">
-        <v>2</v>
-      </c>
-      <c r="C81" s="16">
-        <v>1</v>
-      </c>
-      <c r="D81" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E81" s="16">
-        <v>4055285</v>
-      </c>
-      <c r="F81" s="16" t="s">
+      <c r="G85" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H85" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="I85" s="19"/>
+      <c r="J85" s="19"/>
+      <c r="K85" s="19"/>
+      <c r="L85" s="19"/>
+    </row>
+    <row r="86" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A86" s="16">
+        <v>2007</v>
+      </c>
+      <c r="B86" s="17">
+        <v>2</v>
+      </c>
+      <c r="C86" s="17">
+        <v>1</v>
+      </c>
+      <c r="D86" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86" s="17">
+        <v>4055286</v>
+      </c>
+      <c r="F86" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="G81" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="I81" s="18"/>
-      <c r="J81" s="18"/>
-      <c r="K81" s="18"/>
-      <c r="L81" s="18"/>
-    </row>
-    <row r="82" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="15">
-        <v>2007</v>
-      </c>
-      <c r="B82" s="16">
-        <v>2</v>
-      </c>
-      <c r="C82" s="16">
-        <v>1</v>
-      </c>
-      <c r="D82" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E82" s="16">
-        <v>4055286</v>
-      </c>
-      <c r="F82" s="16" t="s">
+      <c r="G86" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="H86" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="G82" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="H82" s="17" t="s">
+      <c r="I86" s="19"/>
+      <c r="J86" s="19"/>
+      <c r="K86" s="19"/>
+      <c r="L86" s="19"/>
+    </row>
+    <row r="87" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A87" s="16">
+        <v>2100</v>
+      </c>
+      <c r="B87" s="17">
+        <v>2</v>
+      </c>
+      <c r="C87" s="17">
+        <v>1</v>
+      </c>
+      <c r="D87" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E87" s="17"/>
+      <c r="F87" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="I82" s="18"/>
-      <c r="J82" s="18"/>
-      <c r="K82" s="18"/>
-      <c r="L82" s="18"/>
-    </row>
-    <row r="83" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A83" s="15">
-        <v>2100</v>
-      </c>
-      <c r="B83" s="16">
-        <v>2</v>
-      </c>
-      <c r="C83" s="16">
-        <v>1</v>
-      </c>
-      <c r="D83" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16" t="s">
+      <c r="G87" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="G83" s="9" t="s">
+      <c r="H87" s="18"/>
+      <c r="I87" s="19"/>
+      <c r="J87" s="19"/>
+      <c r="K87" s="19"/>
+      <c r="L87" s="19"/>
+    </row>
+    <row r="88" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A88" s="17">
+        <v>2101</v>
+      </c>
+      <c r="B88" s="17">
+        <v>2</v>
+      </c>
+      <c r="C88" s="17">
+        <v>1</v>
+      </c>
+      <c r="D88" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88" s="17">
+        <v>4055301</v>
+      </c>
+      <c r="F88" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="H83" s="17"/>
-      <c r="I83" s="18"/>
-      <c r="J83" s="18"/>
-      <c r="K83" s="18"/>
-      <c r="L83" s="18"/>
-    </row>
-    <row r="84" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A84" s="16">
-        <v>2101</v>
-      </c>
-      <c r="B84" s="16">
-        <v>2</v>
-      </c>
-      <c r="C84" s="16">
-        <v>1</v>
-      </c>
-      <c r="D84" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E84" s="16">
-        <v>4055301</v>
-      </c>
-      <c r="F84" s="16" t="s">
+      <c r="G88" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="G84" s="9" t="s">
+      <c r="H88" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="H84" s="17" t="s">
+      <c r="I88" s="12"/>
+      <c r="J88" s="12"/>
+      <c r="K88" s="12"/>
+      <c r="L88" s="12"/>
+    </row>
+    <row r="89" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A89" s="17">
+        <v>2102</v>
+      </c>
+      <c r="B89" s="17">
+        <v>1</v>
+      </c>
+      <c r="C89" s="17">
+        <v>1</v>
+      </c>
+      <c r="D89" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E89" s="17">
+        <v>4055303</v>
+      </c>
+      <c r="F89" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="I84" s="11"/>
-      <c r="J84" s="11"/>
-      <c r="K84" s="11"/>
-      <c r="L84" s="11"/>
-    </row>
-    <row r="85" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A85" s="16">
-        <v>2102</v>
-      </c>
-      <c r="B85" s="16">
-        <v>1</v>
-      </c>
-      <c r="C85" s="16">
-        <v>1</v>
-      </c>
-      <c r="D85" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E85" s="16">
-        <v>4055303</v>
-      </c>
-      <c r="F85" s="16" t="s">
+      <c r="G89" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H89" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="G85" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="H85" s="17" t="s">
+      <c r="I89" s="12"/>
+      <c r="J89" s="12"/>
+      <c r="K89" s="12"/>
+      <c r="L89" s="12"/>
+    </row>
+    <row r="90" s="11" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A90" s="25">
+        <v>2201</v>
+      </c>
+      <c r="B90" s="25">
+        <v>1</v>
+      </c>
+      <c r="C90" s="25">
+        <v>2</v>
+      </c>
+      <c r="D90" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E90" s="25">
+        <v>4055341</v>
+      </c>
+      <c r="F90" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="I85" s="11"/>
-      <c r="J85" s="11"/>
-      <c r="K85" s="11"/>
-      <c r="L85" s="11"/>
-    </row>
-    <row r="86" s="10" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A86" s="24">
-        <v>2201</v>
-      </c>
-      <c r="B86" s="24">
-        <v>1</v>
-      </c>
-      <c r="C86" s="24">
-        <v>2</v>
-      </c>
-      <c r="D86" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E86" s="24">
-        <v>4055341</v>
-      </c>
-      <c r="F86" s="24" t="s">
+      <c r="G90" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="H90" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="H86" s="17" t="s">
+      <c r="J90" s="35"/>
+      <c r="K90" s="35"/>
+      <c r="L90" s="35"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:12">
+      <c r="A91" s="25">
+        <v>2202</v>
+      </c>
+      <c r="B91" s="25">
+        <v>2</v>
+      </c>
+      <c r="C91" s="25">
+        <v>1</v>
+      </c>
+      <c r="D91" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E91" s="25">
+        <v>4055342</v>
+      </c>
+      <c r="F91" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="J86" s="29"/>
-      <c r="K86" s="29"/>
-      <c r="L86" s="29"/>
-    </row>
-    <row r="87" customHeight="1" spans="1:12">
-      <c r="A87" s="24">
-        <v>2202</v>
-      </c>
-      <c r="B87" s="24">
-        <v>2</v>
-      </c>
-      <c r="C87" s="24">
-        <v>1</v>
-      </c>
-      <c r="D87" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E87" s="24">
-        <v>4055342</v>
-      </c>
-      <c r="F87" s="24" t="s">
+      <c r="G91" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="H91" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="G87" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H87" s="17" t="s">
+    </row>
+    <row r="92" customHeight="1" spans="1:12">
+      <c r="A92" s="25">
+        <v>2203</v>
+      </c>
+      <c r="B92" s="25">
+        <v>2</v>
+      </c>
+      <c r="C92" s="25">
+        <v>1</v>
+      </c>
+      <c r="D92" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92" s="25">
+        <v>4055343</v>
+      </c>
+      <c r="F92" s="25" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="88" customHeight="1" spans="1:12">
-      <c r="A88" s="24">
-        <v>2203</v>
-      </c>
-      <c r="B88" s="24">
-        <v>2</v>
-      </c>
-      <c r="C88" s="24">
-        <v>1</v>
-      </c>
-      <c r="D88" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E88" s="24">
-        <v>4055343</v>
-      </c>
-      <c r="F88" s="24" t="s">
+      <c r="G92" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="H92" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="G88" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H88" s="17" t="s">
+    </row>
+    <row r="93" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A93" s="25">
+        <v>2204</v>
+      </c>
+      <c r="B93" s="25">
+        <v>2</v>
+      </c>
+      <c r="C93" s="25">
+        <v>1</v>
+      </c>
+      <c r="D93" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E93" s="25">
+        <v>4055344</v>
+      </c>
+      <c r="F93" s="25" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="89" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A89" s="24">
-        <v>2204</v>
-      </c>
-      <c r="B89" s="24">
-        <v>2</v>
-      </c>
-      <c r="C89" s="24">
-        <v>1</v>
-      </c>
-      <c r="D89" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E89" s="24">
-        <v>4055344</v>
-      </c>
-      <c r="F89" s="24" t="s">
+      <c r="G93" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H93" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="G89" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="H89" s="17" t="s">
+      <c r="I93" s="12"/>
+      <c r="J93" s="12"/>
+      <c r="K93" s="12"/>
+      <c r="L93" s="12"/>
+    </row>
+    <row r="94" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A94" s="25">
+        <v>2205</v>
+      </c>
+      <c r="B94" s="25">
+        <v>2</v>
+      </c>
+      <c r="C94" s="25">
+        <v>1</v>
+      </c>
+      <c r="D94" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E94" s="25">
+        <v>4055345</v>
+      </c>
+      <c r="F94" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="I89" s="11"/>
-      <c r="J89" s="11"/>
-      <c r="K89" s="11"/>
-      <c r="L89" s="11"/>
-    </row>
-    <row r="90" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A90" s="24">
-        <v>2205</v>
-      </c>
-      <c r="B90" s="24">
-        <v>2</v>
-      </c>
-      <c r="C90" s="24">
-        <v>1</v>
-      </c>
-      <c r="D90" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E90" s="24">
-        <v>4055345</v>
-      </c>
-      <c r="F90" s="24" t="s">
+      <c r="G94" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H94" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="G90" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="H90" s="17" t="s">
+      <c r="I94" s="12"/>
+      <c r="J94" s="12"/>
+      <c r="K94" s="12"/>
+      <c r="L94" s="12"/>
+    </row>
+    <row r="95" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A95" s="25">
+        <v>2206</v>
+      </c>
+      <c r="B95" s="25">
+        <v>2</v>
+      </c>
+      <c r="C95" s="25">
+        <v>1</v>
+      </c>
+      <c r="D95" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E95" s="25">
+        <v>4055346</v>
+      </c>
+      <c r="F95" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="I90" s="11"/>
-      <c r="J90" s="11"/>
-      <c r="K90" s="11"/>
-      <c r="L90" s="11"/>
-    </row>
-    <row r="91" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A91" s="24">
-        <v>2206</v>
-      </c>
-      <c r="B91" s="24">
-        <v>2</v>
-      </c>
-      <c r="C91" s="24">
-        <v>1</v>
-      </c>
-      <c r="D91" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E91" s="24">
-        <v>4055346</v>
-      </c>
-      <c r="F91" s="24" t="s">
+      <c r="G95" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H95" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="G91" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="H91" s="17" t="s">
+      <c r="I95" s="12"/>
+      <c r="J95" s="12"/>
+      <c r="K95" s="12"/>
+      <c r="L95" s="12"/>
+    </row>
+    <row r="96" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A96" s="25">
+        <v>2207</v>
+      </c>
+      <c r="B96" s="25">
+        <v>2</v>
+      </c>
+      <c r="C96" s="25">
+        <v>1</v>
+      </c>
+      <c r="D96" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E96" s="25">
+        <v>4055347</v>
+      </c>
+      <c r="F96" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="I91" s="11"/>
-      <c r="J91" s="11"/>
-      <c r="K91" s="11"/>
-      <c r="L91" s="11"/>
-    </row>
-    <row r="92" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A92" s="24">
-        <v>2207</v>
-      </c>
-      <c r="B92" s="24">
-        <v>2</v>
-      </c>
-      <c r="C92" s="24">
-        <v>1</v>
-      </c>
-      <c r="D92" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E92" s="24">
-        <v>4055347</v>
-      </c>
-      <c r="F92" s="24" t="s">
+      <c r="G96" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H96" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+    </row>
+    <row r="97" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A97" s="25">
+        <v>2208</v>
+      </c>
+      <c r="B97" s="25">
+        <v>2</v>
+      </c>
+      <c r="C97" s="25">
+        <v>1</v>
+      </c>
+      <c r="D97" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E97" s="25">
+        <v>4055348</v>
+      </c>
+      <c r="F97" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="G92" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="H92" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="I92" s="11"/>
-      <c r="J92" s="11"/>
-      <c r="K92" s="11"/>
-      <c r="L92" s="11"/>
-    </row>
-    <row r="93" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A93" s="24">
-        <v>2208</v>
-      </c>
-      <c r="B93" s="24">
-        <v>2</v>
-      </c>
-      <c r="C93" s="24">
-        <v>1</v>
-      </c>
-      <c r="D93" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E93" s="24">
-        <v>4055348</v>
-      </c>
-      <c r="F93" s="24" t="s">
+      <c r="G97" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H97" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="I97" s="12"/>
+      <c r="J97" s="12"/>
+      <c r="K97" s="12"/>
+      <c r="L97" s="12"/>
+    </row>
+    <row r="98" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A98" s="25">
+        <v>2209</v>
+      </c>
+      <c r="B98" s="25">
+        <v>2</v>
+      </c>
+      <c r="C98" s="25">
+        <v>1</v>
+      </c>
+      <c r="D98" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="G93" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="H93" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="I93" s="11"/>
-      <c r="J93" s="11"/>
-      <c r="K93" s="11"/>
-      <c r="L93" s="11"/>
-    </row>
-    <row r="94" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A94" s="24">
-        <v>2209</v>
-      </c>
-      <c r="B94" s="24">
-        <v>2</v>
-      </c>
-      <c r="C94" s="24">
-        <v>1</v>
-      </c>
-      <c r="D94" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24" t="s">
+      <c r="G98" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H98" s="18"/>
+      <c r="I98" s="12"/>
+      <c r="J98" s="12"/>
+      <c r="K98" s="12"/>
+      <c r="L98" s="12"/>
+    </row>
+    <row r="99" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A99" s="25">
+        <v>2210</v>
+      </c>
+      <c r="B99" s="25">
+        <v>2</v>
+      </c>
+      <c r="C99" s="25">
+        <v>1</v>
+      </c>
+      <c r="D99" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E99" s="25">
+        <v>4055350</v>
+      </c>
+      <c r="F99" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="G94" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="H94" s="17"/>
-      <c r="I94" s="11"/>
-      <c r="J94" s="11"/>
-      <c r="K94" s="11"/>
-      <c r="L94" s="11"/>
-    </row>
-    <row r="95" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A95" s="24">
-        <v>2210</v>
-      </c>
-      <c r="B95" s="24">
-        <v>2</v>
-      </c>
-      <c r="C95" s="24">
-        <v>1</v>
-      </c>
-      <c r="D95" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E95" s="24">
-        <v>4055350</v>
-      </c>
-      <c r="F95" s="24" t="s">
+      <c r="G99" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H99" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="J99" s="12"/>
+      <c r="K99" s="12"/>
+      <c r="L99" s="12"/>
+    </row>
+    <row r="100" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A100" s="25">
+        <v>2211</v>
+      </c>
+      <c r="B100" s="25">
+        <v>2</v>
+      </c>
+      <c r="C100" s="25">
+        <v>1</v>
+      </c>
+      <c r="D100" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E100" s="25">
+        <v>4055356</v>
+      </c>
+      <c r="F100" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="G95" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="H95" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="J95" s="11"/>
-      <c r="K95" s="11"/>
-      <c r="L95" s="11"/>
-    </row>
-    <row r="96" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A96" s="24">
-        <v>2211</v>
-      </c>
-      <c r="B96" s="24">
-        <v>2</v>
-      </c>
-      <c r="C96" s="24">
-        <v>1</v>
-      </c>
-      <c r="D96" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E96" s="24">
-        <v>4055356</v>
-      </c>
-      <c r="F96" s="24" t="s">
+      <c r="G100" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H100" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="G96" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="H96" s="17" t="s">
+      <c r="I100" s="9"/>
+      <c r="J100" s="12"/>
+      <c r="K100" s="12"/>
+      <c r="L100" s="12"/>
+    </row>
+    <row r="101" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A101" s="25">
+        <v>2212</v>
+      </c>
+      <c r="B101" s="25">
+        <v>2</v>
+      </c>
+      <c r="C101" s="25">
+        <v>1</v>
+      </c>
+      <c r="D101" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E101" s="25">
+        <v>4055351</v>
+      </c>
+      <c r="F101" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="I96" s="8"/>
-      <c r="J96" s="11"/>
-      <c r="K96" s="11"/>
-      <c r="L96" s="11"/>
-    </row>
-    <row r="97" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A97" s="24">
-        <v>2212</v>
-      </c>
-      <c r="B97" s="24">
-        <v>2</v>
-      </c>
-      <c r="C97" s="24">
-        <v>1</v>
-      </c>
-      <c r="D97" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E97" s="24">
-        <v>4055351</v>
-      </c>
-      <c r="F97" s="24" t="s">
+      <c r="G101" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H101" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="G97" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="H97" s="17" t="s">
+      <c r="I101" s="12"/>
+      <c r="J101" s="12"/>
+      <c r="K101" s="12"/>
+      <c r="L101" s="12"/>
+    </row>
+    <row r="102" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A102" s="25">
+        <v>2213</v>
+      </c>
+      <c r="B102" s="25">
+        <v>2</v>
+      </c>
+      <c r="C102" s="25">
+        <v>1</v>
+      </c>
+      <c r="D102" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102" s="25">
+        <v>4055352</v>
+      </c>
+      <c r="F102" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="I97" s="11"/>
-      <c r="J97" s="11"/>
-      <c r="K97" s="11"/>
-      <c r="L97" s="11"/>
-    </row>
-    <row r="98" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A98" s="24">
-        <v>2213</v>
-      </c>
-      <c r="B98" s="24">
-        <v>2</v>
-      </c>
-      <c r="C98" s="24">
-        <v>1</v>
-      </c>
-      <c r="D98" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E98" s="24">
-        <v>4055352</v>
-      </c>
-      <c r="F98" s="24" t="s">
+      <c r="G102" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H102" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="G98" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="H98" s="17" t="s">
+      <c r="J102" s="12"/>
+      <c r="K102" s="12"/>
+      <c r="L102" s="12"/>
+    </row>
+    <row r="103" s="10" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A103" s="25">
+        <v>2214</v>
+      </c>
+      <c r="B103" s="25">
+        <v>2</v>
+      </c>
+      <c r="C103" s="25">
+        <v>1</v>
+      </c>
+      <c r="D103" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E103" s="25"/>
+      <c r="F103" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="J98" s="11"/>
-      <c r="K98" s="11"/>
-      <c r="L98" s="11"/>
-    </row>
-    <row r="99" s="9" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A99" s="24">
-        <v>2214</v>
-      </c>
-      <c r="B99" s="24">
-        <v>2</v>
-      </c>
-      <c r="C99" s="24">
-        <v>1</v>
-      </c>
-      <c r="D99" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24" t="s">
+      <c r="G103" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H103" s="18"/>
+      <c r="I103" s="12"/>
+      <c r="J103" s="12"/>
+      <c r="K103" s="12"/>
+      <c r="L103" s="12"/>
+    </row>
+    <row r="104" customHeight="1" spans="1:12">
+      <c r="A104" s="25">
+        <v>2215</v>
+      </c>
+      <c r="B104" s="25">
+        <v>2</v>
+      </c>
+      <c r="C104" s="25">
+        <v>1</v>
+      </c>
+      <c r="D104" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E104" s="25"/>
+      <c r="F104" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="G99" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="H99" s="17"/>
-      <c r="I99" s="11"/>
-      <c r="J99" s="11"/>
-      <c r="K99" s="11"/>
-      <c r="L99" s="11"/>
-    </row>
-    <row r="100" customHeight="1" spans="1:12">
-      <c r="A100" s="24">
-        <v>2215</v>
-      </c>
-      <c r="B100" s="24">
-        <v>2</v>
-      </c>
-      <c r="C100" s="24">
-        <v>1</v>
-      </c>
-      <c r="D100" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E100" s="24"/>
-      <c r="F100" s="24" t="s">
+      <c r="G104" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="H104" s="18"/>
+    </row>
+    <row r="105" customHeight="1" spans="1:12">
+      <c r="A105" s="25">
+        <v>2216</v>
+      </c>
+      <c r="B105" s="25">
+        <v>2</v>
+      </c>
+      <c r="C105" s="25">
+        <v>1</v>
+      </c>
+      <c r="D105" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E105" s="25">
+        <v>4055355</v>
+      </c>
+      <c r="F105" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="G100" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H100" s="17"/>
-    </row>
-    <row r="101" customHeight="1" spans="1:12">
-      <c r="A101" s="24">
-        <v>2216</v>
-      </c>
-      <c r="B101" s="24">
-        <v>2</v>
-      </c>
-      <c r="C101" s="24">
-        <v>1</v>
-      </c>
-      <c r="D101" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E101" s="24">
-        <v>4055355</v>
-      </c>
-      <c r="F101" s="24" t="s">
+      <c r="G105" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="H105" s="18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="1:12">
+      <c r="A106" s="25">
+        <v>2217</v>
+      </c>
+      <c r="B106" s="25">
+        <v>2</v>
+      </c>
+      <c r="C106" s="25">
+        <v>1</v>
+      </c>
+      <c r="D106" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E106" s="25">
+        <v>4055357</v>
+      </c>
+      <c r="F106" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="G101" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H101" s="17" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" spans="1:12">
-      <c r="A102" s="24">
-        <v>2217</v>
-      </c>
-      <c r="B102" s="24">
-        <v>2</v>
-      </c>
-      <c r="C102" s="24">
-        <v>1</v>
-      </c>
-      <c r="D102" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E102" s="24">
-        <v>4055357</v>
-      </c>
-      <c r="F102" s="24" t="s">
+      <c r="G106" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="H106" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="G102" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H102" s="17" t="s">
+    </row>
+    <row r="107" customHeight="1" spans="1:12">
+      <c r="A107" s="17">
+        <v>2301</v>
+      </c>
+      <c r="B107" s="17"/>
+      <c r="C107" s="17">
+        <v>2</v>
+      </c>
+      <c r="D107" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E107" s="17"/>
+      <c r="F107" s="17" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="103" customHeight="1" spans="1:12">
-      <c r="A103" s="16">
-        <v>2301</v>
-      </c>
-      <c r="B103" s="16"/>
-      <c r="C103" s="16">
-        <v>2</v>
-      </c>
-      <c r="D103" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E103" s="16"/>
-      <c r="F103" s="16" t="s">
+      <c r="G107" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G103" s="1" t="s">
+      <c r="H107" s="18"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:12">
+      <c r="A108" s="17">
+        <v>2302</v>
+      </c>
+      <c r="B108" s="17">
+        <v>1</v>
+      </c>
+      <c r="C108" s="17">
+        <v>1</v>
+      </c>
+      <c r="D108" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E108" s="17"/>
+      <c r="F108" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="H103" s="17"/>
-    </row>
-    <row r="104" customHeight="1" spans="1:12">
-      <c r="A104" s="16">
-        <v>2302</v>
-      </c>
-      <c r="B104" s="16">
-        <v>1</v>
-      </c>
-      <c r="C104" s="16">
-        <v>1</v>
-      </c>
-      <c r="D104" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E104" s="16"/>
-      <c r="F104" s="16" t="s">
+      <c r="G108" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H108" s="18"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:12">
+      <c r="A109" s="17">
+        <v>2303</v>
+      </c>
+      <c r="B109" s="17">
+        <v>1</v>
+      </c>
+      <c r="C109" s="17">
+        <v>1</v>
+      </c>
+      <c r="D109" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E109" s="17">
+        <v>4055371</v>
+      </c>
+      <c r="F109" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="G104" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H104" s="17"/>
-    </row>
-    <row r="105" customHeight="1" spans="1:12">
-      <c r="A105" s="16">
-        <v>2303</v>
-      </c>
-      <c r="B105" s="16">
-        <v>1</v>
-      </c>
-      <c r="C105" s="16">
-        <v>1</v>
-      </c>
-      <c r="D105" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E105" s="16">
-        <v>4055371</v>
-      </c>
-      <c r="F105" s="16" t="s">
+      <c r="G109" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H109" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="G105" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H105" s="17" t="s">
+    </row>
+    <row r="110" customHeight="1" spans="1:12">
+      <c r="A110" s="1">
+        <v>2401</v>
+      </c>
+      <c r="B110" s="1">
+        <v>2</v>
+      </c>
+      <c r="C110" s="1">
+        <v>1</v>
+      </c>
+      <c r="D110" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>167</v>
+      </c>
+      <c r="H110" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="1:12">
+      <c r="A111" s="1">
+        <v>2402</v>
+      </c>
+      <c r="B111" s="1">
+        <v>2</v>
+      </c>
+      <c r="C111" s="1">
+        <v>1</v>
+      </c>
+      <c r="D111" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H111" s="12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="1:12">
+      <c r="A112" s="1">
+        <v>2403</v>
+      </c>
+      <c r="B112" s="1">
+        <v>2</v>
+      </c>
+      <c r="C112" s="1">
+        <v>1</v>
+      </c>
+      <c r="D112" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H112" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -4895,14 +5075,14 @@
         <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -4911,7 +5091,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -4921,14 +5101,14 @@
         <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4936,14 +5116,14 @@
         <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4951,14 +5131,14 @@
         <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4966,14 +5146,14 @@
         <v>2205</v>
       </c>
       <c r="J9" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
         <v>2205_</v>
       </c>
       <c r="M9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4981,14 +5161,14 @@
         <v>2206</v>
       </c>
       <c r="J10" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>2206_</v>
       </c>
       <c r="M10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4996,14 +5176,14 @@
         <v>2207</v>
       </c>
       <c r="J11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>2207_</v>
       </c>
       <c r="M11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -5011,14 +5191,14 @@
         <v>2208</v>
       </c>
       <c r="J12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>2208_</v>
       </c>
       <c r="M12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -5026,32 +5206,32 @@
         <v>2209</v>
       </c>
       <c r="J13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>2209_</v>
       </c>
       <c r="M13" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I14">
         <v>2210</v>
       </c>
       <c r="J14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>2210_</v>
       </c>
       <c r="M14" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -5059,14 +5239,14 @@
         <v>2211</v>
       </c>
       <c r="J15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>2211_</v>
       </c>
       <c r="M15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -5074,14 +5254,14 @@
         <v>2212</v>
       </c>
       <c r="J16" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>2212_</v>
       </c>
       <c r="M16" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -5089,14 +5269,14 @@
         <v>2213</v>
       </c>
       <c r="J17" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>2213_</v>
       </c>
       <c r="M17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -5104,29 +5284,29 @@
         <v>2214</v>
       </c>
       <c r="J18" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>2214_</v>
       </c>
       <c r="M18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="194">
   <si>
     <t>序号</t>
   </si>
@@ -684,16 +684,25 @@
     <t>在这里可以&lt;color=#00bfff&gt;快速获得金币、娱乐城经验&lt;/color&gt;等资源</t>
   </si>
   <si>
+    <t>2401.mp3</t>
+  </si>
+  <si>
     <t>引导主线离开游戏</t>
   </si>
   <si>
-    <t>当前主线任务已完成，请退出游戏继续主线任务 .</t>
-  </si>
-  <si>
-    <t>点击退出游戏进入经营大厅</t>
-  </si>
-  <si>
-    <t>点击主线界面继续任务</t>
+    <t>点击这里继续任务</t>
+  </si>
+  <si>
+    <t>2402.mp3</t>
+  </si>
+  <si>
+    <t>当前主线任务已完成，任务内容已更新 .</t>
+  </si>
+  <si>
+    <t>2403.mp3</t>
+  </si>
+  <si>
+    <t>让我们返回经营大厅</t>
   </si>
   <si>
     <t>_</t>
@@ -982,12 +991,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4970,11 +4979,17 @@
       <c r="D110" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="E110" s="1">
+        <v>4055372</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>167</v>
+      </c>
       <c r="G110" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:12">
@@ -4990,11 +5005,17 @@
       <c r="D111" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="E111" s="1">
+        <v>4055373</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="G111" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:12">
@@ -5010,11 +5031,17 @@
       <c r="D112" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="E112" s="1">
+        <v>4055374</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>172</v>
+      </c>
       <c r="G112" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H112" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -5075,14 +5102,14 @@
         <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -5091,7 +5118,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -5101,14 +5128,14 @@
         <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -5116,14 +5143,14 @@
         <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -5131,14 +5158,14 @@
         <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -5146,14 +5173,14 @@
         <v>2205</v>
       </c>
       <c r="J9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
         <v>2205_</v>
       </c>
       <c r="M9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -5161,14 +5188,14 @@
         <v>2206</v>
       </c>
       <c r="J10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>2206_</v>
       </c>
       <c r="M10" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -5176,14 +5203,14 @@
         <v>2207</v>
       </c>
       <c r="J11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>2207_</v>
       </c>
       <c r="M11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -5191,14 +5218,14 @@
         <v>2208</v>
       </c>
       <c r="J12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>2208_</v>
       </c>
       <c r="M12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -5206,32 +5233,32 @@
         <v>2209</v>
       </c>
       <c r="J13" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>2209_</v>
       </c>
       <c r="M13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I14">
         <v>2210</v>
       </c>
       <c r="J14" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>2210_</v>
       </c>
       <c r="M14" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -5239,14 +5266,14 @@
         <v>2211</v>
       </c>
       <c r="J15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>2211_</v>
       </c>
       <c r="M15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -5254,14 +5281,14 @@
         <v>2212</v>
       </c>
       <c r="J16" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>2212_</v>
       </c>
       <c r="M16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -5269,14 +5296,14 @@
         <v>2213</v>
       </c>
       <c r="J17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>2213_</v>
       </c>
       <c r="M17" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -5284,29 +5311,29 @@
         <v>2214</v>
       </c>
       <c r="J18" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>2214_</v>
       </c>
       <c r="M18" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="193">
   <si>
     <t>序号</t>
   </si>
@@ -325,9 +325,6 @@
   </si>
   <si>
     <t>点击&lt;color=#00bfff&gt;旋转&lt;/color&gt;按钮，开启旅程！</t>
-  </si>
-  <si>
-    <t>1303.mp3</t>
   </si>
   <si>
     <t>1304.mp3</t>
@@ -1489,12 +1486,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1546,6 +1543,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1560,9 +1560,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2627,7 +2624,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="25" t="b">
         <v>0</v>
@@ -2649,33 +2646,29 @@
       <c r="K23" s="19"/>
       <c r="L23" s="19"/>
     </row>
-    <row r="24" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A24" s="20">
+    <row r="24" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A24" s="24">
         <v>1303</v>
       </c>
-      <c r="B24" s="21">
-        <v>2</v>
-      </c>
-      <c r="C24" s="21">
-        <v>1</v>
-      </c>
-      <c r="D24" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" s="21">
-        <v>4055143</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G24" s="23" t="s">
+      <c r="B24" s="25">
+        <v>2</v>
+      </c>
+      <c r="C24" s="25">
+        <v>2</v>
+      </c>
+      <c r="D24" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
     </row>
     <row r="25" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A25" s="20">
@@ -2690,7 +2683,7 @@
       </c>
       <c r="E25" s="21"/>
       <c r="F25" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G25" s="23" t="s">
         <v>45</v>
@@ -2716,7 +2709,7 @@
         <v>4055144</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G26" s="23" t="s">
         <v>45</v>
@@ -2727,117 +2720,117 @@
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
     </row>
-    <row r="27" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="27">
+    <row r="27" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A27" s="28">
         <v>1311</v>
       </c>
-      <c r="B27" s="28">
-        <v>2</v>
-      </c>
-      <c r="C27" s="28">
-        <v>1</v>
-      </c>
-      <c r="D27" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="28">
+      <c r="B27" s="29">
+        <v>2</v>
+      </c>
+      <c r="C27" s="29">
+        <v>1</v>
+      </c>
+      <c r="D27" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="29">
         <v>4055145</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+    </row>
+    <row r="28" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A28" s="28">
+        <v>1312</v>
+      </c>
+      <c r="B28" s="29">
+        <v>2</v>
+      </c>
+      <c r="C28" s="29">
+        <v>1</v>
+      </c>
+      <c r="D28" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="29">
+        <v>4055146</v>
+      </c>
+      <c r="F28" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="27" t="s">
+      <c r="G28" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-    </row>
-    <row r="28" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="27">
-        <v>1312</v>
-      </c>
-      <c r="B28" s="28">
-        <v>2</v>
-      </c>
-      <c r="C28" s="28">
-        <v>1</v>
-      </c>
-      <c r="D28" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="28">
-        <v>4055146</v>
-      </c>
-      <c r="F28" s="28" t="s">
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+    </row>
+    <row r="29" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A29" s="28">
+        <v>1313</v>
+      </c>
+      <c r="B29" s="29">
+        <v>2</v>
+      </c>
+      <c r="C29" s="29">
+        <v>1</v>
+      </c>
+      <c r="D29" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="29">
+        <v>4055147</v>
+      </c>
+      <c r="F29" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="27" t="s">
+      <c r="G29" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-    </row>
-    <row r="29" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="27">
-        <v>1313</v>
-      </c>
-      <c r="B29" s="28">
-        <v>2</v>
-      </c>
-      <c r="C29" s="28">
-        <v>1</v>
-      </c>
-      <c r="D29" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="28">
-        <v>4055147</v>
-      </c>
-      <c r="F29" s="28" t="s">
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+    </row>
+    <row r="30" s="9" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A30" s="28">
+        <v>1314</v>
+      </c>
+      <c r="B30" s="29">
+        <v>2</v>
+      </c>
+      <c r="C30" s="29">
+        <v>1</v>
+      </c>
+      <c r="D30" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="29">
+        <v>4055148</v>
+      </c>
+      <c r="F30" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="27" t="s">
+      <c r="G30" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-    </row>
-    <row r="30" s="8" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="27">
-        <v>1314</v>
-      </c>
-      <c r="B30" s="28">
-        <v>2</v>
-      </c>
-      <c r="C30" s="28">
-        <v>1</v>
-      </c>
-      <c r="D30" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="28">
-        <v>4055148</v>
-      </c>
-      <c r="F30" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
     </row>
     <row r="31" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A31" s="20">
@@ -2856,10 +2849,10 @@
         <v>4055161</v>
       </c>
       <c r="F31" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="23" t="s">
         <v>55</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>56</v>
       </c>
       <c r="H31" s="22"/>
       <c r="I31" s="22"/>
@@ -2884,10 +2877,10 @@
         <v>4055162</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H32" s="22"/>
       <c r="I32" s="22"/>
@@ -2912,10 +2905,10 @@
         <v>4055163</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G33" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H33" s="22"/>
       <c r="I33" s="22"/>
@@ -2940,10 +2933,10 @@
         <v>4055164</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G34" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H34" s="22"/>
       <c r="I34" s="22"/>
@@ -2964,10 +2957,10 @@
       </c>
       <c r="E35" s="21"/>
       <c r="F35" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G35" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H35" s="22"/>
       <c r="I35" s="22"/>
@@ -2992,10 +2985,10 @@
         <v>4055165</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G36" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H36" s="22"/>
       <c r="I36" s="22"/>
@@ -3020,10 +3013,10 @@
         <v>4055181</v>
       </c>
       <c r="F37" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="23" t="s">
         <v>62</v>
-      </c>
-      <c r="G37" s="23" t="s">
-        <v>63</v>
       </c>
       <c r="H37" s="22"/>
       <c r="I37" s="22"/>
@@ -3048,10 +3041,10 @@
         <v>4055182</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G38" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H38" s="22"/>
       <c r="I38" s="22"/>
@@ -3072,10 +3065,10 @@
       </c>
       <c r="E39" s="21"/>
       <c r="F39" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G39" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H39" s="22"/>
       <c r="I39" s="22"/>
@@ -3096,10 +3089,10 @@
       </c>
       <c r="E40" s="21"/>
       <c r="F40" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G40" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H40" s="22"/>
       <c r="I40" s="22"/>
@@ -3108,20 +3101,20 @@
       <c r="L40" s="22"/>
     </row>
     <row r="41" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="30">
+      <c r="A41" s="31">
         <v>1601</v>
       </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31">
-        <v>1</v>
-      </c>
-      <c r="D41" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32">
+        <v>1</v>
+      </c>
+      <c r="D41" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
       <c r="G41" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H41" s="22"/>
       <c r="I41" s="22"/>
@@ -3129,7 +3122,7 @@
       <c r="K41" s="22"/>
       <c r="L41" s="22"/>
     </row>
-    <row r="42" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="42" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A42" s="16">
         <v>1602</v>
       </c>
@@ -3142,8 +3135,8 @@
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
-      <c r="G42" s="32" t="s">
-        <v>67</v>
+      <c r="G42" s="27" t="s">
+        <v>66</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
@@ -3151,7 +3144,7 @@
       <c r="K42" s="12"/>
       <c r="L42" s="12"/>
     </row>
-    <row r="43" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="43" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A43" s="16">
         <v>1603</v>
       </c>
@@ -3166,20 +3159,20 @@
         <v>4055203</v>
       </c>
       <c r="F43" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G43" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" s="18" t="s">
         <v>68</v>
-      </c>
-      <c r="G43" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="H43" s="18" t="s">
-        <v>69</v>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12"/>
       <c r="K43" s="12"/>
       <c r="L43" s="12"/>
     </row>
-    <row r="44" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="44" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A44" s="16">
         <v>1604</v>
       </c>
@@ -3192,8 +3185,8 @@
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
-      <c r="G44" s="32" t="s">
-        <v>67</v>
+      <c r="G44" s="27" t="s">
+        <v>66</v>
       </c>
       <c r="H44" s="18"/>
       <c r="I44" s="12"/>
@@ -3201,7 +3194,7 @@
       <c r="K44" s="12"/>
       <c r="L44" s="12"/>
     </row>
-    <row r="45" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="45" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A45" s="16">
         <v>1605</v>
       </c>
@@ -3218,20 +3211,20 @@
         <v>4055204</v>
       </c>
       <c r="F45" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" s="18" t="s">
         <v>70</v>
-      </c>
-      <c r="G45" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="H45" s="18" t="s">
-        <v>71</v>
       </c>
       <c r="I45" s="12"/>
       <c r="J45" s="12"/>
       <c r="K45" s="12"/>
       <c r="L45" s="12"/>
     </row>
-    <row r="46" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="46" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A46" s="16">
         <v>1606</v>
       </c>
@@ -3244,8 +3237,8 @@
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="17"/>
-      <c r="G46" s="32" t="s">
-        <v>67</v>
+      <c r="G46" s="27" t="s">
+        <v>66</v>
       </c>
       <c r="H46" s="18"/>
       <c r="I46" s="12"/>
@@ -3253,7 +3246,7 @@
       <c r="K46" s="12"/>
       <c r="L46" s="12"/>
     </row>
-    <row r="47" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="47" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A47" s="16">
         <v>1607</v>
       </c>
@@ -3268,8 +3261,8 @@
       </c>
       <c r="E47" s="17"/>
       <c r="F47" s="17"/>
-      <c r="G47" s="32" t="s">
-        <v>67</v>
+      <c r="G47" s="27" t="s">
+        <v>66</v>
       </c>
       <c r="H47" s="18"/>
       <c r="I47" s="12"/>
@@ -3277,7 +3270,7 @@
       <c r="K47" s="12"/>
       <c r="L47" s="12"/>
     </row>
-    <row r="48" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="48" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A48" s="16">
         <v>1608</v>
       </c>
@@ -3292,20 +3285,20 @@
         <v>4055205</v>
       </c>
       <c r="F48" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G48" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="H48" s="18" t="s">
         <v>72</v>
-      </c>
-      <c r="G48" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="H48" s="18" t="s">
-        <v>73</v>
       </c>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
       <c r="K48" s="12"/>
       <c r="L48" s="12"/>
     </row>
-    <row r="49" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="49" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A49" s="16">
         <v>1609</v>
       </c>
@@ -3320,20 +3313,20 @@
         <v>4055206</v>
       </c>
       <c r="F49" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G49" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="H49" s="18" t="s">
         <v>74</v>
-      </c>
-      <c r="G49" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="H49" s="18" t="s">
-        <v>75</v>
       </c>
       <c r="I49" s="12"/>
       <c r="J49" s="12"/>
       <c r="K49" s="12"/>
       <c r="L49" s="12"/>
     </row>
-    <row r="50" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="50" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A50" s="16">
         <v>1610</v>
       </c>
@@ -3350,20 +3343,20 @@
         <v>4055207</v>
       </c>
       <c r="F50" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G50" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="H50" s="18" t="s">
         <v>76</v>
-      </c>
-      <c r="G50" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="H50" s="18" t="s">
-        <v>77</v>
       </c>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
       <c r="K50" s="12"/>
       <c r="L50" s="12"/>
     </row>
-    <row r="51" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="51" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A51" s="16">
         <v>1611</v>
       </c>
@@ -3380,13 +3373,13 @@
         <v>4055208</v>
       </c>
       <c r="F51" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G51" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="H51" s="18" t="s">
         <v>78</v>
-      </c>
-      <c r="G51" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="H51" s="18" t="s">
-        <v>79</v>
       </c>
       <c r="I51" s="12"/>
       <c r="J51" s="12"/>
@@ -3410,10 +3403,10 @@
         <v>4055209</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H52" s="22"/>
       <c r="I52" s="22"/>
@@ -3434,10 +3427,10 @@
       </c>
       <c r="E53" s="21"/>
       <c r="F53" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G53" s="23" t="s">
         <v>81</v>
-      </c>
-      <c r="G53" s="23" t="s">
-        <v>82</v>
       </c>
       <c r="H53" s="22"/>
       <c r="I53" s="22"/>
@@ -3458,10 +3451,10 @@
       </c>
       <c r="E54" s="33"/>
       <c r="F54" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G54" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H54" s="22"/>
       <c r="I54" s="22"/>
@@ -3486,10 +3479,10 @@
         <v>4055222</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G55" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H55" s="22"/>
       <c r="I55" s="22"/>
@@ -3514,10 +3507,10 @@
         <v>4055223</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G56" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H56" s="22"/>
       <c r="I56" s="22"/>
@@ -3542,10 +3535,10 @@
         <v>4055224</v>
       </c>
       <c r="F57" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H57" s="22"/>
       <c r="I57" s="22"/>
@@ -3566,10 +3559,10 @@
       </c>
       <c r="E58" s="21"/>
       <c r="F58" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G58" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H58" s="22"/>
       <c r="I58" s="22"/>
@@ -3594,10 +3587,10 @@
         <v>4055225</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H59" s="22"/>
       <c r="I59" s="22"/>
@@ -3622,10 +3615,10 @@
         <v>4055226</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G60" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H60" s="22"/>
       <c r="I60" s="22"/>
@@ -3646,10 +3639,10 @@
       </c>
       <c r="E61" s="21"/>
       <c r="F61" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H61" s="22"/>
       <c r="I61" s="22"/>
@@ -3670,10 +3663,10 @@
       </c>
       <c r="E62" s="21"/>
       <c r="F62" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G62" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H62" s="22"/>
       <c r="I62" s="22"/>
@@ -3698,10 +3691,10 @@
         <v>4055227</v>
       </c>
       <c r="F63" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G63" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H63" s="22"/>
       <c r="I63" s="22"/>
@@ -3726,10 +3719,10 @@
         <v>4055228</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G64" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H64" s="22"/>
       <c r="I64" s="22"/>
@@ -3750,10 +3743,10 @@
       </c>
       <c r="E65" s="21"/>
       <c r="F65" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="G65" s="23" t="s">
         <v>94</v>
-      </c>
-      <c r="G65" s="23" t="s">
-        <v>95</v>
       </c>
       <c r="H65" s="22"/>
       <c r="I65" s="22"/>
@@ -3774,10 +3767,10 @@
       </c>
       <c r="E66" s="21"/>
       <c r="F66" s="21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G66" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H66" s="22"/>
       <c r="I66" s="22"/>
@@ -3802,10 +3795,10 @@
         <v>4055243</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G67" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H67" s="22"/>
       <c r="I67" s="22"/>
@@ -3830,10 +3823,10 @@
         <v>4055244</v>
       </c>
       <c r="F68" s="21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G68" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H68" s="22"/>
       <c r="I68" s="22"/>
@@ -3858,10 +3851,10 @@
         <v>4055245</v>
       </c>
       <c r="F69" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G69" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H69" s="22"/>
       <c r="I69" s="22"/>
@@ -3886,10 +3879,10 @@
         <v>4055246</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G70" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H70" s="22"/>
       <c r="I70" s="22"/>
@@ -3914,10 +3907,10 @@
         <v>4055247</v>
       </c>
       <c r="F71" s="21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G71" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H71" s="22"/>
       <c r="I71" s="22"/>
@@ -3938,10 +3931,10 @@
       </c>
       <c r="E72" s="17"/>
       <c r="F72" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G72" s="26" t="s">
         <v>102</v>
-      </c>
-      <c r="G72" s="26" t="s">
-        <v>103</v>
       </c>
       <c r="H72" s="18"/>
       <c r="I72" s="19"/>
@@ -3966,13 +3959,13 @@
         <v>4055263</v>
       </c>
       <c r="F73" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G73" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="H73" s="18" t="s">
         <v>104</v>
-      </c>
-      <c r="G73" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="H73" s="18" t="s">
-        <v>105</v>
       </c>
       <c r="I73" s="19"/>
       <c r="J73" s="19"/>
@@ -3990,10 +3983,10 @@
       </c>
       <c r="E74" s="34"/>
       <c r="F74" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G74" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H74" s="18"/>
       <c r="I74" s="19"/>
@@ -4014,10 +4007,10 @@
       </c>
       <c r="E75" s="17"/>
       <c r="F75" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G75" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H75" s="18"/>
       <c r="I75" s="19"/>
@@ -4042,20 +4035,20 @@
         <v>4055264</v>
       </c>
       <c r="F76" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G76" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="H76" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="G76" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="H76" s="18" t="s">
-        <v>109</v>
       </c>
       <c r="I76" s="19"/>
       <c r="J76" s="19"/>
       <c r="K76" s="19"/>
       <c r="L76" s="19"/>
     </row>
-    <row r="77" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="77" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A77" s="24">
         <v>1981</v>
       </c>
@@ -4068,10 +4061,10 @@
       </c>
       <c r="E77" s="25"/>
       <c r="F77" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="G77" s="27" t="s">
         <v>110</v>
-      </c>
-      <c r="G77" s="32" t="s">
-        <v>111</v>
       </c>
       <c r="H77" s="18"/>
       <c r="I77" s="12"/>
@@ -4079,7 +4072,7 @@
       <c r="K77" s="12"/>
       <c r="L77" s="12"/>
     </row>
-    <row r="78" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="78" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A78" s="24">
         <v>1982</v>
       </c>
@@ -4092,10 +4085,10 @@
       </c>
       <c r="E78" s="25"/>
       <c r="F78" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="G78" s="32" t="s">
         <v>111</v>
+      </c>
+      <c r="G78" s="27" t="s">
+        <v>110</v>
       </c>
       <c r="H78" s="18"/>
       <c r="I78" s="12"/>
@@ -4103,7 +4096,7 @@
       <c r="K78" s="12"/>
       <c r="L78" s="12"/>
     </row>
-    <row r="79" s="9" customFormat="1" customHeight="1" spans="1:12">
+    <row r="79" s="8" customFormat="1" customHeight="1" spans="1:12">
       <c r="A79" s="24">
         <v>1983</v>
       </c>
@@ -4120,13 +4113,13 @@
         <v>4055321</v>
       </c>
       <c r="F79" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="G79" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="H79" s="18" t="s">
         <v>113</v>
-      </c>
-      <c r="G79" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="H79" s="18" t="s">
-        <v>114</v>
       </c>
       <c r="I79" s="12"/>
       <c r="J79" s="12"/>
@@ -4146,10 +4139,10 @@
       </c>
       <c r="E80" s="17"/>
       <c r="F80" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="G80" s="26" t="s">
         <v>115</v>
-      </c>
-      <c r="G80" s="26" t="s">
-        <v>116</v>
       </c>
       <c r="H80" s="18"/>
       <c r="I80" s="19"/>
@@ -4174,13 +4167,13 @@
         <v>4055281</v>
       </c>
       <c r="F81" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="G81" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="H81" s="18" t="s">
         <v>117</v>
-      </c>
-      <c r="G81" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="H81" s="18" t="s">
-        <v>118</v>
       </c>
       <c r="I81" s="19"/>
       <c r="J81" s="19"/>
@@ -4204,13 +4197,13 @@
         <v>4055282</v>
       </c>
       <c r="F82" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="G82" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="H82" s="18" t="s">
         <v>119</v>
-      </c>
-      <c r="G82" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="H82" s="18" t="s">
-        <v>120</v>
       </c>
       <c r="I82" s="19"/>
       <c r="J82" s="19"/>
@@ -4234,13 +4227,13 @@
         <v>4055283</v>
       </c>
       <c r="F83" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="G83" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="H83" s="18" t="s">
         <v>121</v>
-      </c>
-      <c r="G83" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="H83" s="18" t="s">
-        <v>122</v>
       </c>
       <c r="I83" s="19"/>
       <c r="J83" s="19"/>
@@ -4264,13 +4257,13 @@
         <v>4055284</v>
       </c>
       <c r="F84" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G84" s="26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I84" s="19"/>
       <c r="J84" s="19"/>
@@ -4294,13 +4287,13 @@
         <v>4055285</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G85" s="26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I85" s="19"/>
       <c r="J85" s="19"/>
@@ -4324,13 +4317,13 @@
         <v>4055286</v>
       </c>
       <c r="F86" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="G86" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="H86" s="18" t="s">
         <v>125</v>
-      </c>
-      <c r="G86" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="H86" s="18" t="s">
-        <v>126</v>
       </c>
       <c r="I86" s="19"/>
       <c r="J86" s="19"/>
@@ -4352,10 +4345,10 @@
       </c>
       <c r="E87" s="17"/>
       <c r="F87" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G87" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="H87" s="18"/>
       <c r="I87" s="19"/>
@@ -4380,13 +4373,13 @@
         <v>4055301</v>
       </c>
       <c r="F88" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="G88" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="G88" s="10" t="s">
+      <c r="H88" s="18" t="s">
         <v>130</v>
-      </c>
-      <c r="H88" s="18" t="s">
-        <v>131</v>
       </c>
       <c r="I88" s="12"/>
       <c r="J88" s="12"/>
@@ -4410,13 +4403,13 @@
         <v>4055303</v>
       </c>
       <c r="F89" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H89" s="18" t="s">
         <v>132</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="H89" s="18" t="s">
-        <v>133</v>
       </c>
       <c r="I89" s="12"/>
       <c r="J89" s="12"/>
@@ -4440,13 +4433,13 @@
         <v>4055341</v>
       </c>
       <c r="F90" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G90" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G90" s="11" t="s">
+      <c r="H90" s="18" t="s">
         <v>135</v>
-      </c>
-      <c r="H90" s="18" t="s">
-        <v>136</v>
       </c>
       <c r="J90" s="35"/>
       <c r="K90" s="35"/>
@@ -4469,13 +4462,13 @@
         <v>4055342</v>
       </c>
       <c r="F91" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H91" s="18" t="s">
         <v>137</v>
-      </c>
-      <c r="G91" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="H91" s="18" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:12">
@@ -4495,13 +4488,13 @@
         <v>4055343</v>
       </c>
       <c r="F92" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="G92" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H92" s="18" t="s">
         <v>139</v>
-      </c>
-      <c r="G92" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="H92" s="18" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="93" s="10" customFormat="1" customHeight="1" spans="1:12">
@@ -4521,13 +4514,13 @@
         <v>4055344</v>
       </c>
       <c r="F93" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="G93" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="H93" s="18" t="s">
         <v>141</v>
-      </c>
-      <c r="G93" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H93" s="18" t="s">
-        <v>142</v>
       </c>
       <c r="I93" s="12"/>
       <c r="J93" s="12"/>
@@ -4551,13 +4544,13 @@
         <v>4055345</v>
       </c>
       <c r="F94" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="G94" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="H94" s="18" t="s">
         <v>143</v>
-      </c>
-      <c r="G94" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H94" s="18" t="s">
-        <v>144</v>
       </c>
       <c r="I94" s="12"/>
       <c r="J94" s="12"/>
@@ -4581,13 +4574,13 @@
         <v>4055346</v>
       </c>
       <c r="F95" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="G95" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="H95" s="18" t="s">
         <v>145</v>
-      </c>
-      <c r="G95" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H95" s="18" t="s">
-        <v>146</v>
       </c>
       <c r="I95" s="12"/>
       <c r="J95" s="12"/>
@@ -4611,13 +4604,13 @@
         <v>4055347</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="G96" s="28" t="s">
-        <v>135</v>
+        <v>146</v>
+      </c>
+      <c r="G96" s="29" t="s">
+        <v>134</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I96" s="12"/>
       <c r="J96" s="12"/>
@@ -4641,13 +4634,13 @@
         <v>4055348</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="G97" s="28" t="s">
-        <v>135</v>
+        <v>147</v>
+      </c>
+      <c r="G97" s="29" t="s">
+        <v>134</v>
       </c>
       <c r="H97" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I97" s="12"/>
       <c r="J97" s="12"/>
@@ -4669,10 +4662,10 @@
       </c>
       <c r="E98" s="25"/>
       <c r="F98" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="G98" s="28" t="s">
-        <v>135</v>
+        <v>148</v>
+      </c>
+      <c r="G98" s="29" t="s">
+        <v>134</v>
       </c>
       <c r="H98" s="18"/>
       <c r="I98" s="12"/>
@@ -4697,13 +4690,13 @@
         <v>4055350</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="G99" s="28" t="s">
-        <v>135</v>
+        <v>149</v>
+      </c>
+      <c r="G99" s="29" t="s">
+        <v>134</v>
       </c>
       <c r="H99" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J99" s="12"/>
       <c r="K99" s="12"/>
@@ -4726,15 +4719,15 @@
         <v>4055356</v>
       </c>
       <c r="F100" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="G100" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="H100" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="G100" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H100" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="I100" s="9"/>
+      <c r="I100" s="8"/>
       <c r="J100" s="12"/>
       <c r="K100" s="12"/>
       <c r="L100" s="12"/>
@@ -4756,13 +4749,13 @@
         <v>4055351</v>
       </c>
       <c r="F101" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="G101" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="H101" s="18" t="s">
         <v>153</v>
-      </c>
-      <c r="G101" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H101" s="18" t="s">
-        <v>154</v>
       </c>
       <c r="I101" s="12"/>
       <c r="J101" s="12"/>
@@ -4786,13 +4779,13 @@
         <v>4055352</v>
       </c>
       <c r="F102" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="G102" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="H102" s="18" t="s">
         <v>155</v>
-      </c>
-      <c r="G102" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="H102" s="18" t="s">
-        <v>156</v>
       </c>
       <c r="J102" s="12"/>
       <c r="K102" s="12"/>
@@ -4813,10 +4806,10 @@
       </c>
       <c r="E103" s="25"/>
       <c r="F103" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="G103" s="28" t="s">
-        <v>135</v>
+        <v>156</v>
+      </c>
+      <c r="G103" s="29" t="s">
+        <v>134</v>
       </c>
       <c r="H103" s="18"/>
       <c r="I103" s="12"/>
@@ -4839,10 +4832,10 @@
       </c>
       <c r="E104" s="25"/>
       <c r="F104" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G104" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H104" s="18"/>
     </row>
@@ -4863,13 +4856,13 @@
         <v>4055355</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H105" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="1:12">
@@ -4889,13 +4882,13 @@
         <v>4055357</v>
       </c>
       <c r="F106" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="G106" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H106" s="18" t="s">
         <v>160</v>
-      </c>
-      <c r="G106" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="H106" s="18" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:12">
@@ -4911,10 +4904,10 @@
       </c>
       <c r="E107" s="17"/>
       <c r="F107" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="G107" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="H107" s="18"/>
     </row>
@@ -4933,10 +4926,10 @@
       </c>
       <c r="E108" s="17"/>
       <c r="F108" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H108" s="18"/>
     </row>
@@ -4957,13 +4950,13 @@
         <v>4055371</v>
       </c>
       <c r="F109" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H109" s="18" t="s">
         <v>165</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="H109" s="18" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:12">
@@ -4983,13 +4976,13 @@
         <v>4055372</v>
       </c>
       <c r="F110" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G110" s="1" t="s">
+      <c r="H110" s="12" t="s">
         <v>168</v>
-      </c>
-      <c r="H110" s="12" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:12">
@@ -5009,13 +5002,13 @@
         <v>4055373</v>
       </c>
       <c r="F111" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H111" s="12" t="s">
         <v>170</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="H111" s="12" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:12">
@@ -5035,13 +5028,13 @@
         <v>4055374</v>
       </c>
       <c r="F112" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H112" s="12" t="s">
         <v>172</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="H112" s="12" t="s">
-        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -5102,14 +5095,14 @@
         <v>2201</v>
       </c>
       <c r="J5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K5" t="str">
         <f>I5&amp;J5</f>
         <v>2201_</v>
       </c>
       <c r="M5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N5" t="str">
         <f ca="1">PHONETIC(M5:M27)</f>
@@ -5118,7 +5111,7 @@
     </row>
     <row r="6" ht="15" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -5128,14 +5121,14 @@
         <v>2202</v>
       </c>
       <c r="J6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="0">I6&amp;J6</f>
         <v>2202_</v>
       </c>
       <c r="M6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -5143,14 +5136,14 @@
         <v>2203</v>
       </c>
       <c r="J7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="0"/>
         <v>2203_</v>
       </c>
       <c r="M7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -5158,14 +5151,14 @@
         <v>2204</v>
       </c>
       <c r="J8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="0"/>
         <v>2204_</v>
       </c>
       <c r="M8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -5173,14 +5166,14 @@
         <v>2205</v>
       </c>
       <c r="J9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" ref="K9:K18" si="1">I9&amp;J9</f>
         <v>2205_</v>
       </c>
       <c r="M9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -5188,14 +5181,14 @@
         <v>2206</v>
       </c>
       <c r="J10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
         <v>2206_</v>
       </c>
       <c r="M10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -5203,14 +5196,14 @@
         <v>2207</v>
       </c>
       <c r="J11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
         <v>2207_</v>
       </c>
       <c r="M11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -5218,14 +5211,14 @@
         <v>2208</v>
       </c>
       <c r="J12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
         <v>2208_</v>
       </c>
       <c r="M12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -5233,32 +5226,32 @@
         <v>2209</v>
       </c>
       <c r="J13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
         <v>2209_</v>
       </c>
       <c r="M13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I14">
         <v>2210</v>
       </c>
       <c r="J14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
         <v>2210_</v>
       </c>
       <c r="M14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -5266,14 +5259,14 @@
         <v>2211</v>
       </c>
       <c r="J15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
         <v>2211_</v>
       </c>
       <c r="M15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -5281,14 +5274,14 @@
         <v>2212</v>
       </c>
       <c r="J16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
         <v>2212_</v>
       </c>
       <c r="M16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -5296,14 +5289,14 @@
         <v>2213</v>
       </c>
       <c r="J17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
         <v>2213_</v>
       </c>
       <c r="M17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -5311,29 +5304,29 @@
         <v>2214</v>
       </c>
       <c r="J18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
         <v>2214_</v>
       </c>
       <c r="M18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GuideDetails.xlsx
+++ b/hall/resources/sample/GuideDetails.xlsx
@@ -285,7 +285,7 @@
     <t>1009.mp3</t>
   </si>
   <si>
-    <t>开始经营娱乐城</t>
+    <t>好，让我们开始吧！</t>
   </si>
   <si>
     <t>1010.mp3</t>
